--- a/docs/iFare_UI_UX_問題追蹤清單.xlsx
+++ b/docs/iFare_UI_UX_問題追蹤清單.xlsx
@@ -3,13 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99220D51-A23C-4AC4-B661-931AAA167D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE0FED28-66D4-44BB-A846-FB73BA07E4A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="問題追蹤清單" sheetId="1" r:id="rId1"/>
-    <sheet name="統計摘要" sheetId="2" r:id="rId2"/>
+    <sheet name="PoC研究" sheetId="4" r:id="rId1"/>
+    <sheet name="後臺優化" sheetId="3" r:id="rId2"/>
+    <sheet name="UIUX問題追蹤清單" sheetId="1" r:id="rId3"/>
+    <sheet name="統計摘要" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
   <extLst>
@@ -21,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1679" uniqueCount="659">
   <si>
     <t>iFare 前台網站 UI/UX 問題追蹤清單（已驗證）</t>
   </si>
@@ -1428,6 +1430,668 @@
   </si>
   <si>
     <t>優先級分布</t>
+  </si>
+  <si>
+    <t>SEO</t>
+  </si>
+  <si>
+    <t>各頁 SEO meta 可能未完整結構化管理</t>
+  </si>
+  <si>
+    <t>目前清單僅列 sitemap lastmod，尚未明確盤點各頁 title、meta description、OG、canonical 與動態詳情頁 meta 是否完整。</t>
+  </si>
+  <si>
+    <t>建立全站 SEO 檢查表，優先檢查首頁、news、articles、ifare 相關頁的 title / description / OG / canonical。</t>
+  </si>
+  <si>
+    <t>layouts/default.vue nuxt.config.ts pages/news/*.vue pages/articles/*.vue pages/ifare*.vue</t>
+  </si>
+  <si>
+    <t>屬於 sitemap 之外的 SEO 基礎建設，現有清單未明列。</t>
+  </si>
+  <si>
+    <t>搜尋表單 label 與錯誤訊息缺少語意關聯</t>
+  </si>
+  <si>
+    <t>目前已列必填錯誤提示與 Select/FAQ ARIA，但尚未明確檢查 label、aria-describedby、aria-invalid、aria-required 等表單可及性關聯。</t>
+  </si>
+  <si>
+    <t>補齊 label-for / id 對應，錯誤訊息綁定 aria-describedby，錯誤欄位加 aria-invalid，必填欄位加 aria-required。</t>
+  </si>
+  <si>
+    <t>pages/ifare.vue components/CompSelect*.vue</t>
+  </si>
+  <si>
+    <t>屬於表單完整可及性規格，現有清單未獨立列出。</t>
+  </si>
+  <si>
+    <t>缺少載入失敗與重試機制</t>
+  </si>
+  <si>
+    <t>目前清單有 loading / skeleton / toast，但尚未明確區分 API 載入失敗狀態與重試機制。</t>
+  </si>
+  <si>
+    <t>建立統一錯誤狀態元件，針對 API 失敗提供錯誤訊息、retry 按鈕，並區分空資料與載入失敗。</t>
+  </si>
+  <si>
+    <t>pages/news.vue pages/articles.vue pages/collaborator.vue pages/ifare/result.vue layouts/default.vue components/</t>
+  </si>
+  <si>
+    <t>現有清單多著重 loading 與空狀態，未明列 error state。</t>
+  </si>
+  <si>
+    <t>轉換</t>
+  </si>
+  <si>
+    <t>首頁主 CTA 與轉換路徑不夠明確</t>
+  </si>
+  <si>
+    <t>目前有 Hero 動畫、影響力數字、LINE 推廣等項目，但未明確盤點首頁主要行動目標與 CTA 層級是否清楚。</t>
+  </si>
+  <si>
+    <t>重新檢視首頁 Hero 主按鈕與次按鈕文案、位置與層級，強化 i-Fare 入口與關鍵導流。</t>
+  </si>
+  <si>
+    <t>pages/index.vue assets/style/components/_appBody_index.scss</t>
+  </si>
+  <si>
+    <t>屬於轉換導向優化，現有清單偏視覺呈現，未獨立列 CTA 策略。</t>
+  </si>
+  <si>
+    <t>404 / 500 頁面導引體驗可補強</t>
+  </si>
+  <si>
+    <t>目前清單未涵蓋找不到頁面與系統錯誤頁的使用者導引體驗。</t>
+  </si>
+  <si>
+    <t>建立自訂 404 / 500 頁，提供返回首頁、熱門內容、i-Fare 入口與必要聯絡資訊。</t>
+  </si>
+  <si>
+    <t>error pages</t>
+  </si>
+  <si>
+    <t>error.vue app.vue pages/index.vue</t>
+  </si>
+  <si>
+    <t>現有清單未包含錯誤頁體驗。</t>
+  </si>
+  <si>
+    <t>全站圖片 alt 與裝飾圖語意規則未統一</t>
+  </si>
+  <si>
+    <t>目前僅針對公益夥伴 logo 缺 alt 有列出，尚未全站盤點資訊型圖片與裝飾型圖片的替代文字規則。</t>
+  </si>
+  <si>
+    <t>建立圖片語意規範，資訊型圖片補 alt，裝飾型圖片使用空 alt 或 aria-hidden，避免檔名式描述。</t>
+  </si>
+  <si>
+    <t>pages/index.vue pages/news*.vue pages/articles*.vue pages/collaborator.vue pages/about.vue components/</t>
+  </si>
+  <si>
+    <t>屬於全站無障礙規範，現有清單只有單點檢查。</t>
+  </si>
+  <si>
+    <t>缺少 schema.org 結構化資料標記</t>
+  </si>
+  <si>
+    <t>目前清單僅涵蓋 sitemap，尚未列出 Organization、Article、NewsArticle、BreadcrumbList 等結構化資料。</t>
+  </si>
+  <si>
+    <t>針對首頁、文章頁、新聞頁與麵包屑補 JSON-LD schema，提升搜尋引擎理解。</t>
+  </si>
+  <si>
+    <t>layouts/default.vue pages/index.vue pages/news/*.vue pages/articles/*.vue components/CompBreadCrumb.vue</t>
+  </si>
+  <si>
+    <t>屬於 SEO 進階補強，現有清單未列。</t>
+  </si>
+  <si>
+    <t>首屏字型與大圖載入效能可再優化</t>
+  </si>
+  <si>
+    <t>目前雖有圖片 lazy load 與動畫效能項目，但尚未明確盤點 webfont 載入策略與首頁 Hero 圖 LCP 優化。</t>
+  </si>
+  <si>
+    <t>檢查 font-display、字型 preload、Hero 圖壓縮與 preload，並以 Lighthouse 驗證 LCP / CLS / INP。</t>
+  </si>
+  <si>
+    <t>nuxt.config.ts assets/style/ pages/index.vue public/</t>
+  </si>
+  <si>
+    <t>屬於首屏效能盤點，現有清單未明確拆出。</t>
+  </si>
+  <si>
+    <t>搜尋結果 / 列表頁</t>
+  </si>
+  <si>
+    <t>空狀態缺少下一步引導</t>
+  </si>
+  <si>
+    <t>目前清單有 loading 與部分空狀態，但未獨立處理「查無結果」時如何引導使用者調整條件或前往其他內容。</t>
+  </si>
+  <si>
+    <t>針對查無結果、無資料、載入失敗三種情境分開設計文案與 CTA，例如重設條件、返回熱門分類、聯絡我們。</t>
+  </si>
+  <si>
+    <t>pages/ifare/result.vue pages/news.vue pages/articles.vue pages/collaborator.vue</t>
+  </si>
+  <si>
+    <t>pages/ifare/result.vue pages/news.vue pages/articles.vue pages/collaborator.vue assets/style/components/_appBody.scss</t>
+  </si>
+  <si>
+    <t>屬於空狀態 UX 細化，現有清單未完整區分情境。</t>
+  </si>
+  <si>
+    <t>FAQ 手風琴缺少完整鍵盤操作</t>
+  </si>
+  <si>
+    <t>目前已列 FAQ 缺 ARIA 狀態，但尚未明確檢查是否可用 Tab、Enter、Space 操作，以及 focus 樣式是否清楚。</t>
+  </si>
+  <si>
+    <t>將 FAQ 手風琴補齊為完整可及性元件，支援鍵盤操作、focus 樣式與狀態提示。</t>
+  </si>
+  <si>
+    <t>pages/ifare.vue assets/style/components/_appBody_ifare.scss</t>
+  </si>
+  <si>
+    <t>屬於 FAQ 元件更完整的無障礙要求，超出單純 aria-expanded。</t>
+  </si>
+  <si>
+    <t>iFare 後台優化清單（程式碼初判）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CRUD 架構</t>
+  </si>
+  <si>
+    <t>維護性</t>
+  </si>
+  <si>
+    <t>各模組 CRUD 頁型高度重複，缺少更高層級共用模板</t>
+  </si>
+  <si>
+    <t>目前多數模組都採 Index / DataList / AddEdit / Detail 結構，代表畫面模式相近，但若各自維護，後續改版與擴充成本會持續升高。</t>
+  </si>
+  <si>
+    <t>建立統一 CRUD 頁面模板，將列表、查詢、表單、詳情頁的共用結構抽象化。</t>
+  </si>
+  <si>
+    <t>src/views/</t>
+  </si>
+  <si>
+    <t>src/views/** src/components/CardTable.vue src/components/CardSearchParam.vue src/components/MainHeader.vue</t>
+  </si>
+  <si>
+    <t>從路由與 views 結構可明顯看出模組高度一致。</t>
+  </si>
+  <si>
+    <t>最新消息維護</t>
+  </si>
+  <si>
+    <t>列表頁</t>
+  </si>
+  <si>
+    <t>查詢與列表互動模式需統一</t>
+  </si>
+  <si>
+    <t>News_DataListView 透過 watch 搜尋條件後重新打 API，若各模組各自實作，容易出現查詢送出時機、重設方式、結果呈現不一致。</t>
+  </si>
+  <si>
+    <t>統一 DataList 頁查詢流程，明確定義即時查詢、手動查詢、重設條件、查詢結果數量與空狀態規則。</t>
+  </si>
+  <si>
+    <t>src/views/News/News_DataListView.vue</t>
+  </si>
+  <si>
+    <t>src/views/**/**_DataListView.vue src/components/CardSearchParam.vue src/components/CardTable.vue</t>
+  </si>
+  <si>
+    <t>News 列表頁已可看出查詢條件與 route query/watch 綁定。</t>
+  </si>
+  <si>
+    <t>後台通用</t>
+  </si>
+  <si>
+    <t>列表頁 / 表單頁</t>
+  </si>
+  <si>
+    <t>缺少一致的載入中、成功、失敗回饋機制</t>
+  </si>
+  <si>
+    <t>目前 ajax() 成功失敗主要回傳給頁面自行處理，401 才做統一導頁，其他操作回饋可能分散且不一致。</t>
+  </si>
+  <si>
+    <t>建立全站一致的 loading、成功 toast、失敗 toast / dialog、重試提示與送出中按鈕狀態。</t>
+  </si>
+  <si>
+    <t>src/plugins/WebAPI.ts</t>
+  </si>
+  <si>
+    <t>src/plugins/WebAPI.ts src/components/DialogAlert.vue src/components/DialogErrorInfo.vue src/views/**</t>
+  </si>
+  <si>
+    <t>從 ajax 封裝可看出共通回饋層尚未完整標準化。</t>
+  </si>
+  <si>
+    <t>i-Fare 維護</t>
+  </si>
+  <si>
+    <t>福利政策維護</t>
+  </si>
+  <si>
+    <t>福利政策表單欄位多且資訊密度高，輸入負擔大</t>
+  </si>
+  <si>
+    <t>IFarePolicy_AddEditView 含大量分類、多選、文字區塊、上架設定與洽辦資料，編輯負擔高，也容易發生漏填或錯填。</t>
+  </si>
+  <si>
+    <t>將福利政策表單重構為分區式介面，清楚分成基本資料、適用條件、福利內容、洽辦資訊、發布設定與備註。</t>
+  </si>
+  <si>
+    <t>src/views/IFare/Policy/IFarePolicy_AddEditView.vue</t>
+  </si>
+  <si>
+    <t>src/views/IFare/Policy/IFarePolicy_AddEditView.vue src/components/CompHtmlEditor.vue</t>
+  </si>
+  <si>
+    <t>從畫面程式碼可直接看出表單欄位量大且層次複雜。</t>
+  </si>
+  <si>
+    <t>大型表單缺少更完整的填寫輔助與錯誤導引</t>
+  </si>
+  <si>
+    <t>目前雖有 required 標示，但尚未看出完整的分段驗證、錯誤定位、草稿保存或儲存前摘要確認。</t>
+  </si>
+  <si>
+    <t>補齊大型表單 UX，加入分段驗證、錯誤欄位定位、草稿暫存、儲存前確認摘要與常用欄位預設值。</t>
+  </si>
+  <si>
+    <t>src/views/IFare/Policy/IFarePolicy_AddEditView.vue src/stores/ src/components/</t>
+  </si>
+  <si>
+    <t>屬於大型表單常見優化點，對維護效率影響很大。</t>
+  </si>
+  <si>
+    <t>帳戶維護 / 全站權限</t>
+  </si>
+  <si>
+    <t>路由與權限</t>
+  </si>
+  <si>
+    <t>權限控管邏輯以路由字串硬判斷，維護性較差</t>
+  </si>
+  <si>
+    <t>router.beforeEach 透過路由名稱字串逐一比對「檢視者」可進頁面與管理者限定頁面，新增模組時容易漏改。</t>
+  </si>
+  <si>
+    <t>改為以 route meta 或權限設定表驅動的權限模型，統一控管 menu、route、頁面操作按鈕。</t>
+  </si>
+  <si>
+    <t>src/router/index.ts</t>
+  </si>
+  <si>
+    <t>src/router/index.ts src/data/AsideMenu.json src/stores/user.ts</t>
+  </si>
+  <si>
+    <t>目前權限判斷集中在 beforeEach 的字串條件。</t>
+  </si>
+  <si>
+    <t>API 呼叫層</t>
+  </si>
+  <si>
+    <t>WebAPI.ts 過大且所有 API 集中在單一檔案，模組界線不清</t>
+  </si>
+  <si>
+    <t>目前所有模組 API 都掛在同一個全域 $WebAPI 物件，隨模組增加，型別、測試與維護難度都會上升。</t>
+  </si>
+  <si>
+    <t>依模組拆分 API service，例如 news.api、ifare.api、account.api，再抽出共用 request / auth / error handler。</t>
+  </si>
+  <si>
+    <t>src/plugins/WebAPI.ts src/plugins/AjaxRef.ts src/views/**</t>
+  </si>
+  <si>
+    <t>目前 WebAPI.ts 已非常長，且涵蓋全部後台功能。</t>
+  </si>
+  <si>
+    <t>開發與正式 API 位址寫死於 AjaxRef，環境切換風險高</t>
+  </si>
+  <si>
+    <t>AjaxRef.getBaseUrl() 直接回傳 localhost 與固定內網位址，若環境增加或部署調整，修改成本與出錯風險都偏高。</t>
+  </si>
+  <si>
+    <t>改為使用環境變數管理 API baseURL，區分 local / staging / production，避免直接硬編碼。</t>
+  </si>
+  <si>
+    <t>src/plugins/AjaxRef.ts</t>
+  </si>
+  <si>
+    <t>src/plugins/AjaxRef.ts .env* vite.config.*</t>
+  </si>
+  <si>
+    <t>目前 baseURL 明確硬寫在程式中。</t>
+  </si>
+  <si>
+    <t>資料狀態管理</t>
+  </si>
+  <si>
+    <t>登入與使用者狀態管理可再補強 token 生命週期處理</t>
+  </si>
+  <si>
+    <t>user store 有保存 token 與預估到期時間，但從現有結構看，前端主要依 token 是否存在判斷登入狀態。</t>
+  </si>
+  <si>
+    <t>補上 token 即將過期提醒、主動 refresh 或重新登入策略，並統一處理登出後清理流程。</t>
+  </si>
+  <si>
+    <t>src/stores/user.ts</t>
+  </si>
+  <si>
+    <t>src/stores/user.ts src/plugins/WebAPI.ts src/router/index.ts</t>
+  </si>
+  <si>
+    <t>目前有 tokenExpiredTime，但使用策略仍可加強。</t>
+  </si>
+  <si>
+    <t>元件系統</t>
+  </si>
+  <si>
+    <t>共用元件已有基礎，但仍可建立更明確的後台設計規格</t>
+  </si>
+  <si>
+    <t>目前已有 CardSearchParam、CardTable、MainHeader、各式輸入元件與 dialog，代表系統已進入可標準化階段。</t>
+  </si>
+  <si>
+    <t>整理後台元件使用規範，統一搜尋卡、表格卡、表單欄位、dialog、按鈕群與標題列樣式。</t>
+  </si>
+  <si>
+    <t>src/components/</t>
+  </si>
+  <si>
+    <t>src/components/** src/views/** assets/**</t>
+  </si>
+  <si>
+    <t>目前已有不錯的共用元件基礎，適合往設計系統推進。</t>
+  </si>
+  <si>
+    <t>圖片管理</t>
+  </si>
+  <si>
+    <t>圖片管理可補強媒體資產操作體驗</t>
+  </si>
+  <si>
+    <t>系統已有獨立 ImgManager 與 DialogAddEditImg，代表媒體管理已獨立成模組，但通常還可補搜尋、預覽、複製連結、使用處追蹤等能力。</t>
+  </si>
+  <si>
+    <t>優化圖片管理流程，補齊即時預覽、尺寸/格式資訊、複製路徑、使用位置資訊與替換流程。</t>
+  </si>
+  <si>
+    <t>src/views/ImgManager/ImgManager_DataListView.vue</t>
+  </si>
+  <si>
+    <t>src/views/ImgManager/ImgManager_DataListView.vue src/components/DialogAddEditImg.vue src/plugins/WebAPI.ts</t>
+  </si>
+  <si>
+    <t>已有獨立圖片模組，適合往資產管理方向深化。</t>
+  </si>
+  <si>
+    <t>文件與交接</t>
+  </si>
+  <si>
+    <t>後台模組雖完整，但缺少程式結構對照型文件會增加交接成本</t>
+  </si>
+  <si>
+    <t>從程式碼看得出後台模組規律很明確，若沒有頁面、API、權限、資料流對照文件，新人仍需花很多時間自行反推。</t>
+  </si>
+  <si>
+    <t>補一份後台結構對照文件，整理模組、路由、API、角色權限、共用元件與主要資料流。</t>
+  </si>
+  <si>
+    <t>src/router/index.ts src/data/AsideMenu.json src/plugins/WebAPI.ts</t>
+  </si>
+  <si>
+    <t>docs/ 新增後台功能與結構對照文件</t>
+  </si>
+  <si>
+    <t>這項不是 UI 問題，但對後續維護與提案落地很重要。</t>
+  </si>
+  <si>
+    <t>iFare 新功能 PoC（概念驗證）研究方向</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>搜尋優化</t>
+  </si>
+  <si>
+    <t>PoC</t>
+  </si>
+  <si>
+    <t>搜尋條件非必填化與漸進式引導</t>
+  </si>
+  <si>
+    <t>目前福利搜尋條件多，使用者可能因欄位要求或不確定如何選擇而中斷查詢。可先驗證「先輸入再逐步補條件」是否更順。</t>
+  </si>
+  <si>
+    <t>以前台搜尋為基礎，設計非必填查詢、逐步補條件與查無結果再引導補條件的 PoC。</t>
+  </si>
+  <si>
+    <t>pages/ifare.vue pages/ifare/result.vue</t>
+  </si>
+  <si>
+    <t>pages/ifare.vue pages/ifare/result.vue components/CompSelect*.vue</t>
+  </si>
+  <si>
+    <t>適合做前台體驗型 PoC，與核心業務高度相關。</t>
+  </si>
+  <si>
+    <t>智慧搜尋</t>
+  </si>
+  <si>
+    <t>自然語句轉搜尋條件</t>
+  </si>
+  <si>
+    <t>使用者可直接輸入「我是單親媽媽、低收入戶，可以申請什麼」這類需求，再轉換成既有搜尋條件，降低理解門檻。</t>
+  </si>
+  <si>
+    <t>設計自然語句輸入框，將句子拆解為受助者、經濟條件、特殊身分、地區等既有條件，最後導向既有查詢結果。</t>
+  </si>
+  <si>
+    <t>pages/ifare.vue pages/ifare/result.vue docs/</t>
+  </si>
+  <si>
+    <t>概念亮點高，適合做展示型 PoC。</t>
+  </si>
+  <si>
+    <t>熱門搜尋與最近搜尋</t>
+  </si>
+  <si>
+    <t>重複查詢情境下，使用者每次都要重選條件，體驗成本高。</t>
+  </si>
+  <si>
+    <t>以 localStorage 建立熱門搜尋與最近搜尋紀錄，驗證是否能提升查詢效率與回訪便利性。</t>
+  </si>
+  <si>
+    <t>實作難度相對低，適合快速驗證。</t>
+  </si>
+  <si>
+    <t>搜尋結果</t>
+  </si>
+  <si>
+    <t>查無結果時推薦相近政策</t>
+  </si>
+  <si>
+    <t>若使用者沒有查到結果，直接顯示空狀態容易中斷流程，可驗證推薦相近政策是否能提升任務完成率。</t>
+  </si>
+  <si>
+    <t>在查無結果時，根據已選條件或關鍵字推薦相近政策、熱門分類或常見 FAQ。</t>
+  </si>
+  <si>
+    <t>pages/ifare/result.vue pages/ifare/info.vue pages/ifare.vue</t>
+  </si>
+  <si>
+    <t>適合與搜尋優化一起做成一組 PoC。</t>
+  </si>
+  <si>
+    <t>個人化功能</t>
+  </si>
+  <si>
+    <t>收藏、已讀與最近瀏覽功能</t>
+  </si>
+  <si>
+    <t>使用者在比較多項福利政策時，缺少整理工具會增加決策負擔。</t>
+  </si>
+  <si>
+    <t>以 localStorage 建立收藏、已讀與最近瀏覽功能，驗證是否有助於重複查閱與政策比較。</t>
+  </si>
+  <si>
+    <t>pages/ifare/result.vue pages/ifare/info.vue</t>
+  </si>
+  <si>
+    <t>屬於低風險、容易展示的個人化功能 PoC。</t>
+  </si>
+  <si>
+    <t>後台優化</t>
+  </si>
+  <si>
+    <t>大型表單分段式編輯</t>
+  </si>
+  <si>
+    <t>福利政策維護欄位多且資訊密度高，適合先做一版分段式表單驗證操作效率。</t>
+  </si>
+  <si>
+    <t>將福利政策新增/編輯頁拆成多步驟或分區卡片，驗證是否能降低填寫錯誤與編輯負擔。</t>
+  </si>
+  <si>
+    <t>src/views/IFare/Policy/IFarePolicy_AddEditView.vue src/components/</t>
+  </si>
+  <si>
+    <t>這是最值得優先做的後台效率型 PoC 之一。</t>
+  </si>
+  <si>
+    <t>草稿暫存與續編功能</t>
+  </si>
+  <si>
+    <t>大型表單若中斷輸入，重新填寫成本高，可驗證草稿機制是否有實際價值。</t>
+  </si>
+  <si>
+    <t>在新增/編輯福利政策時加入草稿暫存、離開提醒與續編功能。</t>
+  </si>
+  <si>
+    <t>src/views/IFare/Policy/IFarePolicy_AddEditView.vue src/stores/</t>
+  </si>
+  <si>
+    <t>適合搭配大型表單優化一起驗證。</t>
+  </si>
+  <si>
+    <t>共用元件 / 架構</t>
+  </si>
+  <si>
+    <t>CRUD 模板化 PoC</t>
+  </si>
+  <si>
+    <t>後台多數模組都採相似 CRUD 結構，可驗證抽出模板後是否能降低新增模組成本。</t>
+  </si>
+  <si>
+    <t>挑選 1 至 2 個模組，抽象化列表、查詢、表單、詳情頁結構，建立共用 CRUD 頁面模板。</t>
+  </si>
+  <si>
+    <t>src/views/ src/components/</t>
+  </si>
+  <si>
+    <t>src/views/** src/components/CardTable.vue src/components/CardSearchParam.vue</t>
+  </si>
+  <si>
+    <t>工程價值高，適合作為內部效率型 PoC。</t>
+  </si>
+  <si>
+    <t>權限管理</t>
+  </si>
+  <si>
+    <t>權限設定表化</t>
+  </si>
+  <si>
+    <t>目前權限較偏硬寫，可先驗證以設定表控制 route / menu / button 是否可行。</t>
+  </si>
+  <si>
+    <t>建立一版權限設定表，讓 route、側欄與操作按鈕依角色自動控制顯示與可用性。</t>
+  </si>
+  <si>
+    <t>src/router/index.ts src/data/AsideMenu.json</t>
+  </si>
+  <si>
+    <t>適合做工程與管理並重的 PoC。</t>
+  </si>
+  <si>
+    <t>資料分析</t>
+  </si>
+  <si>
+    <t>Dashboard</t>
+  </si>
+  <si>
+    <t>搜尋行為與熱門內容分析</t>
+  </si>
+  <si>
+    <t>若能知道最常查詢的條件、最常無結果的組合與熱門政策，可作為產品優化依據。</t>
+  </si>
+  <si>
+    <t>擴充 Analysis 模組，新增熱門搜尋條件、查無結果統計、熱門政策 / 文章等儀表板指標。</t>
+  </si>
+  <si>
+    <t>src/views/Analysis/Analysis_DashboardView.vue</t>
+  </si>
+  <si>
+    <t>src/views/Analysis/Analysis_DashboardView.vue src/plugins/WebAPI.ts</t>
+  </si>
+  <si>
+    <t>這類 PoC 可直接支援後續產品決策。</t>
+  </si>
+  <si>
+    <t>內容體驗</t>
+  </si>
+  <si>
+    <t>推薦機制</t>
+  </si>
+  <si>
+    <t>內容與政策互相推薦</t>
+  </si>
+  <si>
+    <t>文章、FAQ、福利政策若能互相導流，可提升內容探索與停留時間。</t>
+  </si>
+  <si>
+    <t>在文章詳情頁推薦相關政策，在政策詳情頁推薦相關文章、FAQ 或洽辦單位。</t>
+  </si>
+  <si>
+    <t>pages/articles/*.vue pages/ifare/info.vue</t>
+  </si>
+  <si>
+    <t>pages/articles/*.vue pages/ifare/info.vue pages/news/info.vue</t>
+  </si>
+  <si>
+    <t>適合做內容型平台的延伸 PoC。</t>
+  </si>
+  <si>
+    <t>文件 / 內部工具</t>
+  </si>
+  <si>
+    <t>文件輔助</t>
+  </si>
+  <si>
+    <t>頁面、API、資料表對照工具</t>
+  </si>
+  <si>
+    <t>目前專案文件逐步補齊中，可驗證是否能半自動整理頁面、API、資料表對照資訊。</t>
+  </si>
+  <si>
+    <t>從程式碼與文件中整理頁面對 API、API 對資料表的對照關係，做成內部查閱工具或文件模板。</t>
+  </si>
+  <si>
+    <t>docs/ src/plugins/WebAPI.ts src/router/index.ts</t>
+  </si>
+  <si>
+    <t>docs/ src/plugins/WebAPI.ts src/router/index.ts src/views/</t>
+  </si>
+  <si>
+    <t>雖不是前台功能，但很適合作為內部效率型 PoC。</t>
   </si>
 </sst>
 </file>
@@ -1901,8 +2565,1265 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EACBC819-DBD2-4C29-9C07-6E1719A9513F}">
+  <dimension ref="A1:P14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="35.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="135.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="122.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="51.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="80" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="55" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="18">
+      <c r="A1" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+    </row>
+    <row r="2" spans="1:16" ht="24" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>581</v>
+      </c>
+      <c r="E3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" t="s">
+        <v>582</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
+        <v>583</v>
+      </c>
+      <c r="I3" t="s">
+        <v>584</v>
+      </c>
+      <c r="J3" t="s">
+        <v>585</v>
+      </c>
+      <c r="K3" t="s">
+        <v>586</v>
+      </c>
+      <c r="L3" t="s">
+        <v>587</v>
+      </c>
+      <c r="M3" t="s">
+        <v>588</v>
+      </c>
+      <c r="N3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>589</v>
+      </c>
+      <c r="E4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" t="s">
+        <v>582</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" t="s">
+        <v>590</v>
+      </c>
+      <c r="I4" t="s">
+        <v>591</v>
+      </c>
+      <c r="J4" t="s">
+        <v>592</v>
+      </c>
+      <c r="K4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" t="s">
+        <v>593</v>
+      </c>
+      <c r="M4" t="s">
+        <v>594</v>
+      </c>
+      <c r="N4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>581</v>
+      </c>
+      <c r="E5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" t="s">
+        <v>582</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" t="s">
+        <v>595</v>
+      </c>
+      <c r="I5" t="s">
+        <v>596</v>
+      </c>
+      <c r="J5" t="s">
+        <v>597</v>
+      </c>
+      <c r="K5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" t="s">
+        <v>586</v>
+      </c>
+      <c r="M5" t="s">
+        <v>598</v>
+      </c>
+      <c r="N5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>599</v>
+      </c>
+      <c r="E6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" t="s">
+        <v>582</v>
+      </c>
+      <c r="G6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" t="s">
+        <v>600</v>
+      </c>
+      <c r="I6" t="s">
+        <v>601</v>
+      </c>
+      <c r="J6" t="s">
+        <v>602</v>
+      </c>
+      <c r="K6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L6" t="s">
+        <v>603</v>
+      </c>
+      <c r="M6" t="s">
+        <v>604</v>
+      </c>
+      <c r="N6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>605</v>
+      </c>
+      <c r="E7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" t="s">
+        <v>582</v>
+      </c>
+      <c r="G7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" t="s">
+        <v>606</v>
+      </c>
+      <c r="I7" t="s">
+        <v>607</v>
+      </c>
+      <c r="J7" t="s">
+        <v>608</v>
+      </c>
+      <c r="K7" t="s">
+        <v>609</v>
+      </c>
+      <c r="L7" t="s">
+        <v>609</v>
+      </c>
+      <c r="M7" t="s">
+        <v>610</v>
+      </c>
+      <c r="N7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
+        <v>611</v>
+      </c>
+      <c r="D8" t="s">
+        <v>520</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" t="s">
+        <v>582</v>
+      </c>
+      <c r="G8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" t="s">
+        <v>612</v>
+      </c>
+      <c r="I8" t="s">
+        <v>613</v>
+      </c>
+      <c r="J8" t="s">
+        <v>614</v>
+      </c>
+      <c r="K8" t="s">
+        <v>524</v>
+      </c>
+      <c r="L8" t="s">
+        <v>615</v>
+      </c>
+      <c r="M8" t="s">
+        <v>616</v>
+      </c>
+      <c r="N8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s">
+        <v>611</v>
+      </c>
+      <c r="D9" t="s">
+        <v>520</v>
+      </c>
+      <c r="E9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" t="s">
+        <v>582</v>
+      </c>
+      <c r="G9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" t="s">
+        <v>617</v>
+      </c>
+      <c r="I9" t="s">
+        <v>618</v>
+      </c>
+      <c r="J9" t="s">
+        <v>619</v>
+      </c>
+      <c r="K9" t="s">
+        <v>524</v>
+      </c>
+      <c r="L9" t="s">
+        <v>620</v>
+      </c>
+      <c r="M9" t="s">
+        <v>621</v>
+      </c>
+      <c r="N9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s">
+        <v>611</v>
+      </c>
+      <c r="D10" t="s">
+        <v>622</v>
+      </c>
+      <c r="E10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" t="s">
+        <v>582</v>
+      </c>
+      <c r="G10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" t="s">
+        <v>623</v>
+      </c>
+      <c r="I10" t="s">
+        <v>624</v>
+      </c>
+      <c r="J10" t="s">
+        <v>625</v>
+      </c>
+      <c r="K10" t="s">
+        <v>626</v>
+      </c>
+      <c r="L10" t="s">
+        <v>627</v>
+      </c>
+      <c r="M10" t="s">
+        <v>628</v>
+      </c>
+      <c r="N10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
+        <v>611</v>
+      </c>
+      <c r="D11" t="s">
+        <v>629</v>
+      </c>
+      <c r="E11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" t="s">
+        <v>582</v>
+      </c>
+      <c r="G11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" t="s">
+        <v>630</v>
+      </c>
+      <c r="I11" t="s">
+        <v>631</v>
+      </c>
+      <c r="J11" t="s">
+        <v>632</v>
+      </c>
+      <c r="K11" t="s">
+        <v>633</v>
+      </c>
+      <c r="L11" t="s">
+        <v>538</v>
+      </c>
+      <c r="M11" t="s">
+        <v>634</v>
+      </c>
+      <c r="N11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" t="s">
+        <v>635</v>
+      </c>
+      <c r="D12" t="s">
+        <v>636</v>
+      </c>
+      <c r="E12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" t="s">
+        <v>582</v>
+      </c>
+      <c r="G12" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" t="s">
+        <v>637</v>
+      </c>
+      <c r="I12" t="s">
+        <v>638</v>
+      </c>
+      <c r="J12" t="s">
+        <v>639</v>
+      </c>
+      <c r="K12" t="s">
+        <v>640</v>
+      </c>
+      <c r="L12" t="s">
+        <v>641</v>
+      </c>
+      <c r="M12" t="s">
+        <v>642</v>
+      </c>
+      <c r="N12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>643</v>
+      </c>
+      <c r="D13" t="s">
+        <v>644</v>
+      </c>
+      <c r="E13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" t="s">
+        <v>582</v>
+      </c>
+      <c r="G13" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" t="s">
+        <v>645</v>
+      </c>
+      <c r="I13" t="s">
+        <v>646</v>
+      </c>
+      <c r="J13" t="s">
+        <v>647</v>
+      </c>
+      <c r="K13" t="s">
+        <v>648</v>
+      </c>
+      <c r="L13" t="s">
+        <v>649</v>
+      </c>
+      <c r="M13" t="s">
+        <v>650</v>
+      </c>
+      <c r="N13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
+        <v>651</v>
+      </c>
+      <c r="D14" t="s">
+        <v>652</v>
+      </c>
+      <c r="E14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" t="s">
+        <v>582</v>
+      </c>
+      <c r="G14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14" t="s">
+        <v>653</v>
+      </c>
+      <c r="I14" t="s">
+        <v>654</v>
+      </c>
+      <c r="J14" t="s">
+        <v>655</v>
+      </c>
+      <c r="K14" t="s">
+        <v>656</v>
+      </c>
+      <c r="L14" t="s">
+        <v>657</v>
+      </c>
+      <c r="M14" t="s">
+        <v>658</v>
+      </c>
+      <c r="N14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:P1"/>
+  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0CACFE1-7D96-44AF-8809-A362CA8C358A}">
+  <dimension ref="A1:P14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="68" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="150" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="120.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="64.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="114.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="62.75" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="18">
+      <c r="A1" s="8" t="s">
+        <v>494</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+    </row>
+    <row r="2" spans="1:16" ht="24" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D3" t="s">
+        <v>495</v>
+      </c>
+      <c r="E3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" t="s">
+        <v>496</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
+        <v>497</v>
+      </c>
+      <c r="I3" t="s">
+        <v>498</v>
+      </c>
+      <c r="J3" t="s">
+        <v>499</v>
+      </c>
+      <c r="K3" t="s">
+        <v>500</v>
+      </c>
+      <c r="L3" t="s">
+        <v>501</v>
+      </c>
+      <c r="M3" t="s">
+        <v>502</v>
+      </c>
+      <c r="N3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" t="s">
+        <v>503</v>
+      </c>
+      <c r="D4" t="s">
+        <v>504</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" t="s">
+        <v>505</v>
+      </c>
+      <c r="I4" t="s">
+        <v>506</v>
+      </c>
+      <c r="J4" t="s">
+        <v>507</v>
+      </c>
+      <c r="K4" t="s">
+        <v>508</v>
+      </c>
+      <c r="L4" t="s">
+        <v>509</v>
+      </c>
+      <c r="M4" t="s">
+        <v>510</v>
+      </c>
+      <c r="N4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
+        <v>511</v>
+      </c>
+      <c r="D5" t="s">
+        <v>512</v>
+      </c>
+      <c r="E5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" t="s">
+        <v>513</v>
+      </c>
+      <c r="I5" t="s">
+        <v>514</v>
+      </c>
+      <c r="J5" t="s">
+        <v>515</v>
+      </c>
+      <c r="K5" t="s">
+        <v>516</v>
+      </c>
+      <c r="L5" t="s">
+        <v>517</v>
+      </c>
+      <c r="M5" t="s">
+        <v>518</v>
+      </c>
+      <c r="N5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" t="s">
+        <v>519</v>
+      </c>
+      <c r="D6" t="s">
+        <v>520</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" t="s">
+        <v>521</v>
+      </c>
+      <c r="I6" t="s">
+        <v>522</v>
+      </c>
+      <c r="J6" t="s">
+        <v>523</v>
+      </c>
+      <c r="K6" t="s">
+        <v>524</v>
+      </c>
+      <c r="L6" t="s">
+        <v>525</v>
+      </c>
+      <c r="M6" t="s">
+        <v>526</v>
+      </c>
+      <c r="N6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>519</v>
+      </c>
+      <c r="D7" t="s">
+        <v>520</v>
+      </c>
+      <c r="E7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" t="s">
+        <v>527</v>
+      </c>
+      <c r="I7" t="s">
+        <v>528</v>
+      </c>
+      <c r="J7" t="s">
+        <v>529</v>
+      </c>
+      <c r="K7" t="s">
+        <v>524</v>
+      </c>
+      <c r="L7" t="s">
+        <v>530</v>
+      </c>
+      <c r="M7" t="s">
+        <v>531</v>
+      </c>
+      <c r="N7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
+        <v>532</v>
+      </c>
+      <c r="D8" t="s">
+        <v>533</v>
+      </c>
+      <c r="E8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" t="s">
+        <v>253</v>
+      </c>
+      <c r="G8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" t="s">
+        <v>534</v>
+      </c>
+      <c r="I8" t="s">
+        <v>535</v>
+      </c>
+      <c r="J8" t="s">
+        <v>536</v>
+      </c>
+      <c r="K8" t="s">
+        <v>537</v>
+      </c>
+      <c r="L8" t="s">
+        <v>538</v>
+      </c>
+      <c r="M8" t="s">
+        <v>539</v>
+      </c>
+      <c r="N8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s">
+        <v>511</v>
+      </c>
+      <c r="D9" t="s">
+        <v>540</v>
+      </c>
+      <c r="E9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" t="s">
+        <v>496</v>
+      </c>
+      <c r="G9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" t="s">
+        <v>541</v>
+      </c>
+      <c r="I9" t="s">
+        <v>542</v>
+      </c>
+      <c r="J9" t="s">
+        <v>543</v>
+      </c>
+      <c r="K9" t="s">
+        <v>516</v>
+      </c>
+      <c r="L9" t="s">
+        <v>544</v>
+      </c>
+      <c r="M9" t="s">
+        <v>545</v>
+      </c>
+      <c r="N9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s">
+        <v>511</v>
+      </c>
+      <c r="D10" t="s">
+        <v>540</v>
+      </c>
+      <c r="E10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" t="s">
+        <v>253</v>
+      </c>
+      <c r="G10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" t="s">
+        <v>546</v>
+      </c>
+      <c r="I10" t="s">
+        <v>547</v>
+      </c>
+      <c r="J10" t="s">
+        <v>548</v>
+      </c>
+      <c r="K10" t="s">
+        <v>549</v>
+      </c>
+      <c r="L10" t="s">
+        <v>550</v>
+      </c>
+      <c r="M10" t="s">
+        <v>551</v>
+      </c>
+      <c r="N10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
+        <v>511</v>
+      </c>
+      <c r="D11" t="s">
+        <v>552</v>
+      </c>
+      <c r="E11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" t="s">
+        <v>496</v>
+      </c>
+      <c r="G11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" t="s">
+        <v>553</v>
+      </c>
+      <c r="I11" t="s">
+        <v>554</v>
+      </c>
+      <c r="J11" t="s">
+        <v>555</v>
+      </c>
+      <c r="K11" t="s">
+        <v>556</v>
+      </c>
+      <c r="L11" t="s">
+        <v>557</v>
+      </c>
+      <c r="M11" t="s">
+        <v>558</v>
+      </c>
+      <c r="N11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" t="s">
+        <v>511</v>
+      </c>
+      <c r="D12" t="s">
+        <v>559</v>
+      </c>
+      <c r="E12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" t="s">
+        <v>349</v>
+      </c>
+      <c r="G12" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" t="s">
+        <v>560</v>
+      </c>
+      <c r="I12" t="s">
+        <v>561</v>
+      </c>
+      <c r="J12" t="s">
+        <v>562</v>
+      </c>
+      <c r="K12" t="s">
+        <v>563</v>
+      </c>
+      <c r="L12" t="s">
+        <v>564</v>
+      </c>
+      <c r="M12" t="s">
+        <v>565</v>
+      </c>
+      <c r="N12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>566</v>
+      </c>
+      <c r="D13" t="s">
+        <v>566</v>
+      </c>
+      <c r="E13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" t="s">
+        <v>567</v>
+      </c>
+      <c r="I13" t="s">
+        <v>568</v>
+      </c>
+      <c r="J13" t="s">
+        <v>569</v>
+      </c>
+      <c r="K13" t="s">
+        <v>570</v>
+      </c>
+      <c r="L13" t="s">
+        <v>571</v>
+      </c>
+      <c r="M13" t="s">
+        <v>572</v>
+      </c>
+      <c r="N13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
+        <v>511</v>
+      </c>
+      <c r="D14" t="s">
+        <v>573</v>
+      </c>
+      <c r="E14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" t="s">
+        <v>496</v>
+      </c>
+      <c r="G14" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" t="s">
+        <v>574</v>
+      </c>
+      <c r="I14" t="s">
+        <v>575</v>
+      </c>
+      <c r="J14" t="s">
+        <v>576</v>
+      </c>
+      <c r="K14" t="s">
+        <v>577</v>
+      </c>
+      <c r="L14" t="s">
+        <v>578</v>
+      </c>
+      <c r="M14" t="s">
+        <v>579</v>
+      </c>
+      <c r="N14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:P1"/>
+  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P79"/>
+  <dimension ref="A1:P89"/>
   <sheetFormatPr defaultRowHeight="16.2" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="6" customWidth="1"/>
@@ -5842,6 +7763,452 @@
         <v>30</v>
       </c>
     </row>
+    <row r="80" spans="1:16" ht="45" customHeight="1">
+      <c r="A80" s="6">
+        <v>78</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="D80" s="7"/>
+      <c r="E80" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="G80" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H80" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="I80" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="J80" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="K80" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="L80" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="M80" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="N80" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O80" s="7"/>
+      <c r="P80" s="7"/>
+    </row>
+    <row r="81" spans="1:16" ht="45" customHeight="1">
+      <c r="A81" s="3">
+        <v>79</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="I81" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="J81" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="K81" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L81" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="M81" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="O81" s="4"/>
+      <c r="P81" s="4"/>
+    </row>
+    <row r="82" spans="1:16" ht="45" customHeight="1">
+      <c r="A82" s="6">
+        <v>80</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="D82" s="7"/>
+      <c r="E82" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H82" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="I82" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="J82" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="K82" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="L82" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="M82" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="N82" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O82" s="7"/>
+      <c r="P82" s="7"/>
+    </row>
+    <row r="83" spans="1:16" ht="45" customHeight="1">
+      <c r="A83" s="3">
+        <v>81</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D83" s="4"/>
+      <c r="E83" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="I83" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="J83" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="K83" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="L83" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="M83" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="O83" s="4"/>
+      <c r="P83" s="4"/>
+    </row>
+    <row r="84" spans="1:16" ht="45" customHeight="1">
+      <c r="A84" s="6">
+        <v>82</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="D84" s="7"/>
+      <c r="E84" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H84" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="I84" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="J84" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="K84" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="L84" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="M84" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="N84" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O84" s="7"/>
+      <c r="P84" s="7"/>
+    </row>
+    <row r="85" spans="1:16" ht="45" customHeight="1">
+      <c r="A85" s="3">
+        <v>83</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="I85" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="J85" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="K85" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="L85" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="M85" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="N85" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="O85" s="4"/>
+      <c r="P85" s="4"/>
+    </row>
+    <row r="86" spans="1:16" ht="45" customHeight="1">
+      <c r="A86" s="6">
+        <v>84</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="D86" s="7"/>
+      <c r="E86" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H86" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="I86" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="J86" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="K86" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="L86" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="M86" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="N86" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O86" s="7"/>
+      <c r="P86" s="7"/>
+    </row>
+    <row r="87" spans="1:16" ht="45" customHeight="1">
+      <c r="A87" s="3">
+        <v>85</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="D87" s="4"/>
+      <c r="E87" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="I87" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="J87" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="K87" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="L87" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="M87" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="N87" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="O87" s="4"/>
+      <c r="P87" s="4"/>
+    </row>
+    <row r="88" spans="1:16" ht="45" customHeight="1">
+      <c r="A88" s="6">
+        <v>86</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G88" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H88" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="I88" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="J88" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="K88" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="L88" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="M88" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="N88" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O88" s="7"/>
+      <c r="P88" s="7"/>
+    </row>
+    <row r="89" spans="1:16" ht="45" customHeight="1">
+      <c r="A89" s="3">
+        <v>87</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H89" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="I89" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="J89" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="K89" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L89" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="M89" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="O89" s="4"/>
+      <c r="P89" s="4"/>
+    </row>
   </sheetData>
   <autoFilter ref="A2:O79" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
@@ -5852,7 +8219,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="16.2" customHeight="1"/>

--- a/docs/iFare_UI_UX_問題追蹤清單.xlsx
+++ b/docs/iFare_UI_UX_問題追蹤清單.xlsx
@@ -39,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -83,13 +83,8 @@
       <name val="Calibri"/>
       <color rgb="006100"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <color rgb="9C5700"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -142,12 +137,6 @@
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -168,7 +157,7 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -192,9 +181,6 @@
       <alignment vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -252,10 +238,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂ¯ÃÂ¼ÃÂ­ÃÂ¯ÃÂ¼ÃÂ³ ÃÂ¯ÃÂ¼ÃÂ°ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂ¥ÃÂ®ÃÂÃÂ¤ÃÂ½ÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ­ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ³ ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ°ÃÂÃÂ£ÃÂÃÂÃÂÃÂ´ÃÂÃÂ£ÃÂÃÂÃÂÃÂ·ÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂ«ÃÂÃÂ§ÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂ ÃÂÃÂªÃÂÃÂ³ÃÂÃÂ ÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂ¥ÃÂÃÂ®ÃÂÃÂÃÂÃÂ¤ÃÂÃÂ½ÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂ¦ÃÂÃÂÃÂÃÂ°ÃÂÃÂ§ÃÂÃÂ´ÃÂÃÂ°ÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂ«ÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -287,10 +273,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂ¯ÃÂ¼ÃÂ­ÃÂ¯ÃÂ¼ÃÂ³ ÃÂ¯ÃÂ¼ÃÂ°ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂ¥ÃÂ®ÃÂÃÂ¤ÃÂ½ÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ­ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ³ ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ°ÃÂÃÂ£ÃÂÃÂÃÂÃÂ´ÃÂÃÂ£ÃÂÃÂÃÂÃÂ·ÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂ«ÃÂÃÂ§ÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂ ÃÂÃÂªÃÂÃÂ³ÃÂÃÂ ÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂ¥ÃÂÃÂ®ÃÂÃÂÃÂÃÂ¤ÃÂÃÂ½ÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂ¦ÃÂÃÂÃÂÃÂ°ÃÂÃÂ§ÃÂÃÂ´ÃÂÃÂ°ÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂ«ÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -1760,7 +1746,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P94"/>
+  <dimension ref="A1:P99"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="6"/>
     <col min="2" max="2" customWidth="1" width="6"/>
@@ -2656,45 +2642,45 @@
       </c>
     </row>
     <row r="19" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A19" s="10">
+      <c r="A19" s="8">
         <v>17</v>
       </c>
-      <c r="B19" s="10" t="str">
-        <v>V</v>
-      </c>
-      <c r="C19" s="10" t="str">
+      <c r="B19" s="8" t="str">
+        <v>V</v>
+      </c>
+      <c r="C19" s="8" t="str">
         <v>首頁</v>
       </c>
-      <c r="D19" s="10" t="str">
-        <v/>
-      </c>
-      <c r="E19" s="10" t="str">
+      <c r="D19" s="8" t="str">
+        <v/>
+      </c>
+      <c r="E19" s="8" t="str">
         <v>修復</v>
       </c>
-      <c r="F19" s="10" t="str">
+      <c r="F19" s="8" t="str">
         <v>視覺</v>
       </c>
-      <c r="G19" s="10" t="str">
+      <c r="G19" s="8" t="str">
         <v>中</v>
       </c>
-      <c r="H19" s="10" t="str">
+      <c r="H19" s="8" t="str">
         <v>Footer 社群連結呈現不一致</v>
       </c>
-      <c r="I19" s="10" t="str">
+      <c r="I19" s="8" t="str">
         <v>LINE 用 styled button (.btn-line)，Facebook 用純文字圖示連結 (.ic-facebook-before)</v>
       </c>
-      <c r="J19" s="10" t="str">
+      <c r="J19" s="8" t="str">
         <v>統一為相同呈現方式</v>
       </c>
-      <c r="K19" s="10" t="str">
+      <c r="K19" s="8" t="str">
         <v>components/AppFooter.vue</v>
       </c>
-      <c r="L19" s="10" t="str" xml:space="preserve">
+      <c r="L19" s="8" t="str" xml:space="preserve">
         <v xml:space="preserve">components/AppFooter.vue_x000d_
 assets/style/components/_appFooter.scss_x000d_
 assets/style/_font.scss</v>
       </c>
-      <c r="M19" s="10" t="str">
+      <c r="M19" s="8" t="str">
         <v>兩個社群連結完全不同的 HTML 結構和樣式</v>
       </c>
       <c r="N19" s="9" t="str">
@@ -2967,105 +2953,105 @@
       </c>
     </row>
     <row r="25" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A25" s="3">
+      <c r="A25" s="10">
         <v>23</v>
       </c>
-      <c r="B25" s="3" t="str">
+      <c r="B25" s="10" t="str">
         <v>~</v>
       </c>
-      <c r="C25" s="3" t="str">
+      <c r="C25" s="10" t="str">
         <v>最新消息</v>
       </c>
-      <c r="D25" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E25" s="3" t="str">
+      <c r="D25" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E25" s="10" t="str">
         <v>修復</v>
       </c>
-      <c r="F25" s="3" t="str">
+      <c r="F25" s="10" t="str">
         <v>視覺</v>
       </c>
-      <c r="G25" s="3" t="str">
+      <c r="G25" s="10" t="str">
         <v>低</v>
       </c>
-      <c r="H25" s="3" t="str">
+      <c r="H25" s="10" t="str">
         <v>桌面版內容截斷無省略提示</v>
       </c>
-      <c r="I25" s="3" t="str">
+      <c r="I25" s="10" t="str">
         <v>桌面版 .item-info 無 text-overflow 或 line-clamp</v>
       </c>
-      <c r="J25" s="3" t="str">
+      <c r="J25" s="10" t="str">
         <v>加入 text-overflow: ellipsis 或 line-clamp</v>
       </c>
-      <c r="K25" s="3" t="str">
+      <c r="K25" s="10" t="str">
         <v>pages/news.vue</v>
       </c>
-      <c r="L25" s="3" t="str" xml:space="preserve">
+      <c r="L25" s="10" t="str" xml:space="preserve">
         <v xml:space="preserve">pages/news.vue_x000d_
 assets/style/components/_appBody.scss_x000d_
 assets/style/_font.scss</v>
       </c>
-      <c r="M25" s="3" t="str">
+      <c r="M25" s="10" t="str">
         <v>桌面無省略確認；手機版已有 textLineClamp(2)</v>
       </c>
-      <c r="N25" s="3" t="str">
-        <v>待處理</v>
-      </c>
-      <c r="O25" s="3" t="str">
-        <v/>
-      </c>
-      <c r="P25" s="3" t="str">
-        <v/>
+      <c r="N25" s="9" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O25" s="9" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="P25" s="9" t="str">
+        <v>pages/news.vue 的 .article-item .item-info 加 line-clamp: 2（桌面）/ line-clamp: 3（手機 ≤1024px），超過行數自動省略結尾。</v>
       </c>
     </row>
     <row r="26" ht="45" customHeight="1">
-      <c r="A26" s="3">
+      <c r="A26" s="10">
         <v>24</v>
       </c>
-      <c r="B26" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C26" s="3" t="str">
+      <c r="B26" s="10" t="str">
+        <v>V</v>
+      </c>
+      <c r="C26" s="10" t="str">
         <v>最新消息</v>
       </c>
-      <c r="D26" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E26" s="3" t="str">
+      <c r="D26" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E26" s="10" t="str">
         <v>修復</v>
       </c>
-      <c r="F26" s="3" t="str">
+      <c r="F26" s="10" t="str">
         <v>無障礙</v>
       </c>
-      <c r="G26" s="3" t="str">
+      <c r="G26" s="10" t="str">
         <v>低</v>
       </c>
-      <c r="H26" s="3" t="str">
+      <c r="H26" s="10" t="str">
         <v>純圖示連結缺少 aria-label</v>
       </c>
-      <c r="I26" s="3" t="str">
+      <c r="I26" s="10" t="str">
         <v>&lt;i class="ic-arrow-right"&gt; 無 aria-label/title/隱藏文字</v>
       </c>
-      <c r="J26" s="3" t="str">
+      <c r="J26" s="10" t="str">
         <v>加入 aria-label</v>
       </c>
-      <c r="K26" s="3" t="str">
+      <c r="K26" s="10" t="str">
         <v>pages/news.vue</v>
       </c>
-      <c r="L26" s="3" t="str">
+      <c r="L26" s="10" t="str">
         <v>pages/news.vue</v>
       </c>
-      <c r="M26" s="3" t="str">
+      <c r="M26" s="10" t="str">
         <v>grep aria-label 全站回傳 0 筆</v>
       </c>
-      <c r="N26" s="3" t="str">
-        <v>待處理</v>
-      </c>
-      <c r="O26" s="3" t="str">
-        <v/>
-      </c>
-      <c r="P26" s="3" t="str">
-        <v/>
+      <c r="N26" s="9" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O26" s="9" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="P26" s="9" t="str">
+        <v>pages/news.vue 的 &lt;i class="ic-arrow-right"&gt; 加上 aria-label="閱讀全文"，符合無障礙語意要求。</v>
       </c>
     </row>
     <row r="27" ht="45" customHeight="1" xml:space="preserve">
@@ -3120,55 +3106,55 @@
       </c>
     </row>
     <row r="28" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A28" s="3">
+      <c r="A28" s="10">
         <v>26</v>
       </c>
-      <c r="B28" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C28" s="3" t="str">
+      <c r="B28" s="10" t="str">
+        <v>V</v>
+      </c>
+      <c r="C28" s="10" t="str">
         <v>最新消息</v>
       </c>
-      <c r="D28" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E28" s="3" t="str">
+      <c r="D28" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E28" s="10" t="str">
         <v>提升</v>
       </c>
-      <c r="F28" s="3" t="str">
+      <c r="F28" s="10" t="str">
         <v>視覺</v>
       </c>
-      <c r="G28" s="3" t="str">
+      <c r="G28" s="10" t="str">
         <v>低</v>
       </c>
-      <c r="H28" s="3" t="str">
+      <c r="H28" s="10" t="str">
         <v>新增「NEW」標籤</v>
       </c>
-      <c r="I28" s="3" t="str">
+      <c r="I28" s="10" t="str">
         <v>新消息無醒目標示</v>
       </c>
-      <c r="J28" s="3" t="str">
+      <c r="J28" s="10" t="str">
         <v>7 天內的新消息加上 NEW badge</v>
       </c>
-      <c r="K28" s="3" t="str">
+      <c r="K28" s="10" t="str">
         <v>pages/news.vue</v>
       </c>
-      <c r="L28" s="3" t="str" xml:space="preserve">
+      <c r="L28" s="10" t="str" xml:space="preserve">
         <v xml:space="preserve">pages/news.vue_x000d_
 assets/style/components/_appBody.scss_x000d_
 assets/style/_font.scss</v>
       </c>
-      <c r="M28" s="3" t="str">
+      <c r="M28" s="10" t="str">
         <v>功能確實不存在</v>
       </c>
-      <c r="N28" s="3" t="str">
-        <v>待處理</v>
-      </c>
-      <c r="O28" s="3" t="str">
-        <v/>
-      </c>
-      <c r="P28" s="3" t="str">
-        <v/>
+      <c r="N28" s="9" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O28" s="9" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="P28" s="9" t="str">
+        <v>pages/news.vue 加 isNewItem(releaseTime) helper（7 天內判斷），對應消息右上角顯示橘色 NEW pill 標籤（_appBody.scss .badge-new）。</v>
       </c>
     </row>
     <row r="29" ht="45" customHeight="1" xml:space="preserve">
@@ -4049,55 +4035,55 @@
       </c>
     </row>
     <row r="46" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A46" s="3">
+      <c r="A46" s="10">
         <v>44</v>
       </c>
-      <c r="B46" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C46" s="3" t="str">
+      <c r="B46" s="10" t="str">
+        <v>V</v>
+      </c>
+      <c r="C46" s="10" t="str">
         <v>關於長穩</v>
       </c>
-      <c r="D46" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E46" s="3" t="str">
+      <c r="D46" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E46" s="10" t="str">
         <v>提升</v>
       </c>
-      <c r="F46" s="3" t="str">
+      <c r="F46" s="10" t="str">
         <v>視覺</v>
       </c>
-      <c r="G46" s="3" t="str">
+      <c r="G46" s="10" t="str">
         <v>低</v>
       </c>
-      <c r="H46" s="3" t="str">
+      <c r="H46" s="10" t="str">
         <v>三大核心圖示為靜態 SVG</v>
       </c>
-      <c r="I46" s="3" t="str">
+      <c r="I46" s="10" t="str">
         <v>環境保育/人才培育/社會關懷用靜態 &lt;i class="how-logo"&gt;</v>
       </c>
-      <c r="J46" s="3" t="str">
+      <c r="J46" s="10" t="str">
         <v>加入 SVG 動畫</v>
       </c>
-      <c r="K46" s="3" t="str">
+      <c r="K46" s="10" t="str">
         <v>pages/about.vue</v>
       </c>
-      <c r="L46" s="3" t="str" xml:space="preserve">
+      <c r="L46" s="10" t="str" xml:space="preserve">
         <v xml:space="preserve">pages/about.vue_x000d_
 assets/style/components/_appBody_about.scss_x000d_
 assets/style/_animation.scss</v>
       </c>
-      <c r="M46" s="3" t="str">
+      <c r="M46" s="10" t="str">
         <v>確認無任何動畫 class 或 JS</v>
       </c>
-      <c r="N46" s="3" t="str">
-        <v>待處理</v>
-      </c>
-      <c r="O46" s="3" t="str">
-        <v/>
-      </c>
-      <c r="P46" s="3" t="str">
-        <v/>
+      <c r="N46" s="9" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O46" s="9" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="P46" s="9" t="str">
+        <v>icon SVG 本身仍為靜態，但已包入 Dynamic Island 互動卡片（.how-content）：hover/click toggle 觸發整體 morph 動畫（grid-template-rows 展開、translateY 浮起、background opacity overlay 漸層切換、border 露出青綠光暈）。視覺已不再死板。</v>
       </c>
     </row>
     <row r="47" ht="45" customHeight="1">
@@ -5437,46 +5423,46 @@
       </c>
     </row>
     <row r="73" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A73" s="11">
+      <c r="A73" s="5">
         <v>71</v>
       </c>
-      <c r="B73" s="11" t="str">
-        <v>V</v>
-      </c>
-      <c r="C73" s="11" t="str">
+      <c r="B73" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C73" s="5" t="str">
         <v>全站通用</v>
       </c>
-      <c r="D73" s="11" t="str">
-        <v/>
-      </c>
-      <c r="E73" s="11" t="str">
+      <c r="D73" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E73" s="5" t="str">
         <v>修復</v>
       </c>
-      <c r="F73" s="11" t="str">
+      <c r="F73" s="5" t="str">
         <v>RWD</v>
       </c>
-      <c r="G73" s="11" t="str">
+      <c r="G73" s="5" t="str">
         <v>高</v>
       </c>
-      <c r="H73" s="11" t="str">
+      <c r="H73" s="5" t="str">
         <v>多處觸控目標小於 44x44px</v>
       </c>
-      <c r="I73" s="11" t="str">
+      <c r="I73" s="5" t="str">
         <v>分頁按鈕 30x30px、.btn-reset height:32px、.btn-advance height:40px</v>
       </c>
-      <c r="J73" s="11" t="str">
+      <c r="J73" s="5" t="str">
         <v>確保所有可點擊元素最小 44x44px</v>
       </c>
-      <c r="K73" s="11" t="str">
+      <c r="K73" s="5" t="str">
         <v>全站</v>
       </c>
-      <c r="L73" s="11" t="str" xml:space="preserve">
+      <c r="L73" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">assets/style/components/_compPage.scss_x000d_
 assets/style/components/_button.scss_x000d_
 assets/style/components/_compSelect.scss_x000d_
 assets/style/rwd/_rwd_compPage.scss</v>
       </c>
-      <c r="M73" s="11" t="str">
+      <c r="M73" s="5" t="str">
         <v>確認多處尺寸低於 44px 標準</v>
       </c>
       <c r="N73" s="6" t="str">
@@ -6481,6 +6467,262 @@
       </c>
       <c r="P94" s="9" t="str">
         <v>改版補登；同步修桌面 1025-1280px overflow（加 FB 後 .card-more 內容寬度 ~1300px 會爆）：.card-more 加 flex-wrap: wrap + max-width: calc(100% - 64px)；.info-more 加 max-width: 480px 讓長文字桌面換 2 行</v>
+      </c>
+    </row>
+    <row r="95" xml:space="preserve">
+      <c r="A95" s="9">
+        <v>93</v>
+      </c>
+      <c r="B95" s="9" t="str">
+        <v>V</v>
+      </c>
+      <c r="C95" s="9" t="str">
+        <v>關於長穩</v>
+      </c>
+      <c r="D95" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E95" s="9" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F95" s="9" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G95" s="9" t="str">
+        <v>中</v>
+      </c>
+      <c r="H95" s="9" t="str">
+        <v>About 三大核心介紹缺乏互動性</v>
+      </c>
+      <c r="I95" s="9" t="str">
+        <v>環境保育/人才培育/社會關懷三張卡片原為靜態圖文，使用者掃過無視覺反應，缺乏吸引點擊探索的動機</v>
+      </c>
+      <c r="J95" s="9" t="str">
+        <v>改造為 iOS Dynamic Island 風格 morph 卡片：暖象牙白漸層底 + 圓角 28px + 預設只露 icon+標題 → hover/click toggle 平滑展開內文（grid-template-rows trick）+ translateY 浮起 + 邊框露出青綠光暈</v>
+      </c>
+      <c r="K95" s="9" t="str">
+        <v>pages/about.vue</v>
+      </c>
+      <c r="L95" s="9" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Frontend/pages/about.vue_x000d_
+assets/style/components/_appBody_about.scss_x000d_
+assets/style/rwd/_rwd_about.scss</v>
+      </c>
+      <c r="M95" s="9" t="str">
+        <v>改版補登；HTML 重組（icon+title 合進 .how-top、info 包 .how-info-wrap）；script 加 activeHow ref + toggleHow handler；keyboard a11y (Enter/Space) 與 tabindex；GPU 優化（will-change + ::before opacity overlay 取代 gradient transition）；Apple spring easing cubic-bezier(0.32, 0.72, 0, 1)</v>
+      </c>
+      <c r="N95" s="9" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O95" s="9" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="P95" s="9" t="str">
+        <v>改版補登；對應 #44 三大核心圖示靜態問題已連動修正</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="9">
+        <v>94</v>
+      </c>
+      <c r="B96" s="9" t="str">
+        <v>V</v>
+      </c>
+      <c r="C96" s="9" t="str">
+        <v>關於長穩</v>
+      </c>
+      <c r="D96" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E96" s="9" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F96" s="9" t="str">
+        <v>視覺</v>
+      </c>
+      <c r="G96" s="9" t="str">
+        <v>低</v>
+      </c>
+      <c r="H96" s="9" t="str">
+        <v>About 成員照片缺 hover 互動</v>
+      </c>
+      <c r="I96" s="9" t="str">
+        <v>陳進財/鄔筠軒/顏杏蓉三位成員區塊原無 hover 反饋，掃過時視覺無變化</v>
+      </c>
+      <c r="J96" s="9" t="str">
+        <v>陳進財/鄔筠軒整組 hover：照片 scale(1.06) + 白框 scale(1.03) + box-shadow 加深 + 橘色標牌 translateY(-4px)；顏杏蓉（無照片）標牌 hover translateY(-4px) + scale(1.04)</v>
+      </c>
+      <c r="K96" s="9" t="str">
+        <v>pages/about.vue</v>
+      </c>
+      <c r="L96" s="9" t="str">
+        <v>iFare_Frontend/assets/style/components/_appBody_about.scss</v>
+      </c>
+      <c r="M96" s="9" t="str">
+        <v>改版補登；同套 cubic-bezier(0.32, 0.72, 0, 1) easing；will-change: transform 給 .member-photo 預先建 GPU layer</v>
+      </c>
+      <c r="N96" s="9" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O96" s="9" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="P96" s="9" t="str">
+        <v>改版補登</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9">
+        <v>95</v>
+      </c>
+      <c r="B97" s="9" t="str">
+        <v>V</v>
+      </c>
+      <c r="C97" s="9" t="str">
+        <v>關於長穩</v>
+      </c>
+      <c r="D97" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E97" s="9" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F97" s="9" t="str">
+        <v>視覺</v>
+      </c>
+      <c r="G97" s="9" t="str">
+        <v>低</v>
+      </c>
+      <c r="H97" s="9" t="str">
+        <v>About 底部 CTA 連結缺 hover micro-animation</v>
+      </c>
+      <c r="I97" s="9" t="str">
+        <v>「前往 i-Fare」與「查看最新消息」兩個 advance-link 原為靜態，hover 無互動反饋，無法強化「點我前進」訊號</v>
+      </c>
+      <c r="J97" s="9" t="str">
+        <v>連結 hover 時 translateY(-2px) 上浮，箭頭 icon translateX(6px) 向右滑出，引導視線前進</v>
+      </c>
+      <c r="K97" s="9" t="str">
+        <v>pages/about.vue</v>
+      </c>
+      <c r="L97" s="9" t="str">
+        <v>iFare_Frontend/assets/style/components/_appBody_about.scss</v>
+      </c>
+      <c r="M97" s="9" t="str">
+        <v>改版補登；統一 cubic-bezier(0.32, 0.72, 0, 1) easing 0.22s</v>
+      </c>
+      <c r="N97" s="9" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O97" s="9" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="P97" s="9" t="str">
+        <v>改版補登</v>
+      </c>
+    </row>
+    <row r="98" xml:space="preserve">
+      <c r="A98" s="9">
+        <v>96</v>
+      </c>
+      <c r="B98" s="9" t="str">
+        <v>V</v>
+      </c>
+      <c r="C98" s="9" t="str">
+        <v>最新消息</v>
+      </c>
+      <c r="D98" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E98" s="9" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F98" s="9" t="str">
+        <v>視覺</v>
+      </c>
+      <c r="G98" s="9" t="str">
+        <v>中</v>
+      </c>
+      <c r="H98" s="9" t="str">
+        <v>News 列表呈現升級為浮起卡片 + 入場動畫 + 日期 pill</v>
+      </c>
+      <c r="I98" s="9" t="str">
+        <v>原本最新消息為「底線分隔的清單列」，hover 只是淡白底 + 箭頭轉橘，視覺扁平、缺乏互動感、日期不醒目、長內文無截斷</v>
+      </c>
+      <c r="J98" s="9" t="str">
+        <v>列表整體升級：圓角 16px 浮起卡片（white .7 + shadow）+ stagger fade-up 入場動畫（@for 1~12 each +50ms）+ 日期變橘色 pill 標籤（border + 半透明橘底）+ hover translateY(-3px) + 背景變實白 + 箭頭橘色滑右 6px</v>
+      </c>
+      <c r="K98" s="9" t="str">
+        <v>pages/news.vue</v>
+      </c>
+      <c r="L98" s="9" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Frontend/pages/news.vue_x000d_
+assets/style/components/_appBody.scss_x000d_
+assets/style/_animation.scss_x000d_
+assets/style/rwd/_rwd.scss</v>
+      </c>
+      <c r="M98" s="9" t="str">
+        <v>改版補登；@keyframes newsItemEnter 放 _animation.scss；統一 cubic-bezier(0.32, 0.72, 0, 1) easing；配色全用既有 token 沒引入新色</v>
+      </c>
+      <c r="N98" s="9" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O98" s="9" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="P98" s="9" t="str">
+        <v>改版補登；同次改動連帶解決 #23 (line-clamp 2)、#24 (aria-label)、#26 (NEW badge)</v>
+      </c>
+    </row>
+    <row r="99" xml:space="preserve">
+      <c r="A99" s="9">
+        <v>97</v>
+      </c>
+      <c r="B99" s="9" t="str">
+        <v>V</v>
+      </c>
+      <c r="C99" s="9" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="D99" s="9" t="str">
+        <v>AppFooter / AppHeader</v>
+      </c>
+      <c r="E99" s="9" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F99" s="9" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G99" s="9" t="str">
+        <v>低</v>
+      </c>
+      <c r="H99" s="9" t="str">
+        <v>社群外連結未開新分頁，可能丟失當前頁狀態</v>
+      </c>
+      <c r="I99" s="9" t="str">
+        <v>AppFooter LINE/Facebook 與 AppHeader 手機版社群 icon 連結原為一般 &lt;a href&gt;，點擊會在當前分頁導向，使用者離開站內後返回成本高</v>
+      </c>
+      <c r="J99" s="9" t="str">
+        <v>4 個社群連結都加 target="_blank" + rel="noopener noreferrer"：開新分頁、避免反向 tabnabbing、不洩漏 referrer</v>
+      </c>
+      <c r="K99" s="9" t="str">
+        <v>components/AppFooter.vue components/AppHeader.vue</v>
+      </c>
+      <c r="L99" s="9" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Frontend/components/AppFooter.vue_x000d_
+iFare_Frontend/components/AppHeader.vue</v>
+      </c>
+      <c r="M99" s="9" t="str">
+        <v>改版補登；rel="noopener" 是 W3C 安全建議</v>
+      </c>
+      <c r="N99" s="9" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O99" s="9" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="P99" s="9" t="str">
+        <v>改版補登</v>
       </c>
     </row>
   </sheetData>
@@ -6490,7 +6732,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P94"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P99"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -6529,10 +6771,10 @@
         <v>V 確認</v>
       </c>
       <c r="B3" s="2">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C3" s="2" t="str">
-        <v>87.8%</v>
+        <v>88.5%</v>
       </c>
       <c r="D3" s="3" t="str">
         <v>經程式碼驗證確認問題存在</v>
@@ -6546,7 +6788,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="2" t="str">
-        <v>12.2%</v>
+        <v>11.5%</v>
       </c>
       <c r="D4" s="3" t="str">
         <v>問題存在但原描述部分不正確，已修正描述</v>
@@ -6557,13 +6799,13 @@
         <v>合計</v>
       </c>
       <c r="B5" s="2">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C5" s="3" t="str">
         <v>100%</v>
       </c>
       <c r="D5" s="2" t="str">
-        <v>已移除 8 項原始盤點中不正確的項目；2026-04-28 補登 5 項改版實作項目（#88/#89/#90/#91/#92）</v>
+        <v>已移除 8 項原始盤點中不正確的項目；2026-04-28 補登 10 項改版實作項目（#88-#97）</v>
       </c>
     </row>
     <row r="7" ht="16.2" customHeight="1">
@@ -6620,11 +6862,11 @@
       <c r="B11" s="3">
         <v>3</v>
       </c>
-      <c r="C11" s="3">
-        <v>2</v>
-      </c>
-      <c r="D11" s="3">
-        <v>5</v>
+      <c r="C11" s="2">
+        <v>3</v>
+      </c>
+      <c r="D11" s="2">
+        <v>6</v>
       </c>
     </row>
     <row r="12" ht="16.2" customHeight="1">
@@ -6662,25 +6904,25 @@
       <c r="B14" s="3">
         <v>2</v>
       </c>
-      <c r="C14" s="3">
-        <v>3</v>
-      </c>
-      <c r="D14" s="3">
-        <v>5</v>
+      <c r="C14" s="2">
+        <v>6</v>
+      </c>
+      <c r="D14" s="2">
+        <v>8</v>
       </c>
     </row>
     <row r="15" ht="16.2" customHeight="1">
       <c r="A15" s="3" t="str">
         <v>共用元件</v>
       </c>
-      <c r="B15" s="3">
-        <v>14</v>
+      <c r="B15" s="2">
+        <v>15</v>
       </c>
       <c r="C15" s="2">
         <v>2</v>
       </c>
       <c r="D15" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" ht="16.2" customHeight="1">
@@ -6730,13 +6972,13 @@
         <v>合計</v>
       </c>
       <c r="B19" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C19" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D19" s="2">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" ht="16.2" customHeight="1">
@@ -6780,10 +7022,10 @@
         <v>27</v>
       </c>
       <c r="C24" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D24" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" ht="16.2" customHeight="1">
@@ -6791,13 +7033,13 @@
         <v>低</v>
       </c>
       <c r="B25" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C25" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D25" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/docs/iFare_UI_UX_問題追蹤清單.xlsx
+++ b/docs/iFare_UI_UX_問題追蹤清單.xlsx
@@ -39,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -48,43 +48,8 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <color rgb="9C5700"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <color rgb="9C5700"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <color rgb="9C5700"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <color rgb="006100"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <color rgb="006100"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <color rgb="006100"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <color rgb="006100"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="2">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -92,48 +57,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -157,32 +80,16 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="true"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -238,10 +145,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ­ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ³ ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ°ÃÂÃÂ£ÃÂÃÂÃÂÃÂ´ÃÂÃÂ£ÃÂÃÂÃÂÃÂ·ÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂ«ÃÂÃÂ§ÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂ ÃÂÃÂªÃÂÃÂ³ÃÂÃÂ ÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂ¥ÃÂÃÂ®ÃÂÃÂÃÂÃÂ¤ÃÂÃÂ½ÃÂÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂÃÂ¦ÃÂÃÂÃÂÃÂ°ÃÂÃÂ§ÃÂÃÂ´ÃÂÃÂ°ÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂ«ÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -273,10 +180,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ­ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ³ ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ°ÃÂÃÂ£ÃÂÃÂÃÂÃÂ´ÃÂÃÂ£ÃÂÃÂÃÂÃÂ·ÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂ«ÃÂÃÂ§ÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂ ÃÂÃÂªÃÂÃÂ³ÃÂÃÂ ÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂ¥ÃÂÃÂ®ÃÂÃÂÃÂÃÂ¤ÃÂÃÂ½ÃÂÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂÃÂ¦ÃÂÃÂÃÂÃÂ°ÃÂÃÂ§ÃÂÃÂ´ÃÂÃÂ°ÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂ«ÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -518,19 +425,19 @@
   <cols>
     <col min="1" max="1" customWidth="1" width="6"/>
     <col min="2" max="2" customWidth="1" width="6"/>
-    <col min="3" max="3" customWidth="1" width="17.625"/>
-    <col min="4" max="4" customWidth="1" width="17.625"/>
+    <col min="3" max="3" customWidth="1" width="17.6640625"/>
+    <col min="4" max="4" customWidth="1" width="17.6640625"/>
     <col min="5" max="5" customWidth="1" width="6"/>
     <col min="6" max="6" customWidth="1" width="6"/>
-    <col min="7" max="7" customWidth="1" width="8.125"/>
-    <col min="8" max="8" customWidth="1" width="35.5"/>
-    <col min="9" max="9" customWidth="1" width="135.375"/>
-    <col min="10" max="10" customWidth="1" width="122.875"/>
-    <col min="11" max="11" customWidth="1" width="51.875"/>
+    <col min="7" max="7" customWidth="1" width="8.109375"/>
+    <col min="8" max="8" customWidth="1" width="35.44140625"/>
+    <col min="9" max="9" customWidth="1" width="135.33203125"/>
+    <col min="10" max="10" customWidth="1" width="122.88671875"/>
+    <col min="11" max="11" customWidth="1" width="51.88671875"/>
     <col min="12" max="12" customWidth="1" width="80"/>
     <col min="13" max="13" customWidth="1" width="55"/>
-    <col min="14" max="14" customWidth="1" width="8.25"/>
-    <col min="15" max="15" customWidth="1" width="10.25"/>
+    <col min="14" max="14" customWidth="1" width="8.21875"/>
+    <col min="15" max="15" customWidth="1" width="10.21875"/>
     <col min="16" max="16" customWidth="1" width="6"/>
   </cols>
   <sheetData>
@@ -589,7 +496,7 @@
         <v>備註</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="14.4" customHeight="1">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -633,7 +540,7 @@
         <v>待處理</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="14.4" customHeight="1">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -677,7 +584,7 @@
         <v>待處理</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="14.4" customHeight="1">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -721,7 +628,7 @@
         <v>待處理</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="14.4" customHeight="1">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -765,7 +672,7 @@
         <v>待處理</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="14.4" customHeight="1">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -809,7 +716,7 @@
         <v>待處理</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="14.4" customHeight="1">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -853,7 +760,7 @@
         <v>待處理</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="14.4" customHeight="1">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -897,7 +804,7 @@
         <v>待處理</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="14.4" customHeight="1">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -941,7 +848,7 @@
         <v>待處理</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="14.4" customHeight="1">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -985,7 +892,7 @@
         <v>待處理</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="14.4" customHeight="1">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -1029,7 +936,7 @@
         <v>待處理</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="14.4" customHeight="1">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -1073,7 +980,7 @@
         <v>待處理</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="14.4" customHeight="1">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -1121,7 +1028,6 @@
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:P14"/>
   </ignoredErrors>
@@ -1130,23 +1036,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:Q56"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="6"/>
     <col min="2" max="2" customWidth="1" width="6"/>
-    <col min="3" max="3" customWidth="1" width="22.625"/>
-    <col min="4" max="4" customWidth="1" width="17.625"/>
+    <col min="3" max="3" customWidth="1" width="22.6640625"/>
+    <col min="4" max="4" customWidth="1" width="17.6640625"/>
     <col min="5" max="5" customWidth="1" width="6"/>
-    <col min="6" max="6" customWidth="1" width="8.25"/>
-    <col min="7" max="7" customWidth="1" width="8.125"/>
+    <col min="6" max="6" customWidth="1" width="8.21875"/>
+    <col min="7" max="7" customWidth="1" width="8.109375"/>
     <col min="8" max="8" customWidth="1" width="68"/>
     <col min="9" max="9" customWidth="1" width="150"/>
-    <col min="10" max="10" customWidth="1" width="120.375"/>
-    <col min="11" max="11" customWidth="1" width="64.5"/>
-    <col min="12" max="12" customWidth="1" width="114.125"/>
-    <col min="13" max="13" customWidth="1" width="62.75"/>
-    <col min="14" max="14" customWidth="1" width="8.25"/>
-    <col min="15" max="15" customWidth="1" width="10.25"/>
+    <col min="10" max="10" customWidth="1" width="120.33203125"/>
+    <col min="11" max="11" customWidth="1" width="64.44140625"/>
+    <col min="12" max="12" customWidth="1" width="114.109375"/>
+    <col min="13" max="13" customWidth="1" width="62.77734375"/>
+    <col min="14" max="14" customWidth="1" width="8.21875"/>
+    <col min="15" max="15" customWidth="1" width="10.21875"/>
     <col min="16" max="16" customWidth="1" width="6"/>
   </cols>
   <sheetData>
@@ -1204,8 +1110,11 @@
       <c r="P2" s="3" t="str">
         <v>備註</v>
       </c>
-    </row>
-    <row r="3">
+      <c r="Q2" s="3" t="str">
+        <v>主軸</v>
+      </c>
+    </row>
+    <row r="3" ht="14.4" customHeight="1">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -1248,8 +1157,11 @@
       <c r="N3" s="3" t="str">
         <v>待處理</v>
       </c>
-    </row>
-    <row r="4">
+      <c r="Q3" s="3" t="str">
+        <v>看得懂</v>
+      </c>
+    </row>
+    <row r="4" ht="14.4" customHeight="1">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -1292,8 +1204,11 @@
       <c r="N4" s="3" t="str">
         <v>待處理</v>
       </c>
-    </row>
-    <row r="5">
+      <c r="Q4" s="3" t="str">
+        <v>不容易錯</v>
+      </c>
+    </row>
+    <row r="5" ht="14.4" customHeight="1">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -1336,8 +1251,11 @@
       <c r="N5" s="3" t="str">
         <v>待處理</v>
       </c>
-    </row>
-    <row r="6">
+      <c r="Q5" s="3" t="str">
+        <v>做得快</v>
+      </c>
+    </row>
+    <row r="6" ht="14.4" customHeight="1">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -1380,8 +1298,11 @@
       <c r="N6" s="3" t="str">
         <v>待處理</v>
       </c>
-    </row>
-    <row r="7">
+      <c r="Q6" s="3" t="str">
+        <v>不容易錯</v>
+      </c>
+    </row>
+    <row r="7" ht="14.4" customHeight="1">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -1424,8 +1345,11 @@
       <c r="N7" s="3" t="str">
         <v>待處理</v>
       </c>
-    </row>
-    <row r="8">
+      <c r="Q7" s="3" t="str">
+        <v>不容易錯</v>
+      </c>
+    </row>
+    <row r="8" ht="14.4" customHeight="1">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -1468,8 +1392,11 @@
       <c r="N8" s="3" t="str">
         <v>待處理</v>
       </c>
-    </row>
-    <row r="9">
+      <c r="Q8" s="3" t="str">
+        <v>找得到</v>
+      </c>
+    </row>
+    <row r="9" ht="14.4" customHeight="1">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -1512,8 +1439,11 @@
       <c r="N9" s="3" t="str">
         <v>待處理</v>
       </c>
-    </row>
-    <row r="10">
+      <c r="Q9" s="3" t="str">
+        <v>看得懂</v>
+      </c>
+    </row>
+    <row r="10" ht="14.4" customHeight="1">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -1556,8 +1486,11 @@
       <c r="N10" s="3" t="str">
         <v>待處理</v>
       </c>
-    </row>
-    <row r="11">
+      <c r="Q10" s="3" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="11" ht="14.4" customHeight="1">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -1600,8 +1533,11 @@
       <c r="N11" s="3" t="str">
         <v>待處理</v>
       </c>
-    </row>
-    <row r="12">
+      <c r="Q11" s="3" t="str">
+        <v>出事能追回來</v>
+      </c>
+    </row>
+    <row r="12" ht="14.4" customHeight="1">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -1644,8 +1580,11 @@
       <c r="N12" s="3" t="str">
         <v>待處理</v>
       </c>
-    </row>
-    <row r="13">
+      <c r="Q12" s="3" t="str">
+        <v>看得懂</v>
+      </c>
+    </row>
+    <row r="13" ht="14.4" customHeight="1">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -1688,8 +1627,11 @@
       <c r="N13" s="3" t="str">
         <v>待處理</v>
       </c>
-    </row>
-    <row r="14">
+      <c r="Q13" s="3" t="str">
+        <v>做得快</v>
+      </c>
+    </row>
+    <row r="14" ht="14.4" customHeight="1">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -1731,22 +1673,2312 @@
       </c>
       <c r="N14" s="3" t="str">
         <v>待處理</v>
+      </c>
+      <c r="Q14" s="3" t="str">
+        <v>出事能追回來</v>
+      </c>
+    </row>
+    <row r="15" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A15" s="3">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C15" s="3" t="str">
+        <v>後台通用</v>
+      </c>
+      <c r="D15" s="3" t="str">
+        <v>News</v>
+      </c>
+      <c r="E15" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F15" s="3" t="str">
+        <v>資料</v>
+      </c>
+      <c r="G15" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H15" s="3" t="str">
+        <v>News table 缺 VideoUrl 欄位 (前台已上 iframe 渲染 wiring)</v>
+      </c>
+      <c r="I15" s="3" t="str">
+        <v>前台 news/info.vue 已加 iframe section 與 YouTube URL parser (Round 4 #102)，後台 admin News_AddEditView.vue 已加「影片網址」input + WebAPI.ts 簽章已帶 videoUrl，但 .NET API/DB schema 仍無對應欄位 — admin 存了會被 .NET 丟掉、前台 GetNewsDetail response 也不會有 videoUrl</v>
+      </c>
+      <c r="J15" s="3" t="str">
+        <v>News.cs entity 加 public string VideoUrl + NewsInputDataDto/NewsResultDto/NewsInputData/NewsResult value model 各加 VideoUrl + NewsTaskManager Insert/Update/Get 處理 + EF migration AddVideoUrlToNews，建議 nullable 容錯。同步在 iFare_Frontend_API 補 GetNewsDetail Result 含 VideoUrl</v>
+      </c>
+      <c r="K15" s="3" t="str">
+        <v>iFare_Backend_API/src/IFare_BDAPI.Core/Model/IFare/News.cs</v>
+      </c>
+      <c r="L15" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Backend_API/src/IFare_BDAPI.Core/Model/IFare/News.cs_x000d__x000d__x000d_
+iFare_Backend_API/src/IFare_BDAPI.Application/News/Dto/NewsInputDataDto.cs_x000d__x000d__x000d_
+iFare_Backend_API/src/IFare_BDAPI.Application/News/Dto/NewsResultDto.cs_x000d__x000d__x000d_
+iFare_Backend_API/src/IFare_BDAPI.Core/TaskManager/News/ValueModel/NewsInputData.cs_x000d__x000d__x000d_
+iFare_Backend_API/src/IFare_BDAPI.Core/TaskManager/News/ValueModel/NewsResult.cs_x000d__x000d__x000d_
+iFare_Backend_API/src/IFare_BDAPI.Core/TaskManager/News/NewsTaskManager.cs_x000d__x000d__x000d_
+EF migration: AddVideoUrlToNews</v>
+      </c>
+      <c r="M15" s="3" t="str">
+        <v>對應前台 #102 (Round 4)</v>
+      </c>
+      <c r="N15" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O15" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P15" s="3" t="str">
+        <v>需後端工程師處理；至少 6 .cs + 1 EF migration</v>
+      </c>
+      <c r="Q15" s="3" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="16" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A16" s="3">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C16" s="3" t="str">
+        <v>後台通用</v>
+      </c>
+      <c r="D16" s="3" t="str">
+        <v>API 呼叫層</v>
+      </c>
+      <c r="E16" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F16" s="3" t="str">
+        <v>程式碼</v>
+      </c>
+      <c r="G16" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H16" s="3" t="str">
+        <v>後台 baseURL 暫時硬寫正式 URL (補強 #8 環境變數化議題)</v>
+      </c>
+      <c r="I16" s="3" t="str">
+        <v>Round 4 為了讓本機開發能 reach 後台 API，AjaxRef.getBaseUrl() 暫時改成寫死 https://www.i-fare.org.tw/ifare_bdapi。原本 dev/prod 切換邏輯 (localhost:44311 / 內網 10.200.0.39) 已不堪用；當前所有人不論本機 / staging / prod 都打同一個 URL</v>
+      </c>
+      <c r="J16" s="3" t="str">
+        <v>改用 import.meta.env.VITE_API_BASE_URL；新增 .env.development (指 localhost) / .env.production (指 prod) / .env.example 範本；vite.config.ts 確認 base URL 注入；AjaxRef.getBaseUrl() 直接讀 env</v>
+      </c>
+      <c r="K16" s="3" t="str">
+        <v>src/plugins/AjaxRef.ts</v>
+      </c>
+      <c r="L16" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Backend/src/plugins/AjaxRef.ts_x000d__x000d__x000d_
+iFare_Backend/.env.development (新)_x000d__x000d__x000d_
+iFare_Backend/.env.production (新)_x000d__x000d__x000d_
+iFare_Backend/.env.example (新)_x000d__x000d__x000d_
+iFare_Backend/vite.config.ts (確認)</v>
+      </c>
+      <c r="M16" s="3" t="str">
+        <v>同 #8 主訴；Round 4 是治標</v>
+      </c>
+      <c r="N16" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O16" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P16" s="3" t="str">
+        <v>前台 nuxt.config.ts devProxy 也是同樣狀況 — 但 Nuxt 已有 runtimeConfig 機制，可直接搭 NUXT_FRONTEND_API_SERVER_BASE 環境變數</v>
+      </c>
+      <c r="Q16" s="3" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="17" ht="14.4" customHeight="1">
+      <c r="A17" s="3">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C17" s="3" t="str">
+        <v>後台通用</v>
+      </c>
+      <c r="D17" s="3" t="str">
+        <v>News</v>
+      </c>
+      <c r="E17" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F17" s="3" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G17" s="3" t="str">
+        <v>低</v>
+      </c>
+      <c r="H17" s="3" t="str">
+        <v>News SaveAction 表單驗證不完整</v>
+      </c>
+      <c r="I17" s="3" t="str">
+        <v>News_AddEditView.vue SaveAction() 只驗證 title 不可空，影片網址 / 上下架日期 / 內容 detail 都沒驗證。Round 4 加 videoUrl input 後若使用者貼非 YouTube URL，前台 iframe parser 會回傳空字串靜默失敗</v>
+      </c>
+      <c r="J17" s="3" t="str">
+        <v>加客戶端驗證：(1) videoUrl 非空時驗證符合 YouTube URL 格式 (regex) (2) 上架日期不可晚於下架日期 (3) detail 不可全空白。失敗時 ElMessage warning 顯示</v>
+      </c>
+      <c r="K17" s="3" t="str">
+        <v>src/views/News/News_AddEditView.vue</v>
+      </c>
+      <c r="L17" s="3" t="str">
+        <v>iFare_Backend/src/views/News/News_AddEditView.vue</v>
+      </c>
+      <c r="M17" s="3" t="str">
+        <v>前端先擋 invalid 輸入，避免送 API 才發現</v>
+      </c>
+      <c r="N17" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O17" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P17" s="3" t="str">
+        <v>同類問題可能在 ArticlesWelfare / FarePolicy 各 AddEdit 也有 — 可一起做</v>
+      </c>
+      <c r="Q17" s="3" t="str">
+        <v>不容易錯</v>
+      </c>
+    </row>
+    <row r="18" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A18" s="3">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C18" s="3" t="str">
+        <v>前台通用</v>
+      </c>
+      <c r="D18" s="3" t="str">
+        <v>Visitor</v>
+      </c>
+      <c r="E18" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F18" s="3" t="str">
+        <v>程式碼</v>
+      </c>
+      <c r="G18" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H18" s="3" t="str">
+        <v>Visitor SetVisitorRecord 端點 prod 404 (前台一直噴錯)</v>
+      </c>
+      <c r="I18" s="3" t="str">
+        <v>Round 4 切去正式 API 後，前台 dev server 持續噴 [WebAPI][POST] /Visitor/SetVisitorRecord statusCode: 404 — 看起來這個訪客追蹤端點在正式環境不存在 (或路徑改了)，每次首頁載入都打但都失敗</v>
+      </c>
+      <c r="J18" s="3" t="str">
+        <v>(1) 確認正式環境是否真有 SetVisitorRecord 路由 — 看 iFare_Frontend_API/src/IFare_API.Web.Host/Startup 註冊狀況 (2) 若無，後端新增 endpoint，或前台拿掉呼叫 (3) URL query 異常 ?router=/api/services/app/Visitor/SetVisitorRecord 看起來是 proxy 行為怪</v>
+      </c>
+      <c r="K18" s="3" t="str">
+        <v>iFare_Frontend/plugins/WebAPI.ts (前台)</v>
+      </c>
+      <c r="L18" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">需確認 iFare_Frontend_API/src/IFare_API.Application/Visitor/* 是否實作_x000d__x000d__x000d_
+或前台 plugins/WebAPI.ts 拿掉 SetVisitorRecord 呼叫</v>
+      </c>
+      <c r="M18" s="3" t="str">
+        <v>正式 API 回 404 但不影響其他功能</v>
+      </c>
+      <c r="N18" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O18" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P18" s="3" t="str">
+        <v>低/中 priority，不是 blocker，但 console 噪音影響 debug 體驗</v>
+      </c>
+      <c r="Q18" s="3" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="19" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A19" s="3">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C19" s="3" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="D19" s="3" t="str">
+        <v>CardTable / CardSearchParam</v>
+      </c>
+      <c r="E19" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F19" s="3" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G19" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H19" s="3" t="str">
+        <v>表格列寬分配邏輯複雜且不直觀，部分欄位未充分利用空間</v>
+      </c>
+      <c r="I19" s="3" t="str">
+        <v>CardTable.vue (L10-95) 欄位寬度判斷基於 prop name 含特定字串 (date_/state/id) 導致同性質欄位寬度不一致；操作按鈕固定 180px，寬螢幕浪費、窄螢幕擠壓</v>
+      </c>
+      <c r="J19" s="3" t="str">
+        <v>實作響應式欄位寬度策略 (flex:1 for content, 120px for action) 或建立 ColumnConfig 規範；統一各模組表格欄位排序 (id, 基本資訊, 狀態, 日期, 操作)</v>
+      </c>
+      <c r="K19" s="3" t="str">
+        <v>components/CardTable.vue + 各 DataListView.vue</v>
+      </c>
+      <c r="L19" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">src/components/CardTable.vue (L10-95)_x000d__x000d_
+src/views/*/DataListView.vue (15 個表格)</v>
+      </c>
+      <c r="M19" s="3" t="str">
+        <v>影響所有 15 個 DataListView，改善視覺層級與快速掃讀</v>
+      </c>
+      <c r="N19" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O19" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P19" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q19" s="3" t="str">
+        <v>看得懂</v>
+      </c>
+    </row>
+    <row r="20" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A20" s="3">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C20" s="3" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="D20" s="3" t="str">
+        <v>表單驗證</v>
+      </c>
+      <c r="E20" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F20" s="3" t="str">
+        <v>程式碼</v>
+      </c>
+      <c r="G20" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H20" s="3" t="str">
+        <v>必填欄位僅以 CSS class "required" 標記，無前端驗證邏輯</v>
+      </c>
+      <c r="I20" s="3" t="str">
+        <v>所有 AddEditView 用 &lt;label class="required"&gt; 紅色標記但未實現 el-form + el-form-item 驗證 rules；使用者可提交空欄位，只在後端收到錯誤</v>
+      </c>
+      <c r="J20" s="3" t="str">
+        <v>改用 el-form ref + rules (required: true, message)，SaveAction 前執行 validate()；或建立通用 FormValidator</v>
+      </c>
+      <c r="K20" s="3" t="str">
+        <v>News / Account / ArticlesWelfare / IFarePolicy / Collaborator AddEditView</v>
+      </c>
+      <c r="L20" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">src/views/News/News_AddEditView.vue (L142)_x000d__x000d_
+src/views/Account/Account_AddEditView.vue (L28-88)_x000d__x000d_
+src/views/Articles/Welfare/ArticlesWelfare_AddEditView.vue (L60-107)_x000d__x000d_
+src/views/IFare/Policy/IFarePolicy_AddEditView.vue (L28-139)_x000d__x000d_
+src/views/Collaborator/Collaborator_AddEditView.vue (L29-76)</v>
+      </c>
+      <c r="M20" s="3" t="str">
+        <v>影響 6+ 個新增編輯頁面，降低資料品質錯誤率 30%+</v>
+      </c>
+      <c r="N20" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O20" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P20" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q20" s="3" t="str">
+        <v>不容易錯</v>
+      </c>
+    </row>
+    <row r="21" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A21" s="3">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C21" s="3" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="D21" s="3" t="str">
+        <v>儲存反饋</v>
+      </c>
+      <c r="E21" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F21" s="3" t="str">
+        <v>視覺</v>
+      </c>
+      <c r="G21" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H21" s="3" t="str">
+        <v>儲存成功後缺乏視覺反饋或確認，部分頁面無確認訊息</v>
+      </c>
+      <c r="I21" s="3" t="str">
+        <v>News_AddEditView SaveAction 無 loading 狀態；Account_AddEditView 呼叫 API 後自動返回無成功訊息；IFareOfficeUnit 返回後找不到確認點。對比 Collaborator 有 Message 提示但不統一</v>
+      </c>
+      <c r="J21" s="3" t="str">
+        <v>統一所有 SaveAction：(1) 開始顯示 loading (2) 成功 $Message success (3) 失敗 error + 原因 (4) 2 秒後返回或停留</v>
+      </c>
+      <c r="K21" s="3" t="str">
+        <v>News / Account / IFareOfficeUnit AddEditView</v>
+      </c>
+      <c r="L21" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">src/views/News/News_AddEditView.vue (L142-170)_x000d__x000d_
+src/views/Account/Account_AddEditView.vue (L101-130)_x000d__x000d_
+src/views/IFare/OfficeUnit/IFareOfficeUnit_AddEditView.vue</v>
+      </c>
+      <c r="M21" s="3" t="str">
+        <v>使用者無法確認操作是否成功，易誤以為沒儲存</v>
+      </c>
+      <c r="N21" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O21" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P21" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q21" s="3" t="str">
+        <v>看得懂</v>
+      </c>
+    </row>
+    <row r="22" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A22" s="3">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C22" s="3" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="D22" s="3" t="str">
+        <v>CardSearchParam</v>
+      </c>
+      <c r="E22" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F22" s="3" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G22" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H22" s="3" t="str">
+        <v>搜尋條件清除功能缺失，重置需逐欄清空或刷新頁面</v>
+      </c>
+      <c r="I22" s="3" t="str">
+        <v>CardSearchParam.vue 只有「查詢」按鈕，無「清空」或「重置」；使用者要回列表全貌需手動清除每個欄位或重整頁面，URL query 仍會保留</v>
+      </c>
+      <c r="J22" s="3" t="str">
+        <v>在「查詢」旁加「重置」按鈕，清空所有 ref + router.replace({ query: {} })；可選加「儲存常用搜尋」</v>
+      </c>
+      <c r="K22" s="3" t="str">
+        <v>components/CardSearchParam.vue</v>
+      </c>
+      <c r="L22" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">src/components/CardSearchParam.vue (L119-129)_x000d__x000d_
+src/views/*/DataListView.vue</v>
+      </c>
+      <c r="M22" s="3" t="str">
+        <v>影響 News / Articles / IFare 等所有列表模組，提升尋找特定資料效率</v>
+      </c>
+      <c r="N22" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O22" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P22" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q22" s="3" t="str">
+        <v>做得快</v>
+      </c>
+    </row>
+    <row r="23" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A23" s="3">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C23" s="3" t="str">
+        <v>對話框</v>
+      </c>
+      <c r="D23" s="3" t="str">
+        <v>刪除確認</v>
+      </c>
+      <c r="E23" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F23" s="3" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G23" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H23" s="3" t="str">
+        <v>刪除確認對話框缺乏被刪除項目的識別資訊</v>
+      </c>
+      <c r="I23" s="3" t="str">
+        <v>DialogAlert.vue 只顯示「是否刪除資料？」通用訊息，未顯示被刪除項目的標題/ID/識別資訊；使用者點「刪除」後無法確認是否刪到正確的</v>
+      </c>
+      <c r="J23" s="3" t="str">
+        <v>改進 DialogAlert 支援 confirmData prop，動態顯示 "確定刪除『${title}』(ID: ${id})?"</v>
+      </c>
+      <c r="K23" s="3" t="str">
+        <v>components/DialogAlert.vue + CardTable.vue</v>
+      </c>
+      <c r="L23" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">src/components/DialogAlert.vue_x000d__x000d_
+src/components/CardTable.vue (L250-336)</v>
+      </c>
+      <c r="M23" s="3" t="str">
+        <v>誤刪風險高，尤其列表多項同時編輯時</v>
+      </c>
+      <c r="N23" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O23" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P23" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q23" s="3" t="str">
+        <v>不容易錯</v>
+      </c>
+    </row>
+    <row r="24" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A24" s="3">
+        <v>22</v>
+      </c>
+      <c r="B24" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C24" s="3" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="D24" s="3" t="str">
+        <v>CompItemSelect / CompRadioSelect</v>
+      </c>
+      <c r="E24" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F24" s="3" t="str">
+        <v>程式碼</v>
+      </c>
+      <c r="G24" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H24" s="3" t="str">
+        <v>新增頁面中下拉選單無預設值或預設值邏輯不清</v>
+      </c>
+      <c r="I24" s="3" t="str">
+        <v>CompItemSelect 在 mounted 載入資料但 defaultParams 為空時 modelValue 無預設選項；多 AddEditView 的多選欄位 (codeRecipientIDs 等) 在新增時為 undefined，無「請選擇」提示</v>
+      </c>
+      <c r="J24" s="3" t="str">
+        <v>AddEditView 中初始化多選陣列為 [] 而非 undefined；CompItemSelect 區分新增 vs 編輯，新增明確顯示 placeholder</v>
+      </c>
+      <c r="K24" s="3" t="str">
+        <v>components/CompItemSelect.vue + IFarePolicy AddEditView</v>
+      </c>
+      <c r="L24" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">src/components/CompItemSelect.vue (L42-176)_x000d__x000d_
+src/views/IFare/Policy/IFarePolicy_AddEditView.vue (L54-86)</v>
+      </c>
+      <c r="M24" s="3" t="str">
+        <v>減少使用者困惑，提升表單填寫速度</v>
+      </c>
+      <c r="N24" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O24" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P24" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q24" s="3" t="str">
+        <v>不容易錯</v>
+      </c>
+    </row>
+    <row r="25" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A25" s="3">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C25" s="3" t="str">
+        <v>檔案上傳</v>
+      </c>
+      <c r="D25" s="3" t="str">
+        <v>Collaborator / Articles</v>
+      </c>
+      <c r="E25" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F25" s="3" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H25" s="3" t="str">
+        <v>檔案上傳缺格式、大小預檢驗，僅 accept 屬性</v>
+      </c>
+      <c r="I25" s="3" t="str">
+        <v>Collaborator_AddEditView 只設 accept=".jpg,.png" 和 :limit="1" 未檢查大小 (提示 500KB)；ArticlesLazy 無限制 (:limit="0") 無大小驗證；上傳失敗訊息模糊</v>
+      </c>
+      <c r="J25" s="3" t="str">
+        <v>統一 :on-exceed + :on-change 回呼驗證 (大小 &lt; 500KB, 格式)；用 $Message warning 提示違規；禁用不符檔案的提交</v>
+      </c>
+      <c r="K25" s="3" t="str">
+        <v>Collaborator / ArticlesLazy AddEditView + DialogAddEditImg</v>
+      </c>
+      <c r="L25" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">src/views/Collaborator/Collaborator_AddEditView.vue (L56-75)_x000d__x000d_
+src/views/Articles/Lazy/ArticlesLazy_AddEditView.vue (L71-86)_x000d__x000d_
+src/components/DialogAddEditImg.vue (L27-43)</v>
+      </c>
+      <c r="M25" s="3" t="str">
+        <v>防止上傳無效檔案導致後端錯誤</v>
+      </c>
+      <c r="N25" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O25" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P25" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q25" s="3" t="str">
+        <v>不容易錯</v>
+      </c>
+    </row>
+    <row r="26" ht="14.4" customHeight="1">
+      <c r="A26" s="3">
+        <v>24</v>
+      </c>
+      <c r="B26" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C26" s="3" t="str">
+        <v>帳號管理</v>
+      </c>
+      <c r="D26" s="3" t="str">
+        <v>Account</v>
+      </c>
+      <c r="E26" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F26" s="3" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G26" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H26" s="3" t="str">
+        <v>新增帳號時權限和狀態可編輯，編輯時不可編輯，UI 無清晰說明</v>
+      </c>
+      <c r="I26" s="3" t="str">
+        <v>Account_AddEditView 區分新增 vs 編輯模式，編輯時某些欄位變 read-only (帳號 L38, 權限 L49, 狀態 L62) 但未用視覺/文字說明「此欄位不可修改」</v>
+      </c>
+      <c r="J26" s="3" t="str">
+        <v>(1) 為 read-only 欄位加灰底/虛線 (2) 加小字說明 "建立後不可修改" (3) 若編輯可更新狀態則加 disabled 或移除判斷</v>
+      </c>
+      <c r="K26" s="3" t="str">
+        <v>views/Account/Account_AddEditView.vue</v>
+      </c>
+      <c r="L26" s="3" t="str">
+        <v>src/views/Account/Account_AddEditView.vue (L28-99)</v>
+      </c>
+      <c r="M26" s="3" t="str">
+        <v>使用者理解帳號變更限制的規則</v>
+      </c>
+      <c r="N26" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O26" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P26" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q26" s="3" t="str">
+        <v>看得懂</v>
+      </c>
+    </row>
+    <row r="27" ht="14.4" customHeight="1">
+      <c r="A27" s="3">
+        <v>25</v>
+      </c>
+      <c r="B27" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C27" s="3" t="str">
+        <v>搜尋結果</v>
+      </c>
+      <c r="D27" s="3" t="str">
+        <v>空狀態提示</v>
+      </c>
+      <c r="E27" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F27" s="3" t="str">
+        <v>視覺</v>
+      </c>
+      <c r="G27" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H27" s="3" t="str">
+        <v>搜尋無結果時表格顯示空白，無 empty state 提示</v>
+      </c>
+      <c r="I27" s="3" t="str">
+        <v>CardTable.vue 依 tbData 產生表格，若無資料表格顯示空列，無「未找到符合條件的資料」訊息；使用者無法區別「資料載入中」vs「確實無結果」</v>
+      </c>
+      <c r="J27" s="3" t="str">
+        <v>檢查 tbData.length === 0 時顯示 empty-state 卡片 (圖示 + 文字)；或在 el-table 設 :empty-text</v>
+      </c>
+      <c r="K27" s="3" t="str">
+        <v>components/CardTable.vue</v>
+      </c>
+      <c r="L27" s="3" t="str">
+        <v>src/components/CardTable.vue (L4-9)</v>
+      </c>
+      <c r="M27" s="3" t="str">
+        <v>改善搜尋體驗，減少困惑</v>
+      </c>
+      <c r="N27" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O27" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P27" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q27" s="3" t="str">
+        <v>看得懂</v>
+      </c>
+    </row>
+    <row r="28" ht="14.4" customHeight="1">
+      <c r="A28" s="3">
+        <v>26</v>
+      </c>
+      <c r="B28" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C28" s="3" t="str">
+        <v>日期選擇</v>
+      </c>
+      <c r="D28" s="3" t="str">
+        <v>CompDateRangePicker</v>
+      </c>
+      <c r="E28" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F28" s="3" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G28" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H28" s="3" t="str">
+        <v>搜尋日期範圍選擇器無快捷選項 (本週/本月/最近 30 天)</v>
+      </c>
+      <c r="I28" s="3" t="str">
+        <v>CompDateRangePicker.vue 僅基礎日期範圍選擇，無快捷按鈕；使用者要搜「最近 7 天新增資料」需手動計算日期</v>
+      </c>
+      <c r="J28" s="3" t="str">
+        <v>在 el-date-picker 加 :shortcuts prop 提供 "今天/本週/本月/最近 30 天/最近 90 天"</v>
+      </c>
+      <c r="K28" s="3" t="str">
+        <v>components/CompDateRangePicker.vue</v>
+      </c>
+      <c r="L28" s="3" t="str">
+        <v>src/components/CompDateRangePicker.vue</v>
+      </c>
+      <c r="M28" s="3" t="str">
+        <v>提升搜尋快速性，減少輸入步驟</v>
+      </c>
+      <c r="N28" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O28" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P28" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q28" s="3" t="str">
+        <v>做得快</v>
+      </c>
+    </row>
+    <row r="29" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A29" s="3">
+        <v>27</v>
+      </c>
+      <c r="B29" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C29" s="3" t="str">
+        <v>表單</v>
+      </c>
+      <c r="D29" s="3" t="str">
+        <v>欄位提示</v>
+      </c>
+      <c r="E29" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F29" s="3" t="str">
+        <v>視覺</v>
+      </c>
+      <c r="G29" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H29" s="3" t="str">
+        <v>部分欄位缺詳細說明或範例，placeholder 不夠清晰</v>
+      </c>
+      <c r="I29" s="3" t="str">
+        <v>IFarePolicy 主管機關 placeholder 僅 "請輸入內容" 未說明範例；News videoUrl 提示 "貼上 YouTube 網址" 但未示完整格式</v>
+      </c>
+      <c r="J29" s="3" t="str">
+        <v>(1) 複雜欄位加 el-tooltip 或 help icon (2) 補 placeholder 範例 "例: 教育局" (3) 新增可選欄位說明區塊 (small font, info color)</v>
+      </c>
+      <c r="K29" s="3" t="str">
+        <v>IFarePolicy / News AddEditView</v>
+      </c>
+      <c r="L29" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">src/views/IFare/Policy/IFarePolicy_AddEditView.vue (L110-116)_x000d__x000d_
+src/views/News/News_AddEditView.vue (L37-44)</v>
+      </c>
+      <c r="M29" s="3" t="str">
+        <v>減少使用者困惑，降低後續編輯次數</v>
+      </c>
+      <c r="N29" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O29" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P29" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q29" s="3" t="str">
+        <v>看得懂</v>
+      </c>
+    </row>
+    <row r="30" ht="14.4" customHeight="1">
+      <c r="A30" s="3">
+        <v>28</v>
+      </c>
+      <c r="B30" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C30" s="3" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="D30" s="3" t="str">
+        <v>CardTable 分頁</v>
+      </c>
+      <c r="E30" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F30" s="3" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G30" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H30" s="3" t="str">
+        <v>分頁大小變更後未重設為第 1 頁，導致頁碼超出範圍</v>
+      </c>
+      <c r="I30" s="3" t="str">
+        <v>CardTable.vue 的 el-pagination 允許變更 pageSize (10/50/100)，但若在第 5 頁時從 10 改 50，currentPage 仍 5 (新總頁可能只有 3)，表格顯示空白</v>
+      </c>
+      <c r="J30" s="3" t="str">
+        <v>el-pagination 的 @page-size-change 事件中重設 currentPage = 1</v>
+      </c>
+      <c r="K30" s="3" t="str">
+        <v>components/CardTable.vue</v>
+      </c>
+      <c r="L30" s="3" t="str">
+        <v>src/components/CardTable.vue (L178-185)</v>
+      </c>
+      <c r="M30" s="3" t="str">
+        <v>影響大資料量列表操作</v>
+      </c>
+      <c r="N30" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O30" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P30" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q30" s="3" t="str">
+        <v>做得快</v>
+      </c>
+    </row>
+    <row r="31" ht="14.4" customHeight="1">
+      <c r="A31" s="3">
+        <v>29</v>
+      </c>
+      <c r="B31" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C31" s="3" t="str">
+        <v>側邊欄</v>
+      </c>
+      <c r="D31" s="3" t="str">
+        <v>AppAside</v>
+      </c>
+      <c r="E31" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F31" s="3" t="str">
+        <v>視覺</v>
+      </c>
+      <c r="G31" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H31" s="3" t="str">
+        <v>編輯/詳情頁返回列表後，側邊欄選單項目高亮未更新</v>
+      </c>
+      <c r="I31" s="3" t="str">
+        <v>AppAside.vue 依 defaultActive prop (route.name) 設高亮，但若從列表進編輯頁 (route.name 變) 再返回，側邊欄高亮仍停在編輯項目</v>
+      </c>
+      <c r="J31" s="3" t="str">
+        <v>加 watch(props.route, ...) 更新 defaultActive；或用 route.matched 找上層模組路由名</v>
+      </c>
+      <c r="K31" s="3" t="str">
+        <v>components/AppAside.vue</v>
+      </c>
+      <c r="L31" s="3" t="str">
+        <v>src/components/AppAside.vue (L15-17)</v>
+      </c>
+      <c r="M31" s="3" t="str">
+        <v>改善視覺導航狀態的準確性</v>
+      </c>
+      <c r="N31" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O31" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P31" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q31" s="3" t="str">
+        <v>找得到</v>
+      </c>
+    </row>
+    <row r="32" ht="14.4" customHeight="1">
+      <c r="A32" s="3">
+        <v>30</v>
+      </c>
+      <c r="B32" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C32" s="3" t="str">
+        <v>麵包屑導覽</v>
+      </c>
+      <c r="D32" s="3" t="str">
+        <v>AppHeader</v>
+      </c>
+      <c r="E32" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F32" s="3" t="str">
+        <v>視覺</v>
+      </c>
+      <c r="G32" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H32" s="3" t="str">
+        <v>麵包屑在多層子路由時未正確顯示完整路徑</v>
+      </c>
+      <c r="I32" s="3" t="str">
+        <v>AppHeader.vue refreshRouteInfo 邏輯依賴 route.meta.title_parent / urlName_parent，若路由超過 2 層 (/IFare/Policy/Edit) 或 meta 不全，麵包屑不完整</v>
+      </c>
+      <c r="J32" s="3" t="str">
+        <v>遍歷整個 route.matched 陣列動態構建麵包屑，不依賴單一 meta</v>
+      </c>
+      <c r="K32" s="3" t="str">
+        <v>components/AppHeader.vue</v>
+      </c>
+      <c r="L32" s="3" t="str">
+        <v>src/components/AppHeader.vue (L100-124)</v>
+      </c>
+      <c r="M32" s="3" t="str">
+        <v>複雜路由導航時的使用者定位</v>
+      </c>
+      <c r="N32" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O32" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P32" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q32" s="3" t="str">
+        <v>找得到</v>
+      </c>
+    </row>
+    <row r="33" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A33" s="3">
+        <v>31</v>
+      </c>
+      <c r="B33" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C33" s="3" t="str">
+        <v>WebAPI</v>
+      </c>
+      <c r="D33" s="3" t="str">
+        <v>錯誤處理</v>
+      </c>
+      <c r="E33" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F33" s="3" t="str">
+        <v>程式碼</v>
+      </c>
+      <c r="G33" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H33" s="3" t="str">
+        <v>API 錯誤回應的統一處理缺失，各頁面自行判斷 errCode/errMsg</v>
+      </c>
+      <c r="I33" s="3" t="str">
+        <v>所有 WebAPI 呼叫重複: let _resData = res.data || "error"; if (_resData == "error") return console.error(...); let _res = _resData.result; if (_res.errCode != 0) ...；無統一錯誤提示</v>
+      </c>
+      <c r="J33" s="3" t="str">
+        <v>WebAPI.ts 的 ajax() 統一檢查 errCode，若 !== 0 自動 $Message error 再 callback；或建立共用 interceptor</v>
+      </c>
+      <c r="K33" s="3" t="str">
+        <v>plugins/WebAPI.ts + 所有 SaveAction</v>
+      </c>
+      <c r="L33" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">src/plugins/WebAPI.ts (852 行全文)_x000d__x000d_
+所有 AddEditView 的 SaveAction</v>
+      </c>
+      <c r="M33" s="3" t="str">
+        <v>減少程式碼重複，提升可維護性</v>
+      </c>
+      <c r="N33" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O33" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P33" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q33" s="3" t="str">
+        <v>不容易錯</v>
+      </c>
+    </row>
+    <row r="34" ht="14.4" customHeight="1">
+      <c r="A34" s="3">
+        <v>32</v>
+      </c>
+      <c r="B34" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C34" s="3" t="str">
+        <v>圖片管理</v>
+      </c>
+      <c r="D34" s="3" t="str">
+        <v>ImgManager / DialogAddEditImg</v>
+      </c>
+      <c r="E34" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F34" s="3" t="str">
+        <v>視覺</v>
+      </c>
+      <c r="G34" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H34" s="3" t="str">
+        <v>圖片編輯對話框未顯示上傳進度，缺乏編輯前後對比</v>
+      </c>
+      <c r="I34" s="3" t="str">
+        <v>DialogAddEditImg 上傳檔案時無進度條；編輯圖片屬性後點「確定」未顯示儲存進度；無法預覽編輯前後變化</v>
+      </c>
+      <c r="J34" s="3" t="str">
+        <v>(1) el-upload 加 :show-upload-list="true" + 進度視覺 (2) SaveAction 顯示 loading (3) 編輯模式並排顯示舊圖/新圖預覽</v>
+      </c>
+      <c r="K34" s="3" t="str">
+        <v>components/DialogAddEditImg.vue</v>
+      </c>
+      <c r="L34" s="3" t="str">
+        <v>src/components/DialogAddEditImg.vue (L27-50)</v>
+      </c>
+      <c r="M34" s="3" t="str">
+        <v>提升使用者對編輯結果的信心</v>
+      </c>
+      <c r="N34" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O34" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P34" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q34" s="3" t="str">
+        <v>看得懂</v>
+      </c>
+    </row>
+    <row r="35" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A35" s="3">
+        <v>33</v>
+      </c>
+      <c r="B35" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C35" s="3" t="str">
+        <v>帳號變更密碼</v>
+      </c>
+      <c r="D35" s="3" t="str">
+        <v>Personal_DetailView</v>
+      </c>
+      <c r="E35" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F35" s="3" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G35" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H35" s="3" t="str">
+        <v>個人檔案頁面缺「變更密碼」入口，需知道專屬路徑</v>
+      </c>
+      <c r="I35" s="3" t="str">
+        <v>Personal_DetailView 僅顯示帳號/名稱/權限，無密碼欄位；Personal_ChangePwdView 存在但若路由未設好，使用者難找到入口</v>
+      </c>
+      <c r="J35" s="3" t="str">
+        <v>Personal_DetailView 個人卡片加「變更密碼」按鈕導向 ChangePwdView；或 Edit 頁面下方加密碼欄位區塊</v>
+      </c>
+      <c r="K35" s="3" t="str">
+        <v>views/Personal/Personal_DetailView.vue</v>
+      </c>
+      <c r="L35" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">src/views/Personal/Personal_DetailView.vue_x000d__x000d_
+src/views/Personal/Personal_ChangePwdView.vue</v>
+      </c>
+      <c r="M35" s="3" t="str">
+        <v>提升帳號安全性管理的可用性</v>
+      </c>
+      <c r="N35" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O35" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P35" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q35" s="3" t="str">
+        <v>找得到</v>
+      </c>
+    </row>
+    <row r="36" ht="14.4" customHeight="1">
+      <c r="A36" s="3">
+        <v>34</v>
+      </c>
+      <c r="B36" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C36" s="3" t="str">
+        <v>Code 代碼管理</v>
+      </c>
+      <c r="D36" s="3" t="str">
+        <v>Domicile / Policy / Keyword</v>
+      </c>
+      <c r="E36" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F36" s="3" t="str">
+        <v>程式碼</v>
+      </c>
+      <c r="G36" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H36" s="3" t="str">
+        <v>新增代碼時未檢查重複，可能導致代碼衝突</v>
+      </c>
+      <c r="I36" s="3" t="str">
+        <v>CodePolicy_AddEditView 新增時無前端檢查重複；使用者輸入「教育」後提交，若後端返回重複錯誤需重新編輯</v>
+      </c>
+      <c r="J36" s="3" t="str">
+        <v>SaveAction 前呼叫搜尋 API (e.g., GetCodePolicy with name filter)，若有結果則「名稱已存在」並禁用提交</v>
+      </c>
+      <c r="K36" s="3" t="str">
+        <v>views/Code/*/AddEditView.vue</v>
+      </c>
+      <c r="L36" s="3" t="str">
+        <v>src/views/Code/*/AddEditView.vue (所有代碼管理)</v>
+      </c>
+      <c r="M36" s="3" t="str">
+        <v>減少後端衝突錯誤，提升資料一致性</v>
+      </c>
+      <c r="N36" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O36" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P36" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q36" s="3" t="str">
+        <v>不容易錯</v>
+      </c>
+    </row>
+    <row r="37" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A37" s="3">
+        <v>35</v>
+      </c>
+      <c r="B37" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C37" s="3" t="str">
+        <v>狀態管理</v>
+      </c>
+      <c r="D37" s="3" t="str">
+        <v>資料狀態 vs 上架狀態</v>
+      </c>
+      <c r="E37" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F37" s="3" t="str">
+        <v>視覺</v>
+      </c>
+      <c r="G37" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H37" s="3" t="str">
+        <v>表格中「資料狀態」(啟用/停用) 與「上架狀態」(上架/下架) 易混淆</v>
+      </c>
+      <c r="I37" s="3" t="str">
+        <v>News_DataListView 與 IFarePolicy_DataListView 都有 state_data 欄位 (啟用/停用)；IFarePolicy 額外有上架狀態篩選，兩個狀態未視覺區分，新手易混淆</v>
+      </c>
+      <c r="J37" s="3" t="str">
+        <v>(1) 表格用不同顏色 icon/badge (綠 = 啟用/上架，紅 = 停用/下架) (2) 表頭加 tooltip 說明差異 (3) 篩選時分開欄位</v>
+      </c>
+      <c r="K37" s="3" t="str">
+        <v>CardTable / CardSearchParam</v>
+      </c>
+      <c r="L37" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">src/components/CardTable.vue (L81-84)_x000d__x000d_
+src/components/CardSearchParam.vue (L100-117)</v>
+      </c>
+      <c r="M37" s="3" t="str">
+        <v>減少狀態誤操作，尤其批量編輯時</v>
+      </c>
+      <c r="N37" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O37" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P37" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q37" s="3" t="str">
+        <v>看得懂</v>
+      </c>
+    </row>
+    <row r="38" ht="14.4" customHeight="1">
+      <c r="A38" s="3">
+        <v>36</v>
+      </c>
+      <c r="B38" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C38" s="3" t="str">
+        <v>登入頁面</v>
+      </c>
+      <c r="D38" s="3" t="str">
+        <v>LoginView</v>
+      </c>
+      <c r="E38" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F38" s="3" t="str">
+        <v>視覺</v>
+      </c>
+      <c r="G38" s="3" t="str">
+        <v>低</v>
+      </c>
+      <c r="H38" s="3" t="str">
+        <v>登入頁面密碼欄位無「大小寫鎖定」警告</v>
+      </c>
+      <c r="I38" s="3" t="str">
+        <v>LoginView 密碼輸入框支援 show-password 但無 Caps Lock 偵測警告；使用者若無意中開 Caps Lock 會輸入錯誤密碼而渾然不覺</v>
+      </c>
+      <c r="J38" s="3" t="str">
+        <v>監聽密碼欄位 keydown，偵測 e.getModifierState("CapsLock")，若為真顯示 warning icon/text</v>
+      </c>
+      <c r="K38" s="3" t="str">
+        <v>views/LoginView.vue</v>
+      </c>
+      <c r="L38" s="3" t="str">
+        <v>src/views/LoginView.vue (L26-32)</v>
+      </c>
+      <c r="M38" s="3" t="str">
+        <v>改善登入體驗，減少忘記密碼查詢</v>
+      </c>
+      <c r="N38" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O38" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P38" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q38" s="3" t="str">
+        <v>不容易錯</v>
+      </c>
+    </row>
+    <row r="39" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A39" s="3">
+        <v>37</v>
+      </c>
+      <c r="B39" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C39" s="3" t="str">
+        <v>HTML 編輯器</v>
+      </c>
+      <c r="D39" s="3" t="str">
+        <v>CompHtmlEditor</v>
+      </c>
+      <c r="E39" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F39" s="3" t="str">
+        <v>程式碼</v>
+      </c>
+      <c r="G39" s="3" t="str">
+        <v>低</v>
+      </c>
+      <c r="H39" s="3" t="str">
+        <v>HTML 編輯器在編輯模式載入內容時延遲明顯，無 loading 提示</v>
+      </c>
+      <c r="I39" s="3" t="str">
+        <v>News / ArticlesWelfare 的 editorValue 初值綁定到編輯器，若後端內容很長或編輯器初始化慢，使用者看到空白編輯器直到內容出現</v>
+      </c>
+      <c r="J39" s="3" t="str">
+        <v>(1) 編輯器掛載時顯示 skeleton/loading (2) editorValue 更新前顯示 placeholder (3) 加 onInitialize callback 確認準備就緒再填充</v>
+      </c>
+      <c r="K39" s="3" t="str">
+        <v>components/CompHtmlEditor.vue</v>
+      </c>
+      <c r="L39" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">src/components/CompHtmlEditor.vue (L1-80)_x000d__x000d_
+src/views/News/News_AddEditView.vue (L134-135)</v>
+      </c>
+      <c r="M39" s="3" t="str">
+        <v>編輯體驗改善，低使用頻率所以低優先</v>
+      </c>
+      <c r="N39" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O39" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P39" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q39" s="3" t="str">
+        <v>看得懂</v>
+      </c>
+    </row>
+    <row r="40" ht="14.4" customHeight="1">
+      <c r="A40" s="3">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C40" s="3" t="str">
+        <v>無權限頁</v>
+      </c>
+      <c r="D40" s="3" t="str">
+        <v>NoPermission</v>
+      </c>
+      <c r="E40" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F40" s="3" t="str">
+        <v>視覺</v>
+      </c>
+      <c r="G40" s="3" t="str">
+        <v>低</v>
+      </c>
+      <c r="H40" s="3" t="str">
+        <v>NoPermission 頁面過於簡陋，無返回導航或建議</v>
+      </c>
+      <c r="I40" s="3" t="str">
+        <v>NoPermission.vue 只顯示「您無此權限!」，無返回首頁、聯絡管理員等建議或按鈕；使用者被卡住後不知所措</v>
+      </c>
+      <c r="J40" s="3" t="str">
+        <v>補「請聯絡管理員申請權限」說明，加「返回首頁」按鈕，可選加「聯絡管理員」郵件連結</v>
+      </c>
+      <c r="K40" s="3" t="str">
+        <v>views/NoPermission.vue</v>
+      </c>
+      <c r="L40" s="3" t="str">
+        <v>src/views/NoPermission.vue</v>
+      </c>
+      <c r="M40" s="3" t="str">
+        <v>提升錯誤頁面的可用性，但使用頻率低</v>
+      </c>
+      <c r="N40" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O40" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P40" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q40" s="3" t="str">
+        <v>看得懂</v>
+      </c>
+    </row>
+    <row r="41" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A41" s="3">
+        <v>39</v>
+      </c>
+      <c r="B41" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C41" s="3" t="str">
+        <v>後台通用</v>
+      </c>
+      <c r="D41" s="3" t="str">
+        <v>Dashboard / 角色化首頁</v>
+      </c>
+      <c r="E41" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F41" s="3" t="str">
+        <v>設計</v>
+      </c>
+      <c r="G41" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H41" s="3" t="str">
+        <v>角色化 Dashboard — 不同角色 (管理者 / 操作員 / 客服) 首頁不同</v>
+      </c>
+      <c r="I41" s="3" t="str">
+        <v>目前所有 user 進後台看到同一個首頁，但實際上：管理者要看整體 KPI 與系統健康；操作員要看待辦清單與快速建立入口；客服要看查詢工具與最近處理紀錄</v>
+      </c>
+      <c r="J41" s="3" t="str">
+        <v>依 user.role 動態切換 Dashboard 內容版面：(1) 管理者 → KPI 卡 + 異常告警 (2) 操作員 → 今日待辦 + 快速新增 (3) 客服 → 全站搜尋 + 最近 X 筆 query 紀錄。建立 Dashboard 設定文件</v>
+      </c>
+      <c r="K41" s="3" t="str">
+        <v>views/HomeView.vue / 新建 DashboardAdminView / DashboardOperatorView / DashboardCSView</v>
+      </c>
+      <c r="L41" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">src/views/HomeView.vue_x000d__x000d_
+新增 src/views/Dashboard/AdminView.vue / OperatorView.vue / CSView.vue_x000d__x000d_
+src/router/index.ts (Home route 改判 role)</v>
+      </c>
+      <c r="M41" s="3" t="str">
+        <v>對應使用者主軸「尊重不同角色」</v>
+      </c>
+      <c r="N41" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O41" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P41" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q41" s="3" t="str">
+        <v>看得懂</v>
+      </c>
+    </row>
+    <row r="42" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A42" s="3">
+        <v>40</v>
+      </c>
+      <c r="B42" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C42" s="3" t="str">
+        <v>後台通用</v>
+      </c>
+      <c r="D42" s="3" t="str">
+        <v>Dashboard / 待辦清單</v>
+      </c>
+      <c r="E42" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F42" s="3" t="str">
+        <v>設計</v>
+      </c>
+      <c r="G42" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H42" s="3" t="str">
+        <v>「今日待辦」首頁區塊 — 一打開就看到該處理什麼</v>
+      </c>
+      <c r="I42" s="3" t="str">
+        <v>目前首頁無「需要我關注」的整合入口，使用者要進到各模組才知道有沒有東西。例如：未審核的文章、即將下架的政策、新增帳號待覆核</v>
+      </c>
+      <c r="J42" s="3" t="str">
+        <v>Dashboard 加 .card-todo 區塊，aggregate 跨模組待處理項目 (待審 News / 即將下架 Policy / 待覆核 Account)，每項可直接點擊跳到該模組。需要新 API endpoint /Dashboard/GetMyTodos</v>
+      </c>
+      <c r="K42" s="3" t="str">
+        <v>views/HomeView 或 Dashboard 群組</v>
+      </c>
+      <c r="L42" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">src/views/HomeView.vue_x000d__x000d_
+後端新增 /Dashboard/GetMyTodos endpoint</v>
+      </c>
+      <c r="M42" s="3" t="str">
+        <v>使用者明確要求「把今天要處理什麼放最前面」</v>
+      </c>
+      <c r="N42" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O42" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P42" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q42" s="3" t="str">
+        <v>看得懂</v>
+      </c>
+    </row>
+    <row r="43" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A43" s="3">
+        <v>41</v>
+      </c>
+      <c r="B43" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C43" s="3" t="str">
+        <v>後台通用</v>
+      </c>
+      <c r="D43" s="3" t="str">
+        <v>Dashboard / 資訊組織</v>
+      </c>
+      <c r="E43" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F43" s="3" t="str">
+        <v>設計</v>
+      </c>
+      <c r="G43" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H43" s="3" t="str">
+        <v>Dashboard 卡片化分區 — KPI / 異常 / 待審 / 待處理 各自獨立</v>
+      </c>
+      <c r="I43" s="3" t="str">
+        <v>若 Dashboard 把所有資訊堆在一起，使用者一打開資訊轟炸無從下手。需要明確分區、視覺層級、不同顏色強度</v>
+      </c>
+      <c r="J43" s="3" t="str">
+        <v>Dashboard 分 4 區：(1) KPI 卡 (本月新增/啟用數，藍色) (2) 異常告警 (錯誤、過期，紅色) (3) 待審核 (橘色，可點即跳) (4) 待處理 (灰色，可點即跳)。每區可摺疊</v>
+      </c>
+      <c r="K43" s="3" t="str">
+        <v>views/Dashboard/* + components/Card*</v>
+      </c>
+      <c r="L43" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">src/views/Dashboard/*.vue_x000d__x000d_
+src/components/CardKPI.vue (新)_x000d__x000d_
+src/components/CardAlert.vue (新)_x000d__x000d_
+src/components/CardPending.vue (新)</v>
+      </c>
+      <c r="M43" s="3" t="str">
+        <v>使用者明確要求「KPI、異常、待審核、待處理分開」、「不要一打開就資訊轟炸」</v>
+      </c>
+      <c r="N43" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O43" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P43" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q43" s="3" t="str">
+        <v>看得懂</v>
+      </c>
+    </row>
+    <row r="44" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A44" s="3">
+        <v>45</v>
+      </c>
+      <c r="B44" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C44" s="3" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="D44" s="3" t="str">
+        <v>欄位 / 標籤命名</v>
+      </c>
+      <c r="E44" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F44" s="3" t="str">
+        <v>視覺</v>
+      </c>
+      <c r="G44" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H44" s="3" t="str">
+        <v>欄位 / 標籤白話化規範 — 改掉系統術語</v>
+      </c>
+      <c r="I44" s="3" t="str">
+        <v>目前部分欄位用程式術語：「isEnabled」、「state_data」、「UpdateUserId」、「discontinuedTime」直接顯示給使用者；中文 label 也用「資料狀態」這種抽象名稱，新人需要猜</v>
+      </c>
+      <c r="J44" s="3" t="str">
+        <v>建立術語對照表：isEnabled → 啟用、discontinuedTime → 下架時間、UpdateUserId → 最後修改者、state_data → 啟用狀態。整理 docs/iFare_欄位術語對照.md，所有 view template 套用</v>
+      </c>
+      <c r="K44" s="3" t="str">
+        <v>所有 views + 新增 docs/iFare_欄位術語對照.md</v>
+      </c>
+      <c r="L44" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">所有 src/views/*/AddEditView.vue + DataListView.vue_x000d__x000d_
+新增 docs/iFare_欄位術語對照.md</v>
+      </c>
+      <c r="M44" s="3" t="str">
+        <v>使用者明確要求「欄位名稱講人話，不要只寫系統術語」</v>
+      </c>
+      <c r="N44" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O44" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P44" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q44" s="3" t="str">
+        <v>看得懂</v>
+      </c>
+    </row>
+    <row r="45" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A45" s="3">
+        <v>49</v>
+      </c>
+      <c r="B45" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C45" s="3" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="D45" s="3" t="str">
+        <v>狀態流程視覺化</v>
+      </c>
+      <c r="E45" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F45" s="3" t="str">
+        <v>視覺</v>
+      </c>
+      <c r="G45" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H45" s="3" t="str">
+        <v>狀態流程視覺化 — 進度條 / step indicator 讓人知道現在卡在哪</v>
+      </c>
+      <c r="I45" s="3" t="str">
+        <v>News / Policy 等內容有「草稿 → 待審 → 上架 → 下架」流程，但目前只用「啟用/停用」單一 boolean 表達，使用者無法快速看出資料目前位於哪階段</v>
+      </c>
+      <c r="J45" s="3" t="str">
+        <v>建立 CompStateFlow.vue 元件，吃 currentStage + stages 陣列，渲染水平 step indicator。News/Policy/Articles AddEditView 與 DetailView 都加上方狀態列</v>
+      </c>
+      <c r="K45" s="3" t="str">
+        <v>components/CompStateFlow.vue (新) + 多 AddEditView / DetailView</v>
+      </c>
+      <c r="L45" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">新增 src/components/CompStateFlow.vue_x000d__x000d_
+src/views/News/News_AddEditView.vue + ItemDetailView.vue_x000d__x000d_
+src/views/IFare/Policy/* (同)_x000d__x000d_
+src/views/Articles/Welfare/* (同)</v>
+      </c>
+      <c r="M45" s="3" t="str">
+        <v>使用者明確要求「狀態流程要明確，讓人知道現在卡在哪」</v>
+      </c>
+      <c r="N45" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O45" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P45" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q45" s="3" t="str">
+        <v>看得懂</v>
+      </c>
+    </row>
+    <row r="46" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A46" s="3">
+        <v>44</v>
+      </c>
+      <c r="B46" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C46" s="3" t="str">
+        <v>後台通用</v>
+      </c>
+      <c r="D46" s="3" t="str">
+        <v>全域搜尋</v>
+      </c>
+      <c r="E46" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F46" s="3" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G46" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H46" s="3" t="str">
+        <v>全域快速搜尋與跳轉 (Cmd+K 風格) — 補強 #6</v>
+      </c>
+      <c r="I46" s="3" t="str">
+        <v>#6 指出後台缺全域搜尋。具體做法：實作鍵盤快捷鍵 (Ctrl+K / Cmd+K) 開啟搜尋彈窗，可以模糊搜：(1) 模組名 (新增News) (2) 已有資料 (3) 帳號</v>
+      </c>
+      <c r="J46" s="3" t="str">
+        <v>用 Element Plus el-dialog + el-autocomplete 實作 GlobalSearch 元件；支援 fuzzy match (例如 fuse.js)；列出常用 action shortcut；ESC 關閉</v>
+      </c>
+      <c r="K46" s="3" t="str">
+        <v>components/GlobalSearch.vue (新) + App.vue 引入</v>
+      </c>
+      <c r="L46" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">新增 src/components/GlobalSearch.vue_x000d__x000d_
+src/App.vue (引入 + 鍵盤監聽)_x000d__x000d_
+新增 src/composables/useShortcuts.ts</v>
+      </c>
+      <c r="M46" s="3" t="str">
+        <v>使用者明確要求「搜尋、篩選、排序不要藏太深」</v>
+      </c>
+      <c r="N46" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O46" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P46" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q46" s="3" t="str">
+        <v>找得到</v>
+      </c>
+    </row>
+    <row r="47" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A47" s="3">
+        <v>42</v>
+      </c>
+      <c r="B47" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C47" s="3" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="D47" s="3" t="str">
+        <v>表格批次操作</v>
+      </c>
+      <c r="E47" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F47" s="3" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G47" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H47" s="3" t="str">
+        <v>表格批次操作支援 — 多選 + 批次刪除 / 啟用 / 匯出</v>
+      </c>
+      <c r="I47" s="3" t="str">
+        <v>CardTable 目前每筆資料只能個別點操作；要刪 50 筆要點 50 次。缺多選核取 + 批次工具列</v>
+      </c>
+      <c r="J47" s="3" t="str">
+        <v>CardTable 加 :show-selection-column 顯示多選 checkbox；表格上方出現批次操作 bar (已選 N 筆 [批次刪除] [批次啟用] [批次匯出])。WebAPI.ts 加 BatchDelete/BatchUpdate 對應端點</v>
+      </c>
+      <c r="K47" s="3" t="str">
+        <v>components/CardTable.vue + plugins/WebAPI.ts</v>
+      </c>
+      <c r="L47" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">src/components/CardTable.vue (加 selection column)_x000d__x000d_
+src/components/CardBatchAction.vue (新)_x000d__x000d_
+src/plugins/WebAPI.ts (BatchDelete / BatchUpdate)_x000d__x000d_
+後端 .NET 對應 batch endpoints</v>
+      </c>
+      <c r="M47" s="3" t="str">
+        <v>使用者明確要求「批次操作要明顯」</v>
+      </c>
+      <c r="N47" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O47" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P47" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q47" s="3" t="str">
+        <v>做得快</v>
+      </c>
+    </row>
+    <row r="48" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A48" s="3">
+        <v>43</v>
+      </c>
+      <c r="B48" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C48" s="3" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="D48" s="3" t="str">
+        <v>搜尋條件儲存</v>
+      </c>
+      <c r="E48" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F48" s="3" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G48" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H48" s="3" t="str">
+        <v>儲存常用搜尋條件 — 命名 + 快速套用</v>
+      </c>
+      <c r="I48" s="3" t="str">
+        <v>使用者要查「最近一週新增的福利文章」每次都要重設條件；目前無記憶或儲存功能</v>
+      </c>
+      <c r="J48" s="3" t="str">
+        <v>CardSearchParam 加「儲存此搜尋」按鈕，命名後存到 user.savedFilters (localStorage 或 backend)；加「快速套用」下拉選最近搜尋</v>
+      </c>
+      <c r="K48" s="3" t="str">
+        <v>components/CardSearchParam.vue + stores/user.ts</v>
+      </c>
+      <c r="L48" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">src/components/CardSearchParam.vue_x000d__x000d_
+src/stores/user.ts (savedFilters 欄位)_x000d__x000d_
+後端可選 endpoint /Account/SaveFilter (跨裝置同步)</v>
+      </c>
+      <c r="M48" s="3" t="str">
+        <v>使用者明確要求「常用條件可儲存」</v>
+      </c>
+      <c r="N48" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O48" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P48" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q48" s="3" t="str">
+        <v>做得快</v>
+      </c>
+    </row>
+    <row r="49" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A49" s="3">
+        <v>53</v>
+      </c>
+      <c r="B49" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C49" s="3" t="str">
+        <v>效能</v>
+      </c>
+      <c r="D49" s="3" t="str">
+        <v>大列表優化</v>
+      </c>
+      <c r="E49" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F49" s="3" t="str">
+        <v>效能</v>
+      </c>
+      <c r="G49" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H49" s="3" t="str">
+        <v>大列表 lazy load / 虛擬滾動 — 萬筆資料不卡</v>
+      </c>
+      <c r="I49" s="3" t="str">
+        <v>目前 CardTable 一次渲染所有 row，pageSize 100 已會卡；若資料數萬筆且使用者沒搜尋，瀏覽器會明顯停頓</v>
+      </c>
+      <c r="J49" s="3" t="str">
+        <v>(1) 強制最大 pageSize 限制 (建議 100) (2) 用 el-table 內建 virtual scroll (height + overflow) 或第三方 vue-virtual-scroller (3) 後端 API 強制 SkipCount/MaxResultCount，server-side 分頁</v>
+      </c>
+      <c r="K49" s="3" t="str">
+        <v>components/CardTable.vue + 各 DataListView</v>
+      </c>
+      <c r="L49" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">src/components/CardTable.vue (加 virtual scroll)_x000d__x000d_
+src/views/*/DataListView.vue_x000d__x000d_
+後端 confirm pagination</v>
+      </c>
+      <c r="M49" s="3" t="str">
+        <v>使用者明確要求「不卡、不等，就是最基本的人性化」、「大列表分頁、快取、延遲載入」</v>
+      </c>
+      <c r="N49" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O49" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P49" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q49" s="3" t="str">
+        <v>做得快</v>
+      </c>
+    </row>
+    <row r="50" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A50" s="3">
+        <v>54</v>
+      </c>
+      <c r="B50" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C50" s="3" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="D50" s="3" t="str">
+        <v>匯出 / 匯入進度</v>
+      </c>
+      <c r="E50" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F50" s="3" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G50" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H50" s="3" t="str">
+        <v>匯入匯出進度提示 — 大檔不會以為當機</v>
+      </c>
+      <c r="I50" s="3" t="str">
+        <v>若使用者匯出整份 News/Policy 為 CSV 或匯入 100 筆 Account，目前無進度條或預估時間；按下後使用者只能等</v>
+      </c>
+      <c r="J50" s="3" t="str">
+        <v>建立 CompExportProgress 元件 (彈出 dialog 顯示 X% + ETA)；後端用 SignalR 或 polling endpoint 回報進度；完成後 toast 通知 + 下載連結</v>
+      </c>
+      <c r="K50" s="3" t="str">
+        <v>components/CompExportProgress.vue (新) + 各 DataListView</v>
+      </c>
+      <c r="L50" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">新增 src/components/CompExportProgress.vue_x000d__x000d_
+src/views/*/DataListView.vue (匯出按鈕觸發)_x000d__x000d_
+後端 .NET 加 Hub or polling endpoint</v>
+      </c>
+      <c r="M50" s="3" t="str">
+        <v>使用者明確要求「匯出匯入要給進度與完成提示」</v>
+      </c>
+      <c r="N50" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O50" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P50" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q50" s="3" t="str">
+        <v>做得快</v>
+      </c>
+    </row>
+    <row r="51" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A51" s="3">
+        <v>46</v>
+      </c>
+      <c r="B51" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C51" s="3" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="D51" s="3" t="str">
+        <v>危險操作預覽</v>
+      </c>
+      <c r="E51" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F51" s="3" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G51" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H51" s="3" t="str">
+        <v>危險操作影響範圍預覽 — 「將影響 X 筆 / Y 個關聯」</v>
+      </c>
+      <c r="I51" s="3" t="str">
+        <v>刪除某一筆 Code (e.g., Domicile)，可能連動到 50 筆 Policy 失去戶籍地連結；目前無事前提示，按下「確認」後才知道副作用</v>
+      </c>
+      <c r="J51" s="3" t="str">
+        <v>危險操作前先呼叫 backend GetImpactCount API，DialogAlert 顯示「將影響 50 筆福利政策的戶籍地關聯，確定？」；危險操作清單：刪除 Code / 變更 Account 權限 / 變更 Policy 上下架</v>
+      </c>
+      <c r="K51" s="3" t="str">
+        <v>components/DialogAlert.vue + plugins/WebAPI.ts</v>
+      </c>
+      <c r="L51" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">src/components/DialogAlert.vue (加 impact info 顯示)_x000d__x000d_
+src/plugins/WebAPI.ts (各 GetImpactCount)_x000d__x000d_
+後端 .NET 對應 endpoints</v>
+      </c>
+      <c r="M51" s="3" t="str">
+        <v>使用者明確要求「危險操作前提醒影響範圍」</v>
+      </c>
+      <c r="N51" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O51" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P51" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q51" s="3" t="str">
+        <v>不容易錯</v>
+      </c>
+    </row>
+    <row r="52" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A52" s="3">
+        <v>47</v>
+      </c>
+      <c r="B52" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C52" s="3" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="D52" s="3" t="str">
+        <v>預設值規範</v>
+      </c>
+      <c r="E52" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F52" s="3" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G52" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H52" s="3" t="str">
+        <v>合理預設值規範 — Radio / Select 預設選項、日期預設今天</v>
+      </c>
+      <c r="I52" s="3" t="str">
+        <v>新增 News 時 ReleaseTime / DiscontinuedTime 是空 (使用者要手動點開選日期)；新增 Account 時權限欄位無預設選項；多選欄位無預設常用組合</v>
+      </c>
+      <c r="J52" s="3" t="str">
+        <v>建立預設值規範文件，AddEditView 各欄位都應有合理預設：(1) 上架日期 = 今天 (2) 下架日期 = 今天 + 1 年 (3) 帳號權限 = 操作員 (4) 啟用狀態 = 啟用</v>
+      </c>
+      <c r="K52" s="3" t="str">
+        <v>各 AddEditView + 新增 docs/iFare_預設值規範.md</v>
+      </c>
+      <c r="L52" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">所有 src/views/*/AddEditView.vue 的 ref 初始值_x000d__x000d_
+新增 docs/iFare_預設值規範.md</v>
+      </c>
+      <c r="M52" s="3" t="str">
+        <v>使用者明確要求「有預設值就給合理預設值」</v>
+      </c>
+      <c r="N52" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O52" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P52" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q52" s="3" t="str">
+        <v>不容易錯</v>
+      </c>
+    </row>
+    <row r="53" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A53" s="3">
+        <v>48</v>
+      </c>
+      <c r="B53" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C53" s="3" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="D53" s="3" t="str">
+        <v>錯誤訊息引導</v>
+      </c>
+      <c r="E53" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F53" s="3" t="str">
+        <v>視覺</v>
+      </c>
+      <c r="G53" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H53" s="3" t="str">
+        <v>錯誤訊息附下一步建議 — 不只說「失敗」，還說該怎麼辦</v>
+      </c>
+      <c r="I53" s="3" t="str">
+        <v>目前錯誤多是 "errMsg" 直接拋出 (e.g., "無法儲存")；使用者不知道是 (a) 必填漏 (b) 格式錯 (c) 後端問題；缺修復建議</v>
+      </c>
+      <c r="J53" s="3" t="str">
+        <v>錯誤訊息規範化：(1) 標題：說現象 (e.g., "無法儲存") (2) 描述：說原因 (e.g., "標題不可空") (3) 建議：說怎麼解 (e.g., "請補上「標題」欄位後再試一次")。可選加「複製錯誤碼回報 IT」按鈕</v>
+      </c>
+      <c r="K53" s="3" t="str">
+        <v>components/DialogAlert / Message + plugins/WebAPI 統一處理</v>
+      </c>
+      <c r="L53" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">src/plugins/WebAPI.ts (錯誤格式包裝)_x000d__x000d_
+各 SaveAction (改用結構化錯誤)_x000d__x000d_
+新增 src/composables/useErrorMessage.ts</v>
+      </c>
+      <c r="M53" s="3" t="str">
+        <v>使用者明確要求「不只是顯示錯誤，要告訴他下一步怎麼做」</v>
+      </c>
+      <c r="N53" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O53" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P53" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q53" s="3" t="str">
+        <v>不容易錯</v>
+      </c>
+    </row>
+    <row r="54" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A54" s="3">
+        <v>50</v>
+      </c>
+      <c r="B54" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C54" s="3" t="str">
+        <v>後台通用</v>
+      </c>
+      <c r="D54" s="3" t="str">
+        <v>操作紀錄 (audit log)</v>
+      </c>
+      <c r="E54" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F54" s="3" t="str">
+        <v>維護性</v>
+      </c>
+      <c r="G54" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H54" s="3" t="str">
+        <v>操作紀錄 (audit log) UI — 誰、何時、做了什麼</v>
+      </c>
+      <c r="I54" s="3" t="str">
+        <v>後台所有操作 (新增/編輯/刪除/權限變更) 目前無集中查詢介面；要知道「上週誰刪了某筆 News」沒辦法</v>
+      </c>
+      <c r="J54" s="3" t="str">
+        <v>新增 AuditLogView，列出所有後台操作 (時間 / user / action / target / 詳情 diff)。後端 .NET ABP 已有 AuditLog 機制，只需要做前端 UI 列表 + 篩選 (時間範圍 / user / action type)</v>
+      </c>
+      <c r="K54" s="3" t="str">
+        <v>views/AuditLog/AuditLogView.vue (新) + 路由</v>
+      </c>
+      <c r="L54" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">新增 src/views/AuditLog/AuditLogView.vue_x000d__x000d_
+src/router/index.ts (加 /AuditLog)_x000d__x000d_
+WebAPI.ts (加 GetAuditLog)_x000d__x000d_
+.NET 確認 ABP AuditLog 已開</v>
+      </c>
+      <c r="M54" s="3" t="str">
+        <v>使用者明確要求「操作紀錄清楚」</v>
+      </c>
+      <c r="N54" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O54" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P54" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q54" s="3" t="str">
+        <v>出事能追回來</v>
+      </c>
+    </row>
+    <row r="55" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A55" s="3">
+        <v>51</v>
+      </c>
+      <c r="B55" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C55" s="3" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="D55" s="3" t="str">
+        <v>變更歷史 / 版本</v>
+      </c>
+      <c r="E55" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F55" s="3" t="str">
+        <v>維護性</v>
+      </c>
+      <c r="G55" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H55" s="3" t="str">
+        <v>重要變更歷史 (版本 / diff) — 文章、政策、設定可看歷史版本</v>
+      </c>
+      <c r="I55" s="3" t="str">
+        <v>News / Policy / Articles 文章編輯後，原版本完全消失；若編錯想復原沒辦法；無法看「上週這篇文章原本長怎樣」</v>
+      </c>
+      <c r="J55" s="3" t="str">
+        <v>AddEditView 加「版本歷史」按鈕，彈窗列出 N 個歷史版本 (時間 / user)，可預覽 + 一鍵還原。後端 .NET 需加 NewsHistory / PolicyHistory table 在 Update 時 snapshot</v>
+      </c>
+      <c r="K55" s="3" t="str">
+        <v>各 AddEditView + 新增 DialogVersionHistory + 後端</v>
+      </c>
+      <c r="L55" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">所有重要 src/views/*/AddEditView.vue_x000d__x000d_
+新增 src/components/DialogVersionHistory.vue_x000d__x000d_
+後端 .NET News/Policy/Articles 加 *_History entity + Update 時 snapshot</v>
+      </c>
+      <c r="M55" s="3" t="str">
+        <v>使用者明確要求「重要變更可追溯」</v>
+      </c>
+      <c r="N55" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O55" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P55" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q55" s="3" t="str">
+        <v>出事能追回來</v>
+      </c>
+    </row>
+    <row r="56" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A56" s="3">
+        <v>52</v>
+      </c>
+      <c r="B56" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C56" s="3" t="str">
+        <v>後台通用</v>
+      </c>
+      <c r="D56" s="3" t="str">
+        <v>軟刪除 + 復原</v>
+      </c>
+      <c r="E56" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F56" s="3" t="str">
+        <v>維護性</v>
+      </c>
+      <c r="G56" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H56" s="3" t="str">
+        <v>軟刪除 + 復原機制 — 30 天內可救回</v>
+      </c>
+      <c r="I56" s="3" t="str">
+        <v>目前刪除是 hard delete，誤刪後資料完全消失；後端 ABP 框架支援 ISoftDelete，但前端無「資源回收筒」UI</v>
+      </c>
+      <c r="J56" s="3" t="str">
+        <v>(1) 後端確認所有 Entity 改 ISoftDelete (改 IsDeleted flag) (2) 前端各模組加「已刪除資料」tab 列出 30 天內被刪除的 (3) 列表加「復原」按鈕。Cron job 30 天後 hard delete</v>
+      </c>
+      <c r="K56" s="3" t="str">
+        <v>前後端整合 + 各 DataListView</v>
+      </c>
+      <c r="L56" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">後端 .NET Entity 改 ISoftDelete_x000d__x000d_
+各 src/views/*/DataListView.vue 加 [已刪除] tab_x000d__x000d_
+新增 src/views/Trash/TrashView.vue_x000d__x000d_
+.NET cron job 處理 30 天後 hard delete</v>
+      </c>
+      <c r="M56" s="3" t="str">
+        <v>使用者明確要求「能取消、返回、復原的地方盡量有」、「不要讓人一按就無法挽回」</v>
+      </c>
+      <c r="N56" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O56" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P56" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q56" s="3" t="str">
+        <v>出事能追回來</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q56"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P99"/>
+  <dimension ref="A1:P133"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="6"/>
     <col min="2" max="2" customWidth="1" width="6"/>
@@ -1759,7 +3991,7 @@
     <col min="9" max="9" customWidth="1" width="35"/>
     <col min="10" max="10" customWidth="1" width="25"/>
     <col min="11" max="11" customWidth="1" width="22"/>
-    <col min="12" max="12" customWidth="1" width="40.125"/>
+    <col min="12" max="12" customWidth="1" width="40.109375"/>
     <col min="13" max="13" customWidth="1" width="30"/>
     <col min="14" max="14" customWidth="1" width="8"/>
     <col min="15" max="15" customWidth="1" width="10"/>
@@ -1822,53 +4054,53 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A3" s="4">
+      <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="str">
+      <c r="B3" s="3" t="str">
         <v>~</v>
       </c>
-      <c r="C3" s="5" t="str">
+      <c r="C3" s="3" t="str">
         <v>i-Fare 福利查詢</v>
       </c>
-      <c r="D3" s="5" t="str">
+      <c r="D3" s="3" t="str">
         <v>搜尋介面</v>
       </c>
-      <c r="E3" s="5" t="str">
+      <c r="E3" s="3" t="str">
         <v>修復</v>
       </c>
-      <c r="F3" s="5" t="str">
+      <c r="F3" s="3" t="str">
         <v>互動</v>
       </c>
-      <c r="G3" s="5" t="str">
+      <c r="G3" s="3" t="str">
         <v>高</v>
       </c>
-      <c r="H3" s="5" t="str">
+      <c r="H3" s="3" t="str">
         <v>篩選條件不完整時無錯誤訊息</v>
       </c>
-      <c r="I3" s="5" t="str">
+      <c r="I3" s="3" t="str">
         <v>按鈕變灰(disabled)但使用者不知道缺哪個欄位，Search()直接 return false 無任何提示</v>
       </c>
-      <c r="J3" s="5" t="str">
+      <c r="J3" s="3" t="str">
         <v>加入未填欄位紅框提示 + 錯誤文字</v>
       </c>
-      <c r="K3" s="5" t="str">
+      <c r="K3" s="3" t="str">
         <v>pages/ifare.vue</v>
       </c>
-      <c r="L3" s="5" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/ifare.vue_x000d_
+      <c r="L3" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">pages/ifare.vue_x000d__x000d__x000d_
 assets/style/_font.scss</v>
       </c>
-      <c r="M3" s="5" t="str">
+      <c r="M3" s="3" t="str">
         <v>無錯誤訊息確認；但「(必填)」標示已存在於 _font.scss</v>
       </c>
-      <c r="N3" s="6" t="str">
+      <c r="N3" s="3" t="str">
         <v>部分修正</v>
       </c>
-      <c r="O3" s="6" t="str">
+      <c r="O3" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P3" s="6" t="str">
+      <c r="P3" s="3" t="str">
         <v>已移除三項都空時的 disabled 條件（pages/ifare.vue:75 + pages/ifare/result.vue 三處），改用 hasAnyCondition 顯示「未填條件將顯示最新福利」提示。改採「不阻擋 + 引導文案」策略，與原建議「未填欄位紅框 + 錯誤文字」方向不同。</v>
       </c>
     </row>
@@ -1907,7 +4139,7 @@
         <v>pages/ifare.vue</v>
       </c>
       <c r="L4" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/ifare.vue_x000d_
+        <v xml:space="preserve">pages/ifare.vue_x000d__x000d__x000d_
 assets/style/components/_appBody_ifare.scss</v>
       </c>
       <c r="M4" s="3" t="str">
@@ -2008,8 +4240,8 @@
         <v>pages/ifare.vue</v>
       </c>
       <c r="L6" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/ifare.vue_x000d_
-assets/style/components/_appBody_ifare.scss_x000d_
+        <v xml:space="preserve">pages/ifare.vue_x000d__x000d__x000d_
+assets/style/components/_appBody_ifare.scss_x000d__x000d__x000d_
 assets/style/rwd/_rwd_ifare.scss</v>
       </c>
       <c r="M6" s="3" t="str">
@@ -2060,7 +4292,7 @@
         <v>pages/ifare.vue</v>
       </c>
       <c r="L7" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/ifare.vue_x000d_
+        <v xml:space="preserve">pages/ifare.vue_x000d__x000d__x000d_
 assets/style/components/_appBody_ifare.scss</v>
       </c>
       <c r="M7" s="3" t="str">
@@ -2111,7 +4343,7 @@
         <v>pages/ifare/result.vue</v>
       </c>
       <c r="L8" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/ifare/result.vue_x000d_
+        <v xml:space="preserve">pages/ifare/result.vue_x000d__x000d__x000d_
 assets/style/rwd/_rwd_ifare.scss</v>
       </c>
       <c r="M8" s="3" t="str">
@@ -2162,8 +4394,8 @@
         <v>pages/ifare/result.vue</v>
       </c>
       <c r="L9" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/ifare/result.vue_x000d_
-assets/style/components/_appBodyChild_ifare.scss_x000d_
+        <v xml:space="preserve">pages/ifare/result.vue_x000d__x000d__x000d_
+assets/style/components/_appBodyChild_ifare.scss_x000d__x000d__x000d_
 assets/style/rwd/_rwd_ifare.scss</v>
       </c>
       <c r="M9" s="3" t="str">
@@ -2214,7 +4446,7 @@
         <v>pages/ifare/result.vue</v>
       </c>
       <c r="L10" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/ifare/result.vue_x000d_
+        <v xml:space="preserve">pages/ifare/result.vue_x000d__x000d__x000d_
 assets/style/components/_appBodyChild_ifare.scss</v>
       </c>
       <c r="M10" s="3" t="str">
@@ -2231,54 +4463,54 @@
       </c>
     </row>
     <row r="11" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A11" s="5">
+      <c r="A11" s="3">
         <v>9</v>
       </c>
-      <c r="B11" s="5" t="str">
-        <v>V</v>
-      </c>
-      <c r="C11" s="5" t="str">
+      <c r="B11" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C11" s="3" t="str">
         <v>i-Fare 福利查詢</v>
       </c>
-      <c r="D11" s="5" t="str">
+      <c r="D11" s="3" t="str">
         <v>查詢結果</v>
       </c>
-      <c r="E11" s="5" t="str">
+      <c r="E11" s="3" t="str">
         <v>提升</v>
       </c>
-      <c r="F11" s="5" t="str">
+      <c r="F11" s="3" t="str">
         <v>視覺</v>
       </c>
-      <c r="G11" s="5" t="str">
+      <c r="G11" s="3" t="str">
         <v>低</v>
       </c>
-      <c r="H11" s="5" t="str">
+      <c r="H11" s="3" t="str">
         <v>搜尋結果數量不夠醒目</v>
       </c>
-      <c r="I11" s="5" t="str">
+      <c r="I11" s="3" t="str">
         <v>結果數量 font-size:14px font-weight:400，周圍文字 opacity:0.5</v>
       </c>
-      <c r="J11" s="5" t="str">
+      <c r="J11" s="3" t="str">
         <v>頂部大字顯示 + 計數動畫</v>
       </c>
-      <c r="K11" s="5" t="str">
+      <c r="K11" s="3" t="str">
         <v>pages/ifare/result.vue</v>
       </c>
-      <c r="L11" s="5" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/ifare/result.vue_x000d_
-assets/style/components/_appBodyChild_ifare.scss_x000d_
+      <c r="L11" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">pages/ifare/result.vue_x000d__x000d__x000d_
+assets/style/components/_appBodyChild_ifare.scss_x000d__x000d__x000d_
 assets/style/_font.scss</v>
       </c>
-      <c r="M11" s="5" t="str">
+      <c r="M11" s="3" t="str">
         <v>確認字體小且無強調</v>
       </c>
-      <c r="N11" s="6" t="str">
+      <c r="N11" s="3" t="str">
         <v>部分修正</v>
       </c>
-      <c r="O11" s="6" t="str">
+      <c r="O11" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P11" s="6" t="str">
+      <c r="P11" s="3" t="str">
         <v>結果摘要從「{{count}}」改寫為「共找到 X 項，僅顯示前 X 筆」(pages/ifare/result.vue)；.result-total 從 inline-flex + ::before 結構簡化為 inline；新增 .result-summary-note 樣式。原訴求「頂部大字 + 計數動畫」尚未做。</v>
       </c>
     </row>
@@ -2317,7 +4549,7 @@
         <v>pages/ifare/result.vue</v>
       </c>
       <c r="L12" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/ifare/result.vue_x000d_
+        <v xml:space="preserve">pages/ifare/result.vue_x000d__x000d__x000d_
 assets/style/components/_appBodyChild_ifare.scss</v>
       </c>
       <c r="M12" s="3" t="str">
@@ -2368,7 +4600,7 @@
         <v>pages/ifare/info.vue</v>
       </c>
       <c r="L13" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/ifare/info.vue_x000d_
+        <v xml:space="preserve">pages/ifare/info.vue_x000d__x000d__x000d_
 assets/style/components/_appBodyChild_ifare.scss</v>
       </c>
       <c r="M13" s="3" t="str">
@@ -2419,7 +4651,7 @@
         <v>pages/ifare/info.vue</v>
       </c>
       <c r="L14" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/ifare/info.vue_x000d_
+        <v xml:space="preserve">pages/ifare/info.vue_x000d__x000d__x000d_
 assets/style/components/_button.scss</v>
       </c>
       <c r="M14" s="3" t="str">
@@ -2470,8 +4702,8 @@
         <v>pages/ifare/contact.vue</v>
       </c>
       <c r="L15" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/ifare/contact.vue_x000d_
-assets/style/components/_appBodyChild_ifare.scss_x000d_
+        <v xml:space="preserve">pages/ifare/contact.vue_x000d__x000d__x000d_
+assets/style/components/_appBodyChild_ifare.scss_x000d__x000d__x000d_
 assets/style/rwd/_rwd_ifare.scss</v>
       </c>
       <c r="M15" s="3" t="str">
@@ -2522,8 +4754,8 @@
         <v>pages/ifare/contact.vue</v>
       </c>
       <c r="L16" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/ifare/contact.vue_x000d_
-assets/style/components/_appBodyChild_ifare.scss_x000d_
+        <v xml:space="preserve">pages/ifare/contact.vue_x000d__x000d__x000d_
+assets/style/components/_appBodyChild_ifare.scss_x000d__x000d__x000d_
 assets/style/rwd/_rwd_ifare.scss</v>
       </c>
       <c r="M16" s="3" t="str">
@@ -2590,106 +4822,106 @@
       </c>
     </row>
     <row r="18" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A18" s="7">
+      <c r="A18" s="3">
         <v>16</v>
       </c>
-      <c r="B18" s="8" t="str">
-        <v>V</v>
-      </c>
-      <c r="C18" s="8" t="str">
+      <c r="B18" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C18" s="3" t="str">
         <v>首頁</v>
       </c>
-      <c r="D18" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E18" s="8" t="str">
+      <c r="D18" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E18" s="3" t="str">
         <v>修復</v>
       </c>
-      <c r="F18" s="8" t="str">
+      <c r="F18" s="3" t="str">
         <v>視覺</v>
       </c>
-      <c r="G18" s="8" t="str">
+      <c r="G18" s="3" t="str">
         <v>低</v>
       </c>
-      <c r="H18" s="8" t="str">
+      <c r="H18" s="3" t="str">
         <v>頁面切換無轉場動畫</v>
       </c>
-      <c r="I18" s="8" t="str">
+      <c r="I18" s="3" t="str">
         <v>layouts/default.vue 用 &lt;slot /&gt; 無 &lt;Transition&gt;，nuxt.config 無 pageTransition</v>
       </c>
-      <c r="J18" s="8" t="str">
+      <c r="J18" s="3" t="str">
         <v>加入 Nuxt &lt;transition&gt; 過場效果</v>
       </c>
-      <c r="K18" s="8" t="str">
+      <c r="K18" s="3" t="str">
         <v>layouts/default.vue</v>
       </c>
-      <c r="L18" s="8" t="str" xml:space="preserve">
-        <v xml:space="preserve">layouts/default.vue_x000d_
-nuxt.config.ts_x000d_
+      <c r="L18" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">layouts/default.vue_x000d__x000d__x000d_
+nuxt.config.ts_x000d__x000d__x000d_
 assets/style/_transition.scss</v>
       </c>
-      <c r="M18" s="8" t="str">
+      <c r="M18" s="3" t="str">
         <v>確認無任何 transition 設定</v>
       </c>
-      <c r="N18" s="9" t="str">
+      <c r="N18" s="3" t="str">
         <v>已修正</v>
       </c>
-      <c r="O18" s="9" t="str">
+      <c r="O18" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P18" s="9" t="str">
+      <c r="P18" s="3" t="str">
         <v>app.vue 加 &lt;NuxtPage :transition="{ name: 'page', mode: 'out-in' }" /&gt;；_animation.scss 新增 .page-enter/leave-active 與 .layout-enter/leave-active keyframes（opacity + translateY，純 GPU 屬性）。</v>
       </c>
     </row>
     <row r="19" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A19" s="8">
+      <c r="A19" s="3">
         <v>17</v>
       </c>
-      <c r="B19" s="8" t="str">
-        <v>V</v>
-      </c>
-      <c r="C19" s="8" t="str">
+      <c r="B19" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C19" s="3" t="str">
         <v>首頁</v>
       </c>
-      <c r="D19" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E19" s="8" t="str">
+      <c r="D19" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E19" s="3" t="str">
         <v>修復</v>
       </c>
-      <c r="F19" s="8" t="str">
+      <c r="F19" s="3" t="str">
         <v>視覺</v>
       </c>
-      <c r="G19" s="8" t="str">
+      <c r="G19" s="3" t="str">
         <v>中</v>
       </c>
-      <c r="H19" s="8" t="str">
+      <c r="H19" s="3" t="str">
         <v>Footer 社群連結呈現不一致</v>
       </c>
-      <c r="I19" s="8" t="str">
+      <c r="I19" s="3" t="str">
         <v>LINE 用 styled button (.btn-line)，Facebook 用純文字圖示連結 (.ic-facebook-before)</v>
       </c>
-      <c r="J19" s="8" t="str">
+      <c r="J19" s="3" t="str">
         <v>統一為相同呈現方式</v>
       </c>
-      <c r="K19" s="8" t="str">
+      <c r="K19" s="3" t="str">
         <v>components/AppFooter.vue</v>
       </c>
-      <c r="L19" s="8" t="str" xml:space="preserve">
-        <v xml:space="preserve">components/AppFooter.vue_x000d_
-assets/style/components/_appFooter.scss_x000d_
+      <c r="L19" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">components/AppFooter.vue_x000d__x000d__x000d_
+assets/style/components/_appFooter.scss_x000d__x000d__x000d_
 assets/style/_font.scss</v>
       </c>
-      <c r="M19" s="8" t="str">
+      <c r="M19" s="3" t="str">
         <v>兩個社群連結完全不同的 HTML 結構和樣式</v>
       </c>
-      <c r="N19" s="9" t="str">
+      <c r="N19" s="3" t="str">
         <v>已修正</v>
       </c>
-      <c r="O19" s="9" t="str">
+      <c r="O19" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P19" s="9" t="str">
+      <c r="P19" s="3" t="str">
         <v>LINE 與 Facebook 統一為 .btn-social 白底按鈕（含 icon + 深綠字），Facebook 從 .ic-facebook-before 文字連結改為 button 結構並與 LINE 並排。LINE icon 修正為品牌綠 #06C755（Line-Logo.svg fill），Facebook 改用品牌藍 #1877F2（新增 Facebook-Logo-color.svg）。</v>
       </c>
     </row>
@@ -2728,9 +4960,9 @@
         <v>pages/index.vue</v>
       </c>
       <c r="L20" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/index.vue_x000d_
-assets/style/components/_appBody_index.scss_x000d_
-assets/style/_animation.scss_x000d_
+        <v xml:space="preserve">pages/index.vue_x000d__x000d__x000d_
+assets/style/components/_appBody_index.scss_x000d__x000d__x000d_
+assets/style/_animation.scss_x000d__x000d__x000d_
 assets/style/rwd/_rwd_index.scss</v>
       </c>
       <c r="M20" s="3" t="str">
@@ -2781,8 +5013,8 @@
         <v>pages/index.vue</v>
       </c>
       <c r="L21" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/index.vue_x000d_
-assets/style/components/_appBody_index.scss_x000d_
+        <v xml:space="preserve">pages/index.vue_x000d__x000d__x000d_
+assets/style/components/_appBody_index.scss_x000d__x000d__x000d_
 assets/style/rwd/_rwd_index.scss</v>
       </c>
       <c r="M21" s="3" t="str">
@@ -2833,7 +5065,7 @@
         <v>pages/index.vue</v>
       </c>
       <c r="L22" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/index.vue_x000d_
+        <v xml:space="preserve">pages/index.vue_x000d__x000d__x000d_
 assets/style/components/_appBody_index.scss</v>
       </c>
       <c r="M22" s="3" t="str">
@@ -2884,8 +5116,8 @@
         <v>components/AppFooter.vue</v>
       </c>
       <c r="L23" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/index.vue_x000d_
-components/AppFooter.vue_x000d_
+        <v xml:space="preserve">pages/index.vue_x000d__x000d__x000d_
+components/AppFooter.vue_x000d__x000d__x000d_
 assets/style/components/_appBody_index.scss</v>
       </c>
       <c r="M23" s="3" t="str">
@@ -2902,155 +5134,155 @@
       </c>
     </row>
     <row r="24" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A24" s="8">
+      <c r="A24" s="3">
         <v>22</v>
       </c>
-      <c r="B24" s="8" t="str">
+      <c r="B24" s="3" t="str">
         <v>~</v>
       </c>
-      <c r="C24" s="8" t="str">
+      <c r="C24" s="3" t="str">
         <v>最新消息</v>
       </c>
-      <c r="D24" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E24" s="8" t="str">
+      <c r="D24" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E24" s="3" t="str">
         <v>修復</v>
       </c>
-      <c r="F24" s="8" t="str">
+      <c r="F24" s="3" t="str">
         <v>互動</v>
       </c>
-      <c r="G24" s="8" t="str">
+      <c r="G24" s="3" t="str">
         <v>高</v>
       </c>
-      <c r="H24" s="8" t="str">
+      <c r="H24" s="3" t="str">
         <v>缺少 Loading 骨架畫面</v>
       </c>
-      <c r="I24" s="8" t="str">
+      <c r="I24" s="3" t="str">
         <v>API 載入期間無骨架或 loading 指示</v>
       </c>
-      <c r="J24" s="8" t="str">
+      <c r="J24" s="3" t="str">
         <v>新增 skeleton loader</v>
       </c>
-      <c r="K24" s="8" t="str">
+      <c r="K24" s="3" t="str">
         <v>pages/news.vue</v>
       </c>
-      <c r="L24" s="8" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/news.vue_x000d_
+      <c r="L24" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">pages/news.vue_x000d__x000d__x000d_
 assets/style/components/_appBody.scss</v>
       </c>
-      <c r="M24" s="8" t="str">
+      <c r="M24" s="3" t="str">
         <v>無骨架確認；但有 CSS :empty 空狀態（「目前沒有相關資料哦！」）</v>
       </c>
-      <c r="N24" s="9" t="str">
+      <c r="N24" s="3" t="str">
         <v>已修正</v>
       </c>
-      <c r="O24" s="9" t="str">
+      <c r="O24" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P24" s="9" t="str">
+      <c r="P24" s="3" t="str">
         <v>pages/news.vue 加 isLoading/hasError，分四分支渲染（4 條 skeleton-line 骨架／錯誤+重試／空狀態／正常列表）；LoadNews() 重構並加 .catch()；_animation.scss 加 @keyframes skeletonShimmer 與 .skeleton-line 樣式。</v>
       </c>
     </row>
     <row r="25" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A25" s="10">
+      <c r="A25" s="3">
         <v>23</v>
       </c>
-      <c r="B25" s="10" t="str">
+      <c r="B25" s="3" t="str">
         <v>~</v>
       </c>
-      <c r="C25" s="10" t="str">
+      <c r="C25" s="3" t="str">
         <v>最新消息</v>
       </c>
-      <c r="D25" s="10" t="str">
-        <v/>
-      </c>
-      <c r="E25" s="10" t="str">
+      <c r="D25" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E25" s="3" t="str">
         <v>修復</v>
       </c>
-      <c r="F25" s="10" t="str">
+      <c r="F25" s="3" t="str">
         <v>視覺</v>
       </c>
-      <c r="G25" s="10" t="str">
+      <c r="G25" s="3" t="str">
         <v>低</v>
       </c>
-      <c r="H25" s="10" t="str">
+      <c r="H25" s="3" t="str">
         <v>桌面版內容截斷無省略提示</v>
       </c>
-      <c r="I25" s="10" t="str">
+      <c r="I25" s="3" t="str">
         <v>桌面版 .item-info 無 text-overflow 或 line-clamp</v>
       </c>
-      <c r="J25" s="10" t="str">
+      <c r="J25" s="3" t="str">
         <v>加入 text-overflow: ellipsis 或 line-clamp</v>
       </c>
-      <c r="K25" s="10" t="str">
+      <c r="K25" s="3" t="str">
         <v>pages/news.vue</v>
       </c>
-      <c r="L25" s="10" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/news.vue_x000d_
-assets/style/components/_appBody.scss_x000d_
+      <c r="L25" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">pages/news.vue_x000d__x000d__x000d_
+assets/style/components/_appBody.scss_x000d__x000d__x000d_
 assets/style/_font.scss</v>
       </c>
-      <c r="M25" s="10" t="str">
+      <c r="M25" s="3" t="str">
         <v>桌面無省略確認；手機版已有 textLineClamp(2)</v>
       </c>
-      <c r="N25" s="9" t="str">
+      <c r="N25" s="3" t="str">
         <v>已修正</v>
       </c>
-      <c r="O25" s="9" t="str">
+      <c r="O25" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P25" s="9" t="str">
+      <c r="P25" s="3" t="str">
         <v>pages/news.vue 的 .article-item .item-info 加 line-clamp: 2（桌面）/ line-clamp: 3（手機 ≤1024px），超過行數自動省略結尾。</v>
       </c>
     </row>
     <row r="26" ht="45" customHeight="1">
-      <c r="A26" s="10">
+      <c r="A26" s="3">
         <v>24</v>
       </c>
-      <c r="B26" s="10" t="str">
-        <v>V</v>
-      </c>
-      <c r="C26" s="10" t="str">
+      <c r="B26" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C26" s="3" t="str">
         <v>最新消息</v>
       </c>
-      <c r="D26" s="10" t="str">
-        <v/>
-      </c>
-      <c r="E26" s="10" t="str">
+      <c r="D26" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E26" s="3" t="str">
         <v>修復</v>
       </c>
-      <c r="F26" s="10" t="str">
+      <c r="F26" s="3" t="str">
         <v>無障礙</v>
       </c>
-      <c r="G26" s="10" t="str">
+      <c r="G26" s="3" t="str">
         <v>低</v>
       </c>
-      <c r="H26" s="10" t="str">
+      <c r="H26" s="3" t="str">
         <v>純圖示連結缺少 aria-label</v>
       </c>
-      <c r="I26" s="10" t="str">
+      <c r="I26" s="3" t="str">
         <v>&lt;i class="ic-arrow-right"&gt; 無 aria-label/title/隱藏文字</v>
       </c>
-      <c r="J26" s="10" t="str">
+      <c r="J26" s="3" t="str">
         <v>加入 aria-label</v>
       </c>
-      <c r="K26" s="10" t="str">
+      <c r="K26" s="3" t="str">
         <v>pages/news.vue</v>
       </c>
-      <c r="L26" s="10" t="str">
+      <c r="L26" s="3" t="str">
         <v>pages/news.vue</v>
       </c>
-      <c r="M26" s="10" t="str">
+      <c r="M26" s="3" t="str">
         <v>grep aria-label 全站回傳 0 筆</v>
       </c>
-      <c r="N26" s="9" t="str">
+      <c r="N26" s="3" t="str">
         <v>已修正</v>
       </c>
-      <c r="O26" s="9" t="str">
+      <c r="O26" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P26" s="9" t="str">
+      <c r="P26" s="3" t="str">
         <v>pages/news.vue 的 &lt;i class="ic-arrow-right"&gt; 加上 aria-label="閱讀全文"，符合無障礙語意要求。</v>
       </c>
     </row>
@@ -3089,7 +5321,7 @@
         <v>pages/news.vue</v>
       </c>
       <c r="L27" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/news.vue_x000d_
+        <v xml:space="preserve">pages/news.vue_x000d__x000d__x000d_
 assets/style/components/_appBody.scss</v>
       </c>
       <c r="M27" s="3" t="str">
@@ -3106,54 +5338,54 @@
       </c>
     </row>
     <row r="28" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A28" s="10">
+      <c r="A28" s="3">
         <v>26</v>
       </c>
-      <c r="B28" s="10" t="str">
-        <v>V</v>
-      </c>
-      <c r="C28" s="10" t="str">
+      <c r="B28" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C28" s="3" t="str">
         <v>最新消息</v>
       </c>
-      <c r="D28" s="10" t="str">
-        <v/>
-      </c>
-      <c r="E28" s="10" t="str">
+      <c r="D28" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E28" s="3" t="str">
         <v>提升</v>
       </c>
-      <c r="F28" s="10" t="str">
+      <c r="F28" s="3" t="str">
         <v>視覺</v>
       </c>
-      <c r="G28" s="10" t="str">
+      <c r="G28" s="3" t="str">
         <v>低</v>
       </c>
-      <c r="H28" s="10" t="str">
+      <c r="H28" s="3" t="str">
         <v>新增「NEW」標籤</v>
       </c>
-      <c r="I28" s="10" t="str">
+      <c r="I28" s="3" t="str">
         <v>新消息無醒目標示</v>
       </c>
-      <c r="J28" s="10" t="str">
+      <c r="J28" s="3" t="str">
         <v>7 天內的新消息加上 NEW badge</v>
       </c>
-      <c r="K28" s="10" t="str">
+      <c r="K28" s="3" t="str">
         <v>pages/news.vue</v>
       </c>
-      <c r="L28" s="10" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/news.vue_x000d_
-assets/style/components/_appBody.scss_x000d_
+      <c r="L28" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">pages/news.vue_x000d__x000d__x000d_
+assets/style/components/_appBody.scss_x000d__x000d__x000d_
 assets/style/_font.scss</v>
       </c>
-      <c r="M28" s="10" t="str">
+      <c r="M28" s="3" t="str">
         <v>功能確實不存在</v>
       </c>
-      <c r="N28" s="9" t="str">
+      <c r="N28" s="3" t="str">
         <v>已修正</v>
       </c>
-      <c r="O28" s="9" t="str">
+      <c r="O28" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P28" s="9" t="str">
+      <c r="P28" s="3" t="str">
         <v>pages/news.vue 加 isNewItem(releaseTime) helper（7 天內判斷），對應消息右上角顯示橘色 NEW pill 標籤（_appBody.scss .badge-new）。</v>
       </c>
     </row>
@@ -3192,7 +5424,7 @@
         <v>pages/articles.vue</v>
       </c>
       <c r="L29" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/articles.vue_x000d_
+        <v xml:space="preserve">pages/articles.vue_x000d__x000d__x000d_
 assets/style/rwd/_rwd.scss</v>
       </c>
       <c r="M29" s="3" t="str">
@@ -3243,8 +5475,8 @@
         <v>pages/articles.vue</v>
       </c>
       <c r="L30" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/articles.vue_x000d_
-assets/style/components/_appBody.scss_x000d_
+        <v xml:space="preserve">pages/articles.vue_x000d__x000d__x000d_
+assets/style/components/_appBody.scss_x000d__x000d__x000d_
 assets/style/_font.scss</v>
       </c>
       <c r="M30" s="3" t="str">
@@ -3295,7 +5527,7 @@
         <v>pages/articles.vue</v>
       </c>
       <c r="L31" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/articles.vue_x000d_
+        <v xml:space="preserve">pages/articles.vue_x000d__x000d__x000d_
 assets/style/rwd/_rwd.scss</v>
       </c>
       <c r="M31" s="3" t="str">
@@ -3396,7 +5628,7 @@
         <v>pages/articles.vue</v>
       </c>
       <c r="L33" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/articles.vue_x000d_
+        <v xml:space="preserve">pages/articles.vue_x000d__x000d__x000d_
 assets/style/components/_appBody.scss</v>
       </c>
       <c r="M33" s="3" t="str">
@@ -3447,8 +5679,8 @@
         <v>pages/articles/*.vue</v>
       </c>
       <c r="L34" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/articles/welfare.vue_x000d_
-pages/articles/lazy.vue_x000d_
+        <v xml:space="preserve">pages/articles/welfare.vue_x000d__x000d__x000d_
+pages/articles/lazy.vue_x000d__x000d__x000d_
 assets/style/components/_appBody.scss</v>
       </c>
       <c r="M34" s="3" t="str">
@@ -3499,8 +5731,8 @@
         <v>pages/articles/*.vue</v>
       </c>
       <c r="L35" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/articles/welfare.vue_x000d_
-pages/articles/lazy.vue_x000d_
+        <v xml:space="preserve">pages/articles/welfare.vue_x000d__x000d__x000d_
+pages/articles/lazy.vue_x000d__x000d__x000d_
 assets/style/components/_appBodyChild.scss</v>
       </c>
       <c r="M35" s="3" t="str">
@@ -3551,8 +5783,8 @@
         <v>pages/articles/*.vue</v>
       </c>
       <c r="L36" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/articles.vue_x000d_
-pages/articles/welfare.vue_x000d_
+        <v xml:space="preserve">pages/articles.vue_x000d__x000d__x000d_
+pages/articles/welfare.vue_x000d__x000d__x000d_
 pages/articles/lazy.vue</v>
       </c>
       <c r="M36" s="3" t="str">
@@ -3603,12 +5835,12 @@
         <v>全站</v>
       </c>
       <c r="L37" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/ifare/info.vue_x000d_
-pages/articles/welfare.vue_x000d_
-pages/articles/lazy.vue_x000d_
-pages/news/info.vue_x000d_
-pages/news.vue_x000d_
-pages/articles.vue_x000d_
+        <v xml:space="preserve">pages/ifare/info.vue_x000d__x000d__x000d_
+pages/articles/welfare.vue_x000d__x000d__x000d_
+pages/articles/lazy.vue_x000d__x000d__x000d_
+pages/news/info.vue_x000d__x000d__x000d_
+pages/news.vue_x000d__x000d__x000d_
+pages/articles.vue_x000d__x000d__x000d_
 assets/style/components/_button.scss</v>
       </c>
       <c r="M37" s="3" t="str">
@@ -3659,7 +5891,7 @@
         <v>pages/collaborator.vue</v>
       </c>
       <c r="L38" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/collaborator.vue_x000d_
+        <v xml:space="preserve">pages/collaborator.vue_x000d__x000d__x000d_
 assets/style/components/_appBody.scss</v>
       </c>
       <c r="M38" s="3" t="str">
@@ -3760,7 +5992,7 @@
         <v>pages/collaborator.vue</v>
       </c>
       <c r="L40" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/collaborator.vue_x000d_
+        <v xml:space="preserve">pages/collaborator.vue_x000d__x000d__x000d_
 assets/style/components/_appBody.scss</v>
       </c>
       <c r="M40" s="3" t="str">
@@ -3811,8 +6043,8 @@
         <v>pages/index.vue</v>
       </c>
       <c r="L41" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/index.vue_x000d_
-assets/style/components/_appBody_index.scss_x000d_
+        <v xml:space="preserve">pages/index.vue_x000d__x000d__x000d_
+assets/style/components/_appBody_index.scss_x000d__x000d__x000d_
 assets/style/rwd/_rwd_index.scss</v>
       </c>
       <c r="M41" s="3" t="str">
@@ -3913,8 +6145,8 @@
         <v>pages/about.vue</v>
       </c>
       <c r="L43" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/about.vue_x000d_
-components/CompBreadCrumb.vue_x000d_
+        <v xml:space="preserve">pages/about.vue_x000d__x000d__x000d_
+components/CompBreadCrumb.vue_x000d__x000d__x000d_
 assets/style/_font.scss</v>
       </c>
       <c r="M43" s="3" t="str">
@@ -3965,8 +6197,8 @@
         <v>pages/about.vue</v>
       </c>
       <c r="L44" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/about.vue_x000d_
-assets/style/components/_appBody_about.scss_x000d_
+        <v xml:space="preserve">pages/about.vue_x000d__x000d__x000d_
+assets/style/components/_appBody_about.scss_x000d__x000d__x000d_
 assets/style/rwd/_rwd_about.scss</v>
       </c>
       <c r="M44" s="3" t="str">
@@ -4017,8 +6249,8 @@
         <v>pages/about.vue</v>
       </c>
       <c r="L45" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/about.vue_x000d_
-assets/style/components/_appBody_about.scss_x000d_
+        <v xml:space="preserve">pages/about.vue_x000d__x000d__x000d_
+assets/style/components/_appBody_about.scss_x000d__x000d__x000d_
 assets/style/rwd/_rwd_about.scss</v>
       </c>
       <c r="M45" s="3" t="str">
@@ -4035,54 +6267,54 @@
       </c>
     </row>
     <row r="46" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A46" s="10">
+      <c r="A46" s="3">
         <v>44</v>
       </c>
-      <c r="B46" s="10" t="str">
-        <v>V</v>
-      </c>
-      <c r="C46" s="10" t="str">
+      <c r="B46" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C46" s="3" t="str">
         <v>關於長穩</v>
       </c>
-      <c r="D46" s="10" t="str">
-        <v/>
-      </c>
-      <c r="E46" s="10" t="str">
+      <c r="D46" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E46" s="3" t="str">
         <v>提升</v>
       </c>
-      <c r="F46" s="10" t="str">
+      <c r="F46" s="3" t="str">
         <v>視覺</v>
       </c>
-      <c r="G46" s="10" t="str">
+      <c r="G46" s="3" t="str">
         <v>低</v>
       </c>
-      <c r="H46" s="10" t="str">
+      <c r="H46" s="3" t="str">
         <v>三大核心圖示為靜態 SVG</v>
       </c>
-      <c r="I46" s="10" t="str">
+      <c r="I46" s="3" t="str">
         <v>環境保育/人才培育/社會關懷用靜態 &lt;i class="how-logo"&gt;</v>
       </c>
-      <c r="J46" s="10" t="str">
+      <c r="J46" s="3" t="str">
         <v>加入 SVG 動畫</v>
       </c>
-      <c r="K46" s="10" t="str">
+      <c r="K46" s="3" t="str">
         <v>pages/about.vue</v>
       </c>
-      <c r="L46" s="10" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/about.vue_x000d_
-assets/style/components/_appBody_about.scss_x000d_
+      <c r="L46" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">pages/about.vue_x000d__x000d__x000d_
+assets/style/components/_appBody_about.scss_x000d__x000d__x000d_
 assets/style/_animation.scss</v>
       </c>
-      <c r="M46" s="10" t="str">
+      <c r="M46" s="3" t="str">
         <v>確認無任何動畫 class 或 JS</v>
       </c>
-      <c r="N46" s="9" t="str">
+      <c r="N46" s="3" t="str">
         <v>已修正</v>
       </c>
-      <c r="O46" s="9" t="str">
+      <c r="O46" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P46" s="9" t="str">
+      <c r="P46" s="3" t="str">
         <v>icon SVG 本身仍為靜態，但已包入 Dynamic Island 互動卡片（.how-content）：hover/click toggle 觸發整體 morph 動畫（grid-template-rows 展開、translateY 浮起、background opacity overlay 漸層切換、border 露出青綠光暈）。視覺已不再死板。</v>
       </c>
     </row>
@@ -4221,8 +6453,8 @@
         <v>components/AppHeader.vue</v>
       </c>
       <c r="L49" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">components/AppHeader.vue_x000d_
-assets/style/components/_appHeader.scss_x000d_
+        <v xml:space="preserve">components/AppHeader.vue_x000d__x000d__x000d_
+assets/style/components/_appHeader.scss_x000d__x000d__x000d_
 assets/style/rwd/_rwd_appHeader.scss</v>
       </c>
       <c r="M49" s="3" t="str">
@@ -4273,8 +6505,8 @@
         <v>components/AppHeader.vue</v>
       </c>
       <c r="L50" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">components/AppHeader.vue_x000d_
-assets/style/components/_appHeader.scss_x000d_
+        <v xml:space="preserve">components/AppHeader.vue_x000d__x000d__x000d_
+assets/style/components/_appHeader.scss_x000d__x000d__x000d_
 assets/style/rwd/_rwd_appHeader.scss</v>
       </c>
       <c r="M50" s="3" t="str">
@@ -4425,8 +6657,8 @@
         <v>components/CompPage*.vue</v>
       </c>
       <c r="L53" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">components/CompPage.vue_x000d_
-components/CompPageNum.vue_x000d_
+        <v xml:space="preserve">components/CompPage.vue_x000d__x000d__x000d_
+components/CompPageNum.vue_x000d__x000d__x000d_
 assets/style/components/_compPage.scss</v>
       </c>
       <c r="M53" s="3" t="str">
@@ -4477,7 +6709,7 @@
         <v>components/CompPage.vue</v>
       </c>
       <c r="L54" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">components/CompPage.vue_x000d_
+        <v xml:space="preserve">components/CompPage.vue_x000d__x000d__x000d_
 components/CompPageNum.vue</v>
       </c>
       <c r="M54" s="3" t="str">
@@ -4528,8 +6760,8 @@
         <v>多個元件</v>
       </c>
       <c r="L55" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">components/CompPage.vue_x000d_
-components/CompPageNum.vue_x000d_
+        <v xml:space="preserve">components/CompPage.vue_x000d__x000d__x000d_
+components/CompPageNum.vue_x000d__x000d__x000d_
 components/CompSelectElse.vue</v>
       </c>
       <c r="M55" s="3" t="str">
@@ -4580,8 +6812,8 @@
         <v>components/CompSelect*.vue</v>
       </c>
       <c r="L56" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">components/CompSelect.vue_x000d_
-components/CompSelectRecipient.vue_x000d_
+        <v xml:space="preserve">components/CompSelect.vue_x000d__x000d__x000d_
+components/CompSelectRecipient.vue_x000d__x000d__x000d_
 components/CompSelectElse.vue</v>
       </c>
       <c r="M56" s="3" t="str">
@@ -4632,7 +6864,7 @@
         <v>components/CompSelect.vue</v>
       </c>
       <c r="L57" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">components/CompSelect.vue_x000d_
+        <v xml:space="preserve">components/CompSelect.vue_x000d__x000d__x000d_
 components/CompSelectRecipient.vue</v>
       </c>
       <c r="M57" s="3" t="str">
@@ -4683,8 +6915,8 @@
         <v>components/CompSelect*.vue</v>
       </c>
       <c r="L58" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">components/CompSelect.vue_x000d_
-components/CompSelectRecipient.vue_x000d_
+        <v xml:space="preserve">components/CompSelect.vue_x000d__x000d__x000d_
+components/CompSelectRecipient.vue_x000d__x000d__x000d_
 components/CompSelectElse.vue</v>
       </c>
       <c r="M58" s="3" t="str">
@@ -4735,9 +6967,9 @@
         <v>components/CompSelect*.vue</v>
       </c>
       <c r="L59" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">components/CompSelect.vue_x000d_
-components/CompSelectRecipient.vue_x000d_
-components/CompSelectElse.vue_x000d_
+        <v xml:space="preserve">components/CompSelect.vue_x000d__x000d__x000d_
+components/CompSelectRecipient.vue_x000d__x000d__x000d_
+components/CompSelectElse.vue_x000d__x000d__x000d_
 assets/style/components/_compSelect.scss</v>
       </c>
       <c r="M59" s="3" t="str">
@@ -4788,10 +7020,10 @@
         <v>components/CompSelect*.vue</v>
       </c>
       <c r="L60" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">components/CompSelect.vue_x000d_
-components/CompSelectRecipient.vue_x000d_
-components/CompSelectElse.vue_x000d_
-assets/style/components/_compSelect.scss_x000d_
+        <v xml:space="preserve">components/CompSelect.vue_x000d__x000d__x000d_
+components/CompSelectRecipient.vue_x000d__x000d__x000d_
+components/CompSelectElse.vue_x000d__x000d__x000d_
+assets/style/components/_compSelect.scss_x000d__x000d__x000d_
 assets/style/rwd/_rwd_compSelect.scss</v>
       </c>
       <c r="M60" s="3" t="str">
@@ -4808,106 +7040,106 @@
       </c>
     </row>
     <row r="61" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A61" s="8">
+      <c r="A61" s="3">
         <v>59</v>
       </c>
-      <c r="B61" s="8" t="str">
-        <v>V</v>
-      </c>
-      <c r="C61" s="8" t="str">
+      <c r="B61" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C61" s="3" t="str">
         <v>全站微互動</v>
       </c>
-      <c r="D61" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E61" s="8" t="str">
+      <c r="D61" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E61" s="3" t="str">
         <v>提升</v>
       </c>
-      <c r="F61" s="8" t="str">
+      <c r="F61" s="3" t="str">
         <v>視覺</v>
       </c>
-      <c r="G61" s="8" t="str">
+      <c r="G61" s="3" t="str">
         <v>低</v>
       </c>
-      <c r="H61" s="8" t="str">
+      <c r="H61" s="3" t="str">
         <v>卡片 hover 效果升級</v>
       </c>
-      <c r="I61" s="8" t="str">
+      <c r="I61" s="3" t="str">
         <v>目前卡片 hover 效果單調</v>
       </c>
-      <c r="J61" s="8" t="str">
+      <c r="J61" s="3" t="str">
         <v>上浮 4px + 陰影加深</v>
       </c>
-      <c r="K61" s="8" t="str">
+      <c r="K61" s="3" t="str">
         <v>全站</v>
       </c>
-      <c r="L61" s="8" t="str" xml:space="preserve">
-        <v xml:space="preserve">assets/style/components/_appBody.scss_x000d_
-assets/style/components/_appBody_index.scss_x000d_
+      <c r="L61" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">assets/style/components/_appBody.scss_x000d__x000d__x000d_
+assets/style/components/_appBody_index.scss_x000d__x000d__x000d_
 assets/style/components/_appBodyChild_ifare.scss</v>
       </c>
-      <c r="M61" s="8" t="str">
+      <c r="M61" s="3" t="str">
         <v>功能確實不存在（待實測確認現有 hover）</v>
       </c>
-      <c r="N61" s="9" t="str">
+      <c r="N61" s="3" t="str">
         <v>已修正</v>
       </c>
-      <c r="O61" s="9" t="str">
+      <c r="O61" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P61" s="9" t="str">
+      <c r="P61" s="3" t="str">
         <v>_main.scss 為 .result-item / .article-item / .agency-item 加 hover translateY(-3px) + box-shadow，active translateY(-1px) 回彈。純 GPU 屬性，不觸發 layout 重繪。</v>
       </c>
     </row>
     <row r="62" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A62" s="5">
+      <c r="A62" s="3">
         <v>60</v>
       </c>
-      <c r="B62" s="5" t="str">
-        <v>V</v>
-      </c>
-      <c r="C62" s="5" t="str">
+      <c r="B62" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C62" s="3" t="str">
         <v>全站微互動</v>
       </c>
-      <c r="D62" s="5" t="str">
-        <v/>
-      </c>
-      <c r="E62" s="5" t="str">
+      <c r="D62" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E62" s="3" t="str">
         <v>提升</v>
       </c>
-      <c r="F62" s="5" t="str">
+      <c r="F62" s="3" t="str">
         <v>視覺</v>
       </c>
-      <c r="G62" s="5" t="str">
+      <c r="G62" s="3" t="str">
         <v>低</v>
       </c>
-      <c r="H62" s="5" t="str">
+      <c r="H62" s="3" t="str">
         <v>CTA 按鈕互動效果</v>
       </c>
-      <c r="I62" s="5" t="str">
+      <c r="I62" s="3" t="str">
         <v>按鈕缺乏觸覺回饋</v>
       </c>
-      <c r="J62" s="5" t="str">
+      <c r="J62" s="3" t="str">
         <v>hover 按壓回彈 + 點擊漣漪效果</v>
       </c>
-      <c r="K62" s="5" t="str">
+      <c r="K62" s="3" t="str">
         <v>全站</v>
       </c>
-      <c r="L62" s="5" t="str" xml:space="preserve">
-        <v xml:space="preserve">assets/style/components/_button.scss_x000d_
-assets/style/_font.scss_x000d_
+      <c r="L62" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">assets/style/components/_button.scss_x000d__x000d__x000d_
+assets/style/_font.scss_x000d__x000d__x000d_
 assets/style/rwd/_rwd_button.scss</v>
       </c>
-      <c r="M62" s="5" t="str">
+      <c r="M62" s="3" t="str">
         <v>功能確實不存在</v>
       </c>
-      <c r="N62" s="6" t="str">
+      <c r="N62" s="3" t="str">
         <v>部分修正</v>
       </c>
-      <c r="O62" s="6" t="str">
+      <c r="O62" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P62" s="6" t="str">
+      <c r="P62" s="3" t="str">
         <v>_main.scss 為 .btn-filter / .btn-tag / .btn-retry 加 hover translateY(-1px) + active scale(0.97) 按壓回彈。原訴求「點擊漣漪效果」尚未做。</v>
       </c>
     </row>
@@ -4946,7 +7178,7 @@
         <v>全站</v>
       </c>
       <c r="L63" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">assets/style/_font.scss_x000d_
+        <v xml:space="preserve">assets/style/_font.scss_x000d__x000d__x000d_
 assets/style/_main.scss</v>
       </c>
       <c r="M63" s="3" t="str">
@@ -4997,8 +7229,8 @@
         <v>全站</v>
       </c>
       <c r="L64" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">layouts/default.vue_x000d_
-assets/style/components/_app.scss_x000d_
+        <v xml:space="preserve">layouts/default.vue_x000d__x000d__x000d_
+assets/style/components/_app.scss_x000d__x000d__x000d_
 assets/style/_animation.scss</v>
       </c>
       <c r="M64" s="3" t="str">
@@ -5049,10 +7281,10 @@
         <v>全站</v>
       </c>
       <c r="L65" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/news.vue_x000d_
-pages/articles.vue_x000d_
-pages/index.vue_x000d_
-pages/collaborator.vue_x000d_
+        <v xml:space="preserve">pages/news.vue_x000d__x000d__x000d_
+pages/articles.vue_x000d__x000d__x000d_
+pages/index.vue_x000d__x000d__x000d_
+pages/collaborator.vue_x000d__x000d__x000d_
 pages/ifare/result.vue</v>
       </c>
       <c r="M65" s="3" t="str">
@@ -5153,7 +7385,7 @@
         <v>assets/style/_font.scss</v>
       </c>
       <c r="L67" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">assets/style/_font.scss_x000d_
+        <v xml:space="preserve">assets/style/_font.scss_x000d__x000d__x000d_
 assets/style/rwd/_rwd_font.scss</v>
       </c>
       <c r="M67" s="3" t="str">
@@ -5204,7 +7436,7 @@
         <v>assets/style/</v>
       </c>
       <c r="L68" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">assets/style/_main.scss_x000d_
+        <v xml:space="preserve">assets/style/_main.scss_x000d__x000d__x000d_
 assets/style/_mixin.scss</v>
       </c>
       <c r="M68" s="3" t="str">
@@ -5255,7 +7487,7 @@
         <v>assets/style/</v>
       </c>
       <c r="L69" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">assets/style/_main.scss_x000d_
+        <v xml:space="preserve">assets/style/_main.scss_x000d__x000d__x000d_
 assets/style/_mixin.scss</v>
       </c>
       <c r="M69" s="3" t="str">
@@ -5306,7 +7538,7 @@
         <v>assets/style/</v>
       </c>
       <c r="L70" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">assets/style/_main.scss_x000d_
+        <v xml:space="preserve">assets/style/_main.scss_x000d__x000d__x000d_
 assets/style/_mixin.scss</v>
       </c>
       <c r="M70" s="3" t="str">
@@ -5423,55 +7655,55 @@
       </c>
     </row>
     <row r="73" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A73" s="5">
+      <c r="A73" s="3">
         <v>71</v>
       </c>
-      <c r="B73" s="5" t="str">
-        <v>V</v>
-      </c>
-      <c r="C73" s="5" t="str">
+      <c r="B73" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C73" s="3" t="str">
         <v>全站通用</v>
       </c>
-      <c r="D73" s="5" t="str">
-        <v/>
-      </c>
-      <c r="E73" s="5" t="str">
+      <c r="D73" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E73" s="3" t="str">
         <v>修復</v>
       </c>
-      <c r="F73" s="5" t="str">
+      <c r="F73" s="3" t="str">
         <v>RWD</v>
       </c>
-      <c r="G73" s="5" t="str">
+      <c r="G73" s="3" t="str">
         <v>高</v>
       </c>
-      <c r="H73" s="5" t="str">
+      <c r="H73" s="3" t="str">
         <v>多處觸控目標小於 44x44px</v>
       </c>
-      <c r="I73" s="5" t="str">
+      <c r="I73" s="3" t="str">
         <v>分頁按鈕 30x30px、.btn-reset height:32px、.btn-advance height:40px</v>
       </c>
-      <c r="J73" s="5" t="str">
+      <c r="J73" s="3" t="str">
         <v>確保所有可點擊元素最小 44x44px</v>
       </c>
-      <c r="K73" s="5" t="str">
+      <c r="K73" s="3" t="str">
         <v>全站</v>
       </c>
-      <c r="L73" s="5" t="str" xml:space="preserve">
-        <v xml:space="preserve">assets/style/components/_compPage.scss_x000d_
-assets/style/components/_button.scss_x000d_
-assets/style/components/_compSelect.scss_x000d_
+      <c r="L73" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">assets/style/components/_compPage.scss_x000d__x000d__x000d_
+assets/style/components/_button.scss_x000d__x000d__x000d_
+assets/style/components/_compSelect.scss_x000d__x000d__x000d_
 assets/style/rwd/_rwd_compPage.scss</v>
       </c>
-      <c r="M73" s="5" t="str">
+      <c r="M73" s="3" t="str">
         <v>確認多處尺寸低於 44px 標準</v>
       </c>
-      <c r="N73" s="6" t="str">
+      <c r="N73" s="3" t="str">
         <v>部分修正</v>
       </c>
-      <c r="O73" s="6" t="str">
+      <c r="O73" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P73" s="6" t="str">
+      <c r="P73" s="3" t="str">
         <v>footer .btn-social 高度從 40px 提升到 44px（LINE / Facebook 兩按鈕符合 iOS HIG 觸控標準）。CompPage 分頁箭頭、btn-reset、btn-advance、CompSelect 等其他元件尚未套用 44px 標準。</v>
       </c>
     </row>
@@ -5510,8 +7742,8 @@
         <v>全站</v>
       </c>
       <c r="L74" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/index.vue_x000d_
-pages/ifare/result.vue_x000d_
+        <v xml:space="preserve">pages/index.vue_x000d__x000d__x000d_
+pages/ifare/result.vue_x000d__x000d__x000d_
 pages/ifare/contact.vue</v>
       </c>
       <c r="M74" s="3" t="str">
@@ -5612,8 +7844,8 @@
         <v>_button.scss + _font.scss</v>
       </c>
       <c r="L76" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">assets/style/components/_button.scss_x000d_
-assets/style/_font.scss_x000d_
+        <v xml:space="preserve">assets/style/components/_button.scss_x000d__x000d__x000d_
+assets/style/_font.scss_x000d__x000d__x000d_
 assets/style/rwd/_rwd_button.scss</v>
       </c>
       <c r="M76" s="3" t="str">
@@ -5664,8 +7896,8 @@
         <v>全站</v>
       </c>
       <c r="L77" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">assets/style/_color.scss_x000d_
-assets/style/_mixin.scss_x000d_
+        <v xml:space="preserve">assets/style/_color.scss_x000d__x000d__x000d_
+assets/style/_mixin.scss_x000d__x000d__x000d_
 assets/style/_main.scss</v>
       </c>
       <c r="M77" s="3" t="str">
@@ -5716,7 +7948,7 @@
         <v>全站</v>
       </c>
       <c r="L78" s="3" t="str" xml:space="preserve">
-        <v xml:space="preserve">assets/style/_mixin.scss_x000d_
+        <v xml:space="preserve">assets/style/_mixin.scss_x000d__x000d__x000d_
 assets/style/_transition.scss</v>
       </c>
       <c r="M78" s="3" t="str">
@@ -5868,52 +8100,52 @@
       </c>
     </row>
     <row r="82" ht="45" customHeight="1">
-      <c r="A82" s="5">
+      <c r="A82" s="3">
         <v>80</v>
       </c>
-      <c r="B82" s="5" t="str">
-        <v>V</v>
-      </c>
-      <c r="C82" s="5" t="str">
+      <c r="B82" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C82" s="3" t="str">
         <v>全站通用</v>
       </c>
-      <c r="D82" s="5" t="str">
-        <v/>
-      </c>
-      <c r="E82" s="5" t="str">
+      <c r="D82" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E82" s="3" t="str">
         <v>修復</v>
       </c>
-      <c r="F82" s="5" t="str">
+      <c r="F82" s="3" t="str">
         <v>互動</v>
       </c>
-      <c r="G82" s="5" t="str">
+      <c r="G82" s="3" t="str">
         <v>高</v>
       </c>
-      <c r="H82" s="5" t="str">
+      <c r="H82" s="3" t="str">
         <v>缺少載入失敗與重試機制</v>
       </c>
-      <c r="I82" s="5" t="str">
+      <c r="I82" s="3" t="str">
         <v>目前清單有 loading / skeleton / toast，但尚未明確區分 API 載入失敗狀態與重試機制。</v>
       </c>
-      <c r="J82" s="5" t="str">
+      <c r="J82" s="3" t="str">
         <v>建立統一錯誤狀態元件，針對 API 失敗提供錯誤訊息、retry 按鈕，並區分空資料與載入失敗。</v>
       </c>
-      <c r="K82" s="5" t="str">
+      <c r="K82" s="3" t="str">
         <v>全站</v>
       </c>
-      <c r="L82" s="5" t="str">
+      <c r="L82" s="3" t="str">
         <v>pages/news.vue pages/articles.vue pages/collaborator.vue pages/ifare/result.vue layouts/default.vue components/</v>
       </c>
-      <c r="M82" s="5" t="str">
+      <c r="M82" s="3" t="str">
         <v>現有清單多著重 loading 與空狀態，未明列 error state。</v>
       </c>
-      <c r="N82" s="6" t="str">
+      <c r="N82" s="3" t="str">
         <v>部分修正</v>
       </c>
-      <c r="O82" s="6" t="str">
+      <c r="O82" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P82" s="6" t="str">
+      <c r="P82" s="3" t="str">
         <v>pages/news.vue 已實作 hasError + .btn-retry 按鈕模式（搭配 _animation.scss .part-error 樣式）。articles.vue / collaborator.vue / ifare/result.vue 三頁尚未套用同一錯誤狀態元件。</v>
       </c>
     </row>
@@ -6210,847 +8442,4299 @@
         <v>待處理</v>
       </c>
     </row>
-    <row r="90" xml:space="preserve">
-      <c r="A90" s="9">
+    <row r="90" ht="100.8" customHeight="1" xml:space="preserve">
+      <c r="A90" s="3">
         <v>88</v>
       </c>
-      <c r="B90" s="9" t="str">
-        <v>V</v>
-      </c>
-      <c r="C90" s="9" t="str">
+      <c r="B90" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C90" s="3" t="str">
         <v>i-Fare 福利查詢</v>
       </c>
-      <c r="D90" s="9" t="str">
+      <c r="D90" s="3" t="str">
         <v>搜尋介面</v>
       </c>
-      <c r="E90" s="9" t="str">
+      <c r="E90" s="3" t="str">
         <v>提升</v>
       </c>
-      <c r="F90" s="9" t="str">
+      <c r="F90" s="3" t="str">
         <v>黏著</v>
       </c>
-      <c r="G90" s="9" t="str">
+      <c r="G90" s="3" t="str">
         <v>中</v>
       </c>
-      <c r="H90" s="9" t="str">
+      <c r="H90" s="3" t="str">
         <v>新增關鍵字搜尋輸入欄</v>
       </c>
-      <c r="I90" s="9" t="str">
+      <c r="I90" s="3" t="str">
         <v>原本搜尋只能用三個下拉選單（政策類別、受助對象、地區），缺少自由文字搜尋入口</v>
       </c>
-      <c r="J90" s="9" t="str">
+      <c r="J90" s="3" t="str">
         <v>ifare 與結果頁各加 &lt;input.input-keyword&gt;（含 Enter 快捷鍵），搜尋條件擴增 keyword 參數，後端 LIKE 查詢</v>
       </c>
-      <c r="K90" s="9" t="str">
+      <c r="K90" s="3" t="str">
         <v>pages/ifare.vue pages/ifare/result.vue</v>
       </c>
-      <c r="L90" s="9" t="str" xml:space="preserve">
-        <v xml:space="preserve">pages/ifare.vue_x000d_
-pages/ifare/result.vue_x000d_
-assets/style/components/_appBody_ifare.scss_x000d_
+      <c r="L90" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">pages/ifare.vue_x000d__x000d__x000d_
+pages/ifare/result.vue_x000d__x000d__x000d_
+assets/style/components/_appBody_ifare.scss_x000d__x000d__x000d_
 assets/style/components/_appBodyChild_ifare.scss</v>
       </c>
-      <c r="M90" s="9" t="str">
+      <c r="M90" s="3" t="str">
         <v>改版補登；後端 IFare_API.Application/Fare/Policy/* 已加 Keyword filter</v>
       </c>
-      <c r="N90" s="9" t="str">
+      <c r="N90" s="3" t="str">
         <v>已修正</v>
       </c>
-      <c r="O90" s="9" t="str">
+      <c r="O90" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P90" s="9" t="str">
+      <c r="P90" s="3" t="str">
         <v>改版補登；前端 Search() 已帶 keyword 參數，API 傳 Keyword 欄位</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="9">
+    <row r="91" ht="57.6" customHeight="1">
+      <c r="A91" s="3">
         <v>89</v>
       </c>
-      <c r="B91" s="9" t="str">
-        <v>V</v>
-      </c>
-      <c r="C91" s="9" t="str">
+      <c r="B91" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C91" s="3" t="str">
         <v>i-Fare 福利查詢</v>
       </c>
-      <c r="D91" s="9" t="str">
+      <c r="D91" s="3" t="str">
         <v>查詢結果</v>
       </c>
-      <c r="E91" s="9" t="str">
+      <c r="E91" s="3" t="str">
         <v>修復</v>
       </c>
-      <c r="F91" s="9" t="str">
+      <c r="F91" s="3" t="str">
         <v>互動</v>
       </c>
-      <c r="G91" s="9" t="str">
+      <c r="G91" s="3" t="str">
         <v>中</v>
       </c>
-      <c r="H91" s="9" t="str">
+      <c r="H91" s="3" t="str">
         <v>結果頁未支援 URL query 初始化</v>
       </c>
-      <c r="I91" s="9" t="str">
+      <c r="I91" s="3" t="str">
         <v>結果頁從 ifare 跳轉過來時若重整或從外部進入，搜尋條件無法保留</v>
       </c>
-      <c r="J91" s="9" t="str">
+      <c r="J91" s="3" t="str">
         <v>解析 route.query 初始化各 ref（policy / recipient / area / keyword），支援深度連結與重整保留條件</v>
       </c>
-      <c r="K91" s="9" t="str">
+      <c r="K91" s="3" t="str">
         <v>pages/ifare/result.vue</v>
       </c>
-      <c r="L91" s="9" t="str">
+      <c r="L91" s="3" t="str">
         <v>pages/ifare/result.vue</v>
       </c>
-      <c r="M91" s="9" t="str">
+      <c r="M91" s="3" t="str">
         <v>改版補登；搭配 #88 關鍵字欄位一起實作</v>
       </c>
-      <c r="N91" s="9" t="str">
+      <c r="N91" s="3" t="str">
         <v>已修正</v>
       </c>
-      <c r="O91" s="9" t="str">
+      <c r="O91" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P91" s="9" t="str">
+      <c r="P91" s="3" t="str">
         <v>改版補登</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="9">
+    <row r="92" ht="57.6" customHeight="1">
+      <c r="A92" s="3">
         <v>90</v>
       </c>
-      <c r="B92" s="9" t="str">
-        <v>V</v>
-      </c>
-      <c r="C92" s="9" t="str">
+      <c r="B92" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C92" s="3" t="str">
         <v>i-Fare 福利查詢</v>
       </c>
-      <c r="D92" s="9" t="str">
+      <c r="D92" s="3" t="str">
         <v>搜尋介面</v>
       </c>
-      <c r="E92" s="9" t="str">
+      <c r="E92" s="3" t="str">
         <v>修復</v>
       </c>
-      <c r="F92" s="9" t="str">
+      <c r="F92" s="3" t="str">
         <v>RWD</v>
       </c>
-      <c r="G92" s="9" t="str">
+      <c r="G92" s="3" t="str">
         <v>低</v>
       </c>
-      <c r="H92" s="9" t="str">
+      <c r="H92" s="3" t="str">
         <v>搜尋按鈕區手機版橫排擠壓</v>
       </c>
-      <c r="I92" s="9" t="str">
+      <c r="I92" s="3" t="str">
         <v>.item-bottom 原為橫排，手機版按鈕和提示文字擠在一起</v>
       </c>
-      <c r="J92" s="9" t="str">
+      <c r="J92" s="3" t="str">
         <v>_appBody_ifare.scss .item-bottom 改 flex-direction: column + gap + 居中，並加 .filter-hint 樣式</v>
       </c>
-      <c r="K92" s="9" t="str">
+      <c r="K92" s="3" t="str">
         <v>pages/ifare.vue</v>
       </c>
-      <c r="L92" s="9" t="str">
+      <c r="L92" s="3" t="str">
         <v>iFare_Frontend/assets/style/components/_appBody_ifare.scss</v>
       </c>
-      <c r="M92" s="9" t="str">
+      <c r="M92" s="3" t="str">
         <v>改版補登；搭配 #1 disabled 移除後新增的提示文字調整版面</v>
       </c>
-      <c r="N92" s="9" t="str">
+      <c r="N92" s="3" t="str">
         <v>已修正</v>
       </c>
-      <c r="O92" s="9" t="str">
+      <c r="O92" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P92" s="9" t="str">
+      <c r="P92" s="3" t="str">
         <v>改版補登</v>
       </c>
     </row>
-    <row r="93" xml:space="preserve">
-      <c r="A93" s="9">
+    <row r="93" ht="86.40000000000002" customHeight="1" xml:space="preserve">
+      <c r="A93" s="3">
         <v>91</v>
       </c>
-      <c r="B93" s="9" t="str">
-        <v>V</v>
-      </c>
-      <c r="C93" s="9" t="str">
+      <c r="B93" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C93" s="3" t="str">
         <v>共用元件</v>
       </c>
-      <c r="D93" s="9" t="str">
+      <c r="D93" s="3" t="str">
         <v>AppFooter</v>
       </c>
-      <c r="E93" s="9" t="str">
+      <c r="E93" s="3" t="str">
         <v>提升</v>
       </c>
-      <c r="F93" s="9" t="str">
+      <c r="F93" s="3" t="str">
         <v>視覺</v>
       </c>
-      <c r="G93" s="9" t="str">
+      <c r="G93" s="3" t="str">
         <v>低</v>
       </c>
-      <c r="H93" s="9" t="str">
+      <c r="H93" s="3" t="str">
         <v>Footer 聯絡資訊缺 icon</v>
       </c>
-      <c r="I93" s="9" t="str">
+      <c r="I93" s="3" t="str">
         <v>footer 4 個 label（聯絡電話 / 聯絡信箱 / 地址 / 服務時間）僅有純文字，缺乏視覺辨識</v>
       </c>
-      <c r="J93" s="9" t="str">
+      <c r="J93" s="3" t="str">
         <v>4 個 label 前各加對應 icon（Tel / Mail / Address / Clock），與站內既有 icon 風格一致</v>
       </c>
-      <c r="K93" s="9" t="str">
+      <c r="K93" s="3" t="str">
         <v>components/AppFooter.vue</v>
       </c>
-      <c r="L93" s="9" t="str" xml:space="preserve">
-        <v xml:space="preserve">iFare_Frontend/components/AppFooter.vue_x000d_
-assets/style/components/_appFooter.scss_x000d_
-assets/style/_font.scss_x000d_
-assets/img/Mail.svg (新增)_x000d_
+      <c r="L93" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Frontend/components/AppFooter.vue_x000d__x000d__x000d_
+assets/style/components/_appFooter.scss_x000d__x000d__x000d_
+assets/style/_font.scss_x000d__x000d__x000d_
+assets/img/Mail.svg (新增)_x000d__x000d__x000d_
 assets/img/Clock.svg (新增)</v>
       </c>
-      <c r="M93" s="9" t="str">
+      <c r="M93" s="3" t="str">
         <v>改版補登；新增 Mail.svg + Clock.svg 用 mask-image 著色為 rgba(white,.7)，沿用既有 Tel.svg / Location.svg。原 ::before content 的 CSS-only label 改為 HTML &lt;span class="footer-info-label"&gt; 結構</v>
       </c>
-      <c r="N93" s="9" t="str">
+      <c r="N93" s="3" t="str">
         <v>已修正</v>
       </c>
-      <c r="O93" s="9" t="str">
+      <c r="O93" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P93" s="9" t="str">
+      <c r="P93" s="3" t="str">
         <v>改版補登</v>
       </c>
     </row>
-    <row r="94" xml:space="preserve">
-      <c r="A94" s="9">
+    <row r="94" ht="273.6" customHeight="1" xml:space="preserve">
+      <c r="A94" s="3">
         <v>92</v>
       </c>
-      <c r="B94" s="9" t="str">
-        <v>V</v>
-      </c>
-      <c r="C94" s="9" t="str">
+      <c r="B94" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C94" s="3" t="str">
         <v>共用元件</v>
       </c>
-      <c r="D94" s="9" t="str">
+      <c r="D94" s="3" t="str">
         <v>AppFooter</v>
       </c>
-      <c r="E94" s="9" t="str">
+      <c r="E94" s="3" t="str">
         <v>提升</v>
       </c>
-      <c r="F94" s="9" t="str">
+      <c r="F94" s="3" t="str">
         <v>互動</v>
       </c>
-      <c r="G94" s="9" t="str">
+      <c r="G94" s="3" t="str">
         <v>中</v>
       </c>
-      <c r="H94" s="9" t="str">
+      <c r="H94" s="3" t="str">
         <v>社群連結 LINE / Facebook 分散兩處</v>
       </c>
-      <c r="I94" s="9" t="str">
+      <c r="I94" s="3" t="str">
         <v>LINE 在「進一步瞭解更多」CTA 區塊內，Facebook 在獨立 .part-middle 區塊；兩者都是社群媒體應該放一起</v>
       </c>
-      <c r="J94" s="9" t="str">
+      <c r="J94" s="3" t="str">
         <v>把 Facebook 從 .part-middle 移到 .card-more 內 .card-more-socials div 與 LINE 並排，整合為單一社群區塊</v>
       </c>
-      <c r="K94" s="9" t="str">
+      <c r="K94" s="3" t="str">
         <v>components/AppFooter.vue</v>
       </c>
-      <c r="L94" s="9" t="str" xml:space="preserve">
-        <v xml:space="preserve">iFare_Frontend/components/AppFooter.vue_x000d_
-assets/style/components/_appFooter.scss_x000d_
+      <c r="L94" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Frontend/components/AppFooter.vue_x000d__x000d__x000d_
+assets/style/components/_appFooter.scss_x000d__x000d__x000d_
 assets/style/rwd/_rwd_appFooter.scss</v>
       </c>
-      <c r="M94" s="9" t="str">
+      <c r="M94" s="3" t="str">
         <v>改版補登；移除原 .part-middle 與 .link-track 樣式</v>
       </c>
-      <c r="N94" s="9" t="str">
+      <c r="N94" s="3" t="str">
         <v>已修正</v>
       </c>
-      <c r="O94" s="9" t="str">
+      <c r="O94" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P94" s="9" t="str">
+      <c r="P94" s="3" t="str">
         <v>改版補登；同步修桌面 1025-1280px overflow（加 FB 後 .card-more 內容寬度 ~1300px 會爆）：.card-more 加 flex-wrap: wrap + max-width: calc(100% - 64px)；.info-more 加 max-width: 480px 讓長文字桌面換 2 行</v>
       </c>
     </row>
-    <row r="95" xml:space="preserve">
-      <c r="A95" s="9">
+    <row r="95" ht="129.6" customHeight="1" xml:space="preserve">
+      <c r="A95" s="3">
         <v>93</v>
       </c>
-      <c r="B95" s="9" t="str">
-        <v>V</v>
-      </c>
-      <c r="C95" s="9" t="str">
+      <c r="B95" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C95" s="3" t="str">
         <v>關於長穩</v>
       </c>
-      <c r="D95" s="9" t="str">
-        <v/>
-      </c>
-      <c r="E95" s="9" t="str">
+      <c r="D95" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E95" s="3" t="str">
         <v>提升</v>
       </c>
-      <c r="F95" s="9" t="str">
+      <c r="F95" s="3" t="str">
         <v>互動</v>
       </c>
-      <c r="G95" s="9" t="str">
+      <c r="G95" s="3" t="str">
         <v>中</v>
       </c>
-      <c r="H95" s="9" t="str">
+      <c r="H95" s="3" t="str">
         <v>About 三大核心介紹缺乏互動性</v>
       </c>
-      <c r="I95" s="9" t="str">
+      <c r="I95" s="3" t="str">
         <v>環境保育/人才培育/社會關懷三張卡片原為靜態圖文，使用者掃過無視覺反應，缺乏吸引點擊探索的動機</v>
       </c>
-      <c r="J95" s="9" t="str">
+      <c r="J95" s="3" t="str">
         <v>改造為 iOS Dynamic Island 風格 morph 卡片：暖象牙白漸層底 + 圓角 28px + 預設只露 icon+標題 → hover/click toggle 平滑展開內文（grid-template-rows trick）+ translateY 浮起 + 邊框露出青綠光暈</v>
       </c>
-      <c r="K95" s="9" t="str">
+      <c r="K95" s="3" t="str">
         <v>pages/about.vue</v>
       </c>
-      <c r="L95" s="9" t="str" xml:space="preserve">
-        <v xml:space="preserve">iFare_Frontend/pages/about.vue_x000d_
-assets/style/components/_appBody_about.scss_x000d_
+      <c r="L95" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Frontend/pages/about.vue_x000d__x000d__x000d_
+assets/style/components/_appBody_about.scss_x000d__x000d__x000d_
 assets/style/rwd/_rwd_about.scss</v>
       </c>
-      <c r="M95" s="9" t="str">
+      <c r="M95" s="3" t="str">
         <v>改版補登；HTML 重組（icon+title 合進 .how-top、info 包 .how-info-wrap）；script 加 activeHow ref + toggleHow handler；keyboard a11y (Enter/Space) 與 tabindex；GPU 優化（will-change + ::before opacity overlay 取代 gradient transition）；Apple spring easing cubic-bezier(0.32, 0.72, 0, 1)</v>
       </c>
-      <c r="N95" s="9" t="str">
+      <c r="N95" s="3" t="str">
         <v>已修正</v>
       </c>
-      <c r="O95" s="9" t="str">
+      <c r="O95" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P95" s="9" t="str">
+      <c r="P95" s="3" t="str">
         <v>改版補登；對應 #44 三大核心圖示靜態問題已連動修正</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="9">
+    <row r="96" ht="100.8" customHeight="1">
+      <c r="A96" s="3">
         <v>94</v>
       </c>
-      <c r="B96" s="9" t="str">
-        <v>V</v>
-      </c>
-      <c r="C96" s="9" t="str">
+      <c r="B96" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C96" s="3" t="str">
         <v>關於長穩</v>
       </c>
-      <c r="D96" s="9" t="str">
-        <v/>
-      </c>
-      <c r="E96" s="9" t="str">
+      <c r="D96" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E96" s="3" t="str">
         <v>提升</v>
       </c>
-      <c r="F96" s="9" t="str">
+      <c r="F96" s="3" t="str">
         <v>視覺</v>
       </c>
-      <c r="G96" s="9" t="str">
+      <c r="G96" s="3" t="str">
         <v>低</v>
       </c>
-      <c r="H96" s="9" t="str">
+      <c r="H96" s="3" t="str">
         <v>About 成員照片缺 hover 互動</v>
       </c>
-      <c r="I96" s="9" t="str">
+      <c r="I96" s="3" t="str">
         <v>陳進財/鄔筠軒/顏杏蓉三位成員區塊原無 hover 反饋，掃過時視覺無變化</v>
       </c>
-      <c r="J96" s="9" t="str">
+      <c r="J96" s="3" t="str">
         <v>陳進財/鄔筠軒整組 hover：照片 scale(1.06) + 白框 scale(1.03) + box-shadow 加深 + 橘色標牌 translateY(-4px)；顏杏蓉（無照片）標牌 hover translateY(-4px) + scale(1.04)</v>
       </c>
-      <c r="K96" s="9" t="str">
+      <c r="K96" s="3" t="str">
         <v>pages/about.vue</v>
       </c>
-      <c r="L96" s="9" t="str">
+      <c r="L96" s="3" t="str">
         <v>iFare_Frontend/assets/style/components/_appBody_about.scss</v>
       </c>
-      <c r="M96" s="9" t="str">
+      <c r="M96" s="3" t="str">
         <v>改版補登；同套 cubic-bezier(0.32, 0.72, 0, 1) easing；will-change: transform 給 .member-photo 預先建 GPU layer</v>
       </c>
-      <c r="N96" s="9" t="str">
+      <c r="N96" s="3" t="str">
         <v>已修正</v>
       </c>
-      <c r="O96" s="9" t="str">
+      <c r="O96" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P96" s="9" t="str">
+      <c r="P96" s="3" t="str">
         <v>改版補登</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="9">
+    <row r="97" ht="57.6" customHeight="1">
+      <c r="A97" s="3">
         <v>95</v>
       </c>
-      <c r="B97" s="9" t="str">
-        <v>V</v>
-      </c>
-      <c r="C97" s="9" t="str">
+      <c r="B97" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C97" s="3" t="str">
         <v>關於長穩</v>
       </c>
-      <c r="D97" s="9" t="str">
-        <v/>
-      </c>
-      <c r="E97" s="9" t="str">
+      <c r="D97" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E97" s="3" t="str">
         <v>提升</v>
       </c>
-      <c r="F97" s="9" t="str">
+      <c r="F97" s="3" t="str">
         <v>視覺</v>
       </c>
-      <c r="G97" s="9" t="str">
+      <c r="G97" s="3" t="str">
         <v>低</v>
       </c>
-      <c r="H97" s="9" t="str">
+      <c r="H97" s="3" t="str">
         <v>About 底部 CTA 連結缺 hover micro-animation</v>
       </c>
-      <c r="I97" s="9" t="str">
+      <c r="I97" s="3" t="str">
         <v>「前往 i-Fare」與「查看最新消息」兩個 advance-link 原為靜態，hover 無互動反饋，無法強化「點我前進」訊號</v>
       </c>
-      <c r="J97" s="9" t="str">
+      <c r="J97" s="3" t="str">
         <v>連結 hover 時 translateY(-2px) 上浮，箭頭 icon translateX(6px) 向右滑出，引導視線前進</v>
       </c>
-      <c r="K97" s="9" t="str">
+      <c r="K97" s="3" t="str">
         <v>pages/about.vue</v>
       </c>
-      <c r="L97" s="9" t="str">
+      <c r="L97" s="3" t="str">
         <v>iFare_Frontend/assets/style/components/_appBody_about.scss</v>
       </c>
-      <c r="M97" s="9" t="str">
+      <c r="M97" s="3" t="str">
         <v>改版補登；統一 cubic-bezier(0.32, 0.72, 0, 1) easing 0.22s</v>
       </c>
-      <c r="N97" s="9" t="str">
+      <c r="N97" s="3" t="str">
         <v>已修正</v>
       </c>
-      <c r="O97" s="9" t="str">
+      <c r="O97" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P97" s="9" t="str">
+      <c r="P97" s="3" t="str">
         <v>改版補登</v>
       </c>
     </row>
-    <row r="98" xml:space="preserve">
-      <c r="A98" s="9">
+    <row r="98" ht="129.6" customHeight="1" xml:space="preserve">
+      <c r="A98" s="3">
         <v>96</v>
       </c>
-      <c r="B98" s="9" t="str">
-        <v>V</v>
-      </c>
-      <c r="C98" s="9" t="str">
+      <c r="B98" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C98" s="3" t="str">
         <v>最新消息</v>
       </c>
-      <c r="D98" s="9" t="str">
-        <v/>
-      </c>
-      <c r="E98" s="9" t="str">
+      <c r="D98" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E98" s="3" t="str">
         <v>提升</v>
       </c>
-      <c r="F98" s="9" t="str">
+      <c r="F98" s="3" t="str">
         <v>視覺</v>
       </c>
-      <c r="G98" s="9" t="str">
+      <c r="G98" s="3" t="str">
         <v>中</v>
       </c>
-      <c r="H98" s="9" t="str">
+      <c r="H98" s="3" t="str">
         <v>News 列表呈現升級為浮起卡片 + 入場動畫 + 日期 pill</v>
       </c>
-      <c r="I98" s="9" t="str">
+      <c r="I98" s="3" t="str">
         <v>原本最新消息為「底線分隔的清單列」，hover 只是淡白底 + 箭頭轉橘，視覺扁平、缺乏互動感、日期不醒目、長內文無截斷</v>
       </c>
-      <c r="J98" s="9" t="str">
+      <c r="J98" s="3" t="str">
         <v>列表整體升級：圓角 16px 浮起卡片（white .7 + shadow）+ stagger fade-up 入場動畫（@for 1~12 each +50ms）+ 日期變橘色 pill 標籤（border + 半透明橘底）+ hover translateY(-3px) + 背景變實白 + 箭頭橘色滑右 6px</v>
       </c>
-      <c r="K98" s="9" t="str">
+      <c r="K98" s="3" t="str">
         <v>pages/news.vue</v>
       </c>
-      <c r="L98" s="9" t="str" xml:space="preserve">
-        <v xml:space="preserve">iFare_Frontend/pages/news.vue_x000d_
-assets/style/components/_appBody.scss_x000d_
-assets/style/_animation.scss_x000d_
+      <c r="L98" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Frontend/pages/news.vue_x000d__x000d__x000d_
+assets/style/components/_appBody.scss_x000d__x000d__x000d_
+assets/style/_animation.scss_x000d__x000d__x000d_
 assets/style/rwd/_rwd.scss</v>
       </c>
-      <c r="M98" s="9" t="str">
+      <c r="M98" s="3" t="str">
         <v>改版補登；@keyframes newsItemEnter 放 _animation.scss；統一 cubic-bezier(0.32, 0.72, 0, 1) easing；配色全用既有 token 沒引入新色</v>
       </c>
-      <c r="N98" s="9" t="str">
+      <c r="N98" s="3" t="str">
         <v>已修正</v>
       </c>
-      <c r="O98" s="9" t="str">
+      <c r="O98" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P98" s="9" t="str">
+      <c r="P98" s="3" t="str">
         <v>改版補登；同次改動連帶解決 #23 (line-clamp 2)、#24 (aria-label)、#26 (NEW badge)</v>
       </c>
     </row>
-    <row r="99" xml:space="preserve">
-      <c r="A99" s="9">
+    <row r="99" ht="72" customHeight="1" xml:space="preserve">
+      <c r="A99" s="3">
         <v>97</v>
       </c>
-      <c r="B99" s="9" t="str">
-        <v>V</v>
-      </c>
-      <c r="C99" s="9" t="str">
+      <c r="B99" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C99" s="3" t="str">
         <v>共用元件</v>
       </c>
-      <c r="D99" s="9" t="str">
+      <c r="D99" s="3" t="str">
         <v>AppFooter / AppHeader</v>
       </c>
-      <c r="E99" s="9" t="str">
+      <c r="E99" s="3" t="str">
         <v>修復</v>
       </c>
-      <c r="F99" s="9" t="str">
+      <c r="F99" s="3" t="str">
         <v>互動</v>
       </c>
-      <c r="G99" s="9" t="str">
+      <c r="G99" s="3" t="str">
         <v>低</v>
       </c>
-      <c r="H99" s="9" t="str">
+      <c r="H99" s="3" t="str">
         <v>社群外連結未開新分頁，可能丟失當前頁狀態</v>
       </c>
-      <c r="I99" s="9" t="str">
+      <c r="I99" s="3" t="str">
         <v>AppFooter LINE/Facebook 與 AppHeader 手機版社群 icon 連結原為一般 &lt;a href&gt;，點擊會在當前分頁導向，使用者離開站內後返回成本高</v>
       </c>
-      <c r="J99" s="9" t="str">
+      <c r="J99" s="3" t="str">
         <v>4 個社群連結都加 target="_blank" + rel="noopener noreferrer"：開新分頁、避免反向 tabnabbing、不洩漏 referrer</v>
       </c>
-      <c r="K99" s="9" t="str">
+      <c r="K99" s="3" t="str">
         <v>components/AppFooter.vue components/AppHeader.vue</v>
       </c>
-      <c r="L99" s="9" t="str" xml:space="preserve">
-        <v xml:space="preserve">iFare_Frontend/components/AppFooter.vue_x000d_
+      <c r="L99" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Frontend/components/AppFooter.vue_x000d__x000d__x000d_
 iFare_Frontend/components/AppHeader.vue</v>
       </c>
-      <c r="M99" s="9" t="str">
+      <c r="M99" s="3" t="str">
         <v>改版補登；rel="noopener" 是 W3C 安全建議</v>
       </c>
-      <c r="N99" s="9" t="str">
+      <c r="N99" s="3" t="str">
         <v>已修正</v>
       </c>
-      <c r="O99" s="9" t="str">
+      <c r="O99" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P99" s="9" t="str">
+      <c r="P99" s="3" t="str">
         <v>改版補登</v>
       </c>
     </row>
+    <row r="100" ht="100.8" customHeight="1">
+      <c r="A100" s="3">
+        <v>98</v>
+      </c>
+      <c r="B100" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C100" s="3" t="str">
+        <v>關於長穩</v>
+      </c>
+      <c r="D100" s="3" t="str">
+        <v>三大核心介紹</v>
+      </c>
+      <c r="E100" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F100" s="3" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G100" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H100" s="3" t="str">
+        <v>About 第一張卡 hover 完全無反應 (Round 3 副作用)</v>
+      </c>
+      <c r="I100" s="3" t="str">
+        <v>cf47cfa Round 3 加的 .section-about-member::before 視覺裝飾 (z-index:48 + 1497x1497px 圓形 + top:-300px/left:-750px) 蓋住上方 about-how 區左半邊，攔截「環境保育」第一張 morph 卡的所有 hover/click events。第二、三張位置在中右側未被覆蓋，因此正常運作。</v>
+      </c>
+      <c r="J100" s="3" t="str">
+        <v>裝飾性 ::before 加 pointer-events: none 讓 mouse events 穿透到下層的 .how-content</v>
+      </c>
+      <c r="K100" s="3" t="str">
+        <v>pages/about.vue</v>
+      </c>
+      <c r="L100" s="3" t="str">
+        <v>iFare_Frontend/assets/style/components/_appBody_about.scss</v>
+      </c>
+      <c r="M100" s="3" t="str">
+        <v>修復 cf47cfa 副作用；不影響原視覺 (radial-gradient 橘色光暈仍可見)</v>
+      </c>
+      <c r="N100" s="3" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O100" s="3" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="P100" s="3" t="str">
+        <v>純 1 行 CSS 修法 (.section-about-member::before pointer-events: none)</v>
+      </c>
+    </row>
+    <row r="101" ht="100.8" customHeight="1">
+      <c r="A101" s="3">
+        <v>99</v>
+      </c>
+      <c r="B101" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C101" s="3" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="D101" s="3" t="str">
+        <v>AppFooter</v>
+      </c>
+      <c r="E101" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F101" s="3" t="str">
+        <v>視覺</v>
+      </c>
+      <c r="G101" s="3" t="str">
+        <v>低</v>
+      </c>
+      <c r="H101" s="3" t="str">
+        <v>Footer 聯絡資訊 label 文字重複 (新舊 CSS 共存 bug)</v>
+      </c>
+      <c r="I101" s="3" t="str">
+        <v>5dfbf91/cf47cfa 把 AppFooter.vue 改用顯式 &lt;span class="footer-info-label"&gt; 顯示 label，但舊的 _font.scss `.footer-info-items [name="tel"]::before { content: "聯絡電話" }` 等 4 條規則沒清掉，造成「聯絡電話 📞 聯絡電話 (02)2797-8383」這種重複顯示</v>
+      </c>
+      <c r="J101" s="3" t="str">
+        <v>移除 _font.scss 4 個 ::before content 規則 (tel/mail/address/datetime) 與通用 [name]::before 樣式</v>
+      </c>
+      <c r="K101" s="3" t="str">
+        <v>assets/style/_font.scss</v>
+      </c>
+      <c r="L101" s="3" t="str">
+        <v>iFare_Frontend/assets/style/_font.scss</v>
+      </c>
+      <c r="M101" s="3" t="str">
+        <v>回歸測試 OK；保留 [name="tel"] font-family/color 與 [name="datetime"] span:nth-child Roboto 樣式</v>
+      </c>
+      <c r="N101" s="3" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O101" s="3" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="P101" s="3" t="str">
+        <v>5dfbf91 整理時的 leftover</v>
+      </c>
+    </row>
+    <row r="102" ht="144" customHeight="1">
+      <c r="A102" s="3">
+        <v>100</v>
+      </c>
+      <c r="B102" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C102" s="3" t="str">
+        <v>全站通用</v>
+      </c>
+      <c r="D102" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E102" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F102" s="3" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G102" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H102" s="3" t="str">
+        <v>缺乏全站一致的 hover 靈動回饋</v>
+      </c>
+      <c r="I102" s="3" t="str">
+        <v>既有 hover 散落在 .relation-item / .article-item / .card-* 等個別元件，nav 連結、Footer 按鈕、btn-icon 等沒有統一浮起回饋；使用者「鼠標移到哪都該有靈動」需求未滿足</v>
+      </c>
+      <c r="J102" s="3" t="str">
+        <v>_main.scss 加 .hover-lift utility class (Apple spring 0.22s + translateY -2px) + 自動套用到 .app-header nav / .app-footer .btn / .app-footer a / .btn-social / .btn-icon。既有自訂 hover (about morph 卡、news 浮起卡) 不受影響</v>
+      </c>
+      <c r="K102" s="3" t="str">
+        <v>assets/style/_main.scss</v>
+      </c>
+      <c r="L102" s="3" t="str">
+        <v>iFare_Frontend/assets/style/_main.scss</v>
+      </c>
+      <c r="M102" s="3" t="str">
+        <v>cubic-bezier(0.32, 0.72, 0, 1) 與 about morph 卡同套 easing</v>
+      </c>
+      <c r="N102" s="3" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O102" s="3" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="P102" s="3" t="str">
+        <v>對應 #62 (.btn-filter/.btn-tag hover) 不重疊 — Round 4 涵蓋的是 nav/footer 類；ifare 搜尋按鈕的 ripple 仍待補</v>
+      </c>
+    </row>
+    <row r="103" ht="115.2" customHeight="1" xml:space="preserve">
+      <c r="A103" s="3">
+        <v>101</v>
+      </c>
+      <c r="B103" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C103" s="3" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="D103" s="3" t="str">
+        <v>AppHeader</v>
+      </c>
+      <c r="E103" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F103" s="3" t="str">
+        <v>內容</v>
+      </c>
+      <c r="G103" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H103" s="3" t="str">
+        <v>缺少「未來規劃」頁面入口</v>
+      </c>
+      <c r="I103" s="3" t="str">
+        <v>主管要求增加「未來規劃」展示基金會願景，nav 應有對應入口</v>
+      </c>
+      <c r="J103" s="3" t="str">
+        <v>AppHeader 桌面 nav 在 公益夥伴 與 i-Fare 之間插入「未來規劃」連結；行動 nav 加在最後 (與既有 i-Fare/公益夥伴 mobile 順序一致)；新增 pages/future.vue 標題 + FUTURE shadow + 「內容建置中，敬請期待」佔位</v>
+      </c>
+      <c r="K103" s="3" t="str">
+        <v>components/AppHeader.vue + pages/future.vue (新)</v>
+      </c>
+      <c r="L103" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Frontend/components/AppHeader.vue_x000d__x000d__x000d_
+iFare_Frontend/pages/future.vue (新)</v>
+      </c>
+      <c r="M103" s="3" t="str">
+        <v>route /future 已 wire；之後接 CMS 內容由 admin 管理</v>
+      </c>
+      <c r="N103" s="3" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O103" s="3" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="P103" s="3" t="str">
+        <v>頁面為佔位，等內容/設計稿確認後再填內</v>
+      </c>
+    </row>
+    <row r="104" ht="144" customHeight="1" xml:space="preserve">
+      <c r="A104" s="3">
+        <v>102</v>
+      </c>
+      <c r="B104" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C104" s="3" t="str">
+        <v>最新消息</v>
+      </c>
+      <c r="D104" s="3" t="str">
+        <v>文章詳情</v>
+      </c>
+      <c r="E104" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F104" s="3" t="str">
+        <v>內容</v>
+      </c>
+      <c r="G104" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H104" s="3" t="str">
+        <v>News 詳情頁缺乏多媒體展示能力</v>
+      </c>
+      <c r="I104" s="3" t="str">
+        <v>主管希望最新消息可內嵌 YouTube 影片，目前只有 HTML 編輯器內可手動貼連結，無內嵌影片渲染</v>
+      </c>
+      <c r="J104" s="3" t="str">
+        <v>後台 admin 加「影片網址」el-input + WebAPI.ts InsertNews/UpdateNews 加 videoUrl 參數；前台 news/info.vue 加 iframe section + YouTube URL → embed URL parser (regex 抓 11 字元 video ID) + 16:9 響應式容器 (padding-top: 56.25%)</v>
+      </c>
+      <c r="K104" s="3" t="str">
+        <v>pages/news/info.vue + News_AddEditView.vue (admin) + WebAPI.ts (admin)</v>
+      </c>
+      <c r="L104" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Frontend/pages/news/info.vue_x000d__x000d__x000d_
+iFare_Backend/src/views/News/News_AddEditView.vue_x000d__x000d__x000d_
+iFare_Backend/src/plugins/WebAPI.ts</v>
+      </c>
+      <c r="M104" s="3" t="str">
+        <v>UI 端 wiring 完成；對應後臺優化 #13 (.NET News VideoUrl 欄位)</v>
+      </c>
+      <c r="N104" s="3" t="str">
+        <v>部分修正</v>
+      </c>
+      <c r="O104" s="3" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="P104" s="3" t="str">
+        <v>等 .NET 後端 News.cs entity + DTO + EF migration 加 VideoUrl 才能真實運作</v>
+      </c>
+    </row>
+    <row r="105" ht="115.2" customHeight="1" xml:space="preserve">
+      <c r="A105" s="3">
+        <v>103</v>
+      </c>
+      <c r="B105" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C105" s="3" t="str">
+        <v>全站通用</v>
+      </c>
+      <c r="D105" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E105" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F105" s="3" t="str">
+        <v>程式碼</v>
+      </c>
+      <c r="G105" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H105" s="3" t="str">
+        <v>本機開發 API 連線失敗 (環境設定指本機 .NET，但機器沒 .NET SDK)</v>
+      </c>
+      <c r="I105" s="3" t="str">
+        <v>前台 nuxt.config.ts devProxy target 寫死 https://localhost:44312 / 後台 AjaxRef.ts baseURL prod 寫死 http://10.200.0.39 (公司內網 IP)，導致：(1) 本機 dev 抓 dropdown 全 404 (2) 後台 admin Login 失敗 (家用網路 reach 不到 10.200.0.39 內網 IP)</v>
+      </c>
+      <c r="J105" s="3" t="str">
+        <v>前台 nuxt.config.ts devProxy target 改 https://www.i-fare.org.tw/ifare_api/api/services/app；後台 AjaxRef.getBaseUrl() 改 https://www.i-fare.org.tw/ifare_bdapi (固定走正式)</v>
+      </c>
+      <c r="K105" s="3" t="str">
+        <v>nuxt.config.ts (前台) + AjaxRef.ts (後台)</v>
+      </c>
+      <c r="L105" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Frontend/nuxt.config.ts_x000d__x000d__x000d_
+iFare_Backend/src/plugins/AjaxRef.ts</v>
+      </c>
+      <c r="M105" s="3" t="str">
+        <v>Login 已驗證可通；前台 dropdown 已能抓資料</v>
+      </c>
+      <c r="N105" s="3" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O105" s="3" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="P105" s="3" t="str">
+        <v>對應後臺優化 #8 / #14 (baseURL 環境變數化) — 目前是治標處理，等之後完整改成 .env</v>
+      </c>
+    </row>
+    <row r="106" ht="172.80000000000004" customHeight="1" xml:space="preserve">
+      <c r="A106" s="3">
+        <v>104</v>
+      </c>
+      <c r="B106" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C106" s="3" t="str">
+        <v>全站通用</v>
+      </c>
+      <c r="D106" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E106" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F106" s="3" t="str">
+        <v>程式碼</v>
+      </c>
+      <c r="G106" s="3" t="str">
+        <v>低</v>
+      </c>
+      <c r="H106" s="3" t="str">
+        <v>VS Code 顯示 3 個 TypeScript deprecation warning</v>
+      </c>
+      <c r="I106" s="3" t="str">
+        <v>iFare_Backend/tsconfig.app.json 用 baseUrl + moduleResolution=node10 / iFare_Frontend/tsconfig.json 透過 .nuxt/tsconfig.json extend 也帶 node10，被 TypeScript 5.x 標 deprecated (TS 7.0 才停用)</v>
+      </c>
+      <c r="J106" s="3" t="str">
+        <v>加 "ignoreDeprecations": "6.0" — 後台直接放 tsconfig.app.json compilerOptions；前台改透過 nuxt.config.ts typescript.tsConfig.compilerOptions 注入 .nuxt/tsconfig.json (因為 user-facing tsconfig.json 加 ignoreDeprecations 抑制不到 extend 的 .nuxt/tsconfig.json)</v>
+      </c>
+      <c r="K106" s="3" t="str">
+        <v>tsconfig.app.json + tsconfig.json + nuxt.config.ts</v>
+      </c>
+      <c r="L106" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Backend/tsconfig.app.json_x000d__x000d__x000d_
+iFare_Frontend/tsconfig.json_x000d__x000d__x000d_
+iFare_Frontend/nuxt.config.ts</v>
+      </c>
+      <c r="M106" s="3" t="str">
+        <v>TS 5.x 不影響執行 / build</v>
+      </c>
+      <c r="N106" s="3" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O106" s="3" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="P106" s="3" t="str">
+        <v>純 IDE 觀感修補；VS Code 需 Ctrl+Shift+P → Restart TS Server 才會 reload</v>
+      </c>
+    </row>
+    <row r="107" ht="115.2" customHeight="1" xml:space="preserve">
+      <c r="A107" s="3">
+        <v>105</v>
+      </c>
+      <c r="B107" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C107" s="3" t="str">
+        <v>全站通用</v>
+      </c>
+      <c r="D107" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E107" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F107" s="3" t="str">
+        <v>程式碼</v>
+      </c>
+      <c r="G107" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H107" s="3" t="str">
+        <v>主管手動合併 master 時漏合 5dfbf91/cf47cfa 部分改動</v>
+      </c>
+      <c r="I107" s="3" t="str">
+        <v>切到 master 開 feat/uiux-round4 新分支後抽樣驗證發現：5dfbf91 漏合的 footer 樣式 (LINE 綠/FB 藍 SVG icon、_appFooter.scss 重新設計、_animation.scss page transition、_rwd_appFooter.scss、Mail/Clock SVG)；cf47cfa 整個沒合 (About 靈動島 + News 卡片升級 + 社群外連結) — 9 個檔</v>
+      </c>
+      <c r="J107" s="3" t="str">
+        <v>從 frontend 分支 git show 補回 16 個檔到新分支對應路徑 (Dev/Dev Code/iFare_Frontend/...)；cf47cfa 9 檔以 d5a7674 commit；footer 7 檔以 e2b1cae commit</v>
+      </c>
+      <c r="K107" s="3" t="str">
+        <v>16 個 SCSS / Vue / SVG</v>
+      </c>
+      <c r="L107" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dev/Dev Code/iFare_Frontend/assets/style/components/_appFooter.scss_x000d__x000d__x000d_
+iFare_Frontend/assets/style/_animation.scss_x000d__x000d__x000d_
+iFare_Frontend/components/AppFooter.vue 等 16 檔</v>
+      </c>
+      <c r="M107" s="3" t="str">
+        <v>修補 release 環境必要</v>
+      </c>
+      <c r="N107" s="3" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O107" s="3" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="P107" s="3" t="str">
+        <v>不是純 UI/UX 議題，但屬於 Round 1-3 work 真正落地的前提</v>
+      </c>
+    </row>
+    <row r="108" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A108" s="3">
+        <v>106</v>
+      </c>
+      <c r="B108" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C108" s="3" t="str">
+        <v>安全性</v>
+      </c>
+      <c r="D108" s="3" t="str">
+        <v>v-html XSS</v>
+      </c>
+      <c r="E108" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F108" s="3" t="str">
+        <v>程式碼</v>
+      </c>
+      <c r="G108" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H108" s="3" t="str">
+        <v>v-html 渲染未清理的服務器內容，存在 XSS 風險</v>
+      </c>
+      <c r="I108" s="3" t="str">
+        <v>news/info, articles/lazy, articles/welfare, ifare/info 多頁用 v-html 渲染 API content；若後端未正確清理 HTML/JavaScript，可遭 XSS</v>
+      </c>
+      <c r="J108" s="3" t="str">
+        <v>用 DOMPurify 或 sanitize-html 清理 HTML；至少在伺服器端驗證內容不含危險標籤</v>
+      </c>
+      <c r="K108" s="3" t="str">
+        <v>pages/news/info.vue + articles/lazy/welfare + ifare/info</v>
+      </c>
+      <c r="L108" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Frontend/pages/news/info.vue (L25)_x000d__x000d_
+iFare_Frontend/pages/articles/lazy.vue (L16)_x000d__x000d_
+iFare_Frontend/pages/articles/welfare.vue (L19)_x000d__x000d_
+iFare_Frontend/pages/ifare/info.vue (L23, 31, 40, 47)</v>
+      </c>
+      <c r="M108" s="3" t="str">
+        <v>高優先級安全缺陷</v>
+      </c>
+      <c r="N108" s="3" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O108" s="3" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="P108" s="3" t="str">
+        <v>Round 9 (批次 B): 安裝 isomorphic-dompurify (SSR + client safe)；新增 composables/useSanitize.ts 統一清理規範 (white-list ALLOWED_TAGS / ALLOWED_ATTR、阻 javascript:/data: URI、FORBID script/style/iframe/onerror)；7 處 v-html 用 useSanitize 包起來: news/info、articles/lazy、articles/welfare、ifare/info × 4 (qualification/welfareInfo/evidence/remark)。</v>
+      </c>
+    </row>
+    <row r="109" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A109" s="3">
+        <v>107</v>
+      </c>
+      <c r="B109" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C109" s="3" t="str">
+        <v>全站通用</v>
+      </c>
+      <c r="D109" s="3" t="str">
+        <v>WebAPI 錯誤處理</v>
+      </c>
+      <c r="E109" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F109" s="3" t="str">
+        <v>程式碼</v>
+      </c>
+      <c r="G109" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H109" s="3" t="str">
+        <v>WebAPI.ts 未區分錯誤類型，一律 return null，頁面無法判斷失敗原因</v>
+      </c>
+      <c r="I109" s="3" t="str">
+        <v>plugins/WebAPI.ts (L9-15) 捕獲所有錯誤返回 null，無法區分網路超時/伺服器 500/驗證失敗；news.vue 等雖有 hasError 但無法提示具體原因</v>
+      </c>
+      <c r="J109" s="3" t="str">
+        <v>返回結構化錯誤物件 {code, message, status}，頁面根據錯誤類型顯示不同提示 (網路錯誤、伺服器維護中等)</v>
+      </c>
+      <c r="K109" s="3" t="str">
+        <v>plugins/WebAPI.ts</v>
+      </c>
+      <c r="L109" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Frontend/plugins/WebAPI.ts_x000d__x000d_
+iFare_Frontend/pages/news.vue_x000d__x000d_
+iFare_Frontend/pages/articles.vue_x000d__x000d_
+iFare_Frontend/pages/ifare.vue</v>
+      </c>
+      <c r="M109" s="3" t="str">
+        <v>影響全站用戶體驗</v>
+      </c>
+      <c r="N109" s="3" t="str">
+        <v>部分修正</v>
+      </c>
+      <c r="O109" s="3" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="P109" s="3" t="str">
+        <v>Round 9 (批次 B): plugins/WebAPI.ts 加 categorizeError (timeout/network/client/server/unknown)、結構化 logError 取代 console.error、try-catch wrapper。Return signature 不變 (data/null) 維持向下相容，所有 caller 不用改。**UI 端錯誤呈現** (顯示 toast / 重試提示) 尚未做，需與整體錯誤元件設計一起。</v>
+      </c>
+    </row>
+    <row r="110" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A110" s="3">
+        <v>108</v>
+      </c>
+      <c r="B110" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C110" s="3" t="str">
+        <v>全站通用</v>
+      </c>
+      <c r="D110" s="3" t="str">
+        <v>API 超時</v>
+      </c>
+      <c r="E110" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F110" s="3" t="str">
+        <v>效能</v>
+      </c>
+      <c r="G110" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H110" s="3" t="str">
+        <v>$fetch 無超時設定，API 無回應頁面會無限期卡 loading</v>
+      </c>
+      <c r="I110" s="3" t="str">
+        <v>所有頁面的 API 呼叫未設 timeout，若 API 無回應，UI 會永遠停在 loading 無退出機制</v>
+      </c>
+      <c r="J110" s="3" t="str">
+        <v>WebAPI.ts 設預設 timeout 10-15 秒，超時返回特定錯誤碼讓頁面顯示「連線逾時，請重試」</v>
+      </c>
+      <c r="K110" s="3" t="str">
+        <v>plugins/WebAPI.ts</v>
+      </c>
+      <c r="L110" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Frontend/plugins/WebAPI.ts_x000d__x000d_
+iFare_Frontend/pages/news/info.vue_x000d__x000d_
+iFare_Frontend/pages/articles/lazy.vue_x000d__x000d_
+iFare_Frontend/pages/articles/welfare.vue_x000d__x000d_
+iFare_Frontend/pages/ifare/contact.vue</v>
+      </c>
+      <c r="M110" s="3" t="str">
+        <v>可能導致用戶感知應用無反應</v>
+      </c>
+      <c r="N110" s="3" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O110" s="3" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="P110" s="3" t="str">
+        <v>Round 9 (批次 B): plugins/WebAPI.ts WebApiGet/WebApiPost $fetch 加 timeout: API_TIMEOUT_MS (15000ms)。逾時會被 categorizeError 標記為 timeout 類別。</v>
+      </c>
+    </row>
+    <row r="111" ht="14.4" customHeight="1">
+      <c r="A111" s="3">
+        <v>109</v>
+      </c>
+      <c r="B111" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C111" s="3" t="str">
+        <v>i-Fare 福利查詢</v>
+      </c>
+      <c r="D111" s="3" t="str">
+        <v>ifare/contact</v>
+      </c>
+      <c r="E111" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F111" s="3" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G111" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H111" s="3" t="str">
+        <v>contact.vue 缺 API 失敗處理，API 失敗用戶看不到內容</v>
+      </c>
+      <c r="I111" s="3" t="str">
+        <v>ifare/contact.vue (L153) 呼叫 GetIFareOfficeUnitList 但無檢查 res.result、無 catch 區塊、無 loading/error 狀態。若 API 失敗頁面呈現空白</v>
+      </c>
+      <c r="J111" s="3" t="str">
+        <v>加 try-catch、loading ref、error 狀態，仿 news.vue 的錯誤處理模式</v>
+      </c>
+      <c r="K111" s="3" t="str">
+        <v>pages/ifare/contact.vue</v>
+      </c>
+      <c r="L111" s="3" t="str">
+        <v>iFare_Frontend/pages/ifare/contact.vue</v>
+      </c>
+      <c r="M111" s="3" t="str">
+        <v>用戶無法看到聯絡資訊時毫無提示</v>
+      </c>
+      <c r="N111" s="3" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O111" s="3" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="P111" s="3" t="str">
+        <v>Round 9 (批次 B): pages/ifare/contact.vue 重構為 loadOfficeUnit() async + isLoading/hasError ref。template 加 v-if 三分支: loading (skeleton-line role=status)、error (重試按鈕 role=alert)、success (原內容)。重試會清空既有資料再呼叫。</v>
+      </c>
+    </row>
+    <row r="112" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A112" s="3">
+        <v>110</v>
+      </c>
+      <c r="B112" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C112" s="3" t="str">
+        <v>全站通用</v>
+      </c>
+      <c r="D112" s="3" t="str">
+        <v>console.log</v>
+      </c>
+      <c r="E112" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F112" s="3" t="str">
+        <v>程式碼</v>
+      </c>
+      <c r="G112" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H112" s="3" t="str">
+        <v>生產環境仍有 20+ 個 console.log，洩露內部邏輯</v>
+      </c>
+      <c r="I112" s="3" t="str">
+        <v>news.vue (L198), ifare.vue (L305), ifare/result.vue (L236-265, 385, 541), ifare/contact.vue (L163, 193) 等多處 console.log，可被用戶開發工具看到</v>
+      </c>
+      <c r="J112" s="3" t="str">
+        <v>移除所有生產 console.log，改用生產環境禁用的日誌系統，或開發時用環境變數判斷</v>
+      </c>
+      <c r="K112" s="3" t="str">
+        <v>多 pages</v>
+      </c>
+      <c r="L112" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Frontend/pages/news.vue_x000d__x000d_
+iFare_Frontend/pages/ifare.vue_x000d__x000d_
+iFare_Frontend/pages/ifare/result.vue_x000d__x000d_
+iFare_Frontend/pages/ifare/contact.vue_x000d__x000d_
+iFare_Frontend/components/CompPage.vue_x000d__x000d_
+iFare_Frontend/components/CompPageNum.vue</v>
+      </c>
+      <c r="M112" s="3" t="str">
+        <v>安全與代碼質量問題</v>
+      </c>
+      <c r="N112" s="3" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O112" s="3" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="P112" s="3" t="str">
+        <v>Round 7 (批次 A): 移除 13 處 console.log — pages/news.vue (1)、pages/ifare.vue (1)、pages/ifare/result.vue (5)、pages/ifare/contact.vue (2)、components/CompPage.vue (4)。保留 pages/ifare/info.vue:203 的 console.error (catch 內合理錯誤處理)。</v>
+      </c>
+    </row>
+    <row r="113" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A113" s="3">
+        <v>111</v>
+      </c>
+      <c r="B113" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C113" s="3" t="str">
+        <v>未來規劃</v>
+      </c>
+      <c r="D113" s="3" t="str">
+        <v>future.vue</v>
+      </c>
+      <c r="E113" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F113" s="3" t="str">
+        <v>內容</v>
+      </c>
+      <c r="G113" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H113" s="3" t="str">
+        <v>future.vue 佔位符無實質內容，無 SEO 規劃</v>
+      </c>
+      <c r="I113" s="3" t="str">
+        <v>future.vue 為純佔位「內容建置中」，無 h1/h2 層級標題、無內容日期、無導航結構</v>
+      </c>
+      <c r="J113" s="3" t="str">
+        <v>規劃內容架構 (路線圖/時程表)，新增 h1 + 描述 + 圖片；補 meta description for SEO</v>
+      </c>
+      <c r="K113" s="3" t="str">
+        <v>pages/future.vue</v>
+      </c>
+      <c r="L113" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Frontend/pages/future.vue_x000d__x000d_
+iFare_Frontend/nuxt.config.ts (SEO)</v>
+      </c>
+      <c r="M113" s="3" t="str">
+        <v>用戶感受不佳，搜尋引擎爬蟲無內容</v>
+      </c>
+      <c r="N113" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O113" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P113" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="114" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A114" s="3">
+        <v>112</v>
+      </c>
+      <c r="B114" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C114" s="3" t="str">
+        <v>無障礙</v>
+      </c>
+      <c r="D114" s="3" t="str">
+        <v>圖片 alt</v>
+      </c>
+      <c r="E114" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F114" s="3" t="str">
+        <v>無障礙</v>
+      </c>
+      <c r="G114" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H114" s="3" t="str">
+        <v>多頁圖片 alt 屬性缺失 (collaborator, articles/lazy, index 背景)</v>
+      </c>
+      <c r="I114" s="3" t="str">
+        <v>collaborator.vue (L22) &lt;img&gt; 無 alt；articles/lazy.vue (L77) 自動生成 &lt;img&gt; 無 alt；index 背景 CSS 無 alt</v>
+      </c>
+      <c r="J114" s="3" t="str">
+        <v>所有 img 加 alt (collaborator 用機構名稱，articles/lazy 用文章標題)；背景圖改 img 或加 aria-label</v>
+      </c>
+      <c r="K114" s="3" t="str">
+        <v>collaborator / articles/lazy / index</v>
+      </c>
+      <c r="L114" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Frontend/pages/collaborator.vue_x000d__x000d_
+iFare_Frontend/pages/articles/lazy.vue_x000d__x000d_
+iFare_Frontend/pages/index.vue</v>
+      </c>
+      <c r="M114" s="3" t="str">
+        <v>WCAG 2.1 AA 必要，影響視障用戶</v>
+      </c>
+      <c r="N114" s="3" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O114" s="3" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="P114" s="3" t="str">
+        <v>Round 8 (批次 C): pages/index.vue 的 .part-bg-top 加 aria-hidden="true" — 5 張裝飾性 .bg-img 不需被屏幕閱讀器讀。collaborator.vue + articles/lazy.vue 的 &lt;img&gt; alt 已在 Round 7 (#127) 順手做。</v>
+      </c>
+    </row>
+    <row r="115" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A115" s="3">
+        <v>113</v>
+      </c>
+      <c r="B115" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C115" s="3" t="str">
+        <v>i-Fare 福利查詢</v>
+      </c>
+      <c r="D115" s="3" t="str">
+        <v>搜尋表單</v>
+      </c>
+      <c r="E115" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F115" s="3" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G115" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H115" s="3" t="str">
+        <v>搜尋表單無即時驗證、無字數限制提示、無清空按鈕視覺反饋</v>
+      </c>
+      <c r="I115" s="3" t="str">
+        <v>ifare.vue 關鍵字輸入無 maxlength、無字數計數、無驗證提示；清空按鈕無動畫反饋；ifare/result.vue 篩選表單也無</v>
+      </c>
+      <c r="J115" s="3" t="str">
+        <v>加 maxlength + 字數/上限顯示；清空按鈕加 spin 動畫；驗證失敗 focus 至第一錯誤欄位 + aria-describedby</v>
+      </c>
+      <c r="K115" s="3" t="str">
+        <v>pages/ifare.vue + ifare/result.vue</v>
+      </c>
+      <c r="L115" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Frontend/pages/ifare.vue_x000d__x000d_
+iFare_Frontend/pages/ifare/result.vue</v>
+      </c>
+      <c r="M115" s="3" t="str">
+        <v>提升用戶體驗與表單可用性</v>
+      </c>
+      <c r="N115" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O115" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P115" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="116" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A116" s="3">
+        <v>114</v>
+      </c>
+      <c r="B116" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C116" s="3" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="D116" s="3" t="str">
+        <v>CompSelect 鍵盤</v>
+      </c>
+      <c r="E116" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F116" s="3" t="str">
+        <v>無障礙</v>
+      </c>
+      <c r="G116" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H116" s="3" t="str">
+        <v>CompSelect 系列元件無鍵盤操作 (Tab/Enter/Esc/Arrow)，僅滑鼠</v>
+      </c>
+      <c r="I116" s="3" t="str">
+        <v>CompSelect / CompSelectRecipient / CompSelectElse 的開關、選項點擊均未綁定鍵盤事件，無法用鍵盤導航選擇</v>
+      </c>
+      <c r="J116" s="3" t="str">
+        <v>加 @keydown.tab/enter/esc/arrow-down/up 事件，實現 ARIA authoring practices 完整鍵盤導航</v>
+      </c>
+      <c r="K116" s="3" t="str">
+        <v>components/CompSelect*</v>
+      </c>
+      <c r="L116" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Frontend/components/CompSelect.vue_x000d__x000d_
+iFare_Frontend/components/CompSelectRecipient.vue_x000d__x000d_
+iFare_Frontend/components/CompSelectElse.vue</v>
+      </c>
+      <c r="M116" s="3" t="str">
+        <v>WCAG 2.1 AA 必要</v>
+      </c>
+      <c r="N116" s="3" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O116" s="3" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="P116" s="3" t="str">
+        <v>Round 8 (批次 C): 3 個 component (CompSelect / CompSelectRecipient / CompSelectElse) 加 tabindex="0" + role="combobox" + aria-expanded + aria-haspopup + aria-label。CompSelect / CompSelectRecipient 加完整鍵盤導航 (Enter/Space toggle 或選擇 focused 項目；Esc 關閉；Arrow Up/Down 切換 focused 項目)；CompSelectElse 因含兩組選項 (Income + Identity) 結構複雜，僅加 Enter/Space toggle + Esc 關閉，方向鍵需後續再處理。選項加 role="option" + aria-selected。</v>
+      </c>
+    </row>
+    <row r="117" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A117" s="3">
+        <v>115</v>
+      </c>
+      <c r="B117" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C117" s="3" t="str">
+        <v>無障礙</v>
+      </c>
+      <c r="D117" s="3" t="str">
+        <v>Heading 層級</v>
+      </c>
+      <c r="E117" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F117" s="3" t="str">
+        <v>無障礙</v>
+      </c>
+      <c r="G117" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H117" s="3" t="str">
+        <v>Heading 層級結構不規範，多頁 h3 直接跟 h1 後，h6 用於非末級</v>
+      </c>
+      <c r="I117" s="3" t="str">
+        <v>about.vue (L11 h3 缺 h2)、index.vue (L21 h1 + L38 h3)、news/info.vue (L4 h2 後直接 h6)、ifare/info.vue (L5 h1 + L21 h3) 不遵循層級規則</v>
+      </c>
+      <c r="J117" s="3" t="str">
+        <v>調整 heading 層級遞增 (h1 &gt; h2 &gt; h3...)；不跳級；副標題用適當 h2-h3 而非 h6</v>
+      </c>
+      <c r="K117" s="3" t="str">
+        <v>about / index / news/info / ifare/info / collaborator</v>
+      </c>
+      <c r="L117" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Frontend/pages/about.vue_x000d__x000d_
+iFare_Frontend/pages/index.vue_x000d__x000d_
+iFare_Frontend/pages/news/info.vue_x000d__x000d_
+iFare_Frontend/pages/ifare/info.vue_x000d__x000d_
+iFare_Frontend/pages/collaborator.vue</v>
+      </c>
+      <c r="M117" s="3" t="str">
+        <v>影響屏幕閱讀器用戶導航</v>
+      </c>
+      <c r="N117" s="3" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O117" s="3" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="P117" s="3" t="str">
+        <v>Round 8 (批次 C): 已 grep 確認 SCSS 全用 class selector (.comp-title / .member-name / .news-title 等)，改 tag 不破壞視覺。修正：about.vue (h3 → h1 主標 / h6 → h4 member-name × 3)；index.vue (h3 → p sub-title / h2 → h4 news-title / h2 → h4 card-title)；news/info.vue (h6 → p article-date)；ifare/info.vue (h3 → h2 × 5 區塊標 / h5 → h2 relation-title / h6 → h3 link-title)。</v>
+      </c>
+    </row>
+    <row r="118" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A118" s="3">
+        <v>116</v>
+      </c>
+      <c r="B118" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C118" s="3" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="D118" s="3" t="str">
+        <v>CompPage / CompPageNum</v>
+      </c>
+      <c r="E118" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F118" s="3" t="str">
+        <v>程式碼</v>
+      </c>
+      <c r="G118" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H118" s="3" t="str">
+        <v>分頁元件 CompPage 與 CompPageNum 重複且 isHide 邏輯有 bug</v>
+      </c>
+      <c r="I118" s="3" t="str">
+        <v>CompPage.vue (L70-93) 與 CompPageNum.vue (L53-83) 幾乎完全重複；isHide 隱藏頁碼但未正確更新 currentPage；articles/ifare 同時引入兩個造成混淆</v>
+      </c>
+      <c r="J118" s="3" t="str">
+        <v>合併兩個元件為一個通用 CompPageNum，根據 props 選 num 或 list 模式；修正 isHide 邏輯</v>
+      </c>
+      <c r="K118" s="3" t="str">
+        <v>CompPage.vue + CompPageNum.vue</v>
+      </c>
+      <c r="L118" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Frontend/components/CompPage.vue_x000d__x000d_
+iFare_Frontend/components/CompPageNum.vue_x000d__x000d_
+iFare_Frontend/pages/articles.vue_x000d__x000d_
+iFare_Frontend/pages/ifare.vue_x000d__x000d_
+iFare_Frontend/pages/news.vue</v>
+      </c>
+      <c r="M118" s="3" t="str">
+        <v>代碼重複率高，易維護錯誤</v>
+      </c>
+      <c r="N118" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O118" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P118" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="119" ht="14.4" customHeight="1">
+      <c r="A119" s="3">
+        <v>117</v>
+      </c>
+      <c r="B119" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C119" s="3" t="str">
+        <v>福利專欄</v>
+      </c>
+      <c r="D119" s="3" t="str">
+        <v>articles loading</v>
+      </c>
+      <c r="E119" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F119" s="3" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G119" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H119" s="3" t="str">
+        <v>articles.vue 福利專欄/懶人包列表無 loading 狀態或骨架屏</v>
+      </c>
+      <c r="I119" s="3" t="str">
+        <v>articles.vue 沒顯示是否在加載；若 API 遲緩用戶看不到視覺反饋；news.vue 有骨架屏 (L21-25)，但 articles.vue 沒</v>
+      </c>
+      <c r="J119" s="3" t="str">
+        <v>為 welfareList / lazyList 加 loading ref，加載期間顯示骨架屏或 spinner；完成後顯示內容或空狀態</v>
+      </c>
+      <c r="K119" s="3" t="str">
+        <v>pages/articles.vue</v>
+      </c>
+      <c r="L119" s="3" t="str">
+        <v>iFare_Frontend/pages/articles.vue</v>
+      </c>
+      <c r="M119" s="3" t="str">
+        <v>一致性提升</v>
+      </c>
+      <c r="N119" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O119" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P119" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120" ht="14.4" customHeight="1">
+      <c r="A120" s="3">
+        <v>118</v>
+      </c>
+      <c r="B120" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C120" s="3" t="str">
+        <v>最新消息</v>
+      </c>
+      <c r="D120" s="3" t="str">
+        <v>iframe 安全</v>
+      </c>
+      <c r="E120" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F120" s="3" t="str">
+        <v>程式碼</v>
+      </c>
+      <c r="G120" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H120" s="3" t="str">
+        <v>YouTube iframe 缺 sandbox 屬性，allow 過寬鬆</v>
+      </c>
+      <c r="I120" s="3" t="str">
+        <v>news/info.vue (L12-19) iframe allow 含 accelerometer/autoplay/clipboard-write 等未設 sandbox，可能被跨域腳本利用</v>
+      </c>
+      <c r="J120" s="3" t="str">
+        <v>加 sandbox="allow-same-origin allow-scripts allow-presentation"；移除非必要 allow (例如 clipboard-write)</v>
+      </c>
+      <c r="K120" s="3" t="str">
+        <v>pages/news/info.vue</v>
+      </c>
+      <c r="L120" s="3" t="str">
+        <v>iFare_Frontend/pages/news/info.vue</v>
+      </c>
+      <c r="M120" s="3" t="str">
+        <v>防止潛在跨域攻擊</v>
+      </c>
+      <c r="N120" s="3" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O120" s="3" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="P120" s="3" t="str">
+        <v>Round 9 (批次 B): pages/news/info.vue 的 YouTube iframe 加 sandbox="allow-same-origin allow-scripts allow-presentation allow-popups"；移除非必要 allow="clipboard-write" (剪貼簿權限不應自動給)。</v>
+      </c>
+    </row>
+    <row r="121" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A121" s="3">
+        <v>119</v>
+      </c>
+      <c r="B121" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C121" s="3" t="str">
+        <v>頁面導航</v>
+      </c>
+      <c r="D121" s="3" t="str">
+        <v>reload query</v>
+      </c>
+      <c r="E121" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F121" s="3" t="str">
+        <v>程式碼</v>
+      </c>
+      <c r="G121" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H121" s="3" t="str">
+        <v>articles/lazy/welfare/ifare/info 用 reload query 但未在 watch 監聽</v>
+      </c>
+      <c r="I121" s="3" t="str">
+        <v>NuxtLink query 含 reload: ""，但 script 未 watch route.query.reload 觸發重新加載；從同頁不同 ID 回本頁時可能顯示舊資料</v>
+      </c>
+      <c r="J121" s="3" t="str">
+        <v>setup 中 watch route.query.reload 或整個 route.query，變化時重呼叫 API；或 watchEffect 監 _lazyID/releaseTime</v>
+      </c>
+      <c r="K121" s="3" t="str">
+        <v>pages/articles/lazy/welfare + ifare/info</v>
+      </c>
+      <c r="L121" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Frontend/pages/articles/lazy.vue_x000d__x000d_
+iFare_Frontend/pages/articles/welfare.vue_x000d__x000d_
+iFare_Frontend/pages/ifare/info.vue</v>
+      </c>
+      <c r="M121" s="3" t="str">
+        <v>SPA 路由缺陷</v>
+      </c>
+      <c r="N121" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O121" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P121" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="122" ht="14.4" customHeight="1">
+      <c r="A122" s="3">
+        <v>120</v>
+      </c>
+      <c r="B122" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C122" s="3" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="D122" s="3" t="str">
+        <v>AppFooter 版權</v>
+      </c>
+      <c r="E122" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F122" s="3" t="str">
+        <v>內容</v>
+      </c>
+      <c r="G122" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H122" s="3" t="str">
+        <v>Footer 版權年份過舊 (1995-2020)，已過期 6 年</v>
+      </c>
+      <c r="I122" s="3" t="str">
+        <v>AppFooter.vue (L42) 顯示「© 1995-2020」，現在是 2026</v>
+      </c>
+      <c r="J122" s="3" t="str">
+        <v>改 `© 1995-${new Date().getFullYear()}`，或在 footer data 中維護</v>
+      </c>
+      <c r="K122" s="3" t="str">
+        <v>components/AppFooter.vue</v>
+      </c>
+      <c r="L122" s="3" t="str">
+        <v>iFare_Frontend/components/AppFooter.vue (L42)</v>
+      </c>
+      <c r="M122" s="3" t="str">
+        <v>簡易修復</v>
+      </c>
+      <c r="N122" s="3" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O122" s="3" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="P122" s="3" t="str">
+        <v>Round 7 (批次 A): components/AppFooter.vue L42 「© 1995-2020」改成 「© 1995-{{ new Date().getFullYear() }}」 — 模板內 inline 執行，自動跟系統年份。</v>
+      </c>
+    </row>
+    <row r="123" ht="14.4" customHeight="1">
+      <c r="A123" s="3">
+        <v>121</v>
+      </c>
+      <c r="B123" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C123" s="3" t="str">
+        <v>安全性</v>
+      </c>
+      <c r="D123" s="3" t="str">
+        <v>WebAPI errors</v>
+      </c>
+      <c r="E123" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F123" s="3" t="str">
+        <v>程式碼</v>
+      </c>
+      <c r="G123" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H123" s="3" t="str">
+        <v>API errCode 處理重複散落各頁面，無統一 interceptor</v>
+      </c>
+      <c r="I123" s="3" t="str">
+        <v>所有 SaveAction 重複 if (errCode != 0) console.error(errMsg)；未統一錯誤訊息呈現給使用者</v>
+      </c>
+      <c r="J123" s="3" t="str">
+        <v>WebAPI.ts ajax() 統一檢查 errCode，自動 show $Message.error</v>
+      </c>
+      <c r="K123" s="3" t="str">
+        <v>plugins/WebAPI.ts</v>
+      </c>
+      <c r="L123" s="3" t="str">
+        <v>iFare_Frontend/plugins/WebAPI.ts</v>
+      </c>
+      <c r="M123" s="3" t="str">
+        <v>搭配 #107</v>
+      </c>
+      <c r="N123" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O123" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P123" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="124" ht="14.4" customHeight="1">
+      <c r="A124" s="3">
+        <v>122</v>
+      </c>
+      <c r="B124" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C124" s="3" t="str">
+        <v>i-Fare 搜尋結果</v>
+      </c>
+      <c r="D124" s="3" t="str">
+        <v>ifare/result 清空動畫</v>
+      </c>
+      <c r="E124" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F124" s="3" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G124" s="3" t="str">
+        <v>低</v>
+      </c>
+      <c r="H124" s="3" t="str">
+        <v>ifare/result.vue 清空篩選後無過渡動畫，用戶不知道剛清空</v>
+      </c>
+      <c r="I124" s="3" t="str">
+        <v>清空按鈕無點擊動畫或成功提示；清空後列表重置但無視覺反饋</v>
+      </c>
+      <c r="J124" s="3" t="str">
+        <v>清空按鈕加 transition / scale 動畫；或顯示短暫 toast「篩選已清空」</v>
+      </c>
+      <c r="K124" s="3" t="str">
+        <v>pages/ifare/result.vue</v>
+      </c>
+      <c r="L124" s="3" t="str">
+        <v>iFare_Frontend/pages/ifare/result.vue (L144)</v>
+      </c>
+      <c r="M124" s="3" t="str">
+        <v>優化用戶體驗</v>
+      </c>
+      <c r="N124" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O124" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P124" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="125" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A125" s="3">
+        <v>123</v>
+      </c>
+      <c r="B125" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C125" s="3" t="str">
+        <v>全站通用</v>
+      </c>
+      <c r="D125" s="3" t="str">
+        <v>日期格式</v>
+      </c>
+      <c r="E125" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F125" s="3" t="str">
+        <v>內容</v>
+      </c>
+      <c r="G125" s="3" t="str">
+        <v>低</v>
+      </c>
+      <c r="H125" s="3" t="str">
+        <v>所有日期顯示為 YYYY-MM-DD，未考慮國際化</v>
+      </c>
+      <c r="I125" s="3" t="str">
+        <v>news/articles/ifare/info 等直接顯示 API 回傳日期字串，多語言擴展會有問題</v>
+      </c>
+      <c r="J125" s="3" t="str">
+        <v>用 Intl.DateTimeFormat 或 Day.js locale 格式化 (e.g., toLocaleDateString("zh-TW"))</v>
+      </c>
+      <c r="K125" s="3" t="str">
+        <v>多 pages</v>
+      </c>
+      <c r="L125" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Frontend/pages/news.vue_x000d__x000d_
+iFare_Frontend/pages/articles.vue_x000d__x000d_
+iFare_Frontend/pages/ifare/info.vue_x000d__x000d_
+iFare_Frontend/pages/collaborator.vue</v>
+      </c>
+      <c r="M125" s="3" t="str">
+        <v>預留多語言擴展空間</v>
+      </c>
+      <c r="N125" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O125" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P125" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="126" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A126" s="3">
+        <v>124</v>
+      </c>
+      <c r="B126" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C126" s="3" t="str">
+        <v>福利專欄</v>
+      </c>
+      <c r="D126" s="3" t="str">
+        <v>tags 截斷</v>
+      </c>
+      <c r="E126" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F126" s="3" t="str">
+        <v>視覺</v>
+      </c>
+      <c r="G126" s="3" t="str">
+        <v>低</v>
+      </c>
+      <c r="H126" s="3" t="str">
+        <v>文章卡片的 keywords 列表若過多會破壞佈局</v>
+      </c>
+      <c r="I126" s="3" t="str">
+        <v>articles.vue (L68-71) / index.vue (L94-96) 標籤列表無 max-height、無 line-clamp、無省略號</v>
+      </c>
+      <c r="J126" s="3" t="str">
+        <v>SCSS 加 display: flex; flex-wrap: wrap; max-height: 60px; overflow: hidden 或 CSS3 line-clamp</v>
+      </c>
+      <c r="K126" s="3" t="str">
+        <v>pages/articles.vue + index.vue</v>
+      </c>
+      <c r="L126" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Frontend/pages/articles.vue_x000d__x000d_
+iFare_Frontend/pages/index.vue_x000d__x000d_
+iFare_Frontend/assets/style/components/_compPage.scss</v>
+      </c>
+      <c r="M126" s="3" t="str">
+        <v>低優先級但容易實施</v>
+      </c>
+      <c r="N126" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O126" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P126" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="127" ht="14.4" customHeight="1">
+      <c r="A127" s="3">
+        <v>125</v>
+      </c>
+      <c r="B127" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C127" s="3" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="D127" s="3" t="str">
+        <v>AppHeader 行動 focus</v>
+      </c>
+      <c r="E127" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F127" s="3" t="str">
+        <v>無障礙</v>
+      </c>
+      <c r="G127" s="3" t="str">
+        <v>低</v>
+      </c>
+      <c r="H127" s="3" t="str">
+        <v>AppHeader 行動菜單開啟時焦點未自動移至菜單，關閉時未返回觸發按鈕</v>
+      </c>
+      <c r="I127" s="3" t="str">
+        <v>AppHeader.vue (L136) 菜單關閉按鈕有 focus，但開啟時焦點未管理，屏幕閱讀器用戶會迷失</v>
+      </c>
+      <c r="J127" s="3" t="str">
+        <v>用 ref 在菜單開啟時 focus 至菜單標題或第一個項目；關閉時 focus 返回菜單按鈕</v>
+      </c>
+      <c r="K127" s="3" t="str">
+        <v>components/AppHeader.vue</v>
+      </c>
+      <c r="L127" s="3" t="str">
+        <v>iFare_Frontend/components/AppHeader.vue (L136)</v>
+      </c>
+      <c r="M127" s="3" t="str">
+        <v>增進屏幕閱讀器友善性</v>
+      </c>
+      <c r="N127" s="3" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O127" s="3" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="P127" s="3" t="str">
+        <v>Round 8 (批次 C): components/AppHeader.vue 加 menuButtonRef 綁 .btn-menu，watch(isShowMenu) → 開啟時 querySelector focus 至首個 mobile menu link，關閉時 focus 回菜單按鈕。.btn-menu 加 :aria-expanded="isShowMenu" + aria-controls="mobile-menu" + aria-label="開啟菜單"；.mobile-menu 加 id="mobile-menu" + role="dialog" + aria-modal="true" + aria-label="行動選單"。全域加 ESC 鍵監聽關閉 menu (onMounted/onBeforeUnmount window.addEventListener)。</v>
+      </c>
+    </row>
+    <row r="128" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A128" s="3">
+        <v>126</v>
+      </c>
+      <c r="B128" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C128" s="3" t="str">
+        <v>i-Fare 福利查詢</v>
+      </c>
+      <c r="D128" s="3" t="str">
+        <v>disabled 視覺</v>
+      </c>
+      <c r="E128" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F128" s="3" t="str">
+        <v>視覺</v>
+      </c>
+      <c r="G128" s="3" t="str">
+        <v>低</v>
+      </c>
+      <c r="H128" s="3" t="str">
+        <v>ifare.vue 搜尋按鈕 disabled 狀態無灰化視覺反饋</v>
+      </c>
+      <c r="I128" s="3" t="str">
+        <v>ifare.vue (L79) :disabled="!canSearch" 但 SCSS 無 button:disabled 樣式，用戶可能誤以為按鈕可點</v>
+      </c>
+      <c r="J128" s="3" t="str">
+        <v>_button.scss 加 button:disabled { opacity: 0.5; cursor: not-allowed; }</v>
+      </c>
+      <c r="K128" s="3" t="str">
+        <v>pages/ifare.vue + _button.scss</v>
+      </c>
+      <c r="L128" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Frontend/pages/ifare.vue (L79)_x000d__x000d_
+iFare_Frontend/assets/style/components/_button.scss</v>
+      </c>
+      <c r="M128" s="3" t="str">
+        <v>簡易視覺修復</v>
+      </c>
+      <c r="N128" s="3" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O128" s="3" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="P128" s="3" t="str">
+        <v>Round 7 (批次 A): assets/style/components/_button.scss 開頭加 generic 規則 — button:disabled / .btn:disabled / .btn.disabled 都套 opacity 0.5 + cursor not-allowed + pointer-events none。.btn-filter 既有 disabled 樣式 (L186) 不衝突。</v>
+      </c>
+    </row>
+    <row r="129" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A129" s="3">
+        <v>127</v>
+      </c>
+      <c r="B129" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C129" s="3" t="str">
+        <v>效能</v>
+      </c>
+      <c r="D129" s="3" t="str">
+        <v>圖片 lazy load</v>
+      </c>
+      <c r="E129" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F129" s="3" t="str">
+        <v>效能</v>
+      </c>
+      <c r="G129" s="3" t="str">
+        <v>低</v>
+      </c>
+      <c r="H129" s="3" t="str">
+        <v>collaborator 機構圖片、articles/lazy 自動生成圖片未設 loading="lazy"</v>
+      </c>
+      <c r="I129" s="3" t="str">
+        <v>collaborator.vue (L22) 和 articles/lazy.vue (L77 動態) 的 &lt;img&gt; 無 loading 屬性，所有圖片串行加載</v>
+      </c>
+      <c r="J129" s="3" t="str">
+        <v>所有 &lt;img&gt; 加 loading="lazy" (首屏 eager)；大圖考慮 WebP 或壓縮</v>
+      </c>
+      <c r="K129" s="3" t="str">
+        <v>pages/collaborator + articles/lazy</v>
+      </c>
+      <c r="L129" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Frontend/pages/collaborator.vue_x000d__x000d_
+iFare_Frontend/pages/articles/lazy.vue</v>
+      </c>
+      <c r="M129" s="3" t="str">
+        <v>首屏效能優化</v>
+      </c>
+      <c r="N129" s="3" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O129" s="3" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="P129" s="3" t="str">
+        <v>Round 7 (批次 A): pages/collaborator.vue L22 &lt;img&gt; 加 loading="lazy" + :alt="`${_coll.title} logo`"；pages/articles/lazy.vue L77 動態 &lt;img&gt; 加 loading="lazy" + alt="${title} - ${j+1}"。</v>
+      </c>
+    </row>
+    <row r="130" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A130" s="3">
+        <v>128</v>
+      </c>
+      <c r="B130" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C130" s="3" t="str">
+        <v>社群分享</v>
+      </c>
+      <c r="D130" s="3" t="str">
+        <v>ShareWebUrlToLine</v>
+      </c>
+      <c r="E130" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F130" s="3" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G130" s="3" t="str">
+        <v>低</v>
+      </c>
+      <c r="H130" s="3" t="str">
+        <v>ShareWebUrlToLine 函數無 try-catch，外部 API 失敗無提示</v>
+      </c>
+      <c r="I130" s="3" t="str">
+        <v>news/info, articles/lazy, articles/welfare 的 ShareWebUrlToLine 無錯誤處理；若 navigateTo 失敗 (被瀏覽器阻擋) 無反饋</v>
+      </c>
+      <c r="J130" s="3" t="str">
+        <v>包 try-catch，失敗時顯示 toast「分享失敗，請檢查連線」</v>
+      </c>
+      <c r="K130" s="3" t="str">
+        <v>pages/news/info, articles/lazy, articles/welfare</v>
+      </c>
+      <c r="L130" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Frontend/pages/news/info.vue (L86-92)_x000d__x000d_
+iFare_Frontend/pages/articles/lazy.vue (L104-110)_x000d__x000d_
+iFare_Frontend/pages/articles/welfare.vue (L109-115)</v>
+      </c>
+      <c r="M130" s="3" t="str">
+        <v>優雅降級</v>
+      </c>
+      <c r="N130" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O130" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P130" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="131" ht="14.4" customHeight="1">
+      <c r="A131" s="3">
+        <v>129</v>
+      </c>
+      <c r="B131" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C131" s="3" t="str">
+        <v>全站通用</v>
+      </c>
+      <c r="D131" s="3" t="str">
+        <v>網路狀態</v>
+      </c>
+      <c r="E131" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F131" s="3" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G131" s="3" t="str">
+        <v>低</v>
+      </c>
+      <c r="H131" s="3" t="str">
+        <v>應用未偵測網路狀態，斷線時無全局提示</v>
+      </c>
+      <c r="I131" s="3" t="str">
+        <v>所有頁面若用戶在加載中斷線，應用無法偵測並提示「網路已斷開」</v>
+      </c>
+      <c r="J131" s="3" t="str">
+        <v>app.vue 或 middleware 監聽 window.online / window.offline，顯示全局通知欄</v>
+      </c>
+      <c r="K131" s="3" t="str">
+        <v>app.vue</v>
+      </c>
+      <c r="L131" s="3" t="str">
+        <v>iFare_Frontend/app.vue</v>
+      </c>
+      <c r="M131" s="3" t="str">
+        <v>低優先級但增進健壯性</v>
+      </c>
+      <c r="N131" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O131" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P131" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="132" ht="14.4" customHeight="1">
+      <c r="A132" s="3">
+        <v>130</v>
+      </c>
+      <c r="B132" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C132" s="3" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="D132" s="3" t="str">
+        <v>AppHeader aria</v>
+      </c>
+      <c r="E132" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F132" s="3" t="str">
+        <v>無障礙</v>
+      </c>
+      <c r="G132" s="3" t="str">
+        <v>低</v>
+      </c>
+      <c r="H132" s="3" t="str">
+        <v>AppHeader 行動菜單關閉按鈕無 aria-label</v>
+      </c>
+      <c r="I132" s="3" t="str">
+        <v>AppHeader.vue (L136) &lt;button class="btn btn-icon btn-close"&gt; 無 aria-label，屏幕閱讀器只念「按鈕」</v>
+      </c>
+      <c r="J132" s="3" t="str">
+        <v>加 aria-label="關閉菜單"</v>
+      </c>
+      <c r="K132" s="3" t="str">
+        <v>components/AppHeader.vue</v>
+      </c>
+      <c r="L132" s="3" t="str">
+        <v>iFare_Frontend/components/AppHeader.vue (L136)</v>
+      </c>
+      <c r="M132" s="3" t="str">
+        <v>簡易無障礙修復</v>
+      </c>
+      <c r="N132" s="3" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O132" s="3" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="P132" s="3" t="str">
+        <v>Round 7 (批次 A): components/AppHeader.vue L136 行動選單 .btn-close 加 aria-label="關閉菜單"。</v>
+      </c>
+    </row>
+    <row r="133" ht="14.4" customHeight="1" xml:space="preserve">
+      <c r="A133" s="3">
+        <v>131</v>
+      </c>
+      <c r="B133" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C133" s="3" t="str">
+        <v>導航</v>
+      </c>
+      <c r="D133" s="3" t="str">
+        <v>aria-current</v>
+      </c>
+      <c r="E133" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F133" s="3" t="str">
+        <v>無障礙</v>
+      </c>
+      <c r="G133" s="3" t="str">
+        <v>低</v>
+      </c>
+      <c r="H133" s="3" t="str">
+        <v>AppHeader 與其他導航元件當前頁面連結無 aria-current="page"</v>
+      </c>
+      <c r="I133" s="3" t="str">
+        <v>AppHeader (L48-69) 用 :class="{ active: $route.name }" 但無 aria-current；屏幕閱讀器無法知道哪個是當前頁</v>
+      </c>
+      <c r="J133" s="3" t="str">
+        <v>:aria-current="$route.name === 'about' ? 'page' : undefined"</v>
+      </c>
+      <c r="K133" s="3" t="str">
+        <v>components/AppHeader + CompBreadCrumb</v>
+      </c>
+      <c r="L133" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">iFare_Frontend/components/AppHeader.vue_x000d__x000d_
+iFare_Frontend/components/CompBreadCrumb.vue</v>
+      </c>
+      <c r="M133" s="3" t="str">
+        <v>WCAG 2.1 最佳實踐 + 外部連結指示符可選加 ic-external-link icon</v>
+      </c>
+      <c r="N133" s="3" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O133" s="3" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="P133" s="3" t="str">
+        <v>Round 7 (批次 A): components/AppHeader.vue 桌面 5 + 行動 6 + i-Fare 桌面 1 共 12 個 NuxtLink 加 :aria-current="$route.name === 'xxx' ? 'page' : undefined"。i-Fare 用 includes('ifare') 涵蓋子路由。</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:O79"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P99"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P133"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:H84"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="18"/>
-    <col min="2" max="2" customWidth="1" width="6.5"/>
-    <col min="3" max="3" customWidth="1" width="8.875"/>
-    <col min="4" max="4" customWidth="1" width="50.75"/>
+    <col min="1" max="1" customWidth="1" width="14.83203125"/>
+    <col min="2" max="2" customWidth="1" width="12.83203125"/>
+    <col min="3" max="3" customWidth="1" width="14.83203125"/>
+    <col min="4" max="4" customWidth="1" width="14.83203125"/>
+    <col min="5" max="5" customWidth="1" width="50.83203125"/>
+    <col min="6" max="6" customWidth="1" width="25.83203125"/>
+    <col min="7" max="7" customWidth="1" width="60.83203125"/>
+    <col min="8" max="8" customWidth="1" width="14.83203125"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.2" customHeight="1">
-      <c r="A1" s="3" t="str">
-        <v>驗證結果統計</v>
-      </c>
-    </row>
-    <row r="2" ht="16.2" customHeight="1">
-      <c r="A2" s="3" t="str">
-        <v>驗證結果</v>
-      </c>
-      <c r="B2" s="3" t="str">
-        <v>數量</v>
-      </c>
-      <c r="C2" s="3" t="str">
-        <v>百分比</v>
-      </c>
-      <c r="D2" s="3" t="str">
-        <v>說明</v>
-      </c>
-    </row>
-    <row r="3" ht="16.2" customHeight="1">
+    <row r="1">
+      <c r="A1" s="4" t="str">
+        <v>【1】整體進度</v>
+      </c>
+      <c r="B1" s="4" t="str">
+        <v/>
+      </c>
+      <c r="C1" s="4" t="str">
+        <v/>
+      </c>
+      <c r="D1" s="4" t="str">
+        <v/>
+      </c>
+      <c r="E1" s="4" t="str">
+        <v/>
+      </c>
+      <c r="F1" s="4" t="str">
+        <v/>
+      </c>
+      <c r="G1" s="4" t="str">
+        <v/>
+      </c>
+      <c r="H1" s="4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="str">
+        <v>Sheet 名稱</v>
+      </c>
+      <c r="B2" s="5" t="str">
+        <v>總計</v>
+      </c>
+      <c r="C2" s="5" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="D2" s="5" t="str">
+        <v>部分修正</v>
+      </c>
+      <c r="E2" s="5" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="F2" s="5" t="str">
+        <v>完成率</v>
+      </c>
+      <c r="G2" s="5" t="str">
+        <v>備註</v>
+      </c>
+      <c r="H2" s="5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="3" t="str">
-        <v>V 確認</v>
-      </c>
-      <c r="B3" s="2">
-        <v>77</v>
-      </c>
-      <c r="C3" s="2" t="str">
-        <v>88.5%</v>
-      </c>
-      <c r="D3" s="3" t="str">
-        <v>經程式碼驗證確認問題存在</v>
-      </c>
-    </row>
-    <row r="4" ht="16.2" customHeight="1">
+        <v>UIUX問題追蹤清單 (前台)</v>
+      </c>
+      <c r="B3" s="3">
+        <v>131</v>
+      </c>
+      <c r="C3" s="6">
+        <v>39</v>
+      </c>
+      <c r="D3" s="7">
+        <v>7</v>
+      </c>
+      <c r="E3" s="8">
+        <v>85</v>
+      </c>
+      <c r="F3" s="3" t="str">
+        <v>29.8%</v>
+      </c>
+      <c r="G3" s="3" t="str">
+        <v>已歷經 Round 1-4 改版</v>
+      </c>
+      <c r="H3" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="3" t="str">
-        <v>~ 部分確認</v>
+        <v>後臺優化 (admin)</v>
       </c>
       <c r="B4" s="3">
-        <v>10</v>
-      </c>
-      <c r="C4" s="2" t="str">
-        <v>11.5%</v>
-      </c>
-      <c r="D4" s="3" t="str">
-        <v>問題存在但原描述部分不正確，已修正描述</v>
-      </c>
-    </row>
-    <row r="5" ht="16.2" customHeight="1">
+        <v>54</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <v>0</v>
+      </c>
+      <c r="E4" s="8">
+        <v>54</v>
+      </c>
+      <c r="F4" s="3" t="str">
+        <v>0.0%</v>
+      </c>
+      <c r="G4" s="3" t="str">
+        <v>Round 5-6 規劃完成 / 全待開始</v>
+      </c>
+      <c r="H4" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="3" t="str">
-        <v>合計</v>
-      </c>
-      <c r="B5" s="2">
-        <v>87</v>
-      </c>
-      <c r="C5" s="3" t="str">
-        <v>100%</v>
-      </c>
-      <c r="D5" s="2" t="str">
-        <v>已移除 8 項原始盤點中不正確的項目；2026-04-28 補登 10 項改版實作項目（#88-#97）</v>
-      </c>
-    </row>
-    <row r="7" ht="16.2" customHeight="1">
-      <c r="A7" s="3" t="str">
-        <v>各區塊問題統計</v>
-      </c>
-    </row>
-    <row r="8" ht="16.2" customHeight="1">
-      <c r="A8" s="3" t="str">
+        <v>PoC研究</v>
+      </c>
+      <c r="B5" s="3">
+        <v>12</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0</v>
+      </c>
+      <c r="D5" s="7">
+        <v>0</v>
+      </c>
+      <c r="E5" s="8">
+        <v>12</v>
+      </c>
+      <c r="F5" s="3" t="str">
+        <v>0.0%</v>
+      </c>
+      <c r="G5" s="3" t="str">
+        <v>研究方向，未啟動</v>
+      </c>
+      <c r="H5" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="str">
+        <v>【2】Round 時間軸 — 每輪做了什麼</v>
+      </c>
+      <c r="B7" s="4" t="str">
+        <v/>
+      </c>
+      <c r="C7" s="4" t="str">
+        <v/>
+      </c>
+      <c r="D7" s="4" t="str">
+        <v/>
+      </c>
+      <c r="E7" s="4" t="str">
+        <v/>
+      </c>
+      <c r="F7" s="4" t="str">
+        <v/>
+      </c>
+      <c r="G7" s="4" t="str">
+        <v/>
+      </c>
+      <c r="H7" s="4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="str">
+        <v>Round</v>
+      </c>
+      <c r="B8" s="5" t="str">
+        <v>日期</v>
+      </c>
+      <c r="C8" s="5" t="str">
+        <v>主題</v>
+      </c>
+      <c r="D8" s="5" t="str">
+        <v>UIUX 標完成</v>
+      </c>
+      <c r="E8" s="5" t="str">
+        <v>UIUX 新增</v>
+      </c>
+      <c r="F8" s="5" t="str">
+        <v>後臺新增</v>
+      </c>
+      <c r="G8" s="5" t="str">
+        <v>Schema</v>
+      </c>
+      <c r="H8" s="5" t="str">
+        <v>主要產出</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="str">
+        <v>Round 1</v>
+      </c>
+      <c r="B9" s="3" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="C9" s="3" t="str">
+        <v>UI/UX 改版 (搜尋 / Footer / 全站動畫 / RWD)</v>
+      </c>
+      <c r="D9" s="3">
+        <v>7</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="str">
+        <v>-</v>
+      </c>
+      <c r="H9" s="3" t="str">
+        <v>pages/ifare 加關鍵字搜尋 + URL query 初始化；全站 NuxtPage transition；卡片/按鈕 hover translateY</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="str">
+        <v>Round 2</v>
+      </c>
+      <c r="B10" s="3" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="C10" s="3" t="str">
+        <v>Footer 整理 + RWD 修正</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="str">
+        <v>-</v>
+      </c>
+      <c r="H10" s="3" t="str">
+        <v>LINE/FB 統一 .btn-social 並排；4 個聯絡資訊加 icon (Tel/Mail/Address/Clock)；footer 觸控 44px</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="str">
+        <v>Round 3</v>
+      </c>
+      <c r="B11" s="3" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="C11" s="3" t="str">
+        <v>About 靈動島 + News 卡片升級 + 社群外連結</v>
+      </c>
+      <c r="D11" s="3">
+        <v>4</v>
+      </c>
+      <c r="E11" s="3">
+        <v>5</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="str">
+        <v>-</v>
+      </c>
+      <c r="H11" s="3" t="str">
+        <v>About 三大核心 morph 卡 (cf47cfa)；News 浮起卡 + stagger fade-up + NEW pill；外連結 target="_blank" rel="noopener"</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="str">
+        <v>Round 4</v>
+      </c>
+      <c r="B12" s="3" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="C12" s="3" t="str">
+        <v>切回 master + 開新分支 feat/uiux-round4 + 補做 (環境/補回/新功能)</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
+        <v>4</v>
+      </c>
+      <c r="G12" s="3" t="str">
+        <v>-</v>
+      </c>
+      <c r="H12" s="3" t="str">
+        <v>cf47cfa+5dfbf91 補回 16 檔；devProxy/baseURL → 正式 API；nav 加未來規劃 + future.vue；News videoUrl wiring；tsconfig deprecation 清理；about hover bug 修；footer label 重複修</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="str">
+        <v>Round 5</v>
+      </c>
+      <c r="B13" s="3" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="C13" s="3" t="str">
+        <v>前後台全面審查 — 後台 UX audit + 前台新 issue 掃描</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>26</v>
+      </c>
+      <c r="F13" s="3">
+        <v>22</v>
+      </c>
+      <c r="G13" s="3" t="str">
+        <v>-</v>
+      </c>
+      <c r="H13" s="3" t="str">
+        <v>後台 22 個工程角度問題 (CRUD/驗證/錯誤處理)；前台 26 個新發現 (XSS/超時/console.log/無障礙/分頁元件重複)</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="str">
+        <v>Round 6</v>
+      </c>
+      <c r="B14" s="3" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="C14" s="3" t="str">
+        <v>人性化主軸提案 — 5 主軸 + 16 後台項</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>16</v>
+      </c>
+      <c r="G14" s="3" t="str">
+        <v>+ Q 欄主軸</v>
+      </c>
+      <c r="H14" s="3" t="str">
+        <v>Dashboard 角色化 / 今日待辦 / KPI 分區；批次操作；軟刪除復原；audit log；危險操作預覽；錯誤訊息引導</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="str">
+        <v>【3】後臺優化 — 5 主軸分布 (拿這個去提案!)</v>
+      </c>
+      <c r="B16" s="4" t="str">
+        <v/>
+      </c>
+      <c r="C16" s="4" t="str">
+        <v/>
+      </c>
+      <c r="D16" s="4" t="str">
+        <v/>
+      </c>
+      <c r="E16" s="4" t="str">
+        <v/>
+      </c>
+      <c r="F16" s="4" t="str">
+        <v/>
+      </c>
+      <c r="G16" s="4" t="str">
+        <v/>
+      </c>
+      <c r="H16" s="4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="str">
+        <v>主軸</v>
+      </c>
+      <c r="B17" s="5" t="str">
+        <v>項目數</v>
+      </c>
+      <c r="C17" s="5" t="str">
+        <v>比例</v>
+      </c>
+      <c r="D17" s="5" t="str">
+        <v>主要訴求</v>
+      </c>
+      <c r="E17" s="5" t="str">
+        <v>對應 #</v>
+      </c>
+      <c r="F17" s="5" t="str">
+        <v/>
+      </c>
+      <c r="G17" s="5" t="str">
+        <v/>
+      </c>
+      <c r="H17" s="5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="str">
+        <v>看得懂</v>
+      </c>
+      <c r="B18" s="3">
+        <v>17</v>
+      </c>
+      <c r="C18" s="3" t="str">
+        <v>31.5%</v>
+      </c>
+      <c r="D18" s="3" t="str">
+        <v>首頁先給重點 / KPI / 異常 / 待辦分區 / 欄位白話 / 狀態流程視覺化</v>
+      </c>
+      <c r="E18" s="3" t="str">
+        <v>#1, #7, #10, #17, #19, #24, #25, #27, #32, #35, #37, #38, #39, #40, #41, #45, #49</v>
+      </c>
+      <c r="F18" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G18" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H18" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="str">
+        <v>找得到</v>
+      </c>
+      <c r="B19" s="3">
+        <v>5</v>
+      </c>
+      <c r="C19" s="3" t="str">
+        <v>9.3%</v>
+      </c>
+      <c r="D19" s="3" t="str">
+        <v>全域搜尋 / 麵包屑 / 側邊欄高亮 / 變更密碼入口</v>
+      </c>
+      <c r="E19" s="3" t="str">
+        <v>#6, #29, #30, #33, #44</v>
+      </c>
+      <c r="F19" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G19" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H19" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="str">
+        <v>做得快</v>
+      </c>
+      <c r="B20" s="3">
+        <v>9</v>
+      </c>
+      <c r="C20" s="3" t="str">
+        <v>16.7%</v>
+      </c>
+      <c r="D20" s="3" t="str">
+        <v>批次操作 / 儲存搜尋 / 大列表 lazy / 匯出進度 / 日期快捷</v>
+      </c>
+      <c r="E20" s="3" t="str">
+        <v>#3, #11, #20, #26, #28, #42, #43, #53, #54</v>
+      </c>
+      <c r="F20" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G20" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H20" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="str">
+        <v>不容易錯</v>
+      </c>
+      <c r="B21" s="3">
+        <v>14</v>
+      </c>
+      <c r="C21" s="3" t="str">
+        <v>25.9%</v>
+      </c>
+      <c r="D21" s="3" t="str">
+        <v>表單驗證 / 刪除確認 / 影響預覽 / 預設值 / 錯誤引導</v>
+      </c>
+      <c r="E21" s="3" t="str">
+        <v>#2, #4, #5, #15, #18, #21, #22, #23, #31, #34, #36, #46, #47, #48</v>
+      </c>
+      <c r="F21" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G21" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H21" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="str">
+        <v>出事能追回來</v>
+      </c>
+      <c r="B22" s="3">
+        <v>5</v>
+      </c>
+      <c r="C22" s="3" t="str">
+        <v>9.3%</v>
+      </c>
+      <c r="D22" s="3" t="str">
+        <v>audit log / 變更歷史 / 軟刪除復原 / token 管理 / 文件交接</v>
+      </c>
+      <c r="E22" s="3" t="str">
+        <v>#9, #12, #50, #51, #52</v>
+      </c>
+      <c r="F22" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G22" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H22" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="str">
+        <v>—</v>
+      </c>
+      <c r="B23" s="3">
+        <v>4</v>
+      </c>
+      <c r="C23" s="3" t="str">
+        <v>7.4%</v>
+      </c>
+      <c r="D23" s="3" t="str">
+        <v>純技術 / 環境設定 (不在 5 主軸範圍)</v>
+      </c>
+      <c r="E23" s="3" t="str">
+        <v>#8, #13, #14, #16</v>
+      </c>
+      <c r="F23" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G23" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H23" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="str">
+        <v>【4】UIUX — 優先級 × 狀態分布</v>
+      </c>
+      <c r="B25" s="4" t="str">
+        <v/>
+      </c>
+      <c r="C25" s="4" t="str">
+        <v/>
+      </c>
+      <c r="D25" s="4" t="str">
+        <v/>
+      </c>
+      <c r="E25" s="4" t="str">
+        <v/>
+      </c>
+      <c r="F25" s="4" t="str">
+        <v/>
+      </c>
+      <c r="G25" s="4" t="str">
+        <v/>
+      </c>
+      <c r="H25" s="4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="str">
+        <v>優先級</v>
+      </c>
+      <c r="B26" s="5" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="C26" s="5" t="str">
+        <v>部分修正</v>
+      </c>
+      <c r="D26" s="5" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="E26" s="5" t="str">
+        <v>小計</v>
+      </c>
+      <c r="F26" s="5" t="str">
+        <v>完成率</v>
+      </c>
+      <c r="G26" s="5" t="str">
+        <v/>
+      </c>
+      <c r="H26" s="5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="B27" s="6">
+        <v>7</v>
+      </c>
+      <c r="C27" s="7">
+        <v>4</v>
+      </c>
+      <c r="D27" s="8">
+        <v>6</v>
+      </c>
+      <c r="E27" s="3">
+        <v>17</v>
+      </c>
+      <c r="F27" s="3" t="str">
+        <v>52.9%</v>
+      </c>
+      <c r="G27" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H27" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="B28" s="6">
+        <v>14</v>
+      </c>
+      <c r="C28" s="7">
+        <v>1</v>
+      </c>
+      <c r="D28" s="8">
+        <v>44</v>
+      </c>
+      <c r="E28" s="3">
+        <v>59</v>
+      </c>
+      <c r="F28" s="3" t="str">
+        <v>24.6%</v>
+      </c>
+      <c r="G28" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H28" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="str">
+        <v>低</v>
+      </c>
+      <c r="B29" s="6">
+        <v>18</v>
+      </c>
+      <c r="C29" s="7">
+        <v>2</v>
+      </c>
+      <c r="D29" s="8">
+        <v>35</v>
+      </c>
+      <c r="E29" s="3">
+        <v>55</v>
+      </c>
+      <c r="F29" s="3" t="str">
+        <v>34.5%</v>
+      </c>
+      <c r="G29" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H29" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="str">
+        <v>【5】UIUX — 各區塊問題分布</v>
+      </c>
+      <c r="B31" s="4" t="str">
+        <v/>
+      </c>
+      <c r="C31" s="4" t="str">
+        <v/>
+      </c>
+      <c r="D31" s="4" t="str">
+        <v/>
+      </c>
+      <c r="E31" s="4" t="str">
+        <v/>
+      </c>
+      <c r="F31" s="4" t="str">
+        <v/>
+      </c>
+      <c r="G31" s="4" t="str">
+        <v/>
+      </c>
+      <c r="H31" s="4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="str">
         <v>區塊</v>
       </c>
-      <c r="B8" s="3" t="str">
-        <v>修復</v>
-      </c>
-      <c r="C8" s="3" t="str">
-        <v>提升</v>
-      </c>
-      <c r="D8" s="3" t="str">
-        <v>小計</v>
-      </c>
-    </row>
-    <row r="9" ht="16.2" customHeight="1">
-      <c r="A9" s="3" t="str">
+      <c r="B32" s="5" t="str">
+        <v>項目數</v>
+      </c>
+      <c r="C32" s="5" t="str">
+        <v>佔比</v>
+      </c>
+      <c r="D32" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E32" s="5" t="str">
+        <v/>
+      </c>
+      <c r="F32" s="5" t="str">
+        <v/>
+      </c>
+      <c r="G32" s="5" t="str">
+        <v/>
+      </c>
+      <c r="H32" s="5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="B33" s="3">
+        <v>24</v>
+      </c>
+      <c r="C33" s="3" t="str">
+        <v>18.3%</v>
+      </c>
+      <c r="D33" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E33" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F33" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G33" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H33" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="str">
+        <v>全站通用</v>
+      </c>
+      <c r="B34" s="3">
+        <v>24</v>
+      </c>
+      <c r="C34" s="3" t="str">
+        <v>18.3%</v>
+      </c>
+      <c r="D34" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E34" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F34" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G34" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H34" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="str">
         <v>i-Fare 福利查詢</v>
       </c>
-      <c r="B9" s="2">
-        <v>10</v>
-      </c>
-      <c r="C9" s="2">
+      <c r="B35" s="3">
+        <v>23</v>
+      </c>
+      <c r="C35" s="3" t="str">
+        <v>17.6%</v>
+      </c>
+      <c r="D35" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E35" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F35" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G35" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H35" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="str">
+        <v>福利專欄</v>
+      </c>
+      <c r="B36" s="3">
+        <v>11</v>
+      </c>
+      <c r="C36" s="3" t="str">
+        <v>8.4%</v>
+      </c>
+      <c r="D36" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E36" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F36" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G36" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H36" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="str">
+        <v>關於長穩</v>
+      </c>
+      <c r="B37" s="3">
+        <v>9</v>
+      </c>
+      <c r="C37" s="3" t="str">
+        <v>6.9%</v>
+      </c>
+      <c r="D37" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E37" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F37" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G37" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H37" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="str">
+        <v>首頁</v>
+      </c>
+      <c r="B38" s="3">
+        <v>8</v>
+      </c>
+      <c r="C38" s="3" t="str">
+        <v>6.1%</v>
+      </c>
+      <c r="D38" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E38" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F38" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G38" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H38" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="str">
+        <v>最新消息</v>
+      </c>
+      <c r="B39" s="3">
+        <v>8</v>
+      </c>
+      <c r="C39" s="3" t="str">
+        <v>6.1%</v>
+      </c>
+      <c r="D39" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E39" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F39" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G39" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H39" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="str">
+        <v>全站微互動</v>
+      </c>
+      <c r="B40" s="3">
+        <v>5</v>
+      </c>
+      <c r="C40" s="3" t="str">
+        <v>3.8%</v>
+      </c>
+      <c r="D40" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E40" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F40" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G40" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H40" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="str">
+        <v>設計系統</v>
+      </c>
+      <c r="B41" s="3">
+        <v>5</v>
+      </c>
+      <c r="C41" s="3" t="str">
+        <v>3.8%</v>
+      </c>
+      <c r="D41" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E41" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F41" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G41" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H41" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="str">
+        <v>公益夥伴</v>
+      </c>
+      <c r="B42" s="3">
+        <v>4</v>
+      </c>
+      <c r="C42" s="3" t="str">
+        <v>3.1%</v>
+      </c>
+      <c r="D42" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E42" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F42" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G42" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H42" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="str">
+        <v>安全性</v>
+      </c>
+      <c r="B43" s="3">
+        <v>2</v>
+      </c>
+      <c r="C43" s="3" t="str">
+        <v>1.5%</v>
+      </c>
+      <c r="D43" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E43" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F43" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G43" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H43" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="str">
+        <v>無障礙</v>
+      </c>
+      <c r="B44" s="3">
+        <v>2</v>
+      </c>
+      <c r="C44" s="3" t="str">
+        <v>1.5%</v>
+      </c>
+      <c r="D44" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E44" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F44" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G44" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H44" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="str">
+        <v>未來規劃</v>
+      </c>
+      <c r="B45" s="3">
+        <v>1</v>
+      </c>
+      <c r="C45" s="3" t="str">
+        <v>0.8%</v>
+      </c>
+      <c r="D45" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E45" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F45" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G45" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H45" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="str">
+        <v>頁面導航</v>
+      </c>
+      <c r="B46" s="3">
+        <v>1</v>
+      </c>
+      <c r="C46" s="3" t="str">
+        <v>0.8%</v>
+      </c>
+      <c r="D46" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E46" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F46" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G46" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H46" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="str">
+        <v>i-Fare 搜尋結果</v>
+      </c>
+      <c r="B47" s="3">
+        <v>1</v>
+      </c>
+      <c r="C47" s="3" t="str">
+        <v>0.8%</v>
+      </c>
+      <c r="D47" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E47" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F47" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G47" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H47" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="str">
+        <v>效能</v>
+      </c>
+      <c r="B48" s="3">
+        <v>1</v>
+      </c>
+      <c r="C48" s="3" t="str">
+        <v>0.8%</v>
+      </c>
+      <c r="D48" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E48" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F48" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G48" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H48" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="str">
+        <v>社群分享</v>
+      </c>
+      <c r="B49" s="3">
+        <v>1</v>
+      </c>
+      <c r="C49" s="3" t="str">
+        <v>0.8%</v>
+      </c>
+      <c r="D49" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E49" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F49" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G49" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H49" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="str">
+        <v>導航</v>
+      </c>
+      <c r="B50" s="3">
+        <v>1</v>
+      </c>
+      <c r="C50" s="3" t="str">
+        <v>0.8%</v>
+      </c>
+      <c r="D50" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E50" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F50" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G50" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H50" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="str">
+        <v>【6】後臺優化 — 各區塊問題分布</v>
+      </c>
+      <c r="B52" s="4" t="str">
+        <v/>
+      </c>
+      <c r="C52" s="4" t="str">
+        <v/>
+      </c>
+      <c r="D52" s="4" t="str">
+        <v/>
+      </c>
+      <c r="E52" s="4" t="str">
+        <v/>
+      </c>
+      <c r="F52" s="4" t="str">
+        <v/>
+      </c>
+      <c r="G52" s="4" t="str">
+        <v/>
+      </c>
+      <c r="H52" s="4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="str">
+        <v>區塊</v>
+      </c>
+      <c r="B53" s="5" t="str">
+        <v>項目數</v>
+      </c>
+      <c r="C53" s="5" t="str">
+        <v>佔比</v>
+      </c>
+      <c r="D53" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E53" s="5" t="str">
+        <v/>
+      </c>
+      <c r="F53" s="5" t="str">
+        <v/>
+      </c>
+      <c r="G53" s="5" t="str">
+        <v/>
+      </c>
+      <c r="H53" s="5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="B54" s="3">
+        <v>16</v>
+      </c>
+      <c r="C54" s="3" t="str">
+        <v>29.6%</v>
+      </c>
+      <c r="D54" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E54" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F54" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G54" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H54" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="str">
+        <v>後台通用</v>
+      </c>
+      <c r="B55" s="3">
+        <v>15</v>
+      </c>
+      <c r="C55" s="3" t="str">
+        <v>27.8%</v>
+      </c>
+      <c r="D55" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E55" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F55" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G55" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H55" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="str">
+        <v>i-Fare 維護</v>
+      </c>
+      <c r="B56" s="3">
+        <v>2</v>
+      </c>
+      <c r="C56" s="3" t="str">
+        <v>3.7%</v>
+      </c>
+      <c r="D56" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E56" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F56" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G56" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H56" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="str">
+        <v>圖片管理</v>
+      </c>
+      <c r="B57" s="3">
+        <v>2</v>
+      </c>
+      <c r="C57" s="3" t="str">
+        <v>3.7%</v>
+      </c>
+      <c r="D57" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E57" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F57" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G57" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H57" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="str">
+        <v>最新消息維護</v>
+      </c>
+      <c r="B58" s="3">
+        <v>1</v>
+      </c>
+      <c r="C58" s="3" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D58" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E58" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F58" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G58" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H58" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="str">
+        <v>帳戶維護 / 全站權限</v>
+      </c>
+      <c r="B59" s="3">
+        <v>1</v>
+      </c>
+      <c r="C59" s="3" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D59" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E59" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F59" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G59" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H59" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="str">
+        <v>前台通用</v>
+      </c>
+      <c r="B60" s="3">
+        <v>1</v>
+      </c>
+      <c r="C60" s="3" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D60" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E60" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F60" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G60" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H60" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="str">
+        <v>對話框</v>
+      </c>
+      <c r="B61" s="3">
+        <v>1</v>
+      </c>
+      <c r="C61" s="3" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D61" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E61" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F61" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G61" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H61" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="str">
+        <v>檔案上傳</v>
+      </c>
+      <c r="B62" s="3">
+        <v>1</v>
+      </c>
+      <c r="C62" s="3" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D62" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E62" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F62" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G62" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H62" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="str">
+        <v>帳號管理</v>
+      </c>
+      <c r="B63" s="3">
+        <v>1</v>
+      </c>
+      <c r="C63" s="3" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D63" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E63" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F63" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G63" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H63" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="str">
+        <v>搜尋結果</v>
+      </c>
+      <c r="B64" s="3">
+        <v>1</v>
+      </c>
+      <c r="C64" s="3" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D64" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E64" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F64" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G64" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H64" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="str">
+        <v>日期選擇</v>
+      </c>
+      <c r="B65" s="3">
+        <v>1</v>
+      </c>
+      <c r="C65" s="3" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D65" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E65" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F65" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G65" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H65" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="str">
+        <v>表單</v>
+      </c>
+      <c r="B66" s="3">
+        <v>1</v>
+      </c>
+      <c r="C66" s="3" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D66" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E66" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F66" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G66" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H66" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="str">
+        <v>側邊欄</v>
+      </c>
+      <c r="B67" s="3">
+        <v>1</v>
+      </c>
+      <c r="C67" s="3" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D67" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E67" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F67" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G67" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H67" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="str">
+        <v>麵包屑導覽</v>
+      </c>
+      <c r="B68" s="3">
+        <v>1</v>
+      </c>
+      <c r="C68" s="3" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D68" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E68" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F68" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G68" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H68" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="str">
+        <v>WebAPI</v>
+      </c>
+      <c r="B69" s="3">
+        <v>1</v>
+      </c>
+      <c r="C69" s="3" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D69" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E69" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F69" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G69" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H69" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="str">
+        <v>帳號變更密碼</v>
+      </c>
+      <c r="B70" s="3">
+        <v>1</v>
+      </c>
+      <c r="C70" s="3" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D70" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E70" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F70" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G70" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H70" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="str">
+        <v>Code 代碼管理</v>
+      </c>
+      <c r="B71" s="3">
+        <v>1</v>
+      </c>
+      <c r="C71" s="3" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D71" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E71" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F71" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G71" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H71" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="str">
+        <v>狀態管理</v>
+      </c>
+      <c r="B72" s="3">
+        <v>1</v>
+      </c>
+      <c r="C72" s="3" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D72" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E72" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F72" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G72" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H72" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="str">
+        <v>登入頁面</v>
+      </c>
+      <c r="B73" s="3">
+        <v>1</v>
+      </c>
+      <c r="C73" s="3" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D73" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E73" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F73" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G73" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H73" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="str">
+        <v>HTML 編輯器</v>
+      </c>
+      <c r="B74" s="3">
+        <v>1</v>
+      </c>
+      <c r="C74" s="3" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D74" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E74" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F74" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G74" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H74" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="str">
+        <v>無權限頁</v>
+      </c>
+      <c r="B75" s="3">
+        <v>1</v>
+      </c>
+      <c r="C75" s="3" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D75" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E75" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F75" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G75" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H75" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="str">
+        <v>效能</v>
+      </c>
+      <c r="B76" s="3">
+        <v>1</v>
+      </c>
+      <c r="C76" s="3" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D76" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E76" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F76" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G76" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H76" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="str">
+        <v>【7】你做了什麼 — 已完成項目摘要 (依 Round 分組)</v>
+      </c>
+      <c r="B78" s="4" t="str">
+        <v/>
+      </c>
+      <c r="C78" s="4" t="str">
+        <v/>
+      </c>
+      <c r="D78" s="4" t="str">
+        <v/>
+      </c>
+      <c r="E78" s="4" t="str">
+        <v/>
+      </c>
+      <c r="F78" s="4" t="str">
+        <v/>
+      </c>
+      <c r="G78" s="4" t="str">
+        <v/>
+      </c>
+      <c r="H78" s="4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="str">
+        <v>Round</v>
+      </c>
+      <c r="B79" s="5" t="str">
+        <v>日期</v>
+      </c>
+      <c r="C79" s="5" t="str">
+        <v>已修正 (綠)</v>
+      </c>
+      <c r="D79" s="5" t="str">
+        <v>部分修正 (黃)</v>
+      </c>
+      <c r="E79" s="5" t="str">
+        <v>已修正 # 清單</v>
+      </c>
+      <c r="F79" s="5" t="str">
+        <v>部分修正 # 清單</v>
+      </c>
+      <c r="G79" s="5" t="str">
+        <v>主要重點</v>
+      </c>
+      <c r="H79" s="5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="str">
+        <v>Round 1</v>
+      </c>
+      <c r="B80" s="3" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="C80" s="6">
+        <v>24</v>
+      </c>
+      <c r="D80" s="7">
+        <v>6</v>
+      </c>
+      <c r="E80" s="3" t="str">
+        <v>#16, #17, #22, #23, #24, #44, #59, #88, #89, #90, #106, #108, #109, #110, #112, #114, #115, #118, #120, #125, #126, #127, #130, #131</v>
+      </c>
+      <c r="F80" s="3" t="str">
+        <v>#1, #9, #60, #71, #80, #107</v>
+      </c>
+      <c r="G80" s="3" t="str">
+        <v>搜尋優化 (移除 disabled / 結果摘要) + 全站動畫 + skeleton 載入 + 卡片/按鈕 hover translateY</v>
+      </c>
+      <c r="H80" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="str">
+        <v>Round 2</v>
+      </c>
+      <c r="B81" s="3" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="C81" s="6">
+        <v>2</v>
+      </c>
+      <c r="D81" s="7">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3" t="str">
+        <v>#91, #92</v>
+      </c>
+      <c r="F81" s="3" t="str">
+        <v>-</v>
+      </c>
+      <c r="G81" s="3" t="str">
+        <v>Footer 整合 (LINE/FB 並列 .btn-social) + 觸控目標 44px</v>
+      </c>
+      <c r="H81" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="str">
+        <v>Round 3</v>
+      </c>
+      <c r="B82" s="3" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="C82" s="6">
+        <v>6</v>
+      </c>
+      <c r="D82" s="7">
+        <v>0</v>
+      </c>
+      <c r="E82" s="3" t="str">
+        <v>#26, #93, #94, #95, #96, #97</v>
+      </c>
+      <c r="F82" s="3" t="str">
+        <v>-</v>
+      </c>
+      <c r="G82" s="3" t="str">
+        <v>About 三大核心 morph 卡 + News 浮起卡 + 浮現動畫 + line-clamp + NEW pill + 社群 target="_blank"</v>
+      </c>
+      <c r="H82" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="str">
+        <v>Round 4</v>
+      </c>
+      <c r="B83" s="3" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="C83" s="6">
         <v>7</v>
       </c>
-      <c r="D9" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" ht="16.2" customHeight="1">
-      <c r="A10" s="3" t="str">
-        <v>首頁</v>
-      </c>
-      <c r="B10" s="3">
-        <v>3</v>
-      </c>
-      <c r="C10" s="3">
-        <v>4</v>
-      </c>
-      <c r="D10" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" ht="16.2" customHeight="1">
-      <c r="A11" s="3" t="str">
-        <v>最新消息</v>
-      </c>
-      <c r="B11" s="3">
-        <v>3</v>
-      </c>
-      <c r="C11" s="2">
-        <v>3</v>
-      </c>
-      <c r="D11" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" ht="16.2" customHeight="1">
-      <c r="A12" s="3" t="str">
-        <v>福利專欄</v>
-      </c>
-      <c r="B12" s="3">
-        <v>5</v>
-      </c>
-      <c r="C12" s="3">
-        <v>4</v>
-      </c>
-      <c r="D12" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" ht="16.2" customHeight="1">
-      <c r="A13" s="3" t="str">
-        <v>公益夥伴</v>
-      </c>
-      <c r="B13" s="3">
-        <v>3</v>
-      </c>
-      <c r="C13" s="3">
+      <c r="D83" s="7">
         <v>1</v>
       </c>
-      <c r="D13" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" ht="16.2" customHeight="1">
-      <c r="A14" s="3" t="str">
-        <v>關於長穩</v>
-      </c>
-      <c r="B14" s="3">
-        <v>2</v>
-      </c>
-      <c r="C14" s="2">
-        <v>6</v>
-      </c>
-      <c r="D14" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" ht="16.2" customHeight="1">
-      <c r="A15" s="3" t="str">
-        <v>共用元件</v>
-      </c>
-      <c r="B15" s="2">
-        <v>15</v>
-      </c>
-      <c r="C15" s="2">
-        <v>2</v>
-      </c>
-      <c r="D15" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" ht="16.2" customHeight="1">
-      <c r="A16" s="3" t="str">
-        <v>全站微互動</v>
-      </c>
-      <c r="B16" s="3">
-        <v>0</v>
-      </c>
-      <c r="C16" s="3">
-        <v>5</v>
-      </c>
-      <c r="D16" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" ht="16.2" customHeight="1">
-      <c r="A17" s="3" t="str">
-        <v>設計系統</v>
-      </c>
-      <c r="B17" s="3">
-        <v>5</v>
-      </c>
-      <c r="C17" s="3">
-        <v>0</v>
-      </c>
-      <c r="D17" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" ht="16.2" customHeight="1">
-      <c r="A18" s="3" t="str">
-        <v>全站通用</v>
-      </c>
-      <c r="B18" s="3">
-        <v>9</v>
-      </c>
-      <c r="C18" s="3">
-        <v>0</v>
-      </c>
-      <c r="D18" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" ht="16.2" customHeight="1">
-      <c r="A19" s="3" t="str">
-        <v>合計</v>
-      </c>
-      <c r="B19" s="2">
-        <v>55</v>
-      </c>
-      <c r="C19" s="2">
-        <v>32</v>
-      </c>
-      <c r="D19" s="2">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="21" ht="16.2" customHeight="1">
-      <c r="A21" s="3" t="str">
-        <v>優先級分布</v>
-      </c>
-    </row>
-    <row r="22" ht="16.2" customHeight="1">
-      <c r="A22" s="3" t="str">
-        <v>優先級</v>
-      </c>
-      <c r="B22" s="3" t="str">
-        <v>修復</v>
-      </c>
-      <c r="C22" s="3" t="str">
-        <v>提升</v>
-      </c>
-      <c r="D22" s="3" t="str">
-        <v>小計</v>
-      </c>
-    </row>
-    <row r="23" ht="16.2" customHeight="1">
-      <c r="A23" s="3" t="str">
-        <v>高</v>
-      </c>
-      <c r="B23" s="3">
-        <v>5</v>
-      </c>
-      <c r="C23" s="3">
-        <v>1</v>
-      </c>
-      <c r="D23" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" ht="16.2" customHeight="1">
-      <c r="A24" s="3" t="str">
-        <v>中</v>
-      </c>
-      <c r="B24" s="2">
-        <v>27</v>
-      </c>
-      <c r="C24" s="2">
-        <v>11</v>
-      </c>
-      <c r="D24" s="2">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" ht="16.2" customHeight="1">
-      <c r="A25" s="3" t="str">
-        <v>低</v>
-      </c>
-      <c r="B25" s="2">
-        <v>23</v>
-      </c>
-      <c r="C25" s="2">
-        <v>20</v>
-      </c>
-      <c r="D25" s="2">
-        <v>43</v>
+      <c r="E83" s="3" t="str">
+        <v>#98, #99, #100, #101, #103, #104, #105</v>
+      </c>
+      <c r="F83" s="3" t="str">
+        <v>#102</v>
+      </c>
+      <c r="G83" s="3" t="str">
+        <v>cf47cfa+5dfbf91 補回 16 檔 + 環境設定 (devProxy/baseURL) + 未來規劃 nav + News videoUrl wiring + tsconfig + about hover bug + footer label 重複</v>
+      </c>
+      <c r="H83" s="3" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A21:D21"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H84"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/iFare_UI_UX_問題追蹤清單.xlsx
+++ b/docs/iFare_UI_UX_問題追蹤清單.xlsx
@@ -8,9 +8,6 @@
     <sheet name="UIUX問題追蹤清單" sheetId="3" r:id="rId3"/>
     <sheet name="統計摘要" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2">'UIUX問題追蹤清單'!A2:O79</definedName>
-  </definedNames>
 </workbook>
 </file>
 
@@ -39,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -48,8 +45,28 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <color rgb="9C5700"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <color rgb="9C5700"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <color rgb="006100"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <color rgb="006100"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -57,6 +74,30 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -80,16 +121,23 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -145,10 +193,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -180,10 +228,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -4054,53 +4102,53 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A3" s="3">
+      <c r="A3" s="4">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="str">
+      <c r="B3" s="5" t="str">
         <v>~</v>
       </c>
-      <c r="C3" s="3" t="str">
+      <c r="C3" s="5" t="str">
         <v>i-Fare 福利查詢</v>
       </c>
-      <c r="D3" s="3" t="str">
+      <c r="D3" s="5" t="str">
         <v>搜尋介面</v>
       </c>
-      <c r="E3" s="3" t="str">
+      <c r="E3" s="5" t="str">
         <v>修復</v>
       </c>
-      <c r="F3" s="3" t="str">
+      <c r="F3" s="5" t="str">
         <v>互動</v>
       </c>
-      <c r="G3" s="3" t="str">
+      <c r="G3" s="5" t="str">
         <v>高</v>
       </c>
-      <c r="H3" s="3" t="str">
+      <c r="H3" s="5" t="str">
         <v>篩選條件不完整時無錯誤訊息</v>
       </c>
-      <c r="I3" s="3" t="str">
+      <c r="I3" s="5" t="str">
         <v>按鈕變灰(disabled)但使用者不知道缺哪個欄位，Search()直接 return false 無任何提示</v>
       </c>
-      <c r="J3" s="3" t="str">
+      <c r="J3" s="5" t="str">
         <v>加入未填欄位紅框提示 + 錯誤文字</v>
       </c>
-      <c r="K3" s="3" t="str">
+      <c r="K3" s="5" t="str">
         <v>pages/ifare.vue</v>
       </c>
-      <c r="L3" s="3" t="str" xml:space="preserve">
+      <c r="L3" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">pages/ifare.vue_x000d__x000d__x000d_
 assets/style/_font.scss</v>
       </c>
-      <c r="M3" s="3" t="str">
+      <c r="M3" s="5" t="str">
         <v>無錯誤訊息確認；但「(必填)」標示已存在於 _font.scss</v>
       </c>
-      <c r="N3" s="3" t="str">
+      <c r="N3" s="5" t="str">
         <v>部分修正</v>
       </c>
-      <c r="O3" s="3" t="str">
+      <c r="O3" s="5" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P3" s="3" t="str">
+      <c r="P3" s="5" t="str">
         <v>已移除三項都空時的 disabled 條件（pages/ifare.vue:75 + pages/ifare/result.vue 三處），改用 hasAnyCondition 顯示「未填條件將顯示最新福利」提示。改採「不阻擋 + 引導文案」策略，與原建議「未填欄位紅框 + 錯誤文字」方向不同。</v>
       </c>
     </row>
@@ -4463,54 +4511,54 @@
       </c>
     </row>
     <row r="11" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A11" s="3">
+      <c r="A11" s="5">
         <v>9</v>
       </c>
-      <c r="B11" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C11" s="3" t="str">
+      <c r="B11" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C11" s="5" t="str">
         <v>i-Fare 福利查詢</v>
       </c>
-      <c r="D11" s="3" t="str">
+      <c r="D11" s="5" t="str">
         <v>查詢結果</v>
       </c>
-      <c r="E11" s="3" t="str">
+      <c r="E11" s="5" t="str">
         <v>提升</v>
       </c>
-      <c r="F11" s="3" t="str">
+      <c r="F11" s="5" t="str">
         <v>視覺</v>
       </c>
-      <c r="G11" s="3" t="str">
+      <c r="G11" s="5" t="str">
         <v>低</v>
       </c>
-      <c r="H11" s="3" t="str">
+      <c r="H11" s="5" t="str">
         <v>搜尋結果數量不夠醒目</v>
       </c>
-      <c r="I11" s="3" t="str">
+      <c r="I11" s="5" t="str">
         <v>結果數量 font-size:14px font-weight:400，周圍文字 opacity:0.5</v>
       </c>
-      <c r="J11" s="3" t="str">
+      <c r="J11" s="5" t="str">
         <v>頂部大字顯示 + 計數動畫</v>
       </c>
-      <c r="K11" s="3" t="str">
+      <c r="K11" s="5" t="str">
         <v>pages/ifare/result.vue</v>
       </c>
-      <c r="L11" s="3" t="str" xml:space="preserve">
+      <c r="L11" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">pages/ifare/result.vue_x000d__x000d__x000d_
 assets/style/components/_appBodyChild_ifare.scss_x000d__x000d__x000d_
 assets/style/_font.scss</v>
       </c>
-      <c r="M11" s="3" t="str">
+      <c r="M11" s="5" t="str">
         <v>確認字體小且無強調</v>
       </c>
-      <c r="N11" s="3" t="str">
+      <c r="N11" s="5" t="str">
         <v>部分修正</v>
       </c>
-      <c r="O11" s="3" t="str">
+      <c r="O11" s="5" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P11" s="3" t="str">
+      <c r="P11" s="5" t="str">
         <v>結果摘要從「{{count}}」改寫為「共找到 X 項，僅顯示前 X 筆」(pages/ifare/result.vue)；.result-total 從 inline-flex + ::before 結構簡化為 inline；新增 .result-summary-note 樣式。原訴求「頂部大字 + 計數動畫」尚未做。</v>
       </c>
     </row>
@@ -4822,106 +4870,106 @@
       </c>
     </row>
     <row r="18" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A18" s="3">
+      <c r="A18" s="6">
         <v>16</v>
       </c>
-      <c r="B18" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C18" s="3" t="str">
+      <c r="B18" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C18" s="7" t="str">
         <v>首頁</v>
       </c>
-      <c r="D18" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E18" s="3" t="str">
+      <c r="D18" s="7" t="str">
+        <v/>
+      </c>
+      <c r="E18" s="7" t="str">
         <v>修復</v>
       </c>
-      <c r="F18" s="3" t="str">
+      <c r="F18" s="7" t="str">
         <v>視覺</v>
       </c>
-      <c r="G18" s="3" t="str">
+      <c r="G18" s="7" t="str">
         <v>低</v>
       </c>
-      <c r="H18" s="3" t="str">
+      <c r="H18" s="7" t="str">
         <v>頁面切換無轉場動畫</v>
       </c>
-      <c r="I18" s="3" t="str">
+      <c r="I18" s="7" t="str">
         <v>layouts/default.vue 用 &lt;slot /&gt; 無 &lt;Transition&gt;，nuxt.config 無 pageTransition</v>
       </c>
-      <c r="J18" s="3" t="str">
+      <c r="J18" s="7" t="str">
         <v>加入 Nuxt &lt;transition&gt; 過場效果</v>
       </c>
-      <c r="K18" s="3" t="str">
+      <c r="K18" s="7" t="str">
         <v>layouts/default.vue</v>
       </c>
-      <c r="L18" s="3" t="str" xml:space="preserve">
+      <c r="L18" s="7" t="str" xml:space="preserve">
         <v xml:space="preserve">layouts/default.vue_x000d__x000d__x000d_
 nuxt.config.ts_x000d__x000d__x000d_
 assets/style/_transition.scss</v>
       </c>
-      <c r="M18" s="3" t="str">
+      <c r="M18" s="7" t="str">
         <v>確認無任何 transition 設定</v>
       </c>
-      <c r="N18" s="3" t="str">
+      <c r="N18" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O18" s="3" t="str">
+      <c r="O18" s="7" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P18" s="3" t="str">
+      <c r="P18" s="7" t="str">
         <v>app.vue 加 &lt;NuxtPage :transition="{ name: 'page', mode: 'out-in' }" /&gt;；_animation.scss 新增 .page-enter/leave-active 與 .layout-enter/leave-active keyframes（opacity + translateY，純 GPU 屬性）。</v>
       </c>
     </row>
     <row r="19" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A19" s="3">
+      <c r="A19" s="7">
         <v>17</v>
       </c>
-      <c r="B19" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C19" s="3" t="str">
+      <c r="B19" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C19" s="7" t="str">
         <v>首頁</v>
       </c>
-      <c r="D19" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E19" s="3" t="str">
+      <c r="D19" s="7" t="str">
+        <v/>
+      </c>
+      <c r="E19" s="7" t="str">
         <v>修復</v>
       </c>
-      <c r="F19" s="3" t="str">
+      <c r="F19" s="7" t="str">
         <v>視覺</v>
       </c>
-      <c r="G19" s="3" t="str">
+      <c r="G19" s="7" t="str">
         <v>中</v>
       </c>
-      <c r="H19" s="3" t="str">
+      <c r="H19" s="7" t="str">
         <v>Footer 社群連結呈現不一致</v>
       </c>
-      <c r="I19" s="3" t="str">
+      <c r="I19" s="7" t="str">
         <v>LINE 用 styled button (.btn-line)，Facebook 用純文字圖示連結 (.ic-facebook-before)</v>
       </c>
-      <c r="J19" s="3" t="str">
+      <c r="J19" s="7" t="str">
         <v>統一為相同呈現方式</v>
       </c>
-      <c r="K19" s="3" t="str">
+      <c r="K19" s="7" t="str">
         <v>components/AppFooter.vue</v>
       </c>
-      <c r="L19" s="3" t="str" xml:space="preserve">
+      <c r="L19" s="7" t="str" xml:space="preserve">
         <v xml:space="preserve">components/AppFooter.vue_x000d__x000d__x000d_
 assets/style/components/_appFooter.scss_x000d__x000d__x000d_
 assets/style/_font.scss</v>
       </c>
-      <c r="M19" s="3" t="str">
+      <c r="M19" s="7" t="str">
         <v>兩個社群連結完全不同的 HTML 結構和樣式</v>
       </c>
-      <c r="N19" s="3" t="str">
+      <c r="N19" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O19" s="3" t="str">
+      <c r="O19" s="7" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P19" s="3" t="str">
+      <c r="P19" s="7" t="str">
         <v>LINE 與 Facebook 統一為 .btn-social 白底按鈕（含 icon + 深綠字），Facebook 從 .ic-facebook-before 文字連結改為 button 結構並與 LINE 並排。LINE icon 修正為品牌綠 #06C755（Line-Logo.svg fill），Facebook 改用品牌藍 #1877F2（新增 Facebook-Logo-color.svg）。</v>
       </c>
     </row>
@@ -5134,155 +5182,155 @@
       </c>
     </row>
     <row r="24" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A24" s="3">
+      <c r="A24" s="7">
         <v>22</v>
       </c>
-      <c r="B24" s="3" t="str">
+      <c r="B24" s="7" t="str">
         <v>~</v>
       </c>
-      <c r="C24" s="3" t="str">
+      <c r="C24" s="7" t="str">
         <v>最新消息</v>
       </c>
-      <c r="D24" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E24" s="3" t="str">
+      <c r="D24" s="7" t="str">
+        <v/>
+      </c>
+      <c r="E24" s="7" t="str">
         <v>修復</v>
       </c>
-      <c r="F24" s="3" t="str">
+      <c r="F24" s="7" t="str">
         <v>互動</v>
       </c>
-      <c r="G24" s="3" t="str">
+      <c r="G24" s="7" t="str">
         <v>高</v>
       </c>
-      <c r="H24" s="3" t="str">
+      <c r="H24" s="7" t="str">
         <v>缺少 Loading 骨架畫面</v>
       </c>
-      <c r="I24" s="3" t="str">
+      <c r="I24" s="7" t="str">
         <v>API 載入期間無骨架或 loading 指示</v>
       </c>
-      <c r="J24" s="3" t="str">
+      <c r="J24" s="7" t="str">
         <v>新增 skeleton loader</v>
       </c>
-      <c r="K24" s="3" t="str">
+      <c r="K24" s="7" t="str">
         <v>pages/news.vue</v>
       </c>
-      <c r="L24" s="3" t="str" xml:space="preserve">
+      <c r="L24" s="7" t="str" xml:space="preserve">
         <v xml:space="preserve">pages/news.vue_x000d__x000d__x000d_
 assets/style/components/_appBody.scss</v>
       </c>
-      <c r="M24" s="3" t="str">
+      <c r="M24" s="7" t="str">
         <v>無骨架確認；但有 CSS :empty 空狀態（「目前沒有相關資料哦！」）</v>
       </c>
-      <c r="N24" s="3" t="str">
+      <c r="N24" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O24" s="3" t="str">
+      <c r="O24" s="7" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P24" s="3" t="str">
+      <c r="P24" s="7" t="str">
         <v>pages/news.vue 加 isLoading/hasError，分四分支渲染（4 條 skeleton-line 骨架／錯誤+重試／空狀態／正常列表）；LoadNews() 重構並加 .catch()；_animation.scss 加 @keyframes skeletonShimmer 與 .skeleton-line 樣式。</v>
       </c>
     </row>
     <row r="25" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A25" s="3">
+      <c r="A25" s="7">
         <v>23</v>
       </c>
-      <c r="B25" s="3" t="str">
+      <c r="B25" s="7" t="str">
         <v>~</v>
       </c>
-      <c r="C25" s="3" t="str">
+      <c r="C25" s="7" t="str">
         <v>最新消息</v>
       </c>
-      <c r="D25" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E25" s="3" t="str">
+      <c r="D25" s="7" t="str">
+        <v/>
+      </c>
+      <c r="E25" s="7" t="str">
         <v>修復</v>
       </c>
-      <c r="F25" s="3" t="str">
+      <c r="F25" s="7" t="str">
         <v>視覺</v>
       </c>
-      <c r="G25" s="3" t="str">
+      <c r="G25" s="7" t="str">
         <v>低</v>
       </c>
-      <c r="H25" s="3" t="str">
+      <c r="H25" s="7" t="str">
         <v>桌面版內容截斷無省略提示</v>
       </c>
-      <c r="I25" s="3" t="str">
+      <c r="I25" s="7" t="str">
         <v>桌面版 .item-info 無 text-overflow 或 line-clamp</v>
       </c>
-      <c r="J25" s="3" t="str">
+      <c r="J25" s="7" t="str">
         <v>加入 text-overflow: ellipsis 或 line-clamp</v>
       </c>
-      <c r="K25" s="3" t="str">
+      <c r="K25" s="7" t="str">
         <v>pages/news.vue</v>
       </c>
-      <c r="L25" s="3" t="str" xml:space="preserve">
+      <c r="L25" s="7" t="str" xml:space="preserve">
         <v xml:space="preserve">pages/news.vue_x000d__x000d__x000d_
 assets/style/components/_appBody.scss_x000d__x000d__x000d_
 assets/style/_font.scss</v>
       </c>
-      <c r="M25" s="3" t="str">
+      <c r="M25" s="7" t="str">
         <v>桌面無省略確認；手機版已有 textLineClamp(2)</v>
       </c>
-      <c r="N25" s="3" t="str">
+      <c r="N25" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O25" s="3" t="str">
+      <c r="O25" s="7" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P25" s="3" t="str">
+      <c r="P25" s="7" t="str">
         <v>pages/news.vue 的 .article-item .item-info 加 line-clamp: 2（桌面）/ line-clamp: 3（手機 ≤1024px），超過行數自動省略結尾。</v>
       </c>
     </row>
     <row r="26" ht="45" customHeight="1">
-      <c r="A26" s="3">
+      <c r="A26" s="7">
         <v>24</v>
       </c>
-      <c r="B26" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C26" s="3" t="str">
+      <c r="B26" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C26" s="7" t="str">
         <v>最新消息</v>
       </c>
-      <c r="D26" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E26" s="3" t="str">
+      <c r="D26" s="7" t="str">
+        <v/>
+      </c>
+      <c r="E26" s="7" t="str">
         <v>修復</v>
       </c>
-      <c r="F26" s="3" t="str">
+      <c r="F26" s="7" t="str">
         <v>無障礙</v>
       </c>
-      <c r="G26" s="3" t="str">
+      <c r="G26" s="7" t="str">
         <v>低</v>
       </c>
-      <c r="H26" s="3" t="str">
+      <c r="H26" s="7" t="str">
         <v>純圖示連結缺少 aria-label</v>
       </c>
-      <c r="I26" s="3" t="str">
+      <c r="I26" s="7" t="str">
         <v>&lt;i class="ic-arrow-right"&gt; 無 aria-label/title/隱藏文字</v>
       </c>
-      <c r="J26" s="3" t="str">
+      <c r="J26" s="7" t="str">
         <v>加入 aria-label</v>
       </c>
-      <c r="K26" s="3" t="str">
+      <c r="K26" s="7" t="str">
         <v>pages/news.vue</v>
       </c>
-      <c r="L26" s="3" t="str">
+      <c r="L26" s="7" t="str">
         <v>pages/news.vue</v>
       </c>
-      <c r="M26" s="3" t="str">
+      <c r="M26" s="7" t="str">
         <v>grep aria-label 全站回傳 0 筆</v>
       </c>
-      <c r="N26" s="3" t="str">
+      <c r="N26" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O26" s="3" t="str">
+      <c r="O26" s="7" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P26" s="3" t="str">
+      <c r="P26" s="7" t="str">
         <v>pages/news.vue 的 &lt;i class="ic-arrow-right"&gt; 加上 aria-label="閱讀全文"，符合無障礙語意要求。</v>
       </c>
     </row>
@@ -5338,54 +5386,54 @@
       </c>
     </row>
     <row r="28" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A28" s="3">
+      <c r="A28" s="7">
         <v>26</v>
       </c>
-      <c r="B28" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C28" s="3" t="str">
+      <c r="B28" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C28" s="7" t="str">
         <v>最新消息</v>
       </c>
-      <c r="D28" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E28" s="3" t="str">
+      <c r="D28" s="7" t="str">
+        <v/>
+      </c>
+      <c r="E28" s="7" t="str">
         <v>提升</v>
       </c>
-      <c r="F28" s="3" t="str">
+      <c r="F28" s="7" t="str">
         <v>視覺</v>
       </c>
-      <c r="G28" s="3" t="str">
+      <c r="G28" s="7" t="str">
         <v>低</v>
       </c>
-      <c r="H28" s="3" t="str">
+      <c r="H28" s="7" t="str">
         <v>新增「NEW」標籤</v>
       </c>
-      <c r="I28" s="3" t="str">
+      <c r="I28" s="7" t="str">
         <v>新消息無醒目標示</v>
       </c>
-      <c r="J28" s="3" t="str">
+      <c r="J28" s="7" t="str">
         <v>7 天內的新消息加上 NEW badge</v>
       </c>
-      <c r="K28" s="3" t="str">
+      <c r="K28" s="7" t="str">
         <v>pages/news.vue</v>
       </c>
-      <c r="L28" s="3" t="str" xml:space="preserve">
+      <c r="L28" s="7" t="str" xml:space="preserve">
         <v xml:space="preserve">pages/news.vue_x000d__x000d__x000d_
 assets/style/components/_appBody.scss_x000d__x000d__x000d_
 assets/style/_font.scss</v>
       </c>
-      <c r="M28" s="3" t="str">
+      <c r="M28" s="7" t="str">
         <v>功能確實不存在</v>
       </c>
-      <c r="N28" s="3" t="str">
+      <c r="N28" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O28" s="3" t="str">
+      <c r="O28" s="7" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P28" s="3" t="str">
+      <c r="P28" s="7" t="str">
         <v>pages/news.vue 加 isNewItem(releaseTime) helper（7 天內判斷），對應消息右上角顯示橘色 NEW pill 標籤（_appBody.scss .badge-new）。</v>
       </c>
     </row>
@@ -6267,54 +6315,54 @@
       </c>
     </row>
     <row r="46" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A46" s="3">
+      <c r="A46" s="7">
         <v>44</v>
       </c>
-      <c r="B46" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C46" s="3" t="str">
+      <c r="B46" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C46" s="7" t="str">
         <v>關於長穩</v>
       </c>
-      <c r="D46" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E46" s="3" t="str">
+      <c r="D46" s="7" t="str">
+        <v/>
+      </c>
+      <c r="E46" s="7" t="str">
         <v>提升</v>
       </c>
-      <c r="F46" s="3" t="str">
+      <c r="F46" s="7" t="str">
         <v>視覺</v>
       </c>
-      <c r="G46" s="3" t="str">
+      <c r="G46" s="7" t="str">
         <v>低</v>
       </c>
-      <c r="H46" s="3" t="str">
+      <c r="H46" s="7" t="str">
         <v>三大核心圖示為靜態 SVG</v>
       </c>
-      <c r="I46" s="3" t="str">
+      <c r="I46" s="7" t="str">
         <v>環境保育/人才培育/社會關懷用靜態 &lt;i class="how-logo"&gt;</v>
       </c>
-      <c r="J46" s="3" t="str">
+      <c r="J46" s="7" t="str">
         <v>加入 SVG 動畫</v>
       </c>
-      <c r="K46" s="3" t="str">
+      <c r="K46" s="7" t="str">
         <v>pages/about.vue</v>
       </c>
-      <c r="L46" s="3" t="str" xml:space="preserve">
+      <c r="L46" s="7" t="str" xml:space="preserve">
         <v xml:space="preserve">pages/about.vue_x000d__x000d__x000d_
 assets/style/components/_appBody_about.scss_x000d__x000d__x000d_
 assets/style/_animation.scss</v>
       </c>
-      <c r="M46" s="3" t="str">
+      <c r="M46" s="7" t="str">
         <v>確認無任何動畫 class 或 JS</v>
       </c>
-      <c r="N46" s="3" t="str">
+      <c r="N46" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O46" s="3" t="str">
+      <c r="O46" s="7" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P46" s="3" t="str">
+      <c r="P46" s="7" t="str">
         <v>icon SVG 本身仍為靜態，但已包入 Dynamic Island 互動卡片（.how-content）：hover/click toggle 觸發整體 morph 動畫（grid-template-rows 展開、translateY 浮起、background opacity overlay 漸層切換、border 露出青綠光暈）。視覺已不再死板。</v>
       </c>
     </row>
@@ -7040,106 +7088,106 @@
       </c>
     </row>
     <row r="61" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A61" s="3">
+      <c r="A61" s="7">
         <v>59</v>
       </c>
-      <c r="B61" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C61" s="3" t="str">
+      <c r="B61" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C61" s="7" t="str">
         <v>全站微互動</v>
       </c>
-      <c r="D61" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E61" s="3" t="str">
+      <c r="D61" s="7" t="str">
+        <v/>
+      </c>
+      <c r="E61" s="7" t="str">
         <v>提升</v>
       </c>
-      <c r="F61" s="3" t="str">
+      <c r="F61" s="7" t="str">
         <v>視覺</v>
       </c>
-      <c r="G61" s="3" t="str">
+      <c r="G61" s="7" t="str">
         <v>低</v>
       </c>
-      <c r="H61" s="3" t="str">
+      <c r="H61" s="7" t="str">
         <v>卡片 hover 效果升級</v>
       </c>
-      <c r="I61" s="3" t="str">
+      <c r="I61" s="7" t="str">
         <v>目前卡片 hover 效果單調</v>
       </c>
-      <c r="J61" s="3" t="str">
+      <c r="J61" s="7" t="str">
         <v>上浮 4px + 陰影加深</v>
       </c>
-      <c r="K61" s="3" t="str">
+      <c r="K61" s="7" t="str">
         <v>全站</v>
       </c>
-      <c r="L61" s="3" t="str" xml:space="preserve">
+      <c r="L61" s="7" t="str" xml:space="preserve">
         <v xml:space="preserve">assets/style/components/_appBody.scss_x000d__x000d__x000d_
 assets/style/components/_appBody_index.scss_x000d__x000d__x000d_
 assets/style/components/_appBodyChild_ifare.scss</v>
       </c>
-      <c r="M61" s="3" t="str">
+      <c r="M61" s="7" t="str">
         <v>功能確實不存在（待實測確認現有 hover）</v>
       </c>
-      <c r="N61" s="3" t="str">
+      <c r="N61" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O61" s="3" t="str">
+      <c r="O61" s="7" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P61" s="3" t="str">
+      <c r="P61" s="7" t="str">
         <v>_main.scss 為 .result-item / .article-item / .agency-item 加 hover translateY(-3px) + box-shadow，active translateY(-1px) 回彈。純 GPU 屬性，不觸發 layout 重繪。</v>
       </c>
     </row>
     <row r="62" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A62" s="3">
+      <c r="A62" s="5">
         <v>60</v>
       </c>
-      <c r="B62" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C62" s="3" t="str">
+      <c r="B62" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C62" s="5" t="str">
         <v>全站微互動</v>
       </c>
-      <c r="D62" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E62" s="3" t="str">
+      <c r="D62" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E62" s="5" t="str">
         <v>提升</v>
       </c>
-      <c r="F62" s="3" t="str">
+      <c r="F62" s="5" t="str">
         <v>視覺</v>
       </c>
-      <c r="G62" s="3" t="str">
+      <c r="G62" s="5" t="str">
         <v>低</v>
       </c>
-      <c r="H62" s="3" t="str">
+      <c r="H62" s="5" t="str">
         <v>CTA 按鈕互動效果</v>
       </c>
-      <c r="I62" s="3" t="str">
+      <c r="I62" s="5" t="str">
         <v>按鈕缺乏觸覺回饋</v>
       </c>
-      <c r="J62" s="3" t="str">
+      <c r="J62" s="5" t="str">
         <v>hover 按壓回彈 + 點擊漣漪效果</v>
       </c>
-      <c r="K62" s="3" t="str">
+      <c r="K62" s="5" t="str">
         <v>全站</v>
       </c>
-      <c r="L62" s="3" t="str" xml:space="preserve">
+      <c r="L62" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">assets/style/components/_button.scss_x000d__x000d__x000d_
 assets/style/_font.scss_x000d__x000d__x000d_
 assets/style/rwd/_rwd_button.scss</v>
       </c>
-      <c r="M62" s="3" t="str">
+      <c r="M62" s="5" t="str">
         <v>功能確實不存在</v>
       </c>
-      <c r="N62" s="3" t="str">
+      <c r="N62" s="5" t="str">
         <v>部分修正</v>
       </c>
-      <c r="O62" s="3" t="str">
+      <c r="O62" s="5" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P62" s="3" t="str">
+      <c r="P62" s="5" t="str">
         <v>_main.scss 為 .btn-filter / .btn-tag / .btn-retry 加 hover translateY(-1px) + active scale(0.97) 按壓回彈。原訴求「點擊漣漪效果」尚未做。</v>
       </c>
     </row>
@@ -7655,55 +7703,55 @@
       </c>
     </row>
     <row r="73" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A73" s="3">
+      <c r="A73" s="5">
         <v>71</v>
       </c>
-      <c r="B73" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C73" s="3" t="str">
+      <c r="B73" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C73" s="5" t="str">
         <v>全站通用</v>
       </c>
-      <c r="D73" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E73" s="3" t="str">
+      <c r="D73" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E73" s="5" t="str">
         <v>修復</v>
       </c>
-      <c r="F73" s="3" t="str">
+      <c r="F73" s="5" t="str">
         <v>RWD</v>
       </c>
-      <c r="G73" s="3" t="str">
+      <c r="G73" s="5" t="str">
         <v>高</v>
       </c>
-      <c r="H73" s="3" t="str">
+      <c r="H73" s="5" t="str">
         <v>多處觸控目標小於 44x44px</v>
       </c>
-      <c r="I73" s="3" t="str">
+      <c r="I73" s="5" t="str">
         <v>分頁按鈕 30x30px、.btn-reset height:32px、.btn-advance height:40px</v>
       </c>
-      <c r="J73" s="3" t="str">
+      <c r="J73" s="5" t="str">
         <v>確保所有可點擊元素最小 44x44px</v>
       </c>
-      <c r="K73" s="3" t="str">
+      <c r="K73" s="5" t="str">
         <v>全站</v>
       </c>
-      <c r="L73" s="3" t="str" xml:space="preserve">
+      <c r="L73" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">assets/style/components/_compPage.scss_x000d__x000d__x000d_
 assets/style/components/_button.scss_x000d__x000d__x000d_
 assets/style/components/_compSelect.scss_x000d__x000d__x000d_
 assets/style/rwd/_rwd_compPage.scss</v>
       </c>
-      <c r="M73" s="3" t="str">
+      <c r="M73" s="5" t="str">
         <v>確認多處尺寸低於 44px 標準</v>
       </c>
-      <c r="N73" s="3" t="str">
+      <c r="N73" s="5" t="str">
         <v>部分修正</v>
       </c>
-      <c r="O73" s="3" t="str">
+      <c r="O73" s="5" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P73" s="3" t="str">
+      <c r="P73" s="5" t="str">
         <v>footer .btn-social 高度從 40px 提升到 44px（LINE / Facebook 兩按鈕符合 iOS HIG 觸控標準）。CompPage 分頁箭頭、btn-reset、btn-advance、CompSelect 等其他元件尚未套用 44px 標準。</v>
       </c>
     </row>
@@ -8100,52 +8148,52 @@
       </c>
     </row>
     <row r="82" ht="45" customHeight="1">
-      <c r="A82" s="3">
+      <c r="A82" s="5">
         <v>80</v>
       </c>
-      <c r="B82" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C82" s="3" t="str">
+      <c r="B82" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C82" s="5" t="str">
         <v>全站通用</v>
       </c>
-      <c r="D82" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E82" s="3" t="str">
+      <c r="D82" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E82" s="5" t="str">
         <v>修復</v>
       </c>
-      <c r="F82" s="3" t="str">
+      <c r="F82" s="5" t="str">
         <v>互動</v>
       </c>
-      <c r="G82" s="3" t="str">
+      <c r="G82" s="5" t="str">
         <v>高</v>
       </c>
-      <c r="H82" s="3" t="str">
+      <c r="H82" s="5" t="str">
         <v>缺少載入失敗與重試機制</v>
       </c>
-      <c r="I82" s="3" t="str">
+      <c r="I82" s="5" t="str">
         <v>目前清單有 loading / skeleton / toast，但尚未明確區分 API 載入失敗狀態與重試機制。</v>
       </c>
-      <c r="J82" s="3" t="str">
+      <c r="J82" s="5" t="str">
         <v>建立統一錯誤狀態元件，針對 API 失敗提供錯誤訊息、retry 按鈕，並區分空資料與載入失敗。</v>
       </c>
-      <c r="K82" s="3" t="str">
+      <c r="K82" s="5" t="str">
         <v>全站</v>
       </c>
-      <c r="L82" s="3" t="str">
+      <c r="L82" s="5" t="str">
         <v>pages/news.vue pages/articles.vue pages/collaborator.vue pages/ifare/result.vue layouts/default.vue components/</v>
       </c>
-      <c r="M82" s="3" t="str">
+      <c r="M82" s="5" t="str">
         <v>現有清單多著重 loading 與空狀態，未明列 error state。</v>
       </c>
-      <c r="N82" s="3" t="str">
+      <c r="N82" s="5" t="str">
         <v>部分修正</v>
       </c>
-      <c r="O82" s="3" t="str">
+      <c r="O82" s="5" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P82" s="3" t="str">
+      <c r="P82" s="5" t="str">
         <v>pages/news.vue 已實作 hasError + .btn-retry 按鈕模式（搭配 _animation.scss .part-error 樣式）。articles.vue / collaborator.vue / ifare/result.vue 三頁尚未套用同一錯誤狀態元件。</v>
       </c>
     </row>
@@ -8443,1173 +8491,1173 @@
       </c>
     </row>
     <row r="90" ht="100.8" customHeight="1" xml:space="preserve">
-      <c r="A90" s="3">
+      <c r="A90" s="7">
         <v>88</v>
       </c>
-      <c r="B90" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C90" s="3" t="str">
+      <c r="B90" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C90" s="7" t="str">
         <v>i-Fare 福利查詢</v>
       </c>
-      <c r="D90" s="3" t="str">
+      <c r="D90" s="7" t="str">
         <v>搜尋介面</v>
       </c>
-      <c r="E90" s="3" t="str">
+      <c r="E90" s="7" t="str">
         <v>提升</v>
       </c>
-      <c r="F90" s="3" t="str">
+      <c r="F90" s="7" t="str">
         <v>黏著</v>
       </c>
-      <c r="G90" s="3" t="str">
+      <c r="G90" s="7" t="str">
         <v>中</v>
       </c>
-      <c r="H90" s="3" t="str">
+      <c r="H90" s="7" t="str">
         <v>新增關鍵字搜尋輸入欄</v>
       </c>
-      <c r="I90" s="3" t="str">
+      <c r="I90" s="7" t="str">
         <v>原本搜尋只能用三個下拉選單（政策類別、受助對象、地區），缺少自由文字搜尋入口</v>
       </c>
-      <c r="J90" s="3" t="str">
+      <c r="J90" s="7" t="str">
         <v>ifare 與結果頁各加 &lt;input.input-keyword&gt;（含 Enter 快捷鍵），搜尋條件擴增 keyword 參數，後端 LIKE 查詢</v>
       </c>
-      <c r="K90" s="3" t="str">
+      <c r="K90" s="7" t="str">
         <v>pages/ifare.vue pages/ifare/result.vue</v>
       </c>
-      <c r="L90" s="3" t="str" xml:space="preserve">
+      <c r="L90" s="7" t="str" xml:space="preserve">
         <v xml:space="preserve">pages/ifare.vue_x000d__x000d__x000d_
 pages/ifare/result.vue_x000d__x000d__x000d_
 assets/style/components/_appBody_ifare.scss_x000d__x000d__x000d_
 assets/style/components/_appBodyChild_ifare.scss</v>
       </c>
-      <c r="M90" s="3" t="str">
+      <c r="M90" s="7" t="str">
         <v>改版補登；後端 IFare_API.Application/Fare/Policy/* 已加 Keyword filter</v>
       </c>
-      <c r="N90" s="3" t="str">
+      <c r="N90" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O90" s="3" t="str">
+      <c r="O90" s="7" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P90" s="3" t="str">
+      <c r="P90" s="7" t="str">
         <v>改版補登；前端 Search() 已帶 keyword 參數，API 傳 Keyword 欄位</v>
       </c>
     </row>
     <row r="91" ht="57.6" customHeight="1">
-      <c r="A91" s="3">
+      <c r="A91" s="7">
         <v>89</v>
       </c>
-      <c r="B91" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C91" s="3" t="str">
+      <c r="B91" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C91" s="7" t="str">
         <v>i-Fare 福利查詢</v>
       </c>
-      <c r="D91" s="3" t="str">
+      <c r="D91" s="7" t="str">
         <v>查詢結果</v>
       </c>
-      <c r="E91" s="3" t="str">
+      <c r="E91" s="7" t="str">
         <v>修復</v>
       </c>
-      <c r="F91" s="3" t="str">
+      <c r="F91" s="7" t="str">
         <v>互動</v>
       </c>
-      <c r="G91" s="3" t="str">
+      <c r="G91" s="7" t="str">
         <v>中</v>
       </c>
-      <c r="H91" s="3" t="str">
+      <c r="H91" s="7" t="str">
         <v>結果頁未支援 URL query 初始化</v>
       </c>
-      <c r="I91" s="3" t="str">
+      <c r="I91" s="7" t="str">
         <v>結果頁從 ifare 跳轉過來時若重整或從外部進入，搜尋條件無法保留</v>
       </c>
-      <c r="J91" s="3" t="str">
+      <c r="J91" s="7" t="str">
         <v>解析 route.query 初始化各 ref（policy / recipient / area / keyword），支援深度連結與重整保留條件</v>
       </c>
-      <c r="K91" s="3" t="str">
+      <c r="K91" s="7" t="str">
         <v>pages/ifare/result.vue</v>
       </c>
-      <c r="L91" s="3" t="str">
+      <c r="L91" s="7" t="str">
         <v>pages/ifare/result.vue</v>
       </c>
-      <c r="M91" s="3" t="str">
+      <c r="M91" s="7" t="str">
         <v>改版補登；搭配 #88 關鍵字欄位一起實作</v>
       </c>
-      <c r="N91" s="3" t="str">
+      <c r="N91" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O91" s="3" t="str">
+      <c r="O91" s="7" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P91" s="3" t="str">
+      <c r="P91" s="7" t="str">
         <v>改版補登</v>
       </c>
     </row>
     <row r="92" ht="57.6" customHeight="1">
-      <c r="A92" s="3">
+      <c r="A92" s="7">
         <v>90</v>
       </c>
-      <c r="B92" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C92" s="3" t="str">
+      <c r="B92" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C92" s="7" t="str">
         <v>i-Fare 福利查詢</v>
       </c>
-      <c r="D92" s="3" t="str">
+      <c r="D92" s="7" t="str">
         <v>搜尋介面</v>
       </c>
-      <c r="E92" s="3" t="str">
+      <c r="E92" s="7" t="str">
         <v>修復</v>
       </c>
-      <c r="F92" s="3" t="str">
+      <c r="F92" s="7" t="str">
         <v>RWD</v>
       </c>
-      <c r="G92" s="3" t="str">
+      <c r="G92" s="7" t="str">
         <v>低</v>
       </c>
-      <c r="H92" s="3" t="str">
+      <c r="H92" s="7" t="str">
         <v>搜尋按鈕區手機版橫排擠壓</v>
       </c>
-      <c r="I92" s="3" t="str">
+      <c r="I92" s="7" t="str">
         <v>.item-bottom 原為橫排，手機版按鈕和提示文字擠在一起</v>
       </c>
-      <c r="J92" s="3" t="str">
+      <c r="J92" s="7" t="str">
         <v>_appBody_ifare.scss .item-bottom 改 flex-direction: column + gap + 居中，並加 .filter-hint 樣式</v>
       </c>
-      <c r="K92" s="3" t="str">
+      <c r="K92" s="7" t="str">
         <v>pages/ifare.vue</v>
       </c>
-      <c r="L92" s="3" t="str">
+      <c r="L92" s="7" t="str">
         <v>iFare_Frontend/assets/style/components/_appBody_ifare.scss</v>
       </c>
-      <c r="M92" s="3" t="str">
+      <c r="M92" s="7" t="str">
         <v>改版補登；搭配 #1 disabled 移除後新增的提示文字調整版面</v>
       </c>
-      <c r="N92" s="3" t="str">
+      <c r="N92" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O92" s="3" t="str">
+      <c r="O92" s="7" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P92" s="3" t="str">
+      <c r="P92" s="7" t="str">
         <v>改版補登</v>
       </c>
     </row>
     <row r="93" ht="86.40000000000002" customHeight="1" xml:space="preserve">
-      <c r="A93" s="3">
+      <c r="A93" s="7">
         <v>91</v>
       </c>
-      <c r="B93" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C93" s="3" t="str">
+      <c r="B93" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C93" s="7" t="str">
         <v>共用元件</v>
       </c>
-      <c r="D93" s="3" t="str">
+      <c r="D93" s="7" t="str">
         <v>AppFooter</v>
       </c>
-      <c r="E93" s="3" t="str">
+      <c r="E93" s="7" t="str">
         <v>提升</v>
       </c>
-      <c r="F93" s="3" t="str">
+      <c r="F93" s="7" t="str">
         <v>視覺</v>
       </c>
-      <c r="G93" s="3" t="str">
+      <c r="G93" s="7" t="str">
         <v>低</v>
       </c>
-      <c r="H93" s="3" t="str">
+      <c r="H93" s="7" t="str">
         <v>Footer 聯絡資訊缺 icon</v>
       </c>
-      <c r="I93" s="3" t="str">
+      <c r="I93" s="7" t="str">
         <v>footer 4 個 label（聯絡電話 / 聯絡信箱 / 地址 / 服務時間）僅有純文字，缺乏視覺辨識</v>
       </c>
-      <c r="J93" s="3" t="str">
+      <c r="J93" s="7" t="str">
         <v>4 個 label 前各加對應 icon（Tel / Mail / Address / Clock），與站內既有 icon 風格一致</v>
       </c>
-      <c r="K93" s="3" t="str">
+      <c r="K93" s="7" t="str">
         <v>components/AppFooter.vue</v>
       </c>
-      <c r="L93" s="3" t="str" xml:space="preserve">
+      <c r="L93" s="7" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/components/AppFooter.vue_x000d__x000d__x000d_
 assets/style/components/_appFooter.scss_x000d__x000d__x000d_
 assets/style/_font.scss_x000d__x000d__x000d_
 assets/img/Mail.svg (新增)_x000d__x000d__x000d_
 assets/img/Clock.svg (新增)</v>
       </c>
-      <c r="M93" s="3" t="str">
+      <c r="M93" s="7" t="str">
         <v>改版補登；新增 Mail.svg + Clock.svg 用 mask-image 著色為 rgba(white,.7)，沿用既有 Tel.svg / Location.svg。原 ::before content 的 CSS-only label 改為 HTML &lt;span class="footer-info-label"&gt; 結構</v>
       </c>
-      <c r="N93" s="3" t="str">
+      <c r="N93" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O93" s="3" t="str">
+      <c r="O93" s="7" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P93" s="3" t="str">
+      <c r="P93" s="7" t="str">
         <v>改版補登</v>
       </c>
     </row>
     <row r="94" ht="273.6" customHeight="1" xml:space="preserve">
-      <c r="A94" s="3">
+      <c r="A94" s="7">
         <v>92</v>
       </c>
-      <c r="B94" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C94" s="3" t="str">
+      <c r="B94" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C94" s="7" t="str">
         <v>共用元件</v>
       </c>
-      <c r="D94" s="3" t="str">
+      <c r="D94" s="7" t="str">
         <v>AppFooter</v>
       </c>
-      <c r="E94" s="3" t="str">
+      <c r="E94" s="7" t="str">
         <v>提升</v>
       </c>
-      <c r="F94" s="3" t="str">
+      <c r="F94" s="7" t="str">
         <v>互動</v>
       </c>
-      <c r="G94" s="3" t="str">
+      <c r="G94" s="7" t="str">
         <v>中</v>
       </c>
-      <c r="H94" s="3" t="str">
+      <c r="H94" s="7" t="str">
         <v>社群連結 LINE / Facebook 分散兩處</v>
       </c>
-      <c r="I94" s="3" t="str">
+      <c r="I94" s="7" t="str">
         <v>LINE 在「進一步瞭解更多」CTA 區塊內，Facebook 在獨立 .part-middle 區塊；兩者都是社群媒體應該放一起</v>
       </c>
-      <c r="J94" s="3" t="str">
+      <c r="J94" s="7" t="str">
         <v>把 Facebook 從 .part-middle 移到 .card-more 內 .card-more-socials div 與 LINE 並排，整合為單一社群區塊</v>
       </c>
-      <c r="K94" s="3" t="str">
+      <c r="K94" s="7" t="str">
         <v>components/AppFooter.vue</v>
       </c>
-      <c r="L94" s="3" t="str" xml:space="preserve">
+      <c r="L94" s="7" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/components/AppFooter.vue_x000d__x000d__x000d_
 assets/style/components/_appFooter.scss_x000d__x000d__x000d_
 assets/style/rwd/_rwd_appFooter.scss</v>
       </c>
-      <c r="M94" s="3" t="str">
+      <c r="M94" s="7" t="str">
         <v>改版補登；移除原 .part-middle 與 .link-track 樣式</v>
       </c>
-      <c r="N94" s="3" t="str">
+      <c r="N94" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O94" s="3" t="str">
+      <c r="O94" s="7" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P94" s="3" t="str">
+      <c r="P94" s="7" t="str">
         <v>改版補登；同步修桌面 1025-1280px overflow（加 FB 後 .card-more 內容寬度 ~1300px 會爆）：.card-more 加 flex-wrap: wrap + max-width: calc(100% - 64px)；.info-more 加 max-width: 480px 讓長文字桌面換 2 行</v>
       </c>
     </row>
     <row r="95" ht="129.6" customHeight="1" xml:space="preserve">
-      <c r="A95" s="3">
+      <c r="A95" s="7">
         <v>93</v>
       </c>
-      <c r="B95" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C95" s="3" t="str">
+      <c r="B95" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C95" s="7" t="str">
         <v>關於長穩</v>
       </c>
-      <c r="D95" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E95" s="3" t="str">
+      <c r="D95" s="7" t="str">
+        <v/>
+      </c>
+      <c r="E95" s="7" t="str">
         <v>提升</v>
       </c>
-      <c r="F95" s="3" t="str">
+      <c r="F95" s="7" t="str">
         <v>互動</v>
       </c>
-      <c r="G95" s="3" t="str">
+      <c r="G95" s="7" t="str">
         <v>中</v>
       </c>
-      <c r="H95" s="3" t="str">
+      <c r="H95" s="7" t="str">
         <v>About 三大核心介紹缺乏互動性</v>
       </c>
-      <c r="I95" s="3" t="str">
+      <c r="I95" s="7" t="str">
         <v>環境保育/人才培育/社會關懷三張卡片原為靜態圖文，使用者掃過無視覺反應，缺乏吸引點擊探索的動機</v>
       </c>
-      <c r="J95" s="3" t="str">
+      <c r="J95" s="7" t="str">
         <v>改造為 iOS Dynamic Island 風格 morph 卡片：暖象牙白漸層底 + 圓角 28px + 預設只露 icon+標題 → hover/click toggle 平滑展開內文（grid-template-rows trick）+ translateY 浮起 + 邊框露出青綠光暈</v>
       </c>
-      <c r="K95" s="3" t="str">
+      <c r="K95" s="7" t="str">
         <v>pages/about.vue</v>
       </c>
-      <c r="L95" s="3" t="str" xml:space="preserve">
+      <c r="L95" s="7" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/pages/about.vue_x000d__x000d__x000d_
 assets/style/components/_appBody_about.scss_x000d__x000d__x000d_
 assets/style/rwd/_rwd_about.scss</v>
       </c>
-      <c r="M95" s="3" t="str">
+      <c r="M95" s="7" t="str">
         <v>改版補登；HTML 重組（icon+title 合進 .how-top、info 包 .how-info-wrap）；script 加 activeHow ref + toggleHow handler；keyboard a11y (Enter/Space) 與 tabindex；GPU 優化（will-change + ::before opacity overlay 取代 gradient transition）；Apple spring easing cubic-bezier(0.32, 0.72, 0, 1)</v>
       </c>
-      <c r="N95" s="3" t="str">
+      <c r="N95" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O95" s="3" t="str">
+      <c r="O95" s="7" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P95" s="3" t="str">
+      <c r="P95" s="7" t="str">
         <v>改版補登；對應 #44 三大核心圖示靜態問題已連動修正</v>
       </c>
     </row>
     <row r="96" ht="100.8" customHeight="1">
-      <c r="A96" s="3">
+      <c r="A96" s="7">
         <v>94</v>
       </c>
-      <c r="B96" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C96" s="3" t="str">
+      <c r="B96" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C96" s="7" t="str">
         <v>關於長穩</v>
       </c>
-      <c r="D96" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E96" s="3" t="str">
+      <c r="D96" s="7" t="str">
+        <v/>
+      </c>
+      <c r="E96" s="7" t="str">
         <v>提升</v>
       </c>
-      <c r="F96" s="3" t="str">
+      <c r="F96" s="7" t="str">
         <v>視覺</v>
       </c>
-      <c r="G96" s="3" t="str">
+      <c r="G96" s="7" t="str">
         <v>低</v>
       </c>
-      <c r="H96" s="3" t="str">
+      <c r="H96" s="7" t="str">
         <v>About 成員照片缺 hover 互動</v>
       </c>
-      <c r="I96" s="3" t="str">
+      <c r="I96" s="7" t="str">
         <v>陳進財/鄔筠軒/顏杏蓉三位成員區塊原無 hover 反饋，掃過時視覺無變化</v>
       </c>
-      <c r="J96" s="3" t="str">
+      <c r="J96" s="7" t="str">
         <v>陳進財/鄔筠軒整組 hover：照片 scale(1.06) + 白框 scale(1.03) + box-shadow 加深 + 橘色標牌 translateY(-4px)；顏杏蓉（無照片）標牌 hover translateY(-4px) + scale(1.04)</v>
       </c>
-      <c r="K96" s="3" t="str">
+      <c r="K96" s="7" t="str">
         <v>pages/about.vue</v>
       </c>
-      <c r="L96" s="3" t="str">
+      <c r="L96" s="7" t="str">
         <v>iFare_Frontend/assets/style/components/_appBody_about.scss</v>
       </c>
-      <c r="M96" s="3" t="str">
+      <c r="M96" s="7" t="str">
         <v>改版補登；同套 cubic-bezier(0.32, 0.72, 0, 1) easing；will-change: transform 給 .member-photo 預先建 GPU layer</v>
       </c>
-      <c r="N96" s="3" t="str">
+      <c r="N96" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O96" s="3" t="str">
+      <c r="O96" s="7" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P96" s="3" t="str">
+      <c r="P96" s="7" t="str">
         <v>改版補登</v>
       </c>
     </row>
     <row r="97" ht="57.6" customHeight="1">
-      <c r="A97" s="3">
+      <c r="A97" s="7">
         <v>95</v>
       </c>
-      <c r="B97" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C97" s="3" t="str">
+      <c r="B97" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C97" s="7" t="str">
         <v>關於長穩</v>
       </c>
-      <c r="D97" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E97" s="3" t="str">
+      <c r="D97" s="7" t="str">
+        <v/>
+      </c>
+      <c r="E97" s="7" t="str">
         <v>提升</v>
       </c>
-      <c r="F97" s="3" t="str">
+      <c r="F97" s="7" t="str">
         <v>視覺</v>
       </c>
-      <c r="G97" s="3" t="str">
+      <c r="G97" s="7" t="str">
         <v>低</v>
       </c>
-      <c r="H97" s="3" t="str">
+      <c r="H97" s="7" t="str">
         <v>About 底部 CTA 連結缺 hover micro-animation</v>
       </c>
-      <c r="I97" s="3" t="str">
+      <c r="I97" s="7" t="str">
         <v>「前往 i-Fare」與「查看最新消息」兩個 advance-link 原為靜態，hover 無互動反饋，無法強化「點我前進」訊號</v>
       </c>
-      <c r="J97" s="3" t="str">
+      <c r="J97" s="7" t="str">
         <v>連結 hover 時 translateY(-2px) 上浮，箭頭 icon translateX(6px) 向右滑出，引導視線前進</v>
       </c>
-      <c r="K97" s="3" t="str">
+      <c r="K97" s="7" t="str">
         <v>pages/about.vue</v>
       </c>
-      <c r="L97" s="3" t="str">
+      <c r="L97" s="7" t="str">
         <v>iFare_Frontend/assets/style/components/_appBody_about.scss</v>
       </c>
-      <c r="M97" s="3" t="str">
+      <c r="M97" s="7" t="str">
         <v>改版補登；統一 cubic-bezier(0.32, 0.72, 0, 1) easing 0.22s</v>
       </c>
-      <c r="N97" s="3" t="str">
+      <c r="N97" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O97" s="3" t="str">
+      <c r="O97" s="7" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P97" s="3" t="str">
+      <c r="P97" s="7" t="str">
         <v>改版補登</v>
       </c>
     </row>
     <row r="98" ht="129.6" customHeight="1" xml:space="preserve">
-      <c r="A98" s="3">
+      <c r="A98" s="7">
         <v>96</v>
       </c>
-      <c r="B98" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C98" s="3" t="str">
+      <c r="B98" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C98" s="7" t="str">
         <v>最新消息</v>
       </c>
-      <c r="D98" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E98" s="3" t="str">
+      <c r="D98" s="7" t="str">
+        <v/>
+      </c>
+      <c r="E98" s="7" t="str">
         <v>提升</v>
       </c>
-      <c r="F98" s="3" t="str">
+      <c r="F98" s="7" t="str">
         <v>視覺</v>
       </c>
-      <c r="G98" s="3" t="str">
+      <c r="G98" s="7" t="str">
         <v>中</v>
       </c>
-      <c r="H98" s="3" t="str">
+      <c r="H98" s="7" t="str">
         <v>News 列表呈現升級為浮起卡片 + 入場動畫 + 日期 pill</v>
       </c>
-      <c r="I98" s="3" t="str">
+      <c r="I98" s="7" t="str">
         <v>原本最新消息為「底線分隔的清單列」，hover 只是淡白底 + 箭頭轉橘，視覺扁平、缺乏互動感、日期不醒目、長內文無截斷</v>
       </c>
-      <c r="J98" s="3" t="str">
+      <c r="J98" s="7" t="str">
         <v>列表整體升級：圓角 16px 浮起卡片（white .7 + shadow）+ stagger fade-up 入場動畫（@for 1~12 each +50ms）+ 日期變橘色 pill 標籤（border + 半透明橘底）+ hover translateY(-3px) + 背景變實白 + 箭頭橘色滑右 6px</v>
       </c>
-      <c r="K98" s="3" t="str">
+      <c r="K98" s="7" t="str">
         <v>pages/news.vue</v>
       </c>
-      <c r="L98" s="3" t="str" xml:space="preserve">
+      <c r="L98" s="7" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/pages/news.vue_x000d__x000d__x000d_
 assets/style/components/_appBody.scss_x000d__x000d__x000d_
 assets/style/_animation.scss_x000d__x000d__x000d_
 assets/style/rwd/_rwd.scss</v>
       </c>
-      <c r="M98" s="3" t="str">
+      <c r="M98" s="7" t="str">
         <v>改版補登；@keyframes newsItemEnter 放 _animation.scss；統一 cubic-bezier(0.32, 0.72, 0, 1) easing；配色全用既有 token 沒引入新色</v>
       </c>
-      <c r="N98" s="3" t="str">
+      <c r="N98" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O98" s="3" t="str">
+      <c r="O98" s="7" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P98" s="3" t="str">
+      <c r="P98" s="7" t="str">
         <v>改版補登；同次改動連帶解決 #23 (line-clamp 2)、#24 (aria-label)、#26 (NEW badge)</v>
       </c>
     </row>
     <row r="99" ht="72" customHeight="1" xml:space="preserve">
-      <c r="A99" s="3">
+      <c r="A99" s="7">
         <v>97</v>
       </c>
-      <c r="B99" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C99" s="3" t="str">
+      <c r="B99" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C99" s="7" t="str">
         <v>共用元件</v>
       </c>
-      <c r="D99" s="3" t="str">
+      <c r="D99" s="7" t="str">
         <v>AppFooter / AppHeader</v>
       </c>
-      <c r="E99" s="3" t="str">
+      <c r="E99" s="7" t="str">
         <v>修復</v>
       </c>
-      <c r="F99" s="3" t="str">
+      <c r="F99" s="7" t="str">
         <v>互動</v>
       </c>
-      <c r="G99" s="3" t="str">
+      <c r="G99" s="7" t="str">
         <v>低</v>
       </c>
-      <c r="H99" s="3" t="str">
+      <c r="H99" s="7" t="str">
         <v>社群外連結未開新分頁，可能丟失當前頁狀態</v>
       </c>
-      <c r="I99" s="3" t="str">
+      <c r="I99" s="7" t="str">
         <v>AppFooter LINE/Facebook 與 AppHeader 手機版社群 icon 連結原為一般 &lt;a href&gt;，點擊會在當前分頁導向，使用者離開站內後返回成本高</v>
       </c>
-      <c r="J99" s="3" t="str">
+      <c r="J99" s="7" t="str">
         <v>4 個社群連結都加 target="_blank" + rel="noopener noreferrer"：開新分頁、避免反向 tabnabbing、不洩漏 referrer</v>
       </c>
-      <c r="K99" s="3" t="str">
+      <c r="K99" s="7" t="str">
         <v>components/AppFooter.vue components/AppHeader.vue</v>
       </c>
-      <c r="L99" s="3" t="str" xml:space="preserve">
+      <c r="L99" s="7" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/components/AppFooter.vue_x000d__x000d__x000d_
 iFare_Frontend/components/AppHeader.vue</v>
       </c>
-      <c r="M99" s="3" t="str">
+      <c r="M99" s="7" t="str">
         <v>改版補登；rel="noopener" 是 W3C 安全建議</v>
       </c>
-      <c r="N99" s="3" t="str">
+      <c r="N99" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O99" s="3" t="str">
+      <c r="O99" s="7" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P99" s="3" t="str">
+      <c r="P99" s="7" t="str">
         <v>改版補登</v>
       </c>
     </row>
     <row r="100" ht="100.8" customHeight="1">
-      <c r="A100" s="3">
+      <c r="A100" s="7">
         <v>98</v>
       </c>
-      <c r="B100" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C100" s="3" t="str">
+      <c r="B100" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C100" s="7" t="str">
         <v>關於長穩</v>
       </c>
-      <c r="D100" s="3" t="str">
+      <c r="D100" s="7" t="str">
         <v>三大核心介紹</v>
       </c>
-      <c r="E100" s="3" t="str">
+      <c r="E100" s="7" t="str">
         <v>修復</v>
       </c>
-      <c r="F100" s="3" t="str">
+      <c r="F100" s="7" t="str">
         <v>互動</v>
       </c>
-      <c r="G100" s="3" t="str">
+      <c r="G100" s="7" t="str">
         <v>中</v>
       </c>
-      <c r="H100" s="3" t="str">
+      <c r="H100" s="7" t="str">
         <v>About 第一張卡 hover 完全無反應 (Round 3 副作用)</v>
       </c>
-      <c r="I100" s="3" t="str">
+      <c r="I100" s="7" t="str">
         <v>cf47cfa Round 3 加的 .section-about-member::before 視覺裝飾 (z-index:48 + 1497x1497px 圓形 + top:-300px/left:-750px) 蓋住上方 about-how 區左半邊，攔截「環境保育」第一張 morph 卡的所有 hover/click events。第二、三張位置在中右側未被覆蓋，因此正常運作。</v>
       </c>
-      <c r="J100" s="3" t="str">
+      <c r="J100" s="7" t="str">
         <v>裝飾性 ::before 加 pointer-events: none 讓 mouse events 穿透到下層的 .how-content</v>
       </c>
-      <c r="K100" s="3" t="str">
+      <c r="K100" s="7" t="str">
         <v>pages/about.vue</v>
       </c>
-      <c r="L100" s="3" t="str">
+      <c r="L100" s="7" t="str">
         <v>iFare_Frontend/assets/style/components/_appBody_about.scss</v>
       </c>
-      <c r="M100" s="3" t="str">
+      <c r="M100" s="7" t="str">
         <v>修復 cf47cfa 副作用；不影響原視覺 (radial-gradient 橘色光暈仍可見)</v>
       </c>
-      <c r="N100" s="3" t="str">
+      <c r="N100" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O100" s="3" t="str">
+      <c r="O100" s="7" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P100" s="3" t="str">
+      <c r="P100" s="7" t="str">
         <v>純 1 行 CSS 修法 (.section-about-member::before pointer-events: none)</v>
       </c>
     </row>
     <row r="101" ht="100.8" customHeight="1">
-      <c r="A101" s="3">
+      <c r="A101" s="7">
         <v>99</v>
       </c>
-      <c r="B101" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C101" s="3" t="str">
+      <c r="B101" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C101" s="7" t="str">
         <v>共用元件</v>
       </c>
-      <c r="D101" s="3" t="str">
+      <c r="D101" s="7" t="str">
         <v>AppFooter</v>
       </c>
-      <c r="E101" s="3" t="str">
+      <c r="E101" s="7" t="str">
         <v>修復</v>
       </c>
-      <c r="F101" s="3" t="str">
+      <c r="F101" s="7" t="str">
         <v>視覺</v>
       </c>
-      <c r="G101" s="3" t="str">
+      <c r="G101" s="7" t="str">
         <v>低</v>
       </c>
-      <c r="H101" s="3" t="str">
+      <c r="H101" s="7" t="str">
         <v>Footer 聯絡資訊 label 文字重複 (新舊 CSS 共存 bug)</v>
       </c>
-      <c r="I101" s="3" t="str">
+      <c r="I101" s="7" t="str">
         <v>5dfbf91/cf47cfa 把 AppFooter.vue 改用顯式 &lt;span class="footer-info-label"&gt; 顯示 label，但舊的 _font.scss `.footer-info-items [name="tel"]::before { content: "聯絡電話" }` 等 4 條規則沒清掉，造成「聯絡電話 📞 聯絡電話 (02)2797-8383」這種重複顯示</v>
       </c>
-      <c r="J101" s="3" t="str">
+      <c r="J101" s="7" t="str">
         <v>移除 _font.scss 4 個 ::before content 規則 (tel/mail/address/datetime) 與通用 [name]::before 樣式</v>
       </c>
-      <c r="K101" s="3" t="str">
+      <c r="K101" s="7" t="str">
         <v>assets/style/_font.scss</v>
       </c>
-      <c r="L101" s="3" t="str">
+      <c r="L101" s="7" t="str">
         <v>iFare_Frontend/assets/style/_font.scss</v>
       </c>
-      <c r="M101" s="3" t="str">
+      <c r="M101" s="7" t="str">
         <v>回歸測試 OK；保留 [name="tel"] font-family/color 與 [name="datetime"] span:nth-child Roboto 樣式</v>
       </c>
-      <c r="N101" s="3" t="str">
+      <c r="N101" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O101" s="3" t="str">
+      <c r="O101" s="7" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P101" s="3" t="str">
+      <c r="P101" s="7" t="str">
         <v>5dfbf91 整理時的 leftover</v>
       </c>
     </row>
     <row r="102" ht="144" customHeight="1">
-      <c r="A102" s="3">
+      <c r="A102" s="7">
         <v>100</v>
       </c>
-      <c r="B102" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C102" s="3" t="str">
+      <c r="B102" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C102" s="7" t="str">
         <v>全站通用</v>
       </c>
-      <c r="D102" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E102" s="3" t="str">
+      <c r="D102" s="7" t="str">
+        <v/>
+      </c>
+      <c r="E102" s="7" t="str">
         <v>提升</v>
       </c>
-      <c r="F102" s="3" t="str">
+      <c r="F102" s="7" t="str">
         <v>互動</v>
       </c>
-      <c r="G102" s="3" t="str">
+      <c r="G102" s="7" t="str">
         <v>中</v>
       </c>
-      <c r="H102" s="3" t="str">
+      <c r="H102" s="7" t="str">
         <v>缺乏全站一致的 hover 靈動回饋</v>
       </c>
-      <c r="I102" s="3" t="str">
+      <c r="I102" s="7" t="str">
         <v>既有 hover 散落在 .relation-item / .article-item / .card-* 等個別元件，nav 連結、Footer 按鈕、btn-icon 等沒有統一浮起回饋；使用者「鼠標移到哪都該有靈動」需求未滿足</v>
       </c>
-      <c r="J102" s="3" t="str">
+      <c r="J102" s="7" t="str">
         <v>_main.scss 加 .hover-lift utility class (Apple spring 0.22s + translateY -2px) + 自動套用到 .app-header nav / .app-footer .btn / .app-footer a / .btn-social / .btn-icon。既有自訂 hover (about morph 卡、news 浮起卡) 不受影響</v>
       </c>
-      <c r="K102" s="3" t="str">
+      <c r="K102" s="7" t="str">
         <v>assets/style/_main.scss</v>
       </c>
-      <c r="L102" s="3" t="str">
+      <c r="L102" s="7" t="str">
         <v>iFare_Frontend/assets/style/_main.scss</v>
       </c>
-      <c r="M102" s="3" t="str">
+      <c r="M102" s="7" t="str">
         <v>cubic-bezier(0.32, 0.72, 0, 1) 與 about morph 卡同套 easing</v>
       </c>
-      <c r="N102" s="3" t="str">
+      <c r="N102" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O102" s="3" t="str">
+      <c r="O102" s="7" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P102" s="3" t="str">
+      <c r="P102" s="7" t="str">
         <v>對應 #62 (.btn-filter/.btn-tag hover) 不重疊 — Round 4 涵蓋的是 nav/footer 類；ifare 搜尋按鈕的 ripple 仍待補</v>
       </c>
     </row>
     <row r="103" ht="115.2" customHeight="1" xml:space="preserve">
-      <c r="A103" s="3">
+      <c r="A103" s="7">
         <v>101</v>
       </c>
-      <c r="B103" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C103" s="3" t="str">
+      <c r="B103" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C103" s="7" t="str">
         <v>共用元件</v>
       </c>
-      <c r="D103" s="3" t="str">
+      <c r="D103" s="7" t="str">
         <v>AppHeader</v>
       </c>
-      <c r="E103" s="3" t="str">
+      <c r="E103" s="7" t="str">
         <v>提升</v>
       </c>
-      <c r="F103" s="3" t="str">
+      <c r="F103" s="7" t="str">
         <v>內容</v>
       </c>
-      <c r="G103" s="3" t="str">
+      <c r="G103" s="7" t="str">
         <v>中</v>
       </c>
-      <c r="H103" s="3" t="str">
+      <c r="H103" s="7" t="str">
         <v>缺少「未來規劃」頁面入口</v>
       </c>
-      <c r="I103" s="3" t="str">
+      <c r="I103" s="7" t="str">
         <v>主管要求增加「未來規劃」展示基金會願景，nav 應有對應入口</v>
       </c>
-      <c r="J103" s="3" t="str">
+      <c r="J103" s="7" t="str">
         <v>AppHeader 桌面 nav 在 公益夥伴 與 i-Fare 之間插入「未來規劃」連結；行動 nav 加在最後 (與既有 i-Fare/公益夥伴 mobile 順序一致)；新增 pages/future.vue 標題 + FUTURE shadow + 「內容建置中，敬請期待」佔位</v>
       </c>
-      <c r="K103" s="3" t="str">
+      <c r="K103" s="7" t="str">
         <v>components/AppHeader.vue + pages/future.vue (新)</v>
       </c>
-      <c r="L103" s="3" t="str" xml:space="preserve">
+      <c r="L103" s="7" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/components/AppHeader.vue_x000d__x000d__x000d_
 iFare_Frontend/pages/future.vue (新)</v>
       </c>
-      <c r="M103" s="3" t="str">
+      <c r="M103" s="7" t="str">
         <v>route /future 已 wire；之後接 CMS 內容由 admin 管理</v>
       </c>
-      <c r="N103" s="3" t="str">
+      <c r="N103" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O103" s="3" t="str">
+      <c r="O103" s="7" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P103" s="3" t="str">
+      <c r="P103" s="7" t="str">
         <v>頁面為佔位，等內容/設計稿確認後再填內</v>
       </c>
     </row>
     <row r="104" ht="144" customHeight="1" xml:space="preserve">
-      <c r="A104" s="3">
+      <c r="A104" s="5">
         <v>102</v>
       </c>
-      <c r="B104" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C104" s="3" t="str">
+      <c r="B104" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C104" s="5" t="str">
         <v>最新消息</v>
       </c>
-      <c r="D104" s="3" t="str">
+      <c r="D104" s="5" t="str">
         <v>文章詳情</v>
       </c>
-      <c r="E104" s="3" t="str">
+      <c r="E104" s="5" t="str">
         <v>提升</v>
       </c>
-      <c r="F104" s="3" t="str">
+      <c r="F104" s="5" t="str">
         <v>內容</v>
       </c>
-      <c r="G104" s="3" t="str">
+      <c r="G104" s="5" t="str">
         <v>中</v>
       </c>
-      <c r="H104" s="3" t="str">
+      <c r="H104" s="5" t="str">
         <v>News 詳情頁缺乏多媒體展示能力</v>
       </c>
-      <c r="I104" s="3" t="str">
+      <c r="I104" s="5" t="str">
         <v>主管希望最新消息可內嵌 YouTube 影片，目前只有 HTML 編輯器內可手動貼連結，無內嵌影片渲染</v>
       </c>
-      <c r="J104" s="3" t="str">
+      <c r="J104" s="5" t="str">
         <v>後台 admin 加「影片網址」el-input + WebAPI.ts InsertNews/UpdateNews 加 videoUrl 參數；前台 news/info.vue 加 iframe section + YouTube URL → embed URL parser (regex 抓 11 字元 video ID) + 16:9 響應式容器 (padding-top: 56.25%)</v>
       </c>
-      <c r="K104" s="3" t="str">
+      <c r="K104" s="5" t="str">
         <v>pages/news/info.vue + News_AddEditView.vue (admin) + WebAPI.ts (admin)</v>
       </c>
-      <c r="L104" s="3" t="str" xml:space="preserve">
+      <c r="L104" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/pages/news/info.vue_x000d__x000d__x000d_
 iFare_Backend/src/views/News/News_AddEditView.vue_x000d__x000d__x000d_
 iFare_Backend/src/plugins/WebAPI.ts</v>
       </c>
-      <c r="M104" s="3" t="str">
+      <c r="M104" s="5" t="str">
         <v>UI 端 wiring 完成；對應後臺優化 #13 (.NET News VideoUrl 欄位)</v>
       </c>
-      <c r="N104" s="3" t="str">
+      <c r="N104" s="5" t="str">
         <v>部分修正</v>
       </c>
-      <c r="O104" s="3" t="str">
+      <c r="O104" s="5" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P104" s="3" t="str">
+      <c r="P104" s="5" t="str">
         <v>等 .NET 後端 News.cs entity + DTO + EF migration 加 VideoUrl 才能真實運作</v>
       </c>
     </row>
     <row r="105" ht="115.2" customHeight="1" xml:space="preserve">
-      <c r="A105" s="3">
+      <c r="A105" s="7">
         <v>103</v>
       </c>
-      <c r="B105" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C105" s="3" t="str">
+      <c r="B105" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C105" s="7" t="str">
         <v>全站通用</v>
       </c>
-      <c r="D105" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E105" s="3" t="str">
+      <c r="D105" s="7" t="str">
+        <v/>
+      </c>
+      <c r="E105" s="7" t="str">
         <v>修復</v>
       </c>
-      <c r="F105" s="3" t="str">
+      <c r="F105" s="7" t="str">
         <v>程式碼</v>
       </c>
-      <c r="G105" s="3" t="str">
+      <c r="G105" s="7" t="str">
         <v>高</v>
       </c>
-      <c r="H105" s="3" t="str">
+      <c r="H105" s="7" t="str">
         <v>本機開發 API 連線失敗 (環境設定指本機 .NET，但機器沒 .NET SDK)</v>
       </c>
-      <c r="I105" s="3" t="str">
+      <c r="I105" s="7" t="str">
         <v>前台 nuxt.config.ts devProxy target 寫死 https://localhost:44312 / 後台 AjaxRef.ts baseURL prod 寫死 http://10.200.0.39 (公司內網 IP)，導致：(1) 本機 dev 抓 dropdown 全 404 (2) 後台 admin Login 失敗 (家用網路 reach 不到 10.200.0.39 內網 IP)</v>
       </c>
-      <c r="J105" s="3" t="str">
+      <c r="J105" s="7" t="str">
         <v>前台 nuxt.config.ts devProxy target 改 https://www.i-fare.org.tw/ifare_api/api/services/app；後台 AjaxRef.getBaseUrl() 改 https://www.i-fare.org.tw/ifare_bdapi (固定走正式)</v>
       </c>
-      <c r="K105" s="3" t="str">
+      <c r="K105" s="7" t="str">
         <v>nuxt.config.ts (前台) + AjaxRef.ts (後台)</v>
       </c>
-      <c r="L105" s="3" t="str" xml:space="preserve">
+      <c r="L105" s="7" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/nuxt.config.ts_x000d__x000d__x000d_
 iFare_Backend/src/plugins/AjaxRef.ts</v>
       </c>
-      <c r="M105" s="3" t="str">
+      <c r="M105" s="7" t="str">
         <v>Login 已驗證可通；前台 dropdown 已能抓資料</v>
       </c>
-      <c r="N105" s="3" t="str">
+      <c r="N105" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O105" s="3" t="str">
+      <c r="O105" s="7" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P105" s="3" t="str">
+      <c r="P105" s="7" t="str">
         <v>對應後臺優化 #8 / #14 (baseURL 環境變數化) — 目前是治標處理，等之後完整改成 .env</v>
       </c>
     </row>
     <row r="106" ht="172.80000000000004" customHeight="1" xml:space="preserve">
-      <c r="A106" s="3">
+      <c r="A106" s="7">
         <v>104</v>
       </c>
-      <c r="B106" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C106" s="3" t="str">
+      <c r="B106" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C106" s="7" t="str">
         <v>全站通用</v>
       </c>
-      <c r="D106" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E106" s="3" t="str">
+      <c r="D106" s="7" t="str">
+        <v/>
+      </c>
+      <c r="E106" s="7" t="str">
         <v>修復</v>
       </c>
-      <c r="F106" s="3" t="str">
+      <c r="F106" s="7" t="str">
         <v>程式碼</v>
       </c>
-      <c r="G106" s="3" t="str">
+      <c r="G106" s="7" t="str">
         <v>低</v>
       </c>
-      <c r="H106" s="3" t="str">
+      <c r="H106" s="7" t="str">
         <v>VS Code 顯示 3 個 TypeScript deprecation warning</v>
       </c>
-      <c r="I106" s="3" t="str">
+      <c r="I106" s="7" t="str">
         <v>iFare_Backend/tsconfig.app.json 用 baseUrl + moduleResolution=node10 / iFare_Frontend/tsconfig.json 透過 .nuxt/tsconfig.json extend 也帶 node10，被 TypeScript 5.x 標 deprecated (TS 7.0 才停用)</v>
       </c>
-      <c r="J106" s="3" t="str">
+      <c r="J106" s="7" t="str">
         <v>加 "ignoreDeprecations": "6.0" — 後台直接放 tsconfig.app.json compilerOptions；前台改透過 nuxt.config.ts typescript.tsConfig.compilerOptions 注入 .nuxt/tsconfig.json (因為 user-facing tsconfig.json 加 ignoreDeprecations 抑制不到 extend 的 .nuxt/tsconfig.json)</v>
       </c>
-      <c r="K106" s="3" t="str">
+      <c r="K106" s="7" t="str">
         <v>tsconfig.app.json + tsconfig.json + nuxt.config.ts</v>
       </c>
-      <c r="L106" s="3" t="str" xml:space="preserve">
+      <c r="L106" s="7" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Backend/tsconfig.app.json_x000d__x000d__x000d_
 iFare_Frontend/tsconfig.json_x000d__x000d__x000d_
 iFare_Frontend/nuxt.config.ts</v>
       </c>
-      <c r="M106" s="3" t="str">
+      <c r="M106" s="7" t="str">
         <v>TS 5.x 不影響執行 / build</v>
       </c>
-      <c r="N106" s="3" t="str">
+      <c r="N106" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O106" s="3" t="str">
+      <c r="O106" s="7" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P106" s="3" t="str">
+      <c r="P106" s="7" t="str">
         <v>純 IDE 觀感修補；VS Code 需 Ctrl+Shift+P → Restart TS Server 才會 reload</v>
       </c>
     </row>
     <row r="107" ht="115.2" customHeight="1" xml:space="preserve">
-      <c r="A107" s="3">
+      <c r="A107" s="7">
         <v>105</v>
       </c>
-      <c r="B107" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C107" s="3" t="str">
+      <c r="B107" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C107" s="7" t="str">
         <v>全站通用</v>
       </c>
-      <c r="D107" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E107" s="3" t="str">
+      <c r="D107" s="7" t="str">
+        <v/>
+      </c>
+      <c r="E107" s="7" t="str">
         <v>修復</v>
       </c>
-      <c r="F107" s="3" t="str">
+      <c r="F107" s="7" t="str">
         <v>程式碼</v>
       </c>
-      <c r="G107" s="3" t="str">
+      <c r="G107" s="7" t="str">
         <v>高</v>
       </c>
-      <c r="H107" s="3" t="str">
+      <c r="H107" s="7" t="str">
         <v>主管手動合併 master 時漏合 5dfbf91/cf47cfa 部分改動</v>
       </c>
-      <c r="I107" s="3" t="str">
+      <c r="I107" s="7" t="str">
         <v>切到 master 開 feat/uiux-round4 新分支後抽樣驗證發現：5dfbf91 漏合的 footer 樣式 (LINE 綠/FB 藍 SVG icon、_appFooter.scss 重新設計、_animation.scss page transition、_rwd_appFooter.scss、Mail/Clock SVG)；cf47cfa 整個沒合 (About 靈動島 + News 卡片升級 + 社群外連結) — 9 個檔</v>
       </c>
-      <c r="J107" s="3" t="str">
+      <c r="J107" s="7" t="str">
         <v>從 frontend 分支 git show 補回 16 個檔到新分支對應路徑 (Dev/Dev Code/iFare_Frontend/...)；cf47cfa 9 檔以 d5a7674 commit；footer 7 檔以 e2b1cae commit</v>
       </c>
-      <c r="K107" s="3" t="str">
+      <c r="K107" s="7" t="str">
         <v>16 個 SCSS / Vue / SVG</v>
       </c>
-      <c r="L107" s="3" t="str" xml:space="preserve">
+      <c r="L107" s="7" t="str" xml:space="preserve">
         <v xml:space="preserve">Dev/Dev Code/iFare_Frontend/assets/style/components/_appFooter.scss_x000d__x000d__x000d_
 iFare_Frontend/assets/style/_animation.scss_x000d__x000d__x000d_
 iFare_Frontend/components/AppFooter.vue 等 16 檔</v>
       </c>
-      <c r="M107" s="3" t="str">
+      <c r="M107" s="7" t="str">
         <v>修補 release 環境必要</v>
       </c>
-      <c r="N107" s="3" t="str">
+      <c r="N107" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O107" s="3" t="str">
+      <c r="O107" s="7" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P107" s="3" t="str">
+      <c r="P107" s="7" t="str">
         <v>不是純 UI/UX 議題，但屬於 Round 1-3 work 真正落地的前提</v>
       </c>
     </row>
     <row r="108" ht="14.4" customHeight="1" xml:space="preserve">
-      <c r="A108" s="3">
+      <c r="A108" s="7">
         <v>106</v>
       </c>
-      <c r="B108" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C108" s="3" t="str">
+      <c r="B108" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C108" s="7" t="str">
         <v>安全性</v>
       </c>
-      <c r="D108" s="3" t="str">
+      <c r="D108" s="7" t="str">
         <v>v-html XSS</v>
       </c>
-      <c r="E108" s="3" t="str">
+      <c r="E108" s="7" t="str">
         <v>修復</v>
       </c>
-      <c r="F108" s="3" t="str">
+      <c r="F108" s="7" t="str">
         <v>程式碼</v>
       </c>
-      <c r="G108" s="3" t="str">
+      <c r="G108" s="7" t="str">
         <v>高</v>
       </c>
-      <c r="H108" s="3" t="str">
+      <c r="H108" s="7" t="str">
         <v>v-html 渲染未清理的服務器內容，存在 XSS 風險</v>
       </c>
-      <c r="I108" s="3" t="str">
+      <c r="I108" s="7" t="str">
         <v>news/info, articles/lazy, articles/welfare, ifare/info 多頁用 v-html 渲染 API content；若後端未正確清理 HTML/JavaScript，可遭 XSS</v>
       </c>
-      <c r="J108" s="3" t="str">
+      <c r="J108" s="7" t="str">
         <v>用 DOMPurify 或 sanitize-html 清理 HTML；至少在伺服器端驗證內容不含危險標籤</v>
       </c>
-      <c r="K108" s="3" t="str">
+      <c r="K108" s="7" t="str">
         <v>pages/news/info.vue + articles/lazy/welfare + ifare/info</v>
       </c>
-      <c r="L108" s="3" t="str" xml:space="preserve">
+      <c r="L108" s="7" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/pages/news/info.vue (L25)_x000d__x000d_
 iFare_Frontend/pages/articles/lazy.vue (L16)_x000d__x000d_
 iFare_Frontend/pages/articles/welfare.vue (L19)_x000d__x000d_
 iFare_Frontend/pages/ifare/info.vue (L23, 31, 40, 47)</v>
       </c>
-      <c r="M108" s="3" t="str">
+      <c r="M108" s="7" t="str">
         <v>高優先級安全缺陷</v>
       </c>
-      <c r="N108" s="3" t="str">
+      <c r="N108" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O108" s="3" t="str">
+      <c r="O108" s="7" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P108" s="3" t="str">
+      <c r="P108" s="7" t="str">
         <v>Round 9 (批次 B): 安裝 isomorphic-dompurify (SSR + client safe)；新增 composables/useSanitize.ts 統一清理規範 (white-list ALLOWED_TAGS / ALLOWED_ATTR、阻 javascript:/data: URI、FORBID script/style/iframe/onerror)；7 處 v-html 用 useSanitize 包起來: news/info、articles/lazy、articles/welfare、ifare/info × 4 (qualification/welfareInfo/evidence/remark)。</v>
       </c>
     </row>
     <row r="109" ht="14.4" customHeight="1" xml:space="preserve">
-      <c r="A109" s="3">
+      <c r="A109" s="5">
         <v>107</v>
       </c>
-      <c r="B109" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C109" s="3" t="str">
+      <c r="B109" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C109" s="5" t="str">
         <v>全站通用</v>
       </c>
-      <c r="D109" s="3" t="str">
+      <c r="D109" s="5" t="str">
         <v>WebAPI 錯誤處理</v>
       </c>
-      <c r="E109" s="3" t="str">
+      <c r="E109" s="5" t="str">
         <v>修復</v>
       </c>
-      <c r="F109" s="3" t="str">
+      <c r="F109" s="5" t="str">
         <v>程式碼</v>
       </c>
-      <c r="G109" s="3" t="str">
+      <c r="G109" s="5" t="str">
         <v>高</v>
       </c>
-      <c r="H109" s="3" t="str">
+      <c r="H109" s="5" t="str">
         <v>WebAPI.ts 未區分錯誤類型，一律 return null，頁面無法判斷失敗原因</v>
       </c>
-      <c r="I109" s="3" t="str">
+      <c r="I109" s="5" t="str">
         <v>plugins/WebAPI.ts (L9-15) 捕獲所有錯誤返回 null，無法區分網路超時/伺服器 500/驗證失敗；news.vue 等雖有 hasError 但無法提示具體原因</v>
       </c>
-      <c r="J109" s="3" t="str">
+      <c r="J109" s="5" t="str">
         <v>返回結構化錯誤物件 {code, message, status}，頁面根據錯誤類型顯示不同提示 (網路錯誤、伺服器維護中等)</v>
       </c>
-      <c r="K109" s="3" t="str">
+      <c r="K109" s="5" t="str">
         <v>plugins/WebAPI.ts</v>
       </c>
-      <c r="L109" s="3" t="str" xml:space="preserve">
+      <c r="L109" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/plugins/WebAPI.ts_x000d__x000d_
 iFare_Frontend/pages/news.vue_x000d__x000d_
 iFare_Frontend/pages/articles.vue_x000d__x000d_
 iFare_Frontend/pages/ifare.vue</v>
       </c>
-      <c r="M109" s="3" t="str">
+      <c r="M109" s="5" t="str">
         <v>影響全站用戶體驗</v>
       </c>
-      <c r="N109" s="3" t="str">
+      <c r="N109" s="5" t="str">
         <v>部分修正</v>
       </c>
-      <c r="O109" s="3" t="str">
+      <c r="O109" s="5" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P109" s="3" t="str">
+      <c r="P109" s="5" t="str">
         <v>Round 9 (批次 B): plugins/WebAPI.ts 加 categorizeError (timeout/network/client/server/unknown)、結構化 logError 取代 console.error、try-catch wrapper。Return signature 不變 (data/null) 維持向下相容，所有 caller 不用改。**UI 端錯誤呈現** (顯示 toast / 重試提示) 尚未做，需與整體錯誤元件設計一起。</v>
       </c>
     </row>
     <row r="110" ht="14.4" customHeight="1" xml:space="preserve">
-      <c r="A110" s="3">
+      <c r="A110" s="7">
         <v>108</v>
       </c>
-      <c r="B110" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C110" s="3" t="str">
+      <c r="B110" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C110" s="7" t="str">
         <v>全站通用</v>
       </c>
-      <c r="D110" s="3" t="str">
+      <c r="D110" s="7" t="str">
         <v>API 超時</v>
       </c>
-      <c r="E110" s="3" t="str">
+      <c r="E110" s="7" t="str">
         <v>修復</v>
       </c>
-      <c r="F110" s="3" t="str">
+      <c r="F110" s="7" t="str">
         <v>效能</v>
       </c>
-      <c r="G110" s="3" t="str">
+      <c r="G110" s="7" t="str">
         <v>高</v>
       </c>
-      <c r="H110" s="3" t="str">
+      <c r="H110" s="7" t="str">
         <v>$fetch 無超時設定，API 無回應頁面會無限期卡 loading</v>
       </c>
-      <c r="I110" s="3" t="str">
+      <c r="I110" s="7" t="str">
         <v>所有頁面的 API 呼叫未設 timeout，若 API 無回應，UI 會永遠停在 loading 無退出機制</v>
       </c>
-      <c r="J110" s="3" t="str">
+      <c r="J110" s="7" t="str">
         <v>WebAPI.ts 設預設 timeout 10-15 秒，超時返回特定錯誤碼讓頁面顯示「連線逾時，請重試」</v>
       </c>
-      <c r="K110" s="3" t="str">
+      <c r="K110" s="7" t="str">
         <v>plugins/WebAPI.ts</v>
       </c>
-      <c r="L110" s="3" t="str" xml:space="preserve">
+      <c r="L110" s="7" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/plugins/WebAPI.ts_x000d__x000d_
 iFare_Frontend/pages/news/info.vue_x000d__x000d_
 iFare_Frontend/pages/articles/lazy.vue_x000d__x000d_
 iFare_Frontend/pages/articles/welfare.vue_x000d__x000d_
 iFare_Frontend/pages/ifare/contact.vue</v>
       </c>
-      <c r="M110" s="3" t="str">
+      <c r="M110" s="7" t="str">
         <v>可能導致用戶感知應用無反應</v>
       </c>
-      <c r="N110" s="3" t="str">
+      <c r="N110" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O110" s="3" t="str">
+      <c r="O110" s="7" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P110" s="3" t="str">
+      <c r="P110" s="7" t="str">
         <v>Round 9 (批次 B): plugins/WebAPI.ts WebApiGet/WebApiPost $fetch 加 timeout: API_TIMEOUT_MS (15000ms)。逾時會被 categorizeError 標記為 timeout 類別。</v>
       </c>
     </row>
     <row r="111" ht="14.4" customHeight="1">
-      <c r="A111" s="3">
+      <c r="A111" s="7">
         <v>109</v>
       </c>
-      <c r="B111" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C111" s="3" t="str">
+      <c r="B111" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C111" s="7" t="str">
         <v>i-Fare 福利查詢</v>
       </c>
-      <c r="D111" s="3" t="str">
+      <c r="D111" s="7" t="str">
         <v>ifare/contact</v>
       </c>
-      <c r="E111" s="3" t="str">
+      <c r="E111" s="7" t="str">
         <v>修復</v>
       </c>
-      <c r="F111" s="3" t="str">
+      <c r="F111" s="7" t="str">
         <v>互動</v>
       </c>
-      <c r="G111" s="3" t="str">
+      <c r="G111" s="7" t="str">
         <v>高</v>
       </c>
-      <c r="H111" s="3" t="str">
+      <c r="H111" s="7" t="str">
         <v>contact.vue 缺 API 失敗處理，API 失敗用戶看不到內容</v>
       </c>
-      <c r="I111" s="3" t="str">
+      <c r="I111" s="7" t="str">
         <v>ifare/contact.vue (L153) 呼叫 GetIFareOfficeUnitList 但無檢查 res.result、無 catch 區塊、無 loading/error 狀態。若 API 失敗頁面呈現空白</v>
       </c>
-      <c r="J111" s="3" t="str">
+      <c r="J111" s="7" t="str">
         <v>加 try-catch、loading ref、error 狀態，仿 news.vue 的錯誤處理模式</v>
       </c>
-      <c r="K111" s="3" t="str">
+      <c r="K111" s="7" t="str">
         <v>pages/ifare/contact.vue</v>
       </c>
-      <c r="L111" s="3" t="str">
+      <c r="L111" s="7" t="str">
         <v>iFare_Frontend/pages/ifare/contact.vue</v>
       </c>
-      <c r="M111" s="3" t="str">
+      <c r="M111" s="7" t="str">
         <v>用戶無法看到聯絡資訊時毫無提示</v>
       </c>
-      <c r="N111" s="3" t="str">
+      <c r="N111" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O111" s="3" t="str">
+      <c r="O111" s="7" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P111" s="3" t="str">
+      <c r="P111" s="7" t="str">
         <v>Round 9 (批次 B): pages/ifare/contact.vue 重構為 loadOfficeUnit() async + isLoading/hasError ref。template 加 v-if 三分支: loading (skeleton-line role=status)、error (重試按鈕 role=alert)、success (原內容)。重試會清空既有資料再呼叫。</v>
       </c>
     </row>
     <row r="112" ht="14.4" customHeight="1" xml:space="preserve">
-      <c r="A112" s="3">
+      <c r="A112" s="7">
         <v>110</v>
       </c>
-      <c r="B112" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C112" s="3" t="str">
+      <c r="B112" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C112" s="7" t="str">
         <v>全站通用</v>
       </c>
-      <c r="D112" s="3" t="str">
+      <c r="D112" s="7" t="str">
         <v>console.log</v>
       </c>
-      <c r="E112" s="3" t="str">
+      <c r="E112" s="7" t="str">
         <v>修復</v>
       </c>
-      <c r="F112" s="3" t="str">
+      <c r="F112" s="7" t="str">
         <v>程式碼</v>
       </c>
-      <c r="G112" s="3" t="str">
+      <c r="G112" s="7" t="str">
         <v>高</v>
       </c>
-      <c r="H112" s="3" t="str">
+      <c r="H112" s="7" t="str">
         <v>生產環境仍有 20+ 個 console.log，洩露內部邏輯</v>
       </c>
-      <c r="I112" s="3" t="str">
+      <c r="I112" s="7" t="str">
         <v>news.vue (L198), ifare.vue (L305), ifare/result.vue (L236-265, 385, 541), ifare/contact.vue (L163, 193) 等多處 console.log，可被用戶開發工具看到</v>
       </c>
-      <c r="J112" s="3" t="str">
+      <c r="J112" s="7" t="str">
         <v>移除所有生產 console.log，改用生產環境禁用的日誌系統，或開發時用環境變數判斷</v>
       </c>
-      <c r="K112" s="3" t="str">
+      <c r="K112" s="7" t="str">
         <v>多 pages</v>
       </c>
-      <c r="L112" s="3" t="str" xml:space="preserve">
+      <c r="L112" s="7" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/pages/news.vue_x000d__x000d_
 iFare_Frontend/pages/ifare.vue_x000d__x000d_
 iFare_Frontend/pages/ifare/result.vue_x000d__x000d_
@@ -9617,16 +9665,16 @@
 iFare_Frontend/components/CompPage.vue_x000d__x000d_
 iFare_Frontend/components/CompPageNum.vue</v>
       </c>
-      <c r="M112" s="3" t="str">
+      <c r="M112" s="7" t="str">
         <v>安全與代碼質量問題</v>
       </c>
-      <c r="N112" s="3" t="str">
+      <c r="N112" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O112" s="3" t="str">
+      <c r="O112" s="7" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P112" s="3" t="str">
+      <c r="P112" s="7" t="str">
         <v>Round 7 (批次 A): 移除 13 處 console.log — pages/news.vue (1)、pages/ifare.vue (1)、pages/ifare/result.vue (5)、pages/ifare/contact.vue (2)、components/CompPage.vue (4)。保留 pages/ifare/info.vue:203 的 console.error (catch 內合理錯誤處理)。</v>
       </c>
     </row>
@@ -9682,54 +9730,54 @@
       </c>
     </row>
     <row r="114" ht="14.4" customHeight="1" xml:space="preserve">
-      <c r="A114" s="3">
+      <c r="A114" s="7">
         <v>112</v>
       </c>
-      <c r="B114" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C114" s="3" t="str">
+      <c r="B114" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C114" s="7" t="str">
         <v>無障礙</v>
       </c>
-      <c r="D114" s="3" t="str">
+      <c r="D114" s="7" t="str">
         <v>圖片 alt</v>
       </c>
-      <c r="E114" s="3" t="str">
+      <c r="E114" s="7" t="str">
         <v>修復</v>
       </c>
-      <c r="F114" s="3" t="str">
+      <c r="F114" s="7" t="str">
         <v>無障礙</v>
       </c>
-      <c r="G114" s="3" t="str">
+      <c r="G114" s="7" t="str">
         <v>中</v>
       </c>
-      <c r="H114" s="3" t="str">
+      <c r="H114" s="7" t="str">
         <v>多頁圖片 alt 屬性缺失 (collaborator, articles/lazy, index 背景)</v>
       </c>
-      <c r="I114" s="3" t="str">
+      <c r="I114" s="7" t="str">
         <v>collaborator.vue (L22) &lt;img&gt; 無 alt；articles/lazy.vue (L77) 自動生成 &lt;img&gt; 無 alt；index 背景 CSS 無 alt</v>
       </c>
-      <c r="J114" s="3" t="str">
+      <c r="J114" s="7" t="str">
         <v>所有 img 加 alt (collaborator 用機構名稱，articles/lazy 用文章標題)；背景圖改 img 或加 aria-label</v>
       </c>
-      <c r="K114" s="3" t="str">
+      <c r="K114" s="7" t="str">
         <v>collaborator / articles/lazy / index</v>
       </c>
-      <c r="L114" s="3" t="str" xml:space="preserve">
+      <c r="L114" s="7" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/pages/collaborator.vue_x000d__x000d_
 iFare_Frontend/pages/articles/lazy.vue_x000d__x000d_
 iFare_Frontend/pages/index.vue</v>
       </c>
-      <c r="M114" s="3" t="str">
+      <c r="M114" s="7" t="str">
         <v>WCAG 2.1 AA 必要，影響視障用戶</v>
       </c>
-      <c r="N114" s="3" t="str">
+      <c r="N114" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O114" s="3" t="str">
+      <c r="O114" s="7" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P114" s="3" t="str">
+      <c r="P114" s="7" t="str">
         <v>Round 8 (批次 C): pages/index.vue 的 .part-bg-top 加 aria-hidden="true" — 5 張裝飾性 .bg-img 不需被屏幕閱讀器讀。collaborator.vue + articles/lazy.vue 的 &lt;img&gt; alt 已在 Round 7 (#127) 順手做。</v>
       </c>
     </row>
@@ -9785,108 +9833,108 @@
       </c>
     </row>
     <row r="116" ht="14.4" customHeight="1" xml:space="preserve">
-      <c r="A116" s="3">
+      <c r="A116" s="7">
         <v>114</v>
       </c>
-      <c r="B116" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C116" s="3" t="str">
+      <c r="B116" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C116" s="7" t="str">
         <v>共用元件</v>
       </c>
-      <c r="D116" s="3" t="str">
+      <c r="D116" s="7" t="str">
         <v>CompSelect 鍵盤</v>
       </c>
-      <c r="E116" s="3" t="str">
+      <c r="E116" s="7" t="str">
         <v>修復</v>
       </c>
-      <c r="F116" s="3" t="str">
+      <c r="F116" s="7" t="str">
         <v>無障礙</v>
       </c>
-      <c r="G116" s="3" t="str">
+      <c r="G116" s="7" t="str">
         <v>中</v>
       </c>
-      <c r="H116" s="3" t="str">
+      <c r="H116" s="7" t="str">
         <v>CompSelect 系列元件無鍵盤操作 (Tab/Enter/Esc/Arrow)，僅滑鼠</v>
       </c>
-      <c r="I116" s="3" t="str">
+      <c r="I116" s="7" t="str">
         <v>CompSelect / CompSelectRecipient / CompSelectElse 的開關、選項點擊均未綁定鍵盤事件，無法用鍵盤導航選擇</v>
       </c>
-      <c r="J116" s="3" t="str">
+      <c r="J116" s="7" t="str">
         <v>加 @keydown.tab/enter/esc/arrow-down/up 事件，實現 ARIA authoring practices 完整鍵盤導航</v>
       </c>
-      <c r="K116" s="3" t="str">
+      <c r="K116" s="7" t="str">
         <v>components/CompSelect*</v>
       </c>
-      <c r="L116" s="3" t="str" xml:space="preserve">
+      <c r="L116" s="7" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/components/CompSelect.vue_x000d__x000d_
 iFare_Frontend/components/CompSelectRecipient.vue_x000d__x000d_
 iFare_Frontend/components/CompSelectElse.vue</v>
       </c>
-      <c r="M116" s="3" t="str">
+      <c r="M116" s="7" t="str">
         <v>WCAG 2.1 AA 必要</v>
       </c>
-      <c r="N116" s="3" t="str">
+      <c r="N116" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O116" s="3" t="str">
+      <c r="O116" s="7" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P116" s="3" t="str">
+      <c r="P116" s="7" t="str">
         <v>Round 8 (批次 C): 3 個 component (CompSelect / CompSelectRecipient / CompSelectElse) 加 tabindex="0" + role="combobox" + aria-expanded + aria-haspopup + aria-label。CompSelect / CompSelectRecipient 加完整鍵盤導航 (Enter/Space toggle 或選擇 focused 項目；Esc 關閉；Arrow Up/Down 切換 focused 項目)；CompSelectElse 因含兩組選項 (Income + Identity) 結構複雜，僅加 Enter/Space toggle + Esc 關閉，方向鍵需後續再處理。選項加 role="option" + aria-selected。</v>
       </c>
     </row>
     <row r="117" ht="14.4" customHeight="1" xml:space="preserve">
-      <c r="A117" s="3">
+      <c r="A117" s="7">
         <v>115</v>
       </c>
-      <c r="B117" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C117" s="3" t="str">
+      <c r="B117" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C117" s="7" t="str">
         <v>無障礙</v>
       </c>
-      <c r="D117" s="3" t="str">
+      <c r="D117" s="7" t="str">
         <v>Heading 層級</v>
       </c>
-      <c r="E117" s="3" t="str">
+      <c r="E117" s="7" t="str">
         <v>修復</v>
       </c>
-      <c r="F117" s="3" t="str">
+      <c r="F117" s="7" t="str">
         <v>無障礙</v>
       </c>
-      <c r="G117" s="3" t="str">
+      <c r="G117" s="7" t="str">
         <v>中</v>
       </c>
-      <c r="H117" s="3" t="str">
+      <c r="H117" s="7" t="str">
         <v>Heading 層級結構不規範，多頁 h3 直接跟 h1 後，h6 用於非末級</v>
       </c>
-      <c r="I117" s="3" t="str">
+      <c r="I117" s="7" t="str">
         <v>about.vue (L11 h3 缺 h2)、index.vue (L21 h1 + L38 h3)、news/info.vue (L4 h2 後直接 h6)、ifare/info.vue (L5 h1 + L21 h3) 不遵循層級規則</v>
       </c>
-      <c r="J117" s="3" t="str">
+      <c r="J117" s="7" t="str">
         <v>調整 heading 層級遞增 (h1 &gt; h2 &gt; h3...)；不跳級；副標題用適當 h2-h3 而非 h6</v>
       </c>
-      <c r="K117" s="3" t="str">
+      <c r="K117" s="7" t="str">
         <v>about / index / news/info / ifare/info / collaborator</v>
       </c>
-      <c r="L117" s="3" t="str" xml:space="preserve">
+      <c r="L117" s="7" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/pages/about.vue_x000d__x000d_
 iFare_Frontend/pages/index.vue_x000d__x000d_
 iFare_Frontend/pages/news/info.vue_x000d__x000d_
 iFare_Frontend/pages/ifare/info.vue_x000d__x000d_
 iFare_Frontend/pages/collaborator.vue</v>
       </c>
-      <c r="M117" s="3" t="str">
+      <c r="M117" s="7" t="str">
         <v>影響屏幕閱讀器用戶導航</v>
       </c>
-      <c r="N117" s="3" t="str">
+      <c r="N117" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O117" s="3" t="str">
+      <c r="O117" s="7" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P117" s="3" t="str">
+      <c r="P117" s="7" t="str">
         <v>Round 8 (批次 C): 已 grep 確認 SCSS 全用 class selector (.comp-title / .member-name / .news-title 等)，改 tag 不破壞視覺。修正：about.vue (h3 → h1 主標 / h6 → h4 member-name × 3)；index.vue (h3 → p sub-title / h2 → h4 news-title / h2 → h4 card-title)；news/info.vue (h6 → p article-date)；ifare/info.vue (h3 → h2 × 5 區塊標 / h5 → h2 relation-title / h6 → h3 link-title)。</v>
       </c>
     </row>
@@ -9995,52 +10043,52 @@
       </c>
     </row>
     <row r="120" ht="14.4" customHeight="1">
-      <c r="A120" s="3">
+      <c r="A120" s="7">
         <v>118</v>
       </c>
-      <c r="B120" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C120" s="3" t="str">
+      <c r="B120" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C120" s="7" t="str">
         <v>最新消息</v>
       </c>
-      <c r="D120" s="3" t="str">
+      <c r="D120" s="7" t="str">
         <v>iframe 安全</v>
       </c>
-      <c r="E120" s="3" t="str">
+      <c r="E120" s="7" t="str">
         <v>修復</v>
       </c>
-      <c r="F120" s="3" t="str">
+      <c r="F120" s="7" t="str">
         <v>程式碼</v>
       </c>
-      <c r="G120" s="3" t="str">
+      <c r="G120" s="7" t="str">
         <v>中</v>
       </c>
-      <c r="H120" s="3" t="str">
+      <c r="H120" s="7" t="str">
         <v>YouTube iframe 缺 sandbox 屬性，allow 過寬鬆</v>
       </c>
-      <c r="I120" s="3" t="str">
+      <c r="I120" s="7" t="str">
         <v>news/info.vue (L12-19) iframe allow 含 accelerometer/autoplay/clipboard-write 等未設 sandbox，可能被跨域腳本利用</v>
       </c>
-      <c r="J120" s="3" t="str">
+      <c r="J120" s="7" t="str">
         <v>加 sandbox="allow-same-origin allow-scripts allow-presentation"；移除非必要 allow (例如 clipboard-write)</v>
       </c>
-      <c r="K120" s="3" t="str">
+      <c r="K120" s="7" t="str">
         <v>pages/news/info.vue</v>
       </c>
-      <c r="L120" s="3" t="str">
+      <c r="L120" s="7" t="str">
         <v>iFare_Frontend/pages/news/info.vue</v>
       </c>
-      <c r="M120" s="3" t="str">
+      <c r="M120" s="7" t="str">
         <v>防止潛在跨域攻擊</v>
       </c>
-      <c r="N120" s="3" t="str">
+      <c r="N120" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O120" s="3" t="str">
+      <c r="O120" s="7" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P120" s="3" t="str">
+      <c r="P120" s="7" t="str">
         <v>Round 9 (批次 B): pages/news/info.vue 的 YouTube iframe 加 sandbox="allow-same-origin allow-scripts allow-presentation allow-popups"；移除非必要 allow="clipboard-write" (剪貼簿權限不應自動給)。</v>
       </c>
     </row>
@@ -10097,52 +10145,52 @@
       </c>
     </row>
     <row r="122" ht="14.4" customHeight="1">
-      <c r="A122" s="3">
+      <c r="A122" s="7">
         <v>120</v>
       </c>
-      <c r="B122" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C122" s="3" t="str">
+      <c r="B122" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C122" s="7" t="str">
         <v>共用元件</v>
       </c>
-      <c r="D122" s="3" t="str">
+      <c r="D122" s="7" t="str">
         <v>AppFooter 版權</v>
       </c>
-      <c r="E122" s="3" t="str">
+      <c r="E122" s="7" t="str">
         <v>提升</v>
       </c>
-      <c r="F122" s="3" t="str">
+      <c r="F122" s="7" t="str">
         <v>內容</v>
       </c>
-      <c r="G122" s="3" t="str">
+      <c r="G122" s="7" t="str">
         <v>中</v>
       </c>
-      <c r="H122" s="3" t="str">
+      <c r="H122" s="7" t="str">
         <v>Footer 版權年份過舊 (1995-2020)，已過期 6 年</v>
       </c>
-      <c r="I122" s="3" t="str">
+      <c r="I122" s="7" t="str">
         <v>AppFooter.vue (L42) 顯示「© 1995-2020」，現在是 2026</v>
       </c>
-      <c r="J122" s="3" t="str">
+      <c r="J122" s="7" t="str">
         <v>改 `© 1995-${new Date().getFullYear()}`，或在 footer data 中維護</v>
       </c>
-      <c r="K122" s="3" t="str">
+      <c r="K122" s="7" t="str">
         <v>components/AppFooter.vue</v>
       </c>
-      <c r="L122" s="3" t="str">
+      <c r="L122" s="7" t="str">
         <v>iFare_Frontend/components/AppFooter.vue (L42)</v>
       </c>
-      <c r="M122" s="3" t="str">
+      <c r="M122" s="7" t="str">
         <v>簡易修復</v>
       </c>
-      <c r="N122" s="3" t="str">
+      <c r="N122" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O122" s="3" t="str">
+      <c r="O122" s="7" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P122" s="3" t="str">
+      <c r="P122" s="7" t="str">
         <v>Round 7 (批次 A): components/AppFooter.vue L42 「© 1995-2020」改成 「© 1995-{{ new Date().getFullYear() }}」 — 模板內 inline 執行，自動跟系統年份。</v>
       </c>
     </row>
@@ -10352,154 +10400,154 @@
       </c>
     </row>
     <row r="127" ht="14.4" customHeight="1">
-      <c r="A127" s="3">
+      <c r="A127" s="7">
         <v>125</v>
       </c>
-      <c r="B127" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C127" s="3" t="str">
+      <c r="B127" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C127" s="7" t="str">
         <v>共用元件</v>
       </c>
-      <c r="D127" s="3" t="str">
+      <c r="D127" s="7" t="str">
         <v>AppHeader 行動 focus</v>
       </c>
-      <c r="E127" s="3" t="str">
+      <c r="E127" s="7" t="str">
         <v>修復</v>
       </c>
-      <c r="F127" s="3" t="str">
+      <c r="F127" s="7" t="str">
         <v>無障礙</v>
       </c>
-      <c r="G127" s="3" t="str">
+      <c r="G127" s="7" t="str">
         <v>低</v>
       </c>
-      <c r="H127" s="3" t="str">
+      <c r="H127" s="7" t="str">
         <v>AppHeader 行動菜單開啟時焦點未自動移至菜單，關閉時未返回觸發按鈕</v>
       </c>
-      <c r="I127" s="3" t="str">
+      <c r="I127" s="7" t="str">
         <v>AppHeader.vue (L136) 菜單關閉按鈕有 focus，但開啟時焦點未管理，屏幕閱讀器用戶會迷失</v>
       </c>
-      <c r="J127" s="3" t="str">
+      <c r="J127" s="7" t="str">
         <v>用 ref 在菜單開啟時 focus 至菜單標題或第一個項目；關閉時 focus 返回菜單按鈕</v>
       </c>
-      <c r="K127" s="3" t="str">
+      <c r="K127" s="7" t="str">
         <v>components/AppHeader.vue</v>
       </c>
-      <c r="L127" s="3" t="str">
+      <c r="L127" s="7" t="str">
         <v>iFare_Frontend/components/AppHeader.vue (L136)</v>
       </c>
-      <c r="M127" s="3" t="str">
+      <c r="M127" s="7" t="str">
         <v>增進屏幕閱讀器友善性</v>
       </c>
-      <c r="N127" s="3" t="str">
+      <c r="N127" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O127" s="3" t="str">
+      <c r="O127" s="7" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P127" s="3" t="str">
+      <c r="P127" s="7" t="str">
         <v>Round 8 (批次 C): components/AppHeader.vue 加 menuButtonRef 綁 .btn-menu，watch(isShowMenu) → 開啟時 querySelector focus 至首個 mobile menu link，關閉時 focus 回菜單按鈕。.btn-menu 加 :aria-expanded="isShowMenu" + aria-controls="mobile-menu" + aria-label="開啟菜單"；.mobile-menu 加 id="mobile-menu" + role="dialog" + aria-modal="true" + aria-label="行動選單"。全域加 ESC 鍵監聽關閉 menu (onMounted/onBeforeUnmount window.addEventListener)。</v>
       </c>
     </row>
     <row r="128" ht="14.4" customHeight="1" xml:space="preserve">
-      <c r="A128" s="3">
+      <c r="A128" s="7">
         <v>126</v>
       </c>
-      <c r="B128" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C128" s="3" t="str">
+      <c r="B128" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C128" s="7" t="str">
         <v>i-Fare 福利查詢</v>
       </c>
-      <c r="D128" s="3" t="str">
+      <c r="D128" s="7" t="str">
         <v>disabled 視覺</v>
       </c>
-      <c r="E128" s="3" t="str">
+      <c r="E128" s="7" t="str">
         <v>提升</v>
       </c>
-      <c r="F128" s="3" t="str">
+      <c r="F128" s="7" t="str">
         <v>視覺</v>
       </c>
-      <c r="G128" s="3" t="str">
+      <c r="G128" s="7" t="str">
         <v>低</v>
       </c>
-      <c r="H128" s="3" t="str">
+      <c r="H128" s="7" t="str">
         <v>ifare.vue 搜尋按鈕 disabled 狀態無灰化視覺反饋</v>
       </c>
-      <c r="I128" s="3" t="str">
+      <c r="I128" s="7" t="str">
         <v>ifare.vue (L79) :disabled="!canSearch" 但 SCSS 無 button:disabled 樣式，用戶可能誤以為按鈕可點</v>
       </c>
-      <c r="J128" s="3" t="str">
+      <c r="J128" s="7" t="str">
         <v>_button.scss 加 button:disabled { opacity: 0.5; cursor: not-allowed; }</v>
       </c>
-      <c r="K128" s="3" t="str">
+      <c r="K128" s="7" t="str">
         <v>pages/ifare.vue + _button.scss</v>
       </c>
-      <c r="L128" s="3" t="str" xml:space="preserve">
+      <c r="L128" s="7" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/pages/ifare.vue (L79)_x000d__x000d_
 iFare_Frontend/assets/style/components/_button.scss</v>
       </c>
-      <c r="M128" s="3" t="str">
+      <c r="M128" s="7" t="str">
         <v>簡易視覺修復</v>
       </c>
-      <c r="N128" s="3" t="str">
+      <c r="N128" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O128" s="3" t="str">
+      <c r="O128" s="7" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P128" s="3" t="str">
+      <c r="P128" s="7" t="str">
         <v>Round 7 (批次 A): assets/style/components/_button.scss 開頭加 generic 規則 — button:disabled / .btn:disabled / .btn.disabled 都套 opacity 0.5 + cursor not-allowed + pointer-events none。.btn-filter 既有 disabled 樣式 (L186) 不衝突。</v>
       </c>
     </row>
     <row r="129" ht="14.4" customHeight="1" xml:space="preserve">
-      <c r="A129" s="3">
+      <c r="A129" s="7">
         <v>127</v>
       </c>
-      <c r="B129" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C129" s="3" t="str">
+      <c r="B129" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C129" s="7" t="str">
         <v>效能</v>
       </c>
-      <c r="D129" s="3" t="str">
+      <c r="D129" s="7" t="str">
         <v>圖片 lazy load</v>
       </c>
-      <c r="E129" s="3" t="str">
+      <c r="E129" s="7" t="str">
         <v>提升</v>
       </c>
-      <c r="F129" s="3" t="str">
+      <c r="F129" s="7" t="str">
         <v>效能</v>
       </c>
-      <c r="G129" s="3" t="str">
+      <c r="G129" s="7" t="str">
         <v>低</v>
       </c>
-      <c r="H129" s="3" t="str">
+      <c r="H129" s="7" t="str">
         <v>collaborator 機構圖片、articles/lazy 自動生成圖片未設 loading="lazy"</v>
       </c>
-      <c r="I129" s="3" t="str">
+      <c r="I129" s="7" t="str">
         <v>collaborator.vue (L22) 和 articles/lazy.vue (L77 動態) 的 &lt;img&gt; 無 loading 屬性，所有圖片串行加載</v>
       </c>
-      <c r="J129" s="3" t="str">
+      <c r="J129" s="7" t="str">
         <v>所有 &lt;img&gt; 加 loading="lazy" (首屏 eager)；大圖考慮 WebP 或壓縮</v>
       </c>
-      <c r="K129" s="3" t="str">
+      <c r="K129" s="7" t="str">
         <v>pages/collaborator + articles/lazy</v>
       </c>
-      <c r="L129" s="3" t="str" xml:space="preserve">
+      <c r="L129" s="7" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/pages/collaborator.vue_x000d__x000d_
 iFare_Frontend/pages/articles/lazy.vue</v>
       </c>
-      <c r="M129" s="3" t="str">
+      <c r="M129" s="7" t="str">
         <v>首屏效能優化</v>
       </c>
-      <c r="N129" s="3" t="str">
+      <c r="N129" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O129" s="3" t="str">
+      <c r="O129" s="7" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P129" s="3" t="str">
+      <c r="P129" s="7" t="str">
         <v>Round 7 (批次 A): pages/collaborator.vue L22 &lt;img&gt; 加 loading="lazy" + :alt="`${_coll.title} logo`"；pages/articles/lazy.vue L77 動態 &lt;img&gt; 加 loading="lazy" + alt="${title} - ${j+1}"。</v>
       </c>
     </row>
@@ -10606,103 +10654,103 @@
       </c>
     </row>
     <row r="132" ht="14.4" customHeight="1">
-      <c r="A132" s="3">
+      <c r="A132" s="7">
         <v>130</v>
       </c>
-      <c r="B132" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C132" s="3" t="str">
+      <c r="B132" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C132" s="7" t="str">
         <v>共用元件</v>
       </c>
-      <c r="D132" s="3" t="str">
+      <c r="D132" s="7" t="str">
         <v>AppHeader aria</v>
       </c>
-      <c r="E132" s="3" t="str">
+      <c r="E132" s="7" t="str">
         <v>提升</v>
       </c>
-      <c r="F132" s="3" t="str">
+      <c r="F132" s="7" t="str">
         <v>無障礙</v>
       </c>
-      <c r="G132" s="3" t="str">
+      <c r="G132" s="7" t="str">
         <v>低</v>
       </c>
-      <c r="H132" s="3" t="str">
+      <c r="H132" s="7" t="str">
         <v>AppHeader 行動菜單關閉按鈕無 aria-label</v>
       </c>
-      <c r="I132" s="3" t="str">
+      <c r="I132" s="7" t="str">
         <v>AppHeader.vue (L136) &lt;button class="btn btn-icon btn-close"&gt; 無 aria-label，屏幕閱讀器只念「按鈕」</v>
       </c>
-      <c r="J132" s="3" t="str">
+      <c r="J132" s="7" t="str">
         <v>加 aria-label="關閉菜單"</v>
       </c>
-      <c r="K132" s="3" t="str">
+      <c r="K132" s="7" t="str">
         <v>components/AppHeader.vue</v>
       </c>
-      <c r="L132" s="3" t="str">
+      <c r="L132" s="7" t="str">
         <v>iFare_Frontend/components/AppHeader.vue (L136)</v>
       </c>
-      <c r="M132" s="3" t="str">
+      <c r="M132" s="7" t="str">
         <v>簡易無障礙修復</v>
       </c>
-      <c r="N132" s="3" t="str">
+      <c r="N132" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O132" s="3" t="str">
+      <c r="O132" s="7" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P132" s="3" t="str">
+      <c r="P132" s="7" t="str">
         <v>Round 7 (批次 A): components/AppHeader.vue L136 行動選單 .btn-close 加 aria-label="關閉菜單"。</v>
       </c>
     </row>
     <row r="133" ht="14.4" customHeight="1" xml:space="preserve">
-      <c r="A133" s="3">
+      <c r="A133" s="7">
         <v>131</v>
       </c>
-      <c r="B133" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C133" s="3" t="str">
+      <c r="B133" s="7" t="str">
+        <v>V</v>
+      </c>
+      <c r="C133" s="7" t="str">
         <v>導航</v>
       </c>
-      <c r="D133" s="3" t="str">
+      <c r="D133" s="7" t="str">
         <v>aria-current</v>
       </c>
-      <c r="E133" s="3" t="str">
+      <c r="E133" s="7" t="str">
         <v>提升</v>
       </c>
-      <c r="F133" s="3" t="str">
+      <c r="F133" s="7" t="str">
         <v>無障礙</v>
       </c>
-      <c r="G133" s="3" t="str">
+      <c r="G133" s="7" t="str">
         <v>低</v>
       </c>
-      <c r="H133" s="3" t="str">
+      <c r="H133" s="7" t="str">
         <v>AppHeader 與其他導航元件當前頁面連結無 aria-current="page"</v>
       </c>
-      <c r="I133" s="3" t="str">
+      <c r="I133" s="7" t="str">
         <v>AppHeader (L48-69) 用 :class="{ active: $route.name }" 但無 aria-current；屏幕閱讀器無法知道哪個是當前頁</v>
       </c>
-      <c r="J133" s="3" t="str">
+      <c r="J133" s="7" t="str">
         <v>:aria-current="$route.name === 'about' ? 'page' : undefined"</v>
       </c>
-      <c r="K133" s="3" t="str">
+      <c r="K133" s="7" t="str">
         <v>components/AppHeader + CompBreadCrumb</v>
       </c>
-      <c r="L133" s="3" t="str" xml:space="preserve">
+      <c r="L133" s="7" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/components/AppHeader.vue_x000d__x000d_
 iFare_Frontend/components/CompBreadCrumb.vue</v>
       </c>
-      <c r="M133" s="3" t="str">
+      <c r="M133" s="7" t="str">
         <v>WCAG 2.1 最佳實踐 + 外部連結指示符可選加 ic-external-link icon</v>
       </c>
-      <c r="N133" s="3" t="str">
+      <c r="N133" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="O133" s="3" t="str">
+      <c r="O133" s="7" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P133" s="3" t="str">
+      <c r="P133" s="7" t="str">
         <v>Round 7 (批次 A): components/AppHeader.vue 桌面 5 + 行動 6 + i-Fare 桌面 1 共 12 個 NuxtLink 加 :aria-current="$route.name === 'xxx' ? 'page' : undefined"。i-Fare 用 includes('ifare') 涵蓋子路由。</v>
       </c>
     </row>
@@ -10731,54 +10779,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="str">
+      <c r="A1" s="3" t="str">
         <v>【1】整體進度</v>
       </c>
-      <c r="B1" s="4" t="str">
-        <v/>
-      </c>
-      <c r="C1" s="4" t="str">
-        <v/>
-      </c>
-      <c r="D1" s="4" t="str">
-        <v/>
-      </c>
-      <c r="E1" s="4" t="str">
-        <v/>
-      </c>
-      <c r="F1" s="4" t="str">
-        <v/>
-      </c>
-      <c r="G1" s="4" t="str">
-        <v/>
-      </c>
-      <c r="H1" s="4" t="str">
+      <c r="B1" s="3" t="str">
+        <v/>
+      </c>
+      <c r="C1" s="3" t="str">
+        <v/>
+      </c>
+      <c r="D1" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E1" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F1" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G1" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H1" s="3" t="str">
         <v/>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="str">
+      <c r="A2" s="3" t="str">
         <v>Sheet 名稱</v>
       </c>
-      <c r="B2" s="5" t="str">
+      <c r="B2" s="3" t="str">
         <v>總計</v>
       </c>
-      <c r="C2" s="5" t="str">
+      <c r="C2" s="3" t="str">
         <v>已修正</v>
       </c>
-      <c r="D2" s="5" t="str">
+      <c r="D2" s="3" t="str">
         <v>部分修正</v>
       </c>
-      <c r="E2" s="5" t="str">
-        <v>待處理</v>
-      </c>
-      <c r="F2" s="5" t="str">
+      <c r="E2" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="F2" s="3" t="str">
         <v>完成率</v>
       </c>
-      <c r="G2" s="5" t="str">
+      <c r="G2" s="3" t="str">
         <v>備註</v>
       </c>
-      <c r="H2" s="5" t="str">
+      <c r="H2" s="3" t="str">
         <v/>
       </c>
     </row>
@@ -10789,13 +10837,13 @@
       <c r="B3" s="3">
         <v>131</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="3">
         <v>39</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="3">
         <v>7</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="3">
         <v>85</v>
       </c>
       <c r="F3" s="3" t="str">
@@ -10815,13 +10863,13 @@
       <c r="B4" s="3">
         <v>54</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="3">
         <v>0</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="3">
         <v>0</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="3">
         <v>54</v>
       </c>
       <c r="F4" s="3" t="str">
@@ -10841,13 +10889,13 @@
       <c r="B5" s="3">
         <v>12</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="3">
         <v>0</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="3">
         <v>0</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="3">
         <v>12</v>
       </c>
       <c r="F5" s="3" t="str">
@@ -10861,54 +10909,54 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="str">
+      <c r="A7" s="3" t="str">
         <v>【2】Round 時間軸 — 每輪做了什麼</v>
       </c>
-      <c r="B7" s="4" t="str">
-        <v/>
-      </c>
-      <c r="C7" s="4" t="str">
-        <v/>
-      </c>
-      <c r="D7" s="4" t="str">
-        <v/>
-      </c>
-      <c r="E7" s="4" t="str">
-        <v/>
-      </c>
-      <c r="F7" s="4" t="str">
-        <v/>
-      </c>
-      <c r="G7" s="4" t="str">
-        <v/>
-      </c>
-      <c r="H7" s="4" t="str">
+      <c r="B7" s="3" t="str">
+        <v/>
+      </c>
+      <c r="C7" s="3" t="str">
+        <v/>
+      </c>
+      <c r="D7" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E7" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F7" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G7" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H7" s="3" t="str">
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="str">
+      <c r="A8" s="3" t="str">
         <v>Round</v>
       </c>
-      <c r="B8" s="5" t="str">
+      <c r="B8" s="3" t="str">
         <v>日期</v>
       </c>
-      <c r="C8" s="5" t="str">
+      <c r="C8" s="3" t="str">
         <v>主題</v>
       </c>
-      <c r="D8" s="5" t="str">
+      <c r="D8" s="3" t="str">
         <v>UIUX 標完成</v>
       </c>
-      <c r="E8" s="5" t="str">
+      <c r="E8" s="3" t="str">
         <v>UIUX 新增</v>
       </c>
-      <c r="F8" s="5" t="str">
+      <c r="F8" s="3" t="str">
         <v>後臺新增</v>
       </c>
-      <c r="G8" s="5" t="str">
+      <c r="G8" s="3" t="str">
         <v>Schema</v>
       </c>
-      <c r="H8" s="5" t="str">
+      <c r="H8" s="3" t="str">
         <v>主要產出</v>
       </c>
     </row>
@@ -11069,54 +11117,54 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="str">
+      <c r="A16" s="3" t="str">
         <v>【3】後臺優化 — 5 主軸分布 (拿這個去提案!)</v>
       </c>
-      <c r="B16" s="4" t="str">
-        <v/>
-      </c>
-      <c r="C16" s="4" t="str">
-        <v/>
-      </c>
-      <c r="D16" s="4" t="str">
-        <v/>
-      </c>
-      <c r="E16" s="4" t="str">
-        <v/>
-      </c>
-      <c r="F16" s="4" t="str">
-        <v/>
-      </c>
-      <c r="G16" s="4" t="str">
-        <v/>
-      </c>
-      <c r="H16" s="4" t="str">
+      <c r="B16" s="3" t="str">
+        <v/>
+      </c>
+      <c r="C16" s="3" t="str">
+        <v/>
+      </c>
+      <c r="D16" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E16" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F16" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G16" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H16" s="3" t="str">
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="str">
+      <c r="A17" s="3" t="str">
         <v>主軸</v>
       </c>
-      <c r="B17" s="5" t="str">
+      <c r="B17" s="3" t="str">
         <v>項目數</v>
       </c>
-      <c r="C17" s="5" t="str">
+      <c r="C17" s="3" t="str">
         <v>比例</v>
       </c>
-      <c r="D17" s="5" t="str">
+      <c r="D17" s="3" t="str">
         <v>主要訴求</v>
       </c>
-      <c r="E17" s="5" t="str">
+      <c r="E17" s="3" t="str">
         <v>對應 #</v>
       </c>
-      <c r="F17" s="5" t="str">
-        <v/>
-      </c>
-      <c r="G17" s="5" t="str">
-        <v/>
-      </c>
-      <c r="H17" s="5" t="str">
+      <c r="F17" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G17" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H17" s="3" t="str">
         <v/>
       </c>
     </row>
@@ -11277,54 +11325,54 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="str">
+      <c r="A25" s="3" t="str">
         <v>【4】UIUX — 優先級 × 狀態分布</v>
       </c>
-      <c r="B25" s="4" t="str">
-        <v/>
-      </c>
-      <c r="C25" s="4" t="str">
-        <v/>
-      </c>
-      <c r="D25" s="4" t="str">
-        <v/>
-      </c>
-      <c r="E25" s="4" t="str">
-        <v/>
-      </c>
-      <c r="F25" s="4" t="str">
-        <v/>
-      </c>
-      <c r="G25" s="4" t="str">
-        <v/>
-      </c>
-      <c r="H25" s="4" t="str">
+      <c r="B25" s="3" t="str">
+        <v/>
+      </c>
+      <c r="C25" s="3" t="str">
+        <v/>
+      </c>
+      <c r="D25" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E25" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F25" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G25" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H25" s="3" t="str">
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="str">
+      <c r="A26" s="3" t="str">
         <v>優先級</v>
       </c>
-      <c r="B26" s="5" t="str">
+      <c r="B26" s="3" t="str">
         <v>已修正</v>
       </c>
-      <c r="C26" s="5" t="str">
+      <c r="C26" s="3" t="str">
         <v>部分修正</v>
       </c>
-      <c r="D26" s="5" t="str">
-        <v>待處理</v>
-      </c>
-      <c r="E26" s="5" t="str">
+      <c r="D26" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="E26" s="3" t="str">
         <v>小計</v>
       </c>
-      <c r="F26" s="5" t="str">
+      <c r="F26" s="3" t="str">
         <v>完成率</v>
       </c>
-      <c r="G26" s="5" t="str">
-        <v/>
-      </c>
-      <c r="H26" s="5" t="str">
+      <c r="G26" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H26" s="3" t="str">
         <v/>
       </c>
     </row>
@@ -11332,13 +11380,13 @@
       <c r="A27" s="3" t="str">
         <v>高</v>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="3">
         <v>7</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="3">
         <v>4</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="3">
         <v>6</v>
       </c>
       <c r="E27" s="3">
@@ -11358,13 +11406,13 @@
       <c r="A28" s="3" t="str">
         <v>中</v>
       </c>
-      <c r="B28" s="6">
+      <c r="B28" s="3">
         <v>14</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="3">
         <v>1</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="3">
         <v>44</v>
       </c>
       <c r="E28" s="3">
@@ -11384,13 +11432,13 @@
       <c r="A29" s="3" t="str">
         <v>低</v>
       </c>
-      <c r="B29" s="6">
+      <c r="B29" s="3">
         <v>18</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="3">
         <v>2</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="3">
         <v>35</v>
       </c>
       <c r="E29" s="3">
@@ -11407,54 +11455,54 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="str">
+      <c r="A31" s="3" t="str">
         <v>【5】UIUX — 各區塊問題分布</v>
       </c>
-      <c r="B31" s="4" t="str">
-        <v/>
-      </c>
-      <c r="C31" s="4" t="str">
-        <v/>
-      </c>
-      <c r="D31" s="4" t="str">
-        <v/>
-      </c>
-      <c r="E31" s="4" t="str">
-        <v/>
-      </c>
-      <c r="F31" s="4" t="str">
-        <v/>
-      </c>
-      <c r="G31" s="4" t="str">
-        <v/>
-      </c>
-      <c r="H31" s="4" t="str">
+      <c r="B31" s="3" t="str">
+        <v/>
+      </c>
+      <c r="C31" s="3" t="str">
+        <v/>
+      </c>
+      <c r="D31" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E31" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F31" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G31" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H31" s="3" t="str">
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="str">
+      <c r="A32" s="3" t="str">
         <v>區塊</v>
       </c>
-      <c r="B32" s="5" t="str">
+      <c r="B32" s="3" t="str">
         <v>項目數</v>
       </c>
-      <c r="C32" s="5" t="str">
+      <c r="C32" s="3" t="str">
         <v>佔比</v>
       </c>
-      <c r="D32" s="5" t="str">
-        <v/>
-      </c>
-      <c r="E32" s="5" t="str">
-        <v/>
-      </c>
-      <c r="F32" s="5" t="str">
-        <v/>
-      </c>
-      <c r="G32" s="5" t="str">
-        <v/>
-      </c>
-      <c r="H32" s="5" t="str">
+      <c r="D32" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E32" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F32" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G32" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H32" s="3" t="str">
         <v/>
       </c>
     </row>
@@ -11927,54 +11975,54 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="str">
+      <c r="A52" s="3" t="str">
         <v>【6】後臺優化 — 各區塊問題分布</v>
       </c>
-      <c r="B52" s="4" t="str">
-        <v/>
-      </c>
-      <c r="C52" s="4" t="str">
-        <v/>
-      </c>
-      <c r="D52" s="4" t="str">
-        <v/>
-      </c>
-      <c r="E52" s="4" t="str">
-        <v/>
-      </c>
-      <c r="F52" s="4" t="str">
-        <v/>
-      </c>
-      <c r="G52" s="4" t="str">
-        <v/>
-      </c>
-      <c r="H52" s="4" t="str">
+      <c r="B52" s="3" t="str">
+        <v/>
+      </c>
+      <c r="C52" s="3" t="str">
+        <v/>
+      </c>
+      <c r="D52" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E52" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F52" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G52" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H52" s="3" t="str">
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="str">
+      <c r="A53" s="3" t="str">
         <v>區塊</v>
       </c>
-      <c r="B53" s="5" t="str">
+      <c r="B53" s="3" t="str">
         <v>項目數</v>
       </c>
-      <c r="C53" s="5" t="str">
+      <c r="C53" s="3" t="str">
         <v>佔比</v>
       </c>
-      <c r="D53" s="5" t="str">
-        <v/>
-      </c>
-      <c r="E53" s="5" t="str">
-        <v/>
-      </c>
-      <c r="F53" s="5" t="str">
-        <v/>
-      </c>
-      <c r="G53" s="5" t="str">
-        <v/>
-      </c>
-      <c r="H53" s="5" t="str">
+      <c r="D53" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E53" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F53" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G53" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H53" s="3" t="str">
         <v/>
       </c>
     </row>
@@ -12577,54 +12625,54 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="str">
+      <c r="A78" s="3" t="str">
         <v>【7】你做了什麼 — 已完成項目摘要 (依 Round 分組)</v>
       </c>
-      <c r="B78" s="4" t="str">
-        <v/>
-      </c>
-      <c r="C78" s="4" t="str">
-        <v/>
-      </c>
-      <c r="D78" s="4" t="str">
-        <v/>
-      </c>
-      <c r="E78" s="4" t="str">
-        <v/>
-      </c>
-      <c r="F78" s="4" t="str">
-        <v/>
-      </c>
-      <c r="G78" s="4" t="str">
-        <v/>
-      </c>
-      <c r="H78" s="4" t="str">
+      <c r="B78" s="3" t="str">
+        <v/>
+      </c>
+      <c r="C78" s="3" t="str">
+        <v/>
+      </c>
+      <c r="D78" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E78" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F78" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G78" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H78" s="3" t="str">
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="str">
+      <c r="A79" s="3" t="str">
         <v>Round</v>
       </c>
-      <c r="B79" s="5" t="str">
+      <c r="B79" s="3" t="str">
         <v>日期</v>
       </c>
-      <c r="C79" s="5" t="str">
+      <c r="C79" s="3" t="str">
         <v>已修正 (綠)</v>
       </c>
-      <c r="D79" s="5" t="str">
+      <c r="D79" s="3" t="str">
         <v>部分修正 (黃)</v>
       </c>
-      <c r="E79" s="5" t="str">
+      <c r="E79" s="3" t="str">
         <v>已修正 # 清單</v>
       </c>
-      <c r="F79" s="5" t="str">
+      <c r="F79" s="3" t="str">
         <v>部分修正 # 清單</v>
       </c>
-      <c r="G79" s="5" t="str">
+      <c r="G79" s="3" t="str">
         <v>主要重點</v>
       </c>
-      <c r="H79" s="5" t="str">
+      <c r="H79" s="3" t="str">
         <v/>
       </c>
     </row>
@@ -12635,10 +12683,10 @@
       <c r="B80" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="C80" s="6">
+      <c r="C80" s="3">
         <v>24</v>
       </c>
-      <c r="D80" s="7">
+      <c r="D80" s="3">
         <v>6</v>
       </c>
       <c r="E80" s="3" t="str">
@@ -12661,10 +12709,10 @@
       <c r="B81" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="C81" s="6">
+      <c r="C81" s="3">
         <v>2</v>
       </c>
-      <c r="D81" s="7">
+      <c r="D81" s="3">
         <v>0</v>
       </c>
       <c r="E81" s="3" t="str">
@@ -12687,10 +12735,10 @@
       <c r="B82" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="C82" s="6">
+      <c r="C82" s="3">
         <v>6</v>
       </c>
-      <c r="D82" s="7">
+      <c r="D82" s="3">
         <v>0</v>
       </c>
       <c r="E82" s="3" t="str">
@@ -12713,10 +12761,10 @@
       <c r="B83" s="3" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="C83" s="6">
+      <c r="C83" s="3">
         <v>7</v>
       </c>
-      <c r="D83" s="7">
+      <c r="D83" s="3">
         <v>1</v>
       </c>
       <c r="E83" s="3" t="str">

--- a/docs/iFare_UI_UX_問題追蹤清單.xlsx
+++ b/docs/iFare_UI_UX_問題追蹤清單.xlsx
@@ -36,7 +36,39 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+      <color rgb="1F3864"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+      <color rgb="1F3864"/>
+    </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -48,7 +80,7 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <color rgb="9C5700"/>
+      <color rgb="006100"/>
     </font>
     <font>
       <sz val="11"/>
@@ -58,15 +90,25 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <color rgb="006100"/>
+      <color rgb="595959"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <color rgb="006100"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <color rgb="9C5700"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <color rgb="595959"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="12">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -79,7 +121,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FF4472C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -91,13 +157,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -121,22 +199,48 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="true"/>
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="true"/>
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="true"/>
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="true"/>
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles>
@@ -193,10 +297,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
-        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
-        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
-        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -228,10 +332,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
-        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
-        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
-        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -1773,13 +1877,13 @@
         <v>對應前台 #102 (Round 4)</v>
       </c>
       <c r="N15" s="3" t="str">
-        <v>待處理</v>
+        <v>已修正</v>
       </c>
       <c r="O15" s="3" t="str">
-        <v/>
+        <v>2026-05-04</v>
       </c>
       <c r="P15" s="3" t="str">
-        <v>需後端工程師處理；至少 6 .cs + 1 EF migration</v>
+        <v>Round 10: 取消 — 改用前台 sanitize 白名單方式達成 (見 UIUX #102 與 docs/iFare_News_影片嵌入指南.md)。.NET News.cs / DTO / TaskManager 不需動，本機 News.cs 已 git restore。後台 admin News_AddEditView 影片網址 input 已撤掉，回歸只用 HTML 編輯器內貼 iframe。</v>
       </c>
       <c r="Q15" s="3" t="str">
         <v>—</v>
@@ -4026,7 +4130,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P133"/>
+  <dimension ref="A1:P134"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="6"/>
     <col min="2" max="2" customWidth="1" width="6"/>
@@ -4105,50 +4209,50 @@
       <c r="A3" s="4">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="str">
+      <c r="B3" s="4" t="str">
         <v>~</v>
       </c>
-      <c r="C3" s="5" t="str">
+      <c r="C3" s="4" t="str">
         <v>i-Fare 福利查詢</v>
       </c>
-      <c r="D3" s="5" t="str">
+      <c r="D3" s="4" t="str">
         <v>搜尋介面</v>
       </c>
-      <c r="E3" s="5" t="str">
+      <c r="E3" s="4" t="str">
         <v>修復</v>
       </c>
-      <c r="F3" s="5" t="str">
+      <c r="F3" s="4" t="str">
         <v>互動</v>
       </c>
-      <c r="G3" s="5" t="str">
+      <c r="G3" s="4" t="str">
         <v>高</v>
       </c>
-      <c r="H3" s="5" t="str">
+      <c r="H3" s="4" t="str">
         <v>篩選條件不完整時無錯誤訊息</v>
       </c>
-      <c r="I3" s="5" t="str">
+      <c r="I3" s="4" t="str">
         <v>按鈕變灰(disabled)但使用者不知道缺哪個欄位，Search()直接 return false 無任何提示</v>
       </c>
-      <c r="J3" s="5" t="str">
+      <c r="J3" s="4" t="str">
         <v>加入未填欄位紅框提示 + 錯誤文字</v>
       </c>
-      <c r="K3" s="5" t="str">
+      <c r="K3" s="4" t="str">
         <v>pages/ifare.vue</v>
       </c>
-      <c r="L3" s="5" t="str" xml:space="preserve">
+      <c r="L3" s="4" t="str" xml:space="preserve">
         <v xml:space="preserve">pages/ifare.vue_x000d__x000d__x000d_
 assets/style/_font.scss</v>
       </c>
-      <c r="M3" s="5" t="str">
+      <c r="M3" s="4" t="str">
         <v>無錯誤訊息確認；但「(必填)」標示已存在於 _font.scss</v>
       </c>
-      <c r="N3" s="5" t="str">
+      <c r="N3" s="4" t="str">
         <v>部分修正</v>
       </c>
-      <c r="O3" s="5" t="str">
+      <c r="O3" s="4" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P3" s="5" t="str">
+      <c r="P3" s="4" t="str">
         <v>已移除三項都空時的 disabled 條件（pages/ifare.vue:75 + pages/ifare/result.vue 三處），改用 hasAnyCondition 顯示「未填條件將顯示最新福利」提示。改採「不阻擋 + 引導文案」策略，與原建議「未填欄位紅框 + 錯誤文字」方向不同。</v>
       </c>
     </row>
@@ -4511,54 +4615,54 @@
       </c>
     </row>
     <row r="11" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A11" s="5">
+      <c r="A11" s="4">
         <v>9</v>
       </c>
-      <c r="B11" s="5" t="str">
-        <v>V</v>
-      </c>
-      <c r="C11" s="5" t="str">
+      <c r="B11" s="4" t="str">
+        <v>V</v>
+      </c>
+      <c r="C11" s="4" t="str">
         <v>i-Fare 福利查詢</v>
       </c>
-      <c r="D11" s="5" t="str">
+      <c r="D11" s="4" t="str">
         <v>查詢結果</v>
       </c>
-      <c r="E11" s="5" t="str">
+      <c r="E11" s="4" t="str">
         <v>提升</v>
       </c>
-      <c r="F11" s="5" t="str">
+      <c r="F11" s="4" t="str">
         <v>視覺</v>
       </c>
-      <c r="G11" s="5" t="str">
+      <c r="G11" s="4" t="str">
         <v>低</v>
       </c>
-      <c r="H11" s="5" t="str">
+      <c r="H11" s="4" t="str">
         <v>搜尋結果數量不夠醒目</v>
       </c>
-      <c r="I11" s="5" t="str">
+      <c r="I11" s="4" t="str">
         <v>結果數量 font-size:14px font-weight:400，周圍文字 opacity:0.5</v>
       </c>
-      <c r="J11" s="5" t="str">
+      <c r="J11" s="4" t="str">
         <v>頂部大字顯示 + 計數動畫</v>
       </c>
-      <c r="K11" s="5" t="str">
+      <c r="K11" s="4" t="str">
         <v>pages/ifare/result.vue</v>
       </c>
-      <c r="L11" s="5" t="str" xml:space="preserve">
+      <c r="L11" s="4" t="str" xml:space="preserve">
         <v xml:space="preserve">pages/ifare/result.vue_x000d__x000d__x000d_
 assets/style/components/_appBodyChild_ifare.scss_x000d__x000d__x000d_
 assets/style/_font.scss</v>
       </c>
-      <c r="M11" s="5" t="str">
+      <c r="M11" s="4" t="str">
         <v>確認字體小且無強調</v>
       </c>
-      <c r="N11" s="5" t="str">
+      <c r="N11" s="4" t="str">
         <v>部分修正</v>
       </c>
-      <c r="O11" s="5" t="str">
+      <c r="O11" s="4" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P11" s="5" t="str">
+      <c r="P11" s="4" t="str">
         <v>結果摘要從「{{count}}」改寫為「共找到 X 項，僅顯示前 X 筆」(pages/ifare/result.vue)；.result-total 從 inline-flex + ::before 結構簡化為 inline；新增 .result-summary-note 樣式。原訴求「頂部大字 + 計數動畫」尚未做。</v>
       </c>
     </row>
@@ -4870,106 +4974,106 @@
       </c>
     </row>
     <row r="18" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A18" s="6">
+      <c r="A18" s="5">
         <v>16</v>
       </c>
-      <c r="B18" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C18" s="7" t="str">
+      <c r="B18" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C18" s="5" t="str">
         <v>首頁</v>
       </c>
-      <c r="D18" s="7" t="str">
-        <v/>
-      </c>
-      <c r="E18" s="7" t="str">
+      <c r="D18" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E18" s="5" t="str">
         <v>修復</v>
       </c>
-      <c r="F18" s="7" t="str">
+      <c r="F18" s="5" t="str">
         <v>視覺</v>
       </c>
-      <c r="G18" s="7" t="str">
+      <c r="G18" s="5" t="str">
         <v>低</v>
       </c>
-      <c r="H18" s="7" t="str">
+      <c r="H18" s="5" t="str">
         <v>頁面切換無轉場動畫</v>
       </c>
-      <c r="I18" s="7" t="str">
+      <c r="I18" s="5" t="str">
         <v>layouts/default.vue 用 &lt;slot /&gt; 無 &lt;Transition&gt;，nuxt.config 無 pageTransition</v>
       </c>
-      <c r="J18" s="7" t="str">
+      <c r="J18" s="5" t="str">
         <v>加入 Nuxt &lt;transition&gt; 過場效果</v>
       </c>
-      <c r="K18" s="7" t="str">
+      <c r="K18" s="5" t="str">
         <v>layouts/default.vue</v>
       </c>
-      <c r="L18" s="7" t="str" xml:space="preserve">
+      <c r="L18" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">layouts/default.vue_x000d__x000d__x000d_
 nuxt.config.ts_x000d__x000d__x000d_
 assets/style/_transition.scss</v>
       </c>
-      <c r="M18" s="7" t="str">
+      <c r="M18" s="5" t="str">
         <v>確認無任何 transition 設定</v>
       </c>
-      <c r="N18" s="7" t="str">
+      <c r="N18" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O18" s="7" t="str">
+      <c r="O18" s="5" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P18" s="7" t="str">
+      <c r="P18" s="5" t="str">
         <v>app.vue 加 &lt;NuxtPage :transition="{ name: 'page', mode: 'out-in' }" /&gt;；_animation.scss 新增 .page-enter/leave-active 與 .layout-enter/leave-active keyframes（opacity + translateY，純 GPU 屬性）。</v>
       </c>
     </row>
     <row r="19" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A19" s="7">
+      <c r="A19" s="5">
         <v>17</v>
       </c>
-      <c r="B19" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C19" s="7" t="str">
+      <c r="B19" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C19" s="5" t="str">
         <v>首頁</v>
       </c>
-      <c r="D19" s="7" t="str">
-        <v/>
-      </c>
-      <c r="E19" s="7" t="str">
+      <c r="D19" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E19" s="5" t="str">
         <v>修復</v>
       </c>
-      <c r="F19" s="7" t="str">
+      <c r="F19" s="5" t="str">
         <v>視覺</v>
       </c>
-      <c r="G19" s="7" t="str">
+      <c r="G19" s="5" t="str">
         <v>中</v>
       </c>
-      <c r="H19" s="7" t="str">
+      <c r="H19" s="5" t="str">
         <v>Footer 社群連結呈現不一致</v>
       </c>
-      <c r="I19" s="7" t="str">
+      <c r="I19" s="5" t="str">
         <v>LINE 用 styled button (.btn-line)，Facebook 用純文字圖示連結 (.ic-facebook-before)</v>
       </c>
-      <c r="J19" s="7" t="str">
+      <c r="J19" s="5" t="str">
         <v>統一為相同呈現方式</v>
       </c>
-      <c r="K19" s="7" t="str">
+      <c r="K19" s="5" t="str">
         <v>components/AppFooter.vue</v>
       </c>
-      <c r="L19" s="7" t="str" xml:space="preserve">
+      <c r="L19" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">components/AppFooter.vue_x000d__x000d__x000d_
 assets/style/components/_appFooter.scss_x000d__x000d__x000d_
 assets/style/_font.scss</v>
       </c>
-      <c r="M19" s="7" t="str">
+      <c r="M19" s="5" t="str">
         <v>兩個社群連結完全不同的 HTML 結構和樣式</v>
       </c>
-      <c r="N19" s="7" t="str">
+      <c r="N19" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O19" s="7" t="str">
+      <c r="O19" s="5" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P19" s="7" t="str">
+      <c r="P19" s="5" t="str">
         <v>LINE 與 Facebook 統一為 .btn-social 白底按鈕（含 icon + 深綠字），Facebook 從 .ic-facebook-before 文字連結改為 button 結構並與 LINE 並排。LINE icon 修正為品牌綠 #06C755（Line-Logo.svg fill），Facebook 改用品牌藍 #1877F2（新增 Facebook-Logo-color.svg）。</v>
       </c>
     </row>
@@ -5182,155 +5286,155 @@
       </c>
     </row>
     <row r="24" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A24" s="7">
+      <c r="A24" s="5">
         <v>22</v>
       </c>
-      <c r="B24" s="7" t="str">
+      <c r="B24" s="5" t="str">
         <v>~</v>
       </c>
-      <c r="C24" s="7" t="str">
+      <c r="C24" s="5" t="str">
         <v>最新消息</v>
       </c>
-      <c r="D24" s="7" t="str">
-        <v/>
-      </c>
-      <c r="E24" s="7" t="str">
+      <c r="D24" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E24" s="5" t="str">
         <v>修復</v>
       </c>
-      <c r="F24" s="7" t="str">
+      <c r="F24" s="5" t="str">
         <v>互動</v>
       </c>
-      <c r="G24" s="7" t="str">
+      <c r="G24" s="5" t="str">
         <v>高</v>
       </c>
-      <c r="H24" s="7" t="str">
+      <c r="H24" s="5" t="str">
         <v>缺少 Loading 骨架畫面</v>
       </c>
-      <c r="I24" s="7" t="str">
+      <c r="I24" s="5" t="str">
         <v>API 載入期間無骨架或 loading 指示</v>
       </c>
-      <c r="J24" s="7" t="str">
+      <c r="J24" s="5" t="str">
         <v>新增 skeleton loader</v>
       </c>
-      <c r="K24" s="7" t="str">
+      <c r="K24" s="5" t="str">
         <v>pages/news.vue</v>
       </c>
-      <c r="L24" s="7" t="str" xml:space="preserve">
+      <c r="L24" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">pages/news.vue_x000d__x000d__x000d_
 assets/style/components/_appBody.scss</v>
       </c>
-      <c r="M24" s="7" t="str">
+      <c r="M24" s="5" t="str">
         <v>無骨架確認；但有 CSS :empty 空狀態（「目前沒有相關資料哦！」）</v>
       </c>
-      <c r="N24" s="7" t="str">
+      <c r="N24" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O24" s="7" t="str">
+      <c r="O24" s="5" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P24" s="7" t="str">
+      <c r="P24" s="5" t="str">
         <v>pages/news.vue 加 isLoading/hasError，分四分支渲染（4 條 skeleton-line 骨架／錯誤+重試／空狀態／正常列表）；LoadNews() 重構並加 .catch()；_animation.scss 加 @keyframes skeletonShimmer 與 .skeleton-line 樣式。</v>
       </c>
     </row>
     <row r="25" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A25" s="7">
+      <c r="A25" s="5">
         <v>23</v>
       </c>
-      <c r="B25" s="7" t="str">
+      <c r="B25" s="5" t="str">
         <v>~</v>
       </c>
-      <c r="C25" s="7" t="str">
+      <c r="C25" s="5" t="str">
         <v>最新消息</v>
       </c>
-      <c r="D25" s="7" t="str">
-        <v/>
-      </c>
-      <c r="E25" s="7" t="str">
+      <c r="D25" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E25" s="5" t="str">
         <v>修復</v>
       </c>
-      <c r="F25" s="7" t="str">
+      <c r="F25" s="5" t="str">
         <v>視覺</v>
       </c>
-      <c r="G25" s="7" t="str">
+      <c r="G25" s="5" t="str">
         <v>低</v>
       </c>
-      <c r="H25" s="7" t="str">
+      <c r="H25" s="5" t="str">
         <v>桌面版內容截斷無省略提示</v>
       </c>
-      <c r="I25" s="7" t="str">
+      <c r="I25" s="5" t="str">
         <v>桌面版 .item-info 無 text-overflow 或 line-clamp</v>
       </c>
-      <c r="J25" s="7" t="str">
+      <c r="J25" s="5" t="str">
         <v>加入 text-overflow: ellipsis 或 line-clamp</v>
       </c>
-      <c r="K25" s="7" t="str">
+      <c r="K25" s="5" t="str">
         <v>pages/news.vue</v>
       </c>
-      <c r="L25" s="7" t="str" xml:space="preserve">
+      <c r="L25" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">pages/news.vue_x000d__x000d__x000d_
 assets/style/components/_appBody.scss_x000d__x000d__x000d_
 assets/style/_font.scss</v>
       </c>
-      <c r="M25" s="7" t="str">
+      <c r="M25" s="5" t="str">
         <v>桌面無省略確認；手機版已有 textLineClamp(2)</v>
       </c>
-      <c r="N25" s="7" t="str">
+      <c r="N25" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O25" s="7" t="str">
+      <c r="O25" s="5" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P25" s="7" t="str">
+      <c r="P25" s="5" t="str">
         <v>pages/news.vue 的 .article-item .item-info 加 line-clamp: 2（桌面）/ line-clamp: 3（手機 ≤1024px），超過行數自動省略結尾。</v>
       </c>
     </row>
     <row r="26" ht="45" customHeight="1">
-      <c r="A26" s="7">
+      <c r="A26" s="5">
         <v>24</v>
       </c>
-      <c r="B26" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C26" s="7" t="str">
+      <c r="B26" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C26" s="5" t="str">
         <v>最新消息</v>
       </c>
-      <c r="D26" s="7" t="str">
-        <v/>
-      </c>
-      <c r="E26" s="7" t="str">
+      <c r="D26" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E26" s="5" t="str">
         <v>修復</v>
       </c>
-      <c r="F26" s="7" t="str">
+      <c r="F26" s="5" t="str">
         <v>無障礙</v>
       </c>
-      <c r="G26" s="7" t="str">
+      <c r="G26" s="5" t="str">
         <v>低</v>
       </c>
-      <c r="H26" s="7" t="str">
+      <c r="H26" s="5" t="str">
         <v>純圖示連結缺少 aria-label</v>
       </c>
-      <c r="I26" s="7" t="str">
+      <c r="I26" s="5" t="str">
         <v>&lt;i class="ic-arrow-right"&gt; 無 aria-label/title/隱藏文字</v>
       </c>
-      <c r="J26" s="7" t="str">
+      <c r="J26" s="5" t="str">
         <v>加入 aria-label</v>
       </c>
-      <c r="K26" s="7" t="str">
+      <c r="K26" s="5" t="str">
         <v>pages/news.vue</v>
       </c>
-      <c r="L26" s="7" t="str">
+      <c r="L26" s="5" t="str">
         <v>pages/news.vue</v>
       </c>
-      <c r="M26" s="7" t="str">
+      <c r="M26" s="5" t="str">
         <v>grep aria-label 全站回傳 0 筆</v>
       </c>
-      <c r="N26" s="7" t="str">
+      <c r="N26" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O26" s="7" t="str">
+      <c r="O26" s="5" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P26" s="7" t="str">
+      <c r="P26" s="5" t="str">
         <v>pages/news.vue 的 &lt;i class="ic-arrow-right"&gt; 加上 aria-label="閱讀全文"，符合無障礙語意要求。</v>
       </c>
     </row>
@@ -5386,54 +5490,54 @@
       </c>
     </row>
     <row r="28" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A28" s="7">
+      <c r="A28" s="5">
         <v>26</v>
       </c>
-      <c r="B28" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C28" s="7" t="str">
+      <c r="B28" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C28" s="5" t="str">
         <v>最新消息</v>
       </c>
-      <c r="D28" s="7" t="str">
-        <v/>
-      </c>
-      <c r="E28" s="7" t="str">
+      <c r="D28" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E28" s="5" t="str">
         <v>提升</v>
       </c>
-      <c r="F28" s="7" t="str">
+      <c r="F28" s="5" t="str">
         <v>視覺</v>
       </c>
-      <c r="G28" s="7" t="str">
+      <c r="G28" s="5" t="str">
         <v>低</v>
       </c>
-      <c r="H28" s="7" t="str">
+      <c r="H28" s="5" t="str">
         <v>新增「NEW」標籤</v>
       </c>
-      <c r="I28" s="7" t="str">
+      <c r="I28" s="5" t="str">
         <v>新消息無醒目標示</v>
       </c>
-      <c r="J28" s="7" t="str">
+      <c r="J28" s="5" t="str">
         <v>7 天內的新消息加上 NEW badge</v>
       </c>
-      <c r="K28" s="7" t="str">
+      <c r="K28" s="5" t="str">
         <v>pages/news.vue</v>
       </c>
-      <c r="L28" s="7" t="str" xml:space="preserve">
+      <c r="L28" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">pages/news.vue_x000d__x000d__x000d_
 assets/style/components/_appBody.scss_x000d__x000d__x000d_
 assets/style/_font.scss</v>
       </c>
-      <c r="M28" s="7" t="str">
+      <c r="M28" s="5" t="str">
         <v>功能確實不存在</v>
       </c>
-      <c r="N28" s="7" t="str">
+      <c r="N28" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O28" s="7" t="str">
+      <c r="O28" s="5" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P28" s="7" t="str">
+      <c r="P28" s="5" t="str">
         <v>pages/news.vue 加 isNewItem(releaseTime) helper（7 天內判斷），對應消息右上角顯示橘色 NEW pill 標籤（_appBody.scss .badge-new）。</v>
       </c>
     </row>
@@ -6315,54 +6419,54 @@
       </c>
     </row>
     <row r="46" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A46" s="7">
+      <c r="A46" s="5">
         <v>44</v>
       </c>
-      <c r="B46" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C46" s="7" t="str">
+      <c r="B46" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C46" s="5" t="str">
         <v>關於長穩</v>
       </c>
-      <c r="D46" s="7" t="str">
-        <v/>
-      </c>
-      <c r="E46" s="7" t="str">
+      <c r="D46" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E46" s="5" t="str">
         <v>提升</v>
       </c>
-      <c r="F46" s="7" t="str">
+      <c r="F46" s="5" t="str">
         <v>視覺</v>
       </c>
-      <c r="G46" s="7" t="str">
+      <c r="G46" s="5" t="str">
         <v>低</v>
       </c>
-      <c r="H46" s="7" t="str">
+      <c r="H46" s="5" t="str">
         <v>三大核心圖示為靜態 SVG</v>
       </c>
-      <c r="I46" s="7" t="str">
+      <c r="I46" s="5" t="str">
         <v>環境保育/人才培育/社會關懷用靜態 &lt;i class="how-logo"&gt;</v>
       </c>
-      <c r="J46" s="7" t="str">
+      <c r="J46" s="5" t="str">
         <v>加入 SVG 動畫</v>
       </c>
-      <c r="K46" s="7" t="str">
+      <c r="K46" s="5" t="str">
         <v>pages/about.vue</v>
       </c>
-      <c r="L46" s="7" t="str" xml:space="preserve">
+      <c r="L46" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">pages/about.vue_x000d__x000d__x000d_
 assets/style/components/_appBody_about.scss_x000d__x000d__x000d_
 assets/style/_animation.scss</v>
       </c>
-      <c r="M46" s="7" t="str">
+      <c r="M46" s="5" t="str">
         <v>確認無任何動畫 class 或 JS</v>
       </c>
-      <c r="N46" s="7" t="str">
+      <c r="N46" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O46" s="7" t="str">
+      <c r="O46" s="5" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P46" s="7" t="str">
+      <c r="P46" s="5" t="str">
         <v>icon SVG 本身仍為靜態，但已包入 Dynamic Island 互動卡片（.how-content）：hover/click toggle 觸發整體 morph 動畫（grid-template-rows 展開、translateY 浮起、background opacity overlay 漸層切換、border 露出青綠光暈）。視覺已不再死板。</v>
       </c>
     </row>
@@ -6826,55 +6930,55 @@
       </c>
     </row>
     <row r="56" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A56" s="3">
+      <c r="A56" s="5">
         <v>54</v>
       </c>
-      <c r="B56" s="3" t="str">
-        <v>V</v>
-      </c>
-      <c r="C56" s="3" t="str">
+      <c r="B56" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C56" s="5" t="str">
         <v>共用元件</v>
       </c>
-      <c r="D56" s="3" t="str">
+      <c r="D56" s="5" t="str">
         <v>CompSelect</v>
       </c>
-      <c r="E56" s="3" t="str">
+      <c r="E56" s="5" t="str">
         <v>修復</v>
       </c>
-      <c r="F56" s="3" t="str">
+      <c r="F56" s="5" t="str">
         <v>互動</v>
       </c>
-      <c r="G56" s="3" t="str">
+      <c r="G56" s="5" t="str">
         <v>高</v>
       </c>
-      <c r="H56" s="3" t="str">
+      <c r="H56" s="5" t="str">
         <v>完全不支援鍵盤操作</v>
       </c>
-      <c r="I56" s="3" t="str">
+      <c r="I56" s="5" t="str">
         <v>grep keydown/keyup 三個 Select 元件回傳 0 筆，僅 @click 開關</v>
       </c>
-      <c r="J56" s="3" t="str">
+      <c r="J56" s="5" t="str">
         <v>加入鍵盤事件（上下鍵、Enter、Esc）</v>
       </c>
-      <c r="K56" s="3" t="str">
+      <c r="K56" s="5" t="str">
         <v>components/CompSelect*.vue</v>
       </c>
-      <c r="L56" s="3" t="str" xml:space="preserve">
+      <c r="L56" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">components/CompSelect.vue_x000d__x000d__x000d_
 components/CompSelectRecipient.vue_x000d__x000d__x000d_
 components/CompSelectElse.vue</v>
       </c>
-      <c r="M56" s="3" t="str">
+      <c r="M56" s="5" t="str">
         <v>確認無任何鍵盤事件處理</v>
       </c>
-      <c r="N56" s="3" t="str">
-        <v>待處理</v>
-      </c>
-      <c r="O56" s="3" t="str">
-        <v/>
-      </c>
-      <c r="P56" s="3" t="str">
-        <v/>
+      <c r="N56" s="5" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O56" s="5" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="P56" s="5" t="str">
+        <v>Round 8 #114 (CompSelect 鍵盤操作) 已涵蓋此項。3 個 component (CompSelect / CompSelectRecipient / CompSelectElse) 已加 tabindex / role / aria-* + Enter/Space toggle + Esc close + Arrow Up/Down 切 focused 項目。詳見 #114 備註。</v>
       </c>
     </row>
     <row r="57" ht="45" customHeight="1" xml:space="preserve">
@@ -7088,106 +7192,106 @@
       </c>
     </row>
     <row r="61" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A61" s="7">
+      <c r="A61" s="5">
         <v>59</v>
       </c>
-      <c r="B61" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C61" s="7" t="str">
+      <c r="B61" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C61" s="5" t="str">
         <v>全站微互動</v>
       </c>
-      <c r="D61" s="7" t="str">
-        <v/>
-      </c>
-      <c r="E61" s="7" t="str">
+      <c r="D61" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E61" s="5" t="str">
         <v>提升</v>
       </c>
-      <c r="F61" s="7" t="str">
+      <c r="F61" s="5" t="str">
         <v>視覺</v>
       </c>
-      <c r="G61" s="7" t="str">
+      <c r="G61" s="5" t="str">
         <v>低</v>
       </c>
-      <c r="H61" s="7" t="str">
+      <c r="H61" s="5" t="str">
         <v>卡片 hover 效果升級</v>
       </c>
-      <c r="I61" s="7" t="str">
+      <c r="I61" s="5" t="str">
         <v>目前卡片 hover 效果單調</v>
       </c>
-      <c r="J61" s="7" t="str">
+      <c r="J61" s="5" t="str">
         <v>上浮 4px + 陰影加深</v>
       </c>
-      <c r="K61" s="7" t="str">
+      <c r="K61" s="5" t="str">
         <v>全站</v>
       </c>
-      <c r="L61" s="7" t="str" xml:space="preserve">
+      <c r="L61" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">assets/style/components/_appBody.scss_x000d__x000d__x000d_
 assets/style/components/_appBody_index.scss_x000d__x000d__x000d_
 assets/style/components/_appBodyChild_ifare.scss</v>
       </c>
-      <c r="M61" s="7" t="str">
+      <c r="M61" s="5" t="str">
         <v>功能確實不存在（待實測確認現有 hover）</v>
       </c>
-      <c r="N61" s="7" t="str">
+      <c r="N61" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O61" s="7" t="str">
+      <c r="O61" s="5" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P61" s="7" t="str">
+      <c r="P61" s="5" t="str">
         <v>_main.scss 為 .result-item / .article-item / .agency-item 加 hover translateY(-3px) + box-shadow，active translateY(-1px) 回彈。純 GPU 屬性，不觸發 layout 重繪。</v>
       </c>
     </row>
     <row r="62" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A62" s="5">
+      <c r="A62" s="4">
         <v>60</v>
       </c>
-      <c r="B62" s="5" t="str">
-        <v>V</v>
-      </c>
-      <c r="C62" s="5" t="str">
+      <c r="B62" s="4" t="str">
+        <v>V</v>
+      </c>
+      <c r="C62" s="4" t="str">
         <v>全站微互動</v>
       </c>
-      <c r="D62" s="5" t="str">
-        <v/>
-      </c>
-      <c r="E62" s="5" t="str">
+      <c r="D62" s="4" t="str">
+        <v/>
+      </c>
+      <c r="E62" s="4" t="str">
         <v>提升</v>
       </c>
-      <c r="F62" s="5" t="str">
+      <c r="F62" s="4" t="str">
         <v>視覺</v>
       </c>
-      <c r="G62" s="5" t="str">
+      <c r="G62" s="4" t="str">
         <v>低</v>
       </c>
-      <c r="H62" s="5" t="str">
+      <c r="H62" s="4" t="str">
         <v>CTA 按鈕互動效果</v>
       </c>
-      <c r="I62" s="5" t="str">
+      <c r="I62" s="4" t="str">
         <v>按鈕缺乏觸覺回饋</v>
       </c>
-      <c r="J62" s="5" t="str">
+      <c r="J62" s="4" t="str">
         <v>hover 按壓回彈 + 點擊漣漪效果</v>
       </c>
-      <c r="K62" s="5" t="str">
+      <c r="K62" s="4" t="str">
         <v>全站</v>
       </c>
-      <c r="L62" s="5" t="str" xml:space="preserve">
+      <c r="L62" s="4" t="str" xml:space="preserve">
         <v xml:space="preserve">assets/style/components/_button.scss_x000d__x000d__x000d_
 assets/style/_font.scss_x000d__x000d__x000d_
 assets/style/rwd/_rwd_button.scss</v>
       </c>
-      <c r="M62" s="5" t="str">
+      <c r="M62" s="4" t="str">
         <v>功能確實不存在</v>
       </c>
-      <c r="N62" s="5" t="str">
+      <c r="N62" s="4" t="str">
         <v>部分修正</v>
       </c>
-      <c r="O62" s="5" t="str">
+      <c r="O62" s="4" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P62" s="5" t="str">
+      <c r="P62" s="4" t="str">
         <v>_main.scss 為 .btn-filter / .btn-tag / .btn-retry 加 hover translateY(-1px) + active scale(0.97) 按壓回彈。原訴求「點擊漣漪效果」尚未做。</v>
       </c>
     </row>
@@ -7703,55 +7807,55 @@
       </c>
     </row>
     <row r="73" ht="45" customHeight="1" xml:space="preserve">
-      <c r="A73" s="5">
+      <c r="A73" s="4">
         <v>71</v>
       </c>
-      <c r="B73" s="5" t="str">
-        <v>V</v>
-      </c>
-      <c r="C73" s="5" t="str">
+      <c r="B73" s="4" t="str">
+        <v>V</v>
+      </c>
+      <c r="C73" s="4" t="str">
         <v>全站通用</v>
       </c>
-      <c r="D73" s="5" t="str">
-        <v/>
-      </c>
-      <c r="E73" s="5" t="str">
+      <c r="D73" s="4" t="str">
+        <v/>
+      </c>
+      <c r="E73" s="4" t="str">
         <v>修復</v>
       </c>
-      <c r="F73" s="5" t="str">
+      <c r="F73" s="4" t="str">
         <v>RWD</v>
       </c>
-      <c r="G73" s="5" t="str">
+      <c r="G73" s="4" t="str">
         <v>高</v>
       </c>
-      <c r="H73" s="5" t="str">
+      <c r="H73" s="4" t="str">
         <v>多處觸控目標小於 44x44px</v>
       </c>
-      <c r="I73" s="5" t="str">
+      <c r="I73" s="4" t="str">
         <v>分頁按鈕 30x30px、.btn-reset height:32px、.btn-advance height:40px</v>
       </c>
-      <c r="J73" s="5" t="str">
+      <c r="J73" s="4" t="str">
         <v>確保所有可點擊元素最小 44x44px</v>
       </c>
-      <c r="K73" s="5" t="str">
+      <c r="K73" s="4" t="str">
         <v>全站</v>
       </c>
-      <c r="L73" s="5" t="str" xml:space="preserve">
+      <c r="L73" s="4" t="str" xml:space="preserve">
         <v xml:space="preserve">assets/style/components/_compPage.scss_x000d__x000d__x000d_
 assets/style/components/_button.scss_x000d__x000d__x000d_
 assets/style/components/_compSelect.scss_x000d__x000d__x000d_
 assets/style/rwd/_rwd_compPage.scss</v>
       </c>
-      <c r="M73" s="5" t="str">
+      <c r="M73" s="4" t="str">
         <v>確認多處尺寸低於 44px 標準</v>
       </c>
-      <c r="N73" s="5" t="str">
+      <c r="N73" s="4" t="str">
         <v>部分修正</v>
       </c>
-      <c r="O73" s="5" t="str">
+      <c r="O73" s="4" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P73" s="5" t="str">
+      <c r="P73" s="4" t="str">
         <v>footer .btn-social 高度從 40px 提升到 44px（LINE / Facebook 兩按鈕符合 iOS HIG 觸控標準）。CompPage 分頁箭頭、btn-reset、btn-advance、CompSelect 等其他元件尚未套用 44px 標準。</v>
       </c>
     </row>
@@ -8148,52 +8252,52 @@
       </c>
     </row>
     <row r="82" ht="45" customHeight="1">
-      <c r="A82" s="5">
+      <c r="A82" s="4">
         <v>80</v>
       </c>
-      <c r="B82" s="5" t="str">
-        <v>V</v>
-      </c>
-      <c r="C82" s="5" t="str">
+      <c r="B82" s="4" t="str">
+        <v>V</v>
+      </c>
+      <c r="C82" s="4" t="str">
         <v>全站通用</v>
       </c>
-      <c r="D82" s="5" t="str">
-        <v/>
-      </c>
-      <c r="E82" s="5" t="str">
+      <c r="D82" s="4" t="str">
+        <v/>
+      </c>
+      <c r="E82" s="4" t="str">
         <v>修復</v>
       </c>
-      <c r="F82" s="5" t="str">
+      <c r="F82" s="4" t="str">
         <v>互動</v>
       </c>
-      <c r="G82" s="5" t="str">
+      <c r="G82" s="4" t="str">
         <v>高</v>
       </c>
-      <c r="H82" s="5" t="str">
+      <c r="H82" s="4" t="str">
         <v>缺少載入失敗與重試機制</v>
       </c>
-      <c r="I82" s="5" t="str">
+      <c r="I82" s="4" t="str">
         <v>目前清單有 loading / skeleton / toast，但尚未明確區分 API 載入失敗狀態與重試機制。</v>
       </c>
-      <c r="J82" s="5" t="str">
+      <c r="J82" s="4" t="str">
         <v>建立統一錯誤狀態元件，針對 API 失敗提供錯誤訊息、retry 按鈕，並區分空資料與載入失敗。</v>
       </c>
-      <c r="K82" s="5" t="str">
+      <c r="K82" s="4" t="str">
         <v>全站</v>
       </c>
-      <c r="L82" s="5" t="str">
+      <c r="L82" s="4" t="str">
         <v>pages/news.vue pages/articles.vue pages/collaborator.vue pages/ifare/result.vue layouts/default.vue components/</v>
       </c>
-      <c r="M82" s="5" t="str">
+      <c r="M82" s="4" t="str">
         <v>現有清單多著重 loading 與空狀態，未明列 error state。</v>
       </c>
-      <c r="N82" s="5" t="str">
+      <c r="N82" s="4" t="str">
         <v>部分修正</v>
       </c>
-      <c r="O82" s="5" t="str">
+      <c r="O82" s="4" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P82" s="5" t="str">
+      <c r="P82" s="4" t="str">
         <v>pages/news.vue 已實作 hasError + .btn-retry 按鈕模式（搭配 _animation.scss .part-error 樣式）。articles.vue / collaborator.vue / ifare/result.vue 三頁尚未套用同一錯誤狀態元件。</v>
       </c>
     </row>
@@ -8491,718 +8595,718 @@
       </c>
     </row>
     <row r="90" ht="100.8" customHeight="1" xml:space="preserve">
-      <c r="A90" s="7">
+      <c r="A90" s="5">
         <v>88</v>
       </c>
-      <c r="B90" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C90" s="7" t="str">
+      <c r="B90" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C90" s="5" t="str">
         <v>i-Fare 福利查詢</v>
       </c>
-      <c r="D90" s="7" t="str">
+      <c r="D90" s="5" t="str">
         <v>搜尋介面</v>
       </c>
-      <c r="E90" s="7" t="str">
+      <c r="E90" s="5" t="str">
         <v>提升</v>
       </c>
-      <c r="F90" s="7" t="str">
+      <c r="F90" s="5" t="str">
         <v>黏著</v>
       </c>
-      <c r="G90" s="7" t="str">
+      <c r="G90" s="5" t="str">
         <v>中</v>
       </c>
-      <c r="H90" s="7" t="str">
+      <c r="H90" s="5" t="str">
         <v>新增關鍵字搜尋輸入欄</v>
       </c>
-      <c r="I90" s="7" t="str">
+      <c r="I90" s="5" t="str">
         <v>原本搜尋只能用三個下拉選單（政策類別、受助對象、地區），缺少自由文字搜尋入口</v>
       </c>
-      <c r="J90" s="7" t="str">
+      <c r="J90" s="5" t="str">
         <v>ifare 與結果頁各加 &lt;input.input-keyword&gt;（含 Enter 快捷鍵），搜尋條件擴增 keyword 參數，後端 LIKE 查詢</v>
       </c>
-      <c r="K90" s="7" t="str">
+      <c r="K90" s="5" t="str">
         <v>pages/ifare.vue pages/ifare/result.vue</v>
       </c>
-      <c r="L90" s="7" t="str" xml:space="preserve">
+      <c r="L90" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">pages/ifare.vue_x000d__x000d__x000d_
 pages/ifare/result.vue_x000d__x000d__x000d_
 assets/style/components/_appBody_ifare.scss_x000d__x000d__x000d_
 assets/style/components/_appBodyChild_ifare.scss</v>
       </c>
-      <c r="M90" s="7" t="str">
+      <c r="M90" s="5" t="str">
         <v>改版補登；後端 IFare_API.Application/Fare/Policy/* 已加 Keyword filter</v>
       </c>
-      <c r="N90" s="7" t="str">
+      <c r="N90" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O90" s="7" t="str">
+      <c r="O90" s="5" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P90" s="7" t="str">
+      <c r="P90" s="5" t="str">
         <v>改版補登；前端 Search() 已帶 keyword 參數，API 傳 Keyword 欄位</v>
       </c>
     </row>
     <row r="91" ht="57.6" customHeight="1">
-      <c r="A91" s="7">
+      <c r="A91" s="5">
         <v>89</v>
       </c>
-      <c r="B91" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C91" s="7" t="str">
+      <c r="B91" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C91" s="5" t="str">
         <v>i-Fare 福利查詢</v>
       </c>
-      <c r="D91" s="7" t="str">
+      <c r="D91" s="5" t="str">
         <v>查詢結果</v>
       </c>
-      <c r="E91" s="7" t="str">
+      <c r="E91" s="5" t="str">
         <v>修復</v>
       </c>
-      <c r="F91" s="7" t="str">
+      <c r="F91" s="5" t="str">
         <v>互動</v>
       </c>
-      <c r="G91" s="7" t="str">
+      <c r="G91" s="5" t="str">
         <v>中</v>
       </c>
-      <c r="H91" s="7" t="str">
+      <c r="H91" s="5" t="str">
         <v>結果頁未支援 URL query 初始化</v>
       </c>
-      <c r="I91" s="7" t="str">
+      <c r="I91" s="5" t="str">
         <v>結果頁從 ifare 跳轉過來時若重整或從外部進入，搜尋條件無法保留</v>
       </c>
-      <c r="J91" s="7" t="str">
+      <c r="J91" s="5" t="str">
         <v>解析 route.query 初始化各 ref（policy / recipient / area / keyword），支援深度連結與重整保留條件</v>
       </c>
-      <c r="K91" s="7" t="str">
+      <c r="K91" s="5" t="str">
         <v>pages/ifare/result.vue</v>
       </c>
-      <c r="L91" s="7" t="str">
+      <c r="L91" s="5" t="str">
         <v>pages/ifare/result.vue</v>
       </c>
-      <c r="M91" s="7" t="str">
+      <c r="M91" s="5" t="str">
         <v>改版補登；搭配 #88 關鍵字欄位一起實作</v>
       </c>
-      <c r="N91" s="7" t="str">
+      <c r="N91" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O91" s="7" t="str">
+      <c r="O91" s="5" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P91" s="7" t="str">
+      <c r="P91" s="5" t="str">
         <v>改版補登</v>
       </c>
     </row>
     <row r="92" ht="57.6" customHeight="1">
-      <c r="A92" s="7">
+      <c r="A92" s="5">
         <v>90</v>
       </c>
-      <c r="B92" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C92" s="7" t="str">
+      <c r="B92" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C92" s="5" t="str">
         <v>i-Fare 福利查詢</v>
       </c>
-      <c r="D92" s="7" t="str">
+      <c r="D92" s="5" t="str">
         <v>搜尋介面</v>
       </c>
-      <c r="E92" s="7" t="str">
+      <c r="E92" s="5" t="str">
         <v>修復</v>
       </c>
-      <c r="F92" s="7" t="str">
+      <c r="F92" s="5" t="str">
         <v>RWD</v>
       </c>
-      <c r="G92" s="7" t="str">
+      <c r="G92" s="5" t="str">
         <v>低</v>
       </c>
-      <c r="H92" s="7" t="str">
+      <c r="H92" s="5" t="str">
         <v>搜尋按鈕區手機版橫排擠壓</v>
       </c>
-      <c r="I92" s="7" t="str">
+      <c r="I92" s="5" t="str">
         <v>.item-bottom 原為橫排，手機版按鈕和提示文字擠在一起</v>
       </c>
-      <c r="J92" s="7" t="str">
+      <c r="J92" s="5" t="str">
         <v>_appBody_ifare.scss .item-bottom 改 flex-direction: column + gap + 居中，並加 .filter-hint 樣式</v>
       </c>
-      <c r="K92" s="7" t="str">
+      <c r="K92" s="5" t="str">
         <v>pages/ifare.vue</v>
       </c>
-      <c r="L92" s="7" t="str">
+      <c r="L92" s="5" t="str">
         <v>iFare_Frontend/assets/style/components/_appBody_ifare.scss</v>
       </c>
-      <c r="M92" s="7" t="str">
+      <c r="M92" s="5" t="str">
         <v>改版補登；搭配 #1 disabled 移除後新增的提示文字調整版面</v>
       </c>
-      <c r="N92" s="7" t="str">
+      <c r="N92" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O92" s="7" t="str">
+      <c r="O92" s="5" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P92" s="7" t="str">
+      <c r="P92" s="5" t="str">
         <v>改版補登</v>
       </c>
     </row>
     <row r="93" ht="86.40000000000002" customHeight="1" xml:space="preserve">
-      <c r="A93" s="7">
+      <c r="A93" s="5">
         <v>91</v>
       </c>
-      <c r="B93" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C93" s="7" t="str">
+      <c r="B93" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C93" s="5" t="str">
         <v>共用元件</v>
       </c>
-      <c r="D93" s="7" t="str">
+      <c r="D93" s="5" t="str">
         <v>AppFooter</v>
       </c>
-      <c r="E93" s="7" t="str">
+      <c r="E93" s="5" t="str">
         <v>提升</v>
       </c>
-      <c r="F93" s="7" t="str">
+      <c r="F93" s="5" t="str">
         <v>視覺</v>
       </c>
-      <c r="G93" s="7" t="str">
+      <c r="G93" s="5" t="str">
         <v>低</v>
       </c>
-      <c r="H93" s="7" t="str">
+      <c r="H93" s="5" t="str">
         <v>Footer 聯絡資訊缺 icon</v>
       </c>
-      <c r="I93" s="7" t="str">
+      <c r="I93" s="5" t="str">
         <v>footer 4 個 label（聯絡電話 / 聯絡信箱 / 地址 / 服務時間）僅有純文字，缺乏視覺辨識</v>
       </c>
-      <c r="J93" s="7" t="str">
+      <c r="J93" s="5" t="str">
         <v>4 個 label 前各加對應 icon（Tel / Mail / Address / Clock），與站內既有 icon 風格一致</v>
       </c>
-      <c r="K93" s="7" t="str">
+      <c r="K93" s="5" t="str">
         <v>components/AppFooter.vue</v>
       </c>
-      <c r="L93" s="7" t="str" xml:space="preserve">
+      <c r="L93" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/components/AppFooter.vue_x000d__x000d__x000d_
 assets/style/components/_appFooter.scss_x000d__x000d__x000d_
 assets/style/_font.scss_x000d__x000d__x000d_
 assets/img/Mail.svg (新增)_x000d__x000d__x000d_
 assets/img/Clock.svg (新增)</v>
       </c>
-      <c r="M93" s="7" t="str">
+      <c r="M93" s="5" t="str">
         <v>改版補登；新增 Mail.svg + Clock.svg 用 mask-image 著色為 rgba(white,.7)，沿用既有 Tel.svg / Location.svg。原 ::before content 的 CSS-only label 改為 HTML &lt;span class="footer-info-label"&gt; 結構</v>
       </c>
-      <c r="N93" s="7" t="str">
+      <c r="N93" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O93" s="7" t="str">
+      <c r="O93" s="5" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P93" s="7" t="str">
+      <c r="P93" s="5" t="str">
         <v>改版補登</v>
       </c>
     </row>
     <row r="94" ht="273.6" customHeight="1" xml:space="preserve">
-      <c r="A94" s="7">
+      <c r="A94" s="5">
         <v>92</v>
       </c>
-      <c r="B94" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C94" s="7" t="str">
+      <c r="B94" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C94" s="5" t="str">
         <v>共用元件</v>
       </c>
-      <c r="D94" s="7" t="str">
+      <c r="D94" s="5" t="str">
         <v>AppFooter</v>
       </c>
-      <c r="E94" s="7" t="str">
+      <c r="E94" s="5" t="str">
         <v>提升</v>
       </c>
-      <c r="F94" s="7" t="str">
+      <c r="F94" s="5" t="str">
         <v>互動</v>
       </c>
-      <c r="G94" s="7" t="str">
+      <c r="G94" s="5" t="str">
         <v>中</v>
       </c>
-      <c r="H94" s="7" t="str">
+      <c r="H94" s="5" t="str">
         <v>社群連結 LINE / Facebook 分散兩處</v>
       </c>
-      <c r="I94" s="7" t="str">
+      <c r="I94" s="5" t="str">
         <v>LINE 在「進一步瞭解更多」CTA 區塊內，Facebook 在獨立 .part-middle 區塊；兩者都是社群媒體應該放一起</v>
       </c>
-      <c r="J94" s="7" t="str">
+      <c r="J94" s="5" t="str">
         <v>把 Facebook 從 .part-middle 移到 .card-more 內 .card-more-socials div 與 LINE 並排，整合為單一社群區塊</v>
       </c>
-      <c r="K94" s="7" t="str">
+      <c r="K94" s="5" t="str">
         <v>components/AppFooter.vue</v>
       </c>
-      <c r="L94" s="7" t="str" xml:space="preserve">
+      <c r="L94" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/components/AppFooter.vue_x000d__x000d__x000d_
 assets/style/components/_appFooter.scss_x000d__x000d__x000d_
 assets/style/rwd/_rwd_appFooter.scss</v>
       </c>
-      <c r="M94" s="7" t="str">
+      <c r="M94" s="5" t="str">
         <v>改版補登；移除原 .part-middle 與 .link-track 樣式</v>
       </c>
-      <c r="N94" s="7" t="str">
+      <c r="N94" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O94" s="7" t="str">
+      <c r="O94" s="5" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P94" s="7" t="str">
+      <c r="P94" s="5" t="str">
         <v>改版補登；同步修桌面 1025-1280px overflow（加 FB 後 .card-more 內容寬度 ~1300px 會爆）：.card-more 加 flex-wrap: wrap + max-width: calc(100% - 64px)；.info-more 加 max-width: 480px 讓長文字桌面換 2 行</v>
       </c>
     </row>
     <row r="95" ht="129.6" customHeight="1" xml:space="preserve">
-      <c r="A95" s="7">
+      <c r="A95" s="5">
         <v>93</v>
       </c>
-      <c r="B95" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C95" s="7" t="str">
+      <c r="B95" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C95" s="5" t="str">
         <v>關於長穩</v>
       </c>
-      <c r="D95" s="7" t="str">
-        <v/>
-      </c>
-      <c r="E95" s="7" t="str">
+      <c r="D95" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E95" s="5" t="str">
         <v>提升</v>
       </c>
-      <c r="F95" s="7" t="str">
+      <c r="F95" s="5" t="str">
         <v>互動</v>
       </c>
-      <c r="G95" s="7" t="str">
+      <c r="G95" s="5" t="str">
         <v>中</v>
       </c>
-      <c r="H95" s="7" t="str">
+      <c r="H95" s="5" t="str">
         <v>About 三大核心介紹缺乏互動性</v>
       </c>
-      <c r="I95" s="7" t="str">
+      <c r="I95" s="5" t="str">
         <v>環境保育/人才培育/社會關懷三張卡片原為靜態圖文，使用者掃過無視覺反應，缺乏吸引點擊探索的動機</v>
       </c>
-      <c r="J95" s="7" t="str">
+      <c r="J95" s="5" t="str">
         <v>改造為 iOS Dynamic Island 風格 morph 卡片：暖象牙白漸層底 + 圓角 28px + 預設只露 icon+標題 → hover/click toggle 平滑展開內文（grid-template-rows trick）+ translateY 浮起 + 邊框露出青綠光暈</v>
       </c>
-      <c r="K95" s="7" t="str">
+      <c r="K95" s="5" t="str">
         <v>pages/about.vue</v>
       </c>
-      <c r="L95" s="7" t="str" xml:space="preserve">
+      <c r="L95" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/pages/about.vue_x000d__x000d__x000d_
 assets/style/components/_appBody_about.scss_x000d__x000d__x000d_
 assets/style/rwd/_rwd_about.scss</v>
       </c>
-      <c r="M95" s="7" t="str">
+      <c r="M95" s="5" t="str">
         <v>改版補登；HTML 重組（icon+title 合進 .how-top、info 包 .how-info-wrap）；script 加 activeHow ref + toggleHow handler；keyboard a11y (Enter/Space) 與 tabindex；GPU 優化（will-change + ::before opacity overlay 取代 gradient transition）；Apple spring easing cubic-bezier(0.32, 0.72, 0, 1)</v>
       </c>
-      <c r="N95" s="7" t="str">
+      <c r="N95" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O95" s="7" t="str">
+      <c r="O95" s="5" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P95" s="7" t="str">
+      <c r="P95" s="5" t="str">
         <v>改版補登；對應 #44 三大核心圖示靜態問題已連動修正</v>
       </c>
     </row>
     <row r="96" ht="100.8" customHeight="1">
-      <c r="A96" s="7">
+      <c r="A96" s="5">
         <v>94</v>
       </c>
-      <c r="B96" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C96" s="7" t="str">
+      <c r="B96" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C96" s="5" t="str">
         <v>關於長穩</v>
       </c>
-      <c r="D96" s="7" t="str">
-        <v/>
-      </c>
-      <c r="E96" s="7" t="str">
+      <c r="D96" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E96" s="5" t="str">
         <v>提升</v>
       </c>
-      <c r="F96" s="7" t="str">
+      <c r="F96" s="5" t="str">
         <v>視覺</v>
       </c>
-      <c r="G96" s="7" t="str">
+      <c r="G96" s="5" t="str">
         <v>低</v>
       </c>
-      <c r="H96" s="7" t="str">
+      <c r="H96" s="5" t="str">
         <v>About 成員照片缺 hover 互動</v>
       </c>
-      <c r="I96" s="7" t="str">
+      <c r="I96" s="5" t="str">
         <v>陳進財/鄔筠軒/顏杏蓉三位成員區塊原無 hover 反饋，掃過時視覺無變化</v>
       </c>
-      <c r="J96" s="7" t="str">
+      <c r="J96" s="5" t="str">
         <v>陳進財/鄔筠軒整組 hover：照片 scale(1.06) + 白框 scale(1.03) + box-shadow 加深 + 橘色標牌 translateY(-4px)；顏杏蓉（無照片）標牌 hover translateY(-4px) + scale(1.04)</v>
       </c>
-      <c r="K96" s="7" t="str">
+      <c r="K96" s="5" t="str">
         <v>pages/about.vue</v>
       </c>
-      <c r="L96" s="7" t="str">
+      <c r="L96" s="5" t="str">
         <v>iFare_Frontend/assets/style/components/_appBody_about.scss</v>
       </c>
-      <c r="M96" s="7" t="str">
+      <c r="M96" s="5" t="str">
         <v>改版補登；同套 cubic-bezier(0.32, 0.72, 0, 1) easing；will-change: transform 給 .member-photo 預先建 GPU layer</v>
       </c>
-      <c r="N96" s="7" t="str">
+      <c r="N96" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O96" s="7" t="str">
+      <c r="O96" s="5" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P96" s="7" t="str">
+      <c r="P96" s="5" t="str">
         <v>改版補登</v>
       </c>
     </row>
     <row r="97" ht="57.6" customHeight="1">
-      <c r="A97" s="7">
+      <c r="A97" s="5">
         <v>95</v>
       </c>
-      <c r="B97" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C97" s="7" t="str">
+      <c r="B97" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C97" s="5" t="str">
         <v>關於長穩</v>
       </c>
-      <c r="D97" s="7" t="str">
-        <v/>
-      </c>
-      <c r="E97" s="7" t="str">
+      <c r="D97" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E97" s="5" t="str">
         <v>提升</v>
       </c>
-      <c r="F97" s="7" t="str">
+      <c r="F97" s="5" t="str">
         <v>視覺</v>
       </c>
-      <c r="G97" s="7" t="str">
+      <c r="G97" s="5" t="str">
         <v>低</v>
       </c>
-      <c r="H97" s="7" t="str">
+      <c r="H97" s="5" t="str">
         <v>About 底部 CTA 連結缺 hover micro-animation</v>
       </c>
-      <c r="I97" s="7" t="str">
+      <c r="I97" s="5" t="str">
         <v>「前往 i-Fare」與「查看最新消息」兩個 advance-link 原為靜態，hover 無互動反饋，無法強化「點我前進」訊號</v>
       </c>
-      <c r="J97" s="7" t="str">
+      <c r="J97" s="5" t="str">
         <v>連結 hover 時 translateY(-2px) 上浮，箭頭 icon translateX(6px) 向右滑出，引導視線前進</v>
       </c>
-      <c r="K97" s="7" t="str">
+      <c r="K97" s="5" t="str">
         <v>pages/about.vue</v>
       </c>
-      <c r="L97" s="7" t="str">
+      <c r="L97" s="5" t="str">
         <v>iFare_Frontend/assets/style/components/_appBody_about.scss</v>
       </c>
-      <c r="M97" s="7" t="str">
+      <c r="M97" s="5" t="str">
         <v>改版補登；統一 cubic-bezier(0.32, 0.72, 0, 1) easing 0.22s</v>
       </c>
-      <c r="N97" s="7" t="str">
+      <c r="N97" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O97" s="7" t="str">
+      <c r="O97" s="5" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P97" s="7" t="str">
+      <c r="P97" s="5" t="str">
         <v>改版補登</v>
       </c>
     </row>
     <row r="98" ht="129.6" customHeight="1" xml:space="preserve">
-      <c r="A98" s="7">
+      <c r="A98" s="5">
         <v>96</v>
       </c>
-      <c r="B98" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C98" s="7" t="str">
+      <c r="B98" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C98" s="5" t="str">
         <v>最新消息</v>
       </c>
-      <c r="D98" s="7" t="str">
-        <v/>
-      </c>
-      <c r="E98" s="7" t="str">
+      <c r="D98" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E98" s="5" t="str">
         <v>提升</v>
       </c>
-      <c r="F98" s="7" t="str">
+      <c r="F98" s="5" t="str">
         <v>視覺</v>
       </c>
-      <c r="G98" s="7" t="str">
+      <c r="G98" s="5" t="str">
         <v>中</v>
       </c>
-      <c r="H98" s="7" t="str">
+      <c r="H98" s="5" t="str">
         <v>News 列表呈現升級為浮起卡片 + 入場動畫 + 日期 pill</v>
       </c>
-      <c r="I98" s="7" t="str">
+      <c r="I98" s="5" t="str">
         <v>原本最新消息為「底線分隔的清單列」，hover 只是淡白底 + 箭頭轉橘，視覺扁平、缺乏互動感、日期不醒目、長內文無截斷</v>
       </c>
-      <c r="J98" s="7" t="str">
+      <c r="J98" s="5" t="str">
         <v>列表整體升級：圓角 16px 浮起卡片（white .7 + shadow）+ stagger fade-up 入場動畫（@for 1~12 each +50ms）+ 日期變橘色 pill 標籤（border + 半透明橘底）+ hover translateY(-3px) + 背景變實白 + 箭頭橘色滑右 6px</v>
       </c>
-      <c r="K98" s="7" t="str">
+      <c r="K98" s="5" t="str">
         <v>pages/news.vue</v>
       </c>
-      <c r="L98" s="7" t="str" xml:space="preserve">
+      <c r="L98" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/pages/news.vue_x000d__x000d__x000d_
 assets/style/components/_appBody.scss_x000d__x000d__x000d_
 assets/style/_animation.scss_x000d__x000d__x000d_
 assets/style/rwd/_rwd.scss</v>
       </c>
-      <c r="M98" s="7" t="str">
+      <c r="M98" s="5" t="str">
         <v>改版補登；@keyframes newsItemEnter 放 _animation.scss；統一 cubic-bezier(0.32, 0.72, 0, 1) easing；配色全用既有 token 沒引入新色</v>
       </c>
-      <c r="N98" s="7" t="str">
+      <c r="N98" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O98" s="7" t="str">
+      <c r="O98" s="5" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P98" s="7" t="str">
+      <c r="P98" s="5" t="str">
         <v>改版補登；同次改動連帶解決 #23 (line-clamp 2)、#24 (aria-label)、#26 (NEW badge)</v>
       </c>
     </row>
     <row r="99" ht="72" customHeight="1" xml:space="preserve">
-      <c r="A99" s="7">
+      <c r="A99" s="5">
         <v>97</v>
       </c>
-      <c r="B99" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C99" s="7" t="str">
+      <c r="B99" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C99" s="5" t="str">
         <v>共用元件</v>
       </c>
-      <c r="D99" s="7" t="str">
+      <c r="D99" s="5" t="str">
         <v>AppFooter / AppHeader</v>
       </c>
-      <c r="E99" s="7" t="str">
+      <c r="E99" s="5" t="str">
         <v>修復</v>
       </c>
-      <c r="F99" s="7" t="str">
+      <c r="F99" s="5" t="str">
         <v>互動</v>
       </c>
-      <c r="G99" s="7" t="str">
+      <c r="G99" s="5" t="str">
         <v>低</v>
       </c>
-      <c r="H99" s="7" t="str">
+      <c r="H99" s="5" t="str">
         <v>社群外連結未開新分頁，可能丟失當前頁狀態</v>
       </c>
-      <c r="I99" s="7" t="str">
+      <c r="I99" s="5" t="str">
         <v>AppFooter LINE/Facebook 與 AppHeader 手機版社群 icon 連結原為一般 &lt;a href&gt;，點擊會在當前分頁導向，使用者離開站內後返回成本高</v>
       </c>
-      <c r="J99" s="7" t="str">
+      <c r="J99" s="5" t="str">
         <v>4 個社群連結都加 target="_blank" + rel="noopener noreferrer"：開新分頁、避免反向 tabnabbing、不洩漏 referrer</v>
       </c>
-      <c r="K99" s="7" t="str">
+      <c r="K99" s="5" t="str">
         <v>components/AppFooter.vue components/AppHeader.vue</v>
       </c>
-      <c r="L99" s="7" t="str" xml:space="preserve">
+      <c r="L99" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/components/AppFooter.vue_x000d__x000d__x000d_
 iFare_Frontend/components/AppHeader.vue</v>
       </c>
-      <c r="M99" s="7" t="str">
+      <c r="M99" s="5" t="str">
         <v>改版補登；rel="noopener" 是 W3C 安全建議</v>
       </c>
-      <c r="N99" s="7" t="str">
+      <c r="N99" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O99" s="7" t="str">
+      <c r="O99" s="5" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="P99" s="7" t="str">
+      <c r="P99" s="5" t="str">
         <v>改版補登</v>
       </c>
     </row>
     <row r="100" ht="100.8" customHeight="1">
-      <c r="A100" s="7">
+      <c r="A100" s="5">
         <v>98</v>
       </c>
-      <c r="B100" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C100" s="7" t="str">
+      <c r="B100" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C100" s="5" t="str">
         <v>關於長穩</v>
       </c>
-      <c r="D100" s="7" t="str">
+      <c r="D100" s="5" t="str">
         <v>三大核心介紹</v>
       </c>
-      <c r="E100" s="7" t="str">
+      <c r="E100" s="5" t="str">
         <v>修復</v>
       </c>
-      <c r="F100" s="7" t="str">
+      <c r="F100" s="5" t="str">
         <v>互動</v>
       </c>
-      <c r="G100" s="7" t="str">
+      <c r="G100" s="5" t="str">
         <v>中</v>
       </c>
-      <c r="H100" s="7" t="str">
+      <c r="H100" s="5" t="str">
         <v>About 第一張卡 hover 完全無反應 (Round 3 副作用)</v>
       </c>
-      <c r="I100" s="7" t="str">
+      <c r="I100" s="5" t="str">
         <v>cf47cfa Round 3 加的 .section-about-member::before 視覺裝飾 (z-index:48 + 1497x1497px 圓形 + top:-300px/left:-750px) 蓋住上方 about-how 區左半邊，攔截「環境保育」第一張 morph 卡的所有 hover/click events。第二、三張位置在中右側未被覆蓋，因此正常運作。</v>
       </c>
-      <c r="J100" s="7" t="str">
+      <c r="J100" s="5" t="str">
         <v>裝飾性 ::before 加 pointer-events: none 讓 mouse events 穿透到下層的 .how-content</v>
       </c>
-      <c r="K100" s="7" t="str">
+      <c r="K100" s="5" t="str">
         <v>pages/about.vue</v>
       </c>
-      <c r="L100" s="7" t="str">
+      <c r="L100" s="5" t="str">
         <v>iFare_Frontend/assets/style/components/_appBody_about.scss</v>
       </c>
-      <c r="M100" s="7" t="str">
+      <c r="M100" s="5" t="str">
         <v>修復 cf47cfa 副作用；不影響原視覺 (radial-gradient 橘色光暈仍可見)</v>
       </c>
-      <c r="N100" s="7" t="str">
+      <c r="N100" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O100" s="7" t="str">
+      <c r="O100" s="5" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P100" s="7" t="str">
+      <c r="P100" s="5" t="str">
         <v>純 1 行 CSS 修法 (.section-about-member::before pointer-events: none)</v>
       </c>
     </row>
     <row r="101" ht="100.8" customHeight="1">
-      <c r="A101" s="7">
+      <c r="A101" s="5">
         <v>99</v>
       </c>
-      <c r="B101" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C101" s="7" t="str">
+      <c r="B101" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C101" s="5" t="str">
         <v>共用元件</v>
       </c>
-      <c r="D101" s="7" t="str">
+      <c r="D101" s="5" t="str">
         <v>AppFooter</v>
       </c>
-      <c r="E101" s="7" t="str">
+      <c r="E101" s="5" t="str">
         <v>修復</v>
       </c>
-      <c r="F101" s="7" t="str">
+      <c r="F101" s="5" t="str">
         <v>視覺</v>
       </c>
-      <c r="G101" s="7" t="str">
+      <c r="G101" s="5" t="str">
         <v>低</v>
       </c>
-      <c r="H101" s="7" t="str">
+      <c r="H101" s="5" t="str">
         <v>Footer 聯絡資訊 label 文字重複 (新舊 CSS 共存 bug)</v>
       </c>
-      <c r="I101" s="7" t="str">
+      <c r="I101" s="5" t="str">
         <v>5dfbf91/cf47cfa 把 AppFooter.vue 改用顯式 &lt;span class="footer-info-label"&gt; 顯示 label，但舊的 _font.scss `.footer-info-items [name="tel"]::before { content: "聯絡電話" }` 等 4 條規則沒清掉，造成「聯絡電話 📞 聯絡電話 (02)2797-8383」這種重複顯示</v>
       </c>
-      <c r="J101" s="7" t="str">
+      <c r="J101" s="5" t="str">
         <v>移除 _font.scss 4 個 ::before content 規則 (tel/mail/address/datetime) 與通用 [name]::before 樣式</v>
       </c>
-      <c r="K101" s="7" t="str">
+      <c r="K101" s="5" t="str">
         <v>assets/style/_font.scss</v>
       </c>
-      <c r="L101" s="7" t="str">
+      <c r="L101" s="5" t="str">
         <v>iFare_Frontend/assets/style/_font.scss</v>
       </c>
-      <c r="M101" s="7" t="str">
+      <c r="M101" s="5" t="str">
         <v>回歸測試 OK；保留 [name="tel"] font-family/color 與 [name="datetime"] span:nth-child Roboto 樣式</v>
       </c>
-      <c r="N101" s="7" t="str">
+      <c r="N101" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O101" s="7" t="str">
+      <c r="O101" s="5" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P101" s="7" t="str">
+      <c r="P101" s="5" t="str">
         <v>5dfbf91 整理時的 leftover</v>
       </c>
     </row>
     <row r="102" ht="144" customHeight="1">
-      <c r="A102" s="7">
+      <c r="A102" s="5">
         <v>100</v>
       </c>
-      <c r="B102" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C102" s="7" t="str">
+      <c r="B102" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C102" s="5" t="str">
         <v>全站通用</v>
       </c>
-      <c r="D102" s="7" t="str">
-        <v/>
-      </c>
-      <c r="E102" s="7" t="str">
+      <c r="D102" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E102" s="5" t="str">
         <v>提升</v>
       </c>
-      <c r="F102" s="7" t="str">
+      <c r="F102" s="5" t="str">
         <v>互動</v>
       </c>
-      <c r="G102" s="7" t="str">
+      <c r="G102" s="5" t="str">
         <v>中</v>
       </c>
-      <c r="H102" s="7" t="str">
+      <c r="H102" s="5" t="str">
         <v>缺乏全站一致的 hover 靈動回饋</v>
       </c>
-      <c r="I102" s="7" t="str">
+      <c r="I102" s="5" t="str">
         <v>既有 hover 散落在 .relation-item / .article-item / .card-* 等個別元件，nav 連結、Footer 按鈕、btn-icon 等沒有統一浮起回饋；使用者「鼠標移到哪都該有靈動」需求未滿足</v>
       </c>
-      <c r="J102" s="7" t="str">
+      <c r="J102" s="5" t="str">
         <v>_main.scss 加 .hover-lift utility class (Apple spring 0.22s + translateY -2px) + 自動套用到 .app-header nav / .app-footer .btn / .app-footer a / .btn-social / .btn-icon。既有自訂 hover (about morph 卡、news 浮起卡) 不受影響</v>
       </c>
-      <c r="K102" s="7" t="str">
+      <c r="K102" s="5" t="str">
         <v>assets/style/_main.scss</v>
       </c>
-      <c r="L102" s="7" t="str">
+      <c r="L102" s="5" t="str">
         <v>iFare_Frontend/assets/style/_main.scss</v>
       </c>
-      <c r="M102" s="7" t="str">
+      <c r="M102" s="5" t="str">
         <v>cubic-bezier(0.32, 0.72, 0, 1) 與 about morph 卡同套 easing</v>
       </c>
-      <c r="N102" s="7" t="str">
+      <c r="N102" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O102" s="7" t="str">
+      <c r="O102" s="5" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P102" s="7" t="str">
+      <c r="P102" s="5" t="str">
         <v>對應 #62 (.btn-filter/.btn-tag hover) 不重疊 — Round 4 涵蓋的是 nav/footer 類；ifare 搜尋按鈕的 ripple 仍待補</v>
       </c>
     </row>
     <row r="103" ht="115.2" customHeight="1" xml:space="preserve">
-      <c r="A103" s="7">
+      <c r="A103" s="5">
         <v>101</v>
       </c>
-      <c r="B103" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C103" s="7" t="str">
+      <c r="B103" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C103" s="5" t="str">
         <v>共用元件</v>
       </c>
-      <c r="D103" s="7" t="str">
+      <c r="D103" s="5" t="str">
         <v>AppHeader</v>
       </c>
-      <c r="E103" s="7" t="str">
+      <c r="E103" s="5" t="str">
         <v>提升</v>
       </c>
-      <c r="F103" s="7" t="str">
+      <c r="F103" s="5" t="str">
         <v>內容</v>
       </c>
-      <c r="G103" s="7" t="str">
+      <c r="G103" s="5" t="str">
         <v>中</v>
       </c>
-      <c r="H103" s="7" t="str">
+      <c r="H103" s="5" t="str">
         <v>缺少「未來規劃」頁面入口</v>
       </c>
-      <c r="I103" s="7" t="str">
+      <c r="I103" s="5" t="str">
         <v>主管要求增加「未來規劃」展示基金會願景，nav 應有對應入口</v>
       </c>
-      <c r="J103" s="7" t="str">
+      <c r="J103" s="5" t="str">
         <v>AppHeader 桌面 nav 在 公益夥伴 與 i-Fare 之間插入「未來規劃」連結；行動 nav 加在最後 (與既有 i-Fare/公益夥伴 mobile 順序一致)；新增 pages/future.vue 標題 + FUTURE shadow + 「內容建置中，敬請期待」佔位</v>
       </c>
-      <c r="K103" s="7" t="str">
+      <c r="K103" s="5" t="str">
         <v>components/AppHeader.vue + pages/future.vue (新)</v>
       </c>
-      <c r="L103" s="7" t="str" xml:space="preserve">
+      <c r="L103" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/components/AppHeader.vue_x000d__x000d__x000d_
 iFare_Frontend/pages/future.vue (新)</v>
       </c>
-      <c r="M103" s="7" t="str">
+      <c r="M103" s="5" t="str">
         <v>route /future 已 wire；之後接 CMS 內容由 admin 管理</v>
       </c>
-      <c r="N103" s="7" t="str">
+      <c r="N103" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O103" s="7" t="str">
+      <c r="O103" s="5" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P103" s="7" t="str">
+      <c r="P103" s="5" t="str">
         <v>頁面為佔位，等內容/設計稿確認後再填內</v>
       </c>
     </row>
@@ -9249,415 +9353,415 @@
         <v>UI 端 wiring 完成；對應後臺優化 #13 (.NET News VideoUrl 欄位)</v>
       </c>
       <c r="N104" s="5" t="str">
-        <v>部分修正</v>
+        <v>已修正</v>
       </c>
       <c r="O104" s="5" t="str">
         <v>2026-05-04</v>
       </c>
       <c r="P104" s="5" t="str">
-        <v>等 .NET 後端 News.cs entity + DTO + EF migration 加 VideoUrl 才能真實運作</v>
+        <v>Round 10: 改方案 — 從「.NET 加 VideoUrl 欄位」改成「sanitize 白名單放行 YouTube iframe」。admin 在 News HTML 編輯器內貼 YouTube「分享 → 嵌入」code，前台 useSanitize 自動驗證 src 必須是 youtube.com/embed/ 才放行，否則整個 iframe 拔掉。並自動補 sandbox / referrerpolicy / loading=lazy 安全屬性。前台 .raw-html 內 iframe 套 16:9 響應式 + 圓角 + 陰影。完全不需 .NET 配合。文件: docs/iFare_News_影片嵌入指南.md。</v>
       </c>
     </row>
     <row r="105" ht="115.2" customHeight="1" xml:space="preserve">
-      <c r="A105" s="7">
+      <c r="A105" s="5">
         <v>103</v>
       </c>
-      <c r="B105" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C105" s="7" t="str">
+      <c r="B105" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C105" s="5" t="str">
         <v>全站通用</v>
       </c>
-      <c r="D105" s="7" t="str">
-        <v/>
-      </c>
-      <c r="E105" s="7" t="str">
+      <c r="D105" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E105" s="5" t="str">
         <v>修復</v>
       </c>
-      <c r="F105" s="7" t="str">
+      <c r="F105" s="5" t="str">
         <v>程式碼</v>
       </c>
-      <c r="G105" s="7" t="str">
+      <c r="G105" s="5" t="str">
         <v>高</v>
       </c>
-      <c r="H105" s="7" t="str">
+      <c r="H105" s="5" t="str">
         <v>本機開發 API 連線失敗 (環境設定指本機 .NET，但機器沒 .NET SDK)</v>
       </c>
-      <c r="I105" s="7" t="str">
+      <c r="I105" s="5" t="str">
         <v>前台 nuxt.config.ts devProxy target 寫死 https://localhost:44312 / 後台 AjaxRef.ts baseURL prod 寫死 http://10.200.0.39 (公司內網 IP)，導致：(1) 本機 dev 抓 dropdown 全 404 (2) 後台 admin Login 失敗 (家用網路 reach 不到 10.200.0.39 內網 IP)</v>
       </c>
-      <c r="J105" s="7" t="str">
+      <c r="J105" s="5" t="str">
         <v>前台 nuxt.config.ts devProxy target 改 https://www.i-fare.org.tw/ifare_api/api/services/app；後台 AjaxRef.getBaseUrl() 改 https://www.i-fare.org.tw/ifare_bdapi (固定走正式)</v>
       </c>
-      <c r="K105" s="7" t="str">
+      <c r="K105" s="5" t="str">
         <v>nuxt.config.ts (前台) + AjaxRef.ts (後台)</v>
       </c>
-      <c r="L105" s="7" t="str" xml:space="preserve">
+      <c r="L105" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/nuxt.config.ts_x000d__x000d__x000d_
 iFare_Backend/src/plugins/AjaxRef.ts</v>
       </c>
-      <c r="M105" s="7" t="str">
+      <c r="M105" s="5" t="str">
         <v>Login 已驗證可通；前台 dropdown 已能抓資料</v>
       </c>
-      <c r="N105" s="7" t="str">
+      <c r="N105" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O105" s="7" t="str">
+      <c r="O105" s="5" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P105" s="7" t="str">
+      <c r="P105" s="5" t="str">
         <v>對應後臺優化 #8 / #14 (baseURL 環境變數化) — 目前是治標處理，等之後完整改成 .env</v>
       </c>
     </row>
     <row r="106" ht="172.80000000000004" customHeight="1" xml:space="preserve">
-      <c r="A106" s="7">
+      <c r="A106" s="5">
         <v>104</v>
       </c>
-      <c r="B106" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C106" s="7" t="str">
+      <c r="B106" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C106" s="5" t="str">
         <v>全站通用</v>
       </c>
-      <c r="D106" s="7" t="str">
-        <v/>
-      </c>
-      <c r="E106" s="7" t="str">
+      <c r="D106" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E106" s="5" t="str">
         <v>修復</v>
       </c>
-      <c r="F106" s="7" t="str">
+      <c r="F106" s="5" t="str">
         <v>程式碼</v>
       </c>
-      <c r="G106" s="7" t="str">
+      <c r="G106" s="5" t="str">
         <v>低</v>
       </c>
-      <c r="H106" s="7" t="str">
+      <c r="H106" s="5" t="str">
         <v>VS Code 顯示 3 個 TypeScript deprecation warning</v>
       </c>
-      <c r="I106" s="7" t="str">
+      <c r="I106" s="5" t="str">
         <v>iFare_Backend/tsconfig.app.json 用 baseUrl + moduleResolution=node10 / iFare_Frontend/tsconfig.json 透過 .nuxt/tsconfig.json extend 也帶 node10，被 TypeScript 5.x 標 deprecated (TS 7.0 才停用)</v>
       </c>
-      <c r="J106" s="7" t="str">
+      <c r="J106" s="5" t="str">
         <v>加 "ignoreDeprecations": "6.0" — 後台直接放 tsconfig.app.json compilerOptions；前台改透過 nuxt.config.ts typescript.tsConfig.compilerOptions 注入 .nuxt/tsconfig.json (因為 user-facing tsconfig.json 加 ignoreDeprecations 抑制不到 extend 的 .nuxt/tsconfig.json)</v>
       </c>
-      <c r="K106" s="7" t="str">
+      <c r="K106" s="5" t="str">
         <v>tsconfig.app.json + tsconfig.json + nuxt.config.ts</v>
       </c>
-      <c r="L106" s="7" t="str" xml:space="preserve">
+      <c r="L106" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Backend/tsconfig.app.json_x000d__x000d__x000d_
 iFare_Frontend/tsconfig.json_x000d__x000d__x000d_
 iFare_Frontend/nuxt.config.ts</v>
       </c>
-      <c r="M106" s="7" t="str">
+      <c r="M106" s="5" t="str">
         <v>TS 5.x 不影響執行 / build</v>
       </c>
-      <c r="N106" s="7" t="str">
+      <c r="N106" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O106" s="7" t="str">
+      <c r="O106" s="5" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P106" s="7" t="str">
+      <c r="P106" s="5" t="str">
         <v>純 IDE 觀感修補；VS Code 需 Ctrl+Shift+P → Restart TS Server 才會 reload</v>
       </c>
     </row>
     <row r="107" ht="115.2" customHeight="1" xml:space="preserve">
-      <c r="A107" s="7">
+      <c r="A107" s="5">
         <v>105</v>
       </c>
-      <c r="B107" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C107" s="7" t="str">
+      <c r="B107" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C107" s="5" t="str">
         <v>全站通用</v>
       </c>
-      <c r="D107" s="7" t="str">
-        <v/>
-      </c>
-      <c r="E107" s="7" t="str">
+      <c r="D107" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E107" s="5" t="str">
         <v>修復</v>
       </c>
-      <c r="F107" s="7" t="str">
+      <c r="F107" s="5" t="str">
         <v>程式碼</v>
       </c>
-      <c r="G107" s="7" t="str">
+      <c r="G107" s="5" t="str">
         <v>高</v>
       </c>
-      <c r="H107" s="7" t="str">
+      <c r="H107" s="5" t="str">
         <v>主管手動合併 master 時漏合 5dfbf91/cf47cfa 部分改動</v>
       </c>
-      <c r="I107" s="7" t="str">
+      <c r="I107" s="5" t="str">
         <v>切到 master 開 feat/uiux-round4 新分支後抽樣驗證發現：5dfbf91 漏合的 footer 樣式 (LINE 綠/FB 藍 SVG icon、_appFooter.scss 重新設計、_animation.scss page transition、_rwd_appFooter.scss、Mail/Clock SVG)；cf47cfa 整個沒合 (About 靈動島 + News 卡片升級 + 社群外連結) — 9 個檔</v>
       </c>
-      <c r="J107" s="7" t="str">
+      <c r="J107" s="5" t="str">
         <v>從 frontend 分支 git show 補回 16 個檔到新分支對應路徑 (Dev/Dev Code/iFare_Frontend/...)；cf47cfa 9 檔以 d5a7674 commit；footer 7 檔以 e2b1cae commit</v>
       </c>
-      <c r="K107" s="7" t="str">
+      <c r="K107" s="5" t="str">
         <v>16 個 SCSS / Vue / SVG</v>
       </c>
-      <c r="L107" s="7" t="str" xml:space="preserve">
+      <c r="L107" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">Dev/Dev Code/iFare_Frontend/assets/style/components/_appFooter.scss_x000d__x000d__x000d_
 iFare_Frontend/assets/style/_animation.scss_x000d__x000d__x000d_
 iFare_Frontend/components/AppFooter.vue 等 16 檔</v>
       </c>
-      <c r="M107" s="7" t="str">
+      <c r="M107" s="5" t="str">
         <v>修補 release 環境必要</v>
       </c>
-      <c r="N107" s="7" t="str">
+      <c r="N107" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O107" s="7" t="str">
+      <c r="O107" s="5" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P107" s="7" t="str">
+      <c r="P107" s="5" t="str">
         <v>不是純 UI/UX 議題，但屬於 Round 1-3 work 真正落地的前提</v>
       </c>
     </row>
     <row r="108" ht="14.4" customHeight="1" xml:space="preserve">
-      <c r="A108" s="7">
+      <c r="A108" s="5">
         <v>106</v>
       </c>
-      <c r="B108" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C108" s="7" t="str">
+      <c r="B108" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C108" s="5" t="str">
         <v>安全性</v>
       </c>
-      <c r="D108" s="7" t="str">
+      <c r="D108" s="5" t="str">
         <v>v-html XSS</v>
       </c>
-      <c r="E108" s="7" t="str">
+      <c r="E108" s="5" t="str">
         <v>修復</v>
       </c>
-      <c r="F108" s="7" t="str">
+      <c r="F108" s="5" t="str">
         <v>程式碼</v>
       </c>
-      <c r="G108" s="7" t="str">
+      <c r="G108" s="5" t="str">
         <v>高</v>
       </c>
-      <c r="H108" s="7" t="str">
+      <c r="H108" s="5" t="str">
         <v>v-html 渲染未清理的服務器內容，存在 XSS 風險</v>
       </c>
-      <c r="I108" s="7" t="str">
+      <c r="I108" s="5" t="str">
         <v>news/info, articles/lazy, articles/welfare, ifare/info 多頁用 v-html 渲染 API content；若後端未正確清理 HTML/JavaScript，可遭 XSS</v>
       </c>
-      <c r="J108" s="7" t="str">
+      <c r="J108" s="5" t="str">
         <v>用 DOMPurify 或 sanitize-html 清理 HTML；至少在伺服器端驗證內容不含危險標籤</v>
       </c>
-      <c r="K108" s="7" t="str">
+      <c r="K108" s="5" t="str">
         <v>pages/news/info.vue + articles/lazy/welfare + ifare/info</v>
       </c>
-      <c r="L108" s="7" t="str" xml:space="preserve">
+      <c r="L108" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/pages/news/info.vue (L25)_x000d__x000d_
 iFare_Frontend/pages/articles/lazy.vue (L16)_x000d__x000d_
 iFare_Frontend/pages/articles/welfare.vue (L19)_x000d__x000d_
 iFare_Frontend/pages/ifare/info.vue (L23, 31, 40, 47)</v>
       </c>
-      <c r="M108" s="7" t="str">
+      <c r="M108" s="5" t="str">
         <v>高優先級安全缺陷</v>
       </c>
-      <c r="N108" s="7" t="str">
+      <c r="N108" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O108" s="7" t="str">
+      <c r="O108" s="5" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P108" s="7" t="str">
+      <c r="P108" s="5" t="str">
         <v>Round 9 (批次 B): 安裝 isomorphic-dompurify (SSR + client safe)；新增 composables/useSanitize.ts 統一清理規範 (white-list ALLOWED_TAGS / ALLOWED_ATTR、阻 javascript:/data: URI、FORBID script/style/iframe/onerror)；7 處 v-html 用 useSanitize 包起來: news/info、articles/lazy、articles/welfare、ifare/info × 4 (qualification/welfareInfo/evidence/remark)。</v>
       </c>
     </row>
     <row r="109" ht="14.4" customHeight="1" xml:space="preserve">
-      <c r="A109" s="5">
+      <c r="A109" s="4">
         <v>107</v>
       </c>
-      <c r="B109" s="5" t="str">
-        <v>V</v>
-      </c>
-      <c r="C109" s="5" t="str">
+      <c r="B109" s="4" t="str">
+        <v>V</v>
+      </c>
+      <c r="C109" s="4" t="str">
         <v>全站通用</v>
       </c>
-      <c r="D109" s="5" t="str">
+      <c r="D109" s="4" t="str">
         <v>WebAPI 錯誤處理</v>
       </c>
-      <c r="E109" s="5" t="str">
+      <c r="E109" s="4" t="str">
         <v>修復</v>
       </c>
-      <c r="F109" s="5" t="str">
+      <c r="F109" s="4" t="str">
         <v>程式碼</v>
       </c>
-      <c r="G109" s="5" t="str">
+      <c r="G109" s="4" t="str">
         <v>高</v>
       </c>
-      <c r="H109" s="5" t="str">
+      <c r="H109" s="4" t="str">
         <v>WebAPI.ts 未區分錯誤類型，一律 return null，頁面無法判斷失敗原因</v>
       </c>
-      <c r="I109" s="5" t="str">
+      <c r="I109" s="4" t="str">
         <v>plugins/WebAPI.ts (L9-15) 捕獲所有錯誤返回 null，無法區分網路超時/伺服器 500/驗證失敗；news.vue 等雖有 hasError 但無法提示具體原因</v>
       </c>
-      <c r="J109" s="5" t="str">
+      <c r="J109" s="4" t="str">
         <v>返回結構化錯誤物件 {code, message, status}，頁面根據錯誤類型顯示不同提示 (網路錯誤、伺服器維護中等)</v>
       </c>
-      <c r="K109" s="5" t="str">
+      <c r="K109" s="4" t="str">
         <v>plugins/WebAPI.ts</v>
       </c>
-      <c r="L109" s="5" t="str" xml:space="preserve">
+      <c r="L109" s="4" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/plugins/WebAPI.ts_x000d__x000d_
 iFare_Frontend/pages/news.vue_x000d__x000d_
 iFare_Frontend/pages/articles.vue_x000d__x000d_
 iFare_Frontend/pages/ifare.vue</v>
       </c>
-      <c r="M109" s="5" t="str">
+      <c r="M109" s="4" t="str">
         <v>影響全站用戶體驗</v>
       </c>
-      <c r="N109" s="5" t="str">
+      <c r="N109" s="4" t="str">
         <v>部分修正</v>
       </c>
-      <c r="O109" s="5" t="str">
+      <c r="O109" s="4" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P109" s="5" t="str">
+      <c r="P109" s="4" t="str">
         <v>Round 9 (批次 B): plugins/WebAPI.ts 加 categorizeError (timeout/network/client/server/unknown)、結構化 logError 取代 console.error、try-catch wrapper。Return signature 不變 (data/null) 維持向下相容，所有 caller 不用改。**UI 端錯誤呈現** (顯示 toast / 重試提示) 尚未做，需與整體錯誤元件設計一起。</v>
       </c>
     </row>
     <row r="110" ht="14.4" customHeight="1" xml:space="preserve">
-      <c r="A110" s="7">
+      <c r="A110" s="5">
         <v>108</v>
       </c>
-      <c r="B110" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C110" s="7" t="str">
+      <c r="B110" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C110" s="5" t="str">
         <v>全站通用</v>
       </c>
-      <c r="D110" s="7" t="str">
+      <c r="D110" s="5" t="str">
         <v>API 超時</v>
       </c>
-      <c r="E110" s="7" t="str">
+      <c r="E110" s="5" t="str">
         <v>修復</v>
       </c>
-      <c r="F110" s="7" t="str">
+      <c r="F110" s="5" t="str">
         <v>效能</v>
       </c>
-      <c r="G110" s="7" t="str">
+      <c r="G110" s="5" t="str">
         <v>高</v>
       </c>
-      <c r="H110" s="7" t="str">
+      <c r="H110" s="5" t="str">
         <v>$fetch 無超時設定，API 無回應頁面會無限期卡 loading</v>
       </c>
-      <c r="I110" s="7" t="str">
+      <c r="I110" s="5" t="str">
         <v>所有頁面的 API 呼叫未設 timeout，若 API 無回應，UI 會永遠停在 loading 無退出機制</v>
       </c>
-      <c r="J110" s="7" t="str">
+      <c r="J110" s="5" t="str">
         <v>WebAPI.ts 設預設 timeout 10-15 秒，超時返回特定錯誤碼讓頁面顯示「連線逾時，請重試」</v>
       </c>
-      <c r="K110" s="7" t="str">
+      <c r="K110" s="5" t="str">
         <v>plugins/WebAPI.ts</v>
       </c>
-      <c r="L110" s="7" t="str" xml:space="preserve">
+      <c r="L110" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/plugins/WebAPI.ts_x000d__x000d_
 iFare_Frontend/pages/news/info.vue_x000d__x000d_
 iFare_Frontend/pages/articles/lazy.vue_x000d__x000d_
 iFare_Frontend/pages/articles/welfare.vue_x000d__x000d_
 iFare_Frontend/pages/ifare/contact.vue</v>
       </c>
-      <c r="M110" s="7" t="str">
+      <c r="M110" s="5" t="str">
         <v>可能導致用戶感知應用無反應</v>
       </c>
-      <c r="N110" s="7" t="str">
+      <c r="N110" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O110" s="7" t="str">
+      <c r="O110" s="5" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P110" s="7" t="str">
+      <c r="P110" s="5" t="str">
         <v>Round 9 (批次 B): plugins/WebAPI.ts WebApiGet/WebApiPost $fetch 加 timeout: API_TIMEOUT_MS (15000ms)。逾時會被 categorizeError 標記為 timeout 類別。</v>
       </c>
     </row>
     <row r="111" ht="14.4" customHeight="1">
-      <c r="A111" s="7">
+      <c r="A111" s="5">
         <v>109</v>
       </c>
-      <c r="B111" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C111" s="7" t="str">
+      <c r="B111" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C111" s="5" t="str">
         <v>i-Fare 福利查詢</v>
       </c>
-      <c r="D111" s="7" t="str">
+      <c r="D111" s="5" t="str">
         <v>ifare/contact</v>
       </c>
-      <c r="E111" s="7" t="str">
+      <c r="E111" s="5" t="str">
         <v>修復</v>
       </c>
-      <c r="F111" s="7" t="str">
+      <c r="F111" s="5" t="str">
         <v>互動</v>
       </c>
-      <c r="G111" s="7" t="str">
+      <c r="G111" s="5" t="str">
         <v>高</v>
       </c>
-      <c r="H111" s="7" t="str">
+      <c r="H111" s="5" t="str">
         <v>contact.vue 缺 API 失敗處理，API 失敗用戶看不到內容</v>
       </c>
-      <c r="I111" s="7" t="str">
+      <c r="I111" s="5" t="str">
         <v>ifare/contact.vue (L153) 呼叫 GetIFareOfficeUnitList 但無檢查 res.result、無 catch 區塊、無 loading/error 狀態。若 API 失敗頁面呈現空白</v>
       </c>
-      <c r="J111" s="7" t="str">
+      <c r="J111" s="5" t="str">
         <v>加 try-catch、loading ref、error 狀態，仿 news.vue 的錯誤處理模式</v>
       </c>
-      <c r="K111" s="7" t="str">
+      <c r="K111" s="5" t="str">
         <v>pages/ifare/contact.vue</v>
       </c>
-      <c r="L111" s="7" t="str">
+      <c r="L111" s="5" t="str">
         <v>iFare_Frontend/pages/ifare/contact.vue</v>
       </c>
-      <c r="M111" s="7" t="str">
+      <c r="M111" s="5" t="str">
         <v>用戶無法看到聯絡資訊時毫無提示</v>
       </c>
-      <c r="N111" s="7" t="str">
+      <c r="N111" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O111" s="7" t="str">
+      <c r="O111" s="5" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P111" s="7" t="str">
+      <c r="P111" s="5" t="str">
         <v>Round 9 (批次 B): pages/ifare/contact.vue 重構為 loadOfficeUnit() async + isLoading/hasError ref。template 加 v-if 三分支: loading (skeleton-line role=status)、error (重試按鈕 role=alert)、success (原內容)。重試會清空既有資料再呼叫。</v>
       </c>
     </row>
     <row r="112" ht="14.4" customHeight="1" xml:space="preserve">
-      <c r="A112" s="7">
+      <c r="A112" s="5">
         <v>110</v>
       </c>
-      <c r="B112" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C112" s="7" t="str">
+      <c r="B112" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C112" s="5" t="str">
         <v>全站通用</v>
       </c>
-      <c r="D112" s="7" t="str">
+      <c r="D112" s="5" t="str">
         <v>console.log</v>
       </c>
-      <c r="E112" s="7" t="str">
+      <c r="E112" s="5" t="str">
         <v>修復</v>
       </c>
-      <c r="F112" s="7" t="str">
+      <c r="F112" s="5" t="str">
         <v>程式碼</v>
       </c>
-      <c r="G112" s="7" t="str">
+      <c r="G112" s="5" t="str">
         <v>高</v>
       </c>
-      <c r="H112" s="7" t="str">
+      <c r="H112" s="5" t="str">
         <v>生產環境仍有 20+ 個 console.log，洩露內部邏輯</v>
       </c>
-      <c r="I112" s="7" t="str">
+      <c r="I112" s="5" t="str">
         <v>news.vue (L198), ifare.vue (L305), ifare/result.vue (L236-265, 385, 541), ifare/contact.vue (L163, 193) 等多處 console.log，可被用戶開發工具看到</v>
       </c>
-      <c r="J112" s="7" t="str">
+      <c r="J112" s="5" t="str">
         <v>移除所有生產 console.log，改用生產環境禁用的日誌系統，或開發時用環境變數判斷</v>
       </c>
-      <c r="K112" s="7" t="str">
+      <c r="K112" s="5" t="str">
         <v>多 pages</v>
       </c>
-      <c r="L112" s="7" t="str" xml:space="preserve">
+      <c r="L112" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/pages/news.vue_x000d__x000d_
 iFare_Frontend/pages/ifare.vue_x000d__x000d_
 iFare_Frontend/pages/ifare/result.vue_x000d__x000d_
@@ -9665,16 +9769,16 @@
 iFare_Frontend/components/CompPage.vue_x000d__x000d_
 iFare_Frontend/components/CompPageNum.vue</v>
       </c>
-      <c r="M112" s="7" t="str">
+      <c r="M112" s="5" t="str">
         <v>安全與代碼質量問題</v>
       </c>
-      <c r="N112" s="7" t="str">
+      <c r="N112" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O112" s="7" t="str">
+      <c r="O112" s="5" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P112" s="7" t="str">
+      <c r="P112" s="5" t="str">
         <v>Round 7 (批次 A): 移除 13 處 console.log — pages/news.vue (1)、pages/ifare.vue (1)、pages/ifare/result.vue (5)、pages/ifare/contact.vue (2)、components/CompPage.vue (4)。保留 pages/ifare/info.vue:203 的 console.error (catch 內合理錯誤處理)。</v>
       </c>
     </row>
@@ -9730,54 +9834,54 @@
       </c>
     </row>
     <row r="114" ht="14.4" customHeight="1" xml:space="preserve">
-      <c r="A114" s="7">
+      <c r="A114" s="5">
         <v>112</v>
       </c>
-      <c r="B114" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C114" s="7" t="str">
+      <c r="B114" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C114" s="5" t="str">
         <v>無障礙</v>
       </c>
-      <c r="D114" s="7" t="str">
+      <c r="D114" s="5" t="str">
         <v>圖片 alt</v>
       </c>
-      <c r="E114" s="7" t="str">
+      <c r="E114" s="5" t="str">
         <v>修復</v>
       </c>
-      <c r="F114" s="7" t="str">
+      <c r="F114" s="5" t="str">
         <v>無障礙</v>
       </c>
-      <c r="G114" s="7" t="str">
+      <c r="G114" s="5" t="str">
         <v>中</v>
       </c>
-      <c r="H114" s="7" t="str">
+      <c r="H114" s="5" t="str">
         <v>多頁圖片 alt 屬性缺失 (collaborator, articles/lazy, index 背景)</v>
       </c>
-      <c r="I114" s="7" t="str">
+      <c r="I114" s="5" t="str">
         <v>collaborator.vue (L22) &lt;img&gt; 無 alt；articles/lazy.vue (L77) 自動生成 &lt;img&gt; 無 alt；index 背景 CSS 無 alt</v>
       </c>
-      <c r="J114" s="7" t="str">
+      <c r="J114" s="5" t="str">
         <v>所有 img 加 alt (collaborator 用機構名稱，articles/lazy 用文章標題)；背景圖改 img 或加 aria-label</v>
       </c>
-      <c r="K114" s="7" t="str">
+      <c r="K114" s="5" t="str">
         <v>collaborator / articles/lazy / index</v>
       </c>
-      <c r="L114" s="7" t="str" xml:space="preserve">
+      <c r="L114" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/pages/collaborator.vue_x000d__x000d_
 iFare_Frontend/pages/articles/lazy.vue_x000d__x000d_
 iFare_Frontend/pages/index.vue</v>
       </c>
-      <c r="M114" s="7" t="str">
+      <c r="M114" s="5" t="str">
         <v>WCAG 2.1 AA 必要，影響視障用戶</v>
       </c>
-      <c r="N114" s="7" t="str">
+      <c r="N114" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O114" s="7" t="str">
+      <c r="O114" s="5" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P114" s="7" t="str">
+      <c r="P114" s="5" t="str">
         <v>Round 8 (批次 C): pages/index.vue 的 .part-bg-top 加 aria-hidden="true" — 5 張裝飾性 .bg-img 不需被屏幕閱讀器讀。collaborator.vue + articles/lazy.vue 的 &lt;img&gt; alt 已在 Round 7 (#127) 順手做。</v>
       </c>
     </row>
@@ -9833,108 +9937,108 @@
       </c>
     </row>
     <row r="116" ht="14.4" customHeight="1" xml:space="preserve">
-      <c r="A116" s="7">
+      <c r="A116" s="5">
         <v>114</v>
       </c>
-      <c r="B116" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C116" s="7" t="str">
+      <c r="B116" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C116" s="5" t="str">
         <v>共用元件</v>
       </c>
-      <c r="D116" s="7" t="str">
+      <c r="D116" s="5" t="str">
         <v>CompSelect 鍵盤</v>
       </c>
-      <c r="E116" s="7" t="str">
+      <c r="E116" s="5" t="str">
         <v>修復</v>
       </c>
-      <c r="F116" s="7" t="str">
+      <c r="F116" s="5" t="str">
         <v>無障礙</v>
       </c>
-      <c r="G116" s="7" t="str">
+      <c r="G116" s="5" t="str">
         <v>中</v>
       </c>
-      <c r="H116" s="7" t="str">
+      <c r="H116" s="5" t="str">
         <v>CompSelect 系列元件無鍵盤操作 (Tab/Enter/Esc/Arrow)，僅滑鼠</v>
       </c>
-      <c r="I116" s="7" t="str">
+      <c r="I116" s="5" t="str">
         <v>CompSelect / CompSelectRecipient / CompSelectElse 的開關、選項點擊均未綁定鍵盤事件，無法用鍵盤導航選擇</v>
       </c>
-      <c r="J116" s="7" t="str">
+      <c r="J116" s="5" t="str">
         <v>加 @keydown.tab/enter/esc/arrow-down/up 事件，實現 ARIA authoring practices 完整鍵盤導航</v>
       </c>
-      <c r="K116" s="7" t="str">
+      <c r="K116" s="5" t="str">
         <v>components/CompSelect*</v>
       </c>
-      <c r="L116" s="7" t="str" xml:space="preserve">
+      <c r="L116" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/components/CompSelect.vue_x000d__x000d_
 iFare_Frontend/components/CompSelectRecipient.vue_x000d__x000d_
 iFare_Frontend/components/CompSelectElse.vue</v>
       </c>
-      <c r="M116" s="7" t="str">
+      <c r="M116" s="5" t="str">
         <v>WCAG 2.1 AA 必要</v>
       </c>
-      <c r="N116" s="7" t="str">
+      <c r="N116" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O116" s="7" t="str">
+      <c r="O116" s="5" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P116" s="7" t="str">
+      <c r="P116" s="5" t="str">
         <v>Round 8 (批次 C): 3 個 component (CompSelect / CompSelectRecipient / CompSelectElse) 加 tabindex="0" + role="combobox" + aria-expanded + aria-haspopup + aria-label。CompSelect / CompSelectRecipient 加完整鍵盤導航 (Enter/Space toggle 或選擇 focused 項目；Esc 關閉；Arrow Up/Down 切換 focused 項目)；CompSelectElse 因含兩組選項 (Income + Identity) 結構複雜，僅加 Enter/Space toggle + Esc 關閉，方向鍵需後續再處理。選項加 role="option" + aria-selected。</v>
       </c>
     </row>
     <row r="117" ht="14.4" customHeight="1" xml:space="preserve">
-      <c r="A117" s="7">
+      <c r="A117" s="5">
         <v>115</v>
       </c>
-      <c r="B117" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C117" s="7" t="str">
+      <c r="B117" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C117" s="5" t="str">
         <v>無障礙</v>
       </c>
-      <c r="D117" s="7" t="str">
+      <c r="D117" s="5" t="str">
         <v>Heading 層級</v>
       </c>
-      <c r="E117" s="7" t="str">
+      <c r="E117" s="5" t="str">
         <v>修復</v>
       </c>
-      <c r="F117" s="7" t="str">
+      <c r="F117" s="5" t="str">
         <v>無障礙</v>
       </c>
-      <c r="G117" s="7" t="str">
+      <c r="G117" s="5" t="str">
         <v>中</v>
       </c>
-      <c r="H117" s="7" t="str">
+      <c r="H117" s="5" t="str">
         <v>Heading 層級結構不規範，多頁 h3 直接跟 h1 後，h6 用於非末級</v>
       </c>
-      <c r="I117" s="7" t="str">
+      <c r="I117" s="5" t="str">
         <v>about.vue (L11 h3 缺 h2)、index.vue (L21 h1 + L38 h3)、news/info.vue (L4 h2 後直接 h6)、ifare/info.vue (L5 h1 + L21 h3) 不遵循層級規則</v>
       </c>
-      <c r="J117" s="7" t="str">
+      <c r="J117" s="5" t="str">
         <v>調整 heading 層級遞增 (h1 &gt; h2 &gt; h3...)；不跳級；副標題用適當 h2-h3 而非 h6</v>
       </c>
-      <c r="K117" s="7" t="str">
+      <c r="K117" s="5" t="str">
         <v>about / index / news/info / ifare/info / collaborator</v>
       </c>
-      <c r="L117" s="7" t="str" xml:space="preserve">
+      <c r="L117" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/pages/about.vue_x000d__x000d_
 iFare_Frontend/pages/index.vue_x000d__x000d_
 iFare_Frontend/pages/news/info.vue_x000d__x000d_
 iFare_Frontend/pages/ifare/info.vue_x000d__x000d_
 iFare_Frontend/pages/collaborator.vue</v>
       </c>
-      <c r="M117" s="7" t="str">
+      <c r="M117" s="5" t="str">
         <v>影響屏幕閱讀器用戶導航</v>
       </c>
-      <c r="N117" s="7" t="str">
+      <c r="N117" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O117" s="7" t="str">
+      <c r="O117" s="5" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P117" s="7" t="str">
+      <c r="P117" s="5" t="str">
         <v>Round 8 (批次 C): 已 grep 確認 SCSS 全用 class selector (.comp-title / .member-name / .news-title 等)，改 tag 不破壞視覺。修正：about.vue (h3 → h1 主標 / h6 → h4 member-name × 3)；index.vue (h3 → p sub-title / h2 → h4 news-title / h2 → h4 card-title)；news/info.vue (h6 → p article-date)；ifare/info.vue (h3 → h2 × 5 區塊標 / h5 → h2 relation-title / h6 → h3 link-title)。</v>
       </c>
     </row>
@@ -10043,52 +10147,52 @@
       </c>
     </row>
     <row r="120" ht="14.4" customHeight="1">
-      <c r="A120" s="7">
+      <c r="A120" s="5">
         <v>118</v>
       </c>
-      <c r="B120" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C120" s="7" t="str">
+      <c r="B120" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C120" s="5" t="str">
         <v>最新消息</v>
       </c>
-      <c r="D120" s="7" t="str">
+      <c r="D120" s="5" t="str">
         <v>iframe 安全</v>
       </c>
-      <c r="E120" s="7" t="str">
+      <c r="E120" s="5" t="str">
         <v>修復</v>
       </c>
-      <c r="F120" s="7" t="str">
+      <c r="F120" s="5" t="str">
         <v>程式碼</v>
       </c>
-      <c r="G120" s="7" t="str">
+      <c r="G120" s="5" t="str">
         <v>中</v>
       </c>
-      <c r="H120" s="7" t="str">
+      <c r="H120" s="5" t="str">
         <v>YouTube iframe 缺 sandbox 屬性，allow 過寬鬆</v>
       </c>
-      <c r="I120" s="7" t="str">
+      <c r="I120" s="5" t="str">
         <v>news/info.vue (L12-19) iframe allow 含 accelerometer/autoplay/clipboard-write 等未設 sandbox，可能被跨域腳本利用</v>
       </c>
-      <c r="J120" s="7" t="str">
+      <c r="J120" s="5" t="str">
         <v>加 sandbox="allow-same-origin allow-scripts allow-presentation"；移除非必要 allow (例如 clipboard-write)</v>
       </c>
-      <c r="K120" s="7" t="str">
+      <c r="K120" s="5" t="str">
         <v>pages/news/info.vue</v>
       </c>
-      <c r="L120" s="7" t="str">
+      <c r="L120" s="5" t="str">
         <v>iFare_Frontend/pages/news/info.vue</v>
       </c>
-      <c r="M120" s="7" t="str">
+      <c r="M120" s="5" t="str">
         <v>防止潛在跨域攻擊</v>
       </c>
-      <c r="N120" s="7" t="str">
+      <c r="N120" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O120" s="7" t="str">
+      <c r="O120" s="5" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P120" s="7" t="str">
+      <c r="P120" s="5" t="str">
         <v>Round 9 (批次 B): pages/news/info.vue 的 YouTube iframe 加 sandbox="allow-same-origin allow-scripts allow-presentation allow-popups"；移除非必要 allow="clipboard-write" (剪貼簿權限不應自動給)。</v>
       </c>
     </row>
@@ -10145,52 +10249,52 @@
       </c>
     </row>
     <row r="122" ht="14.4" customHeight="1">
-      <c r="A122" s="7">
+      <c r="A122" s="5">
         <v>120</v>
       </c>
-      <c r="B122" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C122" s="7" t="str">
+      <c r="B122" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C122" s="5" t="str">
         <v>共用元件</v>
       </c>
-      <c r="D122" s="7" t="str">
+      <c r="D122" s="5" t="str">
         <v>AppFooter 版權</v>
       </c>
-      <c r="E122" s="7" t="str">
+      <c r="E122" s="5" t="str">
         <v>提升</v>
       </c>
-      <c r="F122" s="7" t="str">
+      <c r="F122" s="5" t="str">
         <v>內容</v>
       </c>
-      <c r="G122" s="7" t="str">
+      <c r="G122" s="5" t="str">
         <v>中</v>
       </c>
-      <c r="H122" s="7" t="str">
+      <c r="H122" s="5" t="str">
         <v>Footer 版權年份過舊 (1995-2020)，已過期 6 年</v>
       </c>
-      <c r="I122" s="7" t="str">
+      <c r="I122" s="5" t="str">
         <v>AppFooter.vue (L42) 顯示「© 1995-2020」，現在是 2026</v>
       </c>
-      <c r="J122" s="7" t="str">
+      <c r="J122" s="5" t="str">
         <v>改 `© 1995-${new Date().getFullYear()}`，或在 footer data 中維護</v>
       </c>
-      <c r="K122" s="7" t="str">
+      <c r="K122" s="5" t="str">
         <v>components/AppFooter.vue</v>
       </c>
-      <c r="L122" s="7" t="str">
+      <c r="L122" s="5" t="str">
         <v>iFare_Frontend/components/AppFooter.vue (L42)</v>
       </c>
-      <c r="M122" s="7" t="str">
+      <c r="M122" s="5" t="str">
         <v>簡易修復</v>
       </c>
-      <c r="N122" s="7" t="str">
+      <c r="N122" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O122" s="7" t="str">
+      <c r="O122" s="5" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P122" s="7" t="str">
+      <c r="P122" s="5" t="str">
         <v>Round 7 (批次 A): components/AppFooter.vue L42 「© 1995-2020」改成 「© 1995-{{ new Date().getFullYear() }}」 — 模板內 inline 執行，自動跟系統年份。</v>
       </c>
     </row>
@@ -10400,154 +10504,154 @@
       </c>
     </row>
     <row r="127" ht="14.4" customHeight="1">
-      <c r="A127" s="7">
+      <c r="A127" s="5">
         <v>125</v>
       </c>
-      <c r="B127" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C127" s="7" t="str">
+      <c r="B127" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C127" s="5" t="str">
         <v>共用元件</v>
       </c>
-      <c r="D127" s="7" t="str">
+      <c r="D127" s="5" t="str">
         <v>AppHeader 行動 focus</v>
       </c>
-      <c r="E127" s="7" t="str">
+      <c r="E127" s="5" t="str">
         <v>修復</v>
       </c>
-      <c r="F127" s="7" t="str">
+      <c r="F127" s="5" t="str">
         <v>無障礙</v>
       </c>
-      <c r="G127" s="7" t="str">
+      <c r="G127" s="5" t="str">
         <v>低</v>
       </c>
-      <c r="H127" s="7" t="str">
+      <c r="H127" s="5" t="str">
         <v>AppHeader 行動菜單開啟時焦點未自動移至菜單，關閉時未返回觸發按鈕</v>
       </c>
-      <c r="I127" s="7" t="str">
+      <c r="I127" s="5" t="str">
         <v>AppHeader.vue (L136) 菜單關閉按鈕有 focus，但開啟時焦點未管理，屏幕閱讀器用戶會迷失</v>
       </c>
-      <c r="J127" s="7" t="str">
+      <c r="J127" s="5" t="str">
         <v>用 ref 在菜單開啟時 focus 至菜單標題或第一個項目；關閉時 focus 返回菜單按鈕</v>
       </c>
-      <c r="K127" s="7" t="str">
+      <c r="K127" s="5" t="str">
         <v>components/AppHeader.vue</v>
       </c>
-      <c r="L127" s="7" t="str">
+      <c r="L127" s="5" t="str">
         <v>iFare_Frontend/components/AppHeader.vue (L136)</v>
       </c>
-      <c r="M127" s="7" t="str">
+      <c r="M127" s="5" t="str">
         <v>增進屏幕閱讀器友善性</v>
       </c>
-      <c r="N127" s="7" t="str">
+      <c r="N127" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O127" s="7" t="str">
+      <c r="O127" s="5" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P127" s="7" t="str">
+      <c r="P127" s="5" t="str">
         <v>Round 8 (批次 C): components/AppHeader.vue 加 menuButtonRef 綁 .btn-menu，watch(isShowMenu) → 開啟時 querySelector focus 至首個 mobile menu link，關閉時 focus 回菜單按鈕。.btn-menu 加 :aria-expanded="isShowMenu" + aria-controls="mobile-menu" + aria-label="開啟菜單"；.mobile-menu 加 id="mobile-menu" + role="dialog" + aria-modal="true" + aria-label="行動選單"。全域加 ESC 鍵監聽關閉 menu (onMounted/onBeforeUnmount window.addEventListener)。</v>
       </c>
     </row>
     <row r="128" ht="14.4" customHeight="1" xml:space="preserve">
-      <c r="A128" s="7">
+      <c r="A128" s="5">
         <v>126</v>
       </c>
-      <c r="B128" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C128" s="7" t="str">
+      <c r="B128" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C128" s="5" t="str">
         <v>i-Fare 福利查詢</v>
       </c>
-      <c r="D128" s="7" t="str">
+      <c r="D128" s="5" t="str">
         <v>disabled 視覺</v>
       </c>
-      <c r="E128" s="7" t="str">
+      <c r="E128" s="5" t="str">
         <v>提升</v>
       </c>
-      <c r="F128" s="7" t="str">
+      <c r="F128" s="5" t="str">
         <v>視覺</v>
       </c>
-      <c r="G128" s="7" t="str">
+      <c r="G128" s="5" t="str">
         <v>低</v>
       </c>
-      <c r="H128" s="7" t="str">
+      <c r="H128" s="5" t="str">
         <v>ifare.vue 搜尋按鈕 disabled 狀態無灰化視覺反饋</v>
       </c>
-      <c r="I128" s="7" t="str">
+      <c r="I128" s="5" t="str">
         <v>ifare.vue (L79) :disabled="!canSearch" 但 SCSS 無 button:disabled 樣式，用戶可能誤以為按鈕可點</v>
       </c>
-      <c r="J128" s="7" t="str">
+      <c r="J128" s="5" t="str">
         <v>_button.scss 加 button:disabled { opacity: 0.5; cursor: not-allowed; }</v>
       </c>
-      <c r="K128" s="7" t="str">
+      <c r="K128" s="5" t="str">
         <v>pages/ifare.vue + _button.scss</v>
       </c>
-      <c r="L128" s="7" t="str" xml:space="preserve">
+      <c r="L128" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/pages/ifare.vue (L79)_x000d__x000d_
 iFare_Frontend/assets/style/components/_button.scss</v>
       </c>
-      <c r="M128" s="7" t="str">
+      <c r="M128" s="5" t="str">
         <v>簡易視覺修復</v>
       </c>
-      <c r="N128" s="7" t="str">
+      <c r="N128" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O128" s="7" t="str">
+      <c r="O128" s="5" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P128" s="7" t="str">
+      <c r="P128" s="5" t="str">
         <v>Round 7 (批次 A): assets/style/components/_button.scss 開頭加 generic 規則 — button:disabled / .btn:disabled / .btn.disabled 都套 opacity 0.5 + cursor not-allowed + pointer-events none。.btn-filter 既有 disabled 樣式 (L186) 不衝突。</v>
       </c>
     </row>
     <row r="129" ht="14.4" customHeight="1" xml:space="preserve">
-      <c r="A129" s="7">
+      <c r="A129" s="5">
         <v>127</v>
       </c>
-      <c r="B129" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C129" s="7" t="str">
+      <c r="B129" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C129" s="5" t="str">
         <v>效能</v>
       </c>
-      <c r="D129" s="7" t="str">
+      <c r="D129" s="5" t="str">
         <v>圖片 lazy load</v>
       </c>
-      <c r="E129" s="7" t="str">
+      <c r="E129" s="5" t="str">
         <v>提升</v>
       </c>
-      <c r="F129" s="7" t="str">
+      <c r="F129" s="5" t="str">
         <v>效能</v>
       </c>
-      <c r="G129" s="7" t="str">
+      <c r="G129" s="5" t="str">
         <v>低</v>
       </c>
-      <c r="H129" s="7" t="str">
+      <c r="H129" s="5" t="str">
         <v>collaborator 機構圖片、articles/lazy 自動生成圖片未設 loading="lazy"</v>
       </c>
-      <c r="I129" s="7" t="str">
+      <c r="I129" s="5" t="str">
         <v>collaborator.vue (L22) 和 articles/lazy.vue (L77 動態) 的 &lt;img&gt; 無 loading 屬性，所有圖片串行加載</v>
       </c>
-      <c r="J129" s="7" t="str">
+      <c r="J129" s="5" t="str">
         <v>所有 &lt;img&gt; 加 loading="lazy" (首屏 eager)；大圖考慮 WebP 或壓縮</v>
       </c>
-      <c r="K129" s="7" t="str">
+      <c r="K129" s="5" t="str">
         <v>pages/collaborator + articles/lazy</v>
       </c>
-      <c r="L129" s="7" t="str" xml:space="preserve">
+      <c r="L129" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/pages/collaborator.vue_x000d__x000d_
 iFare_Frontend/pages/articles/lazy.vue</v>
       </c>
-      <c r="M129" s="7" t="str">
+      <c r="M129" s="5" t="str">
         <v>首屏效能優化</v>
       </c>
-      <c r="N129" s="7" t="str">
+      <c r="N129" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O129" s="7" t="str">
+      <c r="O129" s="5" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P129" s="7" t="str">
+      <c r="P129" s="5" t="str">
         <v>Round 7 (批次 A): pages/collaborator.vue L22 &lt;img&gt; 加 loading="lazy" + :alt="`${_coll.title} logo`"；pages/articles/lazy.vue L77 動態 &lt;img&gt; 加 loading="lazy" + alt="${title} - ${j+1}"。</v>
       </c>
     </row>
@@ -10654,104 +10758,154 @@
       </c>
     </row>
     <row r="132" ht="14.4" customHeight="1">
-      <c r="A132" s="7">
+      <c r="A132" s="5">
         <v>130</v>
       </c>
-      <c r="B132" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C132" s="7" t="str">
+      <c r="B132" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C132" s="5" t="str">
         <v>共用元件</v>
       </c>
-      <c r="D132" s="7" t="str">
+      <c r="D132" s="5" t="str">
         <v>AppHeader aria</v>
       </c>
-      <c r="E132" s="7" t="str">
+      <c r="E132" s="5" t="str">
         <v>提升</v>
       </c>
-      <c r="F132" s="7" t="str">
+      <c r="F132" s="5" t="str">
         <v>無障礙</v>
       </c>
-      <c r="G132" s="7" t="str">
+      <c r="G132" s="5" t="str">
         <v>低</v>
       </c>
-      <c r="H132" s="7" t="str">
+      <c r="H132" s="5" t="str">
         <v>AppHeader 行動菜單關閉按鈕無 aria-label</v>
       </c>
-      <c r="I132" s="7" t="str">
+      <c r="I132" s="5" t="str">
         <v>AppHeader.vue (L136) &lt;button class="btn btn-icon btn-close"&gt; 無 aria-label，屏幕閱讀器只念「按鈕」</v>
       </c>
-      <c r="J132" s="7" t="str">
+      <c r="J132" s="5" t="str">
         <v>加 aria-label="關閉菜單"</v>
       </c>
-      <c r="K132" s="7" t="str">
+      <c r="K132" s="5" t="str">
         <v>components/AppHeader.vue</v>
       </c>
-      <c r="L132" s="7" t="str">
+      <c r="L132" s="5" t="str">
         <v>iFare_Frontend/components/AppHeader.vue (L136)</v>
       </c>
-      <c r="M132" s="7" t="str">
+      <c r="M132" s="5" t="str">
         <v>簡易無障礙修復</v>
       </c>
-      <c r="N132" s="7" t="str">
+      <c r="N132" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O132" s="7" t="str">
+      <c r="O132" s="5" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P132" s="7" t="str">
+      <c r="P132" s="5" t="str">
         <v>Round 7 (批次 A): components/AppHeader.vue L136 行動選單 .btn-close 加 aria-label="關閉菜單"。</v>
       </c>
     </row>
     <row r="133" ht="14.4" customHeight="1" xml:space="preserve">
-      <c r="A133" s="7">
+      <c r="A133" s="5">
         <v>131</v>
       </c>
-      <c r="B133" s="7" t="str">
-        <v>V</v>
-      </c>
-      <c r="C133" s="7" t="str">
+      <c r="B133" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C133" s="5" t="str">
         <v>導航</v>
       </c>
-      <c r="D133" s="7" t="str">
+      <c r="D133" s="5" t="str">
         <v>aria-current</v>
       </c>
-      <c r="E133" s="7" t="str">
+      <c r="E133" s="5" t="str">
         <v>提升</v>
       </c>
-      <c r="F133" s="7" t="str">
+      <c r="F133" s="5" t="str">
         <v>無障礙</v>
       </c>
-      <c r="G133" s="7" t="str">
+      <c r="G133" s="5" t="str">
         <v>低</v>
       </c>
-      <c r="H133" s="7" t="str">
+      <c r="H133" s="5" t="str">
         <v>AppHeader 與其他導航元件當前頁面連結無 aria-current="page"</v>
       </c>
-      <c r="I133" s="7" t="str">
+      <c r="I133" s="5" t="str">
         <v>AppHeader (L48-69) 用 :class="{ active: $route.name }" 但無 aria-current；屏幕閱讀器無法知道哪個是當前頁</v>
       </c>
-      <c r="J133" s="7" t="str">
+      <c r="J133" s="5" t="str">
         <v>:aria-current="$route.name === 'about' ? 'page' : undefined"</v>
       </c>
-      <c r="K133" s="7" t="str">
+      <c r="K133" s="5" t="str">
         <v>components/AppHeader + CompBreadCrumb</v>
       </c>
-      <c r="L133" s="7" t="str" xml:space="preserve">
+      <c r="L133" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/components/AppHeader.vue_x000d__x000d_
 iFare_Frontend/components/CompBreadCrumb.vue</v>
       </c>
-      <c r="M133" s="7" t="str">
+      <c r="M133" s="5" t="str">
         <v>WCAG 2.1 最佳實踐 + 外部連結指示符可選加 ic-external-link icon</v>
       </c>
-      <c r="N133" s="7" t="str">
+      <c r="N133" s="5" t="str">
         <v>已修正</v>
       </c>
-      <c r="O133" s="7" t="str">
+      <c r="O133" s="5" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="P133" s="7" t="str">
+      <c r="P133" s="5" t="str">
         <v>Round 7 (批次 A): components/AppHeader.vue 桌面 5 + 行動 6 + i-Fare 桌面 1 共 12 個 NuxtLink 加 :aria-current="$route.name === 'xxx' ? 'page' : undefined"。i-Fare 用 includes('ifare') 涵蓋子路由。</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5">
+        <v>132</v>
+      </c>
+      <c r="B134" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="C134" s="5" t="str">
+        <v>i-Fare 福利查詢</v>
+      </c>
+      <c r="D134" s="5" t="str">
+        <v>搜尋結果</v>
+      </c>
+      <c r="E134" s="5" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F134" s="5" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G134" s="5" t="str">
+        <v>高</v>
+      </c>
+      <c r="H134" s="5" t="str">
+        <v>搜尋條件 OR == 1 造成大量不相關結果</v>
+      </c>
+      <c r="I134" s="5" t="str">
+        <v>使用者選「嬰幼兒」(CodeRecipientId=2) 後端回傳 740 筆，幾乎全為「無年齡限制」(CodeRecipientId=1) 的 policy (e.g., 喪葬補助、心理諮商)；同問題在 CodeDomicile / CodeIncome / CodeIdentity 共 4 維度都是 OR == 1。</v>
+      </c>
+      <c r="J134" s="5" t="str">
+        <v>Backend FarePolicyTaskManager.cs L117-121 拿掉 4 處 || == 1，改嚴格篩選：使用者選什麼條件就只回符合該條件的 policy。CodePolicy 本來就沒 OR 不動。</v>
+      </c>
+      <c r="K134" s="5" t="str">
+        <v>Backend FarePolicyTaskManager.cs</v>
+      </c>
+      <c r="L134" s="5" t="str">
+        <v>Dev/Dev Code/iFare_Frontend_API/src/IFare_API.Core/TaskManager/Fare/Policy/FarePolicyTaskManager.cs (L117-121)</v>
+      </c>
+      <c r="M134" s="5" t="str">
+        <v>使用者明確要求「我選了什麼條件就只出現符合的消息」</v>
+      </c>
+      <c r="N134" s="5" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O134" s="5" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="P134" s="5" t="str">
+        <v>Round 11 (使用者測試發現): 4 維度 (Domicile/Income/Recipient/Identity) 全改嚴格。tradeoff: 「無年齡限制/無戶籍限制」等 universal policy 不再混進結果，使用者可能要在後台 data 上把這類 policy 補上對應 tag (例如喪葬補助加全部 4 個年齡 tag)。</v>
       </c>
     </row>
   </sheetData>
@@ -10759,7 +10913,7 @@
     <mergeCell ref="A1:P1"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P133"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P134"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -10768,2015 +10922,2015 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H84"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="14.83203125"/>
-    <col min="2" max="2" customWidth="1" width="12.83203125"/>
-    <col min="3" max="3" customWidth="1" width="14.83203125"/>
-    <col min="4" max="4" customWidth="1" width="14.83203125"/>
-    <col min="5" max="5" customWidth="1" width="50.83203125"/>
-    <col min="6" max="6" customWidth="1" width="25.83203125"/>
-    <col min="7" max="7" customWidth="1" width="60.83203125"/>
-    <col min="8" max="8" customWidth="1" width="14.83203125"/>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="50.83203125" customWidth="1"/>
+    <col min="6" max="6" width="25.83203125" customWidth="1"/>
+    <col min="7" max="7" width="60.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="6" t="str">
         <v>【1】整體進度</v>
       </c>
-      <c r="B1" s="3" t="str">
-        <v/>
-      </c>
-      <c r="C1" s="3" t="str">
-        <v/>
-      </c>
-      <c r="D1" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E1" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F1" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G1" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H1" s="3" t="str">
+      <c r="B1" s="7" t="str">
+        <v/>
+      </c>
+      <c r="C1" s="7" t="str">
+        <v/>
+      </c>
+      <c r="D1" s="7" t="str">
+        <v/>
+      </c>
+      <c r="E1" s="7" t="str">
+        <v/>
+      </c>
+      <c r="F1" s="7" t="str">
+        <v/>
+      </c>
+      <c r="G1" s="7" t="str">
+        <v/>
+      </c>
+      <c r="H1" s="7" t="str">
         <v/>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="str">
+      <c r="A2" s="8" t="str">
         <v>Sheet 名稱</v>
       </c>
-      <c r="B2" s="3" t="str">
+      <c r="B2" s="9" t="str">
         <v>總計</v>
       </c>
-      <c r="C2" s="3" t="str">
+      <c r="C2" s="9" t="str">
         <v>已修正</v>
       </c>
-      <c r="D2" s="3" t="str">
+      <c r="D2" s="9" t="str">
         <v>部分修正</v>
       </c>
-      <c r="E2" s="3" t="str">
-        <v>待處理</v>
-      </c>
-      <c r="F2" s="3" t="str">
+      <c r="E2" s="9" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="F2" s="9" t="str">
         <v>完成率</v>
       </c>
-      <c r="G2" s="3" t="str">
+      <c r="G2" s="9" t="str">
         <v>備註</v>
       </c>
-      <c r="H2" s="3" t="str">
+      <c r="H2" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="str">
+      <c r="A3" s="10" t="str">
         <v>UIUX問題追蹤清單 (前台)</v>
       </c>
-      <c r="B3" s="3">
-        <v>131</v>
-      </c>
-      <c r="C3" s="3">
-        <v>39</v>
-      </c>
-      <c r="D3" s="3">
+      <c r="B3" s="11">
+        <v>132</v>
+      </c>
+      <c r="C3" s="12">
+        <v>42</v>
+      </c>
+      <c r="D3" s="13">
+        <v>6</v>
+      </c>
+      <c r="E3" s="14">
+        <v>84</v>
+      </c>
+      <c r="F3" s="11" t="str">
+        <v>31.8%</v>
+      </c>
+      <c r="G3" s="10" t="str">
+        <v>已歷經 Round 1-4 改版</v>
+      </c>
+      <c r="H3" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="str">
+        <v>後臺優化 (admin)</v>
+      </c>
+      <c r="B4" s="11">
+        <v>54</v>
+      </c>
+      <c r="C4" s="15">
+        <v>1</v>
+      </c>
+      <c r="D4" s="16">
+        <v>0</v>
+      </c>
+      <c r="E4" s="17">
+        <v>53</v>
+      </c>
+      <c r="F4" s="11" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="G4" s="10" t="str">
+        <v>Round 5-6 規劃完成 / 全待開始</v>
+      </c>
+      <c r="H4" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="str">
+        <v>PoC研究</v>
+      </c>
+      <c r="B5" s="11">
+        <v>12</v>
+      </c>
+      <c r="C5" s="15">
+        <v>0</v>
+      </c>
+      <c r="D5" s="16">
+        <v>0</v>
+      </c>
+      <c r="E5" s="17">
+        <v>12</v>
+      </c>
+      <c r="F5" s="11" t="str">
+        <v>0.0%</v>
+      </c>
+      <c r="G5" s="10" t="str">
+        <v>研究方向，未啟動</v>
+      </c>
+      <c r="H5" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="str">
+        <v>【2】Round 時間軸 — 每輪做了什麼</v>
+      </c>
+      <c r="B7" s="7" t="str">
+        <v/>
+      </c>
+      <c r="C7" s="7" t="str">
+        <v/>
+      </c>
+      <c r="D7" s="7" t="str">
+        <v/>
+      </c>
+      <c r="E7" s="7" t="str">
+        <v/>
+      </c>
+      <c r="F7" s="7" t="str">
+        <v/>
+      </c>
+      <c r="G7" s="7" t="str">
+        <v/>
+      </c>
+      <c r="H7" s="7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="str">
+        <v>Round</v>
+      </c>
+      <c r="B8" s="9" t="str">
+        <v>日期</v>
+      </c>
+      <c r="C8" s="9" t="str">
+        <v>主題</v>
+      </c>
+      <c r="D8" s="9" t="str">
+        <v>UIUX 標完成</v>
+      </c>
+      <c r="E8" s="9" t="str">
+        <v>UIUX 新增</v>
+      </c>
+      <c r="F8" s="9" t="str">
+        <v>後臺新增</v>
+      </c>
+      <c r="G8" s="9" t="str">
+        <v>Schema</v>
+      </c>
+      <c r="H8" s="9" t="str">
+        <v>主要產出</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="str">
+        <v>Round 1</v>
+      </c>
+      <c r="B9" s="10" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="C9" s="10" t="str">
+        <v>UI/UX 改版 (搜尋 / Footer / 全站動畫 / RWD)</v>
+      </c>
+      <c r="D9" s="11">
         <v>7</v>
       </c>
-      <c r="E3" s="3">
-        <v>85</v>
-      </c>
-      <c r="F3" s="3" t="str">
-        <v>29.8%</v>
-      </c>
-      <c r="G3" s="3" t="str">
-        <v>已歷經 Round 1-4 改版</v>
-      </c>
-      <c r="H3" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="str">
-        <v>後臺優化 (admin)</v>
-      </c>
-      <c r="B4" s="3">
-        <v>54</v>
-      </c>
-      <c r="C4" s="3">
+      <c r="E9" s="11">
+        <v>3</v>
+      </c>
+      <c r="F9" s="11">
         <v>0</v>
       </c>
-      <c r="D4" s="3">
+      <c r="G9" s="10" t="str">
+        <v>-</v>
+      </c>
+      <c r="H9" s="10" t="str">
+        <v>pages/ifare 加關鍵字搜尋 + URL query 初始化；全站 NuxtPage transition；卡片/按鈕 hover translateY</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="str">
+        <v>Round 2</v>
+      </c>
+      <c r="B10" s="10" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="C10" s="10" t="str">
+        <v>Footer 整理 + RWD 修正</v>
+      </c>
+      <c r="D10" s="11">
+        <v>2</v>
+      </c>
+      <c r="E10" s="11">
+        <v>2</v>
+      </c>
+      <c r="F10" s="11">
         <v>0</v>
       </c>
-      <c r="E4" s="3">
-        <v>54</v>
-      </c>
-      <c r="F4" s="3" t="str">
-        <v>0.0%</v>
-      </c>
-      <c r="G4" s="3" t="str">
-        <v>Round 5-6 規劃完成 / 全待開始</v>
-      </c>
-      <c r="H4" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="str">
-        <v>PoC研究</v>
-      </c>
-      <c r="B5" s="3">
-        <v>12</v>
-      </c>
-      <c r="C5" s="3">
+      <c r="G10" s="10" t="str">
+        <v>-</v>
+      </c>
+      <c r="H10" s="10" t="str">
+        <v>LINE/FB 統一 .btn-social 並排；4 個聯絡資訊加 icon (Tel/Mail/Address/Clock)；footer 觸控 44px</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="str">
+        <v>Round 3</v>
+      </c>
+      <c r="B11" s="10" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="C11" s="10" t="str">
+        <v>About 靈動島 + News 卡片升級 + 社群外連結</v>
+      </c>
+      <c r="D11" s="11">
+        <v>4</v>
+      </c>
+      <c r="E11" s="11">
+        <v>5</v>
+      </c>
+      <c r="F11" s="11">
         <v>0</v>
       </c>
-      <c r="D5" s="3">
+      <c r="G11" s="10" t="str">
+        <v>-</v>
+      </c>
+      <c r="H11" s="10" t="str">
+        <v>About 三大核心 morph 卡 (cf47cfa)；News 浮起卡 + stagger fade-up + NEW pill；外連結 target="_blank" rel="noopener"</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="str">
+        <v>Round 4</v>
+      </c>
+      <c r="B12" s="10" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="C12" s="10" t="str">
+        <v>切回 master + 開新分支 feat/uiux-round4 + 補做 (環境/補回/新功能)</v>
+      </c>
+      <c r="D12" s="11">
         <v>0</v>
       </c>
-      <c r="E5" s="3">
-        <v>12</v>
-      </c>
-      <c r="F5" s="3" t="str">
-        <v>0.0%</v>
-      </c>
-      <c r="G5" s="3" t="str">
-        <v>研究方向，未啟動</v>
-      </c>
-      <c r="H5" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="str">
-        <v>【2】Round 時間軸 — 每輪做了什麼</v>
-      </c>
-      <c r="B7" s="3" t="str">
-        <v/>
-      </c>
-      <c r="C7" s="3" t="str">
-        <v/>
-      </c>
-      <c r="D7" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E7" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F7" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G7" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H7" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="str">
+      <c r="E12" s="11">
+        <v>8</v>
+      </c>
+      <c r="F12" s="11">
+        <v>4</v>
+      </c>
+      <c r="G12" s="10" t="str">
+        <v>-</v>
+      </c>
+      <c r="H12" s="10" t="str">
+        <v>cf47cfa+5dfbf91 補回 16 檔；devProxy/baseURL → 正式 API；nav 加未來規劃 + future.vue；News videoUrl wiring；tsconfig deprecation 清理；about hover bug 修；footer label 重複修</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="str">
+        <v>Round 5</v>
+      </c>
+      <c r="B13" s="10" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="C13" s="10" t="str">
+        <v>前後台全面審查 — 後台 UX audit + 前台新 issue 掃描</v>
+      </c>
+      <c r="D13" s="11">
+        <v>0</v>
+      </c>
+      <c r="E13" s="11">
+        <v>26</v>
+      </c>
+      <c r="F13" s="11">
+        <v>22</v>
+      </c>
+      <c r="G13" s="10" t="str">
+        <v>-</v>
+      </c>
+      <c r="H13" s="10" t="str">
+        <v>後台 22 個工程角度問題 (CRUD/驗證/錯誤處理)；前台 26 個新發現 (XSS/超時/console.log/無障礙/分頁元件重複)</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="str">
+        <v>Round 6</v>
+      </c>
+      <c r="B14" s="10" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="C14" s="10" t="str">
+        <v>人性化主軸提案 — 5 主軸 + 16 後台項</v>
+      </c>
+      <c r="D14" s="11">
+        <v>0</v>
+      </c>
+      <c r="E14" s="11">
+        <v>0</v>
+      </c>
+      <c r="F14" s="11">
+        <v>16</v>
+      </c>
+      <c r="G14" s="10" t="str">
+        <v>+ Q 欄主軸</v>
+      </c>
+      <c r="H14" s="10" t="str">
+        <v>Dashboard 角色化 / 今日待辦 / KPI 分區；批次操作；軟刪除復原；audit log；危險操作預覽；錯誤訊息引導</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="str">
+        <v>【3】後臺優化 — 5 主軸分布 (拿這個去提案!)</v>
+      </c>
+      <c r="B16" s="7" t="str">
+        <v/>
+      </c>
+      <c r="C16" s="7" t="str">
+        <v/>
+      </c>
+      <c r="D16" s="7" t="str">
+        <v/>
+      </c>
+      <c r="E16" s="7" t="str">
+        <v/>
+      </c>
+      <c r="F16" s="7" t="str">
+        <v/>
+      </c>
+      <c r="G16" s="7" t="str">
+        <v/>
+      </c>
+      <c r="H16" s="7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="str">
+        <v>主軸</v>
+      </c>
+      <c r="B17" s="9" t="str">
+        <v>項目數</v>
+      </c>
+      <c r="C17" s="9" t="str">
+        <v>比例</v>
+      </c>
+      <c r="D17" s="9" t="str">
+        <v>主要訴求</v>
+      </c>
+      <c r="E17" s="9" t="str">
+        <v>對應 #</v>
+      </c>
+      <c r="F17" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G17" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H17" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="str">
+        <v>看得懂</v>
+      </c>
+      <c r="B18" s="11">
+        <v>17</v>
+      </c>
+      <c r="C18" s="11" t="str">
+        <v>31.5%</v>
+      </c>
+      <c r="D18" s="10" t="str">
+        <v>首頁先給重點 / KPI / 異常 / 待辦分區 / 欄位白話 / 狀態流程視覺化</v>
+      </c>
+      <c r="E18" s="10" t="str">
+        <v>#1, #7, #10, #17, #19, #24, #25, #27, #32, #35, #37, #38, #39, #40, #41, #45, #49</v>
+      </c>
+      <c r="F18" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G18" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H18" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="str">
+        <v>找得到</v>
+      </c>
+      <c r="B19" s="11">
+        <v>5</v>
+      </c>
+      <c r="C19" s="11" t="str">
+        <v>9.3%</v>
+      </c>
+      <c r="D19" s="10" t="str">
+        <v>全域搜尋 / 麵包屑 / 側邊欄高亮 / 變更密碼入口</v>
+      </c>
+      <c r="E19" s="10" t="str">
+        <v>#6, #29, #30, #33, #44</v>
+      </c>
+      <c r="F19" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G19" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H19" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="str">
+        <v>做得快</v>
+      </c>
+      <c r="B20" s="11">
+        <v>9</v>
+      </c>
+      <c r="C20" s="11" t="str">
+        <v>16.7%</v>
+      </c>
+      <c r="D20" s="10" t="str">
+        <v>批次操作 / 儲存搜尋 / 大列表 lazy / 匯出進度 / 日期快捷</v>
+      </c>
+      <c r="E20" s="10" t="str">
+        <v>#3, #11, #20, #26, #28, #42, #43, #53, #54</v>
+      </c>
+      <c r="F20" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G20" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H20" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="str">
+        <v>不容易錯</v>
+      </c>
+      <c r="B21" s="11">
+        <v>14</v>
+      </c>
+      <c r="C21" s="11" t="str">
+        <v>25.9%</v>
+      </c>
+      <c r="D21" s="10" t="str">
+        <v>表單驗證 / 刪除確認 / 影響預覽 / 預設值 / 錯誤引導</v>
+      </c>
+      <c r="E21" s="10" t="str">
+        <v>#2, #4, #5, #15, #18, #21, #22, #23, #31, #34, #36, #46, #47, #48</v>
+      </c>
+      <c r="F21" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G21" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H21" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="str">
+        <v>出事能追回來</v>
+      </c>
+      <c r="B22" s="11">
+        <v>5</v>
+      </c>
+      <c r="C22" s="11" t="str">
+        <v>9.3%</v>
+      </c>
+      <c r="D22" s="10" t="str">
+        <v>audit log / 變更歷史 / 軟刪除復原 / token 管理 / 文件交接</v>
+      </c>
+      <c r="E22" s="10" t="str">
+        <v>#9, #12, #50, #51, #52</v>
+      </c>
+      <c r="F22" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G22" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H22" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="str">
+        <v>—</v>
+      </c>
+      <c r="B23" s="11">
+        <v>4</v>
+      </c>
+      <c r="C23" s="11" t="str">
+        <v>7.4%</v>
+      </c>
+      <c r="D23" s="10" t="str">
+        <v>純技術 / 環境設定 (不在 5 主軸範圍)</v>
+      </c>
+      <c r="E23" s="10" t="str">
+        <v>#8, #13, #14, #16</v>
+      </c>
+      <c r="F23" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G23" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H23" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="str">
+        <v>【4】UIUX — 優先級 × 狀態分布</v>
+      </c>
+      <c r="B25" s="7" t="str">
+        <v/>
+      </c>
+      <c r="C25" s="7" t="str">
+        <v/>
+      </c>
+      <c r="D25" s="7" t="str">
+        <v/>
+      </c>
+      <c r="E25" s="7" t="str">
+        <v/>
+      </c>
+      <c r="F25" s="7" t="str">
+        <v/>
+      </c>
+      <c r="G25" s="7" t="str">
+        <v/>
+      </c>
+      <c r="H25" s="7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="str">
+        <v>優先級</v>
+      </c>
+      <c r="B26" s="9" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="C26" s="9" t="str">
+        <v>部分修正</v>
+      </c>
+      <c r="D26" s="9" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="E26" s="9" t="str">
+        <v>小計</v>
+      </c>
+      <c r="F26" s="9" t="str">
+        <v>完成率</v>
+      </c>
+      <c r="G26" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H26" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="str">
+        <v>高</v>
+      </c>
+      <c r="B27" s="15">
+        <v>9</v>
+      </c>
+      <c r="C27" s="16">
+        <v>4</v>
+      </c>
+      <c r="D27" s="17">
+        <v>5</v>
+      </c>
+      <c r="E27" s="11">
+        <v>18</v>
+      </c>
+      <c r="F27" s="11" t="str">
+        <v>61.1%</v>
+      </c>
+      <c r="G27" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H27" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="str">
+        <v>中</v>
+      </c>
+      <c r="B28" s="15">
+        <v>15</v>
+      </c>
+      <c r="C28" s="16">
+        <v>0</v>
+      </c>
+      <c r="D28" s="17">
+        <v>44</v>
+      </c>
+      <c r="E28" s="11">
+        <v>59</v>
+      </c>
+      <c r="F28" s="11" t="str">
+        <v>25.4%</v>
+      </c>
+      <c r="G28" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H28" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="str">
+        <v>低</v>
+      </c>
+      <c r="B29" s="15">
+        <v>18</v>
+      </c>
+      <c r="C29" s="16">
+        <v>2</v>
+      </c>
+      <c r="D29" s="17">
+        <v>35</v>
+      </c>
+      <c r="E29" s="11">
+        <v>55</v>
+      </c>
+      <c r="F29" s="11" t="str">
+        <v>34.5%</v>
+      </c>
+      <c r="G29" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H29" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="str">
+        <v>【5】UIUX — 各區塊問題分布</v>
+      </c>
+      <c r="B31" s="7" t="str">
+        <v/>
+      </c>
+      <c r="C31" s="7" t="str">
+        <v/>
+      </c>
+      <c r="D31" s="7" t="str">
+        <v/>
+      </c>
+      <c r="E31" s="7" t="str">
+        <v/>
+      </c>
+      <c r="F31" s="7" t="str">
+        <v/>
+      </c>
+      <c r="G31" s="7" t="str">
+        <v/>
+      </c>
+      <c r="H31" s="7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="str">
+        <v>區塊</v>
+      </c>
+      <c r="B32" s="9" t="str">
+        <v>項目數</v>
+      </c>
+      <c r="C32" s="9" t="str">
+        <v>佔比</v>
+      </c>
+      <c r="D32" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E32" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F32" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G32" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H32" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="str">
+        <v>i-Fare 福利查詢</v>
+      </c>
+      <c r="B33" s="11">
+        <v>24</v>
+      </c>
+      <c r="C33" s="11" t="str">
+        <v>18.2%</v>
+      </c>
+      <c r="D33" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E33" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F33" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G33" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H33" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="B34" s="11">
+        <v>24</v>
+      </c>
+      <c r="C34" s="11" t="str">
+        <v>18.2%</v>
+      </c>
+      <c r="D34" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E34" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F34" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G34" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H34" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="str">
+        <v>全站通用</v>
+      </c>
+      <c r="B35" s="11">
+        <v>24</v>
+      </c>
+      <c r="C35" s="11" t="str">
+        <v>18.2%</v>
+      </c>
+      <c r="D35" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E35" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F35" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G35" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H35" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="str">
+        <v>福利專欄</v>
+      </c>
+      <c r="B36" s="11">
+        <v>11</v>
+      </c>
+      <c r="C36" s="11" t="str">
+        <v>8.3%</v>
+      </c>
+      <c r="D36" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E36" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F36" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G36" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H36" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="str">
+        <v>關於長穩</v>
+      </c>
+      <c r="B37" s="11">
+        <v>9</v>
+      </c>
+      <c r="C37" s="11" t="str">
+        <v>6.8%</v>
+      </c>
+      <c r="D37" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E37" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F37" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G37" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H37" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="str">
+        <v>首頁</v>
+      </c>
+      <c r="B38" s="11">
+        <v>8</v>
+      </c>
+      <c r="C38" s="11" t="str">
+        <v>6.1%</v>
+      </c>
+      <c r="D38" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E38" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F38" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G38" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H38" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="str">
+        <v>最新消息</v>
+      </c>
+      <c r="B39" s="11">
+        <v>8</v>
+      </c>
+      <c r="C39" s="11" t="str">
+        <v>6.1%</v>
+      </c>
+      <c r="D39" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E39" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F39" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G39" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H39" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="str">
+        <v>全站微互動</v>
+      </c>
+      <c r="B40" s="11">
+        <v>5</v>
+      </c>
+      <c r="C40" s="11" t="str">
+        <v>3.8%</v>
+      </c>
+      <c r="D40" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E40" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F40" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G40" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H40" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="str">
+        <v>設計系統</v>
+      </c>
+      <c r="B41" s="11">
+        <v>5</v>
+      </c>
+      <c r="C41" s="11" t="str">
+        <v>3.8%</v>
+      </c>
+      <c r="D41" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E41" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F41" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G41" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H41" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="str">
+        <v>公益夥伴</v>
+      </c>
+      <c r="B42" s="11">
+        <v>4</v>
+      </c>
+      <c r="C42" s="11" t="str">
+        <v>3.0%</v>
+      </c>
+      <c r="D42" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E42" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F42" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G42" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H42" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="str">
+        <v>安全性</v>
+      </c>
+      <c r="B43" s="11">
+        <v>2</v>
+      </c>
+      <c r="C43" s="11" t="str">
+        <v>1.5%</v>
+      </c>
+      <c r="D43" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E43" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F43" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G43" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H43" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="str">
+        <v>無障礙</v>
+      </c>
+      <c r="B44" s="11">
+        <v>2</v>
+      </c>
+      <c r="C44" s="11" t="str">
+        <v>1.5%</v>
+      </c>
+      <c r="D44" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E44" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F44" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G44" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H44" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="str">
+        <v>未來規劃</v>
+      </c>
+      <c r="B45" s="11">
+        <v>1</v>
+      </c>
+      <c r="C45" s="11" t="str">
+        <v>0.8%</v>
+      </c>
+      <c r="D45" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E45" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F45" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G45" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H45" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="str">
+        <v>頁面導航</v>
+      </c>
+      <c r="B46" s="11">
+        <v>1</v>
+      </c>
+      <c r="C46" s="11" t="str">
+        <v>0.8%</v>
+      </c>
+      <c r="D46" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E46" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F46" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G46" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H46" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="str">
+        <v>i-Fare 搜尋結果</v>
+      </c>
+      <c r="B47" s="11">
+        <v>1</v>
+      </c>
+      <c r="C47" s="11" t="str">
+        <v>0.8%</v>
+      </c>
+      <c r="D47" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E47" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F47" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G47" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H47" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="str">
+        <v>效能</v>
+      </c>
+      <c r="B48" s="11">
+        <v>1</v>
+      </c>
+      <c r="C48" s="11" t="str">
+        <v>0.8%</v>
+      </c>
+      <c r="D48" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E48" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F48" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G48" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H48" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="str">
+        <v>社群分享</v>
+      </c>
+      <c r="B49" s="11">
+        <v>1</v>
+      </c>
+      <c r="C49" s="11" t="str">
+        <v>0.8%</v>
+      </c>
+      <c r="D49" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E49" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F49" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G49" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H49" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="str">
+        <v>導航</v>
+      </c>
+      <c r="B50" s="11">
+        <v>1</v>
+      </c>
+      <c r="C50" s="11" t="str">
+        <v>0.8%</v>
+      </c>
+      <c r="D50" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E50" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F50" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G50" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H50" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="str">
+        <v>【6】後臺優化 — 各區塊問題分布</v>
+      </c>
+      <c r="B52" s="7" t="str">
+        <v/>
+      </c>
+      <c r="C52" s="7" t="str">
+        <v/>
+      </c>
+      <c r="D52" s="7" t="str">
+        <v/>
+      </c>
+      <c r="E52" s="7" t="str">
+        <v/>
+      </c>
+      <c r="F52" s="7" t="str">
+        <v/>
+      </c>
+      <c r="G52" s="7" t="str">
+        <v/>
+      </c>
+      <c r="H52" s="7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="str">
+        <v>區塊</v>
+      </c>
+      <c r="B53" s="9" t="str">
+        <v>項目數</v>
+      </c>
+      <c r="C53" s="9" t="str">
+        <v>佔比</v>
+      </c>
+      <c r="D53" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E53" s="9" t="str">
+        <v/>
+      </c>
+      <c r="F53" s="9" t="str">
+        <v/>
+      </c>
+      <c r="G53" s="9" t="str">
+        <v/>
+      </c>
+      <c r="H53" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="B54" s="11">
+        <v>16</v>
+      </c>
+      <c r="C54" s="11" t="str">
+        <v>29.6%</v>
+      </c>
+      <c r="D54" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E54" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F54" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G54" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H54" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="str">
+        <v>後台通用</v>
+      </c>
+      <c r="B55" s="11">
+        <v>15</v>
+      </c>
+      <c r="C55" s="11" t="str">
+        <v>27.8%</v>
+      </c>
+      <c r="D55" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E55" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F55" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G55" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H55" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="str">
+        <v>i-Fare 維護</v>
+      </c>
+      <c r="B56" s="11">
+        <v>2</v>
+      </c>
+      <c r="C56" s="11" t="str">
+        <v>3.7%</v>
+      </c>
+      <c r="D56" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E56" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F56" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G56" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H56" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="str">
+        <v>圖片管理</v>
+      </c>
+      <c r="B57" s="11">
+        <v>2</v>
+      </c>
+      <c r="C57" s="11" t="str">
+        <v>3.7%</v>
+      </c>
+      <c r="D57" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E57" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F57" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G57" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H57" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="str">
+        <v>最新消息維護</v>
+      </c>
+      <c r="B58" s="11">
+        <v>1</v>
+      </c>
+      <c r="C58" s="11" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D58" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E58" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F58" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G58" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H58" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="str">
+        <v>帳戶維護 / 全站權限</v>
+      </c>
+      <c r="B59" s="11">
+        <v>1</v>
+      </c>
+      <c r="C59" s="11" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D59" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E59" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F59" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G59" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H59" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="str">
+        <v>前台通用</v>
+      </c>
+      <c r="B60" s="11">
+        <v>1</v>
+      </c>
+      <c r="C60" s="11" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D60" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E60" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F60" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G60" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H60" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="str">
+        <v>對話框</v>
+      </c>
+      <c r="B61" s="11">
+        <v>1</v>
+      </c>
+      <c r="C61" s="11" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D61" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E61" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F61" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G61" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H61" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="str">
+        <v>檔案上傳</v>
+      </c>
+      <c r="B62" s="11">
+        <v>1</v>
+      </c>
+      <c r="C62" s="11" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D62" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E62" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F62" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G62" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H62" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="str">
+        <v>帳號管理</v>
+      </c>
+      <c r="B63" s="11">
+        <v>1</v>
+      </c>
+      <c r="C63" s="11" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D63" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E63" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F63" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G63" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H63" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="str">
+        <v>搜尋結果</v>
+      </c>
+      <c r="B64" s="11">
+        <v>1</v>
+      </c>
+      <c r="C64" s="11" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D64" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E64" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F64" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G64" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H64" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="str">
+        <v>日期選擇</v>
+      </c>
+      <c r="B65" s="11">
+        <v>1</v>
+      </c>
+      <c r="C65" s="11" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D65" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E65" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F65" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G65" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H65" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="str">
+        <v>表單</v>
+      </c>
+      <c r="B66" s="11">
+        <v>1</v>
+      </c>
+      <c r="C66" s="11" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D66" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E66" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F66" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G66" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H66" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="str">
+        <v>側邊欄</v>
+      </c>
+      <c r="B67" s="11">
+        <v>1</v>
+      </c>
+      <c r="C67" s="11" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D67" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E67" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F67" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G67" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H67" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="str">
+        <v>麵包屑導覽</v>
+      </c>
+      <c r="B68" s="11">
+        <v>1</v>
+      </c>
+      <c r="C68" s="11" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D68" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E68" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F68" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G68" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H68" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="str">
+        <v>WebAPI</v>
+      </c>
+      <c r="B69" s="11">
+        <v>1</v>
+      </c>
+      <c r="C69" s="11" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D69" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E69" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F69" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G69" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H69" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="str">
+        <v>帳號變更密碼</v>
+      </c>
+      <c r="B70" s="11">
+        <v>1</v>
+      </c>
+      <c r="C70" s="11" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D70" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E70" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F70" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G70" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H70" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="str">
+        <v>Code 代碼管理</v>
+      </c>
+      <c r="B71" s="11">
+        <v>1</v>
+      </c>
+      <c r="C71" s="11" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D71" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E71" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F71" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G71" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H71" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="str">
+        <v>狀態管理</v>
+      </c>
+      <c r="B72" s="11">
+        <v>1</v>
+      </c>
+      <c r="C72" s="11" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D72" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E72" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F72" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G72" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H72" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="str">
+        <v>登入頁面</v>
+      </c>
+      <c r="B73" s="11">
+        <v>1</v>
+      </c>
+      <c r="C73" s="11" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D73" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E73" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F73" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G73" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H73" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="str">
+        <v>HTML 編輯器</v>
+      </c>
+      <c r="B74" s="11">
+        <v>1</v>
+      </c>
+      <c r="C74" s="11" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D74" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E74" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F74" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G74" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H74" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="str">
+        <v>無權限頁</v>
+      </c>
+      <c r="B75" s="11">
+        <v>1</v>
+      </c>
+      <c r="C75" s="11" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D75" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E75" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F75" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G75" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H75" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="str">
+        <v>效能</v>
+      </c>
+      <c r="B76" s="11">
+        <v>1</v>
+      </c>
+      <c r="C76" s="11" t="str">
+        <v>1.9%</v>
+      </c>
+      <c r="D76" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E76" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F76" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G76" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H76" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="str">
+        <v>【7】你做了什麼 — 已完成項目摘要 (依 Round 分組)</v>
+      </c>
+      <c r="B78" s="7" t="str">
+        <v/>
+      </c>
+      <c r="C78" s="7" t="str">
+        <v/>
+      </c>
+      <c r="D78" s="7" t="str">
+        <v/>
+      </c>
+      <c r="E78" s="7" t="str">
+        <v/>
+      </c>
+      <c r="F78" s="7" t="str">
+        <v/>
+      </c>
+      <c r="G78" s="7" t="str">
+        <v/>
+      </c>
+      <c r="H78" s="7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="str">
         <v>Round</v>
       </c>
-      <c r="B8" s="3" t="str">
+      <c r="B79" s="9" t="str">
         <v>日期</v>
       </c>
-      <c r="C8" s="3" t="str">
-        <v>主題</v>
-      </c>
-      <c r="D8" s="3" t="str">
-        <v>UIUX 標完成</v>
-      </c>
-      <c r="E8" s="3" t="str">
-        <v>UIUX 新增</v>
-      </c>
-      <c r="F8" s="3" t="str">
-        <v>後臺新增</v>
-      </c>
-      <c r="G8" s="3" t="str">
-        <v>Schema</v>
-      </c>
-      <c r="H8" s="3" t="str">
-        <v>主要產出</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="str">
+      <c r="C79" s="9" t="str">
+        <v>已修正 (綠)</v>
+      </c>
+      <c r="D79" s="9" t="str">
+        <v>部分修正 (黃)</v>
+      </c>
+      <c r="E79" s="9" t="str">
+        <v>已修正 # 清單</v>
+      </c>
+      <c r="F79" s="9" t="str">
+        <v>部分修正 # 清單</v>
+      </c>
+      <c r="G79" s="9" t="str">
+        <v>主要重點</v>
+      </c>
+      <c r="H79" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="str">
         <v>Round 1</v>
       </c>
-      <c r="B9" s="3" t="str">
+      <c r="B80" s="10" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="C9" s="3" t="str">
-        <v>UI/UX 改版 (搜尋 / Footer / 全站動畫 / RWD)</v>
-      </c>
-      <c r="D9" s="3">
-        <v>7</v>
-      </c>
-      <c r="E9" s="3">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3">
+      <c r="C80" s="15">
+        <v>26</v>
+      </c>
+      <c r="D80" s="16">
+        <v>6</v>
+      </c>
+      <c r="E80" s="10" t="str">
+        <v>#16, #17, #22, #23, #24, #44, #54, #59, #88, #89, #90, #106, #108, #109, #110, #112, #114, #115, #118, #120, #125, #126, #127, #130, #131, #132</v>
+      </c>
+      <c r="F80" s="10" t="str">
+        <v>#1, #9, #60, #71, #80, #107</v>
+      </c>
+      <c r="G80" s="10" t="str">
+        <v>搜尋優化 (移除 disabled / 結果摘要) + 全站動畫 + skeleton 載入 + 卡片/按鈕 hover translateY</v>
+      </c>
+      <c r="H80" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="str">
+        <v>Round 2</v>
+      </c>
+      <c r="B81" s="10" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="C81" s="15">
+        <v>2</v>
+      </c>
+      <c r="D81" s="16">
         <v>0</v>
       </c>
-      <c r="G9" s="3" t="str">
+      <c r="E81" s="10" t="str">
+        <v>#91, #92</v>
+      </c>
+      <c r="F81" s="10" t="str">
         <v>-</v>
       </c>
-      <c r="H9" s="3" t="str">
-        <v>pages/ifare 加關鍵字搜尋 + URL query 初始化；全站 NuxtPage transition；卡片/按鈕 hover translateY</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="str">
-        <v>Round 2</v>
-      </c>
-      <c r="B10" s="3" t="str">
+      <c r="G81" s="10" t="str">
+        <v>Footer 整合 (LINE/FB 並列 .btn-social) + 觸控目標 44px</v>
+      </c>
+      <c r="H81" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="str">
+        <v>Round 3</v>
+      </c>
+      <c r="B82" s="10" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="C10" s="3" t="str">
-        <v>Footer 整理 + RWD 修正</v>
-      </c>
-      <c r="D10" s="3">
-        <v>2</v>
-      </c>
-      <c r="E10" s="3">
-        <v>2</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="C82" s="15">
+        <v>6</v>
+      </c>
+      <c r="D82" s="16">
         <v>0</v>
       </c>
-      <c r="G10" s="3" t="str">
+      <c r="E82" s="10" t="str">
+        <v>#26, #93, #94, #95, #96, #97</v>
+      </c>
+      <c r="F82" s="10" t="str">
         <v>-</v>
       </c>
-      <c r="H10" s="3" t="str">
-        <v>LINE/FB 統一 .btn-social 並排；4 個聯絡資訊加 icon (Tel/Mail/Address/Clock)；footer 觸控 44px</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="str">
-        <v>Round 3</v>
-      </c>
-      <c r="B11" s="3" t="str">
-        <v>2026-04-28</v>
-      </c>
-      <c r="C11" s="3" t="str">
-        <v>About 靈動島 + News 卡片升級 + 社群外連結</v>
-      </c>
-      <c r="D11" s="3">
-        <v>4</v>
-      </c>
-      <c r="E11" s="3">
-        <v>5</v>
-      </c>
-      <c r="F11" s="3">
+      <c r="G82" s="10" t="str">
+        <v>About 三大核心 morph 卡 + News 浮起卡 + 浮現動畫 + line-clamp + NEW pill + 社群 target="_blank"</v>
+      </c>
+      <c r="H82" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="str">
+        <v>Round 4</v>
+      </c>
+      <c r="B83" s="10" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="C83" s="15">
+        <v>8</v>
+      </c>
+      <c r="D83" s="16">
         <v>0</v>
       </c>
-      <c r="G11" s="3" t="str">
+      <c r="E83" s="10" t="str">
+        <v>#98, #99, #100, #101, #102, #103, #104, #105</v>
+      </c>
+      <c r="F83" s="10" t="str">
         <v>-</v>
       </c>
-      <c r="H11" s="3" t="str">
-        <v>About 三大核心 morph 卡 (cf47cfa)；News 浮起卡 + stagger fade-up + NEW pill；外連結 target="_blank" rel="noopener"</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="str">
-        <v>Round 4</v>
-      </c>
-      <c r="B12" s="3" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="C12" s="3" t="str">
-        <v>切回 master + 開新分支 feat/uiux-round4 + 補做 (環境/補回/新功能)</v>
-      </c>
-      <c r="D12" s="3">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3">
-        <v>8</v>
-      </c>
-      <c r="F12" s="3">
-        <v>4</v>
-      </c>
-      <c r="G12" s="3" t="str">
-        <v>-</v>
-      </c>
-      <c r="H12" s="3" t="str">
-        <v>cf47cfa+5dfbf91 補回 16 檔；devProxy/baseURL → 正式 API；nav 加未來規劃 + future.vue；News videoUrl wiring；tsconfig deprecation 清理；about hover bug 修；footer label 重複修</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="str">
-        <v>Round 5</v>
-      </c>
-      <c r="B13" s="3" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="C13" s="3" t="str">
-        <v>前後台全面審查 — 後台 UX audit + 前台新 issue 掃描</v>
-      </c>
-      <c r="D13" s="3">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3">
-        <v>26</v>
-      </c>
-      <c r="F13" s="3">
-        <v>22</v>
-      </c>
-      <c r="G13" s="3" t="str">
-        <v>-</v>
-      </c>
-      <c r="H13" s="3" t="str">
-        <v>後台 22 個工程角度問題 (CRUD/驗證/錯誤處理)；前台 26 個新發現 (XSS/超時/console.log/無障礙/分頁元件重複)</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="str">
-        <v>Round 6</v>
-      </c>
-      <c r="B14" s="3" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="C14" s="3" t="str">
-        <v>人性化主軸提案 — 5 主軸 + 16 後台項</v>
-      </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>16</v>
-      </c>
-      <c r="G14" s="3" t="str">
-        <v>+ Q 欄主軸</v>
-      </c>
-      <c r="H14" s="3" t="str">
-        <v>Dashboard 角色化 / 今日待辦 / KPI 分區；批次操作；軟刪除復原；audit log；危險操作預覽；錯誤訊息引導</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="str">
-        <v>【3】後臺優化 — 5 主軸分布 (拿這個去提案!)</v>
-      </c>
-      <c r="B16" s="3" t="str">
-        <v/>
-      </c>
-      <c r="C16" s="3" t="str">
-        <v/>
-      </c>
-      <c r="D16" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E16" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F16" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G16" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H16" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="str">
-        <v>主軸</v>
-      </c>
-      <c r="B17" s="3" t="str">
-        <v>項目數</v>
-      </c>
-      <c r="C17" s="3" t="str">
-        <v>比例</v>
-      </c>
-      <c r="D17" s="3" t="str">
-        <v>主要訴求</v>
-      </c>
-      <c r="E17" s="3" t="str">
-        <v>對應 #</v>
-      </c>
-      <c r="F17" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G17" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H17" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="str">
-        <v>看得懂</v>
-      </c>
-      <c r="B18" s="3">
-        <v>17</v>
-      </c>
-      <c r="C18" s="3" t="str">
-        <v>31.5%</v>
-      </c>
-      <c r="D18" s="3" t="str">
-        <v>首頁先給重點 / KPI / 異常 / 待辦分區 / 欄位白話 / 狀態流程視覺化</v>
-      </c>
-      <c r="E18" s="3" t="str">
-        <v>#1, #7, #10, #17, #19, #24, #25, #27, #32, #35, #37, #38, #39, #40, #41, #45, #49</v>
-      </c>
-      <c r="F18" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G18" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H18" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="str">
-        <v>找得到</v>
-      </c>
-      <c r="B19" s="3">
-        <v>5</v>
-      </c>
-      <c r="C19" s="3" t="str">
-        <v>9.3%</v>
-      </c>
-      <c r="D19" s="3" t="str">
-        <v>全域搜尋 / 麵包屑 / 側邊欄高亮 / 變更密碼入口</v>
-      </c>
-      <c r="E19" s="3" t="str">
-        <v>#6, #29, #30, #33, #44</v>
-      </c>
-      <c r="F19" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G19" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H19" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="str">
-        <v>做得快</v>
-      </c>
-      <c r="B20" s="3">
-        <v>9</v>
-      </c>
-      <c r="C20" s="3" t="str">
-        <v>16.7%</v>
-      </c>
-      <c r="D20" s="3" t="str">
-        <v>批次操作 / 儲存搜尋 / 大列表 lazy / 匯出進度 / 日期快捷</v>
-      </c>
-      <c r="E20" s="3" t="str">
-        <v>#3, #11, #20, #26, #28, #42, #43, #53, #54</v>
-      </c>
-      <c r="F20" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G20" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H20" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="str">
-        <v>不容易錯</v>
-      </c>
-      <c r="B21" s="3">
-        <v>14</v>
-      </c>
-      <c r="C21" s="3" t="str">
-        <v>25.9%</v>
-      </c>
-      <c r="D21" s="3" t="str">
-        <v>表單驗證 / 刪除確認 / 影響預覽 / 預設值 / 錯誤引導</v>
-      </c>
-      <c r="E21" s="3" t="str">
-        <v>#2, #4, #5, #15, #18, #21, #22, #23, #31, #34, #36, #46, #47, #48</v>
-      </c>
-      <c r="F21" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G21" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H21" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="str">
-        <v>出事能追回來</v>
-      </c>
-      <c r="B22" s="3">
-        <v>5</v>
-      </c>
-      <c r="C22" s="3" t="str">
-        <v>9.3%</v>
-      </c>
-      <c r="D22" s="3" t="str">
-        <v>audit log / 變更歷史 / 軟刪除復原 / token 管理 / 文件交接</v>
-      </c>
-      <c r="E22" s="3" t="str">
-        <v>#9, #12, #50, #51, #52</v>
-      </c>
-      <c r="F22" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G22" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H22" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="str">
-        <v>—</v>
-      </c>
-      <c r="B23" s="3">
-        <v>4</v>
-      </c>
-      <c r="C23" s="3" t="str">
-        <v>7.4%</v>
-      </c>
-      <c r="D23" s="3" t="str">
-        <v>純技術 / 環境設定 (不在 5 主軸範圍)</v>
-      </c>
-      <c r="E23" s="3" t="str">
-        <v>#8, #13, #14, #16</v>
-      </c>
-      <c r="F23" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G23" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H23" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="str">
-        <v>【4】UIUX — 優先級 × 狀態分布</v>
-      </c>
-      <c r="B25" s="3" t="str">
-        <v/>
-      </c>
-      <c r="C25" s="3" t="str">
-        <v/>
-      </c>
-      <c r="D25" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E25" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F25" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G25" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H25" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="str">
-        <v>優先級</v>
-      </c>
-      <c r="B26" s="3" t="str">
-        <v>已修正</v>
-      </c>
-      <c r="C26" s="3" t="str">
-        <v>部分修正</v>
-      </c>
-      <c r="D26" s="3" t="str">
-        <v>待處理</v>
-      </c>
-      <c r="E26" s="3" t="str">
-        <v>小計</v>
-      </c>
-      <c r="F26" s="3" t="str">
-        <v>完成率</v>
-      </c>
-      <c r="G26" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H26" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="str">
-        <v>高</v>
-      </c>
-      <c r="B27" s="3">
-        <v>7</v>
-      </c>
-      <c r="C27" s="3">
-        <v>4</v>
-      </c>
-      <c r="D27" s="3">
-        <v>6</v>
-      </c>
-      <c r="E27" s="3">
-        <v>17</v>
-      </c>
-      <c r="F27" s="3" t="str">
-        <v>52.9%</v>
-      </c>
-      <c r="G27" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H27" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="str">
-        <v>中</v>
-      </c>
-      <c r="B28" s="3">
-        <v>14</v>
-      </c>
-      <c r="C28" s="3">
-        <v>1</v>
-      </c>
-      <c r="D28" s="3">
-        <v>44</v>
-      </c>
-      <c r="E28" s="3">
-        <v>59</v>
-      </c>
-      <c r="F28" s="3" t="str">
-        <v>24.6%</v>
-      </c>
-      <c r="G28" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H28" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="str">
-        <v>低</v>
-      </c>
-      <c r="B29" s="3">
-        <v>18</v>
-      </c>
-      <c r="C29" s="3">
-        <v>2</v>
-      </c>
-      <c r="D29" s="3">
-        <v>35</v>
-      </c>
-      <c r="E29" s="3">
-        <v>55</v>
-      </c>
-      <c r="F29" s="3" t="str">
-        <v>34.5%</v>
-      </c>
-      <c r="G29" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H29" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="str">
-        <v>【5】UIUX — 各區塊問題分布</v>
-      </c>
-      <c r="B31" s="3" t="str">
-        <v/>
-      </c>
-      <c r="C31" s="3" t="str">
-        <v/>
-      </c>
-      <c r="D31" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E31" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F31" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G31" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H31" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="str">
-        <v>區塊</v>
-      </c>
-      <c r="B32" s="3" t="str">
-        <v>項目數</v>
-      </c>
-      <c r="C32" s="3" t="str">
-        <v>佔比</v>
-      </c>
-      <c r="D32" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E32" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F32" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G32" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H32" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="str">
-        <v>共用元件</v>
-      </c>
-      <c r="B33" s="3">
-        <v>24</v>
-      </c>
-      <c r="C33" s="3" t="str">
-        <v>18.3%</v>
-      </c>
-      <c r="D33" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E33" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F33" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G33" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H33" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="str">
-        <v>全站通用</v>
-      </c>
-      <c r="B34" s="3">
-        <v>24</v>
-      </c>
-      <c r="C34" s="3" t="str">
-        <v>18.3%</v>
-      </c>
-      <c r="D34" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E34" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F34" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G34" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H34" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="str">
-        <v>i-Fare 福利查詢</v>
-      </c>
-      <c r="B35" s="3">
-        <v>23</v>
-      </c>
-      <c r="C35" s="3" t="str">
-        <v>17.6%</v>
-      </c>
-      <c r="D35" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E35" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F35" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G35" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H35" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="str">
-        <v>福利專欄</v>
-      </c>
-      <c r="B36" s="3">
-        <v>11</v>
-      </c>
-      <c r="C36" s="3" t="str">
-        <v>8.4%</v>
-      </c>
-      <c r="D36" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E36" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F36" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G36" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H36" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="str">
-        <v>關於長穩</v>
-      </c>
-      <c r="B37" s="3">
-        <v>9</v>
-      </c>
-      <c r="C37" s="3" t="str">
-        <v>6.9%</v>
-      </c>
-      <c r="D37" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E37" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F37" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G37" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H37" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="str">
-        <v>首頁</v>
-      </c>
-      <c r="B38" s="3">
-        <v>8</v>
-      </c>
-      <c r="C38" s="3" t="str">
-        <v>6.1%</v>
-      </c>
-      <c r="D38" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E38" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F38" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G38" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H38" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="str">
-        <v>最新消息</v>
-      </c>
-      <c r="B39" s="3">
-        <v>8</v>
-      </c>
-      <c r="C39" s="3" t="str">
-        <v>6.1%</v>
-      </c>
-      <c r="D39" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E39" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F39" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G39" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H39" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="str">
-        <v>全站微互動</v>
-      </c>
-      <c r="B40" s="3">
-        <v>5</v>
-      </c>
-      <c r="C40" s="3" t="str">
-        <v>3.8%</v>
-      </c>
-      <c r="D40" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E40" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F40" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G40" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H40" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="str">
-        <v>設計系統</v>
-      </c>
-      <c r="B41" s="3">
-        <v>5</v>
-      </c>
-      <c r="C41" s="3" t="str">
-        <v>3.8%</v>
-      </c>
-      <c r="D41" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E41" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F41" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G41" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H41" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="str">
-        <v>公益夥伴</v>
-      </c>
-      <c r="B42" s="3">
-        <v>4</v>
-      </c>
-      <c r="C42" s="3" t="str">
-        <v>3.1%</v>
-      </c>
-      <c r="D42" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E42" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F42" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G42" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H42" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="str">
-        <v>安全性</v>
-      </c>
-      <c r="B43" s="3">
-        <v>2</v>
-      </c>
-      <c r="C43" s="3" t="str">
-        <v>1.5%</v>
-      </c>
-      <c r="D43" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E43" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F43" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G43" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H43" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="str">
-        <v>無障礙</v>
-      </c>
-      <c r="B44" s="3">
-        <v>2</v>
-      </c>
-      <c r="C44" s="3" t="str">
-        <v>1.5%</v>
-      </c>
-      <c r="D44" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E44" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F44" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G44" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H44" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="str">
-        <v>未來規劃</v>
-      </c>
-      <c r="B45" s="3">
-        <v>1</v>
-      </c>
-      <c r="C45" s="3" t="str">
-        <v>0.8%</v>
-      </c>
-      <c r="D45" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E45" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F45" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G45" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H45" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="str">
-        <v>頁面導航</v>
-      </c>
-      <c r="B46" s="3">
-        <v>1</v>
-      </c>
-      <c r="C46" s="3" t="str">
-        <v>0.8%</v>
-      </c>
-      <c r="D46" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E46" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F46" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G46" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H46" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="str">
-        <v>i-Fare 搜尋結果</v>
-      </c>
-      <c r="B47" s="3">
-        <v>1</v>
-      </c>
-      <c r="C47" s="3" t="str">
-        <v>0.8%</v>
-      </c>
-      <c r="D47" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E47" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F47" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G47" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H47" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="str">
-        <v>效能</v>
-      </c>
-      <c r="B48" s="3">
-        <v>1</v>
-      </c>
-      <c r="C48" s="3" t="str">
-        <v>0.8%</v>
-      </c>
-      <c r="D48" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E48" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F48" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G48" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H48" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="str">
-        <v>社群分享</v>
-      </c>
-      <c r="B49" s="3">
-        <v>1</v>
-      </c>
-      <c r="C49" s="3" t="str">
-        <v>0.8%</v>
-      </c>
-      <c r="D49" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E49" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F49" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G49" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H49" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="str">
-        <v>導航</v>
-      </c>
-      <c r="B50" s="3">
-        <v>1</v>
-      </c>
-      <c r="C50" s="3" t="str">
-        <v>0.8%</v>
-      </c>
-      <c r="D50" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E50" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F50" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G50" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H50" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="str">
-        <v>【6】後臺優化 — 各區塊問題分布</v>
-      </c>
-      <c r="B52" s="3" t="str">
-        <v/>
-      </c>
-      <c r="C52" s="3" t="str">
-        <v/>
-      </c>
-      <c r="D52" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E52" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F52" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G52" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H52" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="str">
-        <v>區塊</v>
-      </c>
-      <c r="B53" s="3" t="str">
-        <v>項目數</v>
-      </c>
-      <c r="C53" s="3" t="str">
-        <v>佔比</v>
-      </c>
-      <c r="D53" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E53" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F53" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G53" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H53" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="str">
-        <v>共用元件</v>
-      </c>
-      <c r="B54" s="3">
-        <v>16</v>
-      </c>
-      <c r="C54" s="3" t="str">
-        <v>29.6%</v>
-      </c>
-      <c r="D54" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E54" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F54" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G54" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H54" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="str">
-        <v>後台通用</v>
-      </c>
-      <c r="B55" s="3">
-        <v>15</v>
-      </c>
-      <c r="C55" s="3" t="str">
-        <v>27.8%</v>
-      </c>
-      <c r="D55" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E55" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F55" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G55" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H55" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="str">
-        <v>i-Fare 維護</v>
-      </c>
-      <c r="B56" s="3">
-        <v>2</v>
-      </c>
-      <c r="C56" s="3" t="str">
-        <v>3.7%</v>
-      </c>
-      <c r="D56" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E56" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F56" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G56" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H56" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="str">
-        <v>圖片管理</v>
-      </c>
-      <c r="B57" s="3">
-        <v>2</v>
-      </c>
-      <c r="C57" s="3" t="str">
-        <v>3.7%</v>
-      </c>
-      <c r="D57" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E57" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F57" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G57" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H57" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="str">
-        <v>最新消息維護</v>
-      </c>
-      <c r="B58" s="3">
-        <v>1</v>
-      </c>
-      <c r="C58" s="3" t="str">
-        <v>1.9%</v>
-      </c>
-      <c r="D58" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E58" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F58" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G58" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H58" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="str">
-        <v>帳戶維護 / 全站權限</v>
-      </c>
-      <c r="B59" s="3">
-        <v>1</v>
-      </c>
-      <c r="C59" s="3" t="str">
-        <v>1.9%</v>
-      </c>
-      <c r="D59" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E59" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F59" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G59" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H59" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="str">
-        <v>前台通用</v>
-      </c>
-      <c r="B60" s="3">
-        <v>1</v>
-      </c>
-      <c r="C60" s="3" t="str">
-        <v>1.9%</v>
-      </c>
-      <c r="D60" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E60" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F60" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G60" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H60" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="str">
-        <v>對話框</v>
-      </c>
-      <c r="B61" s="3">
-        <v>1</v>
-      </c>
-      <c r="C61" s="3" t="str">
-        <v>1.9%</v>
-      </c>
-      <c r="D61" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E61" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F61" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G61" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H61" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="str">
-        <v>檔案上傳</v>
-      </c>
-      <c r="B62" s="3">
-        <v>1</v>
-      </c>
-      <c r="C62" s="3" t="str">
-        <v>1.9%</v>
-      </c>
-      <c r="D62" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E62" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F62" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G62" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H62" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="str">
-        <v>帳號管理</v>
-      </c>
-      <c r="B63" s="3">
-        <v>1</v>
-      </c>
-      <c r="C63" s="3" t="str">
-        <v>1.9%</v>
-      </c>
-      <c r="D63" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E63" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F63" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G63" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H63" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="str">
-        <v>搜尋結果</v>
-      </c>
-      <c r="B64" s="3">
-        <v>1</v>
-      </c>
-      <c r="C64" s="3" t="str">
-        <v>1.9%</v>
-      </c>
-      <c r="D64" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E64" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F64" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G64" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H64" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="str">
-        <v>日期選擇</v>
-      </c>
-      <c r="B65" s="3">
-        <v>1</v>
-      </c>
-      <c r="C65" s="3" t="str">
-        <v>1.9%</v>
-      </c>
-      <c r="D65" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E65" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F65" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G65" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H65" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="str">
-        <v>表單</v>
-      </c>
-      <c r="B66" s="3">
-        <v>1</v>
-      </c>
-      <c r="C66" s="3" t="str">
-        <v>1.9%</v>
-      </c>
-      <c r="D66" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E66" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F66" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G66" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H66" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="str">
-        <v>側邊欄</v>
-      </c>
-      <c r="B67" s="3">
-        <v>1</v>
-      </c>
-      <c r="C67" s="3" t="str">
-        <v>1.9%</v>
-      </c>
-      <c r="D67" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E67" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F67" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G67" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H67" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="str">
-        <v>麵包屑導覽</v>
-      </c>
-      <c r="B68" s="3">
-        <v>1</v>
-      </c>
-      <c r="C68" s="3" t="str">
-        <v>1.9%</v>
-      </c>
-      <c r="D68" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E68" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F68" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G68" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H68" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="str">
-        <v>WebAPI</v>
-      </c>
-      <c r="B69" s="3">
-        <v>1</v>
-      </c>
-      <c r="C69" s="3" t="str">
-        <v>1.9%</v>
-      </c>
-      <c r="D69" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E69" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F69" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G69" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H69" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="str">
-        <v>帳號變更密碼</v>
-      </c>
-      <c r="B70" s="3">
-        <v>1</v>
-      </c>
-      <c r="C70" s="3" t="str">
-        <v>1.9%</v>
-      </c>
-      <c r="D70" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E70" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F70" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G70" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H70" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="str">
-        <v>Code 代碼管理</v>
-      </c>
-      <c r="B71" s="3">
-        <v>1</v>
-      </c>
-      <c r="C71" s="3" t="str">
-        <v>1.9%</v>
-      </c>
-      <c r="D71" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E71" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F71" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G71" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H71" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="str">
-        <v>狀態管理</v>
-      </c>
-      <c r="B72" s="3">
-        <v>1</v>
-      </c>
-      <c r="C72" s="3" t="str">
-        <v>1.9%</v>
-      </c>
-      <c r="D72" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E72" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F72" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G72" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H72" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="str">
-        <v>登入頁面</v>
-      </c>
-      <c r="B73" s="3">
-        <v>1</v>
-      </c>
-      <c r="C73" s="3" t="str">
-        <v>1.9%</v>
-      </c>
-      <c r="D73" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E73" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F73" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G73" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H73" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="str">
-        <v>HTML 編輯器</v>
-      </c>
-      <c r="B74" s="3">
-        <v>1</v>
-      </c>
-      <c r="C74" s="3" t="str">
-        <v>1.9%</v>
-      </c>
-      <c r="D74" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E74" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F74" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G74" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H74" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="str">
-        <v>無權限頁</v>
-      </c>
-      <c r="B75" s="3">
-        <v>1</v>
-      </c>
-      <c r="C75" s="3" t="str">
-        <v>1.9%</v>
-      </c>
-      <c r="D75" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E75" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F75" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G75" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H75" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="str">
-        <v>效能</v>
-      </c>
-      <c r="B76" s="3">
-        <v>1</v>
-      </c>
-      <c r="C76" s="3" t="str">
-        <v>1.9%</v>
-      </c>
-      <c r="D76" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E76" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F76" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G76" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H76" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="str">
-        <v>【7】你做了什麼 — 已完成項目摘要 (依 Round 分組)</v>
-      </c>
-      <c r="B78" s="3" t="str">
-        <v/>
-      </c>
-      <c r="C78" s="3" t="str">
-        <v/>
-      </c>
-      <c r="D78" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E78" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F78" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G78" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H78" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="str">
-        <v>Round</v>
-      </c>
-      <c r="B79" s="3" t="str">
-        <v>日期</v>
-      </c>
-      <c r="C79" s="3" t="str">
-        <v>已修正 (綠)</v>
-      </c>
-      <c r="D79" s="3" t="str">
-        <v>部分修正 (黃)</v>
-      </c>
-      <c r="E79" s="3" t="str">
-        <v>已修正 # 清單</v>
-      </c>
-      <c r="F79" s="3" t="str">
-        <v>部分修正 # 清單</v>
-      </c>
-      <c r="G79" s="3" t="str">
-        <v>主要重點</v>
-      </c>
-      <c r="H79" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="str">
-        <v>Round 1</v>
-      </c>
-      <c r="B80" s="3" t="str">
-        <v>2026-04-28</v>
-      </c>
-      <c r="C80" s="3">
-        <v>24</v>
-      </c>
-      <c r="D80" s="3">
-        <v>6</v>
-      </c>
-      <c r="E80" s="3" t="str">
-        <v>#16, #17, #22, #23, #24, #44, #59, #88, #89, #90, #106, #108, #109, #110, #112, #114, #115, #118, #120, #125, #126, #127, #130, #131</v>
-      </c>
-      <c r="F80" s="3" t="str">
-        <v>#1, #9, #60, #71, #80, #107</v>
-      </c>
-      <c r="G80" s="3" t="str">
-        <v>搜尋優化 (移除 disabled / 結果摘要) + 全站動畫 + skeleton 載入 + 卡片/按鈕 hover translateY</v>
-      </c>
-      <c r="H80" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="str">
-        <v>Round 2</v>
-      </c>
-      <c r="B81" s="3" t="str">
-        <v>2026-04-28</v>
-      </c>
-      <c r="C81" s="3">
-        <v>2</v>
-      </c>
-      <c r="D81" s="3">
-        <v>0</v>
-      </c>
-      <c r="E81" s="3" t="str">
-        <v>#91, #92</v>
-      </c>
-      <c r="F81" s="3" t="str">
-        <v>-</v>
-      </c>
-      <c r="G81" s="3" t="str">
-        <v>Footer 整合 (LINE/FB 並列 .btn-social) + 觸控目標 44px</v>
-      </c>
-      <c r="H81" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="str">
-        <v>Round 3</v>
-      </c>
-      <c r="B82" s="3" t="str">
-        <v>2026-04-28</v>
-      </c>
-      <c r="C82" s="3">
-        <v>6</v>
-      </c>
-      <c r="D82" s="3">
-        <v>0</v>
-      </c>
-      <c r="E82" s="3" t="str">
-        <v>#26, #93, #94, #95, #96, #97</v>
-      </c>
-      <c r="F82" s="3" t="str">
-        <v>-</v>
-      </c>
-      <c r="G82" s="3" t="str">
-        <v>About 三大核心 morph 卡 + News 浮起卡 + 浮現動畫 + line-clamp + NEW pill + 社群 target="_blank"</v>
-      </c>
-      <c r="H82" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="str">
-        <v>Round 4</v>
-      </c>
-      <c r="B83" s="3" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="C83" s="3">
-        <v>7</v>
-      </c>
-      <c r="D83" s="3">
-        <v>1</v>
-      </c>
-      <c r="E83" s="3" t="str">
-        <v>#98, #99, #100, #101, #103, #104, #105</v>
-      </c>
-      <c r="F83" s="3" t="str">
-        <v>#102</v>
-      </c>
-      <c r="G83" s="3" t="str">
+      <c r="G83" s="10" t="str">
         <v>cf47cfa+5dfbf91 補回 16 檔 + 環境設定 (devProxy/baseURL) + 未來規劃 nav + News videoUrl wiring + tsconfig + about hover bug + footer label 重複</v>
       </c>
-      <c r="H83" s="3" t="str">
+      <c r="H83" s="10" t="str">
         <v/>
       </c>
     </row>

--- a/docs/iFare_UI_UX_問題追蹤清單.xlsx
+++ b/docs/iFare_UI_UX_問題追蹤清單.xlsx
@@ -297,10 +297,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -332,10 +332,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -10859,53 +10859,53 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="5">
+      <c r="A134" s="3">
         <v>132</v>
       </c>
-      <c r="B134" s="5" t="str">
-        <v>V</v>
-      </c>
-      <c r="C134" s="5" t="str">
+      <c r="B134" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C134" s="3" t="str">
         <v>i-Fare 福利查詢</v>
       </c>
-      <c r="D134" s="5" t="str">
+      <c r="D134" s="3" t="str">
         <v>搜尋結果</v>
       </c>
-      <c r="E134" s="5" t="str">
+      <c r="E134" s="3" t="str">
         <v>修復</v>
       </c>
-      <c r="F134" s="5" t="str">
+      <c r="F134" s="3" t="str">
         <v>互動</v>
       </c>
-      <c r="G134" s="5" t="str">
+      <c r="G134" s="3" t="str">
         <v>高</v>
       </c>
-      <c r="H134" s="5" t="str">
+      <c r="H134" s="3" t="str">
         <v>搜尋條件 OR == 1 造成大量不相關結果</v>
       </c>
-      <c r="I134" s="5" t="str">
+      <c r="I134" s="3" t="str">
         <v>使用者選「嬰幼兒」(CodeRecipientId=2) 後端回傳 740 筆，幾乎全為「無年齡限制」(CodeRecipientId=1) 的 policy (e.g., 喪葬補助、心理諮商)；同問題在 CodeDomicile / CodeIncome / CodeIdentity 共 4 維度都是 OR == 1。</v>
       </c>
-      <c r="J134" s="5" t="str">
+      <c r="J134" s="3" t="str">
         <v>Backend FarePolicyTaskManager.cs L117-121 拿掉 4 處 || == 1，改嚴格篩選：使用者選什麼條件就只回符合該條件的 policy。CodePolicy 本來就沒 OR 不動。</v>
       </c>
-      <c r="K134" s="5" t="str">
+      <c r="K134" s="3" t="str">
         <v>Backend FarePolicyTaskManager.cs</v>
       </c>
-      <c r="L134" s="5" t="str">
+      <c r="L134" s="3" t="str">
         <v>Dev/Dev Code/iFare_Frontend_API/src/IFare_API.Core/TaskManager/Fare/Policy/FarePolicyTaskManager.cs (L117-121)</v>
       </c>
-      <c r="M134" s="5" t="str">
+      <c r="M134" s="3" t="str">
         <v>使用者明確要求「我選了什麼條件就只出現符合的消息」</v>
       </c>
-      <c r="N134" s="5" t="str">
-        <v>已修正</v>
-      </c>
-      <c r="O134" s="5" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="P134" s="5" t="str">
-        <v>Round 11 (使用者測試發現): 4 維度 (Domicile/Income/Recipient/Identity) 全改嚴格。tradeoff: 「無年齡限制/無戶籍限制」等 universal policy 不再混進結果，使用者可能要在後台 data 上把這類 policy 補上對應 tag (例如喪葬補助加全部 4 個年齡 tag)。</v>
+      <c r="N134" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O134" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P134" s="3" t="str">
+        <v>Round 11 originally fix .NET (commit 22eac37) 但使用者隨後決定 revert (擔心後端 build / 影響其他人測試)。問題仍存在，需要再決定方案 — B (後端排序) / C (前端排序) / D (前端 keyword filter) / E (toggle)。狀態回 待處理。</v>
       </c>
     </row>
   </sheetData>
@@ -10992,16 +10992,16 @@
         <v>132</v>
       </c>
       <c r="C3" s="12">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D3" s="13">
         <v>6</v>
       </c>
       <c r="E3" s="14">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F3" s="11" t="str">
-        <v>31.8%</v>
+        <v>31.1%</v>
       </c>
       <c r="G3" s="10" t="str">
         <v>已歷經 Round 1-4 改版</v>
@@ -11535,19 +11535,19 @@
         <v>高</v>
       </c>
       <c r="B27" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C27" s="16">
         <v>4</v>
       </c>
       <c r="D27" s="17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E27" s="11">
         <v>18</v>
       </c>
       <c r="F27" s="11" t="str">
-        <v>61.1%</v>
+        <v>55.6%</v>
       </c>
       <c r="G27" s="10" t="str">
         <v/>
@@ -12838,13 +12838,13 @@
         <v>2026-04-28</v>
       </c>
       <c r="C80" s="15">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D80" s="16">
         <v>6</v>
       </c>
       <c r="E80" s="10" t="str">
-        <v>#16, #17, #22, #23, #24, #44, #54, #59, #88, #89, #90, #106, #108, #109, #110, #112, #114, #115, #118, #120, #125, #126, #127, #130, #131, #132</v>
+        <v>#16, #17, #22, #23, #24, #44, #54, #59, #88, #89, #90, #106, #108, #109, #110, #112, #114, #115, #118, #120, #125, #126, #127, #130, #131</v>
       </c>
       <c r="F80" s="10" t="str">
         <v>#1, #9, #60, #71, #80, #107</v>

--- a/docs/iFare_UI_UX_問題追蹤清單.xlsx
+++ b/docs/iFare_UI_UX_問題追蹤清單.xlsx
@@ -12540,16 +12540,16 @@
 Dev/Dev Code/iFare_Frontend/assets/style/rwd/_rwd_appHeader.scss</v>
       </c>
       <c r="M165" s="4" t="str">
-        <v>已於 mobile-menu 新增置中靈動島，顯示「長穩選單」與目前頁面名稱，並調整 safe-area、close 按鈕與 menu list 垂直間距。</v>
+        <v>2026-05-12 撤銷實作：AppHeader.vue 與 _rwd_appHeader.scss 已將 .menu-island 入口（含 __camera / __label / __page 與相關 JS computed mobileMenuPageLabel）整段移除。</v>
       </c>
       <c r="N165" s="5" t="str">
         <v>已修正</v>
       </c>
       <c r="O165" s="4" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="P165" s="4" t="str">
-        <v>AppHeader.vue 新增 mobileMenuIslandLabel / mobileMenuPageLabel；_rwd_appHeader.scss 新增 menu-island 膠囊樣式、暗色毛玻璃與手機版 overlay 專用 top padding。</v>
+        <v>依使用者反饋，這個 dynamic island 視覺非必要；漢堡 toggle / close / focus 管理 / 選單列表均不受影響。</v>
       </c>
     </row>
   </sheetData>
@@ -12649,7 +12649,7 @@
         <v>65.0%</v>
       </c>
       <c r="G3" s="3" t="str">
-        <v>更新 #2/#11/#12/#13/#86/#87：第四批 i-Fare 收尾（受助篩選動畫、洽辦互動拆分、多通道分享、contact RWD 統一、result 空狀態 CTA、FAQ focus-visible 強化）</v>
+        <v>#163 動態島手機選單已依使用者反饋撤銷實作；狀態保留「已修正」並補驗證備註說明。</v>
       </c>
       <c r="H3" s="3" t="str">
         <v/>

--- a/docs/iFare_UI_UX_問題追蹤清單.xlsx
+++ b/docs/iFare_UI_UX_問題追蹤清單.xlsx
@@ -7607,105 +7607,105 @@
       </c>
     </row>
     <row r="69" ht="14.4" customHeight="1" xml:space="preserve">
-      <c r="A69" s="6">
+      <c r="A69" s="8">
         <v>67</v>
       </c>
-      <c r="B69" s="6" t="str">
-        <v>V</v>
-      </c>
-      <c r="C69" s="6" t="str">
+      <c r="B69" s="8" t="str">
+        <v>V</v>
+      </c>
+      <c r="C69" s="8" t="str">
         <v>設計系統</v>
       </c>
-      <c r="D69" s="6" t="str">
-        <v/>
-      </c>
-      <c r="E69" s="6" t="str">
+      <c r="D69" s="8" t="str">
+        <v/>
+      </c>
+      <c r="E69" s="8" t="str">
         <v>修復</v>
       </c>
-      <c r="F69" s="6" t="str">
+      <c r="F69" s="8" t="str">
         <v>設計</v>
       </c>
-      <c r="G69" s="6" t="str">
+      <c r="G69" s="8" t="str">
         <v>低</v>
       </c>
-      <c r="H69" s="6" t="str">
+      <c r="H69" s="8" t="str">
         <v>圓角數值不一致</v>
       </c>
-      <c r="I69" s="6" t="str">
+      <c r="I69" s="8" t="str">
         <v>至少 15 種硬編碼值(4/5/8/12/16/20/24/32/44/48/100/377/656px...)，無變數</v>
       </c>
-      <c r="J69" s="6" t="str">
+      <c r="J69" s="8" t="str">
         <v>統一為 2~3 種圓角變數</v>
       </c>
-      <c r="K69" s="6" t="str">
+      <c r="K69" s="8" t="str">
         <v>assets/style/</v>
       </c>
-      <c r="L69" s="6" t="str" xml:space="preserve">
+      <c r="L69" s="8" t="str" xml:space="preserve">
         <v xml:space="preserve">assets/style/_main.scss_x000d__x000d__x000d__x000d__x000d__x000d__x000d__x000d_
 assets/style/_mixin.scss</v>
       </c>
-      <c r="M69" s="6" t="str">
-        <v>確認大量不一致的圓角值</v>
-      </c>
-      <c r="N69" s="7" t="str">
-        <v>待處理</v>
-      </c>
-      <c r="O69" s="6" t="str">
-        <v/>
-      </c>
-      <c r="P69" s="6" t="str">
-        <v/>
+      <c r="M69" s="8" t="str">
+        <v>assets/style/_design-tokens.scss 已建立 $radius-xs/sm/md/lg/xl/2xl/pill/circle/bg-* 9 個語意化變數並透過 styleIFare.scss 全站可用。</v>
+      </c>
+      <c r="N69" s="9" t="str">
+        <v>部分修正</v>
+      </c>
+      <c r="O69" s="8" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="P69" s="8" t="str">
+        <v>為避免全站視覺差異風險，舊 code 既有數值（4/5/6/8/12/14/16/20/22/24/28/32/44/377/656/750/880/999px）未做 search/replace，留下批 design system audit 處理。新 code 直接用 $radius-* 變數。</v>
       </c>
     </row>
     <row r="70" ht="14.4" customHeight="1" xml:space="preserve">
-      <c r="A70" s="6">
+      <c r="A70" s="8">
         <v>68</v>
       </c>
-      <c r="B70" s="6" t="str">
+      <c r="B70" s="8" t="str">
         <v>~</v>
       </c>
-      <c r="C70" s="6" t="str">
+      <c r="C70" s="8" t="str">
         <v>設計系統</v>
       </c>
-      <c r="D70" s="6" t="str">
-        <v/>
-      </c>
-      <c r="E70" s="6" t="str">
+      <c r="D70" s="8" t="str">
+        <v/>
+      </c>
+      <c r="E70" s="8" t="str">
         <v>修復</v>
       </c>
-      <c r="F70" s="6" t="str">
+      <c r="F70" s="8" t="str">
         <v>設計</v>
       </c>
-      <c r="G70" s="6" t="str">
+      <c r="G70" s="8" t="str">
         <v>低</v>
       </c>
-      <c r="H70" s="6" t="str">
+      <c r="H70" s="8" t="str">
         <v>陰影深度僅一種結構</v>
       </c>
-      <c r="I70" s="6" t="str">
+      <c r="I70" s="8" t="str">
         <v>結構上幾乎都是 0px 11px 30px -8px，僅一處 0px 24px 44px -18px</v>
       </c>
-      <c r="J70" s="6" t="str">
+      <c r="J70" s="8" t="str">
         <v>建立 shadow-sm/md/lg 變數</v>
       </c>
-      <c r="K70" s="6" t="str">
+      <c r="K70" s="8" t="str">
         <v>assets/style/</v>
       </c>
-      <c r="L70" s="6" t="str" xml:space="preserve">
+      <c r="L70" s="8" t="str" xml:space="preserve">
         <v xml:space="preserve">assets/style/_main.scss_x000d__x000d__x000d__x000d__x000d__x000d__x000d__x000d_
 assets/style/_mixin.scss</v>
       </c>
-      <c r="M70" s="6" t="str">
-        <v>有多種顏色變體但結構深度確實只有一種</v>
-      </c>
-      <c r="N70" s="7" t="str">
-        <v>待處理</v>
-      </c>
-      <c r="O70" s="6" t="str">
-        <v/>
-      </c>
-      <c r="P70" s="6" t="str">
-        <v/>
+      <c r="M70" s="8" t="str">
+        <v>_design-tokens.scss 已加 $shadow-rest / card / hover / lift / cta / focus 6 個語意化變數，涵蓋既有的 11px 30px -8px / 8px 22px / 18px 36px / 24px 44px / focus ring 等 pattern。</v>
+      </c>
+      <c r="N70" s="9" t="str">
+        <v>部分修正</v>
+      </c>
+      <c r="O70" s="8" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="P70" s="8" t="str">
+        <v>_shadow-color() helper 用 rgba(black) 通用，呼叫端可改用既有 $color-orange / $color-primary / $color-shadow。下批可逐檔替換並驗證視覺。</v>
       </c>
     </row>
     <row r="71" ht="14.4" customHeight="1">
@@ -7759,53 +7759,53 @@
       </c>
     </row>
     <row r="72" ht="14.4" customHeight="1">
-      <c r="A72" s="6">
+      <c r="A72" s="4">
         <v>70</v>
       </c>
-      <c r="B72" s="6" t="str">
-        <v>V</v>
-      </c>
-      <c r="C72" s="6" t="str">
+      <c r="B72" s="4" t="str">
+        <v>V</v>
+      </c>
+      <c r="C72" s="4" t="str">
         <v>全站通用</v>
       </c>
-      <c r="D72" s="6" t="str">
-        <v/>
-      </c>
-      <c r="E72" s="6" t="str">
+      <c r="D72" s="4" t="str">
+        <v/>
+      </c>
+      <c r="E72" s="4" t="str">
         <v>修復</v>
       </c>
-      <c r="F72" s="6" t="str">
+      <c r="F72" s="4" t="str">
         <v>RWD</v>
       </c>
-      <c r="G72" s="6" t="str">
+      <c r="G72" s="4" t="str">
         <v>中</v>
       </c>
-      <c r="H72" s="6" t="str">
+      <c r="H72" s="4" t="str">
         <v>缺少 768px 斷點</v>
       </c>
-      <c r="I72" s="6" t="str">
+      <c r="I72" s="4" t="str">
         <v>grep 768 全站 SCSS 回傳 0 筆，最近為 1024px</v>
       </c>
-      <c r="J72" s="6" t="str">
+      <c r="J72" s="4" t="str">
         <v>新增 768px 斷點</v>
       </c>
-      <c r="K72" s="6" t="str">
+      <c r="K72" s="4" t="str">
         <v>assets/style/rwd/</v>
       </c>
-      <c r="L72" s="6" t="str">
+      <c r="L72" s="4" t="str">
         <v>assets/style/rwd/_rwd.scss</v>
       </c>
-      <c r="M72" s="6" t="str">
-        <v>確認無 768px 斷點</v>
-      </c>
-      <c r="N72" s="7" t="str">
-        <v>待處理</v>
-      </c>
-      <c r="O72" s="6" t="str">
-        <v/>
-      </c>
-      <c r="P72" s="6" t="str">
-        <v/>
+      <c r="M72" s="4" t="str">
+        <v>rwd/_rwd.scss 已新增 $MAX_WIDTH_TABLET: 768px 變數，與本日 chatbot 手機版 / 福利專欄 chip grid 等 RWD 改動的 768px 邊界對齊。</v>
+      </c>
+      <c r="N72" s="5" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O72" s="4" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="P72" s="4" t="str">
+        <v>舊有 $MAX_WIDTH_MOBILE (1024) / $STANDARD_WIDTH_PHONE (516) 維持原樣。後續若新 RWD 規則用 768，可改用變數避免硬寫。</v>
       </c>
     </row>
     <row r="73" ht="14.4" customHeight="1" xml:space="preserve">
@@ -7914,53 +7914,53 @@
       </c>
     </row>
     <row r="75" ht="14.4" customHeight="1">
-      <c r="A75" s="6">
+      <c r="A75" s="8">
         <v>73</v>
       </c>
-      <c r="B75" s="6" t="str">
-        <v>V</v>
-      </c>
-      <c r="C75" s="6" t="str">
+      <c r="B75" s="8" t="str">
+        <v>V</v>
+      </c>
+      <c r="C75" s="8" t="str">
         <v>全站通用</v>
       </c>
-      <c r="D75" s="6" t="str">
-        <v/>
-      </c>
-      <c r="E75" s="6" t="str">
+      <c r="D75" s="8" t="str">
+        <v/>
+      </c>
+      <c r="E75" s="8" t="str">
         <v>修復</v>
       </c>
-      <c r="F75" s="6" t="str">
+      <c r="F75" s="8" t="str">
         <v>效能</v>
       </c>
-      <c r="G75" s="6" t="str">
+      <c r="G75" s="8" t="str">
         <v>低</v>
       </c>
-      <c r="H75" s="6" t="str">
+      <c r="H75" s="8" t="str">
         <v>高度動畫造成 layout 重繪</v>
       </c>
-      <c r="I75" s="6" t="str">
+      <c r="I75" s="8" t="str">
         <v>mDialog keyframes 動畫用 margin-bottom 而非 transform:translateY()</v>
       </c>
-      <c r="J75" s="6" t="str">
+      <c r="J75" s="8" t="str">
         <v>改用 transform 取代 margin/height 動畫</v>
       </c>
-      <c r="K75" s="6" t="str">
+      <c r="K75" s="8" t="str">
         <v>_animation.scss</v>
       </c>
-      <c r="L75" s="6" t="str">
+      <c r="L75" s="8" t="str">
         <v>assets/style/_animation.scss</v>
       </c>
-      <c r="M75" s="6" t="str">
-        <v>確認 margin-bottom 動畫觸發每幀 layout 計算</v>
-      </c>
-      <c r="N75" s="7" t="str">
-        <v>待處理</v>
-      </c>
-      <c r="O75" s="6" t="str">
-        <v/>
-      </c>
-      <c r="P75" s="6" t="str">
-        <v/>
+      <c r="M75" s="8" t="str">
+        <v>components/_appBody_ifare.scss .item-recipient 從 height:0 → height:auto 改為 opacity + transform: translateY + max-height + will-change 組合，主視覺走 GPU composite，max-height 僅作為塌縮 fallback；FAQ 既有 max-height transition 保持不變。</v>
+      </c>
+      <c r="N75" s="9" t="str">
+        <v>部分修正</v>
+      </c>
+      <c r="O75" s="8" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="P75" s="8" t="str">
+        <v>只示範一個典型 case（受助對象篩選器）。全站其他 max-height/height transition（faq-info 等）保留，下批 audit 可逐一遷移為 grid-template-rows: 0fr↔1fr 新技術或 transform 方案。</v>
       </c>
     </row>
     <row r="76" ht="14.4" customHeight="1" xml:space="preserve">
@@ -8369,53 +8369,53 @@
       </c>
     </row>
     <row r="84" ht="14.4" customHeight="1">
-      <c r="A84" s="6">
+      <c r="A84" s="4">
         <v>82</v>
       </c>
-      <c r="B84" s="6" t="str">
-        <v>V</v>
-      </c>
-      <c r="C84" s="6" t="str">
+      <c r="B84" s="4" t="str">
+        <v>V</v>
+      </c>
+      <c r="C84" s="4" t="str">
         <v>全站通用</v>
       </c>
-      <c r="D84" s="6" t="str">
-        <v/>
-      </c>
-      <c r="E84" s="6" t="str">
+      <c r="D84" s="4" t="str">
+        <v/>
+      </c>
+      <c r="E84" s="4" t="str">
         <v>提升</v>
       </c>
-      <c r="F84" s="6" t="str">
+      <c r="F84" s="4" t="str">
         <v>互動</v>
       </c>
-      <c r="G84" s="6" t="str">
+      <c r="G84" s="4" t="str">
         <v>中</v>
       </c>
-      <c r="H84" s="6" t="str">
+      <c r="H84" s="4" t="str">
         <v>404 / 500 頁面導引體驗可補強</v>
       </c>
-      <c r="I84" s="6" t="str">
+      <c r="I84" s="4" t="str">
         <v>目前清單未涵蓋找不到頁面與系統錯誤頁的使用者導引體驗。</v>
       </c>
-      <c r="J84" s="6" t="str">
+      <c r="J84" s="4" t="str">
         <v>建立自訂 404 / 500 頁，提供返回首頁、熱門內容、i-Fare 入口與必要聯絡資訊。</v>
       </c>
-      <c r="K84" s="6" t="str">
+      <c r="K84" s="4" t="str">
         <v>error pages</v>
       </c>
-      <c r="L84" s="6" t="str">
+      <c r="L84" s="4" t="str">
         <v>error.vue app.vue pages/index.vue</v>
       </c>
-      <c r="M84" s="6" t="str">
-        <v>現有清單未包含錯誤頁體驗。</v>
-      </c>
-      <c r="N84" s="7" t="str">
-        <v>待處理</v>
-      </c>
-      <c r="O84" s="6" t="str">
-        <v/>
-      </c>
-      <c r="P84" s="6" t="str">
-        <v/>
+      <c r="M84" s="4" t="str">
+        <v>Dev/Dev Code/iFare_Frontend/error.vue 新建：根據 statusCode (404/403/500/503) 顯示對應標題與引導文案，三顆 CTA (回首頁 clearError redirect、上一頁 history.back、看 iFare 福利好幫手 NuxtLink)；5xx 補客服電話；RWD 手機 viewport 下三顆 CTA 直排 + 字級縮放。</v>
+      </c>
+      <c r="N84" s="5" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O84" s="4" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="P84" s="4" t="str">
+        <v>Nuxt 3 約定的 root error.vue，自動覆蓋預設 @nuxt/ui-templates 的 error-404/500。useHead 套標題 + role=alert + aria-live 滿足 a11y。</v>
       </c>
     </row>
     <row r="85" ht="14.4" customHeight="1">
@@ -10117,57 +10117,57 @@
       </c>
     </row>
     <row r="118" ht="14.4" customHeight="1" xml:space="preserve">
-      <c r="A118" s="6">
+      <c r="A118" s="4">
         <v>116</v>
       </c>
-      <c r="B118" s="6" t="str">
-        <v>V</v>
-      </c>
-      <c r="C118" s="6" t="str">
+      <c r="B118" s="4" t="str">
+        <v>V</v>
+      </c>
+      <c r="C118" s="4" t="str">
         <v>共用元件</v>
       </c>
-      <c r="D118" s="6" t="str">
+      <c r="D118" s="4" t="str">
         <v>CompPage / CompPageNum</v>
       </c>
-      <c r="E118" s="6" t="str">
+      <c r="E118" s="4" t="str">
         <v>修復</v>
       </c>
-      <c r="F118" s="6" t="str">
+      <c r="F118" s="4" t="str">
         <v>程式碼</v>
       </c>
-      <c r="G118" s="6" t="str">
+      <c r="G118" s="4" t="str">
         <v>中</v>
       </c>
-      <c r="H118" s="6" t="str">
+      <c r="H118" s="4" t="str">
         <v>分頁元件 CompPage 與 CompPageNum 重複且 isHide 邏輯有 bug</v>
       </c>
-      <c r="I118" s="6" t="str">
+      <c r="I118" s="4" t="str">
         <v>CompPage.vue (L70-93) 與 CompPageNum.vue (L53-83) 幾乎完全重複；isHide 隱藏頁碼但未正確更新 currentPage；articles/ifare 同時引入兩個造成混淆</v>
       </c>
-      <c r="J118" s="6" t="str">
+      <c r="J118" s="4" t="str">
         <v>合併兩個元件為一個通用 CompPageNum，根據 props 選 num 或 list 模式；修正 isHide 邏輯</v>
       </c>
-      <c r="K118" s="6" t="str">
+      <c r="K118" s="4" t="str">
         <v>CompPage.vue + CompPageNum.vue</v>
       </c>
-      <c r="L118" s="6" t="str" xml:space="preserve">
+      <c r="L118" s="4" t="str" xml:space="preserve">
         <v xml:space="preserve">iFare_Frontend/components/CompPage.vue_x000d__x000d__x000d__x000d__x000d__x000d__x000d_
 iFare_Frontend/components/CompPageNum.vue_x000d__x000d__x000d__x000d__x000d__x000d__x000d_
 iFare_Frontend/pages/articles.vue_x000d__x000d__x000d__x000d__x000d__x000d__x000d_
 iFare_Frontend/pages/ifare.vue_x000d__x000d__x000d__x000d__x000d__x000d__x000d_
 iFare_Frontend/pages/news.vue</v>
       </c>
-      <c r="M118" s="6" t="str">
-        <v>代碼重複率高，易維護錯誤</v>
-      </c>
-      <c r="N118" s="7" t="str">
-        <v>待處理</v>
-      </c>
-      <c r="O118" s="6" t="str">
-        <v/>
-      </c>
-      <c r="P118" s="6" t="str">
-        <v/>
+      <c r="M118" s="4" t="str">
+        <v>components/CompPage.vue isHide 邏輯重寫：抽出 recomputeVisibleWindow() helper 依容器寬度 / WIDTH_PAGEITEM 計算可見視窗，把 currentPage 居中。PageClick / PageNext / PagePrev 統一呼叫；onMounted + watch(pageList) 也觸發初次計算。</v>
+      </c>
+      <c r="N118" s="5" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O118" s="4" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="P118" s="4" t="str">
+        <v>修正原 PagePrev 只 unhide 當前頁、其他被 PageNext 隱藏的 page 永遠拉不回的 bug。同時補 _elnPageContent.value?.offsetWidth 的 null guard 避免初次掛載 race condition。</v>
       </c>
     </row>
     <row r="119" ht="14.4" customHeight="1">
@@ -12637,19 +12637,19 @@
         <v>163</v>
       </c>
       <c r="C3" s="3">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D3" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E3" s="3">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F3" s="3" t="str">
-        <v>65.0%</v>
+        <v>66.9%</v>
       </c>
       <c r="G3" s="3" t="str">
-        <v>#163 動態島手機選單已依使用者反饋撤銷實作；狀態保留「已修正」並補驗證備註說明。</v>
+        <v>更新 #67/#68/#70/#73/#82/#116：第五批 — design tokens / 768 斷點 / 動畫 layout 重繪 / 404 error 頁 / CompPage isHide bug</v>
       </c>
       <c r="H3" s="3" t="str">
         <v/>

--- a/docs/iFare_UI_UX_問題追蹤清單.xlsx
+++ b/docs/iFare_UI_UX_問題追蹤清單.xlsx
@@ -3668,16 +3668,16 @@
 後端 confirm pagination</v>
       </c>
       <c r="M49" s="3" t="str">
-        <v>HomeView.vue +365 行（commit 93d1186）後台首頁整體重構。</v>
+        <v/>
       </c>
       <c r="N49" s="3" t="str">
-        <v>部分修正</v>
+        <v>待處理</v>
       </c>
       <c r="O49" s="3" t="str">
-        <v>2026-05-12</v>
+        <v/>
       </c>
       <c r="P49" s="3" t="str">
-        <v>部分修正 — Codex 大改完整 Dashboard 結構，但整合搜尋 / 總覽 / 待辦 / 快捷的完整性待 review。</v>
+        <v/>
       </c>
       <c r="Q49" s="3" t="str">
         <v>做得快</v>
@@ -4107,16 +4107,16 @@
         <v>後台 Vue 3：重寫 src/views/Index/IndexView.vue 或新增 src/views/Dashboard/DashboardView.vue + 新增 src/composables/useDashboardSearch.ts；後端需新增 API：Dashboard/GetSummary（系統概況 + 待辦摘要）+ Dashboard/Search（全站搜尋）+ Dashboard/RecentActivity（最近更新）</v>
       </c>
       <c r="M57" s="3" t="str">
-        <v>使用者明確要求「不再只是歡迎頁，是工作入口頁」。第一版可暫緩 ⑦ 數據摘要區。</v>
+        <v>HomeView.vue +365 行（commit 93d1186）後台首頁整體重構。</v>
       </c>
       <c r="N57" s="3" t="str">
-        <v>待處理</v>
+        <v>部分修正</v>
       </c>
       <c r="O57" s="3" t="str">
-        <v/>
+        <v>2026-05-12</v>
       </c>
       <c r="P57" s="3" t="str">
-        <v>來源：2026-05-05 使用者草圖。設計重點：「整合搜尋、總覽、待辦與快捷操作的工作入口頁，讓使用者快速找到要做的事與對應功能位置」。搜尋示例：輸入「步道」應回「功能入口（頁管 &gt; 新增頁面 / 福利專欄 &gt; 新增文章）/ 相關內容（頁管 步道專區、福利專欄 親子步道介紹、最新消息 步道公告）/ 建議操作（新增步道頁面 / 查看步道文章 / 前往圖片管理）」。</v>
+        <v>部分修正 — Codex 大改完整 Dashboard 結構，但整合搜尋 / 總覽 / 待辦 / 快捷的完整性待 review。</v>
       </c>
     </row>
   </sheetData>

--- a/docs/iFare_UI_UX_問題追蹤清單.xlsx
+++ b/docs/iFare_UI_UX_問題追蹤清單.xlsx
@@ -146,7 +146,7 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -169,6 +169,11 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1067,7 +1072,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q57"/>
+  <dimension ref="A1:Q65"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="6"/>
     <col min="2" max="2" customWidth="1" width="6"/>
@@ -2588,13 +2593,13 @@
         <v>減少使用者困惑，降低後續編輯次數</v>
       </c>
       <c r="N29" s="3" t="str">
-        <v>待處理</v>
+        <v>部分修正</v>
       </c>
       <c r="O29" s="3" t="str">
-        <v/>
+        <v>2026-05-12</v>
       </c>
       <c r="P29" s="3" t="str">
-        <v/>
+        <v>2026-05-12：先在 PageManagement_AddEditView 補強欄位說明與範例，包含頁面名稱用途說明、Slug 操作提示、URL 預覽、SEO 描述搜尋結果預覽。屬於單一頁面快改，整體後台尚未全面套用，故標記為部分修正。</v>
       </c>
       <c r="Q29" s="3" t="str">
         <v>看得懂</v>
@@ -3394,13 +3399,13 @@
         <v>使用者明確要求「欄位名稱講人話，不要只寫系統術語」</v>
       </c>
       <c r="N44" s="3" t="str">
-        <v>待處理</v>
+        <v>部分修正</v>
       </c>
       <c r="O44" s="3" t="str">
-        <v/>
+        <v>2026-05-12</v>
       </c>
       <c r="P44" s="3" t="str">
-        <v/>
+        <v>2026-05-12：先把 PageManagement_AddEditView 的關鍵欄位說明改白話，例如頁面狀態改成可理解的說明區塊、Slug 加前台網址預覽、SEO 描述改成更接近使用者語言。其他模組尚未套用，故標記為部分修正。</v>
       </c>
       <c r="Q44" s="3" t="str">
         <v>看得懂</v>
@@ -3450,13 +3455,13 @@
         <v>使用者明確要求「狀態流程要明確，讓人知道現在卡在哪」</v>
       </c>
       <c r="N45" s="3" t="str">
-        <v>待處理</v>
+        <v>部分修正</v>
       </c>
       <c r="O45" s="3" t="str">
-        <v/>
+        <v>2026-05-12</v>
       </c>
       <c r="P45" s="3" t="str">
-        <v/>
+        <v>2026-05-12：先在 PageManagement_AddEditView 補上狀態說明與發布結果摘要，讓使用者知道目前是草稿、前台可見、手動下架或依排程上下架。此版本屬於單頁狀態視覺化，故標記為部分修正。</v>
       </c>
       <c r="Q45" s="3" t="str">
         <v>看得懂</v>
@@ -3505,13 +3510,13 @@
         <v>使用者明確要求「搜尋、篩選、排序不要藏太深」</v>
       </c>
       <c r="N46" s="3" t="str">
-        <v>待處理</v>
+        <v>部分修正</v>
       </c>
       <c r="O46" s="3" t="str">
-        <v/>
+        <v>2026-05-12</v>
       </c>
       <c r="P46" s="3" t="str">
-        <v/>
+        <v>已先完成首頁可搜尋工作入口：HomeView 新增模組搜尋、分組篩選、最近使用與 Ctrl/Cmd+K 聚焦搜尋框。此版本屬於「首頁入口搜尋」而非完整 Cmd+K 全域搜尋彈窗，故標記為部分修正。</v>
       </c>
       <c r="Q46" s="3" t="str">
         <v>找得到</v>
@@ -3835,13 +3840,13 @@
         <v>使用者明確要求「有預設值就給合理預設值」</v>
       </c>
       <c r="N52" s="3" t="str">
-        <v>待處理</v>
+        <v>部分修正</v>
       </c>
       <c r="O52" s="3" t="str">
-        <v/>
+        <v>2026-05-12</v>
       </c>
       <c r="P52" s="3" t="str">
-        <v/>
+        <v>2026-05-12：先在 PageManagement_AddEditView 補上排程快捷鍵（立即發布、今天 18:00、明天 09:00、7 天後 / 30 天後下架），降低使用者手動選時間的成本。尚未建立全後台預設值規範，故標記為部分修正。</v>
       </c>
       <c r="Q52" s="3" t="str">
         <v>不容易錯</v>
@@ -4117,6 +4122,455 @@
       </c>
       <c r="P57" s="3" t="str">
         <v>部分修正 — Codex 大改完整 Dashboard 結構，但整合搜尋 / 總覽 / 待辦 / 快捷的完整性待 review。</v>
+      </c>
+    </row>
+    <row r="58" xml:space="preserve">
+      <c r="A58" s="3">
+        <v>55</v>
+      </c>
+      <c r="B58" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C58" s="3" t="str">
+        <v>後台通用</v>
+      </c>
+      <c r="D58" s="3" t="str">
+        <v>排程 / 任務中心</v>
+      </c>
+      <c r="E58" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F58" s="3" t="str">
+        <v>維護性</v>
+      </c>
+      <c r="G58" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H58" s="3" t="str">
+        <v>同步與排程任務中心 — 匯入 / 匯出 / GA4 / 發布排程都可看狀態</v>
+      </c>
+      <c r="I58" s="3" t="str">
+        <v>未來若加入 GA4 同步、定時發布、批次匯入匯出，管理者需要知道「現在有什麼任務正在跑」「哪個失敗」「上次成功是什麼時候」，否則一出錯很難追。</v>
+      </c>
+      <c r="J58" s="3" t="str">
+        <v>新增 JobCenter / TaskCenter 頁面，列出任務名稱、觸發方式、開始時間、結束時間、執行結果、錯誤訊息與重跑按鈕。可先涵蓋 GA4 sync、匯入匯出、排程發布三類任務。</v>
+      </c>
+      <c r="K58" s="3" t="str">
+        <v>新建 JobCenterView + 後端 JobLog API</v>
+      </c>
+      <c r="L58" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">新增 src/views/JobCenter/JobCenterView.vue
+src/router/index.ts
+src/plugins/WebAPI.ts
+新增 IFare_BDAPI.Application/JobCenter/*
+新增 job_log table</v>
+      </c>
+      <c r="M58" s="3" t="str">
+        <v>來源：2026-05-12 使用者要求補充後台進階功能建議；由 Codex 依現有後台 / API 架構提出。 這是把「背景工作」從黑盒子變成可觀察、可追查。</v>
+      </c>
+      <c r="N58" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O58" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P58" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q58" s="3" t="str">
+        <v>出事能追回來</v>
+      </c>
+    </row>
+    <row r="59" xml:space="preserve">
+      <c r="A59" s="3">
+        <v>56</v>
+      </c>
+      <c r="B59" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C59" s="3" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="D59" s="3" t="str">
+        <v>編輯保護</v>
+      </c>
+      <c r="E59" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F59" s="3" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G59" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H59" s="3" t="str">
+        <v>自動儲存草稿 + 離開提醒 + 多人編輯鎖定</v>
+      </c>
+      <c r="I59" s="3" t="str">
+        <v>大型表單如 PageManagement、News、Policy 若編到一半斷線、誤關頁面或兩個人同時改同一筆資料，目前容易丟資料，且後台使用者通常不會每一步都手動存檔。</v>
+      </c>
+      <c r="J59" s="3" t="str">
+        <v>AddEditView 共用層加入三件事：(1) autosave draft (2) route leave / tab close unsaved changes 警示 (3) record editing lock 或至少 optimistic concurrency 版本檢查。</v>
+      </c>
+      <c r="K59" s="3" t="str">
+        <v>各 AddEditView + PageManagement + 後端版本欄位</v>
+      </c>
+      <c r="L59" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">src/views/*/AddEditView.vue
+src/views/PageManagement/PageManagement_AddEditView.vue
+新增 src/composables/useDraftGuard.ts
+後端 entity 加 RowVersion / UpdateToken</v>
+      </c>
+      <c r="M59" s="3" t="str">
+        <v>來源：2026-05-12 使用者要求補充後台進階功能建議；由 Codex 依現有後台 / API 架構提出。 這項對內容型後台的實際保護價值很高，優先級應高。</v>
+      </c>
+      <c r="N59" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O59" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P59" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q59" s="3" t="str">
+        <v>出事能追回來</v>
+      </c>
+    </row>
+    <row r="60" xml:space="preserve">
+      <c r="A60" s="3">
+        <v>57</v>
+      </c>
+      <c r="B60" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C60" s="3" t="str">
+        <v>後台通用</v>
+      </c>
+      <c r="D60" s="3" t="str">
+        <v>發布排程</v>
+      </c>
+      <c r="E60" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F60" s="3" t="str">
+        <v>效率</v>
+      </c>
+      <c r="G60" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H60" s="3" t="str">
+        <v>定時上架 / 下架排程中心 — 不要靠人工守時間</v>
+      </c>
+      <c r="I60" s="3" t="str">
+        <v>若消息、文章、活動頁或政策需在指定時間上架 / 下架，目前若只能靠人工操作，容易漏掉時間點，尤其跨日晚間、週末或活動檔期時風險更高。</v>
+      </c>
+      <c r="J60" s="3" t="str">
+        <v>建立發布排程中心：內容可設定 publishAt / unpublishAt；後端排程自動切換狀態；後台可看到即將上架 / 即將下架清單，並支援取消排程。</v>
+      </c>
+      <c r="K60" s="3" t="str">
+        <v>News / Articles / Policy AddEdit + 後端排程</v>
+      </c>
+      <c r="L60" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">src/views/News/News_AddEditView.vue
+src/views/Articles/Welfare/ArticlesWelfare_AddEditView.vue
+src/views/IFare/Policy/IFarePolicy_AddEditView.vue
+新增 publish_schedule table
+新增排程 worker</v>
+      </c>
+      <c r="M60" s="3" t="str">
+        <v>來源：2026-05-12 使用者要求補充後台進階功能建議；由 Codex 依現有後台 / API 架構提出。 這是典型能降低人工操作錯誤的後台能力。</v>
+      </c>
+      <c r="N60" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O60" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P60" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q60" s="3" t="str">
+        <v>做得快</v>
+      </c>
+    </row>
+    <row r="61" xml:space="preserve">
+      <c r="A61" s="3">
+        <v>58</v>
+      </c>
+      <c r="B61" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C61" s="3" t="str">
+        <v>後台通用</v>
+      </c>
+      <c r="D61" s="3" t="str">
+        <v>審核工作流</v>
+      </c>
+      <c r="E61" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F61" s="3" t="str">
+        <v>流程</v>
+      </c>
+      <c r="G61" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H61" s="3" t="str">
+        <v>審稿指派與 SLA 提醒 — 誰負責審、卡多久一眼可見</v>
+      </c>
+      <c r="I61" s="3" t="str">
+        <v>目前即使有草稿 / 待審概念，也缺「指派給誰」「多久沒處理」「快到 SLA 了沒」這層管理資訊，容易造成內容卡在中間但沒人知道是誰手上。</v>
+      </c>
+      <c r="J61" s="3" t="str">
+        <v>在待審資料加入 assignee、assignedAt、dueAt、overdue flag；首頁待辦與通知中心一起顯示。支援重新指派與逾時提醒。</v>
+      </c>
+      <c r="K61" s="3" t="str">
+        <v>Dashboard / 待辦 / 後端審核欄位</v>
+      </c>
+      <c r="L61" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">src/views/Dashboard/*.vue
+src/views/News/*
+src/views/Articles/Welfare/*
+新增 review assignment 欄位與 API</v>
+      </c>
+      <c r="M61" s="3" t="str">
+        <v>來源：2026-05-12 使用者要求補充後台進階功能建議；由 Codex 依現有後台 / API 架構提出。 這比單純「待審」多了責任歸屬與時效管理。</v>
+      </c>
+      <c r="N61" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O61" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P61" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q61" s="3" t="str">
+        <v>找得到</v>
+      </c>
+    </row>
+    <row r="62" xml:space="preserve">
+      <c r="A62" s="3">
+        <v>59</v>
+      </c>
+      <c r="B62" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C62" s="3" t="str">
+        <v>內容品質</v>
+      </c>
+      <c r="D62" s="3" t="str">
+        <v>健康檢查中心</v>
+      </c>
+      <c r="E62" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F62" s="3" t="str">
+        <v>品質</v>
+      </c>
+      <c r="G62" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H62" s="3" t="str">
+        <v>內容健康檢查中心 — 一次掃出缺圖、缺 SEO、失效連結、未填欄位</v>
+      </c>
+      <c r="I62" s="3" t="str">
+        <v>內容後台常見問題不是功能壞掉，而是資料品質不一致，例如沒封面圖、沒 meta、URL 錯、外連失效、欄位缺漏。這些問題不會在儲存當下全部發現，但會影響前台品質。</v>
+      </c>
+      <c r="J62" s="3" t="str">
+        <v>建立內容健康檢查頁，定期掃描 News / Articles / Pages，列出缺漏項並可直接跳到對應編輯頁修復。第一版可先檢查：封面圖、摘要、SEO title、SEO description、外連格式、發布狀態異常。</v>
+      </c>
+      <c r="K62" s="3" t="str">
+        <v>新建 ContentHealthView + 掃描 API</v>
+      </c>
+      <c r="L62" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">新增 src/views/ContentHealth/ContentHealthView.vue
+src/router/index.ts
+新增 IFare_BDAPI.Application/ContentHealth/*
+後端批次檢查 service</v>
+      </c>
+      <c r="M62" s="3" t="str">
+        <v>來源：2026-05-12 使用者要求補充後台進階功能建議；由 Codex 依現有後台 / API 架構提出。 這類功能對內容營運很實用，且能和 Dashboard 今日待辦整合。</v>
+      </c>
+      <c r="N62" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O62" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P62" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q62" s="3" t="str">
+        <v>不容易錯</v>
+      </c>
+    </row>
+    <row r="63" xml:space="preserve">
+      <c r="A63" s="3">
+        <v>60</v>
+      </c>
+      <c r="B63" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C63" s="3" t="str">
+        <v>後台通用</v>
+      </c>
+      <c r="D63" s="3" t="str">
+        <v>通知中心</v>
+      </c>
+      <c r="E63" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F63" s="3" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G63" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H63" s="3" t="str">
+        <v>通知中心 (Bell) — 待審、同步失敗、匯入完成、即將下架集中顯示</v>
+      </c>
+      <c r="I63" s="3" t="str">
+        <v>目前重要事件多半只能靠使用者自己進模組檢查，缺少集中通知入口。像 GA4 sync 失敗、匯入完成、內容待審、內容即將下架，都應主動提醒而不是被動發現。</v>
+      </c>
+      <c r="J63" s="3" t="str">
+        <v>AppHeader 增加 Bell 通知中心，至少先支援 4 類：待審提醒、同步失敗、匯入匯出結果、即將上架 / 下架。通知可點擊直達對應頁面，並支援已讀 / 未讀。</v>
+      </c>
+      <c r="K63" s="3" t="str">
+        <v>AppHeader + 通知 API</v>
+      </c>
+      <c r="L63" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">src/components/AppHeader.vue
+新增 src/components/AppNotificationCenter.vue
+新增 notification table / API / read status</v>
+      </c>
+      <c r="M63" s="3" t="str">
+        <v>來源：2026-05-12 使用者要求補充後台進階功能建議；由 Codex 依現有後台 / API 架構提出。 這是把散落在各模組的事件集中回到同一個入口。</v>
+      </c>
+      <c r="N63" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O63" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P63" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q63" s="3" t="str">
+        <v>找得到</v>
+      </c>
+    </row>
+    <row r="64" xml:space="preserve">
+      <c r="A64" s="3">
+        <v>61</v>
+      </c>
+      <c r="B64" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C64" s="3" t="str">
+        <v>圖片管理</v>
+      </c>
+      <c r="D64" s="3" t="str">
+        <v>資產治理</v>
+      </c>
+      <c r="E64" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F64" s="3" t="str">
+        <v>維護性</v>
+      </c>
+      <c r="G64" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H64" s="3" t="str">
+        <v>媒體資產治理中心 — 找出未引用圖片、重複檔案、超大檔與過期素材</v>
+      </c>
+      <c r="I64" s="3" t="str">
+        <v>圖片管理不只要能上傳，更要能管理。若後台長期累積未引用圖片、重複圖、超大圖與已下架內容殘留素材，之後會讓資產庫越來越亂，內容編輯也更難找資料。</v>
+      </c>
+      <c r="J64" s="3" t="str">
+        <v>圖片管理增加治理視圖：顯示未引用素材、重複檔名 / hash、過大檔案、最近 N 天未使用資產、可疑過期素材。可加批次標記、下載報表、清理建議。</v>
+      </c>
+      <c r="K64" s="3" t="str">
+        <v>ImgManager + 後端檔案關聯掃描</v>
+      </c>
+      <c r="L64" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">src/views/ImgManager/ImgManager_DataListView.vue
+新增 src/views/ImgManager/ImgManager_GovernanceView.vue
+後端增加資產引用掃描 service</v>
+      </c>
+      <c r="M64" s="3" t="str">
+        <v>來源：2026-05-12 使用者要求補充後台進階功能建議；由 Codex 依現有後台 / API 架構提出。 這是圖片庫從「檔案倉庫」升級為「可治理資產中心」。</v>
+      </c>
+      <c r="N64" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O64" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P64" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q64" s="3" t="str">
+        <v>做得快</v>
+      </c>
+    </row>
+    <row r="65" xml:space="preserve">
+      <c r="A65" s="3">
+        <v>62</v>
+      </c>
+      <c r="B65" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C65" s="3" t="str">
+        <v>資料分析</v>
+      </c>
+      <c r="D65" s="3" t="str">
+        <v>GA4 儀表板整合</v>
+      </c>
+      <c r="E65" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F65" s="3" t="str">
+        <v>數據</v>
+      </c>
+      <c r="G65" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H65" s="3" t="str">
+        <v>GA4 分析儀表板正式版 — 背景同步快取，不直接即時打外部 API</v>
+      </c>
+      <c r="I65" s="3" t="str">
+        <v>目前後台分析頁已可先做 mock dashboard，但正式版若每次開頁都直接打 GA4 API，會造成頁面慢、多人重複查詢、外部配額消耗與正式環境不穩定。</v>
+      </c>
+      <c r="J65" s="3" t="str">
+        <v>建立 GA4 Data API 同步架構：排程每 30 或 60 分鐘抓 KPI / 趨勢 / 熱門頁面 / 來源 / 裝置，先寫入本地快取資料表，後台只讀快取並顯示最後同步時間。</v>
+      </c>
+      <c r="K65" s="3" t="str">
+        <v>Analysis_DashboardView / VisitorAppService / 新增 Ga4AppService</v>
+      </c>
+      <c r="L65" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dev/Dev Code/iFare_Backend/src/views/Analysis/Analysis_DashboardView.vue
+Dev/Dev Code/iFare_Backend_API/src/IFare_BDAPI.Application/Visitor/VisitorAppService.cs
+新增 IFare_BDAPI.Application/Ga4/Ga4AppService.cs
+新增 IFare_BDAPI.Core/TaskManager/Ga4/*
+新增 GA4 cache tables</v>
+      </c>
+      <c r="M65" s="3" t="str">
+        <v>來源：2026-05-12 使用者要求補充後台進階功能建議；由 Codex 依現有後台 / API 架構提出。 建議採「背景排程同步 + DB 快取 + 後台讀快取」模式，避免伺服器與 GA4 quota 壓力。</v>
+      </c>
+      <c r="N65" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O65" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P65" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Q65" s="3" t="str">
+        <v>看得懂</v>
       </c>
     </row>
   </sheetData>
@@ -4125,14 +4579,14 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q57"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q65"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P165"/>
+  <dimension ref="A1:P167"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="5.77734375"/>
     <col min="2" max="2" customWidth="1" width="5.77734375"/>
@@ -12551,149 +13005,249 @@
         <v>依使用者反饋，這個 dynamic island 視覺非必要；漢堡 toggle / close / focus 管理 / 選單列表均不受影響。</v>
       </c>
     </row>
+    <row r="166">
+      <c r="A166" s="4">
+        <v>164</v>
+      </c>
+      <c r="B166" s="4" t="str">
+        <v>V</v>
+      </c>
+      <c r="C166" s="4" t="str">
+        <v>未來規劃</v>
+      </c>
+      <c r="D166" s="4" t="str">
+        <v>Hero 標題 / RWD</v>
+      </c>
+      <c r="E166" s="4" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F166" s="4" t="str">
+        <v>RWD</v>
+      </c>
+      <c r="G166" s="4" t="str">
+        <v>中</v>
+      </c>
+      <c r="H166" s="4" t="str">
+        <v>future 頁手機版主標題應避免孤字掉行，改為兩行平衡換行</v>
+      </c>
+      <c r="I166" s="4" t="str">
+        <v>目前主標在窄螢幕下容易出現最後單字單獨落在第二行，視覺重心不穩，也會讓標題看起來像被擠斷。</v>
+      </c>
+      <c r="J166" s="4" t="str">
+        <v>主標改為桌機維持單行節奏、手機版明確切成兩行，搭配較平衡的 clamp 字級、line-height 與 max-width，避免「中」單獨掉行。</v>
+      </c>
+      <c r="K166" s="4" t="str">
+        <v>pages/future.vue</v>
+      </c>
+      <c r="L166" s="4" t="str">
+        <v>Dev/Dev Code/iFare_Frontend/pages/future.vue</v>
+      </c>
+      <c r="M166" s="4" t="str">
+        <v>依使用者確認，這次先處理 future 頁主標在手機版的換行與可讀性。</v>
+      </c>
+      <c r="N166" s="5" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O166" s="4" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="P166" s="4" t="str">
+        <v>2026-05-12：future.vue 主標改為桌機同列、手機兩行平衡換行，明確拆成「未來規劃頁面 / 建置中」，並調整 clamp 字級、line-height 與 max-width。</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="4">
+        <v>165</v>
+      </c>
+      <c r="B167" s="4" t="str">
+        <v>V</v>
+      </c>
+      <c r="C167" s="4" t="str">
+        <v>未來規劃</v>
+      </c>
+      <c r="D167" s="4" t="str">
+        <v>空狀態版面 / CTA</v>
+      </c>
+      <c r="E167" s="4" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F167" s="4" t="str">
+        <v>體驗</v>
+      </c>
+      <c r="G167" s="4" t="str">
+        <v>中</v>
+      </c>
+      <c r="H167" s="4" t="str">
+        <v>future 頁空狀態內容過於單薄，需補替代行動並收斂與 footer CTA 的銜接</v>
+      </c>
+      <c r="I167" s="4" t="str">
+        <v>原本頁面僅有 Coming Soon 與一句說明，手機版上方留白偏多，說明文字行寬也較鬆，與下方 footer CTA 之間的銜接略顯突然。</v>
+      </c>
+      <c r="J167" s="4" t="str">
+        <v>收斂 breadcrumb 與主視覺間距、縮短說明文字寬度，並新增兩個替代行動入口，引導使用者先看最新消息或認識基金會，讓空頁也有下一步。</v>
+      </c>
+      <c r="K167" s="4" t="str">
+        <v>pages/future.vue</v>
+      </c>
+      <c r="L167" s="4" t="str">
+        <v>Dev/Dev Code/iFare_Frontend/pages/future.vue</v>
+      </c>
+      <c r="M167" s="4" t="str">
+        <v>同日另有 #164 處理主標兩行換行；這筆專門記錄版面節奏、替代行動與 footer 銜接優化。</v>
+      </c>
+      <c r="N167" s="5" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O167" s="4" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="P167" s="4" t="str">
+        <v>2026-05-12：future.vue 收斂上方留白與底部間距、縮短說明文字寬度，新增「查看最新消息 / 認識基金會」替代行動卡，讓空狀態頁與 footer CTA 的銜接更自然。</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P165"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P167"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H95"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="14.77734375"/>
-    <col min="2" max="2" customWidth="1" width="12.77734375"/>
-    <col min="3" max="3" customWidth="1" width="14.77734375"/>
-    <col min="4" max="4" customWidth="1" width="14.77734375"/>
-    <col min="5" max="5" customWidth="1" width="50.77734375"/>
-    <col min="6" max="6" customWidth="1" width="25.77734375"/>
-    <col min="7" max="7" customWidth="1" width="60.77734375"/>
-    <col min="8" max="8" customWidth="1" width="14.77734375"/>
+    <col min="1" max="1" customWidth="1" width="14.5546875"/>
+    <col min="2" max="2" customWidth="1" width="12.5546875"/>
+    <col min="3" max="3" customWidth="1" width="14.5546875"/>
+    <col min="4" max="4" customWidth="1" width="14.5546875"/>
+    <col min="5" max="5" customWidth="1" width="50.5546875"/>
+    <col min="6" max="6" customWidth="1" width="25.5546875"/>
+    <col min="7" max="7" customWidth="1" width="60.5546875"/>
+    <col min="8" max="8" customWidth="1" width="14.5546875"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.4" customHeight="1">
-      <c r="A1" s="3" t="str">
+    <row r="1">
+      <c r="A1" s="10" t="str">
         <v>【1】整體進度</v>
       </c>
-      <c r="B1" s="3" t="str">
-        <v/>
-      </c>
-      <c r="C1" s="3" t="str">
-        <v/>
-      </c>
-      <c r="D1" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E1" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F1" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G1" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H1" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="2" ht="14.4" customHeight="1">
-      <c r="A2" s="3" t="str">
+      <c r="B1" s="10" t="str">
+        <v/>
+      </c>
+      <c r="C1" s="10" t="str">
+        <v/>
+      </c>
+      <c r="D1" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E1" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F1" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G1" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H1" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="str">
         <v>Sheet 名稱</v>
       </c>
-      <c r="B2" s="3" t="str">
+      <c r="B2" s="11" t="str">
         <v>總計</v>
       </c>
-      <c r="C2" s="3" t="str">
+      <c r="C2" s="11" t="str">
         <v>已修正</v>
       </c>
-      <c r="D2" s="3" t="str">
+      <c r="D2" s="11" t="str">
         <v>部分修正</v>
       </c>
-      <c r="E2" s="3" t="str">
+      <c r="E2" s="11" t="str">
         <v>待處理</v>
       </c>
-      <c r="F2" s="3" t="str">
+      <c r="F2" s="11" t="str">
         <v>完成率</v>
       </c>
-      <c r="G2" s="3" t="str">
+      <c r="G2" s="11" t="str">
         <v>備註</v>
       </c>
-      <c r="H2" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="14.4" customHeight="1">
+      <c r="H2" s="11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="3" t="str">
         <v>UIUX問題追蹤清單 (前台)</v>
       </c>
       <c r="B3" s="3">
-        <v>163</v>
-      </c>
-      <c r="C3" s="3">
-        <v>119</v>
-      </c>
-      <c r="D3" s="3">
+        <v>165</v>
+      </c>
+      <c r="C3" s="12">
+        <v>121</v>
+      </c>
+      <c r="D3" s="13">
         <v>11</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="14">
         <v>33</v>
       </c>
       <c r="F3" s="3" t="str">
-        <v>73.0%</v>
+        <v>73.3%</v>
       </c>
       <c r="G3" s="3" t="str">
-        <v>更新 sheet2 #17/#20/#26/#39-#41/#42/#53 + #18(新)、sheet3 #141/#142 全標部分修正 — 對應 commit 93d1186 第六輪改動。</v>
+        <v>已歷經 Round 1-4 改版</v>
       </c>
       <c r="H3" s="3" t="str">
         <v/>
       </c>
     </row>
-    <row r="4" ht="14.4" customHeight="1">
+    <row r="4">
       <c r="A4" s="3" t="str">
         <v>後臺優化 (admin)</v>
       </c>
       <c r="B4" s="3">
-        <v>55</v>
-      </c>
-      <c r="C4" s="3">
+        <v>63</v>
+      </c>
+      <c r="C4" s="12">
         <v>1</v>
       </c>
-      <c r="D4" s="3">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3">
-        <v>54</v>
+      <c r="D4" s="13">
+        <v>14</v>
+      </c>
+      <c r="E4" s="14">
+        <v>48</v>
       </c>
       <c r="F4" s="3" t="str">
-        <v>1.8%</v>
+        <v>1.6%</v>
       </c>
       <c r="G4" s="3" t="str">
-        <v>Round 5-6 規劃完成 / 全待開始</v>
+        <v>含後台優化規劃與進階功能建議</v>
       </c>
       <c r="H4" s="3" t="str">
         <v/>
       </c>
     </row>
-    <row r="5" ht="14.4" customHeight="1">
+    <row r="5">
       <c r="A5" s="3" t="str">
         <v>PoC研究</v>
       </c>
       <c r="B5" s="3">
         <v>13</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="12">
         <v>0</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="13">
         <v>0</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="14">
         <v>13</v>
       </c>
       <c r="F5" s="3" t="str">
@@ -12706,59 +13260,59 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="14.4" customHeight="1">
-      <c r="A7" s="3" t="str">
+    <row r="7">
+      <c r="A7" s="10" t="str">
         <v>【2】Round 時間軸 — 每輪做了什麼</v>
       </c>
-      <c r="B7" s="3" t="str">
-        <v/>
-      </c>
-      <c r="C7" s="3" t="str">
-        <v/>
-      </c>
-      <c r="D7" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E7" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F7" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G7" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H7" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="14.4" customHeight="1">
-      <c r="A8" s="3" t="str">
+      <c r="B7" s="10" t="str">
+        <v/>
+      </c>
+      <c r="C7" s="10" t="str">
+        <v/>
+      </c>
+      <c r="D7" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E7" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F7" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G7" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H7" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="str">
         <v>Round</v>
       </c>
-      <c r="B8" s="3" t="str">
+      <c r="B8" s="11" t="str">
         <v>日期</v>
       </c>
-      <c r="C8" s="3" t="str">
+      <c r="C8" s="11" t="str">
         <v>主題</v>
       </c>
-      <c r="D8" s="3" t="str">
+      <c r="D8" s="11" t="str">
         <v>UIUX 標完成</v>
       </c>
-      <c r="E8" s="3" t="str">
+      <c r="E8" s="11" t="str">
         <v>UIUX 新增</v>
       </c>
-      <c r="F8" s="3" t="str">
+      <c r="F8" s="11" t="str">
         <v>後臺新增</v>
       </c>
-      <c r="G8" s="3" t="str">
+      <c r="G8" s="11" t="str">
         <v>Schema</v>
       </c>
-      <c r="H8" s="3" t="str">
+      <c r="H8" s="11" t="str">
         <v>主要產出</v>
       </c>
     </row>
-    <row r="9" ht="14.4" customHeight="1">
+    <row r="9">
       <c r="A9" s="3" t="str">
         <v>Round 1</v>
       </c>
@@ -12784,7 +13338,7 @@
         <v>pages/ifare 加關鍵字搜尋 + URL query 初始化；全站 NuxtPage transition；卡片/按鈕 hover translateY</v>
       </c>
     </row>
-    <row r="10" ht="14.4" customHeight="1">
+    <row r="10">
       <c r="A10" s="3" t="str">
         <v>Round 2</v>
       </c>
@@ -12810,7 +13364,7 @@
         <v>LINE/FB 統一 .btn-social 並排；4 個聯絡資訊加 icon (Tel/Mail/Address/Clock)；footer 觸控 44px</v>
       </c>
     </row>
-    <row r="11" ht="14.4" customHeight="1">
+    <row r="11">
       <c r="A11" s="3" t="str">
         <v>Round 3</v>
       </c>
@@ -12836,7 +13390,7 @@
         <v>About 三大核心 morph 卡 (cf47cfa)；News 浮起卡 + stagger fade-up + NEW pill；外連結 target="_blank" rel="noopener"</v>
       </c>
     </row>
-    <row r="12" ht="14.4" customHeight="1">
+    <row r="12">
       <c r="A12" s="3" t="str">
         <v>Round 4</v>
       </c>
@@ -12862,7 +13416,7 @@
         <v>cf47cfa+5dfbf91 補回 16 檔；devProxy/baseURL → 正式 API；nav 加未來規劃 + future.vue；News videoUrl wiring；tsconfig deprecation 清理；about hover bug 修；footer label 重複修</v>
       </c>
     </row>
-    <row r="13" ht="14.4" customHeight="1">
+    <row r="13">
       <c r="A13" s="3" t="str">
         <v>Round 5</v>
       </c>
@@ -12888,7 +13442,7 @@
         <v>後台 22 個工程角度問題 (CRUD/驗證/錯誤處理)；前台 26 個新發現 (XSS/超時/console.log/無障礙/分頁元件重複)</v>
       </c>
     </row>
-    <row r="14" ht="14.4" customHeight="1">
+    <row r="14">
       <c r="A14" s="3" t="str">
         <v>Round 6</v>
       </c>
@@ -12914,821 +13468,821 @@
         <v>Dashboard 角色化 / 今日待辦 / KPI 分區；批次操作；軟刪除復原；audit log；危險操作預覽；錯誤訊息引導</v>
       </c>
     </row>
-    <row r="16" ht="14.4" customHeight="1">
+    <row r="15">
+      <c r="A15" s="3" t="str">
+        <v>Round 7</v>
+      </c>
+      <c r="B15" s="3" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C15" s="3" t="str">
+        <v>後台進階功能建議補充</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3" t="str">
+        <v>-</v>
+      </c>
+      <c r="H15" s="3" t="str">
+        <v>補充 GA4 同步快取、任務中心、自動儲存與編輯鎖定、發布排程、審稿指派、內容健康檢查、通知中心、資產治理</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" s="3" t="str">
+        <v>Round 8</v>
+      </c>
+      <c r="B16" s="3" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C16" s="3" t="str">
+        <v>後台首頁搜尋 + 表單欄位人性化快改</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3" t="str">
+        <v>-</v>
+      </c>
+      <c r="H16" s="3" t="str">
+        <v>HomeView 新增搜尋 / 分組 / 最近使用；PageManagement 補上 URL 預覽、狀態說明、SEO 預覽、常用標籤建議、排程快捷鍵</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="str">
+        <v>Round 9</v>
+      </c>
+      <c r="B17" s="3" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C17" s="3" t="str">
+        <v>前台 future 頁空狀態版面優化</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3" t="str">
+        <v>-</v>
+      </c>
+      <c r="H17" s="3" t="str">
+        <v>future.vue 補強手機版主標換行、空狀態導引卡、上下留白與 footer CTA 銜接</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="str">
         <v>【3】後臺優化 — 5 主軸分布 (拿這個去提案!)</v>
       </c>
-      <c r="B16" s="3" t="str">
-        <v/>
-      </c>
-      <c r="C16" s="3" t="str">
-        <v/>
-      </c>
-      <c r="D16" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E16" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F16" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G16" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H16" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="14.4" customHeight="1">
-      <c r="A17" s="3" t="str">
+      <c r="B19" s="10" t="str">
+        <v/>
+      </c>
+      <c r="C19" s="10" t="str">
+        <v/>
+      </c>
+      <c r="D19" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E19" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F19" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G19" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H19" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="str">
         <v>主軸</v>
       </c>
-      <c r="B17" s="3" t="str">
+      <c r="B20" s="11" t="str">
         <v>項目數</v>
       </c>
-      <c r="C17" s="3" t="str">
+      <c r="C20" s="11" t="str">
         <v>比例</v>
       </c>
-      <c r="D17" s="3" t="str">
+      <c r="D20" s="11" t="str">
         <v>主要訴求</v>
       </c>
-      <c r="E17" s="3" t="str">
+      <c r="E20" s="11" t="str">
         <v>對應 #</v>
       </c>
-      <c r="F17" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G17" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H17" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="14.4" customHeight="1">
-      <c r="A18" s="3" t="str">
+      <c r="F20" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G20" s="11" t="str">
+        <v/>
+      </c>
+      <c r="H20" s="11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="str">
         <v>看得懂</v>
       </c>
-      <c r="B18" s="3">
-        <v>17</v>
-      </c>
-      <c r="C18" s="3" t="str">
-        <v>30.9%</v>
-      </c>
-      <c r="D18" s="3" t="str">
+      <c r="B21" s="3">
+        <v>18</v>
+      </c>
+      <c r="C21" s="3" t="str">
+        <v>28.6%</v>
+      </c>
+      <c r="D21" s="3" t="str">
         <v>首頁先給重點 / KPI / 異常 / 待辦分區 / 欄位白話 / 狀態流程視覺化</v>
       </c>
-      <c r="E18" s="3" t="str">
+      <c r="E21" s="3" t="str">
         <v>#1, #7, #10, #17, #19, #24, #25, #27, #32, #35, #37, #38, #39, #40, #41, #45, #49</v>
       </c>
-      <c r="F18" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G18" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H18" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="14.4" customHeight="1">
-      <c r="A19" s="3" t="str">
+      <c r="F21" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G21" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H21" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="str">
         <v>找得到</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B22" s="3">
+        <v>7</v>
+      </c>
+      <c r="C22" s="3" t="str">
+        <v>11.1%</v>
+      </c>
+      <c r="D22" s="3" t="str">
+        <v>全域搜尋 / 麵包屑 / 側邊欄高亮 / 變更密碼入口</v>
+      </c>
+      <c r="E22" s="3" t="str">
+        <v>#6, #29, #30, #33, #44</v>
+      </c>
+      <c r="F22" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G22" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H22" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="str">
+        <v>做得快</v>
+      </c>
+      <c r="B23" s="3">
+        <v>11</v>
+      </c>
+      <c r="C23" s="3" t="str">
+        <v>17.5%</v>
+      </c>
+      <c r="D23" s="3" t="str">
+        <v>批次操作 / 儲存搜尋 / 大列表 lazy / 匯出進度 / 日期快捷</v>
+      </c>
+      <c r="E23" s="3" t="str">
+        <v>#3, #11, #20, #26, #28, #42, #43, #53, #54</v>
+      </c>
+      <c r="F23" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G23" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H23" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="str">
+        <v>不容易錯</v>
+      </c>
+      <c r="B24" s="3">
+        <v>15</v>
+      </c>
+      <c r="C24" s="3" t="str">
+        <v>23.8%</v>
+      </c>
+      <c r="D24" s="3" t="str">
+        <v>表單驗證 / 刪除確認 / 影響預覽 / 預設值 / 錯誤引導</v>
+      </c>
+      <c r="E24" s="3" t="str">
+        <v>#2, #4, #5, #15, #18, #21, #22, #23, #31, #34, #36, #46, #47, #48</v>
+      </c>
+      <c r="F24" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G24" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H24" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="str">
+        <v>出事能追回來</v>
+      </c>
+      <c r="B25" s="3">
+        <v>7</v>
+      </c>
+      <c r="C25" s="3" t="str">
+        <v>11.1%</v>
+      </c>
+      <c r="D25" s="3" t="str">
+        <v>audit log / 變更歷史 / 軟刪除復原 / token 管理 / 文件交接</v>
+      </c>
+      <c r="E25" s="3" t="str">
+        <v>#9, #12, #50, #51, #52</v>
+      </c>
+      <c r="F25" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G25" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H25" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="str">
+        <v>—</v>
+      </c>
+      <c r="B26" s="3">
         <v>5</v>
       </c>
-      <c r="C19" s="3" t="str">
-        <v>9.1%</v>
-      </c>
-      <c r="D19" s="3" t="str">
-        <v>全域搜尋 / 麵包屑 / 側邊欄高亮 / 變更密碼入口</v>
-      </c>
-      <c r="E19" s="3" t="str">
-        <v>#6, #29, #30, #33, #44</v>
-      </c>
-      <c r="F19" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G19" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H19" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="14.4" customHeight="1">
-      <c r="A20" s="3" t="str">
-        <v>做得快</v>
-      </c>
-      <c r="B20" s="3">
+      <c r="C26" s="3" t="str">
+        <v>7.9%</v>
+      </c>
+      <c r="D26" s="3" t="str">
+        <v>純技術 / 環境設定 (不在 5 主軸範圍)</v>
+      </c>
+      <c r="E26" s="3" t="str">
+        <v>#8, #13, #14, #16</v>
+      </c>
+      <c r="F26" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G26" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H26" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="str">
+        <v>【4】UIUX — 優先級 × 狀態分布</v>
+      </c>
+      <c r="B28" s="10" t="str">
+        <v/>
+      </c>
+      <c r="C28" s="10" t="str">
+        <v/>
+      </c>
+      <c r="D28" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E28" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F28" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G28" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H28" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="str">
+        <v>優先級</v>
+      </c>
+      <c r="B29" s="11" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="C29" s="11" t="str">
+        <v>部分修正</v>
+      </c>
+      <c r="D29" s="11" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="E29" s="11" t="str">
+        <v>小計</v>
+      </c>
+      <c r="F29" s="11" t="str">
+        <v>完成率</v>
+      </c>
+      <c r="G29" s="11" t="str">
+        <v/>
+      </c>
+      <c r="H29" s="11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="B30" s="12">
+        <v>22</v>
+      </c>
+      <c r="C30" s="13">
+        <v>6</v>
+      </c>
+      <c r="D30" s="14">
+        <v>4</v>
+      </c>
+      <c r="E30" s="3">
+        <v>32</v>
+      </c>
+      <c r="F30" s="3" t="str">
+        <v>78.1%</v>
+      </c>
+      <c r="G30" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H30" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="B31" s="12">
+        <v>59</v>
+      </c>
+      <c r="C31" s="13">
+        <v>1</v>
+      </c>
+      <c r="D31" s="14">
+        <v>18</v>
+      </c>
+      <c r="E31" s="3">
+        <v>78</v>
+      </c>
+      <c r="F31" s="3" t="str">
+        <v>76.3%</v>
+      </c>
+      <c r="G31" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H31" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="str">
+        <v>低</v>
+      </c>
+      <c r="B32" s="12">
+        <v>40</v>
+      </c>
+      <c r="C32" s="13">
+        <v>4</v>
+      </c>
+      <c r="D32" s="14">
+        <v>11</v>
+      </c>
+      <c r="E32" s="3">
+        <v>55</v>
+      </c>
+      <c r="F32" s="3" t="str">
+        <v>76.4%</v>
+      </c>
+      <c r="G32" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H32" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="str">
+        <v>【5】UIUX — 各區塊問題分布</v>
+      </c>
+      <c r="B34" s="10" t="str">
+        <v/>
+      </c>
+      <c r="C34" s="10" t="str">
+        <v/>
+      </c>
+      <c r="D34" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E34" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F34" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G34" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H34" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="str">
+        <v>區塊</v>
+      </c>
+      <c r="B35" s="11" t="str">
+        <v>項目數</v>
+      </c>
+      <c r="C35" s="11" t="str">
+        <v>佔比</v>
+      </c>
+      <c r="D35" s="11" t="str">
+        <v/>
+      </c>
+      <c r="E35" s="11" t="str">
+        <v/>
+      </c>
+      <c r="F35" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G35" s="11" t="str">
+        <v/>
+      </c>
+      <c r="H35" s="11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="str">
+        <v>全站通用</v>
+      </c>
+      <c r="B36" s="3">
+        <v>42</v>
+      </c>
+      <c r="C36" s="3" t="str">
+        <v>25.5%</v>
+      </c>
+      <c r="D36" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E36" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F36" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G36" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H36" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="str">
+        <v>i-Fare 福利查詢</v>
+      </c>
+      <c r="B37" s="3">
+        <v>26</v>
+      </c>
+      <c r="C37" s="3" t="str">
+        <v>15.8%</v>
+      </c>
+      <c r="D37" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E37" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F37" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G37" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H37" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="B38" s="3">
+        <v>25</v>
+      </c>
+      <c r="C38" s="3" t="str">
+        <v>15.2%</v>
+      </c>
+      <c r="D38" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E38" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F38" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G38" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H38" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="str">
+        <v>福利專欄</v>
+      </c>
+      <c r="B39" s="3">
+        <v>11</v>
+      </c>
+      <c r="C39" s="3" t="str">
+        <v>6.7%</v>
+      </c>
+      <c r="D39" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E39" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F39" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G39" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H39" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="str">
+        <v>首頁</v>
+      </c>
+      <c r="B40" s="3">
+        <v>10</v>
+      </c>
+      <c r="C40" s="3" t="str">
+        <v>6.1%</v>
+      </c>
+      <c r="D40" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E40" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F40" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G40" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H40" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="str">
+        <v>關於長穩</v>
+      </c>
+      <c r="B41" s="3">
         <v>9</v>
       </c>
-      <c r="C20" s="3" t="str">
-        <v>16.4%</v>
-      </c>
-      <c r="D20" s="3" t="str">
-        <v>批次操作 / 儲存搜尋 / 大列表 lazy / 匯出進度 / 日期快捷</v>
-      </c>
-      <c r="E20" s="3" t="str">
-        <v>#3, #11, #20, #26, #28, #42, #43, #53, #54</v>
-      </c>
-      <c r="F20" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G20" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H20" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="14.4" customHeight="1">
-      <c r="A21" s="3" t="str">
-        <v>不容易錯</v>
-      </c>
-      <c r="B21" s="3">
-        <v>14</v>
-      </c>
-      <c r="C21" s="3" t="str">
-        <v>25.5%</v>
-      </c>
-      <c r="D21" s="3" t="str">
-        <v>表單驗證 / 刪除確認 / 影響預覽 / 預設值 / 錯誤引導</v>
-      </c>
-      <c r="E21" s="3" t="str">
-        <v>#2, #4, #5, #15, #18, #21, #22, #23, #31, #34, #36, #46, #47, #48</v>
-      </c>
-      <c r="F21" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G21" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H21" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="14.4" customHeight="1">
-      <c r="A22" s="3" t="str">
-        <v>出事能追回來</v>
-      </c>
-      <c r="B22" s="3">
+      <c r="C41" s="3" t="str">
+        <v>5.5%</v>
+      </c>
+      <c r="D41" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E41" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F41" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G41" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H41" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="str">
+        <v>最新消息</v>
+      </c>
+      <c r="B42" s="3">
+        <v>8</v>
+      </c>
+      <c r="C42" s="3" t="str">
+        <v>4.8%</v>
+      </c>
+      <c r="D42" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E42" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F42" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G42" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H42" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="str">
+        <v>公益夥伴</v>
+      </c>
+      <c r="B43" s="3">
+        <v>8</v>
+      </c>
+      <c r="C43" s="3" t="str">
+        <v>4.8%</v>
+      </c>
+      <c r="D43" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E43" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F43" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G43" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H43" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="str">
+        <v>全站微互動</v>
+      </c>
+      <c r="B44" s="3">
         <v>5</v>
       </c>
-      <c r="C22" s="3" t="str">
-        <v>9.1%</v>
-      </c>
-      <c r="D22" s="3" t="str">
-        <v>audit log / 變更歷史 / 軟刪除復原 / token 管理 / 文件交接</v>
-      </c>
-      <c r="E22" s="3" t="str">
-        <v>#9, #12, #50, #51, #52</v>
-      </c>
-      <c r="F22" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G22" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H22" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="14.4" customHeight="1">
-      <c r="A23" s="3" t="str">
-        <v>—</v>
-      </c>
-      <c r="B23" s="3">
+      <c r="C44" s="3" t="str">
+        <v>3.0%</v>
+      </c>
+      <c r="D44" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E44" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F44" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G44" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H44" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="str">
+        <v>設計系統</v>
+      </c>
+      <c r="B45" s="3">
         <v>5</v>
       </c>
-      <c r="C23" s="3" t="str">
-        <v>9.1%</v>
-      </c>
-      <c r="D23" s="3" t="str">
-        <v>純技術 / 環境設定 (不在 5 主軸範圍)</v>
-      </c>
-      <c r="E23" s="3" t="str">
-        <v>#8, #13, #14, #16</v>
-      </c>
-      <c r="F23" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G23" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H23" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="14.4" customHeight="1">
-      <c r="A25" s="3" t="str">
-        <v>【4】UIUX — 優先級 × 狀態分布</v>
-      </c>
-      <c r="B25" s="3" t="str">
-        <v/>
-      </c>
-      <c r="C25" s="3" t="str">
-        <v/>
-      </c>
-      <c r="D25" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E25" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F25" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G25" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H25" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="14.4" customHeight="1">
-      <c r="A26" s="3" t="str">
-        <v>優先級</v>
-      </c>
-      <c r="B26" s="3" t="str">
-        <v>已修正</v>
-      </c>
-      <c r="C26" s="3" t="str">
-        <v>部分修正</v>
-      </c>
-      <c r="D26" s="3" t="str">
-        <v>待處理</v>
-      </c>
-      <c r="E26" s="3" t="str">
-        <v>小計</v>
-      </c>
-      <c r="F26" s="3" t="str">
-        <v>完成率</v>
-      </c>
-      <c r="G26" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H26" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="14.4" customHeight="1">
-      <c r="A27" s="3" t="str">
-        <v>高</v>
-      </c>
-      <c r="B27" s="3">
-        <v>11</v>
-      </c>
-      <c r="C27" s="3">
-        <v>4</v>
-      </c>
-      <c r="D27" s="3">
-        <v>10</v>
-      </c>
-      <c r="E27" s="3">
-        <v>25</v>
-      </c>
-      <c r="F27" s="3" t="str">
-        <v>52.0%</v>
-      </c>
-      <c r="G27" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H27" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="14.4" customHeight="1">
-      <c r="A28" s="3" t="str">
-        <v>中</v>
-      </c>
-      <c r="B28" s="3">
-        <v>26</v>
-      </c>
-      <c r="C28" s="3">
-        <v>0</v>
-      </c>
-      <c r="D28" s="3">
-        <v>36</v>
-      </c>
-      <c r="E28" s="3">
-        <v>62</v>
-      </c>
-      <c r="F28" s="3" t="str">
-        <v>41.9%</v>
-      </c>
-      <c r="G28" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H28" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="14.4" customHeight="1">
-      <c r="A29" s="3" t="str">
-        <v>低</v>
-      </c>
-      <c r="B29" s="3">
-        <v>24</v>
-      </c>
-      <c r="C29" s="3">
+      <c r="C45" s="3" t="str">
+        <v>3.0%</v>
+      </c>
+      <c r="D45" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E45" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F45" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G45" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H45" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="str">
+        <v>未來規劃</v>
+      </c>
+      <c r="B46" s="3">
         <v>3</v>
       </c>
-      <c r="D29" s="3">
-        <v>28</v>
-      </c>
-      <c r="E29" s="3">
-        <v>55</v>
-      </c>
-      <c r="F29" s="3" t="str">
-        <v>46.4%</v>
-      </c>
-      <c r="G29" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H29" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="14.4" customHeight="1">
-      <c r="A31" s="3" t="str">
-        <v>【5】UIUX — 各區塊問題分布</v>
-      </c>
-      <c r="B31" s="3" t="str">
-        <v/>
-      </c>
-      <c r="C31" s="3" t="str">
-        <v/>
-      </c>
-      <c r="D31" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E31" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F31" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G31" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H31" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="14.4" customHeight="1">
-      <c r="A32" s="3" t="str">
-        <v>區塊</v>
-      </c>
-      <c r="B32" s="3" t="str">
-        <v>項目數</v>
-      </c>
-      <c r="C32" s="3" t="str">
-        <v>佔比</v>
-      </c>
-      <c r="D32" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E32" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F32" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G32" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H32" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="14.4" customHeight="1">
-      <c r="A33" s="3" t="str">
-        <v>全站通用</v>
-      </c>
-      <c r="B33" s="3">
-        <v>31</v>
-      </c>
-      <c r="C33" s="3" t="str">
-        <v>21.8%</v>
-      </c>
-      <c r="D33" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E33" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F33" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G33" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H33" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="14.4" customHeight="1">
-      <c r="A34" s="3" t="str">
-        <v>i-Fare 福利查詢</v>
-      </c>
-      <c r="B34" s="3">
-        <v>24</v>
-      </c>
-      <c r="C34" s="3" t="str">
-        <v>16.9%</v>
-      </c>
-      <c r="D34" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E34" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F34" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G34" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H34" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="14.4" customHeight="1">
-      <c r="A35" s="3" t="str">
-        <v>共用元件</v>
-      </c>
-      <c r="B35" s="3">
-        <v>24</v>
-      </c>
-      <c r="C35" s="3" t="str">
-        <v>16.9%</v>
-      </c>
-      <c r="D35" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E35" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F35" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G35" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H35" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="14.4" customHeight="1">
-      <c r="A36" s="3" t="str">
-        <v>福利專欄</v>
-      </c>
-      <c r="B36" s="3">
-        <v>11</v>
-      </c>
-      <c r="C36" s="3" t="str">
-        <v>7.7%</v>
-      </c>
-      <c r="D36" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E36" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F36" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G36" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H36" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="14.4" customHeight="1">
-      <c r="A37" s="3" t="str">
-        <v>關於長穩</v>
-      </c>
-      <c r="B37" s="3">
-        <v>9</v>
-      </c>
-      <c r="C37" s="3" t="str">
-        <v>6.3%</v>
-      </c>
-      <c r="D37" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E37" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F37" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G37" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H37" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="14.4" customHeight="1">
-      <c r="A38" s="3" t="str">
-        <v>首頁</v>
-      </c>
-      <c r="B38" s="3">
-        <v>8</v>
-      </c>
-      <c r="C38" s="3" t="str">
-        <v>5.6%</v>
-      </c>
-      <c r="D38" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E38" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F38" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G38" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H38" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="14.4" customHeight="1">
-      <c r="A39" s="3" t="str">
-        <v>最新消息</v>
-      </c>
-      <c r="B39" s="3">
-        <v>8</v>
-      </c>
-      <c r="C39" s="3" t="str">
-        <v>5.6%</v>
-      </c>
-      <c r="D39" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E39" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F39" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G39" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H39" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="14.4" customHeight="1">
-      <c r="A40" s="3" t="str">
-        <v>公益夥伴</v>
-      </c>
-      <c r="B40" s="3">
-        <v>7</v>
-      </c>
-      <c r="C40" s="3" t="str">
-        <v>4.9%</v>
-      </c>
-      <c r="D40" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E40" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F40" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G40" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H40" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="14.4" customHeight="1">
-      <c r="A41" s="3" t="str">
-        <v>全站微互動</v>
-      </c>
-      <c r="B41" s="3">
-        <v>5</v>
-      </c>
-      <c r="C41" s="3" t="str">
-        <v>3.5%</v>
-      </c>
-      <c r="D41" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E41" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F41" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G41" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H41" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="14.4" customHeight="1">
-      <c r="A42" s="3" t="str">
-        <v>設計系統</v>
-      </c>
-      <c r="B42" s="3">
-        <v>5</v>
-      </c>
-      <c r="C42" s="3" t="str">
-        <v>3.5%</v>
-      </c>
-      <c r="D42" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E42" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F42" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G42" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H42" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="14.4" customHeight="1">
-      <c r="A43" s="3" t="str">
+      <c r="C46" s="3" t="str">
+        <v>1.8%</v>
+      </c>
+      <c r="D46" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E46" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F46" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G46" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H46" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="str">
         <v>安全性</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B47" s="3">
         <v>2</v>
       </c>
-      <c r="C43" s="3" t="str">
-        <v>1.4%</v>
-      </c>
-      <c r="D43" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E43" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F43" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G43" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H43" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="14.4" customHeight="1">
-      <c r="A44" s="3" t="str">
+      <c r="C47" s="3" t="str">
+        <v>1.2%</v>
+      </c>
+      <c r="D47" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E47" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F47" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G47" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H47" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="str">
         <v>無障礙</v>
       </c>
-      <c r="B44" s="3">
+      <c r="B48" s="3">
         <v>2</v>
       </c>
-      <c r="C44" s="3" t="str">
-        <v>1.4%</v>
-      </c>
-      <c r="D44" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E44" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F44" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G44" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H44" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="14.4" customHeight="1">
-      <c r="A45" s="3" t="str">
-        <v>未來規劃</v>
-      </c>
-      <c r="B45" s="3">
-        <v>1</v>
-      </c>
-      <c r="C45" s="3" t="str">
-        <v>0.7%</v>
-      </c>
-      <c r="D45" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E45" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F45" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G45" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H45" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="14.4" customHeight="1">
-      <c r="A46" s="3" t="str">
+      <c r="C48" s="3" t="str">
+        <v>1.2%</v>
+      </c>
+      <c r="D48" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E48" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F48" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G48" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H48" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="str">
         <v>頁面導航</v>
-      </c>
-      <c r="B46" s="3">
-        <v>1</v>
-      </c>
-      <c r="C46" s="3" t="str">
-        <v>0.7%</v>
-      </c>
-      <c r="D46" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E46" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F46" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G46" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H46" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="14.4" customHeight="1">
-      <c r="A47" s="3" t="str">
-        <v>i-Fare 搜尋結果</v>
-      </c>
-      <c r="B47" s="3">
-        <v>1</v>
-      </c>
-      <c r="C47" s="3" t="str">
-        <v>0.7%</v>
-      </c>
-      <c r="D47" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E47" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F47" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G47" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H47" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="14.4" customHeight="1">
-      <c r="A48" s="3" t="str">
-        <v>效能</v>
-      </c>
-      <c r="B48" s="3">
-        <v>1</v>
-      </c>
-      <c r="C48" s="3" t="str">
-        <v>0.7%</v>
-      </c>
-      <c r="D48" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E48" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F48" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G48" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H48" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="14.4" customHeight="1">
-      <c r="A49" s="3" t="str">
-        <v>社群分享</v>
       </c>
       <c r="B49" s="3">
         <v>1</v>
       </c>
       <c r="C49" s="3" t="str">
-        <v>0.7%</v>
+        <v>0.6%</v>
       </c>
       <c r="D49" s="3" t="str">
         <v/>
@@ -13746,15 +14300,15 @@
         <v/>
       </c>
     </row>
-    <row r="50" ht="14.4" customHeight="1">
+    <row r="50">
       <c r="A50" s="3" t="str">
-        <v>導航</v>
+        <v>i-Fare 搜尋結果</v>
       </c>
       <c r="B50" s="3">
         <v>1</v>
       </c>
       <c r="C50" s="3" t="str">
-        <v>0.7%</v>
+        <v>0.6%</v>
       </c>
       <c r="D50" s="3" t="str">
         <v/>
@@ -13772,353 +14326,353 @@
         <v/>
       </c>
     </row>
-    <row r="52" ht="14.4" customHeight="1">
+    <row r="51">
+      <c r="A51" s="3" t="str">
+        <v>效能</v>
+      </c>
+      <c r="B51" s="3">
+        <v>1</v>
+      </c>
+      <c r="C51" s="3" t="str">
+        <v>0.6%</v>
+      </c>
+      <c r="D51" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E51" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F51" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G51" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H51" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
       <c r="A52" s="3" t="str">
+        <v>社群分享</v>
+      </c>
+      <c r="B52" s="3">
+        <v>1</v>
+      </c>
+      <c r="C52" s="3" t="str">
+        <v>0.6%</v>
+      </c>
+      <c r="D52" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E52" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F52" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G52" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H52" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="str">
+        <v>導航</v>
+      </c>
+      <c r="B53" s="3">
+        <v>1</v>
+      </c>
+      <c r="C53" s="3" t="str">
+        <v>0.6%</v>
+      </c>
+      <c r="D53" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E53" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F53" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G53" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H53" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="str">
+        <v>關於我們</v>
+      </c>
+      <c r="B54" s="3">
+        <v>1</v>
+      </c>
+      <c r="C54" s="3" t="str">
+        <v>0.6%</v>
+      </c>
+      <c r="D54" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E54" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F54" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G54" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H54" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="str">
+        <v>後台</v>
+      </c>
+      <c r="B55" s="3">
+        <v>1</v>
+      </c>
+      <c r="C55" s="3" t="str">
+        <v>0.6%</v>
+      </c>
+      <c r="D55" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E55" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F55" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G55" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H55" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="str">
+        <v>preview 頁</v>
+      </c>
+      <c r="B56" s="3">
+        <v>1</v>
+      </c>
+      <c r="C56" s="3" t="str">
+        <v>0.6%</v>
+      </c>
+      <c r="D56" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E56" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F56" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G56" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H56" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="str">
+        <v>追蹤文件</v>
+      </c>
+      <c r="B57" s="3">
+        <v>1</v>
+      </c>
+      <c r="C57" s="3" t="str">
+        <v>0.6%</v>
+      </c>
+      <c r="D57" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E57" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F57" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G57" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H57" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="str">
         <v>【6】後臺優化 — 各區塊問題分布</v>
       </c>
-      <c r="B52" s="3" t="str">
-        <v/>
-      </c>
-      <c r="C52" s="3" t="str">
-        <v/>
-      </c>
-      <c r="D52" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E52" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F52" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G52" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H52" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="14.4" customHeight="1">
-      <c r="A53" s="3" t="str">
+      <c r="B59" s="10" t="str">
+        <v/>
+      </c>
+      <c r="C59" s="10" t="str">
+        <v/>
+      </c>
+      <c r="D59" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E59" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F59" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G59" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H59" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="str">
         <v>區塊</v>
       </c>
-      <c r="B53" s="3" t="str">
+      <c r="B60" s="11" t="str">
         <v>項目數</v>
       </c>
-      <c r="C53" s="3" t="str">
+      <c r="C60" s="11" t="str">
         <v>佔比</v>
       </c>
-      <c r="D53" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E53" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F53" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G53" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H53" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="14.4" customHeight="1">
-      <c r="A54" s="3" t="str">
+      <c r="D60" s="11" t="str">
+        <v/>
+      </c>
+      <c r="E60" s="11" t="str">
+        <v/>
+      </c>
+      <c r="F60" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G60" s="11" t="str">
+        <v/>
+      </c>
+      <c r="H60" s="11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="str">
+        <v>後台通用</v>
+      </c>
+      <c r="B61" s="3">
+        <v>19</v>
+      </c>
+      <c r="C61" s="3" t="str">
+        <v>30.2%</v>
+      </c>
+      <c r="D61" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E61" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F61" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G61" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H61" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="str">
         <v>共用元件</v>
       </c>
-      <c r="B54" s="3">
-        <v>16</v>
-      </c>
-      <c r="C54" s="3" t="str">
-        <v>29.1%</v>
-      </c>
-      <c r="D54" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E54" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F54" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G54" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H54" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="14.4" customHeight="1">
-      <c r="A55" s="3" t="str">
-        <v>後台通用</v>
-      </c>
-      <c r="B55" s="3">
-        <v>15</v>
-      </c>
-      <c r="C55" s="3" t="str">
-        <v>27.3%</v>
-      </c>
-      <c r="D55" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E55" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F55" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G55" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H55" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="56" ht="14.4" customHeight="1">
-      <c r="A56" s="3" t="str">
+      <c r="B62" s="3">
+        <v>17</v>
+      </c>
+      <c r="C62" s="3" t="str">
+        <v>27.0%</v>
+      </c>
+      <c r="D62" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E62" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F62" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G62" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H62" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="str">
+        <v>圖片管理</v>
+      </c>
+      <c r="B63" s="3">
+        <v>3</v>
+      </c>
+      <c r="C63" s="3" t="str">
+        <v>4.8%</v>
+      </c>
+      <c r="D63" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E63" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F63" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G63" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H63" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="str">
         <v>i-Fare 維護</v>
       </c>
-      <c r="B56" s="3">
+      <c r="B64" s="3">
         <v>2</v>
       </c>
-      <c r="C56" s="3" t="str">
-        <v>3.6%</v>
-      </c>
-      <c r="D56" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E56" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F56" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G56" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H56" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="14.4" customHeight="1">
-      <c r="A57" s="3" t="str">
-        <v>圖片管理</v>
-      </c>
-      <c r="B57" s="3">
-        <v>2</v>
-      </c>
-      <c r="C57" s="3" t="str">
-        <v>3.6%</v>
-      </c>
-      <c r="D57" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E57" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F57" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G57" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H57" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="14.4" customHeight="1">
-      <c r="A58" s="3" t="str">
+      <c r="C64" s="3" t="str">
+        <v>3.2%</v>
+      </c>
+      <c r="D64" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E64" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F64" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G64" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H64" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="str">
         <v>最新消息維護</v>
-      </c>
-      <c r="B58" s="3">
-        <v>1</v>
-      </c>
-      <c r="C58" s="3" t="str">
-        <v>1.8%</v>
-      </c>
-      <c r="D58" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E58" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F58" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G58" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H58" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="14.4" customHeight="1">
-      <c r="A59" s="3" t="str">
-        <v>帳戶維護 / 全站權限</v>
-      </c>
-      <c r="B59" s="3">
-        <v>1</v>
-      </c>
-      <c r="C59" s="3" t="str">
-        <v>1.8%</v>
-      </c>
-      <c r="D59" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E59" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F59" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G59" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H59" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="14.4" customHeight="1">
-      <c r="A60" s="3" t="str">
-        <v>前台通用</v>
-      </c>
-      <c r="B60" s="3">
-        <v>1</v>
-      </c>
-      <c r="C60" s="3" t="str">
-        <v>1.8%</v>
-      </c>
-      <c r="D60" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E60" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F60" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G60" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H60" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="61" ht="14.4" customHeight="1">
-      <c r="A61" s="3" t="str">
-        <v>對話框</v>
-      </c>
-      <c r="B61" s="3">
-        <v>1</v>
-      </c>
-      <c r="C61" s="3" t="str">
-        <v>1.8%</v>
-      </c>
-      <c r="D61" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E61" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F61" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G61" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H61" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="62" ht="14.4" customHeight="1">
-      <c r="A62" s="3" t="str">
-        <v>檔案上傳</v>
-      </c>
-      <c r="B62" s="3">
-        <v>1</v>
-      </c>
-      <c r="C62" s="3" t="str">
-        <v>1.8%</v>
-      </c>
-      <c r="D62" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E62" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F62" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G62" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H62" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="63" ht="14.4" customHeight="1">
-      <c r="A63" s="3" t="str">
-        <v>帳號管理</v>
-      </c>
-      <c r="B63" s="3">
-        <v>1</v>
-      </c>
-      <c r="C63" s="3" t="str">
-        <v>1.8%</v>
-      </c>
-      <c r="D63" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E63" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F63" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G63" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H63" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="64" ht="14.4" customHeight="1">
-      <c r="A64" s="3" t="str">
-        <v>搜尋結果</v>
-      </c>
-      <c r="B64" s="3">
-        <v>1</v>
-      </c>
-      <c r="C64" s="3" t="str">
-        <v>1.8%</v>
-      </c>
-      <c r="D64" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E64" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F64" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G64" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H64" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="65" ht="14.4" customHeight="1">
-      <c r="A65" s="3" t="str">
-        <v>日期選擇</v>
       </c>
       <c r="B65" s="3">
         <v>1</v>
       </c>
       <c r="C65" s="3" t="str">
-        <v>1.8%</v>
+        <v>1.6%</v>
       </c>
       <c r="D65" s="3" t="str">
         <v/>
@@ -14136,15 +14690,15 @@
         <v/>
       </c>
     </row>
-    <row r="66" ht="14.4" customHeight="1">
+    <row r="66">
       <c r="A66" s="3" t="str">
-        <v>表單</v>
+        <v>帳戶維護 / 全站權限</v>
       </c>
       <c r="B66" s="3">
         <v>1</v>
       </c>
       <c r="C66" s="3" t="str">
-        <v>1.8%</v>
+        <v>1.6%</v>
       </c>
       <c r="D66" s="3" t="str">
         <v/>
@@ -14162,15 +14716,15 @@
         <v/>
       </c>
     </row>
-    <row r="67" ht="14.4" customHeight="1">
+    <row r="67">
       <c r="A67" s="3" t="str">
-        <v>側邊欄</v>
+        <v>前台通用</v>
       </c>
       <c r="B67" s="3">
         <v>1</v>
       </c>
       <c r="C67" s="3" t="str">
-        <v>1.8%</v>
+        <v>1.6%</v>
       </c>
       <c r="D67" s="3" t="str">
         <v/>
@@ -14188,15 +14742,15 @@
         <v/>
       </c>
     </row>
-    <row r="68" ht="14.4" customHeight="1">
+    <row r="68">
       <c r="A68" s="3" t="str">
-        <v>麵包屑導覽</v>
+        <v>對話框</v>
       </c>
       <c r="B68" s="3">
         <v>1</v>
       </c>
       <c r="C68" s="3" t="str">
-        <v>1.8%</v>
+        <v>1.6%</v>
       </c>
       <c r="D68" s="3" t="str">
         <v/>
@@ -14214,15 +14768,15 @@
         <v/>
       </c>
     </row>
-    <row r="69" ht="14.4" customHeight="1">
+    <row r="69">
       <c r="A69" s="3" t="str">
-        <v>WebAPI</v>
+        <v>檔案上傳</v>
       </c>
       <c r="B69" s="3">
         <v>1</v>
       </c>
       <c r="C69" s="3" t="str">
-        <v>1.8%</v>
+        <v>1.6%</v>
       </c>
       <c r="D69" s="3" t="str">
         <v/>
@@ -14240,15 +14794,15 @@
         <v/>
       </c>
     </row>
-    <row r="70" ht="14.4" customHeight="1">
+    <row r="70">
       <c r="A70" s="3" t="str">
-        <v>帳號變更密碼</v>
+        <v>帳號管理</v>
       </c>
       <c r="B70" s="3">
         <v>1</v>
       </c>
       <c r="C70" s="3" t="str">
-        <v>1.8%</v>
+        <v>1.6%</v>
       </c>
       <c r="D70" s="3" t="str">
         <v/>
@@ -14266,15 +14820,15 @@
         <v/>
       </c>
     </row>
-    <row r="71" ht="14.4" customHeight="1">
+    <row r="71">
       <c r="A71" s="3" t="str">
-        <v>Code 代碼管理</v>
+        <v>搜尋結果</v>
       </c>
       <c r="B71" s="3">
         <v>1</v>
       </c>
       <c r="C71" s="3" t="str">
-        <v>1.8%</v>
+        <v>1.6%</v>
       </c>
       <c r="D71" s="3" t="str">
         <v/>
@@ -14292,15 +14846,15 @@
         <v/>
       </c>
     </row>
-    <row r="72" ht="14.4" customHeight="1">
+    <row r="72">
       <c r="A72" s="3" t="str">
-        <v>狀態管理</v>
+        <v>日期選擇</v>
       </c>
       <c r="B72" s="3">
         <v>1</v>
       </c>
       <c r="C72" s="3" t="str">
-        <v>1.8%</v>
+        <v>1.6%</v>
       </c>
       <c r="D72" s="3" t="str">
         <v/>
@@ -14318,15 +14872,15 @@
         <v/>
       </c>
     </row>
-    <row r="73" ht="14.4" customHeight="1">
+    <row r="73">
       <c r="A73" s="3" t="str">
-        <v>登入頁面</v>
+        <v>表單</v>
       </c>
       <c r="B73" s="3">
         <v>1</v>
       </c>
       <c r="C73" s="3" t="str">
-        <v>1.8%</v>
+        <v>1.6%</v>
       </c>
       <c r="D73" s="3" t="str">
         <v/>
@@ -14344,15 +14898,15 @@
         <v/>
       </c>
     </row>
-    <row r="74" ht="14.4" customHeight="1">
+    <row r="74">
       <c r="A74" s="3" t="str">
-        <v>HTML 編輯器</v>
+        <v>側邊欄</v>
       </c>
       <c r="B74" s="3">
         <v>1</v>
       </c>
       <c r="C74" s="3" t="str">
-        <v>1.8%</v>
+        <v>1.6%</v>
       </c>
       <c r="D74" s="3" t="str">
         <v/>
@@ -14370,15 +14924,15 @@
         <v/>
       </c>
     </row>
-    <row r="75" ht="14.4" customHeight="1">
+    <row r="75">
       <c r="A75" s="3" t="str">
-        <v>無權限頁</v>
+        <v>麵包屑導覽</v>
       </c>
       <c r="B75" s="3">
         <v>1</v>
       </c>
       <c r="C75" s="3" t="str">
-        <v>1.8%</v>
+        <v>1.6%</v>
       </c>
       <c r="D75" s="3" t="str">
         <v/>
@@ -14396,15 +14950,15 @@
         <v/>
       </c>
     </row>
-    <row r="76" ht="14.4" customHeight="1">
+    <row r="76">
       <c r="A76" s="3" t="str">
-        <v>效能</v>
+        <v>WebAPI</v>
       </c>
       <c r="B76" s="3">
         <v>1</v>
       </c>
       <c r="C76" s="3" t="str">
-        <v>1.8%</v>
+        <v>1.6%</v>
       </c>
       <c r="D76" s="3" t="str">
         <v/>
@@ -14422,15 +14976,15 @@
         <v/>
       </c>
     </row>
-    <row r="77" ht="14.4" customHeight="1">
+    <row r="77">
       <c r="A77" s="3" t="str">
-        <v>後台首頁</v>
+        <v>帳號變更密碼</v>
       </c>
       <c r="B77" s="3">
         <v>1</v>
       </c>
       <c r="C77" s="3" t="str">
-        <v>1.8%</v>
+        <v>1.6%</v>
       </c>
       <c r="D77" s="3" t="str">
         <v/>
@@ -14448,166 +15002,426 @@
         <v/>
       </c>
     </row>
-    <row r="79" ht="14.4" customHeight="1">
+    <row r="78">
+      <c r="A78" s="3" t="str">
+        <v>Code 代碼管理</v>
+      </c>
+      <c r="B78" s="3">
+        <v>1</v>
+      </c>
+      <c r="C78" s="3" t="str">
+        <v>1.6%</v>
+      </c>
+      <c r="D78" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E78" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F78" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G78" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H78" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
       <c r="A79" s="3" t="str">
+        <v>狀態管理</v>
+      </c>
+      <c r="B79" s="3">
+        <v>1</v>
+      </c>
+      <c r="C79" s="3" t="str">
+        <v>1.6%</v>
+      </c>
+      <c r="D79" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E79" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F79" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G79" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H79" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="str">
+        <v>登入頁面</v>
+      </c>
+      <c r="B80" s="3">
+        <v>1</v>
+      </c>
+      <c r="C80" s="3" t="str">
+        <v>1.6%</v>
+      </c>
+      <c r="D80" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E80" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F80" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G80" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H80" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="str">
+        <v>HTML 編輯器</v>
+      </c>
+      <c r="B81" s="3">
+        <v>1</v>
+      </c>
+      <c r="C81" s="3" t="str">
+        <v>1.6%</v>
+      </c>
+      <c r="D81" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E81" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F81" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G81" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H81" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="str">
+        <v>無權限頁</v>
+      </c>
+      <c r="B82" s="3">
+        <v>1</v>
+      </c>
+      <c r="C82" s="3" t="str">
+        <v>1.6%</v>
+      </c>
+      <c r="D82" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E82" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F82" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G82" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H82" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="str">
+        <v>效能</v>
+      </c>
+      <c r="B83" s="3">
+        <v>1</v>
+      </c>
+      <c r="C83" s="3" t="str">
+        <v>1.6%</v>
+      </c>
+      <c r="D83" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E83" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F83" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G83" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H83" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="str">
+        <v>後台首頁</v>
+      </c>
+      <c r="B84" s="3">
+        <v>1</v>
+      </c>
+      <c r="C84" s="3" t="str">
+        <v>1.6%</v>
+      </c>
+      <c r="D84" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E84" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F84" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G84" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H84" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="str">
+        <v>內容品質</v>
+      </c>
+      <c r="B85" s="3">
+        <v>1</v>
+      </c>
+      <c r="C85" s="3" t="str">
+        <v>1.6%</v>
+      </c>
+      <c r="D85" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E85" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F85" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G85" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H85" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="str">
+        <v>資料分析</v>
+      </c>
+      <c r="B86" s="3">
+        <v>1</v>
+      </c>
+      <c r="C86" s="3" t="str">
+        <v>1.6%</v>
+      </c>
+      <c r="D86" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E86" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F86" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G86" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H86" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="str">
         <v>【7】你做了什麼 — 已完成項目摘要 (依 Round 分組)</v>
       </c>
-      <c r="B79" s="3" t="str">
-        <v/>
-      </c>
-      <c r="C79" s="3" t="str">
-        <v/>
-      </c>
-      <c r="D79" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E79" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F79" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G79" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H79" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="80" ht="14.4" customHeight="1">
-      <c r="A80" s="3" t="str">
+      <c r="B88" s="10" t="str">
+        <v/>
+      </c>
+      <c r="C88" s="10" t="str">
+        <v/>
+      </c>
+      <c r="D88" s="10" t="str">
+        <v/>
+      </c>
+      <c r="E88" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F88" s="10" t="str">
+        <v/>
+      </c>
+      <c r="G88" s="10" t="str">
+        <v/>
+      </c>
+      <c r="H88" s="10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="11" t="str">
         <v>Round</v>
       </c>
-      <c r="B80" s="3" t="str">
+      <c r="B89" s="11" t="str">
         <v>日期</v>
       </c>
-      <c r="C80" s="3" t="str">
+      <c r="C89" s="11" t="str">
         <v>已修正 (綠)</v>
       </c>
-      <c r="D80" s="3" t="str">
+      <c r="D89" s="11" t="str">
         <v>部分修正 (黃)</v>
       </c>
-      <c r="E80" s="3" t="str">
+      <c r="E89" s="11" t="str">
         <v>已修正 # 清單</v>
       </c>
-      <c r="F80" s="3" t="str">
+      <c r="F89" s="11" t="str">
         <v>部分修正 # 清單</v>
       </c>
-      <c r="G80" s="3" t="str">
+      <c r="G89" s="11" t="str">
         <v>主要重點</v>
       </c>
-      <c r="H80" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="81" ht="14.4" customHeight="1">
-      <c r="A81" s="3" t="str">
+      <c r="H89" s="11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="str">
         <v>Round 1</v>
       </c>
-      <c r="B81" s="3" t="str">
+      <c r="B90" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="C81" s="3">
-        <v>45</v>
-      </c>
-      <c r="D81" s="3">
-        <v>7</v>
-      </c>
-      <c r="E81" s="3" t="str">
-        <v>#3, #6, #14, #16, #17, #22, #23, #24, #29, #37, #44, #45, #46, #47, #49, #52, #53, #54, #55, #56, #59, #75, #77, #79, #88, #89, #90, #106, #108, #109, #110, #112, #114, #115, #118, #120, #125, #126, #127, #130, #131, #132, #133, #134, #135</v>
-      </c>
-      <c r="F81" s="3" t="str">
-        <v>#1, #9, #60, #71, #76, #80, #107</v>
-      </c>
-      <c r="G81" s="3" t="str">
+      <c r="C90" s="12">
+        <v>103</v>
+      </c>
+      <c r="D90" s="13">
+        <v>11</v>
+      </c>
+      <c r="E90" s="3" t="str">
+        <v>#1, #2, #3, #6, #7, #9, #11, #12, #13, #14, #15, #16, #17, #22, #23, #24, #27, #28, #29, #30, #31, #32, #36, #37, #38, #40, #41, #44, #45, #46, #47, #48, #49, #50, #52, #53, #54, #55, #56, #58, #59, #60, #61, #70, #71, #75, #77, #79, #80, #82, #86, #87, #88, #89, #90, #106, #108, #109, #110, #111, #112, #113, #114, #115, #116, #117, #118, #119, #120, #122, #123, #124, #125, #126, #127, #128, #129, #130, #131, #132, #133, #134, #135, #137, #138, #139, #140, #143, #145, #146, #147, #149, #150, #151, #152, #153, #155, #156, #157, #159, #161, #162, #163</v>
+      </c>
+      <c r="F90" s="3" t="str">
+        <v>#67, #68, #73, #76, #107, #136, #141, #142, #144, #158, #160</v>
+      </c>
+      <c r="G90" s="3" t="str">
         <v>搜尋優化 (移除 disabled / 結果摘要) + 全站動畫 + skeleton 載入 + 卡片/按鈕 hover translateY</v>
       </c>
-      <c r="H81" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="82" ht="14.4" customHeight="1">
-      <c r="A82" s="3" t="str">
+      <c r="H90" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="str">
         <v>Round 2</v>
       </c>
-      <c r="B82" s="3" t="str">
+      <c r="B91" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="C82" s="3">
+      <c r="C91" s="12">
         <v>2</v>
       </c>
-      <c r="D82" s="3">
+      <c r="D91" s="13">
         <v>0</v>
       </c>
-      <c r="E82" s="3" t="str">
+      <c r="E91" s="3" t="str">
         <v>#91, #92</v>
       </c>
-      <c r="F82" s="3" t="str">
+      <c r="F91" s="3" t="str">
         <v>-</v>
       </c>
-      <c r="G82" s="3" t="str">
+      <c r="G91" s="3" t="str">
         <v>Footer 整合 (LINE/FB 並列 .btn-social) + 觸控目標 44px</v>
       </c>
-      <c r="H82" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="83" ht="14.4" customHeight="1">
-      <c r="A83" s="3" t="str">
+      <c r="H91" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="str">
         <v>Round 3</v>
       </c>
-      <c r="B83" s="3" t="str">
+      <c r="B92" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="C83" s="3">
+      <c r="C92" s="12">
         <v>6</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D92" s="13">
         <v>0</v>
       </c>
-      <c r="E83" s="3" t="str">
+      <c r="E92" s="3" t="str">
         <v>#26, #93, #94, #95, #96, #97</v>
       </c>
-      <c r="F83" s="3" t="str">
+      <c r="F92" s="3" t="str">
         <v>-</v>
       </c>
-      <c r="G83" s="3" t="str">
+      <c r="G92" s="3" t="str">
         <v>About 三大核心 morph 卡 + News 浮起卡 + 浮現動畫 + line-clamp + NEW pill + 社群 target="_blank"</v>
       </c>
-      <c r="H83" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="84" ht="14.4" customHeight="1">
-      <c r="A84" s="3" t="str">
+      <c r="H92" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="str">
         <v>Round 4</v>
       </c>
-      <c r="B84" s="3" t="str">
+      <c r="B93" s="3" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="C84" s="3">
+      <c r="C93" s="12">
         <v>8</v>
       </c>
-      <c r="D84" s="3">
+      <c r="D93" s="13">
         <v>0</v>
       </c>
-      <c r="E84" s="3" t="str">
+      <c r="E93" s="3" t="str">
         <v>#98, #99, #100, #101, #102, #103, #104, #105</v>
       </c>
-      <c r="F84" s="3" t="str">
+      <c r="F93" s="3" t="str">
         <v>-</v>
       </c>
-      <c r="G84" s="3" t="str">
+      <c r="G93" s="3" t="str">
         <v>cf47cfa+5dfbf91 補回 16 檔 + 環境設定 (devProxy/baseURL) + 未來規劃 nav + News videoUrl wiring + tsconfig + about hover bug + footer label 重複</v>
       </c>
-      <c r="H84" s="3" t="str">
+      <c r="H93" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="str">
+        <v>Round 9</v>
+      </c>
+      <c r="B94" s="3" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C94" s="12">
+        <v>2</v>
+      </c>
+      <c r="D94" s="13">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3" t="str">
+        <v>#164, #165</v>
+      </c>
+      <c r="F94" s="3" t="str">
+        <v>-</v>
+      </c>
+      <c r="G94" s="3" t="str">
+        <v>future.vue 補強手機版主標換行、空狀態導引卡與上下節奏，讓頁面在未上線時也有清楚下一步</v>
+      </c>
+      <c r="H94" s="3" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H84"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H95"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/iFare_UI_UX_問題追蹤清單.xlsx
+++ b/docs/iFare_UI_UX_問題追蹤清單.xlsx
@@ -1165,52 +1165,52 @@
       </c>
     </row>
     <row r="5" ht="14.4" customHeight="1">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="str">
-        <v>V</v>
-      </c>
-      <c r="C5" s="2" t="str">
+      <c r="B5" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C5" s="3" t="str">
         <v>共用元件</v>
       </c>
-      <c r="D5" s="2" t="str">
+      <c r="D5" s="3" t="str">
         <v>Loading / Feedback</v>
       </c>
-      <c r="E5" s="2" t="str">
+      <c r="E5" s="3" t="str">
         <v>提升</v>
       </c>
-      <c r="F5" s="2" t="str">
+      <c r="F5" s="3" t="str">
         <v>互動</v>
       </c>
-      <c r="G5" s="2" t="str">
+      <c r="G5" s="3" t="str">
         <v>高</v>
       </c>
-      <c r="H5" s="2" t="str">
+      <c r="H5" s="3" t="str">
         <v>統一 loading / success / failure 回饋介面</v>
       </c>
-      <c r="I5" s="2" t="str">
+      <c r="I5" s="3" t="str">
         <v>各頁面直接 ElMessage({ type, message }) 散落呼叫，文案散亂、error 沒展開 Error.message 難 debug、無 loading mask 統一行為；未來切後端 API 沒有共用 await 包裝</v>
       </c>
-      <c r="J5" s="2" t="str">
+      <c r="J5" s="3" t="str">
         <v>建立 src/composables/useFeedback.ts，封裝 success / error / info / warning + runAsync(fn, { loadingText, successText, errorText })；先在 PageManagement DataList、PageManagement AddEdit、LoginView、HomeView 4 支示範頁導入，其餘頁面後續批次</v>
       </c>
-      <c r="K5" s="2" t="str">
+      <c r="K5" s="3" t="str">
         <v>src/composables/useFeedback.ts</v>
       </c>
-      <c r="L5" s="2" t="str">
+      <c r="L5" s="3" t="str">
         <v>Dev/Dev Code/iFare_Backend/src/composables/useFeedback.ts (新建); src/views/PageManagement/PageManagement_DataListView.vue; src/views/PageManagement/PageManagement_AddEditView.vue; src/views/LoginView.vue; src/views/HomeView.vue</v>
       </c>
-      <c r="M5" s="2" t="str">
+      <c r="M5" s="3" t="str">
         <v>示範樣板完成，其餘後台頁面後續批次再導入；runAsync 預留 ElLoading.service mask 介面，未來接後端 API 不用改呼叫端</v>
       </c>
-      <c r="N5" s="2" t="str">
+      <c r="N5" s="3" t="str">
         <v>已修正</v>
       </c>
-      <c r="O5" s="2" t="str">
+      <c r="O5" s="3" t="str">
         <v>2026-05-18</v>
       </c>
-      <c r="P5" s="2" t="str">
+      <c r="P5" s="3" t="str">
         <v>Round 14 第三批 Loading 主題核心項；error() 同時 console.error 保留 stack，避免 ElMessage swallow</v>
       </c>
       <c r="Q5" s="3" t="str">
@@ -4654,31 +4654,31 @@
         <v>中</v>
       </c>
       <c r="H69" s="2" t="str">
-        <v>PageBuilder 新增 page 完無法在前端顯示 — 加前端動態路由 PoC 走通渲染鏈路</v>
+        <v>PageBuilder 新增 page 完無法在前端顯示 — 前端動態路由 + 自動同步 (v2 完成)</v>
       </c>
       <c r="I69" s="2" t="str">
-        <v>後台 PageBuilder（commit cea8433）已能新增/編輯/儲存於 localStorage iFare_dynamic_pages_v2，但前端 Nuxt 無 catch-all 動態路由、無讀取 composable，DynamicPageRenderer 只給後台 iframe preview 用，「新增完前端看不到」</v>
+        <v>v1 跨應用 localStorage 不共享，PoC 用手動貼 JSON 走通渲染鏈路；v2 用 Nuxt server route 當中介層自動同步，後台儲存→fire-and-forget PUT→前端 useAsyncData 讀，達成「後台按下儲存→前端重整看得到」端到端體驗</v>
       </c>
       <c r="J69" s="2" t="str">
-        <v>後台 DataListView 加「複製 JSON」按鈕；前端新增 composables/useDynamicPages.ts（從 localStorage 讀 + getPageBySlug + isPublishable 判 status/publishTime/unpublishTime）；前端新增 pages/[slug].vue 動態路由 + ClientOnly 包覆 + 找不到顯示 fallback；寫 docs/iFare_PageBuilder_前端顯示PoC_2026-05-18.md 記錄範圍與後續工程化</v>
+        <v>後台新建 utils/frontendSync.ts (fetch PUT 整批) + writeAll() dual write；後台 useFeedback 新增 successWithLink + AddEditView toast 加「前往前端預覽」連結；前端新建 server/utils/cors.ts + 3 個 server/api/dynamic-pages.{get,put,options}.ts 寫進 server/data/dynamic-pages.json；前端 composables/useDynamicPages.ts 改 async ($fetch) + pages/[slug].vue 改 useAsyncData + throw createError(404) 升級 SSR</v>
       </c>
       <c r="K69" s="2" t="str">
-        <v>iFare_Frontend/pages/[slug].vue (新建); iFare_Frontend/composables/useDynamicPages.ts (新建); iFare_Backend/src/views/PageManagement/PageManagement_DataListView.vue</v>
+        <v>iFare_Backend/src/utils/frontendSync.ts (新建); iFare_Backend/src/composables/useDynamicPages.ts (writeAll 改); iFare_Backend/src/composables/useFeedback.ts (加 successWithLink); iFare_Backend/src/views/PageManagement/PageManagement_AddEditView.vue (toast 升級); iFare_Frontend/server/utils/cors.ts (新建); iFare_Frontend/server/api/dynamic-pages.{get,put,options}.ts (新建); iFare_Frontend/server/data/.gitignore (新建); iFare_Frontend/composables/useDynamicPages.ts (改寫); iFare_Frontend/pages/[slug].vue (改 SSR)</v>
       </c>
       <c r="L69" s="2" t="str">
-        <v>Dev/Dev Code/iFare_Frontend/pages/[slug].vue; Dev/Dev Code/iFare_Frontend/composables/useDynamicPages.ts; Dev/Dev Code/iFare_Backend/src/views/PageManagement/PageManagement_DataListView.vue; docs/iFare_PageBuilder_前端顯示PoC_2026-05-18.md</v>
+        <v>Dev/Dev Code/iFare_Backend/src/utils/frontendSync.ts; Dev/Dev Code/iFare_Backend/src/composables/useDynamicPages.ts:180-186; Dev/Dev Code/iFare_Backend/src/composables/useFeedback.ts; Dev/Dev Code/iFare_Backend/src/views/PageManagement/PageManagement_AddEditView.vue; Dev/Dev Code/iFare_Frontend/server/utils/cors.ts; Dev/Dev Code/iFare_Frontend/server/api/dynamic-pages.get.ts; Dev/Dev Code/iFare_Frontend/server/api/dynamic-pages.put.ts; Dev/Dev Code/iFare_Frontend/server/api/dynamic-pages.options.ts; Dev/Dev Code/iFare_Frontend/composables/useDynamicPages.ts; Dev/Dev Code/iFare_Frontend/pages/[slug].vue; docs/iFare_PageBuilder_前端顯示PoC_2026-05-18.md</v>
       </c>
       <c r="M69" s="2" t="str">
-        <v>PoC 階段跨應用同步用「後台複製 JSON → 前端 devtools 貼 localStorage」代替後端 API；後續 SSR/SEO/排程 worker/slug 衝突 待後端 API 接好再做</v>
+        <v>v2 完整端到端：跨應用同步 ⚠️→✅、SSR/SEO ❌→✅、404 真正回傳 ❌→✅；後台 writeAll 是所有 mutation 唯一 persist 入口，改一處 cover insert/update/remove/importJson</v>
       </c>
       <c r="N69" s="2" t="str">
-        <v>部分修正</v>
+        <v>已修正</v>
       </c>
       <c r="O69" s="2" t="str">
         <v>2026-05-18</v>
       </c>
       <c r="P69" s="2" t="str">
-        <v>走通渲染鏈路；尚需 .NET API 把 localStorage 換成真同步，發布排程 worker、SSR、404 真正回傳 都列在 PoC 文件後續工程化</v>
+        <v>dev only — prod 上線要把 Nuxt server JSON 中介層換成 .NET API（已在 frontendSync 預留 VITE_FRONTEND_SYNC_URL env var）；發布排程 worker、slug 衝突、多人協作互蓋仍未做</v>
       </c>
     </row>
     <row r="70" ht="14.4" customHeight="1">

--- a/docs/iFare_UI_UX_問題追蹤清單.xlsx
+++ b/docs/iFare_UI_UX_問題追蹤清單.xlsx
@@ -4632,44 +4632,44 @@
       </c>
     </row>
     <row r="69" ht="14.4" customHeight="1">
-      <c r="A69" s="2">
+      <c r="A69" s="3">
         <v>66</v>
       </c>
-      <c r="B69" s="2" t="str">
-        <v>V</v>
-      </c>
-      <c r="C69" s="2" t="str">
+      <c r="B69" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C69" s="3" t="str">
         <v>頁面管理</v>
       </c>
-      <c r="D69" s="2" t="str">
+      <c r="D69" s="3" t="str">
         <v>PageBuilder 前端顯示</v>
       </c>
-      <c r="E69" s="2" t="str">
+      <c r="E69" s="3" t="str">
         <v>新增</v>
       </c>
-      <c r="F69" s="2" t="str">
+      <c r="F69" s="3" t="str">
         <v>架構</v>
       </c>
-      <c r="G69" s="2" t="str">
+      <c r="G69" s="3" t="str">
         <v>中</v>
       </c>
-      <c r="H69" s="2" t="str">
+      <c r="H69" s="3" t="str">
         <v>PageBuilder 新增 page 完無法在前端顯示 — 前端動態路由 + 自動同步 (v2 完成)</v>
       </c>
-      <c r="I69" s="2" t="str">
+      <c r="I69" s="3" t="str">
         <v>v1 跨應用 localStorage 不共享，PoC 用手動貼 JSON 走通渲染鏈路；v2 用 Nuxt server route 當中介層自動同步，後台儲存→fire-and-forget PUT→前端 useAsyncData 讀，達成「後台按下儲存→前端重整看得到」端到端體驗</v>
       </c>
-      <c r="J69" s="2" t="str">
+      <c r="J69" s="3" t="str">
         <v>後台新建 utils/frontendSync.ts (fetch PUT 整批) + writeAll() dual write；後台 useFeedback 新增 successWithLink + AddEditView toast 加「前往前端預覽」連結；前端新建 server/utils/cors.ts + 3 個 server/api/dynamic-pages.{get,put,options}.ts 寫進 server/data/dynamic-pages.json；前端 composables/useDynamicPages.ts 改 async ($fetch) + pages/[slug].vue 改 useAsyncData + throw createError(404) 升級 SSR</v>
       </c>
-      <c r="K69" s="2" t="str">
+      <c r="K69" s="3" t="str">
         <v>iFare_Backend/src/utils/frontendSync.ts (新建); iFare_Backend/src/composables/useDynamicPages.ts (writeAll 改); iFare_Backend/src/composables/useFeedback.ts (加 successWithLink); iFare_Backend/src/views/PageManagement/PageManagement_AddEditView.vue (toast 升級); iFare_Frontend/server/utils/cors.ts (新建); iFare_Frontend/server/api/dynamic-pages.{get,put,options}.ts (新建); iFare_Frontend/server/data/.gitignore (新建); iFare_Frontend/composables/useDynamicPages.ts (改寫); iFare_Frontend/pages/[slug].vue (改 SSR)</v>
       </c>
-      <c r="L69" s="2" t="str">
+      <c r="L69" s="3" t="str">
         <v>Dev/Dev Code/iFare_Backend/src/utils/frontendSync.ts; Dev/Dev Code/iFare_Backend/src/composables/useDynamicPages.ts:180-186; Dev/Dev Code/iFare_Backend/src/composables/useFeedback.ts; Dev/Dev Code/iFare_Backend/src/views/PageManagement/PageManagement_AddEditView.vue; Dev/Dev Code/iFare_Frontend/server/utils/cors.ts; Dev/Dev Code/iFare_Frontend/server/api/dynamic-pages.get.ts; Dev/Dev Code/iFare_Frontend/server/api/dynamic-pages.put.ts; Dev/Dev Code/iFare_Frontend/server/api/dynamic-pages.options.ts; Dev/Dev Code/iFare_Frontend/composables/useDynamicPages.ts; Dev/Dev Code/iFare_Frontend/pages/[slug].vue; docs/iFare_PageBuilder_前端顯示PoC_2026-05-18.md</v>
       </c>
       <c r="M69" s="2" t="str">
-        <v>v2 完整端到端：跨應用同步 ⚠️→✅、SSR/SEO ❌→✅、404 真正回傳 ❌→✅；後台 writeAll 是所有 mutation 唯一 persist 入口，改一處 cover insert/update/remove/importJson</v>
+        <v>v2 完整端到端：跨應用同步 ⚠️→✅、SSR/SEO ❌→✅、404 真正回傳 ❌→✅；Day2-fix 把 createDefaultPage 預設 status 從 draft 改成 published，符合「按下新增就到前端」體驗；後台 writeAll 是所有 mutation 唯一 persist 入口，改一處 cover insert/update/remove/importJson</v>
       </c>
       <c r="N69" s="2" t="str">
         <v>已修正</v>
@@ -4678,7 +4678,7 @@
         <v>2026-05-18</v>
       </c>
       <c r="P69" s="2" t="str">
-        <v>dev only — prod 上線要把 Nuxt server JSON 中介層換成 .NET API（已在 frontendSync 預留 VITE_FRONTEND_SYNC_URL env var）；發布排程 worker、slug 衝突、多人協作互蓋仍未做</v>
+        <v>dev only — prod 上線要把 Nuxt server JSON 中介層換成 .NET API（已在 frontendSync 預留 VITE_FRONTEND_SYNC_URL env var）；Day2-fix toast 偵測 status=draft 改顯示 warning 提示前端不顯示；發布排程 worker、slug 衝突、多人協作互蓋、預設改回 draft + 審核工作流 仍未做</v>
       </c>
     </row>
     <row r="70" ht="14.4" customHeight="1">

--- a/docs/iFare_UI_UX_問題追蹤清單.xlsx
+++ b/docs/iFare_UI_UX_問題追蹤清單.xlsx
@@ -979,8 +979,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q85"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:Q89"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="6"/>
     <col min="2" max="2" customWidth="1" width="6"/>
@@ -2122,16 +2122,16 @@
 src/views/*/DataListView.vue</v>
       </c>
       <c r="M22" s="3" t="str">
-        <v>CardSearchParam.vue +147 行（commit 93d1186）涉及搜尋條件清除等改動。</v>
+        <v>2026-05-19：補齊 CardSearchParam 清除流程；「清除全部 / 清除條件」會一次重置日期、單選、下拉、文字欄位並清空 URL query。另補 upload 與 imgManagerType query 讀寫，圖片管理重整後可保留/清除搜尋條件。backend type-check 通過。</v>
       </c>
       <c r="N22" s="3" t="str">
-        <v>部分修正</v>
+        <v>已修正</v>
       </c>
       <c r="O22" s="3" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-19</v>
       </c>
       <c r="P22" s="3" t="str">
-        <v>部分修正 — Codex 第六輪涉及，完成度待 review。</v>
+        <v>完成本輪 review：移除日期 console.log，補 reset icon / aria-label；ImgManager 初始載入會讀取 upload/imgManagerType/word query。</v>
       </c>
       <c r="Q22" s="3" t="str">
         <v>做得快</v>
@@ -2176,16 +2176,16 @@
 src/components/CardTable.vue (L250-336)</v>
       </c>
       <c r="M23" s="3" t="str">
-        <v>誤刪風險高，尤其列表多項同時編輯時</v>
+        <v>2026-05-19：CardTable 新增 openDeleteConfirm/getDeleteTargetLabel，刪除前會依序顯示 title、question、user_name、name、account、email 或編號；DialogAlert 改為清楚標題與可換行訊息。backend type-check 通過。</v>
       </c>
       <c r="N23" s="3" t="str">
-        <v>待處理</v>
+        <v>已修正</v>
       </c>
       <c r="O23" s="3" t="str">
-        <v/>
+        <v>2026-05-19</v>
       </c>
       <c r="P23" s="3" t="str">
-        <v/>
+        <v>覆蓋 News、Articles、IFare Policy/QA、Collaborator、ImgManager 共用刪除流程；彈窗文案改為「確定要刪除『名稱』嗎？刪除後無法復原。」</v>
       </c>
       <c r="Q23" s="3" t="str">
         <v>不容易錯</v>
@@ -2391,16 +2391,16 @@
         <v>src/components/CardTable.vue (L4-9)</v>
       </c>
       <c r="M27" s="3" t="str">
-        <v>改善搜尋體驗，減少困惑</v>
+        <v>2026-05-19：確認 CardTable 已有表格 empty slot，無資料時顯示「目前沒有符合條件的資料」與可調整搜尋/新增內容提示。backend type-check/build 通過。</v>
       </c>
       <c r="N27" s="3" t="str">
-        <v>待處理</v>
+        <v>已修正</v>
       </c>
       <c r="O27" s="3" t="str">
-        <v/>
+        <v>2026-05-19</v>
       </c>
       <c r="P27" s="3" t="str">
-        <v/>
+        <v>本項為補登既有完成狀態；空狀態已套用 CardTable 共用列表。</v>
       </c>
       <c r="Q27" s="3" t="str">
         <v>看得懂</v>
@@ -2444,16 +2444,16 @@
         <v>src/components/CompDateRangePicker.vue</v>
       </c>
       <c r="M28" s="3" t="str">
-        <v>CardSearchParam.vue +147 行涉及日期選擇 / 快捷選項。</v>
+        <v>2026-05-19：CompDateRangePicker 加入 Element Plus daterange shortcuts：今天、本週、本月、最近 7 天、最近 30 天；同步設定 format/value-format，讓 URL query 與 API 搜尋維持 MM/DD/YYYY。backend type-check 通過。</v>
       </c>
       <c r="N28" s="3" t="str">
-        <v>部分修正</v>
+        <v>已修正</v>
       </c>
       <c r="O28" s="3" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-19</v>
       </c>
       <c r="P28" s="3" t="str">
-        <v>部分修正 — Codex 第六輪涉及，完成度待 review。</v>
+        <v>日期快捷已套用所有共用搜尋日期欄位。</v>
       </c>
       <c r="Q28" s="3" t="str">
         <v>做得快</v>
@@ -2551,16 +2551,16 @@
         <v>src/components/CardTable.vue (L178-185)</v>
       </c>
       <c r="M30" s="3" t="str">
-        <v>影響大資料量列表操作</v>
+        <v>2026-05-19：CardTable pageSize watcher 改為切換每頁筆數時先回到第 1 頁，再 clamp 頁碼，避免留在不存在頁數造成空列表。backend type-check/build 通過。</v>
       </c>
       <c r="N30" s="3" t="str">
-        <v>待處理</v>
+        <v>已修正</v>
       </c>
       <c r="O30" s="3" t="str">
-        <v/>
+        <v>2026-05-19</v>
       </c>
       <c r="P30" s="3" t="str">
-        <v/>
+        <v>低風險共用元件修正，覆蓋所有使用 CardTable 的列表。</v>
       </c>
       <c r="Q30" s="3" t="str">
         <v>做得快</v>
@@ -2978,16 +2978,16 @@
         <v>src/views/LoginView.vue (L26-32)</v>
       </c>
       <c r="M38" s="3" t="str">
-        <v>改善登入體驗，減少忘記密碼查詢</v>
+        <v>2026-05-19：LoginView 密碼欄位監聽 CapsLock 狀態，開啟時於欄位下方顯示提示；blur 後隱藏。backend type-check/build 通過。</v>
       </c>
       <c r="N38" s="3" t="str">
-        <v>待處理</v>
+        <v>已修正</v>
       </c>
       <c r="O38" s="3" t="str">
-        <v/>
+        <v>2026-05-19</v>
       </c>
       <c r="P38" s="3" t="str">
-        <v/>
+        <v>不改登入流程，只補輸入輔助提示。</v>
       </c>
       <c r="Q38" s="3" t="str">
         <v>不容易錯</v>
@@ -3085,16 +3085,16 @@
         <v>src/views/NoPermission.vue</v>
       </c>
       <c r="M40" s="3" t="str">
-        <v>提升錯誤頁面的可用性，但使用頻率低</v>
+        <v>2026-05-19：NoPermission 頁改為 403 空狀態，加入說明文案、返回上一頁與回首頁按鈕，並補手機版按鈕堆疊。backend type-check/build 通過。</v>
       </c>
       <c r="N40" s="3" t="str">
-        <v>待處理</v>
+        <v>已修正</v>
       </c>
       <c r="O40" s="3" t="str">
-        <v/>
+        <v>2026-05-19</v>
       </c>
       <c r="P40" s="3" t="str">
-        <v/>
+        <v>不改權限邏輯，只改善無權限落地頁。</v>
       </c>
       <c r="Q40" s="3" t="str">
         <v>看得懂</v>
@@ -4919,16 +4919,16 @@
         <v>Dev/Dev Code/iFare_Backend/src/views/Analysis/Analysis_DashboardView.vue (analytics-grid / filter-bar / hero-status-grid 段 + style scoped)</v>
       </c>
       <c r="M74" s="3" t="str">
-        <v>可借用 #63 (PageManagement 編輯頁 RWD) 已驗證的斷點與技巧；本次只動 CSS，不動 chart 設定</v>
+        <v>2026-05-19：Analysis_DashboardView 只調整 CSS/RWD。補 grid 子項 min-width:0、ApexCharts 容器 max-width、filter bar 響應式堆疊、1024px 圖表改單欄、768/640/520px 細化手機斷點。backend type-check / build 通過。</v>
       </c>
       <c r="N74" s="3" t="str">
-        <v>待處理</v>
+        <v>已修正</v>
       </c>
       <c r="O74" s="3" t="str">
-        <v/>
+        <v>2026-05-19</v>
       </c>
       <c r="P74" s="3" t="str">
-        <v>apexcharts 對寬度變化是 reactive 的，CSS 改動後 chart 會自動 redraw 不需手動觸發</v>
+        <v>延續 PageManagement RWD 手法；不動 chart 設定與資料邏輯。</v>
       </c>
     </row>
     <row r="75" ht="14.4" customHeight="1">
@@ -5489,6 +5489,223 @@
       </c>
       <c r="P85" s="3" t="str">
         <v>建議與版本 diff / snapshot 一起規劃。</v>
+      </c>
+    </row>
+    <row r="86" ht="14.4" customHeight="1">
+      <c r="A86" s="3">
+        <v>83</v>
+      </c>
+      <c r="B86" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C86" s="3" t="str">
+        <v>頁面管理</v>
+      </c>
+      <c r="D86" s="3" t="str">
+        <v>前台預覽</v>
+      </c>
+      <c r="E86" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F86" s="3" t="str">
+        <v>RWD</v>
+      </c>
+      <c r="G86" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H86" s="3" t="str">
+        <v>前台預覽裝置切換未依所選版面呈現</v>
+      </c>
+      <c r="I86" s="3" t="str">
+        <v>新增/編輯頁的 PreviewPane template 使用 device-desktop/tablet/mobile class，但 CSS 寫成 .tablet/.mobile，導致選平板或手機時仍以桌機尺寸顯示。</v>
+      </c>
+      <c r="J86" s="3" t="str">
+        <v>統一 device class 命名，補桌機、平板、手機預覽寬度限制，讓預覽跟選取版面同步。</v>
+      </c>
+      <c r="K86" s="3" t="str">
+        <v>src/components/PageBuilder/PreviewPane.vue</v>
+      </c>
+      <c r="L86" s="3" t="str">
+        <v>Dev/Dev Code/iFare_Backend/src/components/PageBuilder/PreviewPane.vue</v>
+      </c>
+      <c r="M86" s="3" t="str">
+        <v>2026-05-19 驗證：backend type-check / build 通過；桌機 max 1280、平板 840、手機 390。</v>
+      </c>
+      <c r="N86" s="3" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O86" s="3" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="P86" s="3" t="str">
+        <v>修正 .device-tablet / .device-mobile CSS selector mismatch。</v>
+      </c>
+      <c r="Q86" s="3" t="str">
+        <v>不容易錯</v>
+      </c>
+    </row>
+    <row r="87" ht="14.4" customHeight="1">
+      <c r="A87" s="3">
+        <v>84</v>
+      </c>
+      <c r="B87" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C87" s="3" t="str">
+        <v>頁面管理</v>
+      </c>
+      <c r="D87" s="3" t="str">
+        <v>圖片欄位 / 本機圖片</v>
+      </c>
+      <c r="E87" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F87" s="3" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G87" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H87" s="3" t="str">
+        <v>圖文並列圖片路徑貼入後無法顯示</v>
+      </c>
+      <c r="I87" s="3" t="str">
+        <v>使用者貼入 C:\Users\... 本機路徑時，前台瀏覽器無法讀取本機檔案；只會顯示「圖片路徑無法載入」或破圖。</v>
+      </c>
+      <c r="J87" s="3" t="str">
+        <v>新增「選擇本機圖片」上傳流程，透過 Nuxt server API 存到 dynamic-assets，圖片欄位改存 http URL；同時補上本機路徑警示。</v>
+      </c>
+      <c r="K87" s="3" t="str">
+        <v>SectionEditor.vue / dynamic-assets API / DynamicPage image resolver</v>
+      </c>
+      <c r="L87" s="3" t="str">
+        <v>Dev/Dev Code/iFare_Backend/src/components/PageBuilder/SectionEditor.vue
+Dev/Dev Code/iFare_Frontend/server/api/dynamic-assets*.ts
+Dev/Dev Code/iFare_Frontend/utils/dynamicImage.ts
+Dev/Dev Code/iFare_Frontend/components/DynamicPage/SectionImageText.vue</v>
+      </c>
+      <c r="M87" s="3" t="str">
+        <v>支援 gif/png/jpg/jpeg/webp/svg/avif，8MB 限制；上傳成功會自動填圖片 URL 和 alt。</v>
+      </c>
+      <c r="N87" s="3" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O87" s="3" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="P87" s="3" t="str">
+        <v>新增 /api/dynamic-assets POST/GET/OPTIONS，server/data/dynamic-assets 已列入 .gitignore。</v>
+      </c>
+      <c r="Q87" s="3" t="str">
+        <v>不容易錯</v>
+      </c>
+    </row>
+    <row r="88" ht="14.4" customHeight="1">
+      <c r="A88" s="3">
+        <v>85</v>
+      </c>
+      <c r="B88" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C88" s="3" t="str">
+        <v>頁面管理</v>
+      </c>
+      <c r="D88" s="3" t="str">
+        <v>儲存流程</v>
+      </c>
+      <c r="E88" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F88" s="3" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G88" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H88" s="3" t="str">
+        <v>更新圖片後儲存按鈕一直 loading</v>
+      </c>
+      <c r="I88" s="3" t="str">
+        <v>圖片若被舊流程存成 data:image base64，localStorage 容量可能超過配額；原儲存流程沒有完整 try/catch，saving 狀態無法恢復。</v>
+      </c>
+      <c r="J88" s="3" t="str">
+        <v>儲存前阻擋嵌入式 base64 圖片並提示改用上傳；insert/update 加 try/catch 與 afterSave，錯誤訊息可落地。</v>
+      </c>
+      <c r="K88" s="3" t="str">
+        <v>PageManagement_AddEditView.vue</v>
+      </c>
+      <c r="L88" s="3" t="str">
+        <v>Dev/Dev Code/iFare_Backend/src/views/PageManagement/PageManagement_AddEditView.vue</v>
+      </c>
+      <c r="M88" s="3" t="str">
+        <v>backend type-check 通過；QuotaExceeded / storage / page not found 會顯示對應錯誤，避免無限轉圈。</v>
+      </c>
+      <c r="N88" s="3" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O88" s="3" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="P88" s="3" t="str">
+        <v>舊 data URL 頁面需重新用「選擇本機圖片」上傳一次。</v>
+      </c>
+      <c r="Q88" s="3" t="str">
+        <v>出事能追回來</v>
+      </c>
+    </row>
+    <row r="89" ht="14.4" customHeight="1">
+      <c r="A89" s="3">
+        <v>86</v>
+      </c>
+      <c r="B89" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C89" s="3" t="str">
+        <v>前台動態頁</v>
+      </c>
+      <c r="D89" s="3" t="str">
+        <v>圖片載入</v>
+      </c>
+      <c r="E89" s="3" t="str">
+        <v>修復</v>
+      </c>
+      <c r="F89" s="3" t="str">
+        <v>資料同步</v>
+      </c>
+      <c r="G89" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H89" s="3" t="str">
+        <v>前端動態頁圖片網址被存成 IPv4:// 導致破圖</v>
+      </c>
+      <c r="I89" s="3" t="str">
+        <v>Nuxt server origin 取 x-forwarded-proto 時可能拿到 IPv4，產生 IPv4://localhost:3000/...；瀏覽器不能載入，前台只顯示破圖 alt。</v>
+      </c>
+      <c r="J89" s="3" t="str">
+        <v>server 端限制 proto 只允許 http/https；前端 image resolver 兼容修正既有 IPv4:// / IPv6:// 壞資料為 http://。</v>
+      </c>
+      <c r="K89" s="3" t="str">
+        <v>server/api/dynamic-assets.post.ts / utils/dynamicImage.ts</v>
+      </c>
+      <c r="L89" s="3" t="str">
+        <v>Dev/Dev Code/iFare_Frontend/server/api/dynamic-assets.post.ts
+Dev/Dev Code/iFare_Frontend/utils/dynamicImage.ts
+Dev/Dev Code/iFare_Frontend/server/data/dynamic-pages.json (local)</v>
+      </c>
+      <c r="M89" s="3" t="str">
+        <v>本機資料已改為 http://localhost:3000/api/dynamic-assets/wave_pro_pro-...gif；frontend build 通過。</v>
+      </c>
+      <c r="N89" s="3" t="str">
+        <v>已修正</v>
+      </c>
+      <c r="O89" s="3" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="P89" s="3" t="str">
+        <v>若 dev server 已啟動很久，需重啟 Nuxt 讓新 server route 生效。</v>
+      </c>
+      <c r="Q89" s="3" t="str">
+        <v>不容易錯</v>
       </c>
     </row>
   </sheetData>
@@ -5503,7 +5720,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:P176"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="5.77734375"/>
@@ -13453,16 +13670,16 @@
 Dev/Dev Code/iFare_Frontend/components/**/*.vue</v>
       </c>
       <c r="M156" s="3" t="str">
-        <v>本次程式碼審查僅能確認 RWD 架構存在，仍需固定 viewport 視覺驗證。</v>
+        <v>2026-05-19：新增 docs/iFare_RWD回歸檢查清單.md，整理桌機、小桌機、平板、手機固定 viewport，以及後台/前台/部署前 smoke test 檢查項目。</v>
       </c>
       <c r="N156" s="3" t="str">
-        <v>待處理</v>
+        <v>已修正</v>
       </c>
       <c r="O156" s="3" t="str">
-        <v/>
+        <v>2026-05-19</v>
       </c>
       <c r="P156" s="3" t="str">
-        <v/>
+        <v>文件型 UIUX 治理項目，先建立可重複執行的回歸檢查基準。</v>
       </c>
     </row>
     <row r="157" ht="14.4" customHeight="1" xml:space="preserve">
@@ -14499,8 +14716,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H94"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:H95"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="14.5546875"/>
     <col min="2" max="2" customWidth="1" width="12.5546875"/>
@@ -14572,19 +14789,19 @@
         <v>174</v>
       </c>
       <c r="C3" s="3">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D3" s="3">
         <v>19</v>
       </c>
       <c r="E3" s="3">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F3" s="3" t="str">
-        <v>70.1%</v>
+        <v>70.7%</v>
       </c>
       <c r="G3" s="3" t="str">
-        <v>2026-05-18：#167-#174 前台福利進階功能皆已完成 MVP，後續可進入後台資料結構與跨裝置同步。</v>
+        <v>2026-05-19：補完成 #154 RWD 固定 viewport 回歸檢查清單，部署前可依清單做 smoke test。</v>
       </c>
       <c r="H3" s="3" t="str">
         <v/>
@@ -14595,22 +14812,22 @@
         <v>後臺優化 (admin)</v>
       </c>
       <c r="B4" s="3">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C4" s="3">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D4" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E4" s="3">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F4" s="3" t="str">
-        <v>4.8%</v>
+        <v>20.7%</v>
       </c>
       <c r="G4" s="3" t="str">
-        <v>2026-05-18：已補入 i-Fare 前台進階功能對應後台支援任務 #73-#82，#80 政策健康檢查完成編輯頁 MVP。</v>
+        <v>2026-05-19：完成 #20/#21/#25/#26/#28/#36/#38/#71，以及 PageManagement / 動態頁圖片修復 #83-#86。</v>
       </c>
       <c r="H4" s="3" t="str">
         <v/>
@@ -16797,6 +17014,32 @@
         <v>future.vue 補強手機版主標換行、空狀態導引卡與上下節奏，讓頁面在未上線時也有清楚下一步</v>
       </c>
       <c r="H94" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95" ht="14.4" customHeight="1">
+      <c r="A95" s="3" t="str">
+        <v>Round 15</v>
+      </c>
+      <c r="B95" s="3" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="C95" s="3">
+        <v>13</v>
+      </c>
+      <c r="D95" s="3">
+        <v>0</v>
+      </c>
+      <c r="E95" s="3" t="str">
+        <v>後臺優化 #20, #21, #25, #26, #28, #36, #38, #71, #83, #84, #85, #86；UIUX #154</v>
+      </c>
+      <c r="F95" s="3" t="str">
+        <v>-</v>
+      </c>
+      <c r="G95" s="3" t="str">
+        <v>PageManagement 預覽與圖片修復；搜尋清除、日期快捷、刪除確認、表格空狀態、分頁重設、登入 Caps Lock、無權限頁、Analysis Dashboard RWD、RWD 回歸清單</v>
+      </c>
+      <c r="H95" s="3" t="str">
         <v/>
       </c>
     </row>

--- a/docs/iFare_UI_UX_問題追蹤清單.xlsx
+++ b/docs/iFare_UI_UX_問題追蹤清單.xlsx
@@ -77,9 +77,15 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
@@ -979,8 +985,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q89"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q102"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="6"/>
     <col min="2" max="2" customWidth="1" width="6"/>
@@ -2013,16 +2019,18 @@
 src/views/Collaborator/Collaborator_AddEditView.vue (L29-76)</v>
       </c>
       <c r="M20" s="3" t="str">
-        <v>2026-05-12 AddEditView.vue 加 errors ref + onSave 失敗時填 inline 紅字 + has-error class 的 el-input 紅框 + label 變紅。</v>
+        <v>Collaborator_AddEditView 與 ArticlesLazy_AddEditView 已新增 inline 必填檢查、紅框錯誤提示與儲存前阻擋；vue-tsc 已通過。</v>
       </c>
       <c r="N20" s="3" t="str">
         <v>部分修正</v>
       </c>
       <c r="O20" s="3" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="P20" s="3" t="str">
-        <v>只針對 title / slug / status 3 個必填欄位，進階設定（SEO / cover / tags / publishTime）尚未套同 pattern，故為部分修正。</v>
+        <v>2026-05-19</v>
+      </c>
+      <c r="P20" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">只針對 title / slug / status 3 個必填欄位，進階設定（SEO / cover / tags / publishTime）尚未套同 pattern，故為部分修正。
+2026-05-19：再套用至 Collaborator / ArticlesLazy - 再套用至 Collaborator_AddEditView 與 ArticlesLazy_AddEditView，補 inline 必填錯誤、欄位提示與儲存前阻擋；其他 AddEditView 尚未全面改為 el-form rules，維持部分修正。
+2026-05-19：新增功能建議補強 - 表單驗證建議由單頁修補升級為共用 helper / composable，統一必填、URL、圖片、儲存 loading 與錯誤提示。</v>
       </c>
       <c r="Q20" s="3" t="str">
         <v>不容易錯</v>
@@ -2068,16 +2076,16 @@
 src/views/IFare/OfficeUnit/IFareOfficeUnit_AddEditView.vue</v>
       </c>
       <c r="M21" s="3" t="str">
-        <v>使用者無法確認操作是否成功，易誤以為沒儲存</v>
+        <v>Collaborator / ArticlesLazy 儲存按鈕已新增 loading / disabled；API 失敗解除 loading 並停留，成功顯示訊息後返回。</v>
       </c>
       <c r="N21" s="3" t="str">
-        <v>待處理</v>
+        <v>部分修正</v>
       </c>
       <c r="O21" s="3" t="str">
-        <v/>
+        <v>2026-05-19</v>
       </c>
       <c r="P21" s="3" t="str">
-        <v/>
+        <v>2026-05-19：Collaborator / ArticlesLazy 儲存回饋 - Collaborator / ArticlesLazy 儲存按鈕新增 loading/disabled，API 失敗會停留並解除 loading，成功顯示訊息後返回；全站 SaveAction 尚未統一，標部分修正。</v>
       </c>
       <c r="Q21" s="3" t="str">
         <v>看得懂</v>
@@ -2230,16 +2238,16 @@
 src/views/IFare/Policy/IFarePolicy_AddEditView.vue (L54-86)</v>
       </c>
       <c r="M24" s="3" t="str">
-        <v>減少使用者困惑，提升表單填寫速度</v>
+        <v>ArticlesLazy 新增頁已以 [] 初始化多選，政策類別載入後預設第一筆，並補 placeholder / hint。</v>
       </c>
       <c r="N24" s="3" t="str">
-        <v>待處理</v>
+        <v>部分修正</v>
       </c>
       <c r="O24" s="3" t="str">
-        <v/>
+        <v>2026-05-19</v>
       </c>
       <c r="P24" s="3" t="str">
-        <v/>
+        <v>2026-05-19：ArticlesLazy 選單預設與 placeholder - ArticlesLazy 新增頁改以 [] 初始化多選、政策類別載入後預設第一筆並補 placeholder/hint；CompItemSelect 與其他頁尚未全域整理。</v>
       </c>
       <c r="Q24" s="3" t="str">
         <v>不容易錯</v>
@@ -2285,16 +2293,16 @@
 src/components/DialogAddEditImg.vue (L27-43)</v>
       </c>
       <c r="M25" s="3" t="str">
-        <v>防止上傳無效檔案導致後端錯誤</v>
+        <v>Collaborator / ArticlesLazy 上傳 on-change 已檢查 JPG/JPEG/PNG 與 500KB，違規檔案會移除並提示。</v>
       </c>
       <c r="N25" s="3" t="str">
-        <v>待處理</v>
+        <v>部分修正</v>
       </c>
       <c r="O25" s="3" t="str">
-        <v/>
+        <v>2026-05-19</v>
       </c>
       <c r="P25" s="3" t="str">
-        <v/>
+        <v>2026-05-19：Collaborator / ArticlesLazy 上傳預檢 - Collaborator / ArticlesLazy on-change 新增 JPG/JPEG/PNG 與 500KB 預檢，違規檔案會移除並提示；DialogAddEditImg 尚未套用。</v>
       </c>
       <c r="Q25" s="3" t="str">
         <v>不容易錯</v>
@@ -2498,16 +2506,17 @@
 src/views/News/News_AddEditView.vue (L37-44)</v>
       </c>
       <c r="M29" s="3" t="str">
-        <v>減少使用者困惑，降低後續編輯次數</v>
+        <v>Collaborator / ArticlesLazy 已補欄位範例、上傳規格、選單提示與說明文字；vue-tsc 已通過。</v>
       </c>
       <c r="N29" s="3" t="str">
         <v>部分修正</v>
       </c>
       <c r="O29" s="3" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="P29" s="3" t="str">
-        <v>2026-05-12：先在 PageManagement_AddEditView 補強欄位說明與範例，包含頁面名稱用途說明、Slug 操作提示、URL 預覽、SEO 描述搜尋結果預覽。屬於單一頁面快改，整體後台尚未全面套用，故標記為部分修正。</v>
+        <v>2026-05-19</v>
+      </c>
+      <c r="P29" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">2026-05-12：先在 PageManagement_AddEditView 補強欄位說明與範例，包含頁面名稱用途說明、Slug 操作提示、URL 預覽、SEO 描述搜尋結果預覽。屬於單一頁面快改，整體後台尚未全面套用，故標記為部分修正。
+2026-05-19：Collaborator / ArticlesLazy 欄位提示 - Collaborator / ArticlesLazy 補欄位範例、上傳規格與選單操作提示；其餘 News/IFarePolicy 待後續。</v>
       </c>
       <c r="Q29" s="3" t="str">
         <v>看得懂</v>
@@ -4308,7 +4317,7 @@
         <v/>
       </c>
       <c r="P62" s="3" t="str">
-        <v/>
+        <v>2026-05-19：新增功能建議補強 - 內容健康檢查中心已被列為部署前後最值得做的新增功能；MVP 可先掃缺 SEO、缺圖、圖片過大、失效連結、動態頁區塊未填。</v>
       </c>
       <c r="Q62" s="3" t="str">
         <v>不容易錯</v>
@@ -4418,7 +4427,7 @@
         <v/>
       </c>
       <c r="P64" s="3" t="str">
-        <v/>
+        <v>2026-05-19：新增功能建議補強 - 媒體資產治理延伸為圖片庫/媒體管理功能：顯示可複製路徑、檔案大小、是否被引用、超大圖警告與過期素材。</v>
       </c>
       <c r="Q64" s="3" t="str">
         <v>做得快</v>
@@ -4668,16 +4677,16 @@
       <c r="L69" s="3" t="str">
         <v>Dev/Dev Code/iFare_Backend/src/utils/frontendSync.ts; Dev/Dev Code/iFare_Backend/src/composables/useDynamicPages.ts:180-186; Dev/Dev Code/iFare_Backend/src/composables/useFeedback.ts; Dev/Dev Code/iFare_Backend/src/views/PageManagement/PageManagement_AddEditView.vue; Dev/Dev Code/iFare_Frontend/server/utils/cors.ts; Dev/Dev Code/iFare_Frontend/server/api/dynamic-pages.get.ts; Dev/Dev Code/iFare_Frontend/server/api/dynamic-pages.put.ts; Dev/Dev Code/iFare_Frontend/server/api/dynamic-pages.options.ts; Dev/Dev Code/iFare_Frontend/composables/useDynamicPages.ts; Dev/Dev Code/iFare_Frontend/pages/[slug].vue; docs/iFare_PageBuilder_前端顯示PoC_2026-05-18.md</v>
       </c>
-      <c r="M69" s="2" t="str">
+      <c r="M69" s="3" t="str">
         <v>v2 完整端到端：跨應用同步 ⚠️→✅、SSR/SEO ❌→✅、404 真正回傳 ❌→✅；Day2-fix 把 createDefaultPage 預設 status 從 draft 改成 published，符合「按下新增就到前端」體驗；後台 writeAll 是所有 mutation 唯一 persist 入口，改一處 cover insert/update/remove/importJson</v>
       </c>
-      <c r="N69" s="2" t="str">
+      <c r="N69" s="3" t="str">
         <v>已修正</v>
       </c>
-      <c r="O69" s="2" t="str">
+      <c r="O69" s="3" t="str">
         <v>2026-05-18</v>
       </c>
-      <c r="P69" s="2" t="str">
+      <c r="P69" s="3" t="str">
         <v>dev only — prod 上線要把 Nuxt server JSON 中介層換成 .NET API（已在 frontendSync 預留 VITE_FRONTEND_SYNC_URL env var）；Day2-fix toast 偵測 status=draft 改顯示 warning 提示前端不顯示；發布排程 worker、slug 衝突、多人協作互蓋、預設改回 draft + 審核工作流 仍未做</v>
       </c>
     </row>
@@ -5544,7 +5553,7 @@
         <v>不容易錯</v>
       </c>
     </row>
-    <row r="87" ht="14.4" customHeight="1">
+    <row r="87" ht="14.4" customHeight="1" xml:space="preserve">
       <c r="A87" s="3">
         <v>84</v>
       </c>
@@ -5578,8 +5587,8 @@
       <c r="K87" s="3" t="str">
         <v>SectionEditor.vue / dynamic-assets API / DynamicPage image resolver</v>
       </c>
-      <c r="L87" s="3" t="str">
-        <v>Dev/Dev Code/iFare_Backend/src/components/PageBuilder/SectionEditor.vue
+      <c r="L87" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dev/Dev Code/iFare_Backend/src/components/PageBuilder/SectionEditor.vue
 Dev/Dev Code/iFare_Frontend/server/api/dynamic-assets*.ts
 Dev/Dev Code/iFare_Frontend/utils/dynamicImage.ts
 Dev/Dev Code/iFare_Frontend/components/DynamicPage/SectionImageText.vue</v>
@@ -5653,7 +5662,7 @@
         <v>出事能追回來</v>
       </c>
     </row>
-    <row r="89" ht="14.4" customHeight="1">
+    <row r="89" ht="14.4" customHeight="1" xml:space="preserve">
       <c r="A89" s="3">
         <v>86</v>
       </c>
@@ -5687,8 +5696,8 @@
       <c r="K89" s="3" t="str">
         <v>server/api/dynamic-assets.post.ts / utils/dynamicImage.ts</v>
       </c>
-      <c r="L89" s="3" t="str">
-        <v>Dev/Dev Code/iFare_Frontend/server/api/dynamic-assets.post.ts
+      <c r="L89" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dev/Dev Code/iFare_Frontend/server/api/dynamic-assets.post.ts
 Dev/Dev Code/iFare_Frontend/utils/dynamicImage.ts
 Dev/Dev Code/iFare_Frontend/server/data/dynamic-pages.json (local)</v>
       </c>
@@ -5706,6 +5715,712 @@
       </c>
       <c r="Q89" s="3" t="str">
         <v>不容易錯</v>
+      </c>
+    </row>
+    <row r="90" xml:space="preserve">
+      <c r="A90" s="3">
+        <v>87</v>
+      </c>
+      <c r="B90" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C90" s="3" t="str">
+        <v>後台通用</v>
+      </c>
+      <c r="D90" s="3" t="str">
+        <v>部署健康檢查</v>
+      </c>
+      <c r="E90" s="3" t="str">
+        <v>新增</v>
+      </c>
+      <c r="F90" s="3" t="str">
+        <v>部署</v>
+      </c>
+      <c r="G90" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H90" s="3" t="str">
+        <v>部署健康檢查頁 — 遠端主機上線後可快速確認環境與服務狀態</v>
+      </c>
+      <c r="I90" s="3" t="str">
+        <v>專案準備上遠端主機，但目前缺少一個集中檢查頁確認 API URL、目前環境、登入狀態、圖片上傳路徑、必要 env 是否缺漏；部署後若設定錯誤，需要靠人工逐頁排查。</v>
+      </c>
+      <c r="J90" s="3" t="str">
+        <v>新增後台 Health Check / Deploy Check 頁：顯示前台 API URL、後台 API URL、目前 mode、必要 env、圖片上傳/讀取路徑、API ping 結果與最後檢查時間；先做 read-only，不牽 DB。</v>
+      </c>
+      <c r="K90" s="3" t="str">
+        <v>Backend admin / env / deploy</v>
+      </c>
+      <c r="L90" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dev/Dev Code/iFare_Backend/src/views/**
+Dev/Dev Code/iFare_Backend/src/router/**
+.env.example / deployment docs</v>
+      </c>
+      <c r="M90" s="3" t="str">
+        <v>新增功能建議，適合部署前先做 MVP。</v>
+      </c>
+      <c r="N90" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O90" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P90" s="3" t="str">
+        <v>2026-05-19：使用流程盤點後新增。此項可降低遠端主機部署後 API/env/圖片路徑設定錯誤的排查成本。</v>
+      </c>
+      <c r="Q90" s="3" t="str">
+        <v>部署與環境治理</v>
+      </c>
+    </row>
+    <row r="91" xml:space="preserve">
+      <c r="A91" s="3">
+        <v>88</v>
+      </c>
+      <c r="B91" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C91" s="3" t="str">
+        <v>後台通用</v>
+      </c>
+      <c r="D91" s="3" t="str">
+        <v>部署驗收</v>
+      </c>
+      <c r="E91" s="3" t="str">
+        <v>新增</v>
+      </c>
+      <c r="F91" s="3" t="str">
+        <v>流程</v>
+      </c>
+      <c r="G91" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H91" s="3" t="str">
+        <v>部署後 Smoke Test 清單頁 — 固定驗收登入、上傳、前台顯示與 API 狀態</v>
+      </c>
+      <c r="I91" s="3" t="str">
+        <v>遠端部署後缺少固定驗收流程，容易只確認首頁能開，漏測後台登入、PageManagement、圖片上傳、前台動態頁、i-Fare 查詢與 chatbot fallback。</v>
+      </c>
+      <c r="J91" s="3" t="str">
+        <v>新增 Smoke Test 清單，可先用文件或後台 read-only checklist；列出必測項目、測試結果、測試時間與備註，作為每次部署後的驗收紀錄。</v>
+      </c>
+      <c r="K91" s="3" t="str">
+        <v>Deployment docs / Backend admin</v>
+      </c>
+      <c r="L91" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">docs/iFare_部署維運與異常處理手冊.md
+Dev/Dev Code/iFare_Backend/src/views/**</v>
+      </c>
+      <c r="M91" s="3" t="str">
+        <v>新增功能建議，部署前可先文件化，後續再做成後台頁。</v>
+      </c>
+      <c r="N91" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O91" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P91" s="3" t="str">
+        <v>2026-05-19：使用流程盤點後新增。建議先列為部署前必做項，降低遠端主機驗收漏項。</v>
+      </c>
+      <c r="Q91" s="3" t="str">
+        <v>部署與環境治理</v>
+      </c>
+    </row>
+    <row r="92" xml:space="preserve">
+      <c r="A92" s="3">
+        <v>89</v>
+      </c>
+      <c r="B92" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C92" s="3" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="D92" s="3" t="str">
+        <v>表單驗證 helper</v>
+      </c>
+      <c r="E92" s="3" t="str">
+        <v>新增</v>
+      </c>
+      <c r="F92" s="3" t="str">
+        <v>程式碼</v>
+      </c>
+      <c r="G92" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H92" s="3" t="str">
+        <v>後台表單共用驗證規格 — 必填、URL、圖片、儲存 loading 與 API 錯誤提示集中管理</v>
+      </c>
+      <c r="I92" s="3" t="str">
+        <v>目前 Collaborator / ArticlesLazy 已先補 inline 驗證與上傳預檢，但各 AddEditView 若持續手刻，規則會分散，後續維護成本高。</v>
+      </c>
+      <c r="J92" s="3" t="str">
+        <v>建立共用 form helper / composable：required、url、image type/size、saving state、API error message formatter；先套高頻新增/編輯頁，再逐步回收重複邏輯。</v>
+      </c>
+      <c r="K92" s="3" t="str">
+        <v>Backend form components / composables</v>
+      </c>
+      <c r="L92" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dev/Dev Code/iFare_Backend/src/composables/**
+Dev/Dev Code/iFare_Backend/src/views/**/*AddEditView.vue
+Dev/Dev Code/iFare_Backend/src/assets/style/_card.scss</v>
+      </c>
+      <c r="M92" s="3" t="str">
+        <v>新增功能建議，承接 #18/#19/#23/#27 的共用化工作。</v>
+      </c>
+      <c r="N92" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O92" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P92" s="3" t="str">
+        <v>2026-05-19：使用流程盤點後新增。今天已在 Collaborator / ArticlesLazy 驗證模式，下一步建議抽共用 helper，避免各頁規則散落。</v>
+      </c>
+      <c r="Q92" s="3" t="str">
+        <v>共用元件與維護性</v>
+      </c>
+    </row>
+    <row r="93" xml:space="preserve">
+      <c r="A93" s="3">
+        <v>90</v>
+      </c>
+      <c r="B93" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C93" s="3" t="str">
+        <v>後台通用</v>
+      </c>
+      <c r="D93" s="3" t="str">
+        <v>維護首頁</v>
+      </c>
+      <c r="E93" s="3" t="str">
+        <v>新增</v>
+      </c>
+      <c r="F93" s="3" t="str">
+        <v>流程</v>
+      </c>
+      <c r="G93" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H93" s="3" t="str">
+        <v>非工程維護首頁 — 用「我要做什麼」取代功能選單搜尋</v>
+      </c>
+      <c r="I93" s="3" t="str">
+        <v>後續維護者沒有程式基礎，若只靠側邊欄模組名稱，容易不知道新增頁面、編輯消息、上傳圖片、預覽前台該從哪裡開始。</v>
+      </c>
+      <c r="J93" s="3" t="str">
+        <v>新增維護首頁，使用任務型入口：我要新增頁面、我要編輯最新消息、我要上傳圖片、我要查看待處理、我要預覽前台；每個入口連到正確功能並附一句白話說明。</v>
+      </c>
+      <c r="K93" s="3" t="str">
+        <v>Backend Dashboard / PageManagement / ImgManager</v>
+      </c>
+      <c r="L93" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dev/Dev Code/iFare_Backend/src/views/HomeView.vue
+Dev/Dev Code/iFare_Backend/src/router/**</v>
+      </c>
+      <c r="M93" s="3" t="str">
+        <v>新增功能規劃，需以非工程使用者操作路徑驗證。</v>
+      </c>
+      <c r="N93" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O93" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P93" s="3" t="str">
+        <v>2026-05-19：因後續維護者無程式基礎，新增「非工程人員網站維護模式」項目。MVP 優先，能降低新接手人員找功能的成本。</v>
+      </c>
+      <c r="Q93" s="3" t="str">
+        <v>非工程人員網站維護模式</v>
+      </c>
+    </row>
+    <row r="94" xml:space="preserve">
+      <c r="A94" s="3">
+        <v>91</v>
+      </c>
+      <c r="B94" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C94" s="3" t="str">
+        <v>頁面管理</v>
+      </c>
+      <c r="D94" s="3" t="str">
+        <v>新增頁面精靈</v>
+      </c>
+      <c r="E94" s="3" t="str">
+        <v>新增</v>
+      </c>
+      <c r="F94" s="3" t="str">
+        <v>互動</v>
+      </c>
+      <c r="G94" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H94" s="3" t="str">
+        <v>新增頁面精靈 — 以步驟式流程完成頁面建立、預覽與發布</v>
+      </c>
+      <c r="I94" s="3" t="str">
+        <v>PageBuilder 若直接給空白編輯器，非工程使用者需要理解版面、區塊、圖片路徑與發布狀態，學習成本高。</v>
+      </c>
+      <c r="J94" s="3" t="str">
+        <v>新增 wizard：選頁面用途 → 選版型 → 填文字 → 上傳/選圖片 → 桌機/手機預覽 → 發布前檢查 → 發布。每步只顯示必要欄位。</v>
+      </c>
+      <c r="K94" s="3" t="str">
+        <v>PageManagement / PageBuilder</v>
+      </c>
+      <c r="L94" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dev/Dev Code/iFare_Backend/src/views/PageManagement/**
+Dev/Dev Code/iFare_Frontend/components/DynamicPage/**</v>
+      </c>
+      <c r="M94" s="3" t="str">
+        <v>新增功能規劃，需驗證使用者不看文件也能建立一頁。</v>
+      </c>
+      <c r="N94" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O94" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P94" s="3" t="str">
+        <v>2026-05-19：因後續維護者無程式基礎，新增「非工程人員網站維護模式」項目。MVP 優先，應先支援活動頁與服務介紹頁兩種用途。</v>
+      </c>
+      <c r="Q94" s="3" t="str">
+        <v>非工程人員網站維護模式</v>
+      </c>
+    </row>
+    <row r="95" xml:space="preserve">
+      <c r="A95" s="3">
+        <v>92</v>
+      </c>
+      <c r="B95" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C95" s="3" t="str">
+        <v>頁面管理</v>
+      </c>
+      <c r="D95" s="3" t="str">
+        <v>頁面範本庫</v>
+      </c>
+      <c r="E95" s="3" t="str">
+        <v>新增</v>
+      </c>
+      <c r="F95" s="3" t="str">
+        <v>效率</v>
+      </c>
+      <c r="G95" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H95" s="3" t="str">
+        <v>頁面範本庫 — 活動報名、服務介紹、公告、圖文、CTA 頁可直接套用</v>
+      </c>
+      <c r="I95" s="3" t="str">
+        <v>非工程使用者若每次從空白頁開始，容易排版不一致，也會重複思考同類頁面該放哪些區塊。</v>
+      </c>
+      <c r="J95" s="3" t="str">
+        <v>建立可選範本：活動報名頁、服務介紹頁、最新公告頁、圖文介紹頁、CTA 行動頁；套用後只需換文字、圖片與按鈕連結。</v>
+      </c>
+      <c r="K95" s="3" t="str">
+        <v>PageManagement templates</v>
+      </c>
+      <c r="L95" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dev/Dev Code/iFare_Backend/src/views/PageManagement/**
+Dev/Dev Code/iFare_Frontend/types/dynamic-page.ts</v>
+      </c>
+      <c r="M95" s="3" t="str">
+        <v>新增功能規劃，需確認範本套用後可正常預覽與儲存。</v>
+      </c>
+      <c r="N95" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O95" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P95" s="3" t="str">
+        <v>2026-05-19：因後續維護者無程式基礎，新增「非工程人員網站維護模式」項目。MVP 優先，可先用前端常數範本，後續再改為後台可管理。</v>
+      </c>
+      <c r="Q95" s="3" t="str">
+        <v>非工程人員網站維護模式</v>
+      </c>
+    </row>
+    <row r="96" xml:space="preserve">
+      <c r="A96" s="3">
+        <v>93</v>
+      </c>
+      <c r="B96" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C96" s="3" t="str">
+        <v>內容管理</v>
+      </c>
+      <c r="D96" s="3" t="str">
+        <v>一鍵複製</v>
+      </c>
+      <c r="E96" s="3" t="str">
+        <v>新增</v>
+      </c>
+      <c r="F96" s="3" t="str">
+        <v>效率</v>
+      </c>
+      <c r="G96" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H96" s="3" t="str">
+        <v>一鍵複製頁面 / 文章 — 從既有內容複製後改標題與內文</v>
+      </c>
+      <c r="I96" s="3" t="str">
+        <v>維護者常會建立相似活動頁、公告或圖文頁，若每次重建，效率低且容易漏欄位。</v>
+      </c>
+      <c r="J96" s="3" t="str">
+        <v>在文章與 PageManagement 列表新增「複製」動作，複製後自動標記為草稿/未上架，標題加「複本」，slug/網址需重新確認，避免覆蓋原頁。</v>
+      </c>
+      <c r="K96" s="3" t="str">
+        <v>PageManagement / News / Articles</v>
+      </c>
+      <c r="L96" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dev/Dev Code/iFare_Backend/src/views/PageManagement/**
+Dev/Dev Code/iFare_Backend/src/views/News/**
+Dev/Dev Code/iFare_Backend/src/views/Articles/**</v>
+      </c>
+      <c r="M96" s="3" t="str">
+        <v>新增功能規劃，需驗證複製內容不會共用原 slug 或發布狀態。</v>
+      </c>
+      <c r="N96" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O96" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P96" s="3" t="str">
+        <v>2026-05-19：因後續維護者無程式基礎，新增「非工程人員網站維護模式」項目。MVP 優先，適合活動頁與公告維護。</v>
+      </c>
+      <c r="Q96" s="3" t="str">
+        <v>非工程人員網站維護模式</v>
+      </c>
+    </row>
+    <row r="97" xml:space="preserve">
+      <c r="A97" s="3">
+        <v>94</v>
+      </c>
+      <c r="B97" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C97" s="3" t="str">
+        <v>內容管理</v>
+      </c>
+      <c r="D97" s="3" t="str">
+        <v>內容完整度</v>
+      </c>
+      <c r="E97" s="3" t="str">
+        <v>新增</v>
+      </c>
+      <c r="F97" s="3" t="str">
+        <v>提示</v>
+      </c>
+      <c r="G97" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H97" s="3" t="str">
+        <v>內容完整度提示 — 編輯時即時顯示缺圖片、缺 SEO、缺 CTA 與未預覽</v>
+      </c>
+      <c r="I97" s="3" t="str">
+        <v>非工程使用者不一定知道哪些欄位會影響前台呈現、SEO 或發布品質，容易儲存後才發現缺圖、缺按鈕或手機版跑版。</v>
+      </c>
+      <c r="J97" s="3" t="str">
+        <v>在編輯頁側欄顯示完成度分數與待補項目：標題、描述、圖片、圖片替代文字、按鈕連結、SEO、上架狀態、手機預覽。</v>
+      </c>
+      <c r="K97" s="3" t="str">
+        <v>PageManagement / News / Articles / SEO fields</v>
+      </c>
+      <c r="L97" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dev/Dev Code/iFare_Backend/src/views/**/*AddEditView.vue
+Dev/Dev Code/iFare_Backend/src/views/PageManagement/**</v>
+      </c>
+      <c r="M97" s="3" t="str">
+        <v>新增功能規劃，需驗證提示項目能在儲存前即時更新。</v>
+      </c>
+      <c r="N97" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O97" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P97" s="3" t="str">
+        <v>2026-05-19：因後續維護者無程式基礎，新增「非工程人員網站維護模式」項目。能把內容健康檢查從事後掃描提前到編輯當下。</v>
+      </c>
+      <c r="Q97" s="3" t="str">
+        <v>非工程人員網站維護模式</v>
+      </c>
+    </row>
+    <row r="98" xml:space="preserve">
+      <c r="A98" s="3">
+        <v>95</v>
+      </c>
+      <c r="B98" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C98" s="3" t="str">
+        <v>圖片管理</v>
+      </c>
+      <c r="D98" s="3" t="str">
+        <v>圖片庫 / 媒體中心</v>
+      </c>
+      <c r="E98" s="3" t="str">
+        <v>新增</v>
+      </c>
+      <c r="F98" s="3" t="str">
+        <v>效率</v>
+      </c>
+      <c r="G98" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H98" s="3" t="str">
+        <v>非工程圖片庫 — 上傳、預覽、複製路徑、套用到頁面一次完成</v>
+      </c>
+      <c r="I98" s="3" t="str">
+        <v>維護者不應手打圖片路徑；目前圖片路徑、預覽與前台載入曾出現問題，若沒有圖片庫，後續仍會反覆踩雷。</v>
+      </c>
+      <c r="J98" s="3" t="str">
+        <v>建立圖片庫：上傳圖片、看預覽、顯示檔案大小/尺寸、複製可用路徑、選取並套用到頁面欄位，超過建議大小時提醒壓縮。</v>
+      </c>
+      <c r="K98" s="3" t="str">
+        <v>ImgManager / PageManagement image fields</v>
+      </c>
+      <c r="L98" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dev/Dev Code/iFare_Backend/src/views/ImgManager/**
+Dev/Dev Code/iFare_Backend/src/views/PageManagement/**
+Dev/Dev Code/iFare_Frontend/server/api/dynamic-assets.post.ts</v>
+      </c>
+      <c r="M98" s="3" t="str">
+        <v>新增功能規劃，需驗證上傳後可直接被前台載入。</v>
+      </c>
+      <c r="N98" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O98" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P98" s="3" t="str">
+        <v>2026-05-19：因後續維護者無程式基礎，新增「非工程人員網站維護模式」項目。MVP 優先，承接媒體資產治理但更偏日常維護操作。</v>
+      </c>
+      <c r="Q98" s="3" t="str">
+        <v>非工程人員網站維護模式</v>
+      </c>
+    </row>
+    <row r="99" xml:space="preserve">
+      <c r="A99" s="3">
+        <v>96</v>
+      </c>
+      <c r="B99" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C99" s="3" t="str">
+        <v>共用元件</v>
+      </c>
+      <c r="D99" s="3" t="str">
+        <v>站內連結選擇器</v>
+      </c>
+      <c r="E99" s="3" t="str">
+        <v>新增</v>
+      </c>
+      <c r="F99" s="3" t="str">
+        <v>防呆</v>
+      </c>
+      <c r="G99" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H99" s="3" t="str">
+        <v>站內連結選擇器 — 按鈕連結改用選頁面，不讓維護者手打網址</v>
+      </c>
+      <c r="I99" s="3" t="str">
+        <v>非工程使用者手打 /xxx 或外部網址時容易打錯，造成前台 CTA 404 或導錯頁。</v>
+      </c>
+      <c r="J99" s="3" t="str">
+        <v>建立 LinkPicker：可選最新消息、動態頁、i-Fare、公益夥伴、外部連結；選站內項目自動帶入 URL，外部連結檢查 https:// 格式。</v>
+      </c>
+      <c r="K99" s="3" t="str">
+        <v>PageManagement CTA / News / Articles links</v>
+      </c>
+      <c r="L99" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dev/Dev Code/iFare_Backend/src/components/**
+Dev/Dev Code/iFare_Backend/src/views/PageManagement/**</v>
+      </c>
+      <c r="M99" s="3" t="str">
+        <v>新增功能規劃，需驗證內部連結能正確導到前台路由。</v>
+      </c>
+      <c r="N99" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O99" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P99" s="3" t="str">
+        <v>2026-05-19：因後續維護者無程式基礎，新增「非工程人員網站維護模式」項目。能大幅降低壞連結與手動輸入錯誤。</v>
+      </c>
+      <c r="Q99" s="3" t="str">
+        <v>非工程人員網站維護模式</v>
+      </c>
+    </row>
+    <row r="100" xml:space="preserve">
+      <c r="A100" s="3">
+        <v>97</v>
+      </c>
+      <c r="B100" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C100" s="3" t="str">
+        <v>發布流程</v>
+      </c>
+      <c r="D100" s="3" t="str">
+        <v>發布前檢查清單</v>
+      </c>
+      <c r="E100" s="3" t="str">
+        <v>新增</v>
+      </c>
+      <c r="F100" s="3" t="str">
+        <v>防呆</v>
+      </c>
+      <c r="G100" s="3" t="str">
+        <v>高</v>
+      </c>
+      <c r="H100" s="3" t="str">
+        <v>發布前檢查清單 — 發布前確認手機預覽、SEO、圖片、連結與上架狀態</v>
+      </c>
+      <c r="I100" s="3" t="str">
+        <v>非工程維護者發布前需要明確 checklist，否則容易忘記手機預覽、SEO、圖片載入、按鈕連結與上架狀態。</v>
+      </c>
+      <c r="J100" s="3" t="str">
+        <v>點擊發布時顯示 checklist modal：已預覽桌機/手機、SEO 已填、圖片正常、CTA 連結可用、上架時間正確；高風險項未通過時提示但可依權限決定是否阻擋。</v>
+      </c>
+      <c r="K100" s="3" t="str">
+        <v>PageManagement / publish flow</v>
+      </c>
+      <c r="L100" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dev/Dev Code/iFare_Backend/src/views/PageManagement/**
+Dev/Dev Code/iFare_Backend/src/components/**</v>
+      </c>
+      <c r="M100" s="3" t="str">
+        <v>新增功能規劃，需驗證發布前可擋下缺圖片/缺連結等常見問題。</v>
+      </c>
+      <c r="N100" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O100" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P100" s="3" t="str">
+        <v>2026-05-19：因後續維護者無程式基礎，新增「非工程人員網站維護模式」項目。MVP 優先，適合部署前後降低發布錯誤。</v>
+      </c>
+      <c r="Q100" s="3" t="str">
+        <v>非工程人員網站維護模式</v>
+      </c>
+    </row>
+    <row r="101" xml:space="preserve">
+      <c r="A101" s="3">
+        <v>98</v>
+      </c>
+      <c r="B101" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C101" s="3" t="str">
+        <v>後台通用</v>
+      </c>
+      <c r="D101" s="3" t="str">
+        <v>欄位白話化</v>
+      </c>
+      <c r="E101" s="3" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F101" s="3" t="str">
+        <v>文案</v>
+      </c>
+      <c r="G101" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H101" s="3" t="str">
+        <v>欄位白話化與範例 — 將 slug、meta、image path 改成維護者看得懂的用語</v>
+      </c>
+      <c r="I101" s="3" t="str">
+        <v>後台若使用工程術語，沒有程式基礎的維護者會不確定欄位用途，容易亂填或跳過。</v>
+      </c>
+      <c r="J101" s="3" t="str">
+        <v>建立欄位命名規範：slug 改「頁面網址」、meta description 改「搜尋結果描述」、image path 改「圖片網址/圖片路徑」；每個欄位補一句用途和範例。</v>
+      </c>
+      <c r="K101" s="3" t="str">
+        <v>Backend forms / PageManagement / SEO fields</v>
+      </c>
+      <c r="L101" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dev/Dev Code/iFare_Backend/src/views/**/*AddEditView.vue
+Dev/Dev Code/iFare_Backend/src/views/PageManagement/**</v>
+      </c>
+      <c r="M101" s="3" t="str">
+        <v>新增功能規劃，需以維護者能否理解欄位用途驗證。</v>
+      </c>
+      <c r="N101" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O101" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P101" s="3" t="str">
+        <v>2026-05-19：因後續維護者無程式基礎，新增「非工程人員網站維護模式」項目。可與表單驗證 helper、欄位提示一起逐頁套用。</v>
+      </c>
+      <c r="Q101" s="3" t="str">
+        <v>非工程人員網站維護模式</v>
+      </c>
+    </row>
+    <row r="102" xml:space="preserve">
+      <c r="A102" s="3">
+        <v>99</v>
+      </c>
+      <c r="B102" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C102" s="3" t="str">
+        <v>後台通用</v>
+      </c>
+      <c r="D102" s="3" t="str">
+        <v>操作提示</v>
+      </c>
+      <c r="E102" s="3" t="str">
+        <v>新增</v>
+      </c>
+      <c r="F102" s="3" t="str">
+        <v>教學</v>
+      </c>
+      <c r="G102" s="3" t="str">
+        <v>中</v>
+      </c>
+      <c r="H102" s="3" t="str">
+        <v>簡易說明與操作提示 — 每個主要頁面只放短句提醒下一步</v>
+      </c>
+      <c r="I102" s="3" t="str">
+        <v>非工程維護者不會想看完整技術文件，若頁面沒有短提示，容易不知道修改後是否要預覽、發布或等待同步。</v>
+      </c>
+      <c r="J102" s="3" t="str">
+        <v>在主要後台頁加入 1-2 句短提示：這頁用來做什麼、修改後下一步是預覽或發布、哪些欄位會影響前台；避免長篇技術說明。</v>
+      </c>
+      <c r="K102" s="3" t="str">
+        <v>Backend views / help text</v>
+      </c>
+      <c r="L102" s="3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dev/Dev Code/iFare_Backend/src/views/**
+Dev/Dev Code/iFare_Backend/src/components/**</v>
+      </c>
+      <c r="M102" s="3" t="str">
+        <v>新增功能規劃，需確認提示不干擾操作且能降低詢問成本。</v>
+      </c>
+      <c r="N102" s="3" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O102" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P102" s="3" t="str">
+        <v>2026-05-19：因後續維護者無程式基礎，新增「非工程人員網站維護模式」項目。適合搭配維護首頁與新增頁面精靈。</v>
+      </c>
+      <c r="Q102" s="3" t="str">
+        <v>非工程人員網站維護模式</v>
       </c>
     </row>
   </sheetData>
@@ -5714,14 +6429,14 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q85"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q102"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P176"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P184"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="5.77734375"/>
     <col min="2" max="2" customWidth="1" width="5.77734375"/>
@@ -13367,16 +14082,16 @@
 Dev/Dev Code/iFare_Frontend/assets/style/**/*.scss</v>
       </c>
       <c r="M150" s="3" t="str">
-        <v>build 輸出與檔案大小排序皆顯示首頁圖片偏大。</v>
+        <v>已產生 Index-Img-0~4.jpg 並切換 _icon.scss 首頁背景引用；dynamicImage eager import 已排除首頁舊 PNG 與 Index-border.png；前台 build 輸出不再列出這批大型 PNG。</v>
       </c>
       <c r="N150" s="3" t="str">
-        <v>待處理</v>
+        <v>已修正</v>
       </c>
       <c r="O150" s="3" t="str">
-        <v/>
+        <v>2026-05-19</v>
       </c>
       <c r="P150" s="3" t="str">
-        <v/>
+        <v>2026-05-19：首頁 Hero 圖片壓縮 - 首頁 Hero 首屏圖片完成 JPG 壓縮與 CSS 切換，並排除 dynamicImage 對首頁舊 PNG / Index-border.png 的 eager 打包；後續可再補 WebP/AVIF 與 preload/lazyload。</v>
       </c>
     </row>
     <row r="151" ht="14.4" customHeight="1">
@@ -14702,6 +15417,430 @@
       </c>
       <c r="P176" s="3" t="str">
         <v>2026-05-18 MVP：新增 useDocumentChecklist，詳情頁把 Evidence 解析成可勾選文件清單。正式版仍需後台結構化文件資料。</v>
+      </c>
+    </row>
+    <row r="177" xml:space="preserve">
+      <c r="A177" s="4">
+        <v>175</v>
+      </c>
+      <c r="B177" s="4" t="str">
+        <v>V</v>
+      </c>
+      <c r="C177" s="4" t="str">
+        <v>前台 Nuxt Server API</v>
+      </c>
+      <c r="D177" s="4" t="str">
+        <v>Dynamic Pages / Assets</v>
+      </c>
+      <c r="E177" s="4" t="str">
+        <v>修正</v>
+      </c>
+      <c r="F177" s="4" t="str">
+        <v>資安</v>
+      </c>
+      <c r="G177" s="4" t="str">
+        <v>高</v>
+      </c>
+      <c r="H177" s="4" t="str">
+        <v>公開 API 可無驗證覆寫頁面資料與上傳檔案</v>
+      </c>
+      <c r="I177" s="4" t="str">
+        <v>dynamic-pages.put 與 dynamic-assets.post 可直接寫入檔案，CORS 允許 *，未看到後端驗證、容量限制或檔案型別安全處理；外部請求可能竄改頁面內容或累積惡意檔案。</v>
+      </c>
+      <c r="J177" s="4" t="str">
+        <v>立即補 server-side 權限驗證或部署密鑰；限制 CORS 來源；production 關閉 PoC 寫入端點；限制檔案大小與 MIME；SVG 改轉檔或消毒後再提供。</v>
+      </c>
+      <c r="K177" s="4" t="str">
+        <v>Nuxt API、Dynamic Pages、Dynamic Assets</v>
+      </c>
+      <c r="L177" s="4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dev/Dev Code/iFare_Frontend/server/api/dynamic-pages.put.ts
+Dev/Dev Code/iFare_Frontend/server/api/dynamic-assets.post.ts
+Dev/Dev Code/iFare_Frontend/server/utils/cors.ts
+Dev/Dev Code/iFare_Frontend/server/api/dynamic-assets/[name].get.ts</v>
+      </c>
+      <c r="M177" s="4" t="str">
+        <v>已讀程式碼：PUT/POST 端點直接 writeFile；CORS 回應 Access-Control-Allow-Origin: *。</v>
+      </c>
+      <c r="N177" s="4" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O177" s="4" t="str">
+        <v/>
+      </c>
+      <c r="P177" s="4" t="str">
+        <v>立即處理；屬內容竄改與檔案上傳風險。</v>
+      </c>
+    </row>
+    <row r="178" xml:space="preserve">
+      <c r="A178" s="4">
+        <v>176</v>
+      </c>
+      <c r="B178" s="4" t="str">
+        <v>V</v>
+      </c>
+      <c r="C178" s="4" t="str">
+        <v>後台 API / 帳號</v>
+      </c>
+      <c r="D178" s="4" t="str">
+        <v>密碼管理</v>
+      </c>
+      <c r="E178" s="4" t="str">
+        <v>修正</v>
+      </c>
+      <c r="F178" s="4" t="str">
+        <v>資安</v>
+      </c>
+      <c r="G178" s="4" t="str">
+        <v>高</v>
+      </c>
+      <c r="H178" s="4" t="str">
+        <v>後台密碼以明文儲存、比對並可回傳到前端</v>
+      </c>
+      <c r="I178" s="4" t="str">
+        <v>SysUser.Password 為字串欄位，登入以 p.Password == pwd 比對；帳號清單與明細 DTO 也帶出 pwd，前端帳號管理頁可讀寫密碼。資料庫或 API 一旦外洩會直接暴露所有後台密碼。</v>
+      </c>
+      <c r="J178" s="4" t="str">
+        <v>導入 PasswordHasher/BCrypt/Argon2；新增密碼雜湊 migration 與強制重設流程；停止回傳 pwd；新增密碼變更專用 API；清除前端密碼欄位與相關 log。</v>
+      </c>
+      <c r="K178" s="4" t="str">
+        <v>後台帳號、登入、密碼欄位</v>
+      </c>
+      <c r="L178" s="4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dev/Dev Code/iFare_WebApi/iFare.WebApi/Models/DBModel/SysUser.cs
+Dev/Dev Code/iFare_WebApi/iFare.WebApi/TaskManager/AuthTaskManager.cs
+Dev/Dev Code/iFare_WebApi/iFare.WebApi/TaskManager/MainTaskManager.cs
+Dev/Dev Code/iFare_WebApi/iFare.WebApi/TaskManager/PersonalTaskManager.cs
+Dev/Dev Code/iFare_WebApi/iFare.WebApi/TaskManager/AccountTaskManager.cs
+Dev/Dev Code/iFare_Admin/src/views/Account/Account_ItemDetailView.vue
+Dev/Dev Code/iFare_Admin/src/views/Account/Account_AddEditView.vue</v>
+      </c>
+      <c r="M178" s="4" t="str">
+        <v>已讀程式碼：登入直接比對明文密碼，帳號 DTO/前端欄位使用 pwd。</v>
+      </c>
+      <c r="N178" s="4" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O178" s="4" t="str">
+        <v/>
+      </c>
+      <c r="P178" s="4" t="str">
+        <v>立即處理；需搭配資料 migration 與使用者重設密碼。</v>
+      </c>
+    </row>
+    <row r="179" xml:space="preserve">
+      <c r="A179" s="4">
+        <v>177</v>
+      </c>
+      <c r="B179" s="4" t="str">
+        <v>V</v>
+      </c>
+      <c r="C179" s="4" t="str">
+        <v>後台 API</v>
+      </c>
+      <c r="D179" s="4" t="str">
+        <v>權限控管</v>
+      </c>
+      <c r="E179" s="4" t="str">
+        <v>修正</v>
+      </c>
+      <c r="F179" s="4" t="str">
+        <v>權限</v>
+      </c>
+      <c r="G179" s="4" t="str">
+        <v>高</v>
+      </c>
+      <c r="H179" s="4" t="str">
+        <v>多數新增/修改/刪除 API 只要求登入，未檢查角色或功能權限</v>
+      </c>
+      <c r="I179" s="4" t="str">
+        <v>JwtAuth policy 僅 RequireAuthenticatedUser，多數 AppService 的 POST/PUT/DELETE 只有 [Authorize]；目前僅 AccountAppService 看到 IsEditorCheckerFilter。任一有效 token 可能呼叫不該使用的管理 API。</v>
+      </c>
+      <c r="J179" s="4" t="str">
+        <v>把 Editor/Admin 權限檢查下沉到 API policy/filter；所有 mutation endpoint 補角色或功能授權；前端選單權限僅作 UI 控制，不可取代 API 授權；補授權測試。</v>
+      </c>
+      <c r="K179" s="4" t="str">
+        <v>後台 API、JWT、角色權限</v>
+      </c>
+      <c r="L179" s="4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dev/Dev Code/iFare_WebApi/iFare.WebApi/Program/AuthConfigurer.cs
+Dev/Dev Code/iFare_WebApi/iFare.WebApi/Controllers/AppService/*.cs
+Dev/Dev Code/iFare_WebApi/iFare.WebApi/Controllers/AppService/AccountAppService.cs</v>
+      </c>
+      <c r="M179" s="4" t="str">
+        <v>已讀程式碼：JwtAuth policy 只檢查登入狀態，多數 AppService mutation 未套角色 filter。</v>
+      </c>
+      <c r="N179" s="4" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O179" s="4" t="str">
+        <v/>
+      </c>
+      <c r="P179" s="4" t="str">
+        <v>立即處理；避免低權限帳號操作管理功能。</v>
+      </c>
+    </row>
+    <row r="180" xml:space="preserve">
+      <c r="A180" s="4">
+        <v>178</v>
+      </c>
+      <c r="B180" s="4" t="str">
+        <v>V</v>
+      </c>
+      <c r="C180" s="4" t="str">
+        <v>後台 API</v>
+      </c>
+      <c r="D180" s="4" t="str">
+        <v>登入 / 停用帳號</v>
+      </c>
+      <c r="E180" s="4" t="str">
+        <v>修正</v>
+      </c>
+      <c r="F180" s="4" t="str">
+        <v>資安</v>
+      </c>
+      <c r="G180" s="4" t="str">
+        <v>高</v>
+      </c>
+      <c r="H180" s="4" t="str">
+        <v>停用帳號仍可先取得 JWT</v>
+      </c>
+      <c r="I180" s="4" t="str">
+        <v>TokenAuthController.Authenticate 只依帳密取得使用者並簽發 token；State 停用檢查出現在後續 LoginCheck 流程。攻擊者可直接呼叫 Authenticate 取得停用帳號的 JWT。</v>
+      </c>
+      <c r="J180" s="4" t="str">
+        <v>在 Authenticate 階段檢查帳號 State/停用狀態；停用或改密碼時撤銷既有 token；JWT claims 加 security stamp 或版本號並於 API 驗證。</v>
+      </c>
+      <c r="K180" s="4" t="str">
+        <v>登入、JWT、帳號停用</v>
+      </c>
+      <c r="L180" s="4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dev/Dev Code/iFare_WebApi/iFare.WebApi/Controllers/TokenAuthController.cs
+Dev/Dev Code/iFare_WebApi/iFare.WebApi/TaskManager/AuthTaskManager.cs
+Dev/Dev Code/iFare_WebApi/iFare.WebApi/TaskManager/MainTaskManager.cs</v>
+      </c>
+      <c r="M180" s="4" t="str">
+        <v>已讀程式碼：Authenticate 呼叫 GetAuthUser 後即產生 token，GetAuthUser 未過濾停用狀態。</v>
+      </c>
+      <c r="N180" s="4" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O180" s="4" t="str">
+        <v/>
+      </c>
+      <c r="P180" s="4" t="str">
+        <v>立即處理；與權限控管問題會互相放大風險。</v>
+      </c>
+    </row>
+    <row r="181" xml:space="preserve">
+      <c r="A181" s="4">
+        <v>179</v>
+      </c>
+      <c r="B181" s="4" t="str">
+        <v>V</v>
+      </c>
+      <c r="C181" s="4" t="str">
+        <v>設定 / 部署</v>
+      </c>
+      <c r="D181" s="4" t="str">
+        <v>JWT Secret</v>
+      </c>
+      <c r="E181" s="4" t="str">
+        <v>修正</v>
+      </c>
+      <c r="F181" s="4" t="str">
+        <v>資安</v>
+      </c>
+      <c r="G181" s="4" t="str">
+        <v>高</v>
+      </c>
+      <c r="H181" s="4" t="str">
+        <v>JWT SecurityKey 寫在版控設定檔與發佈產物</v>
+      </c>
+      <c r="I181" s="4" t="str">
+        <v>appsettings.json 內含固定 SecurityKey，且 Dev/Prd 版本皆在專案內可讀。若 repository 或發佈包外洩，攻擊者可偽造 JWT。</v>
+      </c>
+      <c r="J181" s="4" t="str">
+        <v>改用環境變數、Secret Manager 或部署平台 secret；立即旋轉正式 JWT key；清查歷史外洩範圍；避免把含 secret 的 appsettings 或發佈產物提交進版控。</v>
+      </c>
+      <c r="K181" s="4" t="str">
+        <v>JWT、appsettings、部署設定</v>
+      </c>
+      <c r="L181" s="4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dev/Dev Code/iFare_WebApi/iFare.WebApi/appsettings.json
+Prd/Prd Code/iFare_WebApi/appsettings.json</v>
+      </c>
+      <c r="M181" s="4" t="str">
+        <v>已讀設定檔：JwtBearer.SecurityKey 直接出現在 tracked appsettings.json。</v>
+      </c>
+      <c r="N181" s="4" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O181" s="4" t="str">
+        <v/>
+      </c>
+      <c r="P181" s="4" t="str">
+        <v>立即處理；需同步更新部署環境與 token 失效策略。</v>
+      </c>
+    </row>
+    <row r="182" xml:space="preserve">
+      <c r="A182" s="4">
+        <v>180</v>
+      </c>
+      <c r="B182" s="4" t="str">
+        <v>V</v>
+      </c>
+      <c r="C182" s="4" t="str">
+        <v>後台前端</v>
+      </c>
+      <c r="D182" s="4" t="str">
+        <v>Token / XSS</v>
+      </c>
+      <c r="E182" s="4" t="str">
+        <v>修正</v>
+      </c>
+      <c r="F182" s="4" t="str">
+        <v>資安</v>
+      </c>
+      <c r="G182" s="4" t="str">
+        <v>高</v>
+      </c>
+      <c r="H182" s="4" t="str">
+        <v>後台 token 存 localStorage 且有未消毒 v-html，XSS 後可竊取 token</v>
+      </c>
+      <c r="I182" s="4" t="str">
+        <v>Pinia persist 會把登入資訊保存到瀏覽器儲存區；LoginView 與 WebAPI 有敏感資料/回應 log；多個後台內容頁直接 v-html 顯示 CMS HTML。若內容或第三方腳本被植入 XSS，可讀取 token 並呼叫管理 API。</v>
+      </c>
+      <c r="J182" s="4" t="str">
+        <v>移除 token 與 API response console log；v-html 顯示前使用 DOMPurify 等白名單消毒；限制 TinyMCE 可輸入的危險屬性與 script；評估改短效 token/httpOnly cookie 或至少縮短保存時間。</v>
+      </c>
+      <c r="K182" s="4" t="str">
+        <v>後台登入、localStorage、v-html、TinyMCE</v>
+      </c>
+      <c r="L182" s="4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dev/Dev Code/iFare_Admin/src/stores/user.ts
+Dev/Dev Code/iFare_Admin/src/views/LoginView.vue
+Dev/Dev Code/iFare_Admin/src/plugins/WebAPI.ts
+Dev/Dev Code/iFare_Admin/src/views/**/**/*View.vue</v>
+      </c>
+      <c r="M182" s="4" t="str">
+        <v>已讀程式碼：user store 使用 persist，LoginView 印出 token，WebAPI 印出 response，多處 detail view 直接 v-html。</v>
+      </c>
+      <c r="N182" s="4" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O182" s="4" t="str">
+        <v/>
+      </c>
+      <c r="P182" s="4" t="str">
+        <v>立即處理；與 API 權限不足會形成高風險攻擊鏈。</v>
+      </c>
+    </row>
+    <row r="183" xml:space="preserve">
+      <c r="A183" s="4">
+        <v>181</v>
+      </c>
+      <c r="B183" s="4" t="str">
+        <v>V</v>
+      </c>
+      <c r="C183" s="4" t="str">
+        <v>環境 / API 串接</v>
+      </c>
+      <c r="D183" s="4" t="str">
+        <v>URL 設定</v>
+      </c>
+      <c r="E183" s="4" t="str">
+        <v>修正</v>
+      </c>
+      <c r="F183" s="4" t="str">
+        <v>部署</v>
+      </c>
+      <c r="G183" s="4" t="str">
+        <v>高</v>
+      </c>
+      <c r="H183" s="4" t="str">
+        <v>API 與同步 URL 硬寫，開發可能打正式站、正式同步可能失效</v>
+      </c>
+      <c r="I183" s="4" t="str">
+        <v>後台 AjaxRef 固定指向正式 API URL；前台 PageBuilder 同步與上傳預設 localhost:3000。不同環境 build 時容易誤打正式資料或讓正式同步流程失效。</v>
+      </c>
+      <c r="J183" s="4" t="str">
+        <v>所有 base URL 改由 .env / runtime config / 部署變數注入；建立 dev/stage/prod 設定；build 或 deploy 時檢查必填環境變數，避免 fallback 到正式站或 localhost。</v>
+      </c>
+      <c r="K183" s="4" t="str">
+        <v>API base URL、PageBuilder、部署環境</v>
+      </c>
+      <c r="L183" s="4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dev/Dev Code/iFare_Admin/src/plugins/AjaxRef.ts
+Dev/Dev Code/iFare_Frontend/components/PageBuilder.vue
+Dev/Dev Code/iFare_Frontend/utils/pageBuilderStorage.ts
+Dev/Dev Code/iFare_Frontend/utils/pageBuilderApi.ts</v>
+      </c>
+      <c r="M183" s="4" t="str">
+        <v>已讀程式碼：後台 API_HOST 指向正式站，前台同步/upload API 預設 localhost:3000。</v>
+      </c>
+      <c r="N183" s="4" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O183" s="4" t="str">
+        <v/>
+      </c>
+      <c r="P183" s="4" t="str">
+        <v>立即處理；避免資料誤寫與部署後功能不可用。</v>
+      </c>
+    </row>
+    <row r="184" xml:space="preserve">
+      <c r="A184" s="4">
+        <v>182</v>
+      </c>
+      <c r="B184" s="4" t="str">
+        <v>V</v>
+      </c>
+      <c r="C184" s="4" t="str">
+        <v>工程流程</v>
+      </c>
+      <c r="D184" s="4" t="str">
+        <v>CI / 測試 / Repo</v>
+      </c>
+      <c r="E184" s="4" t="str">
+        <v>提升</v>
+      </c>
+      <c r="F184" s="4" t="str">
+        <v>品質</v>
+      </c>
+      <c r="G184" s="4" t="str">
+        <v>高</v>
+      </c>
+      <c r="H184" s="4" t="str">
+        <v>缺 CI 與測試覆蓋，且 repo 追蹤大量發佈產物</v>
+      </c>
+      <c r="I184" s="4" t="str">
+        <v>專案未看到 CI workflow；Vitest 目前找不到測試；本機也缺 dotnet CLI 導致 C# build 未能驗證；repo 內追蹤大量 Prd/Dev binary、DLL、PDB、EXE 與發佈輸出，會提高審查與部署風險。</v>
+      </c>
+      <c r="J184" s="4" t="str">
+        <v>新增 CI：前後台 npm build/type-check/audit、dotnet build/test；建立最小 API auth/permission/security tests；清理或移出發佈產物，改由 release artifact 或部署流程產生。</v>
+      </c>
+      <c r="K184" s="4" t="str">
+        <v>CI、測試、版控清理</v>
+      </c>
+      <c r="L184" s="4" t="str" xml:space="preserve">
+        <v xml:space="preserve">.github/workflows
+Dev/Dev Code/iFare_Admin
+Dev/Dev Code/iFare_Frontend
+Dev/Dev Code/iFare_WebApi
+Prd/Prd Code</v>
+      </c>
+      <c r="M184" s="4" t="str">
+        <v>已執行盤點：npm build 可過；npm audit 無 high/critical；Vitest 無測試；dotnet 指令不存在，C# build 未驗證。</v>
+      </c>
+      <c r="N184" s="4" t="str">
+        <v>待處理</v>
+      </c>
+      <c r="O184" s="4" t="str">
+        <v/>
+      </c>
+      <c r="P184" s="4" t="str">
+        <v>高優先級流程問題；會降低上述風險修復的可驗證性。</v>
       </c>
     </row>
   </sheetData>
@@ -14710,14 +15849,14 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P176"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P184"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H95"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H101"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="14.5546875"/>
     <col min="2" max="2" customWidth="1" width="12.5546875"/>
@@ -14729,124 +15868,124 @@
     <col min="8" max="8" customWidth="1" width="14.5546875"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.4" customHeight="1">
-      <c r="A1" s="3" t="str">
+    <row r="1">
+      <c r="A1" s="5" t="str">
         <v>【1】整體進度</v>
       </c>
-      <c r="B1" s="3" t="str">
-        <v/>
-      </c>
-      <c r="C1" s="3" t="str">
-        <v/>
-      </c>
-      <c r="D1" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E1" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F1" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G1" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H1" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="2" ht="14.4" customHeight="1">
-      <c r="A2" s="3" t="str">
+      <c r="B1" s="5" t="str">
+        <v/>
+      </c>
+      <c r="C1" s="5" t="str">
+        <v/>
+      </c>
+      <c r="D1" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E1" s="5" t="str">
+        <v/>
+      </c>
+      <c r="F1" s="5" t="str">
+        <v/>
+      </c>
+      <c r="G1" s="5" t="str">
+        <v/>
+      </c>
+      <c r="H1" s="5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="str">
         <v>Sheet 名稱</v>
       </c>
-      <c r="B2" s="3" t="str">
+      <c r="B2" s="6" t="str">
         <v>總計</v>
       </c>
-      <c r="C2" s="3" t="str">
+      <c r="C2" s="6" t="str">
         <v>已修正</v>
       </c>
-      <c r="D2" s="3" t="str">
+      <c r="D2" s="6" t="str">
         <v>部分修正</v>
       </c>
-      <c r="E2" s="3" t="str">
+      <c r="E2" s="6" t="str">
         <v>待處理</v>
       </c>
-      <c r="F2" s="3" t="str">
+      <c r="F2" s="6" t="str">
         <v>完成率</v>
       </c>
-      <c r="G2" s="3" t="str">
+      <c r="G2" s="6" t="str">
         <v>備註</v>
       </c>
-      <c r="H2" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="14.4" customHeight="1">
+      <c r="H2" s="6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="3" t="str">
         <v>UIUX問題追蹤清單 (前台)</v>
       </c>
       <c r="B3" s="3">
         <v>174</v>
       </c>
-      <c r="C3" s="3">
-        <v>123</v>
-      </c>
-      <c r="D3" s="3">
+      <c r="C3" s="7">
+        <v>124</v>
+      </c>
+      <c r="D3" s="8">
         <v>19</v>
       </c>
-      <c r="E3" s="3">
-        <v>32</v>
+      <c r="E3" s="9">
+        <v>31</v>
       </c>
       <c r="F3" s="3" t="str">
-        <v>70.7%</v>
+        <v>71.3%</v>
       </c>
       <c r="G3" s="3" t="str">
-        <v>2026-05-19：補完成 #154 RWD 固定 viewport 回歸檢查清單，部署前可依清單做 smoke test。</v>
+        <v>已歷經 Round 1-4 改版</v>
       </c>
       <c r="H3" s="3" t="str">
         <v/>
       </c>
     </row>
-    <row r="4" ht="14.4" customHeight="1">
+    <row r="4">
       <c r="A4" s="3" t="str">
         <v>後臺優化 (admin)</v>
       </c>
       <c r="B4" s="3">
-        <v>87</v>
-      </c>
-      <c r="C4" s="3">
+        <v>100</v>
+      </c>
+      <c r="C4" s="7">
         <v>18</v>
       </c>
-      <c r="D4" s="3">
-        <v>13</v>
-      </c>
-      <c r="E4" s="3">
-        <v>56</v>
+      <c r="D4" s="8">
+        <v>16</v>
+      </c>
+      <c r="E4" s="9">
+        <v>66</v>
       </c>
       <c r="F4" s="3" t="str">
-        <v>20.7%</v>
+        <v>18.0%</v>
       </c>
       <c r="G4" s="3" t="str">
-        <v>2026-05-19：完成 #20/#21/#25/#26/#28/#36/#38/#71，以及 PageManagement / 動態頁圖片修復 #83-#86。</v>
+        <v>含後台優化規劃與進階功能建議</v>
       </c>
       <c r="H4" s="3" t="str">
         <v/>
       </c>
     </row>
-    <row r="5" ht="14.4" customHeight="1">
+    <row r="5">
       <c r="A5" s="3" t="str">
         <v>PoC研究</v>
       </c>
       <c r="B5" s="3">
         <v>13</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="7">
         <v>0</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="8">
         <v>0</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="9">
         <v>13</v>
       </c>
       <c r="F5" s="3" t="str">
@@ -14859,59 +15998,59 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="14.4" customHeight="1">
-      <c r="A7" s="3" t="str">
+    <row r="7">
+      <c r="A7" s="5" t="str">
         <v>【2】Round 時間軸 — 每輪做了什麼</v>
       </c>
-      <c r="B7" s="3" t="str">
-        <v/>
-      </c>
-      <c r="C7" s="3" t="str">
-        <v/>
-      </c>
-      <c r="D7" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E7" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F7" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G7" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H7" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="14.4" customHeight="1">
-      <c r="A8" s="3" t="str">
+      <c r="B7" s="5" t="str">
+        <v/>
+      </c>
+      <c r="C7" s="5" t="str">
+        <v/>
+      </c>
+      <c r="D7" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E7" s="5" t="str">
+        <v/>
+      </c>
+      <c r="F7" s="5" t="str">
+        <v/>
+      </c>
+      <c r="G7" s="5" t="str">
+        <v/>
+      </c>
+      <c r="H7" s="5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="str">
         <v>Round</v>
       </c>
-      <c r="B8" s="3" t="str">
+      <c r="B8" s="6" t="str">
         <v>日期</v>
       </c>
-      <c r="C8" s="3" t="str">
+      <c r="C8" s="6" t="str">
         <v>主題</v>
       </c>
-      <c r="D8" s="3" t="str">
+      <c r="D8" s="6" t="str">
         <v>UIUX 標完成</v>
       </c>
-      <c r="E8" s="3" t="str">
+      <c r="E8" s="6" t="str">
         <v>UIUX 新增</v>
       </c>
-      <c r="F8" s="3" t="str">
+      <c r="F8" s="6" t="str">
         <v>後臺新增</v>
       </c>
-      <c r="G8" s="3" t="str">
+      <c r="G8" s="6" t="str">
         <v>Schema</v>
       </c>
-      <c r="H8" s="3" t="str">
+      <c r="H8" s="6" t="str">
         <v>主要產出</v>
       </c>
     </row>
-    <row r="9" ht="14.4" customHeight="1">
+    <row r="9">
       <c r="A9" s="3" t="str">
         <v>Round 1</v>
       </c>
@@ -14937,7 +16076,7 @@
         <v>pages/ifare 加關鍵字搜尋 + URL query 初始化；全站 NuxtPage transition；卡片/按鈕 hover translateY</v>
       </c>
     </row>
-    <row r="10" ht="14.4" customHeight="1">
+    <row r="10">
       <c r="A10" s="3" t="str">
         <v>Round 2</v>
       </c>
@@ -14963,7 +16102,7 @@
         <v>LINE/FB 統一 .btn-social 並排；4 個聯絡資訊加 icon (Tel/Mail/Address/Clock)；footer 觸控 44px</v>
       </c>
     </row>
-    <row r="11" ht="14.4" customHeight="1">
+    <row r="11">
       <c r="A11" s="3" t="str">
         <v>Round 3</v>
       </c>
@@ -14989,7 +16128,7 @@
         <v>About 三大核心 morph 卡 (cf47cfa)；News 浮起卡 + stagger fade-up + NEW pill；外連結 target="_blank" rel="noopener"</v>
       </c>
     </row>
-    <row r="12" ht="14.4" customHeight="1">
+    <row r="12">
       <c r="A12" s="3" t="str">
         <v>Round 4</v>
       </c>
@@ -15015,7 +16154,7 @@
         <v>cf47cfa+5dfbf91 補回 16 檔；devProxy/baseURL → 正式 API；nav 加未來規劃 + future.vue；News videoUrl wiring；tsconfig deprecation 清理；about hover bug 修；footer label 重複修</v>
       </c>
     </row>
-    <row r="13" ht="14.4" customHeight="1">
+    <row r="13">
       <c r="A13" s="3" t="str">
         <v>Round 5</v>
       </c>
@@ -15041,7 +16180,7 @@
         <v>後台 22 個工程角度問題 (CRUD/驗證/錯誤處理)；前台 26 個新發現 (XSS/超時/console.log/無障礙/分頁元件重複)</v>
       </c>
     </row>
-    <row r="14" ht="14.4" customHeight="1">
+    <row r="14">
       <c r="A14" s="3" t="str">
         <v>Round 6</v>
       </c>
@@ -15067,7 +16206,7 @@
         <v>Dashboard 角色化 / 今日待辦 / KPI 分區；批次操作；軟刪除復原；audit log；危險操作預覽；錯誤訊息引導</v>
       </c>
     </row>
-    <row r="15" ht="14.4" customHeight="1">
+    <row r="15">
       <c r="A15" s="3" t="str">
         <v>Round 7</v>
       </c>
@@ -15093,7 +16232,7 @@
         <v>補充 GA4 同步快取、任務中心、自動儲存與編輯鎖定、發布排程、審稿指派、內容健康檢查、通知中心、資產治理</v>
       </c>
     </row>
-    <row r="16" ht="14.4" customHeight="1">
+    <row r="16">
       <c r="A16" s="3" t="str">
         <v>Round 8</v>
       </c>
@@ -15119,7 +16258,7 @@
         <v>HomeView 新增搜尋 / 分組 / 最近使用；PageManagement 補上 URL 預覽、狀態說明、SEO 預覽、常用標籤建議、排程快捷鍵</v>
       </c>
     </row>
-    <row r="17" ht="14.4" customHeight="1">
+    <row r="17">
       <c r="A17" s="3" t="str">
         <v>Round 9</v>
       </c>
@@ -15145,59 +16284,59 @@
         <v>future.vue 補強手機版主標換行、空狀態導引卡、上下留白與 footer CTA 銜接</v>
       </c>
     </row>
-    <row r="19" ht="14.4" customHeight="1">
-      <c r="A19" s="3" t="str">
+    <row r="19">
+      <c r="A19" s="5" t="str">
         <v>【3】後臺優化 — 5 主軸分布 (拿這個去提案!)</v>
       </c>
-      <c r="B19" s="3" t="str">
-        <v/>
-      </c>
-      <c r="C19" s="3" t="str">
-        <v/>
-      </c>
-      <c r="D19" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E19" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F19" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G19" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H19" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="14.4" customHeight="1">
-      <c r="A20" s="3" t="str">
+      <c r="B19" s="5" t="str">
+        <v/>
+      </c>
+      <c r="C19" s="5" t="str">
+        <v/>
+      </c>
+      <c r="D19" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E19" s="5" t="str">
+        <v/>
+      </c>
+      <c r="F19" s="5" t="str">
+        <v/>
+      </c>
+      <c r="G19" s="5" t="str">
+        <v/>
+      </c>
+      <c r="H19" s="5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="str">
         <v>主軸</v>
       </c>
-      <c r="B20" s="3" t="str">
+      <c r="B20" s="6" t="str">
         <v>項目數</v>
       </c>
-      <c r="C20" s="3" t="str">
+      <c r="C20" s="6" t="str">
         <v>比例</v>
       </c>
-      <c r="D20" s="3" t="str">
+      <c r="D20" s="6" t="str">
         <v>主要訴求</v>
       </c>
-      <c r="E20" s="3" t="str">
+      <c r="E20" s="6" t="str">
         <v>對應 #</v>
       </c>
-      <c r="F20" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G20" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H20" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="14.4" customHeight="1">
+      <c r="F20" s="6" t="str">
+        <v/>
+      </c>
+      <c r="G20" s="6" t="str">
+        <v/>
+      </c>
+      <c r="H20" s="6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" s="3" t="str">
         <v>看得懂</v>
       </c>
@@ -15205,7 +16344,7 @@
         <v>18</v>
       </c>
       <c r="C21" s="3" t="str">
-        <v>28.6%</v>
+        <v>18.0%</v>
       </c>
       <c r="D21" s="3" t="str">
         <v>首頁先給重點 / KPI / 異常 / 待辦分區 / 欄位白話 / 狀態流程視覺化</v>
@@ -15223,7 +16362,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="14.4" customHeight="1">
+    <row r="22">
       <c r="A22" s="3" t="str">
         <v>找得到</v>
       </c>
@@ -15231,7 +16370,7 @@
         <v>7</v>
       </c>
       <c r="C22" s="3" t="str">
-        <v>11.1%</v>
+        <v>7.0%</v>
       </c>
       <c r="D22" s="3" t="str">
         <v>全域搜尋 / 麵包屑 / 側邊欄高亮 / 變更密碼入口</v>
@@ -15249,7 +16388,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="14.4" customHeight="1">
+    <row r="23">
       <c r="A23" s="3" t="str">
         <v>做得快</v>
       </c>
@@ -15257,7 +16396,7 @@
         <v>11</v>
       </c>
       <c r="C23" s="3" t="str">
-        <v>17.5%</v>
+        <v>11.0%</v>
       </c>
       <c r="D23" s="3" t="str">
         <v>批次操作 / 儲存搜尋 / 大列表 lazy / 匯出進度 / 日期快捷</v>
@@ -15275,15 +16414,15 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="14.4" customHeight="1">
+    <row r="24">
       <c r="A24" s="3" t="str">
         <v>不容易錯</v>
       </c>
       <c r="B24" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C24" s="3" t="str">
-        <v>23.8%</v>
+        <v>18.0%</v>
       </c>
       <c r="D24" s="3" t="str">
         <v>表單驗證 / 刪除確認 / 影響預覽 / 預設值 / 錯誤引導</v>
@@ -15301,15 +16440,15 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="14.4" customHeight="1">
+    <row r="25">
       <c r="A25" s="3" t="str">
         <v>出事能追回來</v>
       </c>
       <c r="B25" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C25" s="3" t="str">
-        <v>11.1%</v>
+        <v>8.0%</v>
       </c>
       <c r="D25" s="3" t="str">
         <v>audit log / 變更歷史 / 軟刪除復原 / token 管理 / 文件交接</v>
@@ -15327,15 +16466,15 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="14.4" customHeight="1">
+    <row r="26">
       <c r="A26" s="3" t="str">
         <v>—</v>
       </c>
       <c r="B26" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C26" s="3" t="str">
-        <v>7.9%</v>
+        <v>25.0%</v>
       </c>
       <c r="D26" s="3" t="str">
         <v>純技術 / 環境設定 (不在 5 主軸範圍)</v>
@@ -15353,76 +16492,76 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="14.4" customHeight="1">
-      <c r="A28" s="3" t="str">
+    <row r="28">
+      <c r="A28" s="5" t="str">
         <v>【4】UIUX — 優先級 × 狀態分布</v>
       </c>
-      <c r="B28" s="3" t="str">
-        <v/>
-      </c>
-      <c r="C28" s="3" t="str">
-        <v/>
-      </c>
-      <c r="D28" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E28" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F28" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G28" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H28" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="14.4" customHeight="1">
-      <c r="A29" s="3" t="str">
+      <c r="B28" s="5" t="str">
+        <v/>
+      </c>
+      <c r="C28" s="5" t="str">
+        <v/>
+      </c>
+      <c r="D28" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E28" s="5" t="str">
+        <v/>
+      </c>
+      <c r="F28" s="5" t="str">
+        <v/>
+      </c>
+      <c r="G28" s="5" t="str">
+        <v/>
+      </c>
+      <c r="H28" s="5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="str">
         <v>優先級</v>
       </c>
-      <c r="B29" s="3" t="str">
+      <c r="B29" s="6" t="str">
         <v>已修正</v>
       </c>
-      <c r="C29" s="3" t="str">
+      <c r="C29" s="6" t="str">
         <v>部分修正</v>
       </c>
-      <c r="D29" s="3" t="str">
+      <c r="D29" s="6" t="str">
         <v>待處理</v>
       </c>
-      <c r="E29" s="3" t="str">
+      <c r="E29" s="6" t="str">
         <v>小計</v>
       </c>
-      <c r="F29" s="3" t="str">
+      <c r="F29" s="6" t="str">
         <v>完成率</v>
       </c>
-      <c r="G29" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H29" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="14.4" customHeight="1">
+      <c r="G29" s="6" t="str">
+        <v/>
+      </c>
+      <c r="H29" s="6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30" s="3" t="str">
         <v>高</v>
       </c>
-      <c r="B30" s="3">
-        <v>22</v>
-      </c>
-      <c r="C30" s="3">
-        <v>6</v>
-      </c>
-      <c r="D30" s="3">
-        <v>4</v>
+      <c r="B30" s="7">
+        <v>23</v>
+      </c>
+      <c r="C30" s="8">
+        <v>10</v>
+      </c>
+      <c r="D30" s="9">
+        <v>3</v>
       </c>
       <c r="E30" s="3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F30" s="3" t="str">
-        <v>78.1%</v>
+        <v>77.8%</v>
       </c>
       <c r="G30" s="3" t="str">
         <v/>
@@ -15431,24 +16570,24 @@
         <v/>
       </c>
     </row>
-    <row r="31" ht="14.4" customHeight="1">
+    <row r="31">
       <c r="A31" s="3" t="str">
         <v>中</v>
       </c>
-      <c r="B31" s="3">
-        <v>59</v>
-      </c>
-      <c r="C31" s="3">
-        <v>1</v>
-      </c>
-      <c r="D31" s="3">
-        <v>18</v>
+      <c r="B31" s="7">
+        <v>61</v>
+      </c>
+      <c r="C31" s="8">
+        <v>5</v>
+      </c>
+      <c r="D31" s="9">
+        <v>17</v>
       </c>
       <c r="E31" s="3">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F31" s="3" t="str">
-        <v>76.3%</v>
+        <v>76.5%</v>
       </c>
       <c r="G31" s="3" t="str">
         <v/>
@@ -15457,17 +16596,17 @@
         <v/>
       </c>
     </row>
-    <row r="32" ht="14.4" customHeight="1">
+    <row r="32">
       <c r="A32" s="3" t="str">
         <v>低</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="7">
         <v>40</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="8">
         <v>4</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="9">
         <v>11</v>
       </c>
       <c r="E32" s="3">
@@ -15483,67 +16622,67 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="14.4" customHeight="1">
-      <c r="A34" s="3" t="str">
+    <row r="34">
+      <c r="A34" s="5" t="str">
         <v>【5】UIUX — 各區塊問題分布</v>
       </c>
-      <c r="B34" s="3" t="str">
-        <v/>
-      </c>
-      <c r="C34" s="3" t="str">
-        <v/>
-      </c>
-      <c r="D34" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E34" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F34" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G34" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H34" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="14.4" customHeight="1">
-      <c r="A35" s="3" t="str">
+      <c r="B34" s="5" t="str">
+        <v/>
+      </c>
+      <c r="C34" s="5" t="str">
+        <v/>
+      </c>
+      <c r="D34" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E34" s="5" t="str">
+        <v/>
+      </c>
+      <c r="F34" s="5" t="str">
+        <v/>
+      </c>
+      <c r="G34" s="5" t="str">
+        <v/>
+      </c>
+      <c r="H34" s="5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="str">
         <v>區塊</v>
       </c>
-      <c r="B35" s="3" t="str">
+      <c r="B35" s="6" t="str">
         <v>項目數</v>
       </c>
-      <c r="C35" s="3" t="str">
+      <c r="C35" s="6" t="str">
         <v>佔比</v>
       </c>
-      <c r="D35" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E35" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F35" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G35" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H35" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="14.4" customHeight="1">
+      <c r="D35" s="6" t="str">
+        <v/>
+      </c>
+      <c r="E35" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F35" s="6" t="str">
+        <v/>
+      </c>
+      <c r="G35" s="6" t="str">
+        <v/>
+      </c>
+      <c r="H35" s="6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36" s="3" t="str">
         <v>全站通用</v>
       </c>
       <c r="B36" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C36" s="3" t="str">
-        <v>25.5%</v>
+        <v>24.7%</v>
       </c>
       <c r="D36" s="3" t="str">
         <v/>
@@ -15561,15 +16700,15 @@
         <v/>
       </c>
     </row>
-    <row r="37" ht="14.4" customHeight="1">
+    <row r="37">
       <c r="A37" s="3" t="str">
         <v>i-Fare 福利查詢</v>
       </c>
       <c r="B37" s="3">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C37" s="3" t="str">
-        <v>15.8%</v>
+        <v>17.2%</v>
       </c>
       <c r="D37" s="3" t="str">
         <v/>
@@ -15587,7 +16726,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="14.4" customHeight="1">
+    <row r="38">
       <c r="A38" s="3" t="str">
         <v>共用元件</v>
       </c>
@@ -15595,7 +16734,7 @@
         <v>25</v>
       </c>
       <c r="C38" s="3" t="str">
-        <v>15.2%</v>
+        <v>14.4%</v>
       </c>
       <c r="D38" s="3" t="str">
         <v/>
@@ -15613,7 +16752,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" ht="14.4" customHeight="1">
+    <row r="39">
       <c r="A39" s="3" t="str">
         <v>福利專欄</v>
       </c>
@@ -15621,7 +16760,7 @@
         <v>11</v>
       </c>
       <c r="C39" s="3" t="str">
-        <v>6.7%</v>
+        <v>6.3%</v>
       </c>
       <c r="D39" s="3" t="str">
         <v/>
@@ -15639,7 +16778,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" ht="14.4" customHeight="1">
+    <row r="40">
       <c r="A40" s="3" t="str">
         <v>首頁</v>
       </c>
@@ -15647,7 +16786,7 @@
         <v>10</v>
       </c>
       <c r="C40" s="3" t="str">
-        <v>6.1%</v>
+        <v>5.7%</v>
       </c>
       <c r="D40" s="3" t="str">
         <v/>
@@ -15665,7 +16804,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" ht="14.4" customHeight="1">
+    <row r="41">
       <c r="A41" s="3" t="str">
         <v>關於長穩</v>
       </c>
@@ -15673,7 +16812,7 @@
         <v>9</v>
       </c>
       <c r="C41" s="3" t="str">
-        <v>5.5%</v>
+        <v>5.2%</v>
       </c>
       <c r="D41" s="3" t="str">
         <v/>
@@ -15691,7 +16830,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="14.4" customHeight="1">
+    <row r="42">
       <c r="A42" s="3" t="str">
         <v>最新消息</v>
       </c>
@@ -15699,7 +16838,7 @@
         <v>8</v>
       </c>
       <c r="C42" s="3" t="str">
-        <v>4.8%</v>
+        <v>4.6%</v>
       </c>
       <c r="D42" s="3" t="str">
         <v/>
@@ -15717,7 +16856,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" ht="14.4" customHeight="1">
+    <row r="43">
       <c r="A43" s="3" t="str">
         <v>公益夥伴</v>
       </c>
@@ -15725,7 +16864,7 @@
         <v>8</v>
       </c>
       <c r="C43" s="3" t="str">
-        <v>4.8%</v>
+        <v>4.6%</v>
       </c>
       <c r="D43" s="3" t="str">
         <v/>
@@ -15743,7 +16882,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" ht="14.4" customHeight="1">
+    <row r="44">
       <c r="A44" s="3" t="str">
         <v>全站微互動</v>
       </c>
@@ -15751,7 +16890,7 @@
         <v>5</v>
       </c>
       <c r="C44" s="3" t="str">
-        <v>3.0%</v>
+        <v>2.9%</v>
       </c>
       <c r="D44" s="3" t="str">
         <v/>
@@ -15769,7 +16908,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" ht="14.4" customHeight="1">
+    <row r="45">
       <c r="A45" s="3" t="str">
         <v>設計系統</v>
       </c>
@@ -15777,7 +16916,7 @@
         <v>5</v>
       </c>
       <c r="C45" s="3" t="str">
-        <v>3.0%</v>
+        <v>2.9%</v>
       </c>
       <c r="D45" s="3" t="str">
         <v/>
@@ -15795,7 +16934,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" ht="14.4" customHeight="1">
+    <row r="46">
       <c r="A46" s="3" t="str">
         <v>未來規劃</v>
       </c>
@@ -15803,7 +16942,7 @@
         <v>3</v>
       </c>
       <c r="C46" s="3" t="str">
-        <v>1.8%</v>
+        <v>1.7%</v>
       </c>
       <c r="D46" s="3" t="str">
         <v/>
@@ -15821,41 +16960,41 @@
         <v/>
       </c>
     </row>
-    <row r="47" ht="14.4" customHeight="1">
+    <row r="47">
       <c r="A47" s="3" t="str">
+        <v>i-Fare 福利詳情</v>
+      </c>
+      <c r="B47" s="3">
+        <v>3</v>
+      </c>
+      <c r="C47" s="3" t="str">
+        <v>1.7%</v>
+      </c>
+      <c r="D47" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E47" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F47" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G47" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H47" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="str">
         <v>安全性</v>
-      </c>
-      <c r="B47" s="3">
-        <v>2</v>
-      </c>
-      <c r="C47" s="3" t="str">
-        <v>1.2%</v>
-      </c>
-      <c r="D47" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E47" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F47" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G47" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H47" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="14.4" customHeight="1">
-      <c r="A48" s="3" t="str">
-        <v>無障礙</v>
       </c>
       <c r="B48" s="3">
         <v>2</v>
       </c>
       <c r="C48" s="3" t="str">
-        <v>1.2%</v>
+        <v>1.1%</v>
       </c>
       <c r="D48" s="3" t="str">
         <v/>
@@ -15873,35 +17012,35 @@
         <v/>
       </c>
     </row>
-    <row r="49" ht="14.4" customHeight="1">
+    <row r="49">
       <c r="A49" s="3" t="str">
+        <v>無障礙</v>
+      </c>
+      <c r="B49" s="3">
+        <v>2</v>
+      </c>
+      <c r="C49" s="3" t="str">
+        <v>1.1%</v>
+      </c>
+      <c r="D49" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E49" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F49" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G49" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H49" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="str">
         <v>頁面導航</v>
-      </c>
-      <c r="B49" s="3">
-        <v>1</v>
-      </c>
-      <c r="C49" s="3" t="str">
-        <v>0.6%</v>
-      </c>
-      <c r="D49" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E49" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F49" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G49" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H49" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="14.4" customHeight="1">
-      <c r="A50" s="3" t="str">
-        <v>i-Fare 搜尋結果</v>
       </c>
       <c r="B50" s="3">
         <v>1</v>
@@ -15925,9 +17064,9 @@
         <v/>
       </c>
     </row>
-    <row r="51" ht="14.4" customHeight="1">
+    <row r="51">
       <c r="A51" s="3" t="str">
-        <v>效能</v>
+        <v>i-Fare 搜尋結果</v>
       </c>
       <c r="B51" s="3">
         <v>1</v>
@@ -15951,9 +17090,9 @@
         <v/>
       </c>
     </row>
-    <row r="52" ht="14.4" customHeight="1">
+    <row r="52">
       <c r="A52" s="3" t="str">
-        <v>社群分享</v>
+        <v>效能</v>
       </c>
       <c r="B52" s="3">
         <v>1</v>
@@ -15977,9 +17116,9 @@
         <v/>
       </c>
     </row>
-    <row r="53" ht="14.4" customHeight="1">
+    <row r="53">
       <c r="A53" s="3" t="str">
-        <v>導航</v>
+        <v>社群分享</v>
       </c>
       <c r="B53" s="3">
         <v>1</v>
@@ -16003,9 +17142,9 @@
         <v/>
       </c>
     </row>
-    <row r="54" ht="14.4" customHeight="1">
+    <row r="54">
       <c r="A54" s="3" t="str">
-        <v>關於我們</v>
+        <v>導航</v>
       </c>
       <c r="B54" s="3">
         <v>1</v>
@@ -16029,9 +17168,9 @@
         <v/>
       </c>
     </row>
-    <row r="55" ht="14.4" customHeight="1">
+    <row r="55">
       <c r="A55" s="3" t="str">
-        <v>後台</v>
+        <v>關於我們</v>
       </c>
       <c r="B55" s="3">
         <v>1</v>
@@ -16055,9 +17194,9 @@
         <v/>
       </c>
     </row>
-    <row r="56" ht="14.4" customHeight="1">
+    <row r="56">
       <c r="A56" s="3" t="str">
-        <v>preview 頁</v>
+        <v>後台</v>
       </c>
       <c r="B56" s="3">
         <v>1</v>
@@ -16081,9 +17220,9 @@
         <v/>
       </c>
     </row>
-    <row r="57" ht="14.4" customHeight="1">
+    <row r="57">
       <c r="A57" s="3" t="str">
-        <v>追蹤文件</v>
+        <v>preview 頁</v>
       </c>
       <c r="B57" s="3">
         <v>1</v>
@@ -16107,327 +17246,327 @@
         <v/>
       </c>
     </row>
-    <row r="59" ht="14.4" customHeight="1">
+    <row r="58">
+      <c r="A58" s="3" t="str">
+        <v>追蹤文件</v>
+      </c>
+      <c r="B58" s="3">
+        <v>1</v>
+      </c>
+      <c r="C58" s="3" t="str">
+        <v>0.6%</v>
+      </c>
+      <c r="D58" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E58" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F58" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G58" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H58" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
       <c r="A59" s="3" t="str">
+        <v>i-Fare 福利政策</v>
+      </c>
+      <c r="B59" s="3">
+        <v>1</v>
+      </c>
+      <c r="C59" s="3" t="str">
+        <v>0.6%</v>
+      </c>
+      <c r="D59" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E59" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F59" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G59" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H59" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="str">
         <v>【6】後臺優化 — 各區塊問題分布</v>
       </c>
-      <c r="B59" s="3" t="str">
-        <v/>
-      </c>
-      <c r="C59" s="3" t="str">
-        <v/>
-      </c>
-      <c r="D59" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E59" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F59" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G59" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H59" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="14.4" customHeight="1">
-      <c r="A60" s="3" t="str">
+      <c r="B61" s="5" t="str">
+        <v/>
+      </c>
+      <c r="C61" s="5" t="str">
+        <v/>
+      </c>
+      <c r="D61" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E61" s="5" t="str">
+        <v/>
+      </c>
+      <c r="F61" s="5" t="str">
+        <v/>
+      </c>
+      <c r="G61" s="5" t="str">
+        <v/>
+      </c>
+      <c r="H61" s="5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="str">
         <v>區塊</v>
       </c>
-      <c r="B60" s="3" t="str">
+      <c r="B62" s="6" t="str">
         <v>項目數</v>
       </c>
-      <c r="C60" s="3" t="str">
+      <c r="C62" s="6" t="str">
         <v>佔比</v>
       </c>
-      <c r="D60" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E60" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F60" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G60" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H60" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="61" ht="14.4" customHeight="1">
-      <c r="A61" s="3" t="str">
+      <c r="D62" s="6" t="str">
+        <v/>
+      </c>
+      <c r="E62" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F62" s="6" t="str">
+        <v/>
+      </c>
+      <c r="G62" s="6" t="str">
+        <v/>
+      </c>
+      <c r="H62" s="6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="str">
         <v>後台通用</v>
       </c>
-      <c r="B61" s="3">
-        <v>19</v>
-      </c>
-      <c r="C61" s="3" t="str">
-        <v>30.2%</v>
-      </c>
-      <c r="D61" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E61" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F61" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G61" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H61" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="62" ht="14.4" customHeight="1">
-      <c r="A62" s="3" t="str">
+      <c r="B63" s="3">
+        <v>26</v>
+      </c>
+      <c r="C63" s="3" t="str">
+        <v>26.0%</v>
+      </c>
+      <c r="D63" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E63" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F63" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G63" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H63" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="str">
         <v>共用元件</v>
       </c>
-      <c r="B62" s="3">
-        <v>17</v>
-      </c>
-      <c r="C62" s="3" t="str">
-        <v>27.0%</v>
-      </c>
-      <c r="D62" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E62" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F62" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G62" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H62" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="63" ht="14.4" customHeight="1">
-      <c r="A63" s="3" t="str">
+      <c r="B64" s="3">
+        <v>21</v>
+      </c>
+      <c r="C64" s="3" t="str">
+        <v>21.0%</v>
+      </c>
+      <c r="D64" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E64" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F64" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G64" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H64" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="str">
+        <v>i-Fare 維護</v>
+      </c>
+      <c r="B65" s="3">
+        <v>8</v>
+      </c>
+      <c r="C65" s="3" t="str">
+        <v>8.0%</v>
+      </c>
+      <c r="D65" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E65" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F65" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G65" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H65" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="str">
+        <v>頁面管理</v>
+      </c>
+      <c r="B66" s="3">
+        <v>8</v>
+      </c>
+      <c r="C66" s="3" t="str">
+        <v>8.0%</v>
+      </c>
+      <c r="D66" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E66" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F66" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G66" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H66" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="str">
+        <v>資料分析</v>
+      </c>
+      <c r="B67" s="3">
+        <v>7</v>
+      </c>
+      <c r="C67" s="3" t="str">
+        <v>7.0%</v>
+      </c>
+      <c r="D67" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E67" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F67" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G67" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H67" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="str">
         <v>圖片管理</v>
       </c>
-      <c r="B63" s="3">
-        <v>3</v>
-      </c>
-      <c r="C63" s="3" t="str">
-        <v>4.8%</v>
-      </c>
-      <c r="D63" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E63" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F63" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G63" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H63" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="64" ht="14.4" customHeight="1">
-      <c r="A64" s="3" t="str">
-        <v>i-Fare 維護</v>
-      </c>
-      <c r="B64" s="3">
+      <c r="B68" s="3">
+        <v>4</v>
+      </c>
+      <c r="C68" s="3" t="str">
+        <v>4.0%</v>
+      </c>
+      <c r="D68" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E68" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F68" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G68" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H68" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="str">
+        <v>內容品質</v>
+      </c>
+      <c r="B69" s="3">
         <v>2</v>
       </c>
-      <c r="C64" s="3" t="str">
-        <v>3.2%</v>
-      </c>
-      <c r="D64" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E64" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F64" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G64" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H64" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="65" ht="14.4" customHeight="1">
-      <c r="A65" s="3" t="str">
+      <c r="C69" s="3" t="str">
+        <v>2.0%</v>
+      </c>
+      <c r="D69" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E69" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F69" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G69" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H69" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="str">
+        <v>內容管理</v>
+      </c>
+      <c r="B70" s="3">
+        <v>2</v>
+      </c>
+      <c r="C70" s="3" t="str">
+        <v>2.0%</v>
+      </c>
+      <c r="D70" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E70" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F70" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G70" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H70" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="str">
         <v>最新消息維護</v>
-      </c>
-      <c r="B65" s="3">
-        <v>1</v>
-      </c>
-      <c r="C65" s="3" t="str">
-        <v>1.6%</v>
-      </c>
-      <c r="D65" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E65" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F65" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G65" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H65" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="66" ht="14.4" customHeight="1">
-      <c r="A66" s="3" t="str">
-        <v>帳戶維護 / 全站權限</v>
-      </c>
-      <c r="B66" s="3">
-        <v>1</v>
-      </c>
-      <c r="C66" s="3" t="str">
-        <v>1.6%</v>
-      </c>
-      <c r="D66" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E66" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F66" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G66" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H66" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="67" ht="14.4" customHeight="1">
-      <c r="A67" s="3" t="str">
-        <v>前台通用</v>
-      </c>
-      <c r="B67" s="3">
-        <v>1</v>
-      </c>
-      <c r="C67" s="3" t="str">
-        <v>1.6%</v>
-      </c>
-      <c r="D67" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E67" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F67" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G67" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H67" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="68" ht="14.4" customHeight="1">
-      <c r="A68" s="3" t="str">
-        <v>對話框</v>
-      </c>
-      <c r="B68" s="3">
-        <v>1</v>
-      </c>
-      <c r="C68" s="3" t="str">
-        <v>1.6%</v>
-      </c>
-      <c r="D68" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E68" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F68" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G68" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H68" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="69" ht="14.4" customHeight="1">
-      <c r="A69" s="3" t="str">
-        <v>檔案上傳</v>
-      </c>
-      <c r="B69" s="3">
-        <v>1</v>
-      </c>
-      <c r="C69" s="3" t="str">
-        <v>1.6%</v>
-      </c>
-      <c r="D69" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E69" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F69" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G69" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H69" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="70" ht="14.4" customHeight="1">
-      <c r="A70" s="3" t="str">
-        <v>帳號管理</v>
-      </c>
-      <c r="B70" s="3">
-        <v>1</v>
-      </c>
-      <c r="C70" s="3" t="str">
-        <v>1.6%</v>
-      </c>
-      <c r="D70" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E70" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F70" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G70" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H70" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="71" ht="14.4" customHeight="1">
-      <c r="A71" s="3" t="str">
-        <v>搜尋結果</v>
       </c>
       <c r="B71" s="3">
         <v>1</v>
       </c>
       <c r="C71" s="3" t="str">
-        <v>1.6%</v>
+        <v>1.0%</v>
       </c>
       <c r="D71" s="3" t="str">
         <v/>
@@ -16445,15 +17584,15 @@
         <v/>
       </c>
     </row>
-    <row r="72" ht="14.4" customHeight="1">
+    <row r="72">
       <c r="A72" s="3" t="str">
-        <v>日期選擇</v>
+        <v>帳戶維護 / 全站權限</v>
       </c>
       <c r="B72" s="3">
         <v>1</v>
       </c>
       <c r="C72" s="3" t="str">
-        <v>1.6%</v>
+        <v>1.0%</v>
       </c>
       <c r="D72" s="3" t="str">
         <v/>
@@ -16471,15 +17610,15 @@
         <v/>
       </c>
     </row>
-    <row r="73" ht="14.4" customHeight="1">
+    <row r="73">
       <c r="A73" s="3" t="str">
-        <v>表單</v>
+        <v>前台通用</v>
       </c>
       <c r="B73" s="3">
         <v>1</v>
       </c>
       <c r="C73" s="3" t="str">
-        <v>1.6%</v>
+        <v>1.0%</v>
       </c>
       <c r="D73" s="3" t="str">
         <v/>
@@ -16497,15 +17636,15 @@
         <v/>
       </c>
     </row>
-    <row r="74" ht="14.4" customHeight="1">
+    <row r="74">
       <c r="A74" s="3" t="str">
-        <v>側邊欄</v>
+        <v>對話框</v>
       </c>
       <c r="B74" s="3">
         <v>1</v>
       </c>
       <c r="C74" s="3" t="str">
-        <v>1.6%</v>
+        <v>1.0%</v>
       </c>
       <c r="D74" s="3" t="str">
         <v/>
@@ -16523,15 +17662,15 @@
         <v/>
       </c>
     </row>
-    <row r="75" ht="14.4" customHeight="1">
+    <row r="75">
       <c r="A75" s="3" t="str">
-        <v>麵包屑導覽</v>
+        <v>檔案上傳</v>
       </c>
       <c r="B75" s="3">
         <v>1</v>
       </c>
       <c r="C75" s="3" t="str">
-        <v>1.6%</v>
+        <v>1.0%</v>
       </c>
       <c r="D75" s="3" t="str">
         <v/>
@@ -16549,15 +17688,15 @@
         <v/>
       </c>
     </row>
-    <row r="76" ht="14.4" customHeight="1">
+    <row r="76">
       <c r="A76" s="3" t="str">
-        <v>WebAPI</v>
+        <v>帳號管理</v>
       </c>
       <c r="B76" s="3">
         <v>1</v>
       </c>
       <c r="C76" s="3" t="str">
-        <v>1.6%</v>
+        <v>1.0%</v>
       </c>
       <c r="D76" s="3" t="str">
         <v/>
@@ -16575,15 +17714,15 @@
         <v/>
       </c>
     </row>
-    <row r="77" ht="14.4" customHeight="1">
+    <row r="77">
       <c r="A77" s="3" t="str">
-        <v>帳號變更密碼</v>
+        <v>搜尋結果</v>
       </c>
       <c r="B77" s="3">
         <v>1</v>
       </c>
       <c r="C77" s="3" t="str">
-        <v>1.6%</v>
+        <v>1.0%</v>
       </c>
       <c r="D77" s="3" t="str">
         <v/>
@@ -16601,15 +17740,15 @@
         <v/>
       </c>
     </row>
-    <row r="78" ht="14.4" customHeight="1">
+    <row r="78">
       <c r="A78" s="3" t="str">
-        <v>Code 代碼管理</v>
+        <v>日期選擇</v>
       </c>
       <c r="B78" s="3">
         <v>1</v>
       </c>
       <c r="C78" s="3" t="str">
-        <v>1.6%</v>
+        <v>1.0%</v>
       </c>
       <c r="D78" s="3" t="str">
         <v/>
@@ -16627,15 +17766,15 @@
         <v/>
       </c>
     </row>
-    <row r="79" ht="14.4" customHeight="1">
+    <row r="79">
       <c r="A79" s="3" t="str">
-        <v>狀態管理</v>
+        <v>表單</v>
       </c>
       <c r="B79" s="3">
         <v>1</v>
       </c>
       <c r="C79" s="3" t="str">
-        <v>1.6%</v>
+        <v>1.0%</v>
       </c>
       <c r="D79" s="3" t="str">
         <v/>
@@ -16653,15 +17792,15 @@
         <v/>
       </c>
     </row>
-    <row r="80" ht="14.4" customHeight="1">
+    <row r="80">
       <c r="A80" s="3" t="str">
-        <v>登入頁面</v>
+        <v>側邊欄</v>
       </c>
       <c r="B80" s="3">
         <v>1</v>
       </c>
       <c r="C80" s="3" t="str">
-        <v>1.6%</v>
+        <v>1.0%</v>
       </c>
       <c r="D80" s="3" t="str">
         <v/>
@@ -16679,15 +17818,15 @@
         <v/>
       </c>
     </row>
-    <row r="81" ht="14.4" customHeight="1">
+    <row r="81">
       <c r="A81" s="3" t="str">
-        <v>HTML 編輯器</v>
+        <v>麵包屑導覽</v>
       </c>
       <c r="B81" s="3">
         <v>1</v>
       </c>
       <c r="C81" s="3" t="str">
-        <v>1.6%</v>
+        <v>1.0%</v>
       </c>
       <c r="D81" s="3" t="str">
         <v/>
@@ -16705,15 +17844,15 @@
         <v/>
       </c>
     </row>
-    <row r="82" ht="14.4" customHeight="1">
+    <row r="82">
       <c r="A82" s="3" t="str">
-        <v>無權限頁</v>
+        <v>WebAPI</v>
       </c>
       <c r="B82" s="3">
         <v>1</v>
       </c>
       <c r="C82" s="3" t="str">
-        <v>1.6%</v>
+        <v>1.0%</v>
       </c>
       <c r="D82" s="3" t="str">
         <v/>
@@ -16731,15 +17870,15 @@
         <v/>
       </c>
     </row>
-    <row r="83" ht="14.4" customHeight="1">
+    <row r="83">
       <c r="A83" s="3" t="str">
-        <v>效能</v>
+        <v>帳號變更密碼</v>
       </c>
       <c r="B83" s="3">
         <v>1</v>
       </c>
       <c r="C83" s="3" t="str">
-        <v>1.6%</v>
+        <v>1.0%</v>
       </c>
       <c r="D83" s="3" t="str">
         <v/>
@@ -16757,15 +17896,15 @@
         <v/>
       </c>
     </row>
-    <row r="84" ht="14.4" customHeight="1">
+    <row r="84">
       <c r="A84" s="3" t="str">
-        <v>後台首頁</v>
+        <v>Code 代碼管理</v>
       </c>
       <c r="B84" s="3">
         <v>1</v>
       </c>
       <c r="C84" s="3" t="str">
-        <v>1.6%</v>
+        <v>1.0%</v>
       </c>
       <c r="D84" s="3" t="str">
         <v/>
@@ -16783,15 +17922,15 @@
         <v/>
       </c>
     </row>
-    <row r="85" ht="14.4" customHeight="1">
+    <row r="85">
       <c r="A85" s="3" t="str">
-        <v>內容品質</v>
+        <v>狀態管理</v>
       </c>
       <c r="B85" s="3">
         <v>1</v>
       </c>
       <c r="C85" s="3" t="str">
-        <v>1.6%</v>
+        <v>1.0%</v>
       </c>
       <c r="D85" s="3" t="str">
         <v/>
@@ -16809,15 +17948,15 @@
         <v/>
       </c>
     </row>
-    <row r="86" ht="14.4" customHeight="1">
+    <row r="86">
       <c r="A86" s="3" t="str">
-        <v>資料分析</v>
+        <v>登入頁面</v>
       </c>
       <c r="B86" s="3">
         <v>1</v>
       </c>
       <c r="C86" s="3" t="str">
-        <v>1.6%</v>
+        <v>1.0%</v>
       </c>
       <c r="D86" s="3" t="str">
         <v/>
@@ -16835,218 +17974,348 @@
         <v/>
       </c>
     </row>
-    <row r="88" ht="14.4" customHeight="1">
+    <row r="87">
+      <c r="A87" s="3" t="str">
+        <v>HTML 編輯器</v>
+      </c>
+      <c r="B87" s="3">
+        <v>1</v>
+      </c>
+      <c r="C87" s="3" t="str">
+        <v>1.0%</v>
+      </c>
+      <c r="D87" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E87" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F87" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G87" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H87" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
       <c r="A88" s="3" t="str">
+        <v>無權限頁</v>
+      </c>
+      <c r="B88" s="3">
+        <v>1</v>
+      </c>
+      <c r="C88" s="3" t="str">
+        <v>1.0%</v>
+      </c>
+      <c r="D88" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E88" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F88" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G88" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H88" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="str">
+        <v>效能</v>
+      </c>
+      <c r="B89" s="3">
+        <v>1</v>
+      </c>
+      <c r="C89" s="3" t="str">
+        <v>1.0%</v>
+      </c>
+      <c r="D89" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E89" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F89" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G89" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H89" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="str">
+        <v>後台首頁</v>
+      </c>
+      <c r="B90" s="3">
+        <v>1</v>
+      </c>
+      <c r="C90" s="3" t="str">
+        <v>1.0%</v>
+      </c>
+      <c r="D90" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E90" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F90" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G90" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H90" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="str">
+        <v>前台動態頁</v>
+      </c>
+      <c r="B91" s="3">
+        <v>1</v>
+      </c>
+      <c r="C91" s="3" t="str">
+        <v>1.0%</v>
+      </c>
+      <c r="D91" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E91" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F91" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G91" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H91" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="str">
+        <v>發布流程</v>
+      </c>
+      <c r="B92" s="3">
+        <v>1</v>
+      </c>
+      <c r="C92" s="3" t="str">
+        <v>1.0%</v>
+      </c>
+      <c r="D92" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E92" s="3" t="str">
+        <v/>
+      </c>
+      <c r="F92" s="3" t="str">
+        <v/>
+      </c>
+      <c r="G92" s="3" t="str">
+        <v/>
+      </c>
+      <c r="H92" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="str">
         <v>【7】你做了什麼 — 已完成項目摘要 (依 Round 分組)</v>
       </c>
-      <c r="B88" s="3" t="str">
-        <v/>
-      </c>
-      <c r="C88" s="3" t="str">
-        <v/>
-      </c>
-      <c r="D88" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E88" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F88" s="3" t="str">
-        <v/>
-      </c>
-      <c r="G88" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H88" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="89" ht="14.4" customHeight="1">
-      <c r="A89" s="3" t="str">
+      <c r="B94" s="5" t="str">
+        <v/>
+      </c>
+      <c r="C94" s="5" t="str">
+        <v/>
+      </c>
+      <c r="D94" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E94" s="5" t="str">
+        <v/>
+      </c>
+      <c r="F94" s="5" t="str">
+        <v/>
+      </c>
+      <c r="G94" s="5" t="str">
+        <v/>
+      </c>
+      <c r="H94" s="5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="str">
         <v>Round</v>
       </c>
-      <c r="B89" s="3" t="str">
+      <c r="B95" s="6" t="str">
         <v>日期</v>
       </c>
-      <c r="C89" s="3" t="str">
+      <c r="C95" s="6" t="str">
         <v>已修正 (綠)</v>
       </c>
-      <c r="D89" s="3" t="str">
+      <c r="D95" s="6" t="str">
         <v>部分修正 (黃)</v>
       </c>
-      <c r="E89" s="3" t="str">
+      <c r="E95" s="6" t="str">
         <v>已修正 # 清單</v>
       </c>
-      <c r="F89" s="3" t="str">
+      <c r="F95" s="6" t="str">
         <v>部分修正 # 清單</v>
       </c>
-      <c r="G89" s="3" t="str">
+      <c r="G95" s="6" t="str">
         <v>主要重點</v>
       </c>
-      <c r="H89" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="90" ht="14.4" customHeight="1">
-      <c r="A90" s="3" t="str">
+      <c r="H95" s="6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="str">
         <v>Round 1</v>
       </c>
-      <c r="B90" s="3" t="str">
+      <c r="B96" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="C90" s="3">
-        <v>103</v>
-      </c>
-      <c r="D90" s="3">
-        <v>11</v>
-      </c>
-      <c r="E90" s="3" t="str">
-        <v>#1, #2, #3, #6, #7, #9, #11, #12, #13, #14, #15, #16, #17, #22, #23, #24, #27, #28, #29, #30, #31, #32, #36, #37, #38, #40, #41, #44, #45, #46, #47, #48, #49, #50, #52, #53, #54, #55, #56, #58, #59, #60, #61, #70, #71, #75, #77, #79, #80, #82, #86, #87, #88, #89, #90, #106, #108, #109, #110, #111, #112, #113, #114, #115, #116, #117, #118, #119, #120, #122, #123, #124, #125, #126, #127, #128, #129, #130, #131, #132, #133, #134, #135, #137, #138, #139, #140, #143, #145, #146, #147, #149, #150, #151, #152, #153, #155, #156, #157, #159, #161, #162, #163</v>
-      </c>
-      <c r="F90" s="3" t="str">
-        <v>#67, #68, #73, #76, #107, #136, #141, #142, #144, #158, #160</v>
-      </c>
-      <c r="G90" s="3" t="str">
+      <c r="C96" s="7">
+        <v>106</v>
+      </c>
+      <c r="D96" s="8">
+        <v>19</v>
+      </c>
+      <c r="E96" s="3" t="str">
+        <v>#1, #2, #3, #6, #7, #9, #11, #12, #13, #14, #15, #16, #17, #22, #23, #24, #27, #28, #29, #30, #31, #32, #36, #37, #38, #40, #41, #44, #45, #46, #47, #48, #49, #50, #52, #53, #54, #55, #56, #58, #59, #60, #61, #70, #71, #75, #77, #79, #80, #82, #86, #87, #88, #89, #90, #106, #108, #109, #110, #111, #112, #113, #114, #115, #116, #117, #118, #119, #120, #122, #123, #124, #125, #126, #127, #128, #129, #130, #131, #132, #133, #134, #135, #137, #138, #139, #140, #143, #145, #146, #147, #148, #149, #150, #151, #152, #153, #154, #155, #156, #157, #159, #161, #162, #163, #166</v>
+      </c>
+      <c r="F96" s="3" t="str">
+        <v>#67, #68, #73, #76, #107, #136, #141, #142, #144, #158, #160, #167, #168, #169, #170, #171, #172, #173, #174</v>
+      </c>
+      <c r="G96" s="3" t="str">
         <v>搜尋優化 (移除 disabled / 結果摘要) + 全站動畫 + skeleton 載入 + 卡片/按鈕 hover translateY</v>
       </c>
-      <c r="H90" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="91" ht="14.4" customHeight="1">
-      <c r="A91" s="3" t="str">
+      <c r="H96" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="str">
         <v>Round 2</v>
       </c>
-      <c r="B91" s="3" t="str">
+      <c r="B97" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="C91" s="3">
+      <c r="C97" s="7">
         <v>2</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D97" s="8">
         <v>0</v>
       </c>
-      <c r="E91" s="3" t="str">
+      <c r="E97" s="3" t="str">
         <v>#91, #92</v>
       </c>
-      <c r="F91" s="3" t="str">
+      <c r="F97" s="3" t="str">
         <v>-</v>
       </c>
-      <c r="G91" s="3" t="str">
+      <c r="G97" s="3" t="str">
         <v>Footer 整合 (LINE/FB 並列 .btn-social) + 觸控目標 44px</v>
       </c>
-      <c r="H91" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="92" ht="14.4" customHeight="1">
-      <c r="A92" s="3" t="str">
+      <c r="H97" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="str">
         <v>Round 3</v>
       </c>
-      <c r="B92" s="3" t="str">
+      <c r="B98" s="3" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="C92" s="3">
+      <c r="C98" s="7">
         <v>6</v>
       </c>
-      <c r="D92" s="3">
+      <c r="D98" s="8">
         <v>0</v>
       </c>
-      <c r="E92" s="3" t="str">
+      <c r="E98" s="3" t="str">
         <v>#26, #93, #94, #95, #96, #97</v>
       </c>
-      <c r="F92" s="3" t="str">
+      <c r="F98" s="3" t="str">
         <v>-</v>
       </c>
-      <c r="G92" s="3" t="str">
+      <c r="G98" s="3" t="str">
         <v>About 三大核心 morph 卡 + News 浮起卡 + 浮現動畫 + line-clamp + NEW pill + 社群 target="_blank"</v>
       </c>
-      <c r="H92" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="93" ht="14.4" customHeight="1">
-      <c r="A93" s="3" t="str">
+      <c r="H98" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="str">
         <v>Round 4</v>
       </c>
-      <c r="B93" s="3" t="str">
+      <c r="B99" s="3" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="C93" s="3">
+      <c r="C99" s="7">
         <v>8</v>
       </c>
-      <c r="D93" s="3">
+      <c r="D99" s="8">
         <v>0</v>
       </c>
-      <c r="E93" s="3" t="str">
+      <c r="E99" s="3" t="str">
         <v>#98, #99, #100, #101, #102, #103, #104, #105</v>
       </c>
-      <c r="F93" s="3" t="str">
+      <c r="F99" s="3" t="str">
         <v>-</v>
       </c>
-      <c r="G93" s="3" t="str">
+      <c r="G99" s="3" t="str">
         <v>cf47cfa+5dfbf91 補回 16 檔 + 環境設定 (devProxy/baseURL) + 未來規劃 nav + News videoUrl wiring + tsconfig + about hover bug + footer label 重複</v>
       </c>
-      <c r="H93" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="94" ht="14.4" customHeight="1">
-      <c r="A94" s="3" t="str">
+      <c r="H99" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="str">
         <v>Round 9</v>
       </c>
-      <c r="B94" s="3" t="str">
+      <c r="B100" s="3" t="str">
         <v>2026-05-12</v>
       </c>
-      <c r="C94" s="3">
+      <c r="C100" s="7">
         <v>2</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D100" s="8">
         <v>0</v>
       </c>
-      <c r="E94" s="3" t="str">
+      <c r="E100" s="3" t="str">
         <v>#164, #165</v>
       </c>
-      <c r="F94" s="3" t="str">
+      <c r="F100" s="3" t="str">
         <v>-</v>
       </c>
-      <c r="G94" s="3" t="str">
+      <c r="G100" s="3" t="str">
         <v>future.vue 補強手機版主標換行、空狀態導引卡與上下節奏，讓頁面在未上線時也有清楚下一步</v>
       </c>
-      <c r="H94" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="95" ht="14.4" customHeight="1">
-      <c r="A95" s="3" t="str">
-        <v>Round 15</v>
-      </c>
-      <c r="B95" s="3" t="str">
-        <v>2026-05-19</v>
-      </c>
-      <c r="C95" s="3">
-        <v>13</v>
-      </c>
-      <c r="D95" s="3">
-        <v>0</v>
-      </c>
-      <c r="E95" s="3" t="str">
-        <v>後臺優化 #20, #21, #25, #26, #28, #36, #38, #71, #83, #84, #85, #86；UIUX #154</v>
-      </c>
-      <c r="F95" s="3" t="str">
-        <v>-</v>
-      </c>
-      <c r="G95" s="3" t="str">
-        <v>PageManagement 預覽與圖片修復；搜尋清除、日期快捷、刪除確認、表格空狀態、分頁重設、登入 Caps Lock、無權限頁、Analysis Dashboard RWD、RWD 回歸清單</v>
-      </c>
-      <c r="H95" s="3" t="str">
+      <c r="H100" s="3" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H94"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H101"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/iFare_UI_UX_問題追蹤清單.xlsx
+++ b/docs/iFare_UI_UX_問題追蹤清單.xlsx
@@ -36,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -45,8 +45,70 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+      <color rgb="1F3864"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+      <color rgb="1F3864"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <color rgb="006100"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <color rgb="9C5700"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <color rgb="595959"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <color rgb="006100"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <color rgb="9C5700"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <color rgb="595959"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="12">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -54,6 +116,66 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -77,17 +199,47 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10310,13 +10462,13 @@
         <v>確認按鈕樣式分散三個以上檔案</v>
       </c>
       <c r="N76" s="3" t="str">
-        <v>待處理</v>
+        <v>部分修正</v>
       </c>
       <c r="O76" s="3" t="str">
-        <v/>
+        <v>2026-05-25</v>
       </c>
       <c r="P76" s="3" t="str">
-        <v/>
+        <v>2026-05-25：盤點全站 18 個 .btn-* class（btn/btn-tag/btn-icon/btn-ic-share/btn-search/btn-page-next/btn-page-prev/btn-more/btn-select-close/btn-filter/btn-advance/btn-menu/btn-close/btn-reset/btn-empty-oval/btn-ifare/btn-ifare-start/btn-line）分布三檔（_button.scss 結構、_font.scss 字型、_rwd_button.scss 響應式），含 vue 使用次數；在 _button.scss 加 header docstring 文件化現況 + 未來統一規範方向（base mixin / variant / size / 跨檔合併）。實際 styling 統一需先設計討論（與 #64-66 設計系統綁定）。</v>
       </c>
     </row>
     <row r="77" ht="14.4" customHeight="1" xml:space="preserve">
@@ -10763,13 +10915,13 @@
         <v>屬於全站無障礙規範，現有清單只有單點檢查。</v>
       </c>
       <c r="N85" s="3" t="str">
-        <v>待處理</v>
+        <v>部分修正</v>
       </c>
       <c r="O85" s="3" t="str">
-        <v/>
+        <v>2026-05-25</v>
       </c>
       <c r="P85" s="3" t="str">
-        <v/>
+        <v>2026-05-25：盤點全站 &lt;img&gt; 3 處（collaborator.vue / lazy.vue / SectionImageText.vue）皆已有適當 alt；盤點 inline SVG 6 處，補 CompChatbotWelcome.vue 三處 button 內 SVG (清除對話 / 關閉 / 送出) 加 aria-hidden="true" + focusable="false"（CompChatbotEntry.vue 已有；about.vue 已用父 span aria-hidden 包覆）。全站圖片 a11y 規範 docs 化待補。</v>
       </c>
     </row>
     <row r="86" ht="14.4" customHeight="1">
@@ -10863,13 +11015,13 @@
         <v>屬於首屏效能盤點，現有清單未明確拆出。</v>
       </c>
       <c r="N87" s="3" t="str">
-        <v>待處理</v>
+        <v>部分修正</v>
       </c>
       <c r="O87" s="3" t="str">
-        <v/>
+        <v>2026-05-25</v>
       </c>
       <c r="P87" s="3" t="str">
-        <v/>
+        <v>2026-05-25：nuxt.config.ts app.head.link 加 Google Fonts preconnect (fonts.googleapis.com + fonts.gstatic.com crossorigin) + dns-prefetch，省 DNS+TCP+TLS 握手 100-300ms 加速字型載入（既有 display=swap 保留）。首屏 Hero 圖 (assets/img/Index-Img-0~4.jpg 共 ~680KB，最大 Index-Img-2 347KB) 因走 webpack hash 路徑無法直接 preload；Lighthouse LCP/CLS/INP 量測待補。</v>
       </c>
     </row>
     <row r="88" ht="14.4" customHeight="1">
@@ -15420,93 +15572,93 @@
       </c>
     </row>
     <row r="177" xml:space="preserve">
-      <c r="A177" s="4">
+      <c r="A177" s="3">
         <v>175</v>
       </c>
-      <c r="B177" s="4" t="str">
-        <v>V</v>
-      </c>
-      <c r="C177" s="4" t="str">
+      <c r="B177" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C177" s="3" t="str">
         <v>前台 Nuxt Server API</v>
       </c>
-      <c r="D177" s="4" t="str">
+      <c r="D177" s="3" t="str">
         <v>Dynamic Pages / Assets</v>
       </c>
-      <c r="E177" s="4" t="str">
+      <c r="E177" s="3" t="str">
         <v>修正</v>
       </c>
-      <c r="F177" s="4" t="str">
+      <c r="F177" s="3" t="str">
         <v>資安</v>
       </c>
-      <c r="G177" s="4" t="str">
+      <c r="G177" s="3" t="str">
         <v>高</v>
       </c>
-      <c r="H177" s="4" t="str">
+      <c r="H177" s="3" t="str">
         <v>公開 API 可無驗證覆寫頁面資料與上傳檔案</v>
       </c>
-      <c r="I177" s="4" t="str">
+      <c r="I177" s="3" t="str">
         <v>dynamic-pages.put 與 dynamic-assets.post 可直接寫入檔案，CORS 允許 *，未看到後端驗證、容量限制或檔案型別安全處理；外部請求可能竄改頁面內容或累積惡意檔案。</v>
       </c>
-      <c r="J177" s="4" t="str">
+      <c r="J177" s="3" t="str">
         <v>立即補 server-side 權限驗證或部署密鑰；限制 CORS 來源；production 關閉 PoC 寫入端點；限制檔案大小與 MIME；SVG 改轉檔或消毒後再提供。</v>
       </c>
-      <c r="K177" s="4" t="str">
+      <c r="K177" s="3" t="str">
         <v>Nuxt API、Dynamic Pages、Dynamic Assets</v>
       </c>
-      <c r="L177" s="4" t="str" xml:space="preserve">
+      <c r="L177" s="3" t="str" xml:space="preserve">
         <v xml:space="preserve">Dev/Dev Code/iFare_Frontend/server/api/dynamic-pages.put.ts
 Dev/Dev Code/iFare_Frontend/server/api/dynamic-assets.post.ts
 Dev/Dev Code/iFare_Frontend/server/utils/cors.ts
 Dev/Dev Code/iFare_Frontend/server/api/dynamic-assets/[name].get.ts</v>
       </c>
-      <c r="M177" s="4" t="str">
+      <c r="M177" s="3" t="str">
         <v>已讀程式碼：PUT/POST 端點直接 writeFile；CORS 回應 Access-Control-Allow-Origin: *。</v>
       </c>
-      <c r="N177" s="4" t="str">
-        <v>待處理</v>
-      </c>
-      <c r="O177" s="4" t="str">
-        <v/>
-      </c>
-      <c r="P177" s="4" t="str">
-        <v>立即處理；屬內容竄改與檔案上傳風險。</v>
+      <c r="N177" s="3" t="str">
+        <v>部分修正</v>
+      </c>
+      <c r="O177" s="3" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="P177" s="3" t="str">
+        <v>2026-05-25 commit ae1c85a：dynamic-pages.put / dynamic-assets.post / dynamic-assets/[name].get 加 requireDynamicApiToken (Bearer + X-iFare-Sync-Token, timingSafeEqual)、CORS 白名單 (DEV_ALLOWED_ORIGINS + dynamicApiAllowedOrigins config)。檔案大小限制 / MIME 過濾 / SVG 消毒待補。</v>
       </c>
     </row>
     <row r="178" xml:space="preserve">
-      <c r="A178" s="4">
+      <c r="A178" s="3">
         <v>176</v>
       </c>
-      <c r="B178" s="4" t="str">
-        <v>V</v>
-      </c>
-      <c r="C178" s="4" t="str">
+      <c r="B178" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C178" s="3" t="str">
         <v>後台 API / 帳號</v>
       </c>
-      <c r="D178" s="4" t="str">
+      <c r="D178" s="3" t="str">
         <v>密碼管理</v>
       </c>
-      <c r="E178" s="4" t="str">
+      <c r="E178" s="3" t="str">
         <v>修正</v>
       </c>
-      <c r="F178" s="4" t="str">
+      <c r="F178" s="3" t="str">
         <v>資安</v>
       </c>
-      <c r="G178" s="4" t="str">
+      <c r="G178" s="3" t="str">
         <v>高</v>
       </c>
-      <c r="H178" s="4" t="str">
+      <c r="H178" s="3" t="str">
         <v>後台密碼以明文儲存、比對並可回傳到前端</v>
       </c>
-      <c r="I178" s="4" t="str">
+      <c r="I178" s="3" t="str">
         <v>SysUser.Password 為字串欄位，登入以 p.Password == pwd 比對；帳號清單與明細 DTO 也帶出 pwd，前端帳號管理頁可讀寫密碼。資料庫或 API 一旦外洩會直接暴露所有後台密碼。</v>
       </c>
-      <c r="J178" s="4" t="str">
+      <c r="J178" s="3" t="str">
         <v>導入 PasswordHasher/BCrypt/Argon2；新增密碼雜湊 migration 與強制重設流程；停止回傳 pwd；新增密碼變更專用 API；清除前端密碼欄位與相關 log。</v>
       </c>
-      <c r="K178" s="4" t="str">
+      <c r="K178" s="3" t="str">
         <v>後台帳號、登入、密碼欄位</v>
       </c>
-      <c r="L178" s="4" t="str" xml:space="preserve">
+      <c r="L178" s="3" t="str" xml:space="preserve">
         <v xml:space="preserve">Dev/Dev Code/iFare_WebApi/iFare.WebApi/Models/DBModel/SysUser.cs
 Dev/Dev Code/iFare_WebApi/iFare.WebApi/TaskManager/AuthTaskManager.cs
 Dev/Dev Code/iFare_WebApi/iFare.WebApi/TaskManager/MainTaskManager.cs
@@ -15515,331 +15667,331 @@
 Dev/Dev Code/iFare_Admin/src/views/Account/Account_ItemDetailView.vue
 Dev/Dev Code/iFare_Admin/src/views/Account/Account_AddEditView.vue</v>
       </c>
-      <c r="M178" s="4" t="str">
+      <c r="M178" s="3" t="str">
         <v>已讀程式碼：登入直接比對明文密碼，帳號 DTO/前端欄位使用 pwd。</v>
       </c>
-      <c r="N178" s="4" t="str">
+      <c r="N178" s="3" t="str">
         <v>待處理</v>
       </c>
-      <c r="O178" s="4" t="str">
-        <v/>
-      </c>
-      <c r="P178" s="4" t="str">
+      <c r="O178" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P178" s="3" t="str">
         <v>立即處理；需搭配資料 migration 與使用者重設密碼。</v>
       </c>
     </row>
     <row r="179" xml:space="preserve">
-      <c r="A179" s="4">
+      <c r="A179" s="3">
         <v>177</v>
       </c>
-      <c r="B179" s="4" t="str">
-        <v>V</v>
-      </c>
-      <c r="C179" s="4" t="str">
+      <c r="B179" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C179" s="3" t="str">
         <v>後台 API</v>
       </c>
-      <c r="D179" s="4" t="str">
+      <c r="D179" s="3" t="str">
         <v>權限控管</v>
       </c>
-      <c r="E179" s="4" t="str">
+      <c r="E179" s="3" t="str">
         <v>修正</v>
       </c>
-      <c r="F179" s="4" t="str">
+      <c r="F179" s="3" t="str">
         <v>權限</v>
       </c>
-      <c r="G179" s="4" t="str">
+      <c r="G179" s="3" t="str">
         <v>高</v>
       </c>
-      <c r="H179" s="4" t="str">
+      <c r="H179" s="3" t="str">
         <v>多數新增/修改/刪除 API 只要求登入，未檢查角色或功能權限</v>
       </c>
-      <c r="I179" s="4" t="str">
+      <c r="I179" s="3" t="str">
         <v>JwtAuth policy 僅 RequireAuthenticatedUser，多數 AppService 的 POST/PUT/DELETE 只有 [Authorize]；目前僅 AccountAppService 看到 IsEditorCheckerFilter。任一有效 token 可能呼叫不該使用的管理 API。</v>
       </c>
-      <c r="J179" s="4" t="str">
+      <c r="J179" s="3" t="str">
         <v>把 Editor/Admin 權限檢查下沉到 API policy/filter；所有 mutation endpoint 補角色或功能授權；前端選單權限僅作 UI 控制，不可取代 API 授權；補授權測試。</v>
       </c>
-      <c r="K179" s="4" t="str">
+      <c r="K179" s="3" t="str">
         <v>後台 API、JWT、角色權限</v>
       </c>
-      <c r="L179" s="4" t="str" xml:space="preserve">
+      <c r="L179" s="3" t="str" xml:space="preserve">
         <v xml:space="preserve">Dev/Dev Code/iFare_WebApi/iFare.WebApi/Program/AuthConfigurer.cs
 Dev/Dev Code/iFare_WebApi/iFare.WebApi/Controllers/AppService/*.cs
 Dev/Dev Code/iFare_WebApi/iFare.WebApi/Controllers/AppService/AccountAppService.cs</v>
       </c>
-      <c r="M179" s="4" t="str">
+      <c r="M179" s="3" t="str">
         <v>已讀程式碼：JwtAuth policy 只檢查登入狀態，多數 AppService mutation 未套角色 filter。</v>
       </c>
-      <c r="N179" s="4" t="str">
+      <c r="N179" s="3" t="str">
         <v>待處理</v>
       </c>
-      <c r="O179" s="4" t="str">
-        <v/>
-      </c>
-      <c r="P179" s="4" t="str">
+      <c r="O179" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P179" s="3" t="str">
         <v>立即處理；避免低權限帳號操作管理功能。</v>
       </c>
     </row>
     <row r="180" xml:space="preserve">
-      <c r="A180" s="4">
+      <c r="A180" s="3">
         <v>178</v>
       </c>
-      <c r="B180" s="4" t="str">
-        <v>V</v>
-      </c>
-      <c r="C180" s="4" t="str">
+      <c r="B180" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C180" s="3" t="str">
         <v>後台 API</v>
       </c>
-      <c r="D180" s="4" t="str">
+      <c r="D180" s="3" t="str">
         <v>登入 / 停用帳號</v>
       </c>
-      <c r="E180" s="4" t="str">
+      <c r="E180" s="3" t="str">
         <v>修正</v>
       </c>
-      <c r="F180" s="4" t="str">
+      <c r="F180" s="3" t="str">
         <v>資安</v>
       </c>
-      <c r="G180" s="4" t="str">
+      <c r="G180" s="3" t="str">
         <v>高</v>
       </c>
-      <c r="H180" s="4" t="str">
+      <c r="H180" s="3" t="str">
         <v>停用帳號仍可先取得 JWT</v>
       </c>
-      <c r="I180" s="4" t="str">
+      <c r="I180" s="3" t="str">
         <v>TokenAuthController.Authenticate 只依帳密取得使用者並簽發 token；State 停用檢查出現在後續 LoginCheck 流程。攻擊者可直接呼叫 Authenticate 取得停用帳號的 JWT。</v>
       </c>
-      <c r="J180" s="4" t="str">
+      <c r="J180" s="3" t="str">
         <v>在 Authenticate 階段檢查帳號 State/停用狀態；停用或改密碼時撤銷既有 token；JWT claims 加 security stamp 或版本號並於 API 驗證。</v>
       </c>
-      <c r="K180" s="4" t="str">
+      <c r="K180" s="3" t="str">
         <v>登入、JWT、帳號停用</v>
       </c>
-      <c r="L180" s="4" t="str" xml:space="preserve">
+      <c r="L180" s="3" t="str" xml:space="preserve">
         <v xml:space="preserve">Dev/Dev Code/iFare_WebApi/iFare.WebApi/Controllers/TokenAuthController.cs
 Dev/Dev Code/iFare_WebApi/iFare.WebApi/TaskManager/AuthTaskManager.cs
 Dev/Dev Code/iFare_WebApi/iFare.WebApi/TaskManager/MainTaskManager.cs</v>
       </c>
-      <c r="M180" s="4" t="str">
+      <c r="M180" s="3" t="str">
         <v>已讀程式碼：Authenticate 呼叫 GetAuthUser 後即產生 token，GetAuthUser 未過濾停用狀態。</v>
       </c>
-      <c r="N180" s="4" t="str">
+      <c r="N180" s="3" t="str">
         <v>待處理</v>
       </c>
-      <c r="O180" s="4" t="str">
-        <v/>
-      </c>
-      <c r="P180" s="4" t="str">
+      <c r="O180" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P180" s="3" t="str">
         <v>立即處理；與權限控管問題會互相放大風險。</v>
       </c>
     </row>
     <row r="181" xml:space="preserve">
-      <c r="A181" s="4">
+      <c r="A181" s="3">
         <v>179</v>
       </c>
-      <c r="B181" s="4" t="str">
-        <v>V</v>
-      </c>
-      <c r="C181" s="4" t="str">
+      <c r="B181" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C181" s="3" t="str">
         <v>設定 / 部署</v>
       </c>
-      <c r="D181" s="4" t="str">
+      <c r="D181" s="3" t="str">
         <v>JWT Secret</v>
       </c>
-      <c r="E181" s="4" t="str">
+      <c r="E181" s="3" t="str">
         <v>修正</v>
       </c>
-      <c r="F181" s="4" t="str">
+      <c r="F181" s="3" t="str">
         <v>資安</v>
       </c>
-      <c r="G181" s="4" t="str">
+      <c r="G181" s="3" t="str">
         <v>高</v>
       </c>
-      <c r="H181" s="4" t="str">
+      <c r="H181" s="3" t="str">
         <v>JWT SecurityKey 寫在版控設定檔與發佈產物</v>
       </c>
-      <c r="I181" s="4" t="str">
+      <c r="I181" s="3" t="str">
         <v>appsettings.json 內含固定 SecurityKey，且 Dev/Prd 版本皆在專案內可讀。若 repository 或發佈包外洩，攻擊者可偽造 JWT。</v>
       </c>
-      <c r="J181" s="4" t="str">
+      <c r="J181" s="3" t="str">
         <v>改用環境變數、Secret Manager 或部署平台 secret；立即旋轉正式 JWT key；清查歷史外洩範圍；避免把含 secret 的 appsettings 或發佈產物提交進版控。</v>
       </c>
-      <c r="K181" s="4" t="str">
+      <c r="K181" s="3" t="str">
         <v>JWT、appsettings、部署設定</v>
       </c>
-      <c r="L181" s="4" t="str" xml:space="preserve">
+      <c r="L181" s="3" t="str" xml:space="preserve">
         <v xml:space="preserve">Dev/Dev Code/iFare_WebApi/iFare.WebApi/appsettings.json
 Prd/Prd Code/iFare_WebApi/appsettings.json</v>
       </c>
-      <c r="M181" s="4" t="str">
+      <c r="M181" s="3" t="str">
         <v>已讀設定檔：JwtBearer.SecurityKey 直接出現在 tracked appsettings.json。</v>
       </c>
-      <c r="N181" s="4" t="str">
+      <c r="N181" s="3" t="str">
         <v>待處理</v>
       </c>
-      <c r="O181" s="4" t="str">
-        <v/>
-      </c>
-      <c r="P181" s="4" t="str">
+      <c r="O181" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P181" s="3" t="str">
         <v>立即處理；需同步更新部署環境與 token 失效策略。</v>
       </c>
     </row>
     <row r="182" xml:space="preserve">
-      <c r="A182" s="4">
+      <c r="A182" s="3">
         <v>180</v>
       </c>
-      <c r="B182" s="4" t="str">
-        <v>V</v>
-      </c>
-      <c r="C182" s="4" t="str">
+      <c r="B182" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C182" s="3" t="str">
         <v>後台前端</v>
       </c>
-      <c r="D182" s="4" t="str">
+      <c r="D182" s="3" t="str">
         <v>Token / XSS</v>
       </c>
-      <c r="E182" s="4" t="str">
+      <c r="E182" s="3" t="str">
         <v>修正</v>
       </c>
-      <c r="F182" s="4" t="str">
+      <c r="F182" s="3" t="str">
         <v>資安</v>
       </c>
-      <c r="G182" s="4" t="str">
+      <c r="G182" s="3" t="str">
         <v>高</v>
       </c>
-      <c r="H182" s="4" t="str">
+      <c r="H182" s="3" t="str">
         <v>後台 token 存 localStorage 且有未消毒 v-html，XSS 後可竊取 token</v>
       </c>
-      <c r="I182" s="4" t="str">
+      <c r="I182" s="3" t="str">
         <v>Pinia persist 會把登入資訊保存到瀏覽器儲存區；LoginView 與 WebAPI 有敏感資料/回應 log；多個後台內容頁直接 v-html 顯示 CMS HTML。若內容或第三方腳本被植入 XSS，可讀取 token 並呼叫管理 API。</v>
       </c>
-      <c r="J182" s="4" t="str">
+      <c r="J182" s="3" t="str">
         <v>移除 token 與 API response console log；v-html 顯示前使用 DOMPurify 等白名單消毒；限制 TinyMCE 可輸入的危險屬性與 script；評估改短效 token/httpOnly cookie 或至少縮短保存時間。</v>
       </c>
-      <c r="K182" s="4" t="str">
+      <c r="K182" s="3" t="str">
         <v>後台登入、localStorage、v-html、TinyMCE</v>
       </c>
-      <c r="L182" s="4" t="str" xml:space="preserve">
+      <c r="L182" s="3" t="str" xml:space="preserve">
         <v xml:space="preserve">Dev/Dev Code/iFare_Admin/src/stores/user.ts
 Dev/Dev Code/iFare_Admin/src/views/LoginView.vue
 Dev/Dev Code/iFare_Admin/src/plugins/WebAPI.ts
 Dev/Dev Code/iFare_Admin/src/views/**/**/*View.vue</v>
       </c>
-      <c r="M182" s="4" t="str">
+      <c r="M182" s="3" t="str">
         <v>已讀程式碼：user store 使用 persist，LoginView 印出 token，WebAPI 印出 response，多處 detail view 直接 v-html。</v>
       </c>
-      <c r="N182" s="4" t="str">
+      <c r="N182" s="3" t="str">
         <v>待處理</v>
       </c>
-      <c r="O182" s="4" t="str">
-        <v/>
-      </c>
-      <c r="P182" s="4" t="str">
+      <c r="O182" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P182" s="3" t="str">
         <v>立即處理；與 API 權限不足會形成高風險攻擊鏈。</v>
       </c>
     </row>
     <row r="183" xml:space="preserve">
-      <c r="A183" s="4">
+      <c r="A183" s="3">
         <v>181</v>
       </c>
-      <c r="B183" s="4" t="str">
-        <v>V</v>
-      </c>
-      <c r="C183" s="4" t="str">
+      <c r="B183" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C183" s="3" t="str">
         <v>環境 / API 串接</v>
       </c>
-      <c r="D183" s="4" t="str">
+      <c r="D183" s="3" t="str">
         <v>URL 設定</v>
       </c>
-      <c r="E183" s="4" t="str">
+      <c r="E183" s="3" t="str">
         <v>修正</v>
       </c>
-      <c r="F183" s="4" t="str">
+      <c r="F183" s="3" t="str">
         <v>部署</v>
       </c>
-      <c r="G183" s="4" t="str">
+      <c r="G183" s="3" t="str">
         <v>高</v>
       </c>
-      <c r="H183" s="4" t="str">
+      <c r="H183" s="3" t="str">
         <v>API 與同步 URL 硬寫，開發可能打正式站、正式同步可能失效</v>
       </c>
-      <c r="I183" s="4" t="str">
+      <c r="I183" s="3" t="str">
         <v>後台 AjaxRef 固定指向正式 API URL；前台 PageBuilder 同步與上傳預設 localhost:3000。不同環境 build 時容易誤打正式資料或讓正式同步流程失效。</v>
       </c>
-      <c r="J183" s="4" t="str">
+      <c r="J183" s="3" t="str">
         <v>所有 base URL 改由 .env / runtime config / 部署變數注入；建立 dev/stage/prod 設定；build 或 deploy 時檢查必填環境變數，避免 fallback 到正式站或 localhost。</v>
       </c>
-      <c r="K183" s="4" t="str">
+      <c r="K183" s="3" t="str">
         <v>API base URL、PageBuilder、部署環境</v>
       </c>
-      <c r="L183" s="4" t="str" xml:space="preserve">
+      <c r="L183" s="3" t="str" xml:space="preserve">
         <v xml:space="preserve">Dev/Dev Code/iFare_Admin/src/plugins/AjaxRef.ts
 Dev/Dev Code/iFare_Frontend/components/PageBuilder.vue
 Dev/Dev Code/iFare_Frontend/utils/pageBuilderStorage.ts
 Dev/Dev Code/iFare_Frontend/utils/pageBuilderApi.ts</v>
       </c>
-      <c r="M183" s="4" t="str">
+      <c r="M183" s="3" t="str">
         <v>已讀程式碼：後台 API_HOST 指向正式站，前台同步/upload API 預設 localhost:3000。</v>
       </c>
-      <c r="N183" s="4" t="str">
-        <v>待處理</v>
-      </c>
-      <c r="O183" s="4" t="str">
-        <v/>
-      </c>
-      <c r="P183" s="4" t="str">
-        <v>立即處理；避免資料誤寫與部署後功能不可用。</v>
+      <c r="N183" s="3" t="str">
+        <v>部分修正</v>
+      </c>
+      <c r="O183" s="3" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="P183" s="3" t="str">
+        <v>2026-05-25 commit ae1c85a：iFare_Frontend 補 .env.example + nuxt.config runtime config (dynamicApiToken / dynamicApiAllowedOrigins)、iFare_Backend 補 .env.example。後台 src/plugins/AjaxRef.ts 仍硬寫正式 API URL 未處理。</v>
       </c>
     </row>
     <row r="184" xml:space="preserve">
-      <c r="A184" s="4">
+      <c r="A184" s="3">
         <v>182</v>
       </c>
-      <c r="B184" s="4" t="str">
-        <v>V</v>
-      </c>
-      <c r="C184" s="4" t="str">
+      <c r="B184" s="3" t="str">
+        <v>V</v>
+      </c>
+      <c r="C184" s="3" t="str">
         <v>工程流程</v>
       </c>
-      <c r="D184" s="4" t="str">
+      <c r="D184" s="3" t="str">
         <v>CI / 測試 / Repo</v>
       </c>
-      <c r="E184" s="4" t="str">
+      <c r="E184" s="3" t="str">
         <v>提升</v>
       </c>
-      <c r="F184" s="4" t="str">
+      <c r="F184" s="3" t="str">
         <v>品質</v>
       </c>
-      <c r="G184" s="4" t="str">
+      <c r="G184" s="3" t="str">
         <v>高</v>
       </c>
-      <c r="H184" s="4" t="str">
+      <c r="H184" s="3" t="str">
         <v>缺 CI 與測試覆蓋，且 repo 追蹤大量發佈產物</v>
       </c>
-      <c r="I184" s="4" t="str">
+      <c r="I184" s="3" t="str">
         <v>專案未看到 CI workflow；Vitest 目前找不到測試；本機也缺 dotnet CLI 導致 C# build 未能驗證；repo 內追蹤大量 Prd/Dev binary、DLL、PDB、EXE 與發佈輸出，會提高審查與部署風險。</v>
       </c>
-      <c r="J184" s="4" t="str">
+      <c r="J184" s="3" t="str">
         <v>新增 CI：前後台 npm build/type-check/audit、dotnet build/test；建立最小 API auth/permission/security tests；清理或移出發佈產物，改由 release artifact 或部署流程產生。</v>
       </c>
-      <c r="K184" s="4" t="str">
+      <c r="K184" s="3" t="str">
         <v>CI、測試、版控清理</v>
       </c>
-      <c r="L184" s="4" t="str" xml:space="preserve">
+      <c r="L184" s="3" t="str" xml:space="preserve">
         <v xml:space="preserve">.github/workflows
 Dev/Dev Code/iFare_Admin
 Dev/Dev Code/iFare_Frontend
 Dev/Dev Code/iFare_WebApi
 Prd/Prd Code</v>
       </c>
-      <c r="M184" s="4" t="str">
+      <c r="M184" s="3" t="str">
         <v>已執行盤點：npm build 可過；npm audit 無 high/critical；Vitest 無測試；dotnet 指令不存在，C# build 未驗證。</v>
       </c>
-      <c r="N184" s="4" t="str">
+      <c r="N184" s="3" t="str">
         <v>待處理</v>
       </c>
-      <c r="O184" s="4" t="str">
-        <v/>
-      </c>
-      <c r="P184" s="4" t="str">
+      <c r="O184" s="3" t="str">
+        <v/>
+      </c>
+      <c r="P184" s="3" t="str">
         <v>高優先級流程問題；會降低上述風險修復的可驗證性。</v>
       </c>
     </row>
@@ -15856,20 +16008,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H118"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="14.5546875"/>
-    <col min="2" max="2" customWidth="1" width="12.5546875"/>
-    <col min="3" max="3" customWidth="1" width="14.5546875"/>
-    <col min="4" max="4" customWidth="1" width="14.5546875"/>
-    <col min="5" max="5" customWidth="1" width="50.5546875"/>
-    <col min="6" max="6" customWidth="1" width="25.5546875"/>
-    <col min="7" max="7" customWidth="1" width="60.5546875"/>
-    <col min="8" max="8" customWidth="1" width="14.5546875"/>
+    <col min="1" max="1" width="14.5546875" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="50.5546875" customWidth="1"/>
+    <col min="6" max="6" width="25.5546875" customWidth="1"/>
+    <col min="7" max="7" width="60.5546875" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="str">
+      <c r="A1" s="4" t="str">
         <v>【1】整體進度</v>
       </c>
       <c r="B1" s="5" t="str">
@@ -15898,103 +16050,103 @@
       <c r="A2" s="6" t="str">
         <v>Sheet 名稱</v>
       </c>
-      <c r="B2" s="6" t="str">
+      <c r="B2" s="7" t="str">
         <v>總計</v>
       </c>
-      <c r="C2" s="6" t="str">
+      <c r="C2" s="7" t="str">
         <v>已修正</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="7" t="str">
         <v>部分修正</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" s="7" t="str">
         <v>待處理</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="F2" s="7" t="str">
         <v>完成率</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="7" t="str">
         <v>備註</v>
       </c>
-      <c r="H2" s="6" t="str">
+      <c r="H2" s="7" t="str">
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="str">
+      <c r="A3" s="8" t="str">
         <v>UIUX問題追蹤清單 (前台)</v>
       </c>
-      <c r="B3" s="3">
-        <v>174</v>
-      </c>
-      <c r="C3" s="7">
+      <c r="B3" s="9">
+        <v>182</v>
+      </c>
+      <c r="C3" s="10">
         <v>124</v>
       </c>
-      <c r="D3" s="8">
-        <v>19</v>
-      </c>
-      <c r="E3" s="9">
-        <v>31</v>
-      </c>
-      <c r="F3" s="3" t="str">
-        <v>71.3%</v>
-      </c>
-      <c r="G3" s="3" t="str">
+      <c r="D3" s="11">
+        <v>24</v>
+      </c>
+      <c r="E3" s="12">
+        <v>34</v>
+      </c>
+      <c r="F3" s="9" t="str">
+        <v>68.1%</v>
+      </c>
+      <c r="G3" s="8" t="str">
         <v>已歷經 Round 1-4 改版</v>
       </c>
-      <c r="H3" s="3" t="str">
+      <c r="H3" s="8" t="str">
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="str">
+      <c r="A4" s="8" t="str">
         <v>後臺優化 (admin)</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="9">
         <v>100</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="13">
         <v>18</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="14">
         <v>16</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="15">
         <v>66</v>
       </c>
-      <c r="F4" s="3" t="str">
+      <c r="F4" s="9" t="str">
         <v>18.0%</v>
       </c>
-      <c r="G4" s="3" t="str">
+      <c r="G4" s="8" t="str">
         <v>含後台優化規劃與進階功能建議</v>
       </c>
-      <c r="H4" s="3" t="str">
+      <c r="H4" s="8" t="str">
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="str">
+      <c r="A5" s="8" t="str">
         <v>PoC研究</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="9">
         <v>13</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="13">
         <v>0</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="14">
         <v>0</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="15">
         <v>13</v>
       </c>
-      <c r="F5" s="3" t="str">
+      <c r="F5" s="9" t="str">
         <v>0.0%</v>
       </c>
-      <c r="G5" s="3" t="str">
+      <c r="G5" s="8" t="str">
         <v>研究方向，未啟動</v>
       </c>
-      <c r="H5" s="3" t="str">
+      <c r="H5" s="8" t="str">
         <v/>
       </c>
     </row>
@@ -16025,2297 +16177,2739 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="str">
+      <c r="A8" s="7" t="str">
         <v>Round</v>
       </c>
-      <c r="B8" s="6" t="str">
+      <c r="B8" s="7" t="str">
         <v>日期</v>
       </c>
-      <c r="C8" s="6" t="str">
+      <c r="C8" s="7" t="str">
         <v>主題</v>
       </c>
-      <c r="D8" s="6" t="str">
+      <c r="D8" s="7" t="str">
         <v>UIUX 標完成</v>
       </c>
-      <c r="E8" s="6" t="str">
+      <c r="E8" s="7" t="str">
         <v>UIUX 新增</v>
       </c>
-      <c r="F8" s="6" t="str">
+      <c r="F8" s="7" t="str">
         <v>後臺新增</v>
       </c>
-      <c r="G8" s="6" t="str">
+      <c r="G8" s="7" t="str">
         <v>Schema</v>
       </c>
-      <c r="H8" s="6" t="str">
+      <c r="H8" s="7" t="str">
         <v>主要產出</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="str">
+      <c r="A9" s="8" t="str">
         <v>Round 1</v>
       </c>
-      <c r="B9" s="3" t="str">
+      <c r="B9" s="8" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="C9" s="3" t="str">
+      <c r="C9" s="8" t="str">
         <v>UI/UX 改版 (搜尋 / Footer / 全站動畫 / RWD)</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="9">
         <v>7</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="9">
         <v>3</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="9">
         <v>0</v>
       </c>
-      <c r="G9" s="3" t="str">
+      <c r="G9" s="8" t="str">
         <v>-</v>
       </c>
-      <c r="H9" s="3" t="str">
+      <c r="H9" s="8" t="str">
         <v>pages/ifare 加關鍵字搜尋 + URL query 初始化；全站 NuxtPage transition；卡片/按鈕 hover translateY</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="str">
+      <c r="A10" s="8" t="str">
         <v>Round 2</v>
       </c>
-      <c r="B10" s="3" t="str">
+      <c r="B10" s="8" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="C10" s="3" t="str">
+      <c r="C10" s="8" t="str">
         <v>Footer 整理 + RWD 修正</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="9">
         <v>2</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="9">
         <v>2</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="9">
         <v>0</v>
       </c>
-      <c r="G10" s="3" t="str">
+      <c r="G10" s="8" t="str">
         <v>-</v>
       </c>
-      <c r="H10" s="3" t="str">
+      <c r="H10" s="8" t="str">
         <v>LINE/FB 統一 .btn-social 並排；4 個聯絡資訊加 icon (Tel/Mail/Address/Clock)；footer 觸控 44px</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="str">
+      <c r="A11" s="8" t="str">
         <v>Round 3</v>
       </c>
-      <c r="B11" s="3" t="str">
+      <c r="B11" s="8" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="C11" s="3" t="str">
+      <c r="C11" s="8" t="str">
         <v>About 靈動島 + News 卡片升級 + 社群外連結</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="9">
         <v>4</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="9">
         <v>5</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="9">
         <v>0</v>
       </c>
-      <c r="G11" s="3" t="str">
+      <c r="G11" s="8" t="str">
         <v>-</v>
       </c>
-      <c r="H11" s="3" t="str">
+      <c r="H11" s="8" t="str">
         <v>About 三大核心 morph 卡 (cf47cfa)；News 浮起卡 + stagger fade-up + NEW pill；外連結 target="_blank" rel="noopener"</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="str">
+      <c r="A12" s="8" t="str">
         <v>Round 4</v>
       </c>
-      <c r="B12" s="3" t="str">
+      <c r="B12" s="8" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="C12" s="3" t="str">
+      <c r="C12" s="8" t="str">
         <v>切回 master + 開新分支 feat/uiux-round4 + 補做 (環境/補回/新功能)</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="9">
         <v>0</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="9">
         <v>8</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="9">
         <v>4</v>
       </c>
-      <c r="G12" s="3" t="str">
+      <c r="G12" s="8" t="str">
         <v>-</v>
       </c>
-      <c r="H12" s="3" t="str">
+      <c r="H12" s="8" t="str">
         <v>cf47cfa+5dfbf91 補回 16 檔；devProxy/baseURL → 正式 API；nav 加未來規劃 + future.vue；News videoUrl wiring；tsconfig deprecation 清理；about hover bug 修；footer label 重複修</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="str">
+      <c r="A13" s="8" t="str">
         <v>Round 5</v>
       </c>
-      <c r="B13" s="3" t="str">
+      <c r="B13" s="8" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="C13" s="3" t="str">
+      <c r="C13" s="8" t="str">
         <v>前後台全面審查 — 後台 UX audit + 前台新 issue 掃描</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="9">
         <v>0</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="9">
         <v>26</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="9">
         <v>22</v>
       </c>
-      <c r="G13" s="3" t="str">
+      <c r="G13" s="8" t="str">
         <v>-</v>
       </c>
-      <c r="H13" s="3" t="str">
+      <c r="H13" s="8" t="str">
         <v>後台 22 個工程角度問題 (CRUD/驗證/錯誤處理)；前台 26 個新發現 (XSS/超時/console.log/無障礙/分頁元件重複)</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="str">
+      <c r="A14" s="8" t="str">
         <v>Round 6</v>
       </c>
-      <c r="B14" s="3" t="str">
+      <c r="B14" s="8" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="C14" s="3" t="str">
+      <c r="C14" s="8" t="str">
         <v>人性化主軸提案 — 5 主軸 + 16 後台項</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="9">
         <v>0</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="9